--- a/Customer Rate Tariff Template_Week 33_2026.xlsx
+++ b/Customer Rate Tariff Template_Week 33_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stephanie.galera.RAMPSLOGISTICS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC35440-D9CA-4084-A187-3751ED310E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E222F8-5DF3-42AC-A47C-88BC61611122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
   </bookViews>
   <sheets>
     <sheet name="TT" sheetId="28" r:id="rId1"/>
@@ -1730,7 +1730,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="369">
+  <cellXfs count="361">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2224,25 +2224,16 @@
     <xf numFmtId="8" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2251,13 +2242,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2278,10 +2263,28 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2292,6 +2295,135 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2323,131 +2455,56 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2485,69 +2542,68 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2561,71 +2617,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2651,38 +2642,23 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4143,23 +4119,23 @@
       <c r="P7" s="18"/>
     </row>
     <row r="8" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="219" t="s">
+      <c r="B8" s="216" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="219"/>
-      <c r="D8" s="219"/>
-      <c r="E8" s="219"/>
-      <c r="F8" s="219"/>
-      <c r="G8" s="219"/>
-      <c r="H8" s="219"/>
-      <c r="I8" s="219"/>
-      <c r="J8" s="219"/>
-      <c r="K8" s="219"/>
-      <c r="L8" s="219"/>
-      <c r="M8" s="219"/>
-      <c r="N8" s="219"/>
-      <c r="O8" s="219"/>
-      <c r="P8" s="219"/>
+      <c r="C8" s="216"/>
+      <c r="D8" s="216"/>
+      <c r="E8" s="216"/>
+      <c r="F8" s="216"/>
+      <c r="G8" s="216"/>
+      <c r="H8" s="216"/>
+      <c r="I8" s="216"/>
+      <c r="J8" s="216"/>
+      <c r="K8" s="216"/>
+      <c r="L8" s="216"/>
+      <c r="M8" s="216"/>
+      <c r="N8" s="216"/>
+      <c r="O8" s="216"/>
+      <c r="P8" s="216"/>
     </row>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
@@ -4207,10 +4183,10 @@
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="279" t="s">
+      <c r="B10" s="235" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="279" t="s">
+      <c r="C10" s="235" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="20" t="s">
@@ -4256,8 +4232,8 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="280"/>
-      <c r="C11" s="280"/>
+      <c r="B11" s="236"/>
+      <c r="C11" s="236"/>
       <c r="D11" s="20" t="s">
         <v>22</v>
       </c>
@@ -4301,8 +4277,8 @@
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="280"/>
-      <c r="C12" s="279" t="s">
+      <c r="B12" s="236"/>
+      <c r="C12" s="235" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="111" t="s">
@@ -4349,8 +4325,8 @@
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="280"/>
-      <c r="C13" s="280"/>
+      <c r="B13" s="236"/>
+      <c r="C13" s="236"/>
       <c r="D13" s="111" t="s">
         <v>22</v>
       </c>
@@ -4396,10 +4372,10 @@
       <c r="Q13" s="26"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="281" t="s">
+      <c r="B14" s="237" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="244" t="s">
+      <c r="C14" s="239" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="20" t="s">
@@ -4446,8 +4422,8 @@
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="282"/>
-      <c r="C15" s="244"/>
+      <c r="B15" s="238"/>
+      <c r="C15" s="239"/>
       <c r="D15" s="20" t="s">
         <v>22</v>
       </c>
@@ -4492,10 +4468,10 @@
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="281" t="s">
+      <c r="B16" s="237" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="281" t="s">
+      <c r="C16" s="237" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="20" t="s">
@@ -4542,8 +4518,8 @@
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B17" s="282"/>
-      <c r="C17" s="282"/>
+      <c r="B17" s="238"/>
+      <c r="C17" s="238"/>
       <c r="D17" s="20" t="s">
         <v>22</v>
       </c>
@@ -4588,10 +4564,10 @@
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="281" t="s">
+      <c r="B18" s="237" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="239" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -4639,8 +4615,8 @@
       <c r="Q18" s="26"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="285"/>
-      <c r="C19" s="244"/>
+      <c r="B19" s="247"/>
+      <c r="C19" s="239"/>
       <c r="D19" s="20" t="s">
         <v>22</v>
       </c>
@@ -4686,8 +4662,8 @@
       <c r="Q19" s="26"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="285"/>
-      <c r="C20" s="244" t="s">
+      <c r="B20" s="247"/>
+      <c r="C20" s="239" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="20" t="s">
@@ -4734,8 +4710,8 @@
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="282"/>
-      <c r="C21" s="244"/>
+      <c r="B21" s="238"/>
+      <c r="C21" s="239"/>
       <c r="D21" s="20" t="s">
         <v>22</v>
       </c>
@@ -4817,74 +4793,74 @@
       <c r="P23" s="186"/>
     </row>
     <row r="24" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="276" t="s">
+      <c r="B24" s="250" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="276"/>
-      <c r="D24" s="276"/>
-      <c r="E24" s="276"/>
-      <c r="F24" s="276"/>
-      <c r="G24" s="276"/>
-      <c r="H24" s="276"/>
-      <c r="I24" s="276"/>
-      <c r="J24" s="276"/>
-      <c r="K24" s="276"/>
-      <c r="L24" s="276"/>
-      <c r="M24" s="276"/>
-      <c r="N24" s="276"/>
-      <c r="O24" s="276"/>
-      <c r="P24" s="276"/>
+      <c r="C24" s="250"/>
+      <c r="D24" s="250"/>
+      <c r="E24" s="250"/>
+      <c r="F24" s="250"/>
+      <c r="G24" s="250"/>
+      <c r="H24" s="250"/>
+      <c r="I24" s="250"/>
+      <c r="J24" s="250"/>
+      <c r="K24" s="250"/>
+      <c r="L24" s="250"/>
+      <c r="M24" s="250"/>
+      <c r="N24" s="250"/>
+      <c r="O24" s="250"/>
+      <c r="P24" s="250"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B25" s="276"/>
-      <c r="C25" s="276"/>
-      <c r="D25" s="276"/>
-      <c r="E25" s="276"/>
-      <c r="F25" s="276"/>
-      <c r="G25" s="276"/>
-      <c r="H25" s="276"/>
-      <c r="I25" s="276"/>
-      <c r="J25" s="276"/>
-      <c r="K25" s="276"/>
-      <c r="L25" s="276"/>
-      <c r="M25" s="276"/>
-      <c r="N25" s="276"/>
-      <c r="O25" s="276"/>
-      <c r="P25" s="276"/>
+      <c r="B25" s="250"/>
+      <c r="C25" s="250"/>
+      <c r="D25" s="250"/>
+      <c r="E25" s="250"/>
+      <c r="F25" s="250"/>
+      <c r="G25" s="250"/>
+      <c r="H25" s="250"/>
+      <c r="I25" s="250"/>
+      <c r="J25" s="250"/>
+      <c r="K25" s="250"/>
+      <c r="L25" s="250"/>
+      <c r="M25" s="250"/>
+      <c r="N25" s="250"/>
+      <c r="O25" s="250"/>
+      <c r="P25" s="250"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B26" s="276"/>
-      <c r="C26" s="276"/>
-      <c r="D26" s="276"/>
-      <c r="E26" s="276"/>
-      <c r="F26" s="276"/>
-      <c r="G26" s="276"/>
-      <c r="H26" s="276"/>
-      <c r="I26" s="276"/>
-      <c r="J26" s="276"/>
-      <c r="K26" s="276"/>
-      <c r="L26" s="276"/>
-      <c r="M26" s="276"/>
-      <c r="N26" s="276"/>
-      <c r="O26" s="276"/>
-      <c r="P26" s="276"/>
+      <c r="B26" s="250"/>
+      <c r="C26" s="250"/>
+      <c r="D26" s="250"/>
+      <c r="E26" s="250"/>
+      <c r="F26" s="250"/>
+      <c r="G26" s="250"/>
+      <c r="H26" s="250"/>
+      <c r="I26" s="250"/>
+      <c r="J26" s="250"/>
+      <c r="K26" s="250"/>
+      <c r="L26" s="250"/>
+      <c r="M26" s="250"/>
+      <c r="N26" s="250"/>
+      <c r="O26" s="250"/>
+      <c r="P26" s="250"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B27" s="276"/>
-      <c r="C27" s="276"/>
-      <c r="D27" s="276"/>
-      <c r="E27" s="276"/>
-      <c r="F27" s="276"/>
-      <c r="G27" s="276"/>
-      <c r="H27" s="276"/>
-      <c r="I27" s="276"/>
-      <c r="J27" s="276"/>
-      <c r="K27" s="276"/>
-      <c r="L27" s="276"/>
-      <c r="M27" s="276"/>
-      <c r="N27" s="276"/>
-      <c r="O27" s="276"/>
-      <c r="P27" s="276"/>
+      <c r="B27" s="250"/>
+      <c r="C27" s="250"/>
+      <c r="D27" s="250"/>
+      <c r="E27" s="250"/>
+      <c r="F27" s="250"/>
+      <c r="G27" s="250"/>
+      <c r="H27" s="250"/>
+      <c r="I27" s="250"/>
+      <c r="J27" s="250"/>
+      <c r="K27" s="250"/>
+      <c r="L27" s="250"/>
+      <c r="M27" s="250"/>
+      <c r="N27" s="250"/>
+      <c r="O27" s="250"/>
+      <c r="P27" s="250"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B28" s="35"/>
@@ -5013,23 +4989,23 @@
       <c r="Q34" s="28"/>
     </row>
     <row r="35" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="283" t="s">
+      <c r="B35" s="240" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="230"/>
-      <c r="D35" s="230"/>
-      <c r="E35" s="230"/>
-      <c r="F35" s="230"/>
-      <c r="G35" s="230"/>
-      <c r="H35" s="230"/>
-      <c r="I35" s="230"/>
-      <c r="J35" s="230"/>
-      <c r="K35" s="230"/>
-      <c r="L35" s="230"/>
-      <c r="M35" s="230"/>
-      <c r="N35" s="230"/>
-      <c r="O35" s="230"/>
-      <c r="P35" s="230"/>
+      <c r="C35" s="213"/>
+      <c r="D35" s="213"/>
+      <c r="E35" s="213"/>
+      <c r="F35" s="213"/>
+      <c r="G35" s="213"/>
+      <c r="H35" s="213"/>
+      <c r="I35" s="213"/>
+      <c r="J35" s="213"/>
+      <c r="K35" s="213"/>
+      <c r="L35" s="213"/>
+      <c r="M35" s="213"/>
+      <c r="N35" s="213"/>
+      <c r="O35" s="213"/>
+      <c r="P35" s="213"/>
     </row>
     <row r="36" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B36" s="120" t="s">
@@ -5075,7 +5051,7 @@
       <c r="P36" s="217"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B37" s="284" t="s">
+      <c r="B37" s="241" t="s">
         <v>37</v>
       </c>
       <c r="C37" s="136" t="s">
@@ -5117,13 +5093,13 @@
       <c r="N37" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O37" s="266" t="s">
+      <c r="O37" s="242" t="s">
         <v>40</v>
       </c>
-      <c r="P37" s="267"/>
+      <c r="P37" s="243"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B38" s="284"/>
+      <c r="B38" s="241"/>
       <c r="C38" s="136" t="s">
         <v>16</v>
       </c>
@@ -5163,8 +5139,8 @@
       <c r="N38" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O38" s="268"/>
-      <c r="P38" s="269"/>
+      <c r="O38" s="244"/>
+      <c r="P38" s="245"/>
     </row>
     <row r="39" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="187" t="s">
@@ -5177,7 +5153,7 @@
         <v>17</v>
       </c>
       <c r="E39" s="210">
-        <v>3545</v>
+        <v>3395</v>
       </c>
       <c r="F39" s="22">
         <v>355</v>
@@ -5190,14 +5166,14 @@
       </c>
       <c r="I39" s="39">
         <f>SUM(E39:H39)</f>
-        <v>4006.5</v>
+        <v>3856.5</v>
       </c>
       <c r="J39" s="24">
         <v>200</v>
       </c>
       <c r="K39" s="23">
         <f>I39+J39</f>
-        <v>4206.5</v>
+        <v>4056.5</v>
       </c>
       <c r="L39" s="40" t="s">
         <v>42</v>
@@ -5208,10 +5184,10 @@
       <c r="N39" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="O39" s="245" t="s">
+      <c r="O39" s="246" t="s">
         <v>44</v>
       </c>
-      <c r="P39" s="245"/>
+      <c r="P39" s="246"/>
     </row>
     <row r="40" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="187" t="s">
@@ -5256,10 +5232,10 @@
       <c r="N40" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O40" s="245" t="s">
+      <c r="O40" s="246" t="s">
         <v>44</v>
       </c>
-      <c r="P40" s="245"/>
+      <c r="P40" s="246"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B41" s="42"/>
@@ -5300,78 +5276,78 @@
       <c r="Q42" s="7"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B43" s="211" t="s">
+      <c r="B43" s="224" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="212"/>
-      <c r="D43" s="212"/>
-      <c r="E43" s="212"/>
-      <c r="F43" s="212"/>
-      <c r="G43" s="212"/>
-      <c r="H43" s="212"/>
-      <c r="I43" s="212"/>
-      <c r="J43" s="212"/>
-      <c r="K43" s="212"/>
-      <c r="L43" s="212"/>
-      <c r="M43" s="212"/>
-      <c r="N43" s="212"/>
-      <c r="O43" s="212"/>
-      <c r="P43" s="212"/>
-      <c r="Q43" s="213"/>
+      <c r="C43" s="225"/>
+      <c r="D43" s="225"/>
+      <c r="E43" s="225"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="225"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="225"/>
+      <c r="K43" s="225"/>
+      <c r="L43" s="225"/>
+      <c r="M43" s="225"/>
+      <c r="N43" s="225"/>
+      <c r="O43" s="225"/>
+      <c r="P43" s="225"/>
+      <c r="Q43" s="226"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B44" s="211"/>
-      <c r="C44" s="212"/>
-      <c r="D44" s="212"/>
-      <c r="E44" s="212"/>
-      <c r="F44" s="212"/>
-      <c r="G44" s="212"/>
-      <c r="H44" s="212"/>
-      <c r="I44" s="212"/>
-      <c r="J44" s="212"/>
-      <c r="K44" s="212"/>
-      <c r="L44" s="212"/>
-      <c r="M44" s="212"/>
-      <c r="N44" s="212"/>
-      <c r="O44" s="212"/>
-      <c r="P44" s="212"/>
-      <c r="Q44" s="213"/>
+      <c r="B44" s="224"/>
+      <c r="C44" s="225"/>
+      <c r="D44" s="225"/>
+      <c r="E44" s="225"/>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="225"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="225"/>
+      <c r="K44" s="225"/>
+      <c r="L44" s="225"/>
+      <c r="M44" s="225"/>
+      <c r="N44" s="225"/>
+      <c r="O44" s="225"/>
+      <c r="P44" s="225"/>
+      <c r="Q44" s="226"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B45" s="211"/>
-      <c r="C45" s="212"/>
-      <c r="D45" s="212"/>
-      <c r="E45" s="212"/>
-      <c r="F45" s="212"/>
-      <c r="G45" s="212"/>
-      <c r="H45" s="212"/>
-      <c r="I45" s="212"/>
-      <c r="J45" s="212"/>
-      <c r="K45" s="212"/>
-      <c r="L45" s="212"/>
-      <c r="M45" s="212"/>
-      <c r="N45" s="212"/>
-      <c r="O45" s="212"/>
-      <c r="P45" s="212"/>
-      <c r="Q45" s="213"/>
+      <c r="B45" s="224"/>
+      <c r="C45" s="225"/>
+      <c r="D45" s="225"/>
+      <c r="E45" s="225"/>
+      <c r="F45" s="225"/>
+      <c r="G45" s="225"/>
+      <c r="H45" s="225"/>
+      <c r="I45" s="225"/>
+      <c r="J45" s="225"/>
+      <c r="K45" s="225"/>
+      <c r="L45" s="225"/>
+      <c r="M45" s="225"/>
+      <c r="N45" s="225"/>
+      <c r="O45" s="225"/>
+      <c r="P45" s="225"/>
+      <c r="Q45" s="226"/>
     </row>
     <row r="46" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B46" s="214"/>
-      <c r="C46" s="215"/>
-      <c r="D46" s="215"/>
-      <c r="E46" s="215"/>
-      <c r="F46" s="215"/>
-      <c r="G46" s="215"/>
-      <c r="H46" s="215"/>
-      <c r="I46" s="215"/>
-      <c r="J46" s="215"/>
-      <c r="K46" s="215"/>
-      <c r="L46" s="215"/>
-      <c r="M46" s="215"/>
-      <c r="N46" s="215"/>
-      <c r="O46" s="215"/>
-      <c r="P46" s="215"/>
-      <c r="Q46" s="216"/>
+      <c r="B46" s="227"/>
+      <c r="C46" s="228"/>
+      <c r="D46" s="228"/>
+      <c r="E46" s="228"/>
+      <c r="F46" s="228"/>
+      <c r="G46" s="228"/>
+      <c r="H46" s="228"/>
+      <c r="I46" s="228"/>
+      <c r="J46" s="228"/>
+      <c r="K46" s="228"/>
+      <c r="L46" s="228"/>
+      <c r="M46" s="228"/>
+      <c r="N46" s="228"/>
+      <c r="O46" s="228"/>
+      <c r="P46" s="228"/>
+      <c r="Q46" s="229"/>
     </row>
     <row r="47" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B47" s="35"/>
@@ -5537,26 +5513,26 @@
       <c r="R55" s="28"/>
     </row>
     <row r="56" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B56" s="231" t="s">
+      <c r="B56" s="232" t="s">
         <v>46</v>
       </c>
-      <c r="C56" s="232"/>
-      <c r="D56" s="232"/>
-      <c r="E56" s="232"/>
-      <c r="F56" s="232"/>
-      <c r="G56" s="232"/>
-      <c r="H56" s="232"/>
-      <c r="I56" s="232"/>
-      <c r="J56" s="232"/>
-      <c r="K56" s="232"/>
-      <c r="L56" s="232"/>
-      <c r="M56" s="232"/>
-      <c r="N56" s="232"/>
-      <c r="O56" s="232"/>
-      <c r="P56" s="232"/>
-      <c r="Q56" s="232"/>
-      <c r="R56" s="232"/>
-      <c r="S56" s="246"/>
+      <c r="C56" s="233"/>
+      <c r="D56" s="233"/>
+      <c r="E56" s="233"/>
+      <c r="F56" s="233"/>
+      <c r="G56" s="233"/>
+      <c r="H56" s="233"/>
+      <c r="I56" s="233"/>
+      <c r="J56" s="233"/>
+      <c r="K56" s="233"/>
+      <c r="L56" s="233"/>
+      <c r="M56" s="233"/>
+      <c r="N56" s="233"/>
+      <c r="O56" s="233"/>
+      <c r="P56" s="233"/>
+      <c r="Q56" s="233"/>
+      <c r="R56" s="233"/>
+      <c r="S56" s="251"/>
     </row>
     <row r="57" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
@@ -5605,16 +5581,16 @@
       <c r="Q57" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R57" s="277" t="s">
+      <c r="R57" s="252" t="s">
         <v>36</v>
       </c>
-      <c r="S57" s="278"/>
+      <c r="S57" s="253"/>
     </row>
     <row r="58" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="250" t="s">
+      <c r="B58" s="248" t="s">
         <v>51</v>
       </c>
-      <c r="C58" s="251" t="s">
+      <c r="C58" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D58" s="137" t="s">
@@ -5662,14 +5638,14 @@
       <c r="Q58" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R58" s="252" t="s">
+      <c r="R58" s="254" t="s">
         <v>55</v>
       </c>
-      <c r="S58" s="253"/>
+      <c r="S58" s="255"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B59" s="250"/>
-      <c r="C59" s="251"/>
+      <c r="B59" s="248"/>
+      <c r="C59" s="249"/>
       <c r="D59" s="137" t="s">
         <v>22</v>
       </c>
@@ -5715,14 +5691,14 @@
       <c r="Q59" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R59" s="254"/>
-      <c r="S59" s="255"/>
+      <c r="R59" s="256"/>
+      <c r="S59" s="257"/>
     </row>
     <row r="60" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="250" t="s">
+      <c r="B60" s="248" t="s">
         <v>56</v>
       </c>
-      <c r="C60" s="251" t="s">
+      <c r="C60" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="137" t="s">
@@ -5770,12 +5746,12 @@
       <c r="Q60" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R60" s="254"/>
-      <c r="S60" s="255"/>
+      <c r="R60" s="256"/>
+      <c r="S60" s="257"/>
     </row>
     <row r="61" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B61" s="250"/>
-      <c r="C61" s="251"/>
+      <c r="B61" s="248"/>
+      <c r="C61" s="249"/>
       <c r="D61" s="137" t="s">
         <v>22</v>
       </c>
@@ -5821,14 +5797,14 @@
       <c r="Q61" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R61" s="262"/>
-      <c r="S61" s="263"/>
+      <c r="R61" s="258"/>
+      <c r="S61" s="259"/>
     </row>
     <row r="62" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="264" t="s">
+      <c r="B62" s="265" t="s">
         <v>57</v>
       </c>
-      <c r="C62" s="223" t="s">
+      <c r="C62" s="218" t="s">
         <v>29</v>
       </c>
       <c r="D62" s="117" t="s">
@@ -5876,14 +5852,14 @@
       <c r="Q62" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="R62" s="266" t="s">
+      <c r="R62" s="242" t="s">
         <v>59</v>
       </c>
-      <c r="S62" s="267"/>
+      <c r="S62" s="243"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B63" s="265"/>
-      <c r="C63" s="224"/>
+      <c r="B63" s="266"/>
+      <c r="C63" s="219"/>
       <c r="D63" s="117" t="s">
         <v>22</v>
       </c>
@@ -5929,14 +5905,14 @@
       <c r="Q63" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="R63" s="268"/>
-      <c r="S63" s="269"/>
+      <c r="R63" s="244"/>
+      <c r="S63" s="245"/>
     </row>
     <row r="64" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="250" t="s">
+      <c r="B64" s="248" t="s">
         <v>60</v>
       </c>
-      <c r="C64" s="251" t="s">
+      <c r="C64" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D64" s="137" t="s">
@@ -5984,14 +5960,14 @@
       <c r="Q64" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R64" s="252" t="s">
+      <c r="R64" s="254" t="s">
         <v>55</v>
       </c>
-      <c r="S64" s="253"/>
+      <c r="S64" s="255"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B65" s="250"/>
-      <c r="C65" s="251"/>
+      <c r="B65" s="248"/>
+      <c r="C65" s="249"/>
       <c r="D65" s="137" t="s">
         <v>22</v>
       </c>
@@ -6037,20 +6013,20 @@
       <c r="Q65" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R65" s="254"/>
-      <c r="S65" s="255"/>
+      <c r="R65" s="256"/>
+      <c r="S65" s="257"/>
     </row>
     <row r="66" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="359" t="s">
+      <c r="B66" s="269" t="s">
         <v>61</v>
       </c>
-      <c r="C66" s="360" t="s">
+      <c r="C66" s="267" t="s">
         <v>29</v>
       </c>
-      <c r="D66" s="361" t="s">
+      <c r="D66" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="E66" s="362">
+      <c r="E66" s="138">
         <f>CEILING(((7790+115+289)*1.12)-439,50)</f>
         <v>8750</v>
       </c>
@@ -6083,27 +6059,27 @@
         <f t="shared" si="3"/>
         <v>9528.3799999999992</v>
       </c>
-      <c r="O66" s="363" t="s">
+      <c r="O66" s="140" t="s">
         <v>53</v>
       </c>
-      <c r="P66" s="364" t="s">
+      <c r="P66" s="204" t="s">
         <v>54</v>
       </c>
-      <c r="Q66" s="363" t="s">
+      <c r="Q66" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="R66" s="266" t="s">
+      <c r="R66" s="242" t="s">
         <v>59</v>
       </c>
-      <c r="S66" s="267"/>
+      <c r="S66" s="243"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B67" s="365"/>
-      <c r="C67" s="366"/>
-      <c r="D67" s="361" t="s">
-        <v>22</v>
-      </c>
-      <c r="E67" s="362">
+      <c r="B67" s="270"/>
+      <c r="C67" s="268"/>
+      <c r="D67" s="137" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" s="138">
         <f>CEILING(((7980+115+289)*1.12)-439,50)</f>
         <v>9000</v>
       </c>
@@ -6136,23 +6112,23 @@
         <f t="shared" si="3"/>
         <v>9778.3799999999992</v>
       </c>
-      <c r="O67" s="363" t="s">
+      <c r="O67" s="140" t="s">
         <v>53</v>
       </c>
-      <c r="P67" s="364" t="s">
+      <c r="P67" s="204" t="s">
         <v>54</v>
       </c>
-      <c r="Q67" s="363" t="s">
+      <c r="Q67" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="R67" s="268"/>
-      <c r="S67" s="269"/>
+      <c r="R67" s="244"/>
+      <c r="S67" s="245"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B68" s="270" t="s">
+      <c r="B68" s="269" t="s">
         <v>62</v>
       </c>
-      <c r="C68" s="251" t="s">
+      <c r="C68" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D68" s="137" t="s">
@@ -6200,14 +6176,14 @@
       <c r="Q68" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R68" s="252" t="s">
+      <c r="R68" s="254" t="s">
         <v>55</v>
       </c>
-      <c r="S68" s="253"/>
+      <c r="S68" s="255"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B69" s="271"/>
-      <c r="C69" s="251"/>
+      <c r="B69" s="270"/>
+      <c r="C69" s="249"/>
       <c r="D69" s="137" t="s">
         <v>22</v>
       </c>
@@ -6253,14 +6229,14 @@
       <c r="Q69" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R69" s="254"/>
-      <c r="S69" s="255"/>
+      <c r="R69" s="256"/>
+      <c r="S69" s="257"/>
     </row>
     <row r="70" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="250" t="s">
+      <c r="B70" s="248" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="251" t="s">
+      <c r="C70" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D70" s="137" t="s">
@@ -6308,12 +6284,12 @@
       <c r="Q70" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R70" s="254"/>
-      <c r="S70" s="255"/>
+      <c r="R70" s="256"/>
+      <c r="S70" s="257"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B71" s="250"/>
-      <c r="C71" s="251"/>
+      <c r="B71" s="248"/>
+      <c r="C71" s="249"/>
       <c r="D71" s="137" t="s">
         <v>22</v>
       </c>
@@ -6359,20 +6335,20 @@
       <c r="Q71" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R71" s="262"/>
-      <c r="S71" s="263"/>
+      <c r="R71" s="258"/>
+      <c r="S71" s="259"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B72" s="367" t="s">
+      <c r="B72" s="248" t="s">
         <v>64</v>
       </c>
-      <c r="C72" s="360" t="s">
+      <c r="C72" s="267" t="s">
         <v>29</v>
       </c>
-      <c r="D72" s="361" t="s">
+      <c r="D72" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="E72" s="362">
+      <c r="E72" s="138">
         <f>CEILING(((7700+115+340)*1.12)-490,50)</f>
         <v>8650</v>
       </c>
@@ -6405,27 +6381,27 @@
         <f t="shared" si="3"/>
         <v>9492.8700000000008</v>
       </c>
-      <c r="O72" s="363" t="s">
+      <c r="O72" s="140" t="s">
         <v>53</v>
       </c>
-      <c r="P72" s="364" t="s">
+      <c r="P72" s="204" t="s">
         <v>54</v>
       </c>
-      <c r="Q72" s="368" t="s">
+      <c r="Q72" s="211" t="s">
         <v>65</v>
       </c>
-      <c r="R72" s="257" t="s">
+      <c r="R72" s="261" t="s">
         <v>66</v>
       </c>
-      <c r="S72" s="258"/>
+      <c r="S72" s="262"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B73" s="367"/>
-      <c r="C73" s="366"/>
-      <c r="D73" s="361" t="s">
-        <v>22</v>
-      </c>
-      <c r="E73" s="362">
+      <c r="B73" s="248"/>
+      <c r="C73" s="268"/>
+      <c r="D73" s="137" t="s">
+        <v>22</v>
+      </c>
+      <c r="E73" s="138">
         <f>CEILING(((7800+115+340)*1.12)-490,50)</f>
         <v>8800</v>
       </c>
@@ -6458,23 +6434,23 @@
         <f t="shared" si="3"/>
         <v>9642.8700000000008</v>
       </c>
-      <c r="O73" s="363" t="s">
+      <c r="O73" s="140" t="s">
         <v>53</v>
       </c>
-      <c r="P73" s="364" t="s">
+      <c r="P73" s="204" t="s">
         <v>54</v>
       </c>
-      <c r="Q73" s="368" t="s">
+      <c r="Q73" s="211" t="s">
         <v>65</v>
       </c>
-      <c r="R73" s="259"/>
-      <c r="S73" s="260"/>
+      <c r="R73" s="263"/>
+      <c r="S73" s="264"/>
     </row>
     <row r="74" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="250" t="s">
+      <c r="B74" s="248" t="s">
         <v>67</v>
       </c>
-      <c r="C74" s="251" t="s">
+      <c r="C74" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D74" s="137" t="s">
@@ -6522,14 +6498,14 @@
       <c r="Q74" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R74" s="252" t="s">
+      <c r="R74" s="254" t="s">
         <v>55</v>
       </c>
-      <c r="S74" s="253"/>
+      <c r="S74" s="255"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B75" s="250"/>
-      <c r="C75" s="251"/>
+      <c r="B75" s="248"/>
+      <c r="C75" s="249"/>
       <c r="D75" s="137" t="s">
         <v>22</v>
       </c>
@@ -6575,14 +6551,14 @@
       <c r="Q75" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R75" s="254"/>
-      <c r="S75" s="255"/>
+      <c r="R75" s="256"/>
+      <c r="S75" s="257"/>
     </row>
     <row r="76" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="250" t="s">
+      <c r="B76" s="248" t="s">
         <v>68</v>
       </c>
-      <c r="C76" s="251" t="s">
+      <c r="C76" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D76" s="137" t="s">
@@ -6630,12 +6606,12 @@
       <c r="Q76" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R76" s="254"/>
-      <c r="S76" s="255"/>
+      <c r="R76" s="256"/>
+      <c r="S76" s="257"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B77" s="250"/>
-      <c r="C77" s="251"/>
+      <c r="B77" s="248"/>
+      <c r="C77" s="249"/>
       <c r="D77" s="137" t="s">
         <v>22</v>
       </c>
@@ -6681,14 +6657,14 @@
       <c r="Q77" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R77" s="254"/>
-      <c r="S77" s="255"/>
+      <c r="R77" s="256"/>
+      <c r="S77" s="257"/>
     </row>
     <row r="78" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="250" t="s">
+      <c r="B78" s="248" t="s">
         <v>69</v>
       </c>
-      <c r="C78" s="251" t="s">
+      <c r="C78" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D78" s="137" t="s">
@@ -6736,12 +6712,12 @@
       <c r="Q78" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R78" s="254"/>
-      <c r="S78" s="255"/>
+      <c r="R78" s="256"/>
+      <c r="S78" s="257"/>
     </row>
     <row r="79" spans="2:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="250"/>
-      <c r="C79" s="251"/>
+      <c r="B79" s="248"/>
+      <c r="C79" s="249"/>
       <c r="D79" s="137" t="s">
         <v>22</v>
       </c>
@@ -6787,39 +6763,39 @@
       <c r="Q79" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R79" s="262"/>
-      <c r="S79" s="263"/>
+      <c r="R79" s="258"/>
+      <c r="S79" s="259"/>
     </row>
     <row r="80" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B80" s="231" t="s">
+      <c r="B80" s="232" t="s">
         <v>70</v>
       </c>
-      <c r="C80" s="232"/>
-      <c r="D80" s="232"/>
-      <c r="E80" s="232"/>
-      <c r="F80" s="232"/>
-      <c r="G80" s="232"/>
-      <c r="H80" s="232"/>
-      <c r="I80" s="232"/>
-      <c r="J80" s="232"/>
-      <c r="K80" s="232"/>
-      <c r="L80" s="232"/>
-      <c r="M80" s="232"/>
-      <c r="N80" s="232"/>
-      <c r="O80" s="232"/>
-      <c r="P80" s="232"/>
-      <c r="Q80" s="232"/>
-      <c r="R80" s="219"/>
-      <c r="S80" s="261"/>
+      <c r="C80" s="233"/>
+      <c r="D80" s="233"/>
+      <c r="E80" s="233"/>
+      <c r="F80" s="233"/>
+      <c r="G80" s="233"/>
+      <c r="H80" s="233"/>
+      <c r="I80" s="233"/>
+      <c r="J80" s="233"/>
+      <c r="K80" s="233"/>
+      <c r="L80" s="233"/>
+      <c r="M80" s="233"/>
+      <c r="N80" s="233"/>
+      <c r="O80" s="233"/>
+      <c r="P80" s="233"/>
+      <c r="Q80" s="233"/>
+      <c r="R80" s="216"/>
+      <c r="S80" s="274"/>
     </row>
     <row r="81" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B81" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C81" s="247" t="s">
+      <c r="C81" s="271" t="s">
         <v>2</v>
       </c>
-      <c r="D81" s="248"/>
+      <c r="D81" s="272"/>
       <c r="E81" s="120" t="s">
         <v>3</v>
       </c>
@@ -6859,16 +6835,16 @@
       <c r="Q81" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R81" s="247" t="s">
+      <c r="R81" s="271" t="s">
         <v>36</v>
       </c>
-      <c r="S81" s="249"/>
+      <c r="S81" s="273"/>
     </row>
     <row r="82" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="272" t="s">
+      <c r="B82" s="275" t="s">
         <v>71</v>
       </c>
-      <c r="C82" s="274" t="s">
+      <c r="C82" s="267" t="s">
         <v>72</v>
       </c>
       <c r="D82" s="137" t="s">
@@ -6916,14 +6892,14 @@
       <c r="Q82" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R82" s="257" t="s">
+      <c r="R82" s="261" t="s">
         <v>73</v>
       </c>
-      <c r="S82" s="258"/>
+      <c r="S82" s="262"/>
     </row>
     <row r="83" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="273"/>
-      <c r="C83" s="275"/>
+      <c r="B83" s="276"/>
+      <c r="C83" s="277"/>
       <c r="D83" s="137" t="s">
         <v>22</v>
       </c>
@@ -6969,39 +6945,39 @@
       <c r="Q83" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R83" s="259"/>
-      <c r="S83" s="260"/>
+      <c r="R83" s="263"/>
+      <c r="S83" s="264"/>
     </row>
     <row r="84" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B84" s="231" t="s">
+      <c r="B84" s="232" t="s">
         <v>74</v>
       </c>
-      <c r="C84" s="232"/>
-      <c r="D84" s="232"/>
-      <c r="E84" s="232"/>
-      <c r="F84" s="232"/>
-      <c r="G84" s="232"/>
-      <c r="H84" s="232"/>
-      <c r="I84" s="232"/>
-      <c r="J84" s="232"/>
-      <c r="K84" s="232"/>
-      <c r="L84" s="232"/>
-      <c r="M84" s="232"/>
-      <c r="N84" s="232"/>
-      <c r="O84" s="232"/>
-      <c r="P84" s="232"/>
-      <c r="Q84" s="232"/>
-      <c r="R84" s="232"/>
-      <c r="S84" s="246"/>
+      <c r="C84" s="233"/>
+      <c r="D84" s="233"/>
+      <c r="E84" s="233"/>
+      <c r="F84" s="233"/>
+      <c r="G84" s="233"/>
+      <c r="H84" s="233"/>
+      <c r="I84" s="233"/>
+      <c r="J84" s="233"/>
+      <c r="K84" s="233"/>
+      <c r="L84" s="233"/>
+      <c r="M84" s="233"/>
+      <c r="N84" s="233"/>
+      <c r="O84" s="233"/>
+      <c r="P84" s="233"/>
+      <c r="Q84" s="233"/>
+      <c r="R84" s="233"/>
+      <c r="S84" s="251"/>
     </row>
     <row r="85" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B85" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="247" t="s">
+      <c r="C85" s="271" t="s">
         <v>2</v>
       </c>
-      <c r="D85" s="248"/>
+      <c r="D85" s="272"/>
       <c r="E85" s="120" t="s">
         <v>3</v>
       </c>
@@ -7041,16 +7017,16 @@
       <c r="Q85" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R85" s="247" t="s">
+      <c r="R85" s="271" t="s">
         <v>36</v>
       </c>
-      <c r="S85" s="249"/>
+      <c r="S85" s="273"/>
     </row>
     <row r="86" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="250" t="s">
-        <v>75</v>
-      </c>
-      <c r="C86" s="251" t="s">
+      <c r="B86" s="248" t="s">
+        <v>75</v>
+      </c>
+      <c r="C86" s="249" t="s">
         <v>72</v>
       </c>
       <c r="D86" s="137" t="s">
@@ -7098,14 +7074,14 @@
       <c r="Q86" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R86" s="257" t="s">
+      <c r="R86" s="261" t="s">
         <v>73</v>
       </c>
-      <c r="S86" s="258"/>
+      <c r="S86" s="262"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B87" s="250"/>
-      <c r="C87" s="251"/>
+      <c r="B87" s="248"/>
+      <c r="C87" s="249"/>
       <c r="D87" s="137" t="s">
         <v>22</v>
       </c>
@@ -7151,39 +7127,39 @@
       <c r="Q87" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R87" s="259"/>
-      <c r="S87" s="260"/>
+      <c r="R87" s="263"/>
+      <c r="S87" s="264"/>
     </row>
     <row r="88" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B88" s="229" t="s">
+      <c r="B88" s="212" t="s">
         <v>77</v>
       </c>
-      <c r="C88" s="230"/>
-      <c r="D88" s="230"/>
-      <c r="E88" s="230"/>
-      <c r="F88" s="230"/>
-      <c r="G88" s="230"/>
-      <c r="H88" s="230"/>
-      <c r="I88" s="230"/>
-      <c r="J88" s="230"/>
-      <c r="K88" s="230"/>
-      <c r="L88" s="230"/>
-      <c r="M88" s="230"/>
-      <c r="N88" s="230"/>
-      <c r="O88" s="230"/>
-      <c r="P88" s="230"/>
-      <c r="Q88" s="230"/>
-      <c r="R88" s="230"/>
-      <c r="S88" s="256"/>
+      <c r="C88" s="213"/>
+      <c r="D88" s="213"/>
+      <c r="E88" s="213"/>
+      <c r="F88" s="213"/>
+      <c r="G88" s="213"/>
+      <c r="H88" s="213"/>
+      <c r="I88" s="213"/>
+      <c r="J88" s="213"/>
+      <c r="K88" s="213"/>
+      <c r="L88" s="213"/>
+      <c r="M88" s="213"/>
+      <c r="N88" s="213"/>
+      <c r="O88" s="213"/>
+      <c r="P88" s="213"/>
+      <c r="Q88" s="213"/>
+      <c r="R88" s="213"/>
+      <c r="S88" s="260"/>
     </row>
     <row r="89" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B89" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C89" s="247" t="s">
+      <c r="C89" s="271" t="s">
         <v>2</v>
       </c>
-      <c r="D89" s="248"/>
+      <c r="D89" s="272"/>
       <c r="E89" s="120" t="s">
         <v>3</v>
       </c>
@@ -7223,16 +7199,16 @@
       <c r="Q89" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R89" s="247" t="s">
+      <c r="R89" s="271" t="s">
         <v>36</v>
       </c>
-      <c r="S89" s="249"/>
+      <c r="S89" s="273"/>
     </row>
     <row r="90" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="250" t="s">
+      <c r="B90" s="248" t="s">
         <v>78</v>
       </c>
-      <c r="C90" s="251" t="s">
+      <c r="C90" s="249" t="s">
         <v>72</v>
       </c>
       <c r="D90" s="137" t="s">
@@ -7280,14 +7256,14 @@
       <c r="Q90" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R90" s="257" t="s">
+      <c r="R90" s="261" t="s">
         <v>73</v>
       </c>
-      <c r="S90" s="258"/>
+      <c r="S90" s="262"/>
     </row>
     <row r="91" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="250"/>
-      <c r="C91" s="251"/>
+      <c r="B91" s="248"/>
+      <c r="C91" s="249"/>
       <c r="D91" s="137" t="s">
         <v>22</v>
       </c>
@@ -7333,39 +7309,39 @@
       <c r="Q91" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R91" s="259"/>
-      <c r="S91" s="260"/>
+      <c r="R91" s="263"/>
+      <c r="S91" s="264"/>
     </row>
     <row r="92" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B92" s="229" t="s">
+      <c r="B92" s="212" t="s">
         <v>79</v>
       </c>
-      <c r="C92" s="230"/>
-      <c r="D92" s="230"/>
-      <c r="E92" s="230"/>
-      <c r="F92" s="230"/>
-      <c r="G92" s="230"/>
-      <c r="H92" s="230"/>
-      <c r="I92" s="230"/>
-      <c r="J92" s="230"/>
-      <c r="K92" s="230"/>
-      <c r="L92" s="230"/>
-      <c r="M92" s="230"/>
-      <c r="N92" s="230"/>
-      <c r="O92" s="230"/>
-      <c r="P92" s="230"/>
-      <c r="Q92" s="230"/>
-      <c r="R92" s="230"/>
-      <c r="S92" s="256"/>
+      <c r="C92" s="213"/>
+      <c r="D92" s="213"/>
+      <c r="E92" s="213"/>
+      <c r="F92" s="213"/>
+      <c r="G92" s="213"/>
+      <c r="H92" s="213"/>
+      <c r="I92" s="213"/>
+      <c r="J92" s="213"/>
+      <c r="K92" s="213"/>
+      <c r="L92" s="213"/>
+      <c r="M92" s="213"/>
+      <c r="N92" s="213"/>
+      <c r="O92" s="213"/>
+      <c r="P92" s="213"/>
+      <c r="Q92" s="213"/>
+      <c r="R92" s="213"/>
+      <c r="S92" s="260"/>
     </row>
     <row r="93" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B93" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C93" s="247" t="s">
+      <c r="C93" s="271" t="s">
         <v>2</v>
       </c>
-      <c r="D93" s="248"/>
+      <c r="D93" s="272"/>
       <c r="E93" s="120" t="s">
         <v>3</v>
       </c>
@@ -7405,16 +7381,16 @@
       <c r="Q93" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R93" s="247" t="s">
+      <c r="R93" s="271" t="s">
         <v>36</v>
       </c>
-      <c r="S93" s="249"/>
+      <c r="S93" s="273"/>
     </row>
     <row r="94" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="250" t="s">
+      <c r="B94" s="248" t="s">
         <v>80</v>
       </c>
-      <c r="C94" s="251" t="s">
+      <c r="C94" s="249" t="s">
         <v>72</v>
       </c>
       <c r="D94" s="137" t="s">
@@ -7462,14 +7438,14 @@
       <c r="Q94" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R94" s="257" t="s">
+      <c r="R94" s="261" t="s">
         <v>73</v>
       </c>
-      <c r="S94" s="258"/>
+      <c r="S94" s="262"/>
     </row>
     <row r="95" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="250"/>
-      <c r="C95" s="251"/>
+      <c r="B95" s="248"/>
+      <c r="C95" s="249"/>
       <c r="D95" s="137" t="s">
         <v>22</v>
       </c>
@@ -7515,39 +7491,39 @@
       <c r="Q95" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R95" s="259"/>
-      <c r="S95" s="260"/>
+      <c r="R95" s="263"/>
+      <c r="S95" s="264"/>
     </row>
     <row r="96" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B96" s="231" t="s">
+      <c r="B96" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="C96" s="232"/>
-      <c r="D96" s="232"/>
-      <c r="E96" s="232"/>
-      <c r="F96" s="232"/>
-      <c r="G96" s="232"/>
-      <c r="H96" s="232"/>
-      <c r="I96" s="232"/>
-      <c r="J96" s="232"/>
-      <c r="K96" s="232"/>
-      <c r="L96" s="232"/>
-      <c r="M96" s="232"/>
-      <c r="N96" s="232"/>
-      <c r="O96" s="232"/>
-      <c r="P96" s="232"/>
-      <c r="Q96" s="232"/>
-      <c r="R96" s="219"/>
-      <c r="S96" s="219"/>
+      <c r="C96" s="233"/>
+      <c r="D96" s="233"/>
+      <c r="E96" s="233"/>
+      <c r="F96" s="233"/>
+      <c r="G96" s="233"/>
+      <c r="H96" s="233"/>
+      <c r="I96" s="233"/>
+      <c r="J96" s="233"/>
+      <c r="K96" s="233"/>
+      <c r="L96" s="233"/>
+      <c r="M96" s="233"/>
+      <c r="N96" s="233"/>
+      <c r="O96" s="233"/>
+      <c r="P96" s="233"/>
+      <c r="Q96" s="233"/>
+      <c r="R96" s="216"/>
+      <c r="S96" s="216"/>
     </row>
     <row r="97" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B97" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C97" s="247" t="s">
+      <c r="C97" s="271" t="s">
         <v>2</v>
       </c>
-      <c r="D97" s="248"/>
+      <c r="D97" s="272"/>
       <c r="E97" s="120" t="s">
         <v>3</v>
       </c>
@@ -7587,16 +7563,16 @@
       <c r="Q97" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R97" s="247" t="s">
+      <c r="R97" s="271" t="s">
         <v>36</v>
       </c>
-      <c r="S97" s="249"/>
+      <c r="S97" s="273"/>
     </row>
     <row r="98" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B98" s="250" t="s">
+      <c r="B98" s="248" t="s">
         <v>84</v>
       </c>
-      <c r="C98" s="251" t="s">
+      <c r="C98" s="249" t="s">
         <v>72</v>
       </c>
       <c r="D98" s="137" t="s">
@@ -7644,15 +7620,15 @@
       <c r="Q98" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R98" s="252" t="s">
-        <v>85</v>
-      </c>
-      <c r="S98" s="253"/>
+      <c r="R98" s="254" t="s">
+        <v>85</v>
+      </c>
+      <c r="S98" s="255"/>
       <c r="T98"/>
     </row>
     <row r="99" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="250"/>
-      <c r="C99" s="251"/>
+      <c r="B99" s="248"/>
+      <c r="C99" s="249"/>
       <c r="D99" s="137" t="s">
         <v>22</v>
       </c>
@@ -7698,40 +7674,40 @@
       <c r="Q99" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R99" s="254"/>
-      <c r="S99" s="255"/>
+      <c r="R99" s="256"/>
+      <c r="S99" s="257"/>
       <c r="T99"/>
     </row>
     <row r="100" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B100" s="231" t="s">
+      <c r="B100" s="232" t="s">
         <v>86</v>
       </c>
-      <c r="C100" s="232"/>
-      <c r="D100" s="232"/>
-      <c r="E100" s="232"/>
-      <c r="F100" s="232"/>
-      <c r="G100" s="232"/>
-      <c r="H100" s="232"/>
-      <c r="I100" s="232"/>
-      <c r="J100" s="232"/>
-      <c r="K100" s="232"/>
-      <c r="L100" s="232"/>
-      <c r="M100" s="232"/>
-      <c r="N100" s="232"/>
-      <c r="O100" s="232"/>
-      <c r="P100" s="232"/>
-      <c r="Q100" s="232"/>
-      <c r="R100" s="232"/>
-      <c r="S100" s="246"/>
+      <c r="C100" s="233"/>
+      <c r="D100" s="233"/>
+      <c r="E100" s="233"/>
+      <c r="F100" s="233"/>
+      <c r="G100" s="233"/>
+      <c r="H100" s="233"/>
+      <c r="I100" s="233"/>
+      <c r="J100" s="233"/>
+      <c r="K100" s="233"/>
+      <c r="L100" s="233"/>
+      <c r="M100" s="233"/>
+      <c r="N100" s="233"/>
+      <c r="O100" s="233"/>
+      <c r="P100" s="233"/>
+      <c r="Q100" s="233"/>
+      <c r="R100" s="233"/>
+      <c r="S100" s="251"/>
     </row>
     <row r="101" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B101" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C101" s="247" t="s">
+      <c r="C101" s="271" t="s">
         <v>2</v>
       </c>
-      <c r="D101" s="248"/>
+      <c r="D101" s="272"/>
       <c r="E101" s="120" t="s">
         <v>3</v>
       </c>
@@ -7771,16 +7747,16 @@
       <c r="Q101" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R101" s="247" t="s">
+      <c r="R101" s="271" t="s">
         <v>36</v>
       </c>
-      <c r="S101" s="249"/>
+      <c r="S101" s="273"/>
     </row>
     <row r="102" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B102" s="250" t="s">
+      <c r="B102" s="248" t="s">
         <v>87</v>
       </c>
-      <c r="C102" s="251" t="s">
+      <c r="C102" s="249" t="s">
         <v>29</v>
       </c>
       <c r="D102" s="137" t="s">
@@ -7828,15 +7804,15 @@
       <c r="Q102" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R102" s="252" t="s">
-        <v>85</v>
-      </c>
-      <c r="S102" s="253"/>
+      <c r="R102" s="254" t="s">
+        <v>85</v>
+      </c>
+      <c r="S102" s="255"/>
       <c r="T102"/>
     </row>
     <row r="103" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B103" s="250"/>
-      <c r="C103" s="251"/>
+      <c r="B103" s="248"/>
+      <c r="C103" s="249"/>
       <c r="D103" s="137" t="s">
         <v>22</v>
       </c>
@@ -7882,8 +7858,8 @@
       <c r="Q103" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R103" s="254"/>
-      <c r="S103" s="255"/>
+      <c r="R103" s="256"/>
+      <c r="S103" s="257"/>
       <c r="T103"/>
     </row>
     <row r="104" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7907,127 +7883,127 @@
       <c r="S104" s="134"/>
     </row>
     <row r="105" spans="2:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B105" s="234" t="s">
+      <c r="B105" s="278" t="s">
         <v>32</v>
       </c>
-      <c r="C105" s="235"/>
-      <c r="D105" s="235"/>
-      <c r="E105" s="235"/>
-      <c r="F105" s="235"/>
-      <c r="G105" s="235"/>
-      <c r="H105" s="235"/>
-      <c r="I105" s="235"/>
-      <c r="J105" s="235"/>
-      <c r="K105" s="235"/>
-      <c r="L105" s="235"/>
-      <c r="M105" s="235"/>
-      <c r="N105" s="235"/>
-      <c r="O105" s="235"/>
-      <c r="P105" s="235"/>
-      <c r="Q105" s="235"/>
-      <c r="R105" s="235"/>
-      <c r="S105" s="236"/>
+      <c r="C105" s="279"/>
+      <c r="D105" s="279"/>
+      <c r="E105" s="279"/>
+      <c r="F105" s="279"/>
+      <c r="G105" s="279"/>
+      <c r="H105" s="279"/>
+      <c r="I105" s="279"/>
+      <c r="J105" s="279"/>
+      <c r="K105" s="279"/>
+      <c r="L105" s="279"/>
+      <c r="M105" s="279"/>
+      <c r="N105" s="279"/>
+      <c r="O105" s="279"/>
+      <c r="P105" s="279"/>
+      <c r="Q105" s="279"/>
+      <c r="R105" s="279"/>
+      <c r="S105" s="280"/>
     </row>
     <row r="106" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B106" s="237" t="s">
+      <c r="B106" s="281" t="s">
         <v>33</v>
       </c>
-      <c r="C106" s="238"/>
-      <c r="D106" s="238"/>
-      <c r="E106" s="238"/>
-      <c r="F106" s="238"/>
-      <c r="G106" s="238"/>
-      <c r="H106" s="238"/>
-      <c r="I106" s="238"/>
-      <c r="J106" s="238"/>
-      <c r="K106" s="238"/>
-      <c r="L106" s="238"/>
-      <c r="M106" s="238"/>
-      <c r="N106" s="238"/>
-      <c r="O106" s="238"/>
-      <c r="P106" s="238"/>
-      <c r="Q106" s="238"/>
-      <c r="R106" s="238"/>
-      <c r="S106" s="239"/>
+      <c r="C106" s="282"/>
+      <c r="D106" s="282"/>
+      <c r="E106" s="282"/>
+      <c r="F106" s="282"/>
+      <c r="G106" s="282"/>
+      <c r="H106" s="282"/>
+      <c r="I106" s="282"/>
+      <c r="J106" s="282"/>
+      <c r="K106" s="282"/>
+      <c r="L106" s="282"/>
+      <c r="M106" s="282"/>
+      <c r="N106" s="282"/>
+      <c r="O106" s="282"/>
+      <c r="P106" s="282"/>
+      <c r="Q106" s="282"/>
+      <c r="R106" s="282"/>
+      <c r="S106" s="283"/>
     </row>
     <row r="107" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B107" s="237"/>
-      <c r="C107" s="238"/>
-      <c r="D107" s="238"/>
-      <c r="E107" s="238"/>
-      <c r="F107" s="238"/>
-      <c r="G107" s="238"/>
-      <c r="H107" s="238"/>
-      <c r="I107" s="238"/>
-      <c r="J107" s="238"/>
-      <c r="K107" s="238"/>
-      <c r="L107" s="238"/>
-      <c r="M107" s="238"/>
-      <c r="N107" s="238"/>
-      <c r="O107" s="238"/>
-      <c r="P107" s="238"/>
-      <c r="Q107" s="238"/>
-      <c r="R107" s="238"/>
-      <c r="S107" s="239"/>
+      <c r="B107" s="281"/>
+      <c r="C107" s="282"/>
+      <c r="D107" s="282"/>
+      <c r="E107" s="282"/>
+      <c r="F107" s="282"/>
+      <c r="G107" s="282"/>
+      <c r="H107" s="282"/>
+      <c r="I107" s="282"/>
+      <c r="J107" s="282"/>
+      <c r="K107" s="282"/>
+      <c r="L107" s="282"/>
+      <c r="M107" s="282"/>
+      <c r="N107" s="282"/>
+      <c r="O107" s="282"/>
+      <c r="P107" s="282"/>
+      <c r="Q107" s="282"/>
+      <c r="R107" s="282"/>
+      <c r="S107" s="283"/>
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B108" s="237"/>
-      <c r="C108" s="238"/>
-      <c r="D108" s="238"/>
-      <c r="E108" s="238"/>
-      <c r="F108" s="238"/>
-      <c r="G108" s="238"/>
-      <c r="H108" s="238"/>
-      <c r="I108" s="238"/>
-      <c r="J108" s="238"/>
-      <c r="K108" s="238"/>
-      <c r="L108" s="238"/>
-      <c r="M108" s="238"/>
-      <c r="N108" s="238"/>
-      <c r="O108" s="238"/>
-      <c r="P108" s="238"/>
-      <c r="Q108" s="238"/>
-      <c r="R108" s="238"/>
-      <c r="S108" s="239"/>
+      <c r="B108" s="281"/>
+      <c r="C108" s="282"/>
+      <c r="D108" s="282"/>
+      <c r="E108" s="282"/>
+      <c r="F108" s="282"/>
+      <c r="G108" s="282"/>
+      <c r="H108" s="282"/>
+      <c r="I108" s="282"/>
+      <c r="J108" s="282"/>
+      <c r="K108" s="282"/>
+      <c r="L108" s="282"/>
+      <c r="M108" s="282"/>
+      <c r="N108" s="282"/>
+      <c r="O108" s="282"/>
+      <c r="P108" s="282"/>
+      <c r="Q108" s="282"/>
+      <c r="R108" s="282"/>
+      <c r="S108" s="283"/>
     </row>
     <row r="109" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="240"/>
-      <c r="C109" s="241"/>
-      <c r="D109" s="241"/>
-      <c r="E109" s="241"/>
-      <c r="F109" s="241"/>
-      <c r="G109" s="241"/>
-      <c r="H109" s="241"/>
-      <c r="I109" s="241"/>
-      <c r="J109" s="241"/>
-      <c r="K109" s="241"/>
-      <c r="L109" s="241"/>
-      <c r="M109" s="241"/>
-      <c r="N109" s="241"/>
-      <c r="O109" s="241"/>
-      <c r="P109" s="241"/>
-      <c r="Q109" s="241"/>
-      <c r="R109" s="241"/>
-      <c r="S109" s="242"/>
+      <c r="B109" s="284"/>
+      <c r="C109" s="285"/>
+      <c r="D109" s="285"/>
+      <c r="E109" s="285"/>
+      <c r="F109" s="285"/>
+      <c r="G109" s="285"/>
+      <c r="H109" s="285"/>
+      <c r="I109" s="285"/>
+      <c r="J109" s="285"/>
+      <c r="K109" s="285"/>
+      <c r="L109" s="285"/>
+      <c r="M109" s="285"/>
+      <c r="N109" s="285"/>
+      <c r="O109" s="285"/>
+      <c r="P109" s="285"/>
+      <c r="Q109" s="285"/>
+      <c r="R109" s="285"/>
+      <c r="S109" s="286"/>
     </row>
     <row r="118" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B118" s="243" t="s">
+      <c r="B118" s="287" t="s">
         <v>88</v>
       </c>
-      <c r="C118" s="243"/>
-      <c r="D118" s="243"/>
-      <c r="E118" s="243"/>
-      <c r="F118" s="243"/>
-      <c r="G118" s="243"/>
-      <c r="H118" s="243"/>
-      <c r="I118" s="243"/>
-      <c r="J118" s="243"/>
-      <c r="K118" s="243"/>
-      <c r="L118" s="243"/>
-      <c r="M118" s="243"/>
-      <c r="N118" s="243"/>
-      <c r="O118" s="243"/>
-      <c r="P118" s="243"/>
+      <c r="C118" s="287"/>
+      <c r="D118" s="287"/>
+      <c r="E118" s="287"/>
+      <c r="F118" s="287"/>
+      <c r="G118" s="287"/>
+      <c r="H118" s="287"/>
+      <c r="I118" s="287"/>
+      <c r="J118" s="287"/>
+      <c r="K118" s="287"/>
+      <c r="L118" s="287"/>
+      <c r="M118" s="287"/>
+      <c r="N118" s="287"/>
+      <c r="O118" s="287"/>
+      <c r="P118" s="287"/>
       <c r="Q118" s="129"/>
     </row>
     <row r="119" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -8075,10 +8051,10 @@
       <c r="Q119" s="217"/>
     </row>
     <row r="120" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="220" t="s">
+      <c r="B120" s="214" t="s">
         <v>90</v>
       </c>
-      <c r="C120" s="244" t="s">
+      <c r="C120" s="239" t="s">
         <v>16</v>
       </c>
       <c r="D120" s="20" t="s">
@@ -8116,15 +8092,15 @@
       <c r="N120" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="O120" s="245" t="s">
+      <c r="O120" s="246" t="s">
         <v>44</v>
       </c>
-      <c r="P120" s="245"/>
-      <c r="Q120" s="245"/>
+      <c r="P120" s="246"/>
+      <c r="Q120" s="246"/>
     </row>
     <row r="121" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B121" s="220"/>
-      <c r="C121" s="244"/>
+      <c r="B121" s="214"/>
+      <c r="C121" s="239"/>
       <c r="D121" s="20" t="s">
         <v>22</v>
       </c>
@@ -8160,9 +8136,9 @@
       <c r="N121" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="O121" s="245"/>
-      <c r="P121" s="245"/>
-      <c r="Q121" s="245"/>
+      <c r="O121" s="246"/>
+      <c r="P121" s="246"/>
+      <c r="Q121" s="246"/>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B122" s="42"/>
@@ -8203,78 +8179,78 @@
       <c r="Q123" s="7"/>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B124" s="211" t="s">
+      <c r="B124" s="224" t="s">
         <v>33</v>
       </c>
-      <c r="C124" s="212"/>
-      <c r="D124" s="212"/>
-      <c r="E124" s="212"/>
-      <c r="F124" s="212"/>
-      <c r="G124" s="212"/>
-      <c r="H124" s="212"/>
-      <c r="I124" s="212"/>
-      <c r="J124" s="212"/>
-      <c r="K124" s="212"/>
-      <c r="L124" s="212"/>
-      <c r="M124" s="212"/>
-      <c r="N124" s="212"/>
-      <c r="O124" s="212"/>
-      <c r="P124" s="212"/>
-      <c r="Q124" s="213"/>
+      <c r="C124" s="225"/>
+      <c r="D124" s="225"/>
+      <c r="E124" s="225"/>
+      <c r="F124" s="225"/>
+      <c r="G124" s="225"/>
+      <c r="H124" s="225"/>
+      <c r="I124" s="225"/>
+      <c r="J124" s="225"/>
+      <c r="K124" s="225"/>
+      <c r="L124" s="225"/>
+      <c r="M124" s="225"/>
+      <c r="N124" s="225"/>
+      <c r="O124" s="225"/>
+      <c r="P124" s="225"/>
+      <c r="Q124" s="226"/>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B125" s="211"/>
-      <c r="C125" s="212"/>
-      <c r="D125" s="212"/>
-      <c r="E125" s="212"/>
-      <c r="F125" s="212"/>
-      <c r="G125" s="212"/>
-      <c r="H125" s="212"/>
-      <c r="I125" s="212"/>
-      <c r="J125" s="212"/>
-      <c r="K125" s="212"/>
-      <c r="L125" s="212"/>
-      <c r="M125" s="212"/>
-      <c r="N125" s="212"/>
-      <c r="O125" s="212"/>
-      <c r="P125" s="212"/>
-      <c r="Q125" s="213"/>
+      <c r="B125" s="224"/>
+      <c r="C125" s="225"/>
+      <c r="D125" s="225"/>
+      <c r="E125" s="225"/>
+      <c r="F125" s="225"/>
+      <c r="G125" s="225"/>
+      <c r="H125" s="225"/>
+      <c r="I125" s="225"/>
+      <c r="J125" s="225"/>
+      <c r="K125" s="225"/>
+      <c r="L125" s="225"/>
+      <c r="M125" s="225"/>
+      <c r="N125" s="225"/>
+      <c r="O125" s="225"/>
+      <c r="P125" s="225"/>
+      <c r="Q125" s="226"/>
     </row>
     <row r="126" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B126" s="211"/>
-      <c r="C126" s="212"/>
-      <c r="D126" s="212"/>
-      <c r="E126" s="212"/>
-      <c r="F126" s="212"/>
-      <c r="G126" s="212"/>
-      <c r="H126" s="212"/>
-      <c r="I126" s="212"/>
-      <c r="J126" s="212"/>
-      <c r="K126" s="212"/>
-      <c r="L126" s="212"/>
-      <c r="M126" s="212"/>
-      <c r="N126" s="212"/>
-      <c r="O126" s="212"/>
-      <c r="P126" s="212"/>
-      <c r="Q126" s="213"/>
+      <c r="B126" s="224"/>
+      <c r="C126" s="225"/>
+      <c r="D126" s="225"/>
+      <c r="E126" s="225"/>
+      <c r="F126" s="225"/>
+      <c r="G126" s="225"/>
+      <c r="H126" s="225"/>
+      <c r="I126" s="225"/>
+      <c r="J126" s="225"/>
+      <c r="K126" s="225"/>
+      <c r="L126" s="225"/>
+      <c r="M126" s="225"/>
+      <c r="N126" s="225"/>
+      <c r="O126" s="225"/>
+      <c r="P126" s="225"/>
+      <c r="Q126" s="226"/>
     </row>
     <row r="127" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B127" s="214"/>
-      <c r="C127" s="215"/>
-      <c r="D127" s="215"/>
-      <c r="E127" s="215"/>
-      <c r="F127" s="215"/>
-      <c r="G127" s="215"/>
-      <c r="H127" s="215"/>
-      <c r="I127" s="215"/>
-      <c r="J127" s="215"/>
-      <c r="K127" s="215"/>
-      <c r="L127" s="215"/>
-      <c r="M127" s="215"/>
-      <c r="N127" s="215"/>
-      <c r="O127" s="215"/>
-      <c r="P127" s="215"/>
-      <c r="Q127" s="216"/>
+      <c r="B127" s="227"/>
+      <c r="C127" s="228"/>
+      <c r="D127" s="228"/>
+      <c r="E127" s="228"/>
+      <c r="F127" s="228"/>
+      <c r="G127" s="228"/>
+      <c r="H127" s="228"/>
+      <c r="I127" s="228"/>
+      <c r="J127" s="228"/>
+      <c r="K127" s="228"/>
+      <c r="L127" s="228"/>
+      <c r="M127" s="228"/>
+      <c r="N127" s="228"/>
+      <c r="O127" s="228"/>
+      <c r="P127" s="228"/>
+      <c r="Q127" s="229"/>
     </row>
     <row r="128" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B128" s="35"/>
@@ -8296,23 +8272,23 @@
     </row>
     <row r="133" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="134" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B134" s="231" t="s">
+      <c r="B134" s="232" t="s">
         <v>92</v>
       </c>
-      <c r="C134" s="232"/>
-      <c r="D134" s="232"/>
-      <c r="E134" s="232"/>
-      <c r="F134" s="232"/>
-      <c r="G134" s="232"/>
-      <c r="H134" s="232"/>
-      <c r="I134" s="232"/>
-      <c r="J134" s="232"/>
-      <c r="K134" s="232"/>
-      <c r="L134" s="232"/>
-      <c r="M134" s="232"/>
-      <c r="N134" s="232"/>
-      <c r="O134" s="232"/>
-      <c r="P134" s="232"/>
+      <c r="C134" s="233"/>
+      <c r="D134" s="233"/>
+      <c r="E134" s="233"/>
+      <c r="F134" s="233"/>
+      <c r="G134" s="233"/>
+      <c r="H134" s="233"/>
+      <c r="I134" s="233"/>
+      <c r="J134" s="233"/>
+      <c r="K134" s="233"/>
+      <c r="L134" s="233"/>
+      <c r="M134" s="233"/>
+      <c r="N134" s="233"/>
+      <c r="O134" s="233"/>
+      <c r="P134" s="233"/>
     </row>
     <row r="135" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B135" s="97" t="s">
@@ -8409,10 +8385,10 @@
       </c>
     </row>
     <row r="137" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B137" s="233" t="s">
+      <c r="B137" s="234" t="s">
         <v>96</v>
       </c>
-      <c r="C137" s="220" t="s">
+      <c r="C137" s="214" t="s">
         <v>29</v>
       </c>
       <c r="D137" s="117" t="s">
@@ -8459,8 +8435,8 @@
       </c>
     </row>
     <row r="138" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B138" s="233"/>
-      <c r="C138" s="220"/>
+      <c r="B138" s="234"/>
+      <c r="C138" s="214"/>
       <c r="D138" s="117" t="s">
         <v>22</v>
       </c>
@@ -8506,23 +8482,23 @@
     </row>
     <row r="140" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="141" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B141" s="231" t="s">
+      <c r="B141" s="232" t="s">
         <v>97</v>
       </c>
-      <c r="C141" s="232"/>
-      <c r="D141" s="232"/>
-      <c r="E141" s="232"/>
-      <c r="F141" s="232"/>
-      <c r="G141" s="232"/>
-      <c r="H141" s="232"/>
-      <c r="I141" s="232"/>
-      <c r="J141" s="232"/>
-      <c r="K141" s="232"/>
-      <c r="L141" s="232"/>
-      <c r="M141" s="232"/>
-      <c r="N141" s="232"/>
-      <c r="O141" s="232"/>
-      <c r="P141" s="232"/>
+      <c r="C141" s="233"/>
+      <c r="D141" s="233"/>
+      <c r="E141" s="233"/>
+      <c r="F141" s="233"/>
+      <c r="G141" s="233"/>
+      <c r="H141" s="233"/>
+      <c r="I141" s="233"/>
+      <c r="J141" s="233"/>
+      <c r="K141" s="233"/>
+      <c r="L141" s="233"/>
+      <c r="M141" s="233"/>
+      <c r="N141" s="233"/>
+      <c r="O141" s="233"/>
+      <c r="P141" s="233"/>
     </row>
     <row r="142" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B142" s="97" t="s">
@@ -8570,10 +8546,10 @@
       </c>
     </row>
     <row r="143" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B143" s="220" t="s">
+      <c r="B143" s="214" t="s">
         <v>98</v>
       </c>
-      <c r="C143" s="220" t="s">
+      <c r="C143" s="214" t="s">
         <v>16</v>
       </c>
       <c r="D143" s="117" t="s">
@@ -8619,8 +8595,8 @@
       </c>
     </row>
     <row r="144" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B144" s="220"/>
-      <c r="C144" s="220"/>
+      <c r="B144" s="214"/>
+      <c r="C144" s="214"/>
       <c r="D144" s="117" t="s">
         <v>22</v>
       </c>
@@ -8664,10 +8640,10 @@
       </c>
     </row>
     <row r="145" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B145" s="220" t="s">
+      <c r="B145" s="214" t="s">
         <v>100</v>
       </c>
-      <c r="C145" s="220" t="s">
+      <c r="C145" s="214" t="s">
         <v>29</v>
       </c>
       <c r="D145" s="117" t="s">
@@ -8713,8 +8689,8 @@
       </c>
     </row>
     <row r="146" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B146" s="220"/>
-      <c r="C146" s="220"/>
+      <c r="B146" s="214"/>
+      <c r="C146" s="214"/>
       <c r="D146" s="117" t="s">
         <v>22</v>
       </c>
@@ -8784,78 +8760,78 @@
       <c r="Q148" s="7"/>
     </row>
     <row r="149" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B149" s="211" t="s">
+      <c r="B149" s="224" t="s">
         <v>33</v>
       </c>
-      <c r="C149" s="212"/>
-      <c r="D149" s="212"/>
-      <c r="E149" s="212"/>
-      <c r="F149" s="212"/>
-      <c r="G149" s="212"/>
-      <c r="H149" s="212"/>
-      <c r="I149" s="212"/>
-      <c r="J149" s="212"/>
-      <c r="K149" s="212"/>
-      <c r="L149" s="212"/>
-      <c r="M149" s="212"/>
-      <c r="N149" s="212"/>
-      <c r="O149" s="212"/>
-      <c r="P149" s="212"/>
-      <c r="Q149" s="213"/>
+      <c r="C149" s="225"/>
+      <c r="D149" s="225"/>
+      <c r="E149" s="225"/>
+      <c r="F149" s="225"/>
+      <c r="G149" s="225"/>
+      <c r="H149" s="225"/>
+      <c r="I149" s="225"/>
+      <c r="J149" s="225"/>
+      <c r="K149" s="225"/>
+      <c r="L149" s="225"/>
+      <c r="M149" s="225"/>
+      <c r="N149" s="225"/>
+      <c r="O149" s="225"/>
+      <c r="P149" s="225"/>
+      <c r="Q149" s="226"/>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B150" s="211"/>
-      <c r="C150" s="212"/>
-      <c r="D150" s="212"/>
-      <c r="E150" s="212"/>
-      <c r="F150" s="212"/>
-      <c r="G150" s="212"/>
-      <c r="H150" s="212"/>
-      <c r="I150" s="212"/>
-      <c r="J150" s="212"/>
-      <c r="K150" s="212"/>
-      <c r="L150" s="212"/>
-      <c r="M150" s="212"/>
-      <c r="N150" s="212"/>
-      <c r="O150" s="212"/>
-      <c r="P150" s="212"/>
-      <c r="Q150" s="213"/>
+      <c r="B150" s="224"/>
+      <c r="C150" s="225"/>
+      <c r="D150" s="225"/>
+      <c r="E150" s="225"/>
+      <c r="F150" s="225"/>
+      <c r="G150" s="225"/>
+      <c r="H150" s="225"/>
+      <c r="I150" s="225"/>
+      <c r="J150" s="225"/>
+      <c r="K150" s="225"/>
+      <c r="L150" s="225"/>
+      <c r="M150" s="225"/>
+      <c r="N150" s="225"/>
+      <c r="O150" s="225"/>
+      <c r="P150" s="225"/>
+      <c r="Q150" s="226"/>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B151" s="211"/>
-      <c r="C151" s="212"/>
-      <c r="D151" s="212"/>
-      <c r="E151" s="212"/>
-      <c r="F151" s="212"/>
-      <c r="G151" s="212"/>
-      <c r="H151" s="212"/>
-      <c r="I151" s="212"/>
-      <c r="J151" s="212"/>
-      <c r="K151" s="212"/>
-      <c r="L151" s="212"/>
-      <c r="M151" s="212"/>
-      <c r="N151" s="212"/>
-      <c r="O151" s="212"/>
-      <c r="P151" s="212"/>
-      <c r="Q151" s="213"/>
+      <c r="B151" s="224"/>
+      <c r="C151" s="225"/>
+      <c r="D151" s="225"/>
+      <c r="E151" s="225"/>
+      <c r="F151" s="225"/>
+      <c r="G151" s="225"/>
+      <c r="H151" s="225"/>
+      <c r="I151" s="225"/>
+      <c r="J151" s="225"/>
+      <c r="K151" s="225"/>
+      <c r="L151" s="225"/>
+      <c r="M151" s="225"/>
+      <c r="N151" s="225"/>
+      <c r="O151" s="225"/>
+      <c r="P151" s="225"/>
+      <c r="Q151" s="226"/>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B152" s="214"/>
-      <c r="C152" s="215"/>
-      <c r="D152" s="215"/>
-      <c r="E152" s="215"/>
-      <c r="F152" s="215"/>
-      <c r="G152" s="215"/>
-      <c r="H152" s="215"/>
-      <c r="I152" s="215"/>
-      <c r="J152" s="215"/>
-      <c r="K152" s="215"/>
-      <c r="L152" s="215"/>
-      <c r="M152" s="215"/>
-      <c r="N152" s="215"/>
-      <c r="O152" s="215"/>
-      <c r="P152" s="215"/>
-      <c r="Q152" s="216"/>
+      <c r="B152" s="227"/>
+      <c r="C152" s="228"/>
+      <c r="D152" s="228"/>
+      <c r="E152" s="228"/>
+      <c r="F152" s="228"/>
+      <c r="G152" s="228"/>
+      <c r="H152" s="228"/>
+      <c r="I152" s="228"/>
+      <c r="J152" s="228"/>
+      <c r="K152" s="228"/>
+      <c r="L152" s="228"/>
+      <c r="M152" s="228"/>
+      <c r="N152" s="228"/>
+      <c r="O152" s="228"/>
+      <c r="P152" s="228"/>
+      <c r="Q152" s="229"/>
     </row>
     <row r="154" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B154" s="35"/>
@@ -8876,23 +8852,23 @@
     </row>
     <row r="159" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="160" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B160" s="231" t="s">
+      <c r="B160" s="232" t="s">
         <v>101</v>
       </c>
-      <c r="C160" s="232"/>
-      <c r="D160" s="232"/>
-      <c r="E160" s="232"/>
-      <c r="F160" s="232"/>
-      <c r="G160" s="232"/>
-      <c r="H160" s="232"/>
-      <c r="I160" s="232"/>
-      <c r="J160" s="232"/>
-      <c r="K160" s="232"/>
-      <c r="L160" s="232"/>
-      <c r="M160" s="232"/>
-      <c r="N160" s="232"/>
-      <c r="O160" s="232"/>
-      <c r="P160" s="232"/>
+      <c r="C160" s="233"/>
+      <c r="D160" s="233"/>
+      <c r="E160" s="233"/>
+      <c r="F160" s="233"/>
+      <c r="G160" s="233"/>
+      <c r="H160" s="233"/>
+      <c r="I160" s="233"/>
+      <c r="J160" s="233"/>
+      <c r="K160" s="233"/>
+      <c r="L160" s="233"/>
+      <c r="M160" s="233"/>
+      <c r="N160" s="233"/>
+      <c r="O160" s="233"/>
+      <c r="P160" s="233"/>
     </row>
     <row r="161" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B161" s="97" t="s">
@@ -8940,10 +8916,10 @@
       </c>
     </row>
     <row r="162" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B162" s="233" t="s">
+      <c r="B162" s="234" t="s">
         <v>102</v>
       </c>
-      <c r="C162" s="220" t="s">
+      <c r="C162" s="214" t="s">
         <v>103</v>
       </c>
       <c r="D162" s="117" t="s">
@@ -8989,8 +8965,8 @@
       </c>
     </row>
     <row r="163" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B163" s="233"/>
-      <c r="C163" s="220"/>
+      <c r="B163" s="234"/>
+      <c r="C163" s="214"/>
       <c r="D163" s="117" t="s">
         <v>22</v>
       </c>
@@ -9054,78 +9030,78 @@
       <c r="Q165" s="7"/>
     </row>
     <row r="166" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B166" s="211" t="s">
+      <c r="B166" s="224" t="s">
         <v>33</v>
       </c>
-      <c r="C166" s="212"/>
-      <c r="D166" s="212"/>
-      <c r="E166" s="212"/>
-      <c r="F166" s="212"/>
-      <c r="G166" s="212"/>
-      <c r="H166" s="212"/>
-      <c r="I166" s="212"/>
-      <c r="J166" s="212"/>
-      <c r="K166" s="212"/>
-      <c r="L166" s="212"/>
-      <c r="M166" s="212"/>
-      <c r="N166" s="212"/>
-      <c r="O166" s="212"/>
-      <c r="P166" s="212"/>
-      <c r="Q166" s="213"/>
+      <c r="C166" s="225"/>
+      <c r="D166" s="225"/>
+      <c r="E166" s="225"/>
+      <c r="F166" s="225"/>
+      <c r="G166" s="225"/>
+      <c r="H166" s="225"/>
+      <c r="I166" s="225"/>
+      <c r="J166" s="225"/>
+      <c r="K166" s="225"/>
+      <c r="L166" s="225"/>
+      <c r="M166" s="225"/>
+      <c r="N166" s="225"/>
+      <c r="O166" s="225"/>
+      <c r="P166" s="225"/>
+      <c r="Q166" s="226"/>
     </row>
     <row r="167" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B167" s="211"/>
-      <c r="C167" s="212"/>
-      <c r="D167" s="212"/>
-      <c r="E167" s="212"/>
-      <c r="F167" s="212"/>
-      <c r="G167" s="212"/>
-      <c r="H167" s="212"/>
-      <c r="I167" s="212"/>
-      <c r="J167" s="212"/>
-      <c r="K167" s="212"/>
-      <c r="L167" s="212"/>
-      <c r="M167" s="212"/>
-      <c r="N167" s="212"/>
-      <c r="O167" s="212"/>
-      <c r="P167" s="212"/>
-      <c r="Q167" s="213"/>
+      <c r="B167" s="224"/>
+      <c r="C167" s="225"/>
+      <c r="D167" s="225"/>
+      <c r="E167" s="225"/>
+      <c r="F167" s="225"/>
+      <c r="G167" s="225"/>
+      <c r="H167" s="225"/>
+      <c r="I167" s="225"/>
+      <c r="J167" s="225"/>
+      <c r="K167" s="225"/>
+      <c r="L167" s="225"/>
+      <c r="M167" s="225"/>
+      <c r="N167" s="225"/>
+      <c r="O167" s="225"/>
+      <c r="P167" s="225"/>
+      <c r="Q167" s="226"/>
     </row>
     <row r="168" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B168" s="211"/>
-      <c r="C168" s="212"/>
-      <c r="D168" s="212"/>
-      <c r="E168" s="212"/>
-      <c r="F168" s="212"/>
-      <c r="G168" s="212"/>
-      <c r="H168" s="212"/>
-      <c r="I168" s="212"/>
-      <c r="J168" s="212"/>
-      <c r="K168" s="212"/>
-      <c r="L168" s="212"/>
-      <c r="M168" s="212"/>
-      <c r="N168" s="212"/>
-      <c r="O168" s="212"/>
-      <c r="P168" s="212"/>
-      <c r="Q168" s="213"/>
+      <c r="B168" s="224"/>
+      <c r="C168" s="225"/>
+      <c r="D168" s="225"/>
+      <c r="E168" s="225"/>
+      <c r="F168" s="225"/>
+      <c r="G168" s="225"/>
+      <c r="H168" s="225"/>
+      <c r="I168" s="225"/>
+      <c r="J168" s="225"/>
+      <c r="K168" s="225"/>
+      <c r="L168" s="225"/>
+      <c r="M168" s="225"/>
+      <c r="N168" s="225"/>
+      <c r="O168" s="225"/>
+      <c r="P168" s="225"/>
+      <c r="Q168" s="226"/>
     </row>
     <row r="169" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B169" s="214"/>
-      <c r="C169" s="215"/>
-      <c r="D169" s="215"/>
-      <c r="E169" s="215"/>
-      <c r="F169" s="215"/>
-      <c r="G169" s="215"/>
-      <c r="H169" s="215"/>
-      <c r="I169" s="215"/>
-      <c r="J169" s="215"/>
-      <c r="K169" s="215"/>
-      <c r="L169" s="215"/>
-      <c r="M169" s="215"/>
-      <c r="N169" s="215"/>
-      <c r="O169" s="215"/>
-      <c r="P169" s="215"/>
-      <c r="Q169" s="216"/>
+      <c r="B169" s="227"/>
+      <c r="C169" s="228"/>
+      <c r="D169" s="228"/>
+      <c r="E169" s="228"/>
+      <c r="F169" s="228"/>
+      <c r="G169" s="228"/>
+      <c r="H169" s="228"/>
+      <c r="I169" s="228"/>
+      <c r="J169" s="228"/>
+      <c r="K169" s="228"/>
+      <c r="L169" s="228"/>
+      <c r="M169" s="228"/>
+      <c r="N169" s="228"/>
+      <c r="O169" s="228"/>
+      <c r="P169" s="228"/>
+      <c r="Q169" s="229"/>
     </row>
     <row r="170" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B170" s="35"/>
@@ -9164,24 +9140,24 @@
       <c r="Q171" s="35"/>
     </row>
     <row r="173" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B173" s="218" t="s">
+      <c r="B173" s="215" t="s">
         <v>104</v>
       </c>
-      <c r="C173" s="219"/>
-      <c r="D173" s="219"/>
-      <c r="E173" s="219"/>
-      <c r="F173" s="219"/>
-      <c r="G173" s="219"/>
-      <c r="H173" s="219"/>
-      <c r="I173" s="219"/>
-      <c r="J173" s="219"/>
-      <c r="K173" s="219"/>
-      <c r="L173" s="219"/>
-      <c r="M173" s="219"/>
-      <c r="N173" s="219"/>
-      <c r="O173" s="219"/>
-      <c r="P173" s="219"/>
-      <c r="Q173" s="219"/>
+      <c r="C173" s="216"/>
+      <c r="D173" s="216"/>
+      <c r="E173" s="216"/>
+      <c r="F173" s="216"/>
+      <c r="G173" s="216"/>
+      <c r="H173" s="216"/>
+      <c r="I173" s="216"/>
+      <c r="J173" s="216"/>
+      <c r="K173" s="216"/>
+      <c r="L173" s="216"/>
+      <c r="M173" s="216"/>
+      <c r="N173" s="216"/>
+      <c r="O173" s="216"/>
+      <c r="P173" s="216"/>
+      <c r="Q173" s="216"/>
     </row>
     <row r="174" spans="2:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B174" s="97" t="s">
@@ -9232,10 +9208,10 @@
       </c>
     </row>
     <row r="175" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B175" s="223" t="s">
+      <c r="B175" s="218" t="s">
         <v>110</v>
       </c>
-      <c r="C175" s="220" t="s">
+      <c r="C175" s="214" t="s">
         <v>29</v>
       </c>
       <c r="D175" s="117" t="s">
@@ -9284,8 +9260,8 @@
       </c>
     </row>
     <row r="176" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B176" s="224"/>
-      <c r="C176" s="220"/>
+      <c r="B176" s="219"/>
+      <c r="C176" s="214"/>
       <c r="D176" s="117" t="s">
         <v>22</v>
       </c>
@@ -9350,23 +9326,23 @@
     </row>
     <row r="185" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="186" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B186" s="231" t="s">
+      <c r="B186" s="232" t="s">
         <v>112</v>
       </c>
-      <c r="C186" s="232"/>
-      <c r="D186" s="232"/>
-      <c r="E186" s="232"/>
-      <c r="F186" s="232"/>
-      <c r="G186" s="232"/>
-      <c r="H186" s="232"/>
-      <c r="I186" s="232"/>
-      <c r="J186" s="232"/>
-      <c r="K186" s="232"/>
-      <c r="L186" s="232"/>
-      <c r="M186" s="232"/>
-      <c r="N186" s="232"/>
-      <c r="O186" s="232"/>
-      <c r="P186" s="232"/>
+      <c r="C186" s="233"/>
+      <c r="D186" s="233"/>
+      <c r="E186" s="233"/>
+      <c r="F186" s="233"/>
+      <c r="G186" s="233"/>
+      <c r="H186" s="233"/>
+      <c r="I186" s="233"/>
+      <c r="J186" s="233"/>
+      <c r="K186" s="233"/>
+      <c r="L186" s="233"/>
+      <c r="M186" s="233"/>
+      <c r="N186" s="233"/>
+      <c r="O186" s="233"/>
+      <c r="P186" s="233"/>
     </row>
     <row r="187" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B187" s="97" t="s">
@@ -9414,10 +9390,10 @@
       </c>
     </row>
     <row r="188" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B188" s="233" t="s">
+      <c r="B188" s="234" t="s">
         <v>114</v>
       </c>
-      <c r="C188" s="220" t="s">
+      <c r="C188" s="214" t="s">
         <v>81</v>
       </c>
       <c r="D188" s="117" t="s">
@@ -9463,8 +9439,8 @@
       </c>
     </row>
     <row r="189" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B189" s="233"/>
-      <c r="C189" s="220"/>
+      <c r="B189" s="234"/>
+      <c r="C189" s="214"/>
       <c r="D189" s="117" t="s">
         <v>22</v>
       </c>
@@ -9512,6 +9488,104 @@
     </row>
   </sheetData>
   <mergeCells count="122">
+    <mergeCell ref="B160:P160"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="B166:Q169"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="C145:C146"/>
+    <mergeCell ref="B149:Q152"/>
+    <mergeCell ref="B124:Q127"/>
+    <mergeCell ref="B134:P134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="B141:P141"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="B105:S105"/>
+    <mergeCell ref="B106:S109"/>
+    <mergeCell ref="B118:P118"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="O119:Q119"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="O120:Q121"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="R101:S101"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="R102:S103"/>
+    <mergeCell ref="B96:S96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="R97:S97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="R98:S99"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="R94:S95"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="R89:S89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="R90:S91"/>
+    <mergeCell ref="B100:S100"/>
+    <mergeCell ref="R86:S87"/>
+    <mergeCell ref="B80:S80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="R82:S83"/>
+    <mergeCell ref="B92:S92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="B88:S88"/>
+    <mergeCell ref="B173:Q173"/>
+    <mergeCell ref="R72:S73"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="R64:S65"/>
+    <mergeCell ref="R62:S63"/>
+    <mergeCell ref="R66:S67"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="R68:S71"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B84:S84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="R85:S85"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B24:P27"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="B43:Q46"/>
+    <mergeCell ref="B56:S56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="R58:S61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="R74:S79"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
     <mergeCell ref="B186:P186"/>
     <mergeCell ref="C187:D187"/>
     <mergeCell ref="B188:B189"/>
@@ -9536,104 +9610,6 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C18:C19"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B24:P27"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="B43:Q46"/>
-    <mergeCell ref="B56:S56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="R58:S61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="R74:S79"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="B88:S88"/>
-    <mergeCell ref="B173:Q173"/>
-    <mergeCell ref="R72:S73"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="R64:S65"/>
-    <mergeCell ref="R62:S63"/>
-    <mergeCell ref="R66:S67"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="R68:S71"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="B84:S84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="R85:S85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="R86:S87"/>
-    <mergeCell ref="B80:S80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="R82:S83"/>
-    <mergeCell ref="B92:S92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="R94:S95"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="R89:S89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="R90:S91"/>
-    <mergeCell ref="B100:S100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="R101:S101"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="R102:S103"/>
-    <mergeCell ref="B96:S96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="R97:S97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="R98:S99"/>
-    <mergeCell ref="B124:Q127"/>
-    <mergeCell ref="B134:P134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="B141:P141"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="B105:S105"/>
-    <mergeCell ref="B106:S109"/>
-    <mergeCell ref="B118:P118"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="O119:Q119"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="O120:Q121"/>
-    <mergeCell ref="B160:P160"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="B166:Q169"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="C145:C146"/>
-    <mergeCell ref="B149:Q152"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9670,33 +9646,33 @@
   </cols>
   <sheetData>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="219" t="s">
+      <c r="B9" s="216" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="219"/>
-      <c r="D9" s="219"/>
-      <c r="E9" s="219"/>
-      <c r="F9" s="219"/>
-      <c r="G9" s="219"/>
-      <c r="H9" s="219"/>
-      <c r="I9" s="219"/>
-      <c r="J9" s="219"/>
-      <c r="K9" s="219"/>
-      <c r="L9" s="219"/>
-      <c r="M9" s="219"/>
-      <c r="N9" s="219"/>
-      <c r="O9" s="219"/>
-      <c r="P9" s="219"/>
-      <c r="Q9" s="219"/>
+      <c r="C9" s="216"/>
+      <c r="D9" s="216"/>
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="216"/>
+      <c r="H9" s="216"/>
+      <c r="I9" s="216"/>
+      <c r="J9" s="216"/>
+      <c r="K9" s="216"/>
+      <c r="L9" s="216"/>
+      <c r="M9" s="216"/>
+      <c r="N9" s="216"/>
+      <c r="O9" s="216"/>
+      <c r="P9" s="216"/>
+      <c r="Q9" s="216"/>
     </row>
     <row r="10" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="298" t="s">
+      <c r="C10" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="298"/>
+      <c r="D10" s="303"/>
       <c r="E10" s="8" t="s">
         <v>3</v>
       </c>
@@ -9736,10 +9712,10 @@
       <c r="Q10" s="17"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="244" t="s">
+      <c r="B11" s="239" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="244" t="s">
+      <c r="C11" s="239" t="s">
         <v>110</v>
       </c>
       <c r="D11" s="53" t="s">
@@ -9787,8 +9763,8 @@
       <c r="Q11" s="49"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="244"/>
-      <c r="C12" s="244"/>
+      <c r="B12" s="239"/>
+      <c r="C12" s="239"/>
       <c r="D12" s="53" t="s">
         <v>22</v>
       </c>
@@ -9834,10 +9810,10 @@
       <c r="Q12" s="49"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="244" t="s">
+      <c r="B13" s="239" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="244" t="s">
+      <c r="C13" s="239" t="s">
         <v>110</v>
       </c>
       <c r="D13" s="53" t="s">
@@ -9885,8 +9861,8 @@
       <c r="Q13" s="49"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="244"/>
-      <c r="C14" s="244"/>
+      <c r="B14" s="239"/>
+      <c r="C14" s="239"/>
       <c r="D14" s="53" t="s">
         <v>22</v>
       </c>
@@ -9932,10 +9908,10 @@
       <c r="Q14" s="49"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="281" t="s">
+      <c r="B15" s="237" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="244" t="s">
+      <c r="C15" s="239" t="s">
         <v>110</v>
       </c>
       <c r="D15" s="53" t="s">
@@ -9983,8 +9959,8 @@
       <c r="Q15" s="49"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="281"/>
-      <c r="C16" s="244"/>
+      <c r="B16" s="237"/>
+      <c r="C16" s="239"/>
       <c r="D16" s="53" t="s">
         <v>22</v>
       </c>
@@ -10030,10 +10006,10 @@
       <c r="Q16" s="49"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="244" t="s">
+      <c r="B17" s="239" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="244" t="s">
+      <c r="C17" s="239" t="s">
         <v>110</v>
       </c>
       <c r="D17" s="53" t="s">
@@ -10081,8 +10057,8 @@
       <c r="Q17" s="49"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="244"/>
-      <c r="C18" s="244"/>
+      <c r="B18" s="239"/>
+      <c r="C18" s="239"/>
       <c r="D18" s="53" t="s">
         <v>22</v>
       </c>
@@ -10145,103 +10121,103 @@
       <c r="Q19" s="34"/>
     </row>
     <row r="20" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="287" t="s">
+      <c r="B20" s="306" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="288"/>
-      <c r="D20" s="288"/>
-      <c r="E20" s="288"/>
-      <c r="F20" s="288"/>
-      <c r="G20" s="288"/>
-      <c r="H20" s="288"/>
-      <c r="I20" s="288"/>
-      <c r="J20" s="288"/>
-      <c r="K20" s="288"/>
-      <c r="L20" s="288"/>
-      <c r="M20" s="288"/>
-      <c r="N20" s="288"/>
-      <c r="O20" s="288"/>
-      <c r="P20" s="288"/>
-      <c r="Q20" s="288"/>
-      <c r="R20" s="289"/>
+      <c r="C20" s="307"/>
+      <c r="D20" s="307"/>
+      <c r="E20" s="307"/>
+      <c r="F20" s="307"/>
+      <c r="G20" s="307"/>
+      <c r="H20" s="307"/>
+      <c r="I20" s="307"/>
+      <c r="J20" s="307"/>
+      <c r="K20" s="307"/>
+      <c r="L20" s="307"/>
+      <c r="M20" s="307"/>
+      <c r="N20" s="307"/>
+      <c r="O20" s="307"/>
+      <c r="P20" s="307"/>
+      <c r="Q20" s="307"/>
+      <c r="R20" s="308"/>
     </row>
     <row r="21" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="290" t="s">
+      <c r="B21" s="309" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="291"/>
-      <c r="D21" s="291"/>
-      <c r="E21" s="291"/>
-      <c r="F21" s="291"/>
-      <c r="G21" s="291"/>
-      <c r="H21" s="291"/>
-      <c r="I21" s="291"/>
-      <c r="J21" s="291"/>
-      <c r="K21" s="291"/>
-      <c r="L21" s="291"/>
-      <c r="M21" s="291"/>
-      <c r="N21" s="291"/>
-      <c r="O21" s="291"/>
-      <c r="P21" s="291"/>
-      <c r="Q21" s="291"/>
-      <c r="R21" s="292"/>
+      <c r="C21" s="310"/>
+      <c r="D21" s="310"/>
+      <c r="E21" s="310"/>
+      <c r="F21" s="310"/>
+      <c r="G21" s="310"/>
+      <c r="H21" s="310"/>
+      <c r="I21" s="310"/>
+      <c r="J21" s="310"/>
+      <c r="K21" s="310"/>
+      <c r="L21" s="310"/>
+      <c r="M21" s="310"/>
+      <c r="N21" s="310"/>
+      <c r="O21" s="310"/>
+      <c r="P21" s="310"/>
+      <c r="Q21" s="310"/>
+      <c r="R21" s="311"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B22" s="293"/>
-      <c r="C22" s="238"/>
-      <c r="D22" s="238"/>
-      <c r="E22" s="238"/>
-      <c r="F22" s="238"/>
-      <c r="G22" s="238"/>
-      <c r="H22" s="238"/>
-      <c r="I22" s="238"/>
-      <c r="J22" s="238"/>
-      <c r="K22" s="238"/>
-      <c r="L22" s="238"/>
-      <c r="M22" s="238"/>
-      <c r="N22" s="238"/>
-      <c r="O22" s="238"/>
-      <c r="P22" s="238"/>
-      <c r="Q22" s="238"/>
-      <c r="R22" s="294"/>
+      <c r="B22" s="312"/>
+      <c r="C22" s="282"/>
+      <c r="D22" s="282"/>
+      <c r="E22" s="282"/>
+      <c r="F22" s="282"/>
+      <c r="G22" s="282"/>
+      <c r="H22" s="282"/>
+      <c r="I22" s="282"/>
+      <c r="J22" s="282"/>
+      <c r="K22" s="282"/>
+      <c r="L22" s="282"/>
+      <c r="M22" s="282"/>
+      <c r="N22" s="282"/>
+      <c r="O22" s="282"/>
+      <c r="P22" s="282"/>
+      <c r="Q22" s="282"/>
+      <c r="R22" s="313"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B23" s="293"/>
-      <c r="C23" s="238"/>
-      <c r="D23" s="238"/>
-      <c r="E23" s="238"/>
-      <c r="F23" s="238"/>
-      <c r="G23" s="238"/>
-      <c r="H23" s="238"/>
-      <c r="I23" s="238"/>
-      <c r="J23" s="238"/>
-      <c r="K23" s="238"/>
-      <c r="L23" s="238"/>
-      <c r="M23" s="238"/>
-      <c r="N23" s="238"/>
-      <c r="O23" s="238"/>
-      <c r="P23" s="238"/>
-      <c r="Q23" s="238"/>
-      <c r="R23" s="294"/>
+      <c r="B23" s="312"/>
+      <c r="C23" s="282"/>
+      <c r="D23" s="282"/>
+      <c r="E23" s="282"/>
+      <c r="F23" s="282"/>
+      <c r="G23" s="282"/>
+      <c r="H23" s="282"/>
+      <c r="I23" s="282"/>
+      <c r="J23" s="282"/>
+      <c r="K23" s="282"/>
+      <c r="L23" s="282"/>
+      <c r="M23" s="282"/>
+      <c r="N23" s="282"/>
+      <c r="O23" s="282"/>
+      <c r="P23" s="282"/>
+      <c r="Q23" s="282"/>
+      <c r="R23" s="313"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B24" s="295"/>
-      <c r="C24" s="296"/>
-      <c r="D24" s="296"/>
-      <c r="E24" s="296"/>
-      <c r="F24" s="296"/>
-      <c r="G24" s="296"/>
-      <c r="H24" s="296"/>
-      <c r="I24" s="296"/>
-      <c r="J24" s="296"/>
-      <c r="K24" s="296"/>
-      <c r="L24" s="296"/>
-      <c r="M24" s="296"/>
-      <c r="N24" s="296"/>
-      <c r="O24" s="296"/>
-      <c r="P24" s="296"/>
-      <c r="Q24" s="296"/>
-      <c r="R24" s="297"/>
+      <c r="B24" s="314"/>
+      <c r="C24" s="315"/>
+      <c r="D24" s="315"/>
+      <c r="E24" s="315"/>
+      <c r="F24" s="315"/>
+      <c r="G24" s="315"/>
+      <c r="H24" s="315"/>
+      <c r="I24" s="315"/>
+      <c r="J24" s="315"/>
+      <c r="K24" s="315"/>
+      <c r="L24" s="315"/>
+      <c r="M24" s="315"/>
+      <c r="N24" s="315"/>
+      <c r="O24" s="315"/>
+      <c r="P24" s="315"/>
+      <c r="Q24" s="315"/>
+      <c r="R24" s="316"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B25" s="27"/>
@@ -10397,34 +10373,34 @@
       <c r="Q33" s="34"/>
     </row>
     <row r="34" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B34" s="283" t="s">
+      <c r="B34" s="240" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="283"/>
-      <c r="D34" s="283"/>
-      <c r="E34" s="283"/>
-      <c r="F34" s="283"/>
-      <c r="G34" s="283"/>
-      <c r="H34" s="283"/>
-      <c r="I34" s="283"/>
-      <c r="J34" s="283"/>
-      <c r="K34" s="283"/>
-      <c r="L34" s="283"/>
-      <c r="M34" s="283"/>
-      <c r="N34" s="283"/>
-      <c r="O34" s="283"/>
-      <c r="P34" s="283"/>
-      <c r="Q34" s="283"/>
-      <c r="R34" s="283"/>
+      <c r="C34" s="240"/>
+      <c r="D34" s="240"/>
+      <c r="E34" s="240"/>
+      <c r="F34" s="240"/>
+      <c r="G34" s="240"/>
+      <c r="H34" s="240"/>
+      <c r="I34" s="240"/>
+      <c r="J34" s="240"/>
+      <c r="K34" s="240"/>
+      <c r="L34" s="240"/>
+      <c r="M34" s="240"/>
+      <c r="N34" s="240"/>
+      <c r="O34" s="240"/>
+      <c r="P34" s="240"/>
+      <c r="Q34" s="240"/>
+      <c r="R34" s="240"/>
     </row>
     <row r="35" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="298" t="s">
+      <c r="C35" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="298"/>
+      <c r="D35" s="303"/>
       <c r="E35" s="127" t="s">
         <v>125</v>
       </c>
@@ -10463,10 +10439,10 @@
       <c r="R35" s="217"/>
     </row>
     <row r="36" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="284" t="s">
+      <c r="B36" s="241" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="244" t="s">
+      <c r="C36" s="239" t="s">
         <v>110</v>
       </c>
       <c r="D36" s="53" t="s">
@@ -10506,15 +10482,15 @@
         <v>91</v>
       </c>
       <c r="O36" s="53"/>
-      <c r="P36" s="266" t="s">
+      <c r="P36" s="242" t="s">
         <v>129</v>
       </c>
-      <c r="Q36" s="311"/>
-      <c r="R36" s="267"/>
+      <c r="Q36" s="298"/>
+      <c r="R36" s="243"/>
     </row>
     <row r="37" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B37" s="284"/>
-      <c r="C37" s="244"/>
+      <c r="B37" s="241"/>
+      <c r="C37" s="239"/>
       <c r="D37" s="53" t="s">
         <v>22</v>
       </c>
@@ -10552,9 +10528,9 @@
         <v>91</v>
       </c>
       <c r="O37" s="53"/>
-      <c r="P37" s="312"/>
-      <c r="Q37" s="313"/>
-      <c r="R37" s="314"/>
+      <c r="P37" s="299"/>
+      <c r="Q37" s="300"/>
+      <c r="R37" s="301"/>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B38" s="123" t="s">
@@ -10567,7 +10543,7 @@
         <v>17</v>
       </c>
       <c r="E38" s="150">
-        <v>4100</v>
+        <v>4150</v>
       </c>
       <c r="F38" s="150" t="s">
         <v>131</v>
@@ -10580,30 +10556,30 @@
       </c>
       <c r="I38" s="194">
         <f t="shared" si="2"/>
-        <v>4218</v>
+        <v>4268</v>
       </c>
       <c r="J38" s="150">
         <v>200</v>
       </c>
       <c r="K38" s="194">
         <f t="shared" si="3"/>
-        <v>4418</v>
+        <v>4468</v>
       </c>
       <c r="L38" s="107">
         <v>35</v>
       </c>
       <c r="M38" s="208" t="s">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="N38" s="20" t="s">
         <v>43</v>
       </c>
       <c r="O38" s="53"/>
-      <c r="P38" s="304" t="s">
+      <c r="P38" s="295" t="s">
         <v>132</v>
       </c>
-      <c r="Q38" s="305"/>
-      <c r="R38" s="306"/>
+      <c r="Q38" s="296"/>
+      <c r="R38" s="297"/>
     </row>
     <row r="39" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="125" t="s">
@@ -10649,11 +10625,11 @@
         <v>91</v>
       </c>
       <c r="O39" s="53"/>
-      <c r="P39" s="304" t="s">
+      <c r="P39" s="295" t="s">
         <v>132</v>
       </c>
-      <c r="Q39" s="305"/>
-      <c r="R39" s="306"/>
+      <c r="Q39" s="296"/>
+      <c r="R39" s="297"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="42"/>
@@ -10696,86 +10672,86 @@
       <c r="S41" s="7"/>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B42" s="211" t="s">
+      <c r="B42" s="224" t="s">
         <v>33</v>
       </c>
-      <c r="C42" s="211"/>
-      <c r="D42" s="211"/>
-      <c r="E42" s="211"/>
-      <c r="F42" s="211"/>
-      <c r="G42" s="211"/>
-      <c r="H42" s="211"/>
-      <c r="I42" s="211"/>
-      <c r="J42" s="211"/>
-      <c r="K42" s="211"/>
-      <c r="L42" s="211"/>
-      <c r="M42" s="211"/>
-      <c r="N42" s="211"/>
-      <c r="O42" s="211"/>
-      <c r="P42" s="211"/>
-      <c r="Q42" s="211"/>
-      <c r="R42" s="211"/>
-      <c r="S42" s="211"/>
+      <c r="C42" s="224"/>
+      <c r="D42" s="224"/>
+      <c r="E42" s="224"/>
+      <c r="F42" s="224"/>
+      <c r="G42" s="224"/>
+      <c r="H42" s="224"/>
+      <c r="I42" s="224"/>
+      <c r="J42" s="224"/>
+      <c r="K42" s="224"/>
+      <c r="L42" s="224"/>
+      <c r="M42" s="224"/>
+      <c r="N42" s="224"/>
+      <c r="O42" s="224"/>
+      <c r="P42" s="224"/>
+      <c r="Q42" s="224"/>
+      <c r="R42" s="224"/>
+      <c r="S42" s="224"/>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B43" s="211"/>
-      <c r="C43" s="211"/>
-      <c r="D43" s="211"/>
-      <c r="E43" s="211"/>
-      <c r="F43" s="211"/>
-      <c r="G43" s="211"/>
-      <c r="H43" s="211"/>
-      <c r="I43" s="211"/>
-      <c r="J43" s="211"/>
-      <c r="K43" s="211"/>
-      <c r="L43" s="211"/>
-      <c r="M43" s="211"/>
-      <c r="N43" s="211"/>
-      <c r="O43" s="211"/>
-      <c r="P43" s="211"/>
-      <c r="Q43" s="211"/>
-      <c r="R43" s="211"/>
-      <c r="S43" s="211"/>
+      <c r="B43" s="224"/>
+      <c r="C43" s="224"/>
+      <c r="D43" s="224"/>
+      <c r="E43" s="224"/>
+      <c r="F43" s="224"/>
+      <c r="G43" s="224"/>
+      <c r="H43" s="224"/>
+      <c r="I43" s="224"/>
+      <c r="J43" s="224"/>
+      <c r="K43" s="224"/>
+      <c r="L43" s="224"/>
+      <c r="M43" s="224"/>
+      <c r="N43" s="224"/>
+      <c r="O43" s="224"/>
+      <c r="P43" s="224"/>
+      <c r="Q43" s="224"/>
+      <c r="R43" s="224"/>
+      <c r="S43" s="224"/>
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B44" s="211"/>
-      <c r="C44" s="211"/>
-      <c r="D44" s="211"/>
-      <c r="E44" s="211"/>
-      <c r="F44" s="211"/>
-      <c r="G44" s="211"/>
-      <c r="H44" s="211"/>
-      <c r="I44" s="211"/>
-      <c r="J44" s="211"/>
-      <c r="K44" s="211"/>
-      <c r="L44" s="211"/>
-      <c r="M44" s="211"/>
-      <c r="N44" s="211"/>
-      <c r="O44" s="211"/>
-      <c r="P44" s="211"/>
-      <c r="Q44" s="211"/>
-      <c r="R44" s="211"/>
-      <c r="S44" s="211"/>
+      <c r="B44" s="224"/>
+      <c r="C44" s="224"/>
+      <c r="D44" s="224"/>
+      <c r="E44" s="224"/>
+      <c r="F44" s="224"/>
+      <c r="G44" s="224"/>
+      <c r="H44" s="224"/>
+      <c r="I44" s="224"/>
+      <c r="J44" s="224"/>
+      <c r="K44" s="224"/>
+      <c r="L44" s="224"/>
+      <c r="M44" s="224"/>
+      <c r="N44" s="224"/>
+      <c r="O44" s="224"/>
+      <c r="P44" s="224"/>
+      <c r="Q44" s="224"/>
+      <c r="R44" s="224"/>
+      <c r="S44" s="224"/>
     </row>
     <row r="45" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B45" s="214"/>
-      <c r="C45" s="214"/>
-      <c r="D45" s="214"/>
-      <c r="E45" s="214"/>
-      <c r="F45" s="214"/>
-      <c r="G45" s="214"/>
-      <c r="H45" s="214"/>
-      <c r="I45" s="214"/>
-      <c r="J45" s="214"/>
-      <c r="K45" s="214"/>
-      <c r="L45" s="214"/>
-      <c r="M45" s="214"/>
-      <c r="N45" s="214"/>
-      <c r="O45" s="214"/>
-      <c r="P45" s="214"/>
-      <c r="Q45" s="214"/>
-      <c r="R45" s="214"/>
-      <c r="S45" s="214"/>
+      <c r="B45" s="227"/>
+      <c r="C45" s="227"/>
+      <c r="D45" s="227"/>
+      <c r="E45" s="227"/>
+      <c r="F45" s="227"/>
+      <c r="G45" s="227"/>
+      <c r="H45" s="227"/>
+      <c r="I45" s="227"/>
+      <c r="J45" s="227"/>
+      <c r="K45" s="227"/>
+      <c r="L45" s="227"/>
+      <c r="M45" s="227"/>
+      <c r="N45" s="227"/>
+      <c r="O45" s="227"/>
+      <c r="P45" s="227"/>
+      <c r="Q45" s="227"/>
+      <c r="R45" s="227"/>
+      <c r="S45" s="227"/>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B46" s="42"/>
@@ -10933,24 +10909,24 @@
       <c r="R54" s="126"/>
     </row>
     <row r="55" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B55" s="231" t="s">
+      <c r="B55" s="232" t="s">
         <v>135</v>
       </c>
-      <c r="C55" s="231"/>
-      <c r="D55" s="231"/>
-      <c r="E55" s="231"/>
-      <c r="F55" s="231"/>
-      <c r="G55" s="231"/>
-      <c r="H55" s="231"/>
-      <c r="I55" s="231"/>
-      <c r="J55" s="231"/>
-      <c r="K55" s="231"/>
-      <c r="L55" s="231"/>
-      <c r="M55" s="231"/>
-      <c r="N55" s="231"/>
-      <c r="O55" s="231"/>
-      <c r="P55" s="231"/>
-      <c r="Q55" s="231"/>
+      <c r="C55" s="232"/>
+      <c r="D55" s="232"/>
+      <c r="E55" s="232"/>
+      <c r="F55" s="232"/>
+      <c r="G55" s="232"/>
+      <c r="H55" s="232"/>
+      <c r="I55" s="232"/>
+      <c r="J55" s="232"/>
+      <c r="K55" s="232"/>
+      <c r="L55" s="232"/>
+      <c r="M55" s="232"/>
+      <c r="N55" s="232"/>
+      <c r="O55" s="232"/>
+      <c r="P55" s="232"/>
+      <c r="Q55" s="232"/>
     </row>
     <row r="56" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B56" s="97" t="s">
@@ -10999,10 +10975,10 @@
       <c r="Q56" s="121"/>
     </row>
     <row r="57" spans="2:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="299" t="s">
+      <c r="B57" s="294" t="s">
         <v>139</v>
       </c>
-      <c r="C57" s="300" t="s">
+      <c r="C57" s="302" t="s">
         <v>110</v>
       </c>
       <c r="D57" s="141" t="s">
@@ -11044,14 +11020,14 @@
       <c r="O57" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P57" s="302" t="s">
+      <c r="P57" s="288" t="s">
         <v>73</v>
       </c>
       <c r="Q57" s="141"/>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B58" s="299"/>
-      <c r="C58" s="300"/>
+      <c r="B58" s="294"/>
+      <c r="C58" s="302"/>
       <c r="D58" s="141" t="s">
         <v>22</v>
       </c>
@@ -11091,14 +11067,14 @@
       <c r="O58" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P58" s="303"/>
+      <c r="P58" s="289"/>
       <c r="Q58" s="141"/>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B59" s="299" t="s">
+      <c r="B59" s="294" t="s">
         <v>140</v>
       </c>
-      <c r="C59" s="300" t="s">
+      <c r="C59" s="302" t="s">
         <v>110</v>
       </c>
       <c r="D59" s="141" t="s">
@@ -11140,12 +11116,12 @@
       <c r="O59" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P59" s="303"/>
+      <c r="P59" s="289"/>
       <c r="Q59" s="141"/>
     </row>
     <row r="60" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="299"/>
-      <c r="C60" s="300"/>
+      <c r="B60" s="294"/>
+      <c r="C60" s="302"/>
       <c r="D60" s="141" t="s">
         <v>22</v>
       </c>
@@ -11185,14 +11161,14 @@
       <c r="O60" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P60" s="307"/>
+      <c r="P60" s="290"/>
       <c r="Q60" s="141"/>
     </row>
     <row r="61" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="299" t="s">
+      <c r="B61" s="294" t="s">
         <v>141</v>
       </c>
-      <c r="C61" s="300" t="s">
+      <c r="C61" s="302" t="s">
         <v>110</v>
       </c>
       <c r="D61" s="141" t="s">
@@ -11234,14 +11210,14 @@
       <c r="O61" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P61" s="308" t="s">
+      <c r="P61" s="291" t="s">
         <v>59</v>
       </c>
       <c r="Q61" s="141"/>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B62" s="299"/>
-      <c r="C62" s="300"/>
+      <c r="B62" s="294"/>
+      <c r="C62" s="302"/>
       <c r="D62" s="141" t="s">
         <v>22</v>
       </c>
@@ -11281,14 +11257,14 @@
       <c r="O62" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P62" s="309"/>
+      <c r="P62" s="292"/>
       <c r="Q62" s="141"/>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B63" s="299" t="s">
+      <c r="B63" s="294" t="s">
         <v>143</v>
       </c>
-      <c r="C63" s="300" t="s">
+      <c r="C63" s="302" t="s">
         <v>110</v>
       </c>
       <c r="D63" s="141" t="s">
@@ -11330,12 +11306,12 @@
       <c r="O63" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P63" s="309"/>
+      <c r="P63" s="292"/>
       <c r="Q63" s="141"/>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B64" s="299"/>
-      <c r="C64" s="300"/>
+      <c r="B64" s="294"/>
+      <c r="C64" s="302"/>
       <c r="D64" s="141" t="s">
         <v>22</v>
       </c>
@@ -11375,28 +11351,28 @@
       <c r="O64" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P64" s="310"/>
+      <c r="P64" s="293"/>
       <c r="Q64" s="141"/>
     </row>
     <row r="65" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="229" t="s">
+      <c r="B65" s="212" t="s">
         <v>144</v>
       </c>
-      <c r="C65" s="229"/>
-      <c r="D65" s="218"/>
-      <c r="E65" s="218"/>
-      <c r="F65" s="229"/>
-      <c r="G65" s="218"/>
-      <c r="H65" s="218"/>
-      <c r="I65" s="229"/>
-      <c r="J65" s="218"/>
-      <c r="K65" s="218"/>
-      <c r="L65" s="218"/>
-      <c r="M65" s="229"/>
-      <c r="N65" s="218"/>
-      <c r="O65" s="218"/>
-      <c r="P65" s="218"/>
-      <c r="Q65" s="218"/>
+      <c r="C65" s="212"/>
+      <c r="D65" s="215"/>
+      <c r="E65" s="215"/>
+      <c r="F65" s="212"/>
+      <c r="G65" s="215"/>
+      <c r="H65" s="215"/>
+      <c r="I65" s="212"/>
+      <c r="J65" s="215"/>
+      <c r="K65" s="215"/>
+      <c r="L65" s="215"/>
+      <c r="M65" s="212"/>
+      <c r="N65" s="215"/>
+      <c r="O65" s="215"/>
+      <c r="P65" s="215"/>
+      <c r="Q65" s="215"/>
     </row>
     <row r="66" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B66" s="97" t="s">
@@ -11445,7 +11421,7 @@
       <c r="Q66" s="103"/>
     </row>
     <row r="67" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B67" s="272" t="s">
+      <c r="B67" s="275" t="s">
         <v>145</v>
       </c>
       <c r="C67" s="202" t="s">
@@ -11490,7 +11466,7 @@
       <c r="O67" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P67" s="302" t="s">
+      <c r="P67" s="288" t="s">
         <v>73</v>
       </c>
       <c r="Q67" s="147"/>
@@ -42944,7 +42920,7 @@
       </c>
     </row>
     <row r="68" spans="2:62 3072:12198 12789:15082" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="301"/>
+      <c r="B68" s="304"/>
       <c r="C68" s="202" t="s">
         <v>110</v>
       </c>
@@ -42987,7 +42963,7 @@
       <c r="O68" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P68" s="303"/>
+      <c r="P68" s="289"/>
       <c r="Q68" s="147"/>
       <c r="R68" s="170"/>
       <c r="S68" s="163"/>
@@ -54457,24 +54433,24 @@
       <c r="VHB68" s="156"/>
     </row>
     <row r="69" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B69" s="231" t="s">
+      <c r="B69" s="232" t="s">
         <v>146</v>
       </c>
-      <c r="C69" s="231"/>
-      <c r="D69" s="231"/>
-      <c r="E69" s="231"/>
-      <c r="F69" s="231"/>
-      <c r="G69" s="231"/>
-      <c r="H69" s="231"/>
-      <c r="I69" s="231"/>
-      <c r="J69" s="231"/>
-      <c r="K69" s="231"/>
-      <c r="L69" s="231"/>
-      <c r="M69" s="231"/>
-      <c r="N69" s="231"/>
-      <c r="O69" s="231"/>
-      <c r="P69" s="231"/>
-      <c r="Q69" s="231"/>
+      <c r="C69" s="232"/>
+      <c r="D69" s="232"/>
+      <c r="E69" s="232"/>
+      <c r="F69" s="232"/>
+      <c r="G69" s="232"/>
+      <c r="H69" s="232"/>
+      <c r="I69" s="232"/>
+      <c r="J69" s="232"/>
+      <c r="K69" s="232"/>
+      <c r="L69" s="232"/>
+      <c r="M69" s="232"/>
+      <c r="N69" s="232"/>
+      <c r="O69" s="232"/>
+      <c r="P69" s="232"/>
+      <c r="Q69" s="232"/>
     </row>
     <row r="70" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B70" s="97" t="s">
@@ -54523,7 +54499,7 @@
       <c r="Q70" s="103"/>
     </row>
     <row r="71" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B71" s="272" t="s">
+      <c r="B71" s="275" t="s">
         <v>147</v>
       </c>
       <c r="C71" s="202" t="s">
@@ -54568,13 +54544,13 @@
       <c r="O71" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P71" s="302" t="s">
+      <c r="P71" s="288" t="s">
         <v>73</v>
       </c>
       <c r="Q71" s="147"/>
     </row>
     <row r="72" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B72" s="301"/>
+      <c r="B72" s="304"/>
       <c r="C72" s="202" t="s">
         <v>110</v>
       </c>
@@ -54617,7 +54593,7 @@
       <c r="O72" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P72" s="303"/>
+      <c r="P72" s="289"/>
       <c r="Q72" s="147"/>
     </row>
     <row r="74" spans="2:62 3072:12198 12789:15082" ht="15.6" x14ac:dyDescent="0.3">
@@ -54644,121 +54620,121 @@
       <c r="T74" s="6"/>
     </row>
     <row r="75" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B75" s="276" t="s">
+      <c r="B75" s="250" t="s">
         <v>33</v>
       </c>
-      <c r="C75" s="276"/>
-      <c r="D75" s="276"/>
-      <c r="E75" s="276"/>
-      <c r="F75" s="276"/>
-      <c r="G75" s="276"/>
-      <c r="H75" s="276"/>
-      <c r="I75" s="276"/>
-      <c r="J75" s="276"/>
-      <c r="K75" s="276"/>
-      <c r="L75" s="276"/>
-      <c r="M75" s="276"/>
-      <c r="N75" s="276"/>
-      <c r="O75" s="276"/>
-      <c r="P75" s="276"/>
-      <c r="Q75" s="276"/>
-      <c r="R75" s="276"/>
-      <c r="S75" s="276"/>
-      <c r="T75" s="276"/>
+      <c r="C75" s="250"/>
+      <c r="D75" s="250"/>
+      <c r="E75" s="250"/>
+      <c r="F75" s="250"/>
+      <c r="G75" s="250"/>
+      <c r="H75" s="250"/>
+      <c r="I75" s="250"/>
+      <c r="J75" s="250"/>
+      <c r="K75" s="250"/>
+      <c r="L75" s="250"/>
+      <c r="M75" s="250"/>
+      <c r="N75" s="250"/>
+      <c r="O75" s="250"/>
+      <c r="P75" s="250"/>
+      <c r="Q75" s="250"/>
+      <c r="R75" s="250"/>
+      <c r="S75" s="250"/>
+      <c r="T75" s="250"/>
     </row>
     <row r="76" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B76" s="276"/>
-      <c r="C76" s="276"/>
-      <c r="D76" s="276"/>
-      <c r="E76" s="276"/>
-      <c r="F76" s="276"/>
-      <c r="G76" s="276"/>
-      <c r="H76" s="276"/>
-      <c r="I76" s="276"/>
-      <c r="J76" s="276"/>
-      <c r="K76" s="276"/>
-      <c r="L76" s="276"/>
-      <c r="M76" s="276"/>
-      <c r="N76" s="276"/>
-      <c r="O76" s="276"/>
-      <c r="P76" s="276"/>
-      <c r="Q76" s="276"/>
-      <c r="R76" s="276"/>
-      <c r="S76" s="276"/>
-      <c r="T76" s="276"/>
+      <c r="B76" s="250"/>
+      <c r="C76" s="250"/>
+      <c r="D76" s="250"/>
+      <c r="E76" s="250"/>
+      <c r="F76" s="250"/>
+      <c r="G76" s="250"/>
+      <c r="H76" s="250"/>
+      <c r="I76" s="250"/>
+      <c r="J76" s="250"/>
+      <c r="K76" s="250"/>
+      <c r="L76" s="250"/>
+      <c r="M76" s="250"/>
+      <c r="N76" s="250"/>
+      <c r="O76" s="250"/>
+      <c r="P76" s="250"/>
+      <c r="Q76" s="250"/>
+      <c r="R76" s="250"/>
+      <c r="S76" s="250"/>
+      <c r="T76" s="250"/>
     </row>
     <row r="77" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B77" s="276"/>
-      <c r="C77" s="276"/>
-      <c r="D77" s="276"/>
-      <c r="E77" s="276"/>
-      <c r="F77" s="276"/>
-      <c r="G77" s="276"/>
-      <c r="H77" s="276"/>
-      <c r="I77" s="276"/>
-      <c r="J77" s="276"/>
-      <c r="K77" s="276"/>
-      <c r="L77" s="276"/>
-      <c r="M77" s="276"/>
-      <c r="N77" s="276"/>
-      <c r="O77" s="276"/>
-      <c r="P77" s="276"/>
-      <c r="Q77" s="276"/>
-      <c r="R77" s="276"/>
-      <c r="S77" s="276"/>
-      <c r="T77" s="276"/>
+      <c r="B77" s="250"/>
+      <c r="C77" s="250"/>
+      <c r="D77" s="250"/>
+      <c r="E77" s="250"/>
+      <c r="F77" s="250"/>
+      <c r="G77" s="250"/>
+      <c r="H77" s="250"/>
+      <c r="I77" s="250"/>
+      <c r="J77" s="250"/>
+      <c r="K77" s="250"/>
+      <c r="L77" s="250"/>
+      <c r="M77" s="250"/>
+      <c r="N77" s="250"/>
+      <c r="O77" s="250"/>
+      <c r="P77" s="250"/>
+      <c r="Q77" s="250"/>
+      <c r="R77" s="250"/>
+      <c r="S77" s="250"/>
+      <c r="T77" s="250"/>
     </row>
     <row r="78" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B78" s="276"/>
-      <c r="C78" s="276"/>
-      <c r="D78" s="276"/>
-      <c r="E78" s="276"/>
-      <c r="F78" s="276"/>
-      <c r="G78" s="276"/>
-      <c r="H78" s="276"/>
-      <c r="I78" s="276"/>
-      <c r="J78" s="276"/>
-      <c r="K78" s="276"/>
-      <c r="L78" s="276"/>
-      <c r="M78" s="276"/>
-      <c r="N78" s="276"/>
-      <c r="O78" s="276"/>
-      <c r="P78" s="276"/>
-      <c r="Q78" s="276"/>
-      <c r="R78" s="276"/>
-      <c r="S78" s="276"/>
-      <c r="T78" s="276"/>
+      <c r="B78" s="250"/>
+      <c r="C78" s="250"/>
+      <c r="D78" s="250"/>
+      <c r="E78" s="250"/>
+      <c r="F78" s="250"/>
+      <c r="G78" s="250"/>
+      <c r="H78" s="250"/>
+      <c r="I78" s="250"/>
+      <c r="J78" s="250"/>
+      <c r="K78" s="250"/>
+      <c r="L78" s="250"/>
+      <c r="M78" s="250"/>
+      <c r="N78" s="250"/>
+      <c r="O78" s="250"/>
+      <c r="P78" s="250"/>
+      <c r="Q78" s="250"/>
+      <c r="R78" s="250"/>
+      <c r="S78" s="250"/>
+      <c r="T78" s="250"/>
     </row>
     <row r="87" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B87" s="219" t="s">
+      <c r="B87" s="216" t="s">
         <v>149</v>
       </c>
-      <c r="C87" s="219"/>
-      <c r="D87" s="219"/>
-      <c r="E87" s="219"/>
-      <c r="F87" s="219"/>
-      <c r="G87" s="219"/>
-      <c r="H87" s="219"/>
-      <c r="I87" s="219"/>
-      <c r="J87" s="219"/>
-      <c r="K87" s="219"/>
-      <c r="L87" s="219"/>
-      <c r="M87" s="219"/>
-      <c r="N87" s="219"/>
-      <c r="O87" s="219"/>
-      <c r="P87" s="219"/>
-      <c r="Q87" s="219"/>
-      <c r="R87" s="219"/>
-      <c r="S87" s="219"/>
+      <c r="C87" s="216"/>
+      <c r="D87" s="216"/>
+      <c r="E87" s="216"/>
+      <c r="F87" s="216"/>
+      <c r="G87" s="216"/>
+      <c r="H87" s="216"/>
+      <c r="I87" s="216"/>
+      <c r="J87" s="216"/>
+      <c r="K87" s="216"/>
+      <c r="L87" s="216"/>
+      <c r="M87" s="216"/>
+      <c r="N87" s="216"/>
+      <c r="O87" s="216"/>
+      <c r="P87" s="216"/>
+      <c r="Q87" s="216"/>
+      <c r="R87" s="216"/>
+      <c r="S87" s="216"/>
     </row>
     <row r="88" spans="2:20" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C88" s="298" t="s">
+      <c r="C88" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D88" s="298"/>
+      <c r="D88" s="303"/>
       <c r="E88" s="127" t="s">
         <v>125</v>
       </c>
@@ -54800,10 +54776,10 @@
       <c r="S88" s="217"/>
     </row>
     <row r="89" spans="2:20" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="223" t="s">
+      <c r="B89" s="218" t="s">
         <v>90</v>
       </c>
-      <c r="C89" s="244" t="s">
+      <c r="C89" s="239" t="s">
         <v>110</v>
       </c>
       <c r="D89" s="53" t="s">
@@ -54845,15 +54821,15 @@
         <v>43</v>
       </c>
       <c r="P89" s="53"/>
-      <c r="Q89" s="245" t="s">
+      <c r="Q89" s="246" t="s">
         <v>44</v>
       </c>
-      <c r="R89" s="245"/>
-      <c r="S89" s="245"/>
+      <c r="R89" s="246"/>
+      <c r="S89" s="246"/>
     </row>
     <row r="90" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B90" s="220"/>
-      <c r="C90" s="244"/>
+      <c r="B90" s="214"/>
+      <c r="C90" s="239"/>
       <c r="D90" s="53" t="s">
         <v>22</v>
       </c>
@@ -54893,9 +54869,9 @@
         <v>43</v>
       </c>
       <c r="P90" s="53"/>
-      <c r="Q90" s="245"/>
-      <c r="R90" s="245"/>
-      <c r="S90" s="245"/>
+      <c r="Q90" s="246"/>
+      <c r="R90" s="246"/>
+      <c r="S90" s="246"/>
     </row>
     <row r="92" spans="2:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B92" s="5" t="s">
@@ -54921,111 +54897,111 @@
       <c r="T92" s="6"/>
     </row>
     <row r="93" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B93" s="276" t="s">
+      <c r="B93" s="250" t="s">
         <v>33</v>
       </c>
-      <c r="C93" s="276"/>
-      <c r="D93" s="276"/>
-      <c r="E93" s="276"/>
-      <c r="F93" s="276"/>
-      <c r="G93" s="276"/>
-      <c r="H93" s="276"/>
-      <c r="I93" s="276"/>
-      <c r="J93" s="276"/>
-      <c r="K93" s="276"/>
-      <c r="L93" s="276"/>
-      <c r="M93" s="276"/>
-      <c r="N93" s="276"/>
-      <c r="O93" s="276"/>
-      <c r="P93" s="276"/>
-      <c r="Q93" s="276"/>
-      <c r="R93" s="276"/>
-      <c r="S93" s="276"/>
-      <c r="T93" s="276"/>
+      <c r="C93" s="250"/>
+      <c r="D93" s="250"/>
+      <c r="E93" s="250"/>
+      <c r="F93" s="250"/>
+      <c r="G93" s="250"/>
+      <c r="H93" s="250"/>
+      <c r="I93" s="250"/>
+      <c r="J93" s="250"/>
+      <c r="K93" s="250"/>
+      <c r="L93" s="250"/>
+      <c r="M93" s="250"/>
+      <c r="N93" s="250"/>
+      <c r="O93" s="250"/>
+      <c r="P93" s="250"/>
+      <c r="Q93" s="250"/>
+      <c r="R93" s="250"/>
+      <c r="S93" s="250"/>
+      <c r="T93" s="250"/>
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B94" s="276"/>
-      <c r="C94" s="276"/>
-      <c r="D94" s="276"/>
-      <c r="E94" s="276"/>
-      <c r="F94" s="276"/>
-      <c r="G94" s="276"/>
-      <c r="H94" s="276"/>
-      <c r="I94" s="276"/>
-      <c r="J94" s="276"/>
-      <c r="K94" s="276"/>
-      <c r="L94" s="276"/>
-      <c r="M94" s="276"/>
-      <c r="N94" s="276"/>
-      <c r="O94" s="276"/>
-      <c r="P94" s="276"/>
-      <c r="Q94" s="276"/>
-      <c r="R94" s="276"/>
-      <c r="S94" s="276"/>
-      <c r="T94" s="276"/>
+      <c r="B94" s="250"/>
+      <c r="C94" s="250"/>
+      <c r="D94" s="250"/>
+      <c r="E94" s="250"/>
+      <c r="F94" s="250"/>
+      <c r="G94" s="250"/>
+      <c r="H94" s="250"/>
+      <c r="I94" s="250"/>
+      <c r="J94" s="250"/>
+      <c r="K94" s="250"/>
+      <c r="L94" s="250"/>
+      <c r="M94" s="250"/>
+      <c r="N94" s="250"/>
+      <c r="O94" s="250"/>
+      <c r="P94" s="250"/>
+      <c r="Q94" s="250"/>
+      <c r="R94" s="250"/>
+      <c r="S94" s="250"/>
+      <c r="T94" s="250"/>
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B95" s="276"/>
-      <c r="C95" s="276"/>
-      <c r="D95" s="276"/>
-      <c r="E95" s="276"/>
-      <c r="F95" s="276"/>
-      <c r="G95" s="276"/>
-      <c r="H95" s="276"/>
-      <c r="I95" s="276"/>
-      <c r="J95" s="276"/>
-      <c r="K95" s="276"/>
-      <c r="L95" s="276"/>
-      <c r="M95" s="276"/>
-      <c r="N95" s="276"/>
-      <c r="O95" s="276"/>
-      <c r="P95" s="276"/>
-      <c r="Q95" s="276"/>
-      <c r="R95" s="276"/>
-      <c r="S95" s="276"/>
-      <c r="T95" s="276"/>
+      <c r="B95" s="250"/>
+      <c r="C95" s="250"/>
+      <c r="D95" s="250"/>
+      <c r="E95" s="250"/>
+      <c r="F95" s="250"/>
+      <c r="G95" s="250"/>
+      <c r="H95" s="250"/>
+      <c r="I95" s="250"/>
+      <c r="J95" s="250"/>
+      <c r="K95" s="250"/>
+      <c r="L95" s="250"/>
+      <c r="M95" s="250"/>
+      <c r="N95" s="250"/>
+      <c r="O95" s="250"/>
+      <c r="P95" s="250"/>
+      <c r="Q95" s="250"/>
+      <c r="R95" s="250"/>
+      <c r="S95" s="250"/>
+      <c r="T95" s="250"/>
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B96" s="276"/>
-      <c r="C96" s="276"/>
-      <c r="D96" s="276"/>
-      <c r="E96" s="276"/>
-      <c r="F96" s="276"/>
-      <c r="G96" s="276"/>
-      <c r="H96" s="276"/>
-      <c r="I96" s="276"/>
-      <c r="J96" s="276"/>
-      <c r="K96" s="276"/>
-      <c r="L96" s="276"/>
-      <c r="M96" s="276"/>
-      <c r="N96" s="276"/>
-      <c r="O96" s="276"/>
-      <c r="P96" s="276"/>
-      <c r="Q96" s="276"/>
-      <c r="R96" s="276"/>
-      <c r="S96" s="276"/>
-      <c r="T96" s="276"/>
+      <c r="B96" s="250"/>
+      <c r="C96" s="250"/>
+      <c r="D96" s="250"/>
+      <c r="E96" s="250"/>
+      <c r="F96" s="250"/>
+      <c r="G96" s="250"/>
+      <c r="H96" s="250"/>
+      <c r="I96" s="250"/>
+      <c r="J96" s="250"/>
+      <c r="K96" s="250"/>
+      <c r="L96" s="250"/>
+      <c r="M96" s="250"/>
+      <c r="N96" s="250"/>
+      <c r="O96" s="250"/>
+      <c r="P96" s="250"/>
+      <c r="Q96" s="250"/>
+      <c r="R96" s="250"/>
+      <c r="S96" s="250"/>
+      <c r="T96" s="250"/>
     </row>
     <row r="106" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="107" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B107" s="231" t="s">
+      <c r="B107" s="232" t="s">
         <v>153</v>
       </c>
-      <c r="C107" s="231"/>
-      <c r="D107" s="231"/>
-      <c r="E107" s="231"/>
-      <c r="F107" s="231"/>
-      <c r="G107" s="231"/>
-      <c r="H107" s="231"/>
-      <c r="I107" s="231"/>
-      <c r="J107" s="231"/>
-      <c r="K107" s="231"/>
-      <c r="L107" s="231"/>
-      <c r="M107" s="231"/>
-      <c r="N107" s="231"/>
-      <c r="O107" s="231"/>
-      <c r="P107" s="231"/>
-      <c r="Q107" s="231"/>
+      <c r="C107" s="232"/>
+      <c r="D107" s="232"/>
+      <c r="E107" s="232"/>
+      <c r="F107" s="232"/>
+      <c r="G107" s="232"/>
+      <c r="H107" s="232"/>
+      <c r="I107" s="232"/>
+      <c r="J107" s="232"/>
+      <c r="K107" s="232"/>
+      <c r="L107" s="232"/>
+      <c r="M107" s="232"/>
+      <c r="N107" s="232"/>
+      <c r="O107" s="232"/>
+      <c r="P107" s="232"/>
+      <c r="Q107" s="232"/>
     </row>
     <row r="108" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B108" s="97" t="s">
@@ -55074,10 +55050,10 @@
       <c r="Q108" s="103"/>
     </row>
     <row r="109" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B109" s="286" t="s">
+      <c r="B109" s="305" t="s">
         <v>154</v>
       </c>
-      <c r="C109" s="244" t="s">
+      <c r="C109" s="239" t="s">
         <v>110</v>
       </c>
       <c r="D109" s="53" t="s">
@@ -55124,8 +55100,8 @@
       <c r="Q109" s="104"/>
     </row>
     <row r="110" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B110" s="286"/>
-      <c r="C110" s="244"/>
+      <c r="B110" s="305"/>
+      <c r="C110" s="239"/>
       <c r="D110" s="53" t="s">
         <v>22</v>
       </c>
@@ -55171,24 +55147,24 @@
     </row>
     <row r="119" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="120" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B120" s="231" t="s">
+      <c r="B120" s="232" t="s">
         <v>158</v>
       </c>
-      <c r="C120" s="231"/>
-      <c r="D120" s="231"/>
-      <c r="E120" s="231"/>
-      <c r="F120" s="231"/>
-      <c r="G120" s="231"/>
-      <c r="H120" s="231"/>
-      <c r="I120" s="231"/>
-      <c r="J120" s="231"/>
-      <c r="K120" s="231"/>
-      <c r="L120" s="231"/>
-      <c r="M120" s="231"/>
-      <c r="N120" s="231"/>
-      <c r="O120" s="231"/>
-      <c r="P120" s="231"/>
-      <c r="Q120" s="231"/>
+      <c r="C120" s="232"/>
+      <c r="D120" s="232"/>
+      <c r="E120" s="232"/>
+      <c r="F120" s="232"/>
+      <c r="G120" s="232"/>
+      <c r="H120" s="232"/>
+      <c r="I120" s="232"/>
+      <c r="J120" s="232"/>
+      <c r="K120" s="232"/>
+      <c r="L120" s="232"/>
+      <c r="M120" s="232"/>
+      <c r="N120" s="232"/>
+      <c r="O120" s="232"/>
+      <c r="P120" s="232"/>
+      <c r="Q120" s="232"/>
     </row>
     <row r="121" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B121" s="97" t="s">
@@ -55237,10 +55213,10 @@
       <c r="Q121" s="103"/>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B122" s="286" t="s">
+      <c r="B122" s="305" t="s">
         <v>159</v>
       </c>
-      <c r="C122" s="244" t="s">
+      <c r="C122" s="239" t="s">
         <v>110</v>
       </c>
       <c r="D122" s="53" t="s">
@@ -55287,10 +55263,10 @@
       <c r="Q122" s="196"/>
     </row>
     <row r="123" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B123" s="286" t="s">
+      <c r="B123" s="305" t="s">
         <v>159</v>
       </c>
-      <c r="C123" s="244" t="s">
+      <c r="C123" s="239" t="s">
         <v>110</v>
       </c>
       <c r="D123" s="53" t="s">
@@ -55337,10 +55313,10 @@
       <c r="Q123" s="196"/>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B124" s="286" t="s">
+      <c r="B124" s="305" t="s">
         <v>160</v>
       </c>
-      <c r="C124" s="244" t="s">
+      <c r="C124" s="239" t="s">
         <v>110</v>
       </c>
       <c r="D124" s="53" t="s">
@@ -55388,8 +55364,8 @@
       <c r="Q124" s="196"/>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B125" s="286"/>
-      <c r="C125" s="244"/>
+      <c r="B125" s="305"/>
+      <c r="C125" s="239"/>
       <c r="D125" s="53" t="s">
         <v>22</v>
       </c>
@@ -55436,19 +55412,36 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="P57:P60"/>
-    <mergeCell ref="P61:P64"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="P39:R39"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="P36:R37"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="B20:R20"/>
+    <mergeCell ref="B21:R24"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="Q89:S90"/>
+    <mergeCell ref="B93:T96"/>
+    <mergeCell ref="B107:Q107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B120:Q120"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="Q88:S88"/>
+    <mergeCell ref="B87:S87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="B65:Q65"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="B75:T78"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B69:Q69"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="P67:P68"/>
+    <mergeCell ref="P71:P72"/>
     <mergeCell ref="B9:Q9"/>
     <mergeCell ref="C61:C62"/>
     <mergeCell ref="B13:B14"/>
@@ -55465,36 +55458,19 @@
     <mergeCell ref="B59:B60"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="Q88:S88"/>
-    <mergeCell ref="B87:S87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="B65:Q65"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="B75:T78"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="B69:Q69"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="P67:P68"/>
-    <mergeCell ref="P71:P72"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="B20:R20"/>
-    <mergeCell ref="B21:R24"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="Q89:S90"/>
-    <mergeCell ref="B93:T96"/>
-    <mergeCell ref="B107:Q107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B120:Q120"/>
-    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="P57:P60"/>
+    <mergeCell ref="P61:P64"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="P36:R37"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55531,8 +55507,8 @@
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B8" s="126"/>
       <c r="C8" s="126"/>
-      <c r="D8" s="315"/>
-      <c r="E8" s="315"/>
+      <c r="D8" s="319"/>
+      <c r="E8" s="319"/>
       <c r="F8" s="126"/>
       <c r="G8" s="126"/>
       <c r="H8" s="126"/>
@@ -55548,32 +55524,32 @@
       <c r="R8" s="126"/>
     </row>
     <row r="9" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="320" t="s">
+      <c r="B9" s="328" t="s">
         <v>161</v>
       </c>
-      <c r="C9" s="320"/>
-      <c r="D9" s="320"/>
-      <c r="E9" s="320"/>
-      <c r="F9" s="320"/>
-      <c r="G9" s="320"/>
-      <c r="H9" s="320"/>
-      <c r="I9" s="320"/>
-      <c r="J9" s="320"/>
-      <c r="K9" s="320"/>
-      <c r="L9" s="320"/>
-      <c r="M9" s="320"/>
-      <c r="N9" s="320"/>
-      <c r="O9" s="320"/>
-      <c r="P9" s="320"/>
+      <c r="C9" s="328"/>
+      <c r="D9" s="328"/>
+      <c r="E9" s="328"/>
+      <c r="F9" s="328"/>
+      <c r="G9" s="328"/>
+      <c r="H9" s="328"/>
+      <c r="I9" s="328"/>
+      <c r="J9" s="328"/>
+      <c r="K9" s="328"/>
+      <c r="L9" s="328"/>
+      <c r="M9" s="328"/>
+      <c r="N9" s="328"/>
+      <c r="O9" s="328"/>
+      <c r="P9" s="328"/>
     </row>
     <row r="10" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="316" t="s">
+      <c r="C10" s="338" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="317"/>
+      <c r="D10" s="339"/>
       <c r="E10" s="12" t="s">
         <v>3</v>
       </c>
@@ -55613,10 +55589,10 @@
       <c r="Q10" s="126"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B11" s="318" t="s">
+      <c r="B11" s="340" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="318" t="s">
+      <c r="C11" s="340" t="s">
         <v>165</v>
       </c>
       <c r="D11" s="41" t="s">
@@ -55664,8 +55640,8 @@
       <c r="Q11" s="126"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="319"/>
-      <c r="C12" s="319"/>
+      <c r="B12" s="341"/>
+      <c r="C12" s="341"/>
       <c r="D12" s="41" t="s">
         <v>22</v>
       </c>
@@ -55711,10 +55687,10 @@
       <c r="Q12" s="126"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="318" t="s">
+      <c r="B13" s="340" t="s">
         <v>167</v>
       </c>
-      <c r="C13" s="318" t="s">
+      <c r="C13" s="340" t="s">
         <v>165</v>
       </c>
       <c r="D13" s="41" t="s">
@@ -55762,8 +55738,8 @@
       <c r="Q13" s="126"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B14" s="319"/>
-      <c r="C14" s="319"/>
+      <c r="B14" s="341"/>
+      <c r="C14" s="341"/>
       <c r="D14" s="41" t="s">
         <v>22</v>
       </c>
@@ -55809,10 +55785,10 @@
       <c r="Q14" s="126"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="318" t="s">
+      <c r="B15" s="340" t="s">
         <v>122</v>
       </c>
-      <c r="C15" s="318" t="s">
+      <c r="C15" s="340" t="s">
         <v>165</v>
       </c>
       <c r="D15" s="41" t="s">
@@ -55860,8 +55836,8 @@
       <c r="Q15" s="126"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B16" s="319"/>
-      <c r="C16" s="319"/>
+      <c r="B16" s="341"/>
+      <c r="C16" s="341"/>
       <c r="D16" s="41" t="s">
         <v>22</v>
       </c>
@@ -55921,93 +55897,93 @@
       <c r="N17" s="34"/>
     </row>
     <row r="18" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="324" t="s">
+      <c r="B18" s="344" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="325"/>
-      <c r="D18" s="325"/>
-      <c r="E18" s="325"/>
-      <c r="F18" s="325"/>
-      <c r="G18" s="325"/>
-      <c r="H18" s="325"/>
-      <c r="I18" s="325"/>
-      <c r="J18" s="325"/>
-      <c r="K18" s="325"/>
-      <c r="L18" s="325"/>
-      <c r="M18" s="325"/>
-      <c r="N18" s="325"/>
-      <c r="O18" s="325"/>
-      <c r="P18" s="326"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
+      <c r="G18" s="345"/>
+      <c r="H18" s="345"/>
+      <c r="I18" s="345"/>
+      <c r="J18" s="345"/>
+      <c r="K18" s="345"/>
+      <c r="L18" s="345"/>
+      <c r="M18" s="345"/>
+      <c r="N18" s="345"/>
+      <c r="O18" s="345"/>
+      <c r="P18" s="346"/>
     </row>
     <row r="19" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="290" t="s">
+      <c r="B19" s="309" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="291"/>
-      <c r="D19" s="291"/>
-      <c r="E19" s="291"/>
-      <c r="F19" s="291"/>
-      <c r="G19" s="291"/>
-      <c r="H19" s="291"/>
-      <c r="I19" s="291"/>
-      <c r="J19" s="291"/>
-      <c r="K19" s="291"/>
-      <c r="L19" s="291"/>
-      <c r="M19" s="291"/>
-      <c r="N19" s="291"/>
-      <c r="O19" s="291"/>
-      <c r="P19" s="292"/>
+      <c r="C19" s="310"/>
+      <c r="D19" s="310"/>
+      <c r="E19" s="310"/>
+      <c r="F19" s="310"/>
+      <c r="G19" s="310"/>
+      <c r="H19" s="310"/>
+      <c r="I19" s="310"/>
+      <c r="J19" s="310"/>
+      <c r="K19" s="310"/>
+      <c r="L19" s="310"/>
+      <c r="M19" s="310"/>
+      <c r="N19" s="310"/>
+      <c r="O19" s="310"/>
+      <c r="P19" s="311"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="293"/>
-      <c r="C20" s="238"/>
-      <c r="D20" s="238"/>
-      <c r="E20" s="238"/>
-      <c r="F20" s="238"/>
-      <c r="G20" s="238"/>
-      <c r="H20" s="238"/>
-      <c r="I20" s="238"/>
-      <c r="J20" s="238"/>
-      <c r="K20" s="238"/>
-      <c r="L20" s="238"/>
-      <c r="M20" s="238"/>
-      <c r="N20" s="238"/>
-      <c r="O20" s="238"/>
-      <c r="P20" s="294"/>
+      <c r="B20" s="312"/>
+      <c r="C20" s="282"/>
+      <c r="D20" s="282"/>
+      <c r="E20" s="282"/>
+      <c r="F20" s="282"/>
+      <c r="G20" s="282"/>
+      <c r="H20" s="282"/>
+      <c r="I20" s="282"/>
+      <c r="J20" s="282"/>
+      <c r="K20" s="282"/>
+      <c r="L20" s="282"/>
+      <c r="M20" s="282"/>
+      <c r="N20" s="282"/>
+      <c r="O20" s="282"/>
+      <c r="P20" s="313"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="293"/>
-      <c r="C21" s="238"/>
-      <c r="D21" s="238"/>
-      <c r="E21" s="238"/>
-      <c r="F21" s="238"/>
-      <c r="G21" s="238"/>
-      <c r="H21" s="238"/>
-      <c r="I21" s="238"/>
-      <c r="J21" s="238"/>
-      <c r="K21" s="238"/>
-      <c r="L21" s="238"/>
-      <c r="M21" s="238"/>
-      <c r="N21" s="238"/>
-      <c r="O21" s="238"/>
-      <c r="P21" s="294"/>
+      <c r="B21" s="312"/>
+      <c r="C21" s="282"/>
+      <c r="D21" s="282"/>
+      <c r="E21" s="282"/>
+      <c r="F21" s="282"/>
+      <c r="G21" s="282"/>
+      <c r="H21" s="282"/>
+      <c r="I21" s="282"/>
+      <c r="J21" s="282"/>
+      <c r="K21" s="282"/>
+      <c r="L21" s="282"/>
+      <c r="M21" s="282"/>
+      <c r="N21" s="282"/>
+      <c r="O21" s="282"/>
+      <c r="P21" s="313"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="295"/>
-      <c r="C22" s="296"/>
-      <c r="D22" s="296"/>
-      <c r="E22" s="296"/>
-      <c r="F22" s="296"/>
-      <c r="G22" s="296"/>
-      <c r="H22" s="296"/>
-      <c r="I22" s="296"/>
-      <c r="J22" s="296"/>
-      <c r="K22" s="296"/>
-      <c r="L22" s="296"/>
-      <c r="M22" s="296"/>
-      <c r="N22" s="296"/>
-      <c r="O22" s="296"/>
-      <c r="P22" s="297"/>
+      <c r="B22" s="314"/>
+      <c r="C22" s="315"/>
+      <c r="D22" s="315"/>
+      <c r="E22" s="315"/>
+      <c r="F22" s="315"/>
+      <c r="G22" s="315"/>
+      <c r="H22" s="315"/>
+      <c r="I22" s="315"/>
+      <c r="J22" s="315"/>
+      <c r="K22" s="315"/>
+      <c r="L22" s="315"/>
+      <c r="M22" s="315"/>
+      <c r="N22" s="315"/>
+      <c r="O22" s="315"/>
+      <c r="P22" s="316"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="27"/>
@@ -56137,7 +56113,7 @@
       <c r="N31" s="34"/>
     </row>
     <row r="32" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="321" t="s">
+      <c r="B32" s="342" t="s">
         <v>169</v>
       </c>
       <c r="C32" s="322"/>
@@ -56154,16 +56130,16 @@
       <c r="N32" s="322"/>
       <c r="O32" s="322"/>
       <c r="P32" s="322"/>
-      <c r="Q32" s="323"/>
+      <c r="Q32" s="343"/>
     </row>
     <row r="33" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B33" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="327" t="s">
+      <c r="C33" s="332" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="327"/>
+      <c r="D33" s="332"/>
       <c r="E33" s="127" t="s">
         <v>125</v>
       </c>
@@ -56197,16 +56173,16 @@
       <c r="O33" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="P33" s="247" t="s">
+      <c r="P33" s="271" t="s">
         <v>36</v>
       </c>
-      <c r="Q33" s="248"/>
+      <c r="Q33" s="272"/>
     </row>
     <row r="34" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="332" t="s">
+      <c r="B34" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="C34" s="333" t="s">
+      <c r="C34" s="337" t="s">
         <v>165</v>
       </c>
       <c r="D34" s="40" t="s">
@@ -56247,14 +56223,14 @@
       <c r="O34" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P34" s="266" t="s">
+      <c r="P34" s="242" t="s">
         <v>174</v>
       </c>
-      <c r="Q34" s="267"/>
+      <c r="Q34" s="243"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B35" s="332"/>
-      <c r="C35" s="333"/>
+      <c r="B35" s="336"/>
+      <c r="C35" s="337"/>
       <c r="D35" s="40" t="s">
         <v>22</v>
       </c>
@@ -56293,8 +56269,8 @@
       <c r="O35" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P35" s="312"/>
-      <c r="Q35" s="314"/>
+      <c r="P35" s="299"/>
+      <c r="Q35" s="301"/>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B36" s="119" t="s">
@@ -56341,8 +56317,8 @@
       <c r="O36" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P36" s="268"/>
-      <c r="Q36" s="269"/>
+      <c r="P36" s="244"/>
+      <c r="Q36" s="245"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B37" s="72"/>
@@ -56395,74 +56371,74 @@
       <c r="P39" s="7"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B40" s="211" t="s">
+      <c r="B40" s="224" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="212"/>
-      <c r="D40" s="212"/>
-      <c r="E40" s="212"/>
-      <c r="F40" s="212"/>
-      <c r="G40" s="212"/>
-      <c r="H40" s="212"/>
-      <c r="I40" s="212"/>
-      <c r="J40" s="212"/>
-      <c r="K40" s="212"/>
-      <c r="L40" s="212"/>
-      <c r="M40" s="212"/>
-      <c r="N40" s="212"/>
-      <c r="O40" s="212"/>
-      <c r="P40" s="213"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="225"/>
+      <c r="I40" s="225"/>
+      <c r="J40" s="225"/>
+      <c r="K40" s="225"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="225"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="225"/>
+      <c r="P40" s="226"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B41" s="211"/>
-      <c r="C41" s="212"/>
-      <c r="D41" s="212"/>
-      <c r="E41" s="212"/>
-      <c r="F41" s="212"/>
-      <c r="G41" s="212"/>
-      <c r="H41" s="212"/>
-      <c r="I41" s="212"/>
-      <c r="J41" s="212"/>
-      <c r="K41" s="212"/>
-      <c r="L41" s="212"/>
-      <c r="M41" s="212"/>
-      <c r="N41" s="212"/>
-      <c r="O41" s="212"/>
-      <c r="P41" s="213"/>
+      <c r="B41" s="224"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="225"/>
+      <c r="E41" s="225"/>
+      <c r="F41" s="225"/>
+      <c r="G41" s="225"/>
+      <c r="H41" s="225"/>
+      <c r="I41" s="225"/>
+      <c r="J41" s="225"/>
+      <c r="K41" s="225"/>
+      <c r="L41" s="225"/>
+      <c r="M41" s="225"/>
+      <c r="N41" s="225"/>
+      <c r="O41" s="225"/>
+      <c r="P41" s="226"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B42" s="211"/>
-      <c r="C42" s="212"/>
-      <c r="D42" s="212"/>
-      <c r="E42" s="212"/>
-      <c r="F42" s="212"/>
-      <c r="G42" s="212"/>
-      <c r="H42" s="212"/>
-      <c r="I42" s="212"/>
-      <c r="J42" s="212"/>
-      <c r="K42" s="212"/>
-      <c r="L42" s="212"/>
-      <c r="M42" s="212"/>
-      <c r="N42" s="212"/>
-      <c r="O42" s="212"/>
-      <c r="P42" s="213"/>
+      <c r="B42" s="224"/>
+      <c r="C42" s="225"/>
+      <c r="D42" s="225"/>
+      <c r="E42" s="225"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="225"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="225"/>
+      <c r="K42" s="225"/>
+      <c r="L42" s="225"/>
+      <c r="M42" s="225"/>
+      <c r="N42" s="225"/>
+      <c r="O42" s="225"/>
+      <c r="P42" s="226"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B43" s="214"/>
-      <c r="C43" s="215"/>
-      <c r="D43" s="215"/>
-      <c r="E43" s="215"/>
-      <c r="F43" s="215"/>
-      <c r="G43" s="215"/>
-      <c r="H43" s="215"/>
-      <c r="I43" s="215"/>
-      <c r="J43" s="215"/>
-      <c r="K43" s="215"/>
-      <c r="L43" s="215"/>
-      <c r="M43" s="215"/>
-      <c r="N43" s="215"/>
-      <c r="O43" s="215"/>
-      <c r="P43" s="216"/>
+      <c r="B43" s="227"/>
+      <c r="C43" s="228"/>
+      <c r="D43" s="228"/>
+      <c r="E43" s="228"/>
+      <c r="F43" s="228"/>
+      <c r="G43" s="228"/>
+      <c r="H43" s="228"/>
+      <c r="I43" s="228"/>
+      <c r="J43" s="228"/>
+      <c r="K43" s="228"/>
+      <c r="L43" s="228"/>
+      <c r="M43" s="228"/>
+      <c r="N43" s="228"/>
+      <c r="O43" s="228"/>
+      <c r="P43" s="229"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B44" s="42"/>
@@ -56577,24 +56553,24 @@
       <c r="O51" s="126"/>
     </row>
     <row r="52" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="329" t="s">
+      <c r="B52" s="333" t="s">
         <v>178</v>
       </c>
-      <c r="C52" s="330"/>
-      <c r="D52" s="330"/>
-      <c r="E52" s="330"/>
-      <c r="F52" s="330"/>
-      <c r="G52" s="330"/>
-      <c r="H52" s="330"/>
-      <c r="I52" s="330"/>
-      <c r="J52" s="330"/>
-      <c r="K52" s="330"/>
-      <c r="L52" s="330"/>
-      <c r="M52" s="330"/>
-      <c r="N52" s="330"/>
-      <c r="O52" s="330"/>
-      <c r="P52" s="330"/>
-      <c r="Q52" s="331"/>
+      <c r="C52" s="334"/>
+      <c r="D52" s="334"/>
+      <c r="E52" s="334"/>
+      <c r="F52" s="334"/>
+      <c r="G52" s="334"/>
+      <c r="H52" s="334"/>
+      <c r="I52" s="334"/>
+      <c r="J52" s="334"/>
+      <c r="K52" s="334"/>
+      <c r="L52" s="334"/>
+      <c r="M52" s="334"/>
+      <c r="N52" s="334"/>
+      <c r="O52" s="334"/>
+      <c r="P52" s="334"/>
+      <c r="Q52" s="335"/>
     </row>
     <row r="53" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B53" s="97" t="s">
@@ -56645,10 +56621,10 @@
       </c>
     </row>
     <row r="54" spans="2:17" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="233" t="s">
+      <c r="B54" s="234" t="s">
         <v>179</v>
       </c>
-      <c r="C54" s="328" t="s">
+      <c r="C54" s="317" t="s">
         <v>165</v>
       </c>
       <c r="D54" s="53" t="s">
@@ -56698,8 +56674,8 @@
       </c>
     </row>
     <row r="55" spans="2:17" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="233"/>
-      <c r="C55" s="328"/>
+      <c r="B55" s="234"/>
+      <c r="C55" s="317"/>
       <c r="D55" s="53" t="s">
         <v>22</v>
       </c>
@@ -56747,24 +56723,24 @@
       </c>
     </row>
     <row r="56" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="329" t="s">
+      <c r="B56" s="333" t="s">
         <v>181</v>
       </c>
-      <c r="C56" s="330"/>
-      <c r="D56" s="330"/>
-      <c r="E56" s="330"/>
-      <c r="F56" s="330"/>
-      <c r="G56" s="330"/>
-      <c r="H56" s="330"/>
-      <c r="I56" s="330"/>
-      <c r="J56" s="330"/>
-      <c r="K56" s="330"/>
-      <c r="L56" s="330"/>
-      <c r="M56" s="330"/>
-      <c r="N56" s="330"/>
-      <c r="O56" s="330"/>
-      <c r="P56" s="330"/>
-      <c r="Q56" s="331"/>
+      <c r="C56" s="334"/>
+      <c r="D56" s="334"/>
+      <c r="E56" s="334"/>
+      <c r="F56" s="334"/>
+      <c r="G56" s="334"/>
+      <c r="H56" s="334"/>
+      <c r="I56" s="334"/>
+      <c r="J56" s="334"/>
+      <c r="K56" s="334"/>
+      <c r="L56" s="334"/>
+      <c r="M56" s="334"/>
+      <c r="N56" s="334"/>
+      <c r="O56" s="334"/>
+      <c r="P56" s="334"/>
+      <c r="Q56" s="335"/>
     </row>
     <row r="57" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
@@ -56815,10 +56791,10 @@
       </c>
     </row>
     <row r="58" spans="2:17" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="233" t="s">
+      <c r="B58" s="234" t="s">
         <v>71</v>
       </c>
-      <c r="C58" s="328" t="s">
+      <c r="C58" s="317" t="s">
         <v>165</v>
       </c>
       <c r="D58" s="53" t="s">
@@ -56863,13 +56839,13 @@
       <c r="P58" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q58" s="337" t="s">
+      <c r="Q58" s="324" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="59" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B59" s="233"/>
-      <c r="C59" s="328"/>
+      <c r="B59" s="234"/>
+      <c r="C59" s="317"/>
       <c r="D59" s="53" t="s">
         <v>22</v>
       </c>
@@ -56912,10 +56888,10 @@
       <c r="P59" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q59" s="338"/>
+      <c r="Q59" s="325"/>
     </row>
     <row r="60" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="334" t="s">
+      <c r="B60" s="321" t="s">
         <v>183</v>
       </c>
       <c r="C60" s="322"/>
@@ -56932,16 +56908,16 @@
       <c r="N60" s="322"/>
       <c r="O60" s="322"/>
       <c r="P60" s="322"/>
-      <c r="Q60" s="335"/>
+      <c r="Q60" s="323"/>
     </row>
     <row r="61" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B61" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C61" s="298" t="s">
+      <c r="C61" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D61" s="298"/>
+      <c r="D61" s="303"/>
       <c r="E61" s="8" t="s">
         <v>3</v>
       </c>
@@ -56983,10 +56959,10 @@
       </c>
     </row>
     <row r="62" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="336" t="s">
+      <c r="B62" s="329" t="s">
         <v>184</v>
       </c>
-      <c r="C62" s="328" t="s">
+      <c r="C62" s="317" t="s">
         <v>165</v>
       </c>
       <c r="D62" s="53" t="s">
@@ -57031,13 +57007,13 @@
       <c r="P62" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q62" s="337" t="s">
+      <c r="Q62" s="324" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="63" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B63" s="336"/>
-      <c r="C63" s="328"/>
+      <c r="B63" s="329"/>
+      <c r="C63" s="317"/>
       <c r="D63" s="53" t="s">
         <v>22</v>
       </c>
@@ -57080,10 +57056,10 @@
       <c r="P63" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q63" s="338"/>
+      <c r="Q63" s="325"/>
     </row>
     <row r="64" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="334" t="s">
+      <c r="B64" s="321" t="s">
         <v>185</v>
       </c>
       <c r="C64" s="322"/>
@@ -57100,16 +57076,16 @@
       <c r="N64" s="322"/>
       <c r="O64" s="322"/>
       <c r="P64" s="322"/>
-      <c r="Q64" s="335"/>
+      <c r="Q64" s="323"/>
     </row>
     <row r="65" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B65" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="298" t="s">
+      <c r="C65" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D65" s="298"/>
+      <c r="D65" s="303"/>
       <c r="E65" s="8" t="s">
         <v>3</v>
       </c>
@@ -57151,10 +57127,10 @@
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B66" s="336" t="s">
+      <c r="B66" s="329" t="s">
         <v>186</v>
       </c>
-      <c r="C66" s="328" t="s">
+      <c r="C66" s="317" t="s">
         <v>165</v>
       </c>
       <c r="D66" s="53" t="s">
@@ -57199,13 +57175,13 @@
       <c r="P66" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q66" s="339" t="s">
+      <c r="Q66" s="326" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B67" s="336"/>
-      <c r="C67" s="328"/>
+      <c r="B67" s="329"/>
+      <c r="C67" s="317"/>
       <c r="D67" s="53" t="s">
         <v>22</v>
       </c>
@@ -57248,10 +57224,10 @@
       <c r="P67" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q67" s="340"/>
+      <c r="Q67" s="330"/>
     </row>
     <row r="68" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="334" t="s">
+      <c r="B68" s="321" t="s">
         <v>188</v>
       </c>
       <c r="C68" s="322"/>
@@ -57268,16 +57244,16 @@
       <c r="N68" s="322"/>
       <c r="O68" s="322"/>
       <c r="P68" s="322"/>
-      <c r="Q68" s="335"/>
+      <c r="Q68" s="323"/>
     </row>
     <row r="69" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B69" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C69" s="298" t="s">
+      <c r="C69" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D69" s="298"/>
+      <c r="D69" s="303"/>
       <c r="E69" s="8" t="s">
         <v>3</v>
       </c>
@@ -57319,10 +57295,10 @@
       </c>
     </row>
     <row r="70" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="233" t="s">
+      <c r="B70" s="234" t="s">
         <v>189</v>
       </c>
-      <c r="C70" s="328" t="s">
+      <c r="C70" s="317" t="s">
         <v>165</v>
       </c>
       <c r="D70" s="53" t="s">
@@ -57367,13 +57343,13 @@
       <c r="P70" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="Q70" s="339" t="s">
+      <c r="Q70" s="326" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B71" s="233"/>
-      <c r="C71" s="328"/>
+      <c r="B71" s="234"/>
+      <c r="C71" s="317"/>
       <c r="D71" s="53" t="s">
         <v>22</v>
       </c>
@@ -57416,10 +57392,10 @@
       <c r="P71" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="Q71" s="341"/>
+      <c r="Q71" s="331"/>
     </row>
     <row r="72" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="334" t="s">
+      <c r="B72" s="321" t="s">
         <v>190</v>
       </c>
       <c r="C72" s="322"/>
@@ -57433,19 +57409,19 @@
       <c r="K72" s="322"/>
       <c r="L72" s="322"/>
       <c r="M72" s="322"/>
-      <c r="N72" s="320"/>
+      <c r="N72" s="328"/>
       <c r="O72" s="322"/>
       <c r="P72" s="322"/>
-      <c r="Q72" s="335"/>
+      <c r="Q72" s="323"/>
     </row>
     <row r="73" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B73" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C73" s="298" t="s">
+      <c r="C73" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D73" s="298"/>
+      <c r="D73" s="303"/>
       <c r="E73" s="8" t="s">
         <v>3</v>
       </c>
@@ -57487,10 +57463,10 @@
       </c>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B74" s="233" t="s">
+      <c r="B74" s="234" t="s">
         <v>191</v>
       </c>
-      <c r="C74" s="328" t="s">
+      <c r="C74" s="317" t="s">
         <v>165</v>
       </c>
       <c r="D74" s="53" t="s">
@@ -57535,13 +57511,13 @@
       <c r="P74" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q74" s="339" t="s">
+      <c r="Q74" s="326" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="75" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="344"/>
-      <c r="C75" s="343"/>
+      <c r="B75" s="320"/>
+      <c r="C75" s="318"/>
       <c r="D75" s="90" t="s">
         <v>22</v>
       </c>
@@ -57584,15 +57560,15 @@
       <c r="P75" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="Q75" s="342"/>
+      <c r="Q75" s="327"/>
     </row>
     <row r="76" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="126"/>
       <c r="C76" s="126"/>
-      <c r="D76" s="315" t="s">
+      <c r="D76" s="319" t="s">
         <v>192</v>
       </c>
-      <c r="E76" s="315"/>
+      <c r="E76" s="319"/>
       <c r="F76" s="126"/>
       <c r="G76" s="126"/>
       <c r="H76" s="126"/>
@@ -57608,133 +57584,133 @@
       <c r="R76" s="126"/>
     </row>
     <row r="77" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B77" s="234" t="s">
+      <c r="B77" s="278" t="s">
         <v>32</v>
       </c>
-      <c r="C77" s="235"/>
-      <c r="D77" s="235"/>
-      <c r="E77" s="235"/>
-      <c r="F77" s="235"/>
-      <c r="G77" s="235"/>
-      <c r="H77" s="235"/>
-      <c r="I77" s="235"/>
-      <c r="J77" s="235"/>
-      <c r="K77" s="235"/>
-      <c r="L77" s="235"/>
-      <c r="M77" s="235"/>
-      <c r="N77" s="235"/>
-      <c r="O77" s="235"/>
-      <c r="P77" s="235"/>
-      <c r="Q77" s="235"/>
-      <c r="R77" s="236"/>
+      <c r="C77" s="279"/>
+      <c r="D77" s="279"/>
+      <c r="E77" s="279"/>
+      <c r="F77" s="279"/>
+      <c r="G77" s="279"/>
+      <c r="H77" s="279"/>
+      <c r="I77" s="279"/>
+      <c r="J77" s="279"/>
+      <c r="K77" s="279"/>
+      <c r="L77" s="279"/>
+      <c r="M77" s="279"/>
+      <c r="N77" s="279"/>
+      <c r="O77" s="279"/>
+      <c r="P77" s="279"/>
+      <c r="Q77" s="279"/>
+      <c r="R77" s="280"/>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B78" s="237" t="s">
+      <c r="B78" s="281" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="238"/>
-      <c r="D78" s="238"/>
-      <c r="E78" s="238"/>
-      <c r="F78" s="238"/>
-      <c r="G78" s="238"/>
-      <c r="H78" s="238"/>
-      <c r="I78" s="238"/>
-      <c r="J78" s="238"/>
-      <c r="K78" s="238"/>
-      <c r="L78" s="238"/>
-      <c r="M78" s="238"/>
-      <c r="N78" s="238"/>
-      <c r="O78" s="238"/>
-      <c r="P78" s="238"/>
-      <c r="Q78" s="238"/>
-      <c r="R78" s="239"/>
+      <c r="C78" s="282"/>
+      <c r="D78" s="282"/>
+      <c r="E78" s="282"/>
+      <c r="F78" s="282"/>
+      <c r="G78" s="282"/>
+      <c r="H78" s="282"/>
+      <c r="I78" s="282"/>
+      <c r="J78" s="282"/>
+      <c r="K78" s="282"/>
+      <c r="L78" s="282"/>
+      <c r="M78" s="282"/>
+      <c r="N78" s="282"/>
+      <c r="O78" s="282"/>
+      <c r="P78" s="282"/>
+      <c r="Q78" s="282"/>
+      <c r="R78" s="283"/>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B79" s="237"/>
-      <c r="C79" s="238"/>
-      <c r="D79" s="238"/>
-      <c r="E79" s="238"/>
-      <c r="F79" s="238"/>
-      <c r="G79" s="238"/>
-      <c r="H79" s="238"/>
-      <c r="I79" s="238"/>
-      <c r="J79" s="238"/>
-      <c r="K79" s="238"/>
-      <c r="L79" s="238"/>
-      <c r="M79" s="238"/>
-      <c r="N79" s="238"/>
-      <c r="O79" s="238"/>
-      <c r="P79" s="238"/>
-      <c r="Q79" s="238"/>
-      <c r="R79" s="239"/>
+      <c r="B79" s="281"/>
+      <c r="C79" s="282"/>
+      <c r="D79" s="282"/>
+      <c r="E79" s="282"/>
+      <c r="F79" s="282"/>
+      <c r="G79" s="282"/>
+      <c r="H79" s="282"/>
+      <c r="I79" s="282"/>
+      <c r="J79" s="282"/>
+      <c r="K79" s="282"/>
+      <c r="L79" s="282"/>
+      <c r="M79" s="282"/>
+      <c r="N79" s="282"/>
+      <c r="O79" s="282"/>
+      <c r="P79" s="282"/>
+      <c r="Q79" s="282"/>
+      <c r="R79" s="283"/>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B80" s="237"/>
-      <c r="C80" s="238"/>
-      <c r="D80" s="238"/>
-      <c r="E80" s="238"/>
-      <c r="F80" s="238"/>
-      <c r="G80" s="238"/>
-      <c r="H80" s="238"/>
-      <c r="I80" s="238"/>
-      <c r="J80" s="238"/>
-      <c r="K80" s="238"/>
-      <c r="L80" s="238"/>
-      <c r="M80" s="238"/>
-      <c r="N80" s="238"/>
-      <c r="O80" s="238"/>
-      <c r="P80" s="238"/>
-      <c r="Q80" s="238"/>
-      <c r="R80" s="239"/>
+      <c r="B80" s="281"/>
+      <c r="C80" s="282"/>
+      <c r="D80" s="282"/>
+      <c r="E80" s="282"/>
+      <c r="F80" s="282"/>
+      <c r="G80" s="282"/>
+      <c r="H80" s="282"/>
+      <c r="I80" s="282"/>
+      <c r="J80" s="282"/>
+      <c r="K80" s="282"/>
+      <c r="L80" s="282"/>
+      <c r="M80" s="282"/>
+      <c r="N80" s="282"/>
+      <c r="O80" s="282"/>
+      <c r="P80" s="282"/>
+      <c r="Q80" s="282"/>
+      <c r="R80" s="283"/>
     </row>
     <row r="81" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="240"/>
-      <c r="C81" s="241"/>
-      <c r="D81" s="241"/>
-      <c r="E81" s="241"/>
-      <c r="F81" s="241"/>
-      <c r="G81" s="241"/>
-      <c r="H81" s="241"/>
-      <c r="I81" s="241"/>
-      <c r="J81" s="241"/>
-      <c r="K81" s="241"/>
-      <c r="L81" s="241"/>
-      <c r="M81" s="241"/>
-      <c r="N81" s="241"/>
-      <c r="O81" s="241"/>
-      <c r="P81" s="241"/>
-      <c r="Q81" s="241"/>
-      <c r="R81" s="242"/>
+      <c r="B81" s="284"/>
+      <c r="C81" s="285"/>
+      <c r="D81" s="285"/>
+      <c r="E81" s="285"/>
+      <c r="F81" s="285"/>
+      <c r="G81" s="285"/>
+      <c r="H81" s="285"/>
+      <c r="I81" s="285"/>
+      <c r="J81" s="285"/>
+      <c r="K81" s="285"/>
+      <c r="L81" s="285"/>
+      <c r="M81" s="285"/>
+      <c r="N81" s="285"/>
+      <c r="O81" s="285"/>
+      <c r="P81" s="285"/>
+      <c r="Q81" s="285"/>
+      <c r="R81" s="286"/>
     </row>
     <row r="89" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B89" s="243" t="s">
+      <c r="B89" s="287" t="s">
         <v>193</v>
       </c>
-      <c r="C89" s="243"/>
-      <c r="D89" s="243"/>
-      <c r="E89" s="243"/>
-      <c r="F89" s="243"/>
-      <c r="G89" s="243"/>
-      <c r="H89" s="243"/>
-      <c r="I89" s="243"/>
-      <c r="J89" s="243"/>
-      <c r="K89" s="243"/>
-      <c r="L89" s="243"/>
-      <c r="M89" s="243"/>
-      <c r="N89" s="243"/>
-      <c r="O89" s="243"/>
-      <c r="P89" s="243"/>
-      <c r="Q89" s="243"/>
-      <c r="R89" s="243"/>
+      <c r="C89" s="287"/>
+      <c r="D89" s="287"/>
+      <c r="E89" s="287"/>
+      <c r="F89" s="287"/>
+      <c r="G89" s="287"/>
+      <c r="H89" s="287"/>
+      <c r="I89" s="287"/>
+      <c r="J89" s="287"/>
+      <c r="K89" s="287"/>
+      <c r="L89" s="287"/>
+      <c r="M89" s="287"/>
+      <c r="N89" s="287"/>
+      <c r="O89" s="287"/>
+      <c r="P89" s="287"/>
+      <c r="Q89" s="287"/>
+      <c r="R89" s="287"/>
     </row>
     <row r="90" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C90" s="298" t="s">
+      <c r="C90" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D90" s="298"/>
+      <c r="D90" s="303"/>
       <c r="E90" s="127" t="s">
         <v>125</v>
       </c>
@@ -57777,10 +57753,10 @@
       <c r="R90" s="217"/>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B91" s="220" t="s">
+      <c r="B91" s="214" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="244" t="s">
+      <c r="C91" s="239" t="s">
         <v>165</v>
       </c>
       <c r="D91" s="53" t="s">
@@ -57824,14 +57800,14 @@
       <c r="P91" s="53" t="s">
         <v>152</v>
       </c>
-      <c r="Q91" s="245" t="s">
+      <c r="Q91" s="246" t="s">
         <v>44</v>
       </c>
-      <c r="R91" s="245"/>
+      <c r="R91" s="246"/>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B92" s="220"/>
-      <c r="C92" s="244"/>
+      <c r="B92" s="214"/>
+      <c r="C92" s="239"/>
       <c r="D92" s="53" t="s">
         <v>22</v>
       </c>
@@ -57873,8 +57849,8 @@
       <c r="P92" s="53" t="s">
         <v>152</v>
       </c>
-      <c r="Q92" s="245"/>
-      <c r="R92" s="245"/>
+      <c r="Q92" s="246"/>
+      <c r="R92" s="246"/>
     </row>
     <row r="94" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B94" s="5" t="s">
@@ -57898,82 +57874,82 @@
       <c r="R94" s="6"/>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B95" s="276" t="s">
+      <c r="B95" s="250" t="s">
         <v>33</v>
       </c>
-      <c r="C95" s="276"/>
-      <c r="D95" s="276"/>
-      <c r="E95" s="276"/>
-      <c r="F95" s="276"/>
-      <c r="G95" s="276"/>
-      <c r="H95" s="276"/>
-      <c r="I95" s="276"/>
-      <c r="J95" s="276"/>
-      <c r="K95" s="276"/>
-      <c r="L95" s="276"/>
-      <c r="M95" s="276"/>
-      <c r="N95" s="276"/>
-      <c r="O95" s="276"/>
-      <c r="P95" s="276"/>
-      <c r="Q95" s="276"/>
-      <c r="R95" s="276"/>
+      <c r="C95" s="250"/>
+      <c r="D95" s="250"/>
+      <c r="E95" s="250"/>
+      <c r="F95" s="250"/>
+      <c r="G95" s="250"/>
+      <c r="H95" s="250"/>
+      <c r="I95" s="250"/>
+      <c r="J95" s="250"/>
+      <c r="K95" s="250"/>
+      <c r="L95" s="250"/>
+      <c r="M95" s="250"/>
+      <c r="N95" s="250"/>
+      <c r="O95" s="250"/>
+      <c r="P95" s="250"/>
+      <c r="Q95" s="250"/>
+      <c r="R95" s="250"/>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B96" s="276"/>
-      <c r="C96" s="276"/>
-      <c r="D96" s="276"/>
-      <c r="E96" s="276"/>
-      <c r="F96" s="276"/>
-      <c r="G96" s="276"/>
-      <c r="H96" s="276"/>
-      <c r="I96" s="276"/>
-      <c r="J96" s="276"/>
-      <c r="K96" s="276"/>
-      <c r="L96" s="276"/>
-      <c r="M96" s="276"/>
-      <c r="N96" s="276"/>
-      <c r="O96" s="276"/>
-      <c r="P96" s="276"/>
-      <c r="Q96" s="276"/>
-      <c r="R96" s="276"/>
+      <c r="B96" s="250"/>
+      <c r="C96" s="250"/>
+      <c r="D96" s="250"/>
+      <c r="E96" s="250"/>
+      <c r="F96" s="250"/>
+      <c r="G96" s="250"/>
+      <c r="H96" s="250"/>
+      <c r="I96" s="250"/>
+      <c r="J96" s="250"/>
+      <c r="K96" s="250"/>
+      <c r="L96" s="250"/>
+      <c r="M96" s="250"/>
+      <c r="N96" s="250"/>
+      <c r="O96" s="250"/>
+      <c r="P96" s="250"/>
+      <c r="Q96" s="250"/>
+      <c r="R96" s="250"/>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B97" s="276"/>
-      <c r="C97" s="276"/>
-      <c r="D97" s="276"/>
-      <c r="E97" s="276"/>
-      <c r="F97" s="276"/>
-      <c r="G97" s="276"/>
-      <c r="H97" s="276"/>
-      <c r="I97" s="276"/>
-      <c r="J97" s="276"/>
-      <c r="K97" s="276"/>
-      <c r="L97" s="276"/>
-      <c r="M97" s="276"/>
-      <c r="N97" s="276"/>
-      <c r="O97" s="276"/>
-      <c r="P97" s="276"/>
-      <c r="Q97" s="276"/>
-      <c r="R97" s="276"/>
+      <c r="B97" s="250"/>
+      <c r="C97" s="250"/>
+      <c r="D97" s="250"/>
+      <c r="E97" s="250"/>
+      <c r="F97" s="250"/>
+      <c r="G97" s="250"/>
+      <c r="H97" s="250"/>
+      <c r="I97" s="250"/>
+      <c r="J97" s="250"/>
+      <c r="K97" s="250"/>
+      <c r="L97" s="250"/>
+      <c r="M97" s="250"/>
+      <c r="N97" s="250"/>
+      <c r="O97" s="250"/>
+      <c r="P97" s="250"/>
+      <c r="Q97" s="250"/>
+      <c r="R97" s="250"/>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B98" s="276"/>
-      <c r="C98" s="276"/>
-      <c r="D98" s="276"/>
-      <c r="E98" s="276"/>
-      <c r="F98" s="276"/>
-      <c r="G98" s="276"/>
-      <c r="H98" s="276"/>
-      <c r="I98" s="276"/>
-      <c r="J98" s="276"/>
-      <c r="K98" s="276"/>
-      <c r="L98" s="276"/>
-      <c r="M98" s="276"/>
-      <c r="N98" s="276"/>
-      <c r="O98" s="276"/>
-      <c r="P98" s="276"/>
-      <c r="Q98" s="276"/>
-      <c r="R98" s="276"/>
+      <c r="B98" s="250"/>
+      <c r="C98" s="250"/>
+      <c r="D98" s="250"/>
+      <c r="E98" s="250"/>
+      <c r="F98" s="250"/>
+      <c r="G98" s="250"/>
+      <c r="H98" s="250"/>
+      <c r="I98" s="250"/>
+      <c r="J98" s="250"/>
+      <c r="K98" s="250"/>
+      <c r="L98" s="250"/>
+      <c r="M98" s="250"/>
+      <c r="N98" s="250"/>
+      <c r="O98" s="250"/>
+      <c r="P98" s="250"/>
+      <c r="Q98" s="250"/>
+      <c r="R98" s="250"/>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B99" s="122"/>
@@ -58013,25 +57989,25 @@
       <c r="C106" s="28"/>
     </row>
     <row r="107" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B107" s="218" t="s">
+      <c r="B107" s="215" t="s">
         <v>196</v>
       </c>
-      <c r="C107" s="219"/>
-      <c r="D107" s="219"/>
-      <c r="E107" s="219"/>
-      <c r="F107" s="219"/>
-      <c r="G107" s="219"/>
-      <c r="H107" s="219"/>
-      <c r="I107" s="219"/>
-      <c r="J107" s="219"/>
-      <c r="K107" s="219"/>
-      <c r="L107" s="219"/>
-      <c r="M107" s="219"/>
-      <c r="N107" s="219"/>
-      <c r="O107" s="219"/>
-      <c r="P107" s="219"/>
-      <c r="Q107" s="219"/>
-      <c r="R107" s="219"/>
+      <c r="C107" s="216"/>
+      <c r="D107" s="216"/>
+      <c r="E107" s="216"/>
+      <c r="F107" s="216"/>
+      <c r="G107" s="216"/>
+      <c r="H107" s="216"/>
+      <c r="I107" s="216"/>
+      <c r="J107" s="216"/>
+      <c r="K107" s="216"/>
+      <c r="L107" s="216"/>
+      <c r="M107" s="216"/>
+      <c r="N107" s="216"/>
+      <c r="O107" s="216"/>
+      <c r="P107" s="216"/>
+      <c r="Q107" s="216"/>
+      <c r="R107" s="216"/>
     </row>
     <row r="108" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B108" s="97" t="s">
@@ -58085,10 +58061,10 @@
       </c>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B109" s="286" t="s">
+      <c r="B109" s="305" t="s">
         <v>98</v>
       </c>
-      <c r="C109" s="244" t="s">
+      <c r="C109" s="239" t="s">
         <v>165</v>
       </c>
       <c r="D109" s="53" t="s">
@@ -58140,8 +58116,8 @@
       </c>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B110" s="286"/>
-      <c r="C110" s="244"/>
+      <c r="B110" s="305"/>
+      <c r="C110" s="239"/>
       <c r="D110" s="53" t="s">
         <v>22</v>
       </c>
@@ -58191,10 +58167,10 @@
       </c>
     </row>
     <row r="111" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B111" s="286" t="s">
+      <c r="B111" s="305" t="s">
         <v>160</v>
       </c>
-      <c r="C111" s="244" t="s">
+      <c r="C111" s="239" t="s">
         <v>165</v>
       </c>
       <c r="D111" s="53" t="s">
@@ -58247,8 +58223,8 @@
       </c>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B112" s="286"/>
-      <c r="C112" s="244"/>
+      <c r="B112" s="305"/>
+      <c r="C112" s="239"/>
       <c r="D112" s="53" t="s">
         <v>22</v>
       </c>
@@ -58300,27 +58276,29 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B89:R89"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="B77:R77"/>
-    <mergeCell ref="B78:R81"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="B64:Q64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="Q58:Q59"/>
-    <mergeCell ref="B95:R98"/>
-    <mergeCell ref="Q90:R90"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="Q91:R92"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="B32:Q32"/>
+    <mergeCell ref="B18:P18"/>
+    <mergeCell ref="B19:P22"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B9:P9"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B56:Q56"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B40:P43"/>
+    <mergeCell ref="B52:Q52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="P34:Q36"/>
     <mergeCell ref="C57:D57"/>
     <mergeCell ref="B68:Q68"/>
     <mergeCell ref="C69:D69"/>
@@ -58337,32 +58315,30 @@
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="Q66:Q67"/>
     <mergeCell ref="Q70:Q71"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B56:Q56"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B40:P43"/>
-    <mergeCell ref="B52:Q52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="P34:Q36"/>
+    <mergeCell ref="B64:Q64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="Q58:Q59"/>
+    <mergeCell ref="B95:R98"/>
+    <mergeCell ref="Q90:R90"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="Q91:R92"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B89:R89"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="B77:R77"/>
+    <mergeCell ref="B78:R81"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C90:D90"/>
     <mergeCell ref="B109:B110"/>
     <mergeCell ref="C109:C110"/>
     <mergeCell ref="B107:R107"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B9:P9"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="B32:Q32"/>
-    <mergeCell ref="B18:P18"/>
-    <mergeCell ref="B19:P22"/>
   </mergeCells>
   <phoneticPr fontId="12" alignment="center"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -58405,24 +58381,24 @@
   </cols>
   <sheetData>
     <row r="8" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="218" t="s">
+      <c r="B8" s="215" t="s">
         <v>197</v>
       </c>
-      <c r="C8" s="219"/>
-      <c r="D8" s="219"/>
-      <c r="E8" s="219"/>
-      <c r="F8" s="219"/>
-      <c r="G8" s="219"/>
-      <c r="H8" s="219"/>
-      <c r="I8" s="219"/>
-      <c r="J8" s="219"/>
-      <c r="K8" s="219"/>
-      <c r="L8" s="219"/>
-      <c r="M8" s="219"/>
-      <c r="N8" s="219"/>
-      <c r="O8" s="219"/>
-      <c r="P8" s="219"/>
-      <c r="Q8" s="219"/>
+      <c r="C8" s="216"/>
+      <c r="D8" s="216"/>
+      <c r="E8" s="216"/>
+      <c r="F8" s="216"/>
+      <c r="G8" s="216"/>
+      <c r="H8" s="216"/>
+      <c r="I8" s="216"/>
+      <c r="J8" s="216"/>
+      <c r="K8" s="216"/>
+      <c r="L8" s="216"/>
+      <c r="M8" s="216"/>
+      <c r="N8" s="216"/>
+      <c r="O8" s="216"/>
+      <c r="P8" s="216"/>
+      <c r="Q8" s="216"/>
     </row>
     <row r="9" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B9" s="97" t="s">
@@ -58473,10 +58449,10 @@
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="223" t="s">
+      <c r="B10" s="218" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="220" t="s">
+      <c r="C10" s="214" t="s">
         <v>110</v>
       </c>
       <c r="D10" s="117" t="s">
@@ -58525,8 +58501,8 @@
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="224"/>
-      <c r="C11" s="220"/>
+      <c r="B11" s="219"/>
+      <c r="C11" s="214"/>
       <c r="D11" s="117" t="s">
         <v>22</v>
       </c>
@@ -58573,25 +58549,25 @@
       </c>
     </row>
     <row r="12" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="218" t="s">
+      <c r="B12" s="215" t="s">
         <v>199</v>
       </c>
-      <c r="C12" s="219"/>
-      <c r="D12" s="219"/>
-      <c r="E12" s="219"/>
-      <c r="F12" s="219"/>
-      <c r="G12" s="219"/>
-      <c r="H12" s="219"/>
-      <c r="I12" s="219"/>
-      <c r="J12" s="219"/>
-      <c r="K12" s="219"/>
-      <c r="L12" s="219"/>
-      <c r="M12" s="219"/>
-      <c r="N12" s="219"/>
-      <c r="O12" s="219"/>
-      <c r="P12" s="219"/>
-      <c r="Q12" s="219"/>
-      <c r="R12" s="219"/>
+      <c r="C12" s="216"/>
+      <c r="D12" s="216"/>
+      <c r="E12" s="216"/>
+      <c r="F12" s="216"/>
+      <c r="G12" s="216"/>
+      <c r="H12" s="216"/>
+      <c r="I12" s="216"/>
+      <c r="J12" s="216"/>
+      <c r="K12" s="216"/>
+      <c r="L12" s="216"/>
+      <c r="M12" s="216"/>
+      <c r="N12" s="216"/>
+      <c r="O12" s="216"/>
+      <c r="P12" s="216"/>
+      <c r="Q12" s="216"/>
+      <c r="R12" s="216"/>
     </row>
     <row r="13" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B13" s="97" t="s">
@@ -58648,10 +58624,10 @@
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="220" t="s">
+      <c r="B14" s="214" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="220" t="s">
+      <c r="C14" s="214" t="s">
         <v>165</v>
       </c>
       <c r="D14" s="117" t="s">
@@ -58706,8 +58682,8 @@
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="220"/>
-      <c r="C15" s="220"/>
+      <c r="B15" s="214"/>
+      <c r="C15" s="214"/>
       <c r="D15" s="117" t="s">
         <v>22</v>
       </c>
@@ -58760,24 +58736,24 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="227" t="s">
+      <c r="B16" s="222" t="s">
         <v>203</v>
       </c>
-      <c r="C16" s="228"/>
-      <c r="D16" s="228"/>
-      <c r="E16" s="228"/>
-      <c r="F16" s="228"/>
-      <c r="G16" s="228"/>
-      <c r="H16" s="228"/>
-      <c r="I16" s="228"/>
-      <c r="J16" s="228"/>
-      <c r="K16" s="228"/>
-      <c r="L16" s="228"/>
-      <c r="M16" s="228"/>
-      <c r="N16" s="228"/>
-      <c r="O16" s="228"/>
-      <c r="P16" s="228"/>
-      <c r="Q16" s="228"/>
+      <c r="C16" s="223"/>
+      <c r="D16" s="223"/>
+      <c r="E16" s="223"/>
+      <c r="F16" s="223"/>
+      <c r="G16" s="223"/>
+      <c r="H16" s="223"/>
+      <c r="I16" s="223"/>
+      <c r="J16" s="223"/>
+      <c r="K16" s="223"/>
+      <c r="L16" s="223"/>
+      <c r="M16" s="223"/>
+      <c r="N16" s="223"/>
+      <c r="O16" s="223"/>
+      <c r="P16" s="223"/>
+      <c r="Q16" s="223"/>
     </row>
     <row r="17" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B17" s="97" t="s">
@@ -58820,16 +58796,16 @@
       <c r="O17" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="P17" s="225" t="s">
+      <c r="P17" s="220" t="s">
         <v>137</v>
       </c>
-      <c r="Q17" s="226"/>
+      <c r="Q17" s="221"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="220" t="s">
+      <c r="B18" s="214" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="220" t="s">
+      <c r="C18" s="214" t="s">
         <v>204</v>
       </c>
       <c r="D18" s="117" t="s">
@@ -58876,8 +58852,8 @@
       <c r="Q18" s="53"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="220"/>
-      <c r="C19" s="220"/>
+      <c r="B19" s="214"/>
+      <c r="C19" s="214"/>
       <c r="D19" s="117" t="s">
         <v>22</v>
       </c>
@@ -58922,22 +58898,22 @@
       <c r="Q19" s="53"/>
     </row>
     <row r="20" spans="2:17" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="229" t="s">
+      <c r="B20" s="212" t="s">
         <v>206</v>
       </c>
-      <c r="C20" s="230"/>
-      <c r="D20" s="230"/>
-      <c r="E20" s="230"/>
-      <c r="F20" s="230"/>
-      <c r="G20" s="230"/>
-      <c r="H20" s="230"/>
-      <c r="I20" s="230"/>
-      <c r="J20" s="230"/>
-      <c r="K20" s="230"/>
-      <c r="L20" s="230"/>
-      <c r="M20" s="230"/>
-      <c r="N20" s="230"/>
-      <c r="O20" s="230"/>
+      <c r="C20" s="213"/>
+      <c r="D20" s="213"/>
+      <c r="E20" s="213"/>
+      <c r="F20" s="213"/>
+      <c r="G20" s="213"/>
+      <c r="H20" s="213"/>
+      <c r="I20" s="213"/>
+      <c r="J20" s="213"/>
+      <c r="K20" s="213"/>
+      <c r="L20" s="213"/>
+      <c r="M20" s="213"/>
+      <c r="N20" s="213"/>
+      <c r="O20" s="213"/>
       <c r="P20" s="207"/>
     </row>
     <row r="21" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -58981,14 +58957,14 @@
       <c r="O21" s="120" t="s">
         <v>137</v>
       </c>
-      <c r="P21" s="221"/>
-      <c r="Q21" s="222"/>
+      <c r="P21" s="230"/>
+      <c r="Q21" s="231"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="220" t="s">
+      <c r="B22" s="214" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="220" t="s">
+      <c r="C22" s="214" t="s">
         <v>207</v>
       </c>
       <c r="D22" s="117" t="s">
@@ -59033,8 +59009,8 @@
       <c r="P22" s="205"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B23" s="220"/>
-      <c r="C23" s="220"/>
+      <c r="B23" s="214"/>
+      <c r="C23" s="214"/>
       <c r="D23" s="117" t="s">
         <v>22</v>
       </c>
@@ -59077,22 +59053,22 @@
       <c r="P23" s="205"/>
     </row>
     <row r="24" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="218" t="s">
+      <c r="B24" s="215" t="s">
         <v>209</v>
       </c>
-      <c r="C24" s="219"/>
-      <c r="D24" s="219"/>
-      <c r="E24" s="219"/>
-      <c r="F24" s="219"/>
-      <c r="G24" s="219"/>
-      <c r="H24" s="219"/>
-      <c r="I24" s="219"/>
-      <c r="J24" s="219"/>
-      <c r="K24" s="219"/>
-      <c r="L24" s="219"/>
-      <c r="M24" s="219"/>
-      <c r="N24" s="219"/>
-      <c r="O24" s="219"/>
+      <c r="C24" s="216"/>
+      <c r="D24" s="216"/>
+      <c r="E24" s="216"/>
+      <c r="F24" s="216"/>
+      <c r="G24" s="216"/>
+      <c r="H24" s="216"/>
+      <c r="I24" s="216"/>
+      <c r="J24" s="216"/>
+      <c r="K24" s="216"/>
+      <c r="L24" s="216"/>
+      <c r="M24" s="216"/>
+      <c r="N24" s="216"/>
+      <c r="O24" s="216"/>
       <c r="P24" s="61"/>
     </row>
     <row r="25" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -59139,10 +59115,10 @@
       <c r="P25" s="61"/>
     </row>
     <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="220" t="s">
+      <c r="B26" s="214" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="220" t="s">
+      <c r="C26" s="214" t="s">
         <v>114</v>
       </c>
       <c r="D26" s="117" t="s">
@@ -59188,8 +59164,8 @@
       <c r="P26" s="61"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B27" s="220"/>
-      <c r="C27" s="220"/>
+      <c r="B27" s="214"/>
+      <c r="C27" s="214"/>
       <c r="D27" s="117" t="s">
         <v>22</v>
       </c>
@@ -59253,78 +59229,78 @@
       <c r="Q29" s="7"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B30" s="211" t="s">
+      <c r="B30" s="224" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="212"/>
-      <c r="D30" s="212"/>
-      <c r="E30" s="212"/>
-      <c r="F30" s="212"/>
-      <c r="G30" s="212"/>
-      <c r="H30" s="212"/>
-      <c r="I30" s="212"/>
-      <c r="J30" s="212"/>
-      <c r="K30" s="212"/>
-      <c r="L30" s="212"/>
-      <c r="M30" s="212"/>
-      <c r="N30" s="212"/>
-      <c r="O30" s="212"/>
-      <c r="P30" s="212"/>
-      <c r="Q30" s="213"/>
+      <c r="C30" s="225"/>
+      <c r="D30" s="225"/>
+      <c r="E30" s="225"/>
+      <c r="F30" s="225"/>
+      <c r="G30" s="225"/>
+      <c r="H30" s="225"/>
+      <c r="I30" s="225"/>
+      <c r="J30" s="225"/>
+      <c r="K30" s="225"/>
+      <c r="L30" s="225"/>
+      <c r="M30" s="225"/>
+      <c r="N30" s="225"/>
+      <c r="O30" s="225"/>
+      <c r="P30" s="225"/>
+      <c r="Q30" s="226"/>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B31" s="211"/>
-      <c r="C31" s="212"/>
-      <c r="D31" s="212"/>
-      <c r="E31" s="212"/>
-      <c r="F31" s="212"/>
-      <c r="G31" s="212"/>
-      <c r="H31" s="212"/>
-      <c r="I31" s="212"/>
-      <c r="J31" s="212"/>
-      <c r="K31" s="212"/>
-      <c r="L31" s="212"/>
-      <c r="M31" s="212"/>
-      <c r="N31" s="212"/>
-      <c r="O31" s="212"/>
-      <c r="P31" s="212"/>
-      <c r="Q31" s="213"/>
+      <c r="B31" s="224"/>
+      <c r="C31" s="225"/>
+      <c r="D31" s="225"/>
+      <c r="E31" s="225"/>
+      <c r="F31" s="225"/>
+      <c r="G31" s="225"/>
+      <c r="H31" s="225"/>
+      <c r="I31" s="225"/>
+      <c r="J31" s="225"/>
+      <c r="K31" s="225"/>
+      <c r="L31" s="225"/>
+      <c r="M31" s="225"/>
+      <c r="N31" s="225"/>
+      <c r="O31" s="225"/>
+      <c r="P31" s="225"/>
+      <c r="Q31" s="226"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B32" s="211"/>
-      <c r="C32" s="212"/>
-      <c r="D32" s="212"/>
-      <c r="E32" s="212"/>
-      <c r="F32" s="212"/>
-      <c r="G32" s="212"/>
-      <c r="H32" s="212"/>
-      <c r="I32" s="212"/>
-      <c r="J32" s="212"/>
-      <c r="K32" s="212"/>
-      <c r="L32" s="212"/>
-      <c r="M32" s="212"/>
-      <c r="N32" s="212"/>
-      <c r="O32" s="212"/>
-      <c r="P32" s="212"/>
-      <c r="Q32" s="213"/>
+      <c r="B32" s="224"/>
+      <c r="C32" s="225"/>
+      <c r="D32" s="225"/>
+      <c r="E32" s="225"/>
+      <c r="F32" s="225"/>
+      <c r="G32" s="225"/>
+      <c r="H32" s="225"/>
+      <c r="I32" s="225"/>
+      <c r="J32" s="225"/>
+      <c r="K32" s="225"/>
+      <c r="L32" s="225"/>
+      <c r="M32" s="225"/>
+      <c r="N32" s="225"/>
+      <c r="O32" s="225"/>
+      <c r="P32" s="225"/>
+      <c r="Q32" s="226"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B33" s="214"/>
-      <c r="C33" s="215"/>
-      <c r="D33" s="215"/>
-      <c r="E33" s="215"/>
-      <c r="F33" s="215"/>
-      <c r="G33" s="215"/>
-      <c r="H33" s="215"/>
-      <c r="I33" s="215"/>
-      <c r="J33" s="215"/>
-      <c r="K33" s="215"/>
-      <c r="L33" s="215"/>
-      <c r="M33" s="215"/>
-      <c r="N33" s="215"/>
-      <c r="O33" s="215"/>
-      <c r="P33" s="215"/>
-      <c r="Q33" s="216"/>
+      <c r="B33" s="227"/>
+      <c r="C33" s="228"/>
+      <c r="D33" s="228"/>
+      <c r="E33" s="228"/>
+      <c r="F33" s="228"/>
+      <c r="G33" s="228"/>
+      <c r="H33" s="228"/>
+      <c r="I33" s="228"/>
+      <c r="J33" s="228"/>
+      <c r="K33" s="228"/>
+      <c r="L33" s="228"/>
+      <c r="M33" s="228"/>
+      <c r="N33" s="228"/>
+      <c r="O33" s="228"/>
+      <c r="P33" s="228"/>
+      <c r="Q33" s="229"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B34" s="35"/>
@@ -59454,11 +59430,15 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B20:O20"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B30:Q33"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B24:O24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="P21:Q21"/>
     <mergeCell ref="B8:Q8"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C17:D17"/>
@@ -59468,15 +59448,11 @@
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="P17:Q17"/>
     <mergeCell ref="B16:Q16"/>
-    <mergeCell ref="B30:Q33"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B24:O24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="B20:O20"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B18:B19"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -59663,10 +59639,10 @@
       <c r="B10" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="345" t="s">
+      <c r="C10" s="359" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="345"/>
+      <c r="D10" s="359"/>
       <c r="E10" s="15" t="s">
         <v>3</v>
       </c>
@@ -59705,10 +59681,10 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="346" t="s">
+      <c r="B11" s="355" t="s">
         <v>211</v>
       </c>
-      <c r="C11" s="349" t="s">
+      <c r="C11" s="357" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="45" t="s">
@@ -59754,8 +59730,8 @@
       </c>
     </row>
     <row r="12" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="347"/>
-      <c r="C12" s="349"/>
+      <c r="B12" s="360"/>
+      <c r="C12" s="357"/>
       <c r="D12" s="45" t="s">
         <v>22</v>
       </c>
@@ -59799,8 +59775,8 @@
       </c>
     </row>
     <row r="13" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="347"/>
-      <c r="C13" s="349" t="s">
+      <c r="B13" s="360"/>
+      <c r="C13" s="357" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="45" t="s">
@@ -59846,8 +59822,8 @@
       </c>
     </row>
     <row r="14" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="347"/>
-      <c r="C14" s="349"/>
+      <c r="B14" s="360"/>
+      <c r="C14" s="357"/>
       <c r="D14" s="45" t="s">
         <v>22</v>
       </c>
@@ -59891,8 +59867,8 @@
       </c>
     </row>
     <row r="15" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="347"/>
-      <c r="C15" s="349" t="s">
+      <c r="B15" s="360"/>
+      <c r="C15" s="357" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="45" t="s">
@@ -59938,8 +59914,8 @@
       </c>
     </row>
     <row r="16" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="347"/>
-      <c r="C16" s="349"/>
+      <c r="B16" s="360"/>
+      <c r="C16" s="357"/>
       <c r="D16" s="45" t="s">
         <v>22</v>
       </c>
@@ -59983,8 +59959,8 @@
       </c>
     </row>
     <row r="17" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="347"/>
-      <c r="C17" s="349" t="s">
+      <c r="B17" s="360"/>
+      <c r="C17" s="357" t="s">
         <v>29</v>
       </c>
       <c r="D17" s="45" t="s">
@@ -60030,8 +60006,8 @@
       </c>
     </row>
     <row r="18" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="347"/>
-      <c r="C18" s="349"/>
+      <c r="B18" s="360"/>
+      <c r="C18" s="357"/>
       <c r="D18" s="45" t="s">
         <v>22</v>
       </c>
@@ -60075,8 +60051,8 @@
       </c>
     </row>
     <row r="19" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="347"/>
-      <c r="C19" s="349" t="s">
+      <c r="B19" s="360"/>
+      <c r="C19" s="357" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="45" t="s">
@@ -60122,8 +60098,8 @@
       </c>
     </row>
     <row r="20" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="348"/>
-      <c r="C20" s="349"/>
+      <c r="B20" s="356"/>
+      <c r="C20" s="357"/>
       <c r="D20" s="45" t="s">
         <v>22</v>
       </c>
@@ -60167,10 +60143,10 @@
       </c>
     </row>
     <row r="21" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="346" t="s">
+      <c r="B21" s="355" t="s">
         <v>216</v>
       </c>
-      <c r="C21" s="349" t="s">
+      <c r="C21" s="357" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="45" t="s">
@@ -60216,8 +60192,8 @@
       </c>
     </row>
     <row r="22" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="348"/>
-      <c r="C22" s="349"/>
+      <c r="B22" s="356"/>
+      <c r="C22" s="357"/>
       <c r="D22" s="45" t="s">
         <v>22</v>
       </c>
@@ -60261,10 +60237,10 @@
       </c>
     </row>
     <row r="23" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B23" s="346" t="s">
+      <c r="B23" s="355" t="s">
         <v>217</v>
       </c>
-      <c r="C23" s="349" t="s">
+      <c r="C23" s="357" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="45" t="s">
@@ -60310,8 +60286,8 @@
       </c>
     </row>
     <row r="24" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="348"/>
-      <c r="C24" s="349"/>
+      <c r="B24" s="356"/>
+      <c r="C24" s="357"/>
       <c r="D24" s="45" t="s">
         <v>22</v>
       </c>
@@ -60355,10 +60331,10 @@
       </c>
     </row>
     <row r="25" spans="2:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="233" t="s">
+      <c r="B25" s="234" t="s">
         <v>219</v>
       </c>
-      <c r="C25" s="220" t="s">
+      <c r="C25" s="214" t="s">
         <v>29</v>
       </c>
       <c r="D25" s="40" t="s">
@@ -60404,8 +60380,8 @@
       </c>
     </row>
     <row r="26" spans="2:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="233"/>
-      <c r="C26" s="220"/>
+      <c r="B26" s="234"/>
+      <c r="C26" s="214"/>
       <c r="D26" s="40" t="s">
         <v>22</v>
       </c>
@@ -60449,7 +60425,7 @@
       </c>
     </row>
     <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="344"/>
+      <c r="B27" s="320"/>
       <c r="C27" s="358"/>
       <c r="D27" s="84" t="s">
         <v>17</v>
@@ -60510,96 +60486,103 @@
       <c r="O28" s="28"/>
     </row>
     <row r="29" spans="2:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="350" t="s">
+      <c r="B29" s="347" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="351"/>
-      <c r="D29" s="351"/>
-      <c r="E29" s="351"/>
-      <c r="F29" s="351"/>
-      <c r="G29" s="351"/>
-      <c r="H29" s="351"/>
-      <c r="I29" s="351"/>
-      <c r="J29" s="351"/>
-      <c r="K29" s="351"/>
-      <c r="L29" s="351"/>
-      <c r="M29" s="351"/>
-      <c r="N29" s="351"/>
-      <c r="O29" s="351"/>
-      <c r="P29" s="352"/>
+      <c r="C29" s="348"/>
+      <c r="D29" s="348"/>
+      <c r="E29" s="348"/>
+      <c r="F29" s="348"/>
+      <c r="G29" s="348"/>
+      <c r="H29" s="348"/>
+      <c r="I29" s="348"/>
+      <c r="J29" s="348"/>
+      <c r="K29" s="348"/>
+      <c r="L29" s="348"/>
+      <c r="M29" s="348"/>
+      <c r="N29" s="348"/>
+      <c r="O29" s="348"/>
+      <c r="P29" s="349"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B30" s="353" t="s">
+      <c r="B30" s="350" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="212"/>
-      <c r="D30" s="212"/>
-      <c r="E30" s="212"/>
-      <c r="F30" s="212"/>
-      <c r="G30" s="212"/>
-      <c r="H30" s="212"/>
-      <c r="I30" s="212"/>
-      <c r="J30" s="212"/>
-      <c r="K30" s="212"/>
-      <c r="L30" s="212"/>
-      <c r="M30" s="212"/>
-      <c r="N30" s="212"/>
-      <c r="O30" s="212"/>
-      <c r="P30" s="354"/>
+      <c r="C30" s="225"/>
+      <c r="D30" s="225"/>
+      <c r="E30" s="225"/>
+      <c r="F30" s="225"/>
+      <c r="G30" s="225"/>
+      <c r="H30" s="225"/>
+      <c r="I30" s="225"/>
+      <c r="J30" s="225"/>
+      <c r="K30" s="225"/>
+      <c r="L30" s="225"/>
+      <c r="M30" s="225"/>
+      <c r="N30" s="225"/>
+      <c r="O30" s="225"/>
+      <c r="P30" s="351"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="353"/>
-      <c r="C31" s="212"/>
-      <c r="D31" s="212"/>
-      <c r="E31" s="212"/>
-      <c r="F31" s="212"/>
-      <c r="G31" s="212"/>
-      <c r="H31" s="212"/>
-      <c r="I31" s="212"/>
-      <c r="J31" s="212"/>
-      <c r="K31" s="212"/>
-      <c r="L31" s="212"/>
-      <c r="M31" s="212"/>
-      <c r="N31" s="212"/>
-      <c r="O31" s="212"/>
-      <c r="P31" s="354"/>
+      <c r="B31" s="350"/>
+      <c r="C31" s="225"/>
+      <c r="D31" s="225"/>
+      <c r="E31" s="225"/>
+      <c r="F31" s="225"/>
+      <c r="G31" s="225"/>
+      <c r="H31" s="225"/>
+      <c r="I31" s="225"/>
+      <c r="J31" s="225"/>
+      <c r="K31" s="225"/>
+      <c r="L31" s="225"/>
+      <c r="M31" s="225"/>
+      <c r="N31" s="225"/>
+      <c r="O31" s="225"/>
+      <c r="P31" s="351"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B32" s="353"/>
-      <c r="C32" s="212"/>
-      <c r="D32" s="212"/>
-      <c r="E32" s="212"/>
-      <c r="F32" s="212"/>
-      <c r="G32" s="212"/>
-      <c r="H32" s="212"/>
-      <c r="I32" s="212"/>
-      <c r="J32" s="212"/>
-      <c r="K32" s="212"/>
-      <c r="L32" s="212"/>
-      <c r="M32" s="212"/>
-      <c r="N32" s="212"/>
-      <c r="O32" s="212"/>
-      <c r="P32" s="354"/>
+      <c r="B32" s="350"/>
+      <c r="C32" s="225"/>
+      <c r="D32" s="225"/>
+      <c r="E32" s="225"/>
+      <c r="F32" s="225"/>
+      <c r="G32" s="225"/>
+      <c r="H32" s="225"/>
+      <c r="I32" s="225"/>
+      <c r="J32" s="225"/>
+      <c r="K32" s="225"/>
+      <c r="L32" s="225"/>
+      <c r="M32" s="225"/>
+      <c r="N32" s="225"/>
+      <c r="O32" s="225"/>
+      <c r="P32" s="351"/>
     </row>
     <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="355"/>
-      <c r="C33" s="356"/>
-      <c r="D33" s="356"/>
-      <c r="E33" s="356"/>
-      <c r="F33" s="356"/>
-      <c r="G33" s="356"/>
-      <c r="H33" s="356"/>
-      <c r="I33" s="356"/>
-      <c r="J33" s="356"/>
-      <c r="K33" s="356"/>
-      <c r="L33" s="356"/>
-      <c r="M33" s="356"/>
-      <c r="N33" s="356"/>
-      <c r="O33" s="356"/>
-      <c r="P33" s="357"/>
+      <c r="B33" s="352"/>
+      <c r="C33" s="353"/>
+      <c r="D33" s="353"/>
+      <c r="E33" s="353"/>
+      <c r="F33" s="353"/>
+      <c r="G33" s="353"/>
+      <c r="H33" s="353"/>
+      <c r="I33" s="353"/>
+      <c r="J33" s="353"/>
+      <c r="K33" s="353"/>
+      <c r="L33" s="353"/>
+      <c r="M33" s="353"/>
+      <c r="N33" s="353"/>
+      <c r="O33" s="353"/>
+      <c r="P33" s="354"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B20"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
     <mergeCell ref="B29:P29"/>
     <mergeCell ref="B30:P33"/>
     <mergeCell ref="B21:B22"/>
@@ -60608,13 +60591,6 @@
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="B25:B27"/>
     <mergeCell ref="C25:C27"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B20"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="67" orientation="landscape" r:id="rId1"/>
@@ -60623,6 +60599,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BF631F92D611394D900040A4BC36CE07" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="711a2ec75ffd0c152903cfa2dedf38be">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8bf418b7-79e0-4993-aa07-d31c53a64380" xmlns:ns3="268ad1c4-fabf-4dd0-b894-8fd5403102c0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0628c710989f2757c815e19c03677863" ns2:_="" ns3:_="">
     <xsd:import namespace="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
@@ -60845,15 +60830,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -60866,6 +60842,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A722593-7143-4ACD-9A00-2A0E70214590}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -60884,14 +60868,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
   <ds:schemaRefs>

--- a/Customer Rate Tariff Template_Week 33_2026.xlsx
+++ b/Customer Rate Tariff Template_Week 33_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stephanie.galera.RAMPSLOGISTICS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E222F8-5DF3-42AC-A47C-88BC61611122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40202C9-680B-46E2-8F05-6892BF060277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
   </bookViews>
   <sheets>
     <sheet name="TT" sheetId="28" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4327" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4335" uniqueCount="224">
   <si>
     <t>USA / TRINIDAD SHIPPING TARIFF</t>
   </si>
@@ -1730,7 +1730,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="361">
+  <cellXfs count="364">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2227,286 +2227,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2530,6 +2257,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2542,50 +2272,291 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2599,24 +2570,71 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2642,23 +2660,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4119,32 +4128,32 @@
       <c r="P7" s="18"/>
     </row>
     <row r="8" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="216" t="s">
+      <c r="B8" s="233" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="216"/>
-      <c r="D8" s="216"/>
-      <c r="E8" s="216"/>
-      <c r="F8" s="216"/>
-      <c r="G8" s="216"/>
-      <c r="H8" s="216"/>
-      <c r="I8" s="216"/>
-      <c r="J8" s="216"/>
-      <c r="K8" s="216"/>
-      <c r="L8" s="216"/>
-      <c r="M8" s="216"/>
-      <c r="N8" s="216"/>
-      <c r="O8" s="216"/>
-      <c r="P8" s="216"/>
+      <c r="C8" s="233"/>
+      <c r="D8" s="233"/>
+      <c r="E8" s="233"/>
+      <c r="F8" s="233"/>
+      <c r="G8" s="233"/>
+      <c r="H8" s="233"/>
+      <c r="I8" s="233"/>
+      <c r="J8" s="233"/>
+      <c r="K8" s="233"/>
+      <c r="L8" s="233"/>
+      <c r="M8" s="233"/>
+      <c r="N8" s="233"/>
+      <c r="O8" s="233"/>
+      <c r="P8" s="233"/>
     </row>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="217" t="s">
+      <c r="C9" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="217"/>
+      <c r="D9" s="232"/>
       <c r="E9" s="120" t="s">
         <v>3</v>
       </c>
@@ -4183,10 +4192,10 @@
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="235" t="s">
+      <c r="B10" s="308" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="235" t="s">
+      <c r="C10" s="308" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="20" t="s">
@@ -4232,8 +4241,8 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="236"/>
-      <c r="C11" s="236"/>
+      <c r="B11" s="309"/>
+      <c r="C11" s="309"/>
       <c r="D11" s="20" t="s">
         <v>22</v>
       </c>
@@ -4277,8 +4286,8 @@
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="236"/>
-      <c r="C12" s="235" t="s">
+      <c r="B12" s="309"/>
+      <c r="C12" s="308" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="111" t="s">
@@ -4325,8 +4334,8 @@
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="236"/>
-      <c r="C13" s="236"/>
+      <c r="B13" s="309"/>
+      <c r="C13" s="309"/>
       <c r="D13" s="111" t="s">
         <v>22</v>
       </c>
@@ -4372,10 +4381,10 @@
       <c r="Q13" s="26"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="237" t="s">
+      <c r="B14" s="253" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="239" t="s">
+      <c r="C14" s="214" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="20" t="s">
@@ -4422,8 +4431,8 @@
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="238"/>
-      <c r="C15" s="239"/>
+      <c r="B15" s="310"/>
+      <c r="C15" s="214"/>
       <c r="D15" s="20" t="s">
         <v>22</v>
       </c>
@@ -4468,10 +4477,10 @@
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="237" t="s">
+      <c r="B16" s="253" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="237" t="s">
+      <c r="C16" s="253" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="20" t="s">
@@ -4518,8 +4527,8 @@
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B17" s="238"/>
-      <c r="C17" s="238"/>
+      <c r="B17" s="310"/>
+      <c r="C17" s="310"/>
       <c r="D17" s="20" t="s">
         <v>22</v>
       </c>
@@ -4564,10 +4573,10 @@
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="237" t="s">
+      <c r="B18" s="253" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="239" t="s">
+      <c r="C18" s="214" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -4615,8 +4624,8 @@
       <c r="Q18" s="26"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="247"/>
-      <c r="C19" s="239"/>
+      <c r="B19" s="311"/>
+      <c r="C19" s="214"/>
       <c r="D19" s="20" t="s">
         <v>22</v>
       </c>
@@ -4662,8 +4671,8 @@
       <c r="Q19" s="26"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="247"/>
-      <c r="C20" s="239" t="s">
+      <c r="B20" s="311"/>
+      <c r="C20" s="214" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="20" t="s">
@@ -4710,8 +4719,8 @@
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="238"/>
-      <c r="C21" s="239"/>
+      <c r="B21" s="310"/>
+      <c r="C21" s="214"/>
       <c r="D21" s="20" t="s">
         <v>22</v>
       </c>
@@ -4793,74 +4802,74 @@
       <c r="P23" s="186"/>
     </row>
     <row r="24" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="250" t="s">
+      <c r="B24" s="230" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="250"/>
-      <c r="D24" s="250"/>
-      <c r="E24" s="250"/>
-      <c r="F24" s="250"/>
-      <c r="G24" s="250"/>
-      <c r="H24" s="250"/>
-      <c r="I24" s="250"/>
-      <c r="J24" s="250"/>
-      <c r="K24" s="250"/>
-      <c r="L24" s="250"/>
-      <c r="M24" s="250"/>
-      <c r="N24" s="250"/>
-      <c r="O24" s="250"/>
-      <c r="P24" s="250"/>
+      <c r="C24" s="230"/>
+      <c r="D24" s="230"/>
+      <c r="E24" s="230"/>
+      <c r="F24" s="230"/>
+      <c r="G24" s="230"/>
+      <c r="H24" s="230"/>
+      <c r="I24" s="230"/>
+      <c r="J24" s="230"/>
+      <c r="K24" s="230"/>
+      <c r="L24" s="230"/>
+      <c r="M24" s="230"/>
+      <c r="N24" s="230"/>
+      <c r="O24" s="230"/>
+      <c r="P24" s="230"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B25" s="250"/>
-      <c r="C25" s="250"/>
-      <c r="D25" s="250"/>
-      <c r="E25" s="250"/>
-      <c r="F25" s="250"/>
-      <c r="G25" s="250"/>
-      <c r="H25" s="250"/>
-      <c r="I25" s="250"/>
-      <c r="J25" s="250"/>
-      <c r="K25" s="250"/>
-      <c r="L25" s="250"/>
-      <c r="M25" s="250"/>
-      <c r="N25" s="250"/>
-      <c r="O25" s="250"/>
-      <c r="P25" s="250"/>
+      <c r="B25" s="230"/>
+      <c r="C25" s="230"/>
+      <c r="D25" s="230"/>
+      <c r="E25" s="230"/>
+      <c r="F25" s="230"/>
+      <c r="G25" s="230"/>
+      <c r="H25" s="230"/>
+      <c r="I25" s="230"/>
+      <c r="J25" s="230"/>
+      <c r="K25" s="230"/>
+      <c r="L25" s="230"/>
+      <c r="M25" s="230"/>
+      <c r="N25" s="230"/>
+      <c r="O25" s="230"/>
+      <c r="P25" s="230"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B26" s="250"/>
-      <c r="C26" s="250"/>
-      <c r="D26" s="250"/>
-      <c r="E26" s="250"/>
-      <c r="F26" s="250"/>
-      <c r="G26" s="250"/>
-      <c r="H26" s="250"/>
-      <c r="I26" s="250"/>
-      <c r="J26" s="250"/>
-      <c r="K26" s="250"/>
-      <c r="L26" s="250"/>
-      <c r="M26" s="250"/>
-      <c r="N26" s="250"/>
-      <c r="O26" s="250"/>
-      <c r="P26" s="250"/>
+      <c r="B26" s="230"/>
+      <c r="C26" s="230"/>
+      <c r="D26" s="230"/>
+      <c r="E26" s="230"/>
+      <c r="F26" s="230"/>
+      <c r="G26" s="230"/>
+      <c r="H26" s="230"/>
+      <c r="I26" s="230"/>
+      <c r="J26" s="230"/>
+      <c r="K26" s="230"/>
+      <c r="L26" s="230"/>
+      <c r="M26" s="230"/>
+      <c r="N26" s="230"/>
+      <c r="O26" s="230"/>
+      <c r="P26" s="230"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B27" s="250"/>
-      <c r="C27" s="250"/>
-      <c r="D27" s="250"/>
-      <c r="E27" s="250"/>
-      <c r="F27" s="250"/>
-      <c r="G27" s="250"/>
-      <c r="H27" s="250"/>
-      <c r="I27" s="250"/>
-      <c r="J27" s="250"/>
-      <c r="K27" s="250"/>
-      <c r="L27" s="250"/>
-      <c r="M27" s="250"/>
-      <c r="N27" s="250"/>
-      <c r="O27" s="250"/>
-      <c r="P27" s="250"/>
+      <c r="B27" s="230"/>
+      <c r="C27" s="230"/>
+      <c r="D27" s="230"/>
+      <c r="E27" s="230"/>
+      <c r="F27" s="230"/>
+      <c r="G27" s="230"/>
+      <c r="H27" s="230"/>
+      <c r="I27" s="230"/>
+      <c r="J27" s="230"/>
+      <c r="K27" s="230"/>
+      <c r="L27" s="230"/>
+      <c r="M27" s="230"/>
+      <c r="N27" s="230"/>
+      <c r="O27" s="230"/>
+      <c r="P27" s="230"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B28" s="35"/>
@@ -4989,32 +4998,32 @@
       <c r="Q34" s="28"/>
     </row>
     <row r="35" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="240" t="s">
+      <c r="B35" s="245" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="213"/>
-      <c r="D35" s="213"/>
-      <c r="E35" s="213"/>
-      <c r="F35" s="213"/>
-      <c r="G35" s="213"/>
-      <c r="H35" s="213"/>
-      <c r="I35" s="213"/>
-      <c r="J35" s="213"/>
-      <c r="K35" s="213"/>
-      <c r="L35" s="213"/>
-      <c r="M35" s="213"/>
-      <c r="N35" s="213"/>
-      <c r="O35" s="213"/>
-      <c r="P35" s="213"/>
+      <c r="C35" s="294"/>
+      <c r="D35" s="294"/>
+      <c r="E35" s="294"/>
+      <c r="F35" s="294"/>
+      <c r="G35" s="294"/>
+      <c r="H35" s="294"/>
+      <c r="I35" s="294"/>
+      <c r="J35" s="294"/>
+      <c r="K35" s="294"/>
+      <c r="L35" s="294"/>
+      <c r="M35" s="294"/>
+      <c r="N35" s="294"/>
+      <c r="O35" s="294"/>
+      <c r="P35" s="294"/>
     </row>
     <row r="36" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B36" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="217" t="s">
+      <c r="C36" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="217"/>
+      <c r="D36" s="232"/>
       <c r="E36" s="120" t="s">
         <v>3</v>
       </c>
@@ -5045,13 +5054,13 @@
       <c r="N36" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="O36" s="217" t="s">
+      <c r="O36" s="232" t="s">
         <v>36</v>
       </c>
-      <c r="P36" s="217"/>
+      <c r="P36" s="232"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B37" s="241" t="s">
+      <c r="B37" s="254" t="s">
         <v>37</v>
       </c>
       <c r="C37" s="136" t="s">
@@ -5093,13 +5102,13 @@
       <c r="N37" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O37" s="242" t="s">
+      <c r="O37" s="255" t="s">
         <v>40</v>
       </c>
-      <c r="P37" s="243"/>
+      <c r="P37" s="257"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B38" s="241"/>
+      <c r="B38" s="254"/>
       <c r="C38" s="136" t="s">
         <v>16</v>
       </c>
@@ -5139,8 +5148,8 @@
       <c r="N38" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O38" s="244"/>
-      <c r="P38" s="245"/>
+      <c r="O38" s="299"/>
+      <c r="P38" s="300"/>
     </row>
     <row r="39" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="187" t="s">
@@ -5184,10 +5193,10 @@
       <c r="N39" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="O39" s="246" t="s">
+      <c r="O39" s="229" t="s">
         <v>44</v>
       </c>
-      <c r="P39" s="246"/>
+      <c r="P39" s="229"/>
     </row>
     <row r="40" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="187" t="s">
@@ -5232,10 +5241,10 @@
       <c r="N40" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O40" s="246" t="s">
+      <c r="O40" s="229" t="s">
         <v>44</v>
       </c>
-      <c r="P40" s="246"/>
+      <c r="P40" s="229"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B41" s="42"/>
@@ -5276,78 +5285,78 @@
       <c r="Q42" s="7"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B43" s="224" t="s">
+      <c r="B43" s="243" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="225"/>
-      <c r="D43" s="225"/>
-      <c r="E43" s="225"/>
-      <c r="F43" s="225"/>
-      <c r="G43" s="225"/>
-      <c r="H43" s="225"/>
-      <c r="I43" s="225"/>
-      <c r="J43" s="225"/>
-      <c r="K43" s="225"/>
-      <c r="L43" s="225"/>
-      <c r="M43" s="225"/>
-      <c r="N43" s="225"/>
-      <c r="O43" s="225"/>
-      <c r="P43" s="225"/>
-      <c r="Q43" s="226"/>
+      <c r="C43" s="263"/>
+      <c r="D43" s="263"/>
+      <c r="E43" s="263"/>
+      <c r="F43" s="263"/>
+      <c r="G43" s="263"/>
+      <c r="H43" s="263"/>
+      <c r="I43" s="263"/>
+      <c r="J43" s="263"/>
+      <c r="K43" s="263"/>
+      <c r="L43" s="263"/>
+      <c r="M43" s="263"/>
+      <c r="N43" s="263"/>
+      <c r="O43" s="263"/>
+      <c r="P43" s="263"/>
+      <c r="Q43" s="264"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B44" s="224"/>
-      <c r="C44" s="225"/>
-      <c r="D44" s="225"/>
-      <c r="E44" s="225"/>
-      <c r="F44" s="225"/>
-      <c r="G44" s="225"/>
-      <c r="H44" s="225"/>
-      <c r="I44" s="225"/>
-      <c r="J44" s="225"/>
-      <c r="K44" s="225"/>
-      <c r="L44" s="225"/>
-      <c r="M44" s="225"/>
-      <c r="N44" s="225"/>
-      <c r="O44" s="225"/>
-      <c r="P44" s="225"/>
-      <c r="Q44" s="226"/>
+      <c r="B44" s="243"/>
+      <c r="C44" s="263"/>
+      <c r="D44" s="263"/>
+      <c r="E44" s="263"/>
+      <c r="F44" s="263"/>
+      <c r="G44" s="263"/>
+      <c r="H44" s="263"/>
+      <c r="I44" s="263"/>
+      <c r="J44" s="263"/>
+      <c r="K44" s="263"/>
+      <c r="L44" s="263"/>
+      <c r="M44" s="263"/>
+      <c r="N44" s="263"/>
+      <c r="O44" s="263"/>
+      <c r="P44" s="263"/>
+      <c r="Q44" s="264"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B45" s="224"/>
-      <c r="C45" s="225"/>
-      <c r="D45" s="225"/>
-      <c r="E45" s="225"/>
-      <c r="F45" s="225"/>
-      <c r="G45" s="225"/>
-      <c r="H45" s="225"/>
-      <c r="I45" s="225"/>
-      <c r="J45" s="225"/>
-      <c r="K45" s="225"/>
-      <c r="L45" s="225"/>
-      <c r="M45" s="225"/>
-      <c r="N45" s="225"/>
-      <c r="O45" s="225"/>
-      <c r="P45" s="225"/>
-      <c r="Q45" s="226"/>
+      <c r="B45" s="243"/>
+      <c r="C45" s="263"/>
+      <c r="D45" s="263"/>
+      <c r="E45" s="263"/>
+      <c r="F45" s="263"/>
+      <c r="G45" s="263"/>
+      <c r="H45" s="263"/>
+      <c r="I45" s="263"/>
+      <c r="J45" s="263"/>
+      <c r="K45" s="263"/>
+      <c r="L45" s="263"/>
+      <c r="M45" s="263"/>
+      <c r="N45" s="263"/>
+      <c r="O45" s="263"/>
+      <c r="P45" s="263"/>
+      <c r="Q45" s="264"/>
     </row>
     <row r="46" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B46" s="227"/>
-      <c r="C46" s="228"/>
-      <c r="D46" s="228"/>
-      <c r="E46" s="228"/>
-      <c r="F46" s="228"/>
-      <c r="G46" s="228"/>
-      <c r="H46" s="228"/>
-      <c r="I46" s="228"/>
-      <c r="J46" s="228"/>
-      <c r="K46" s="228"/>
-      <c r="L46" s="228"/>
-      <c r="M46" s="228"/>
-      <c r="N46" s="228"/>
-      <c r="O46" s="228"/>
-      <c r="P46" s="228"/>
-      <c r="Q46" s="229"/>
+      <c r="B46" s="244"/>
+      <c r="C46" s="265"/>
+      <c r="D46" s="265"/>
+      <c r="E46" s="265"/>
+      <c r="F46" s="265"/>
+      <c r="G46" s="265"/>
+      <c r="H46" s="265"/>
+      <c r="I46" s="265"/>
+      <c r="J46" s="265"/>
+      <c r="K46" s="265"/>
+      <c r="L46" s="265"/>
+      <c r="M46" s="265"/>
+      <c r="N46" s="265"/>
+      <c r="O46" s="265"/>
+      <c r="P46" s="265"/>
+      <c r="Q46" s="266"/>
     </row>
     <row r="47" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B47" s="35"/>
@@ -5513,35 +5522,35 @@
       <c r="R55" s="28"/>
     </row>
     <row r="56" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B56" s="232" t="s">
+      <c r="B56" s="231" t="s">
         <v>46</v>
       </c>
-      <c r="C56" s="233"/>
-      <c r="D56" s="233"/>
-      <c r="E56" s="233"/>
-      <c r="F56" s="233"/>
-      <c r="G56" s="233"/>
-      <c r="H56" s="233"/>
-      <c r="I56" s="233"/>
-      <c r="J56" s="233"/>
-      <c r="K56" s="233"/>
-      <c r="L56" s="233"/>
-      <c r="M56" s="233"/>
-      <c r="N56" s="233"/>
-      <c r="O56" s="233"/>
-      <c r="P56" s="233"/>
-      <c r="Q56" s="233"/>
-      <c r="R56" s="233"/>
-      <c r="S56" s="251"/>
+      <c r="C56" s="261"/>
+      <c r="D56" s="261"/>
+      <c r="E56" s="261"/>
+      <c r="F56" s="261"/>
+      <c r="G56" s="261"/>
+      <c r="H56" s="261"/>
+      <c r="I56" s="261"/>
+      <c r="J56" s="261"/>
+      <c r="K56" s="261"/>
+      <c r="L56" s="261"/>
+      <c r="M56" s="261"/>
+      <c r="N56" s="261"/>
+      <c r="O56" s="261"/>
+      <c r="P56" s="261"/>
+      <c r="Q56" s="261"/>
+      <c r="R56" s="261"/>
+      <c r="S56" s="289"/>
     </row>
     <row r="57" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="217" t="s">
+      <c r="C57" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="217"/>
+      <c r="D57" s="232"/>
       <c r="E57" s="120" t="s">
         <v>3</v>
       </c>
@@ -5581,16 +5590,16 @@
       <c r="Q57" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R57" s="252" t="s">
+      <c r="R57" s="306" t="s">
         <v>36</v>
       </c>
-      <c r="S57" s="253"/>
+      <c r="S57" s="307"/>
     </row>
     <row r="58" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="248" t="s">
+      <c r="B58" s="279" t="s">
         <v>51</v>
       </c>
-      <c r="C58" s="249" t="s">
+      <c r="C58" s="280" t="s">
         <v>52</v>
       </c>
       <c r="D58" s="137" t="s">
@@ -5638,14 +5647,14 @@
       <c r="Q58" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R58" s="254" t="s">
+      <c r="R58" s="281" t="s">
         <v>55</v>
       </c>
-      <c r="S58" s="255"/>
+      <c r="S58" s="282"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B59" s="248"/>
-      <c r="C59" s="249"/>
+      <c r="B59" s="279"/>
+      <c r="C59" s="280"/>
       <c r="D59" s="137" t="s">
         <v>22</v>
       </c>
@@ -5691,14 +5700,14 @@
       <c r="Q59" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R59" s="256"/>
-      <c r="S59" s="257"/>
+      <c r="R59" s="283"/>
+      <c r="S59" s="284"/>
     </row>
     <row r="60" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="248" t="s">
+      <c r="B60" s="279" t="s">
         <v>56</v>
       </c>
-      <c r="C60" s="249" t="s">
+      <c r="C60" s="280" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="137" t="s">
@@ -5746,12 +5755,12 @@
       <c r="Q60" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R60" s="256"/>
-      <c r="S60" s="257"/>
+      <c r="R60" s="283"/>
+      <c r="S60" s="284"/>
     </row>
     <row r="61" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B61" s="248"/>
-      <c r="C61" s="249"/>
+      <c r="B61" s="279"/>
+      <c r="C61" s="280"/>
       <c r="D61" s="137" t="s">
         <v>22</v>
       </c>
@@ -5797,14 +5806,14 @@
       <c r="Q61" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R61" s="258"/>
-      <c r="S61" s="259"/>
+      <c r="R61" s="302"/>
+      <c r="S61" s="303"/>
     </row>
     <row r="62" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="265" t="s">
+      <c r="B62" s="296" t="s">
         <v>57</v>
       </c>
-      <c r="C62" s="218" t="s">
+      <c r="C62" s="227" t="s">
         <v>29</v>
       </c>
       <c r="D62" s="117" t="s">
@@ -5852,14 +5861,14 @@
       <c r="Q62" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="R62" s="242" t="s">
+      <c r="R62" s="255" t="s">
         <v>59</v>
       </c>
-      <c r="S62" s="243"/>
+      <c r="S62" s="257"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B63" s="266"/>
-      <c r="C63" s="219"/>
+      <c r="B63" s="297"/>
+      <c r="C63" s="298"/>
       <c r="D63" s="117" t="s">
         <v>22</v>
       </c>
@@ -5905,14 +5914,14 @@
       <c r="Q63" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="R63" s="244"/>
-      <c r="S63" s="245"/>
+      <c r="R63" s="299"/>
+      <c r="S63" s="300"/>
     </row>
     <row r="64" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="248" t="s">
+      <c r="B64" s="279" t="s">
         <v>60</v>
       </c>
-      <c r="C64" s="249" t="s">
+      <c r="C64" s="280" t="s">
         <v>52</v>
       </c>
       <c r="D64" s="137" t="s">
@@ -5960,14 +5969,14 @@
       <c r="Q64" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R64" s="254" t="s">
+      <c r="R64" s="281" t="s">
         <v>55</v>
       </c>
-      <c r="S64" s="255"/>
+      <c r="S64" s="282"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B65" s="248"/>
-      <c r="C65" s="249"/>
+      <c r="B65" s="279"/>
+      <c r="C65" s="280"/>
       <c r="D65" s="137" t="s">
         <v>22</v>
       </c>
@@ -6013,14 +6022,14 @@
       <c r="Q65" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R65" s="256"/>
-      <c r="S65" s="257"/>
+      <c r="R65" s="283"/>
+      <c r="S65" s="284"/>
     </row>
     <row r="66" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="269" t="s">
+      <c r="B66" s="304" t="s">
         <v>61</v>
       </c>
-      <c r="C66" s="267" t="s">
+      <c r="C66" s="292" t="s">
         <v>29</v>
       </c>
       <c r="D66" s="137" t="s">
@@ -6068,14 +6077,14 @@
       <c r="Q66" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="R66" s="242" t="s">
+      <c r="R66" s="255" t="s">
         <v>59</v>
       </c>
-      <c r="S66" s="243"/>
+      <c r="S66" s="257"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B67" s="270"/>
-      <c r="C67" s="268"/>
+      <c r="B67" s="305"/>
+      <c r="C67" s="301"/>
       <c r="D67" s="137" t="s">
         <v>22</v>
       </c>
@@ -6121,14 +6130,14 @@
       <c r="Q67" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="R67" s="244"/>
-      <c r="S67" s="245"/>
+      <c r="R67" s="299"/>
+      <c r="S67" s="300"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B68" s="269" t="s">
+      <c r="B68" s="304" t="s">
         <v>62</v>
       </c>
-      <c r="C68" s="249" t="s">
+      <c r="C68" s="280" t="s">
         <v>52</v>
       </c>
       <c r="D68" s="137" t="s">
@@ -6176,14 +6185,14 @@
       <c r="Q68" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R68" s="254" t="s">
+      <c r="R68" s="281" t="s">
         <v>55</v>
       </c>
-      <c r="S68" s="255"/>
+      <c r="S68" s="282"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B69" s="270"/>
-      <c r="C69" s="249"/>
+      <c r="B69" s="305"/>
+      <c r="C69" s="280"/>
       <c r="D69" s="137" t="s">
         <v>22</v>
       </c>
@@ -6229,14 +6238,14 @@
       <c r="Q69" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R69" s="256"/>
-      <c r="S69" s="257"/>
+      <c r="R69" s="283"/>
+      <c r="S69" s="284"/>
     </row>
     <row r="70" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="248" t="s">
+      <c r="B70" s="279" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="249" t="s">
+      <c r="C70" s="280" t="s">
         <v>52</v>
       </c>
       <c r="D70" s="137" t="s">
@@ -6284,12 +6293,12 @@
       <c r="Q70" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R70" s="256"/>
-      <c r="S70" s="257"/>
+      <c r="R70" s="283"/>
+      <c r="S70" s="284"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B71" s="248"/>
-      <c r="C71" s="249"/>
+      <c r="B71" s="279"/>
+      <c r="C71" s="280"/>
       <c r="D71" s="137" t="s">
         <v>22</v>
       </c>
@@ -6335,14 +6344,14 @@
       <c r="Q71" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R71" s="258"/>
-      <c r="S71" s="259"/>
+      <c r="R71" s="302"/>
+      <c r="S71" s="303"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B72" s="248" t="s">
+      <c r="B72" s="279" t="s">
         <v>64</v>
       </c>
-      <c r="C72" s="267" t="s">
+      <c r="C72" s="292" t="s">
         <v>29</v>
       </c>
       <c r="D72" s="137" t="s">
@@ -6390,14 +6399,14 @@
       <c r="Q72" s="211" t="s">
         <v>65</v>
       </c>
-      <c r="R72" s="261" t="s">
+      <c r="R72" s="285" t="s">
         <v>66</v>
       </c>
-      <c r="S72" s="262"/>
+      <c r="S72" s="286"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B73" s="248"/>
-      <c r="C73" s="268"/>
+      <c r="B73" s="279"/>
+      <c r="C73" s="301"/>
       <c r="D73" s="137" t="s">
         <v>22</v>
       </c>
@@ -6443,14 +6452,14 @@
       <c r="Q73" s="211" t="s">
         <v>65</v>
       </c>
-      <c r="R73" s="263"/>
-      <c r="S73" s="264"/>
+      <c r="R73" s="287"/>
+      <c r="S73" s="288"/>
     </row>
     <row r="74" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="248" t="s">
+      <c r="B74" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="C74" s="249" t="s">
+      <c r="C74" s="280" t="s">
         <v>52</v>
       </c>
       <c r="D74" s="137" t="s">
@@ -6498,14 +6507,14 @@
       <c r="Q74" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R74" s="254" t="s">
+      <c r="R74" s="281" t="s">
         <v>55</v>
       </c>
-      <c r="S74" s="255"/>
+      <c r="S74" s="282"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B75" s="248"/>
-      <c r="C75" s="249"/>
+      <c r="B75" s="279"/>
+      <c r="C75" s="280"/>
       <c r="D75" s="137" t="s">
         <v>22</v>
       </c>
@@ -6551,14 +6560,14 @@
       <c r="Q75" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R75" s="256"/>
-      <c r="S75" s="257"/>
+      <c r="R75" s="283"/>
+      <c r="S75" s="284"/>
     </row>
     <row r="76" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="248" t="s">
+      <c r="B76" s="279" t="s">
         <v>68</v>
       </c>
-      <c r="C76" s="249" t="s">
+      <c r="C76" s="280" t="s">
         <v>52</v>
       </c>
       <c r="D76" s="137" t="s">
@@ -6606,12 +6615,12 @@
       <c r="Q76" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R76" s="256"/>
-      <c r="S76" s="257"/>
+      <c r="R76" s="283"/>
+      <c r="S76" s="284"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B77" s="248"/>
-      <c r="C77" s="249"/>
+      <c r="B77" s="279"/>
+      <c r="C77" s="280"/>
       <c r="D77" s="137" t="s">
         <v>22</v>
       </c>
@@ -6657,14 +6666,14 @@
       <c r="Q77" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R77" s="256"/>
-      <c r="S77" s="257"/>
+      <c r="R77" s="283"/>
+      <c r="S77" s="284"/>
     </row>
     <row r="78" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="248" t="s">
+      <c r="B78" s="279" t="s">
         <v>69</v>
       </c>
-      <c r="C78" s="249" t="s">
+      <c r="C78" s="280" t="s">
         <v>52</v>
       </c>
       <c r="D78" s="137" t="s">
@@ -6712,12 +6721,12 @@
       <c r="Q78" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R78" s="256"/>
-      <c r="S78" s="257"/>
+      <c r="R78" s="283"/>
+      <c r="S78" s="284"/>
     </row>
     <row r="79" spans="2:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="248"/>
-      <c r="C79" s="249"/>
+      <c r="B79" s="279"/>
+      <c r="C79" s="280"/>
       <c r="D79" s="137" t="s">
         <v>22</v>
       </c>
@@ -6763,39 +6772,39 @@
       <c r="Q79" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R79" s="258"/>
-      <c r="S79" s="259"/>
+      <c r="R79" s="302"/>
+      <c r="S79" s="303"/>
     </row>
     <row r="80" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B80" s="232" t="s">
+      <c r="B80" s="231" t="s">
         <v>70</v>
       </c>
-      <c r="C80" s="233"/>
-      <c r="D80" s="233"/>
-      <c r="E80" s="233"/>
-      <c r="F80" s="233"/>
-      <c r="G80" s="233"/>
-      <c r="H80" s="233"/>
-      <c r="I80" s="233"/>
-      <c r="J80" s="233"/>
-      <c r="K80" s="233"/>
-      <c r="L80" s="233"/>
-      <c r="M80" s="233"/>
-      <c r="N80" s="233"/>
-      <c r="O80" s="233"/>
-      <c r="P80" s="233"/>
-      <c r="Q80" s="233"/>
-      <c r="R80" s="216"/>
-      <c r="S80" s="274"/>
+      <c r="C80" s="261"/>
+      <c r="D80" s="261"/>
+      <c r="E80" s="261"/>
+      <c r="F80" s="261"/>
+      <c r="G80" s="261"/>
+      <c r="H80" s="261"/>
+      <c r="I80" s="261"/>
+      <c r="J80" s="261"/>
+      <c r="K80" s="261"/>
+      <c r="L80" s="261"/>
+      <c r="M80" s="261"/>
+      <c r="N80" s="261"/>
+      <c r="O80" s="261"/>
+      <c r="P80" s="261"/>
+      <c r="Q80" s="261"/>
+      <c r="R80" s="233"/>
+      <c r="S80" s="290"/>
     </row>
     <row r="81" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B81" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C81" s="271" t="s">
+      <c r="C81" s="276" t="s">
         <v>2</v>
       </c>
-      <c r="D81" s="272"/>
+      <c r="D81" s="277"/>
       <c r="E81" s="120" t="s">
         <v>3</v>
       </c>
@@ -6835,16 +6844,16 @@
       <c r="Q81" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R81" s="271" t="s">
+      <c r="R81" s="276" t="s">
         <v>36</v>
       </c>
-      <c r="S81" s="273"/>
+      <c r="S81" s="278"/>
     </row>
     <row r="82" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="275" t="s">
+      <c r="B82" s="239" t="s">
         <v>71</v>
       </c>
-      <c r="C82" s="267" t="s">
+      <c r="C82" s="292" t="s">
         <v>72</v>
       </c>
       <c r="D82" s="137" t="s">
@@ -6892,14 +6901,14 @@
       <c r="Q82" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R82" s="261" t="s">
+      <c r="R82" s="285" t="s">
         <v>73</v>
       </c>
-      <c r="S82" s="262"/>
+      <c r="S82" s="286"/>
     </row>
     <row r="83" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="276"/>
-      <c r="C83" s="277"/>
+      <c r="B83" s="291"/>
+      <c r="C83" s="293"/>
       <c r="D83" s="137" t="s">
         <v>22</v>
       </c>
@@ -6945,39 +6954,39 @@
       <c r="Q83" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R83" s="263"/>
-      <c r="S83" s="264"/>
+      <c r="R83" s="287"/>
+      <c r="S83" s="288"/>
     </row>
     <row r="84" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B84" s="232" t="s">
+      <c r="B84" s="231" t="s">
         <v>74</v>
       </c>
-      <c r="C84" s="233"/>
-      <c r="D84" s="233"/>
-      <c r="E84" s="233"/>
-      <c r="F84" s="233"/>
-      <c r="G84" s="233"/>
-      <c r="H84" s="233"/>
-      <c r="I84" s="233"/>
-      <c r="J84" s="233"/>
-      <c r="K84" s="233"/>
-      <c r="L84" s="233"/>
-      <c r="M84" s="233"/>
-      <c r="N84" s="233"/>
-      <c r="O84" s="233"/>
-      <c r="P84" s="233"/>
-      <c r="Q84" s="233"/>
-      <c r="R84" s="233"/>
-      <c r="S84" s="251"/>
+      <c r="C84" s="261"/>
+      <c r="D84" s="261"/>
+      <c r="E84" s="261"/>
+      <c r="F84" s="261"/>
+      <c r="G84" s="261"/>
+      <c r="H84" s="261"/>
+      <c r="I84" s="261"/>
+      <c r="J84" s="261"/>
+      <c r="K84" s="261"/>
+      <c r="L84" s="261"/>
+      <c r="M84" s="261"/>
+      <c r="N84" s="261"/>
+      <c r="O84" s="261"/>
+      <c r="P84" s="261"/>
+      <c r="Q84" s="261"/>
+      <c r="R84" s="261"/>
+      <c r="S84" s="289"/>
     </row>
     <row r="85" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B85" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="271" t="s">
+      <c r="C85" s="276" t="s">
         <v>2</v>
       </c>
-      <c r="D85" s="272"/>
+      <c r="D85" s="277"/>
       <c r="E85" s="120" t="s">
         <v>3</v>
       </c>
@@ -7017,16 +7026,16 @@
       <c r="Q85" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R85" s="271" t="s">
+      <c r="R85" s="276" t="s">
         <v>36</v>
       </c>
-      <c r="S85" s="273"/>
+      <c r="S85" s="278"/>
     </row>
     <row r="86" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="248" t="s">
-        <v>75</v>
-      </c>
-      <c r="C86" s="249" t="s">
+      <c r="B86" s="279" t="s">
+        <v>75</v>
+      </c>
+      <c r="C86" s="280" t="s">
         <v>72</v>
       </c>
       <c r="D86" s="137" t="s">
@@ -7074,14 +7083,14 @@
       <c r="Q86" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R86" s="261" t="s">
+      <c r="R86" s="285" t="s">
         <v>73</v>
       </c>
-      <c r="S86" s="262"/>
+      <c r="S86" s="286"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B87" s="248"/>
-      <c r="C87" s="249"/>
+      <c r="B87" s="279"/>
+      <c r="C87" s="280"/>
       <c r="D87" s="137" t="s">
         <v>22</v>
       </c>
@@ -7127,39 +7136,39 @@
       <c r="Q87" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R87" s="263"/>
-      <c r="S87" s="264"/>
+      <c r="R87" s="287"/>
+      <c r="S87" s="288"/>
     </row>
     <row r="88" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B88" s="212" t="s">
+      <c r="B88" s="237" t="s">
         <v>77</v>
       </c>
-      <c r="C88" s="213"/>
-      <c r="D88" s="213"/>
-      <c r="E88" s="213"/>
-      <c r="F88" s="213"/>
-      <c r="G88" s="213"/>
-      <c r="H88" s="213"/>
-      <c r="I88" s="213"/>
-      <c r="J88" s="213"/>
-      <c r="K88" s="213"/>
-      <c r="L88" s="213"/>
-      <c r="M88" s="213"/>
-      <c r="N88" s="213"/>
-      <c r="O88" s="213"/>
-      <c r="P88" s="213"/>
-      <c r="Q88" s="213"/>
-      <c r="R88" s="213"/>
-      <c r="S88" s="260"/>
+      <c r="C88" s="294"/>
+      <c r="D88" s="294"/>
+      <c r="E88" s="294"/>
+      <c r="F88" s="294"/>
+      <c r="G88" s="294"/>
+      <c r="H88" s="294"/>
+      <c r="I88" s="294"/>
+      <c r="J88" s="294"/>
+      <c r="K88" s="294"/>
+      <c r="L88" s="294"/>
+      <c r="M88" s="294"/>
+      <c r="N88" s="294"/>
+      <c r="O88" s="294"/>
+      <c r="P88" s="294"/>
+      <c r="Q88" s="294"/>
+      <c r="R88" s="294"/>
+      <c r="S88" s="295"/>
     </row>
     <row r="89" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B89" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C89" s="271" t="s">
+      <c r="C89" s="276" t="s">
         <v>2</v>
       </c>
-      <c r="D89" s="272"/>
+      <c r="D89" s="277"/>
       <c r="E89" s="120" t="s">
         <v>3</v>
       </c>
@@ -7199,16 +7208,16 @@
       <c r="Q89" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R89" s="271" t="s">
+      <c r="R89" s="276" t="s">
         <v>36</v>
       </c>
-      <c r="S89" s="273"/>
+      <c r="S89" s="278"/>
     </row>
     <row r="90" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="248" t="s">
+      <c r="B90" s="279" t="s">
         <v>78</v>
       </c>
-      <c r="C90" s="249" t="s">
+      <c r="C90" s="280" t="s">
         <v>72</v>
       </c>
       <c r="D90" s="137" t="s">
@@ -7256,14 +7265,14 @@
       <c r="Q90" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R90" s="261" t="s">
+      <c r="R90" s="285" t="s">
         <v>73</v>
       </c>
-      <c r="S90" s="262"/>
+      <c r="S90" s="286"/>
     </row>
     <row r="91" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="248"/>
-      <c r="C91" s="249"/>
+      <c r="B91" s="279"/>
+      <c r="C91" s="280"/>
       <c r="D91" s="137" t="s">
         <v>22</v>
       </c>
@@ -7309,39 +7318,39 @@
       <c r="Q91" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R91" s="263"/>
-      <c r="S91" s="264"/>
+      <c r="R91" s="287"/>
+      <c r="S91" s="288"/>
     </row>
     <row r="92" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B92" s="212" t="s">
+      <c r="B92" s="237" t="s">
         <v>79</v>
       </c>
-      <c r="C92" s="213"/>
-      <c r="D92" s="213"/>
-      <c r="E92" s="213"/>
-      <c r="F92" s="213"/>
-      <c r="G92" s="213"/>
-      <c r="H92" s="213"/>
-      <c r="I92" s="213"/>
-      <c r="J92" s="213"/>
-      <c r="K92" s="213"/>
-      <c r="L92" s="213"/>
-      <c r="M92" s="213"/>
-      <c r="N92" s="213"/>
-      <c r="O92" s="213"/>
-      <c r="P92" s="213"/>
-      <c r="Q92" s="213"/>
-      <c r="R92" s="213"/>
-      <c r="S92" s="260"/>
+      <c r="C92" s="294"/>
+      <c r="D92" s="294"/>
+      <c r="E92" s="294"/>
+      <c r="F92" s="294"/>
+      <c r="G92" s="294"/>
+      <c r="H92" s="294"/>
+      <c r="I92" s="294"/>
+      <c r="J92" s="294"/>
+      <c r="K92" s="294"/>
+      <c r="L92" s="294"/>
+      <c r="M92" s="294"/>
+      <c r="N92" s="294"/>
+      <c r="O92" s="294"/>
+      <c r="P92" s="294"/>
+      <c r="Q92" s="294"/>
+      <c r="R92" s="294"/>
+      <c r="S92" s="295"/>
     </row>
     <row r="93" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B93" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C93" s="271" t="s">
+      <c r="C93" s="276" t="s">
         <v>2</v>
       </c>
-      <c r="D93" s="272"/>
+      <c r="D93" s="277"/>
       <c r="E93" s="120" t="s">
         <v>3</v>
       </c>
@@ -7381,16 +7390,16 @@
       <c r="Q93" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R93" s="271" t="s">
+      <c r="R93" s="276" t="s">
         <v>36</v>
       </c>
-      <c r="S93" s="273"/>
+      <c r="S93" s="278"/>
     </row>
     <row r="94" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="248" t="s">
+      <c r="B94" s="279" t="s">
         <v>80</v>
       </c>
-      <c r="C94" s="249" t="s">
+      <c r="C94" s="280" t="s">
         <v>72</v>
       </c>
       <c r="D94" s="137" t="s">
@@ -7438,14 +7447,14 @@
       <c r="Q94" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R94" s="261" t="s">
+      <c r="R94" s="285" t="s">
         <v>73</v>
       </c>
-      <c r="S94" s="262"/>
+      <c r="S94" s="286"/>
     </row>
     <row r="95" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="248"/>
-      <c r="C95" s="249"/>
+      <c r="B95" s="279"/>
+      <c r="C95" s="280"/>
       <c r="D95" s="137" t="s">
         <v>22</v>
       </c>
@@ -7491,39 +7500,39 @@
       <c r="Q95" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R95" s="263"/>
-      <c r="S95" s="264"/>
+      <c r="R95" s="287"/>
+      <c r="S95" s="288"/>
     </row>
     <row r="96" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B96" s="232" t="s">
+      <c r="B96" s="231" t="s">
         <v>83</v>
       </c>
-      <c r="C96" s="233"/>
-      <c r="D96" s="233"/>
-      <c r="E96" s="233"/>
-      <c r="F96" s="233"/>
-      <c r="G96" s="233"/>
-      <c r="H96" s="233"/>
-      <c r="I96" s="233"/>
-      <c r="J96" s="233"/>
-      <c r="K96" s="233"/>
-      <c r="L96" s="233"/>
-      <c r="M96" s="233"/>
-      <c r="N96" s="233"/>
-      <c r="O96" s="233"/>
-      <c r="P96" s="233"/>
-      <c r="Q96" s="233"/>
-      <c r="R96" s="216"/>
-      <c r="S96" s="216"/>
+      <c r="C96" s="261"/>
+      <c r="D96" s="261"/>
+      <c r="E96" s="261"/>
+      <c r="F96" s="261"/>
+      <c r="G96" s="261"/>
+      <c r="H96" s="261"/>
+      <c r="I96" s="261"/>
+      <c r="J96" s="261"/>
+      <c r="K96" s="261"/>
+      <c r="L96" s="261"/>
+      <c r="M96" s="261"/>
+      <c r="N96" s="261"/>
+      <c r="O96" s="261"/>
+      <c r="P96" s="261"/>
+      <c r="Q96" s="261"/>
+      <c r="R96" s="233"/>
+      <c r="S96" s="233"/>
     </row>
     <row r="97" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B97" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C97" s="271" t="s">
+      <c r="C97" s="276" t="s">
         <v>2</v>
       </c>
-      <c r="D97" s="272"/>
+      <c r="D97" s="277"/>
       <c r="E97" s="120" t="s">
         <v>3</v>
       </c>
@@ -7563,16 +7572,16 @@
       <c r="Q97" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R97" s="271" t="s">
+      <c r="R97" s="276" t="s">
         <v>36</v>
       </c>
-      <c r="S97" s="273"/>
+      <c r="S97" s="278"/>
     </row>
     <row r="98" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B98" s="248" t="s">
+      <c r="B98" s="279" t="s">
         <v>84</v>
       </c>
-      <c r="C98" s="249" t="s">
+      <c r="C98" s="280" t="s">
         <v>72</v>
       </c>
       <c r="D98" s="137" t="s">
@@ -7620,15 +7629,15 @@
       <c r="Q98" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R98" s="254" t="s">
-        <v>85</v>
-      </c>
-      <c r="S98" s="255"/>
+      <c r="R98" s="281" t="s">
+        <v>85</v>
+      </c>
+      <c r="S98" s="282"/>
       <c r="T98"/>
     </row>
     <row r="99" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="248"/>
-      <c r="C99" s="249"/>
+      <c r="B99" s="279"/>
+      <c r="C99" s="280"/>
       <c r="D99" s="137" t="s">
         <v>22</v>
       </c>
@@ -7674,40 +7683,40 @@
       <c r="Q99" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R99" s="256"/>
-      <c r="S99" s="257"/>
+      <c r="R99" s="283"/>
+      <c r="S99" s="284"/>
       <c r="T99"/>
     </row>
     <row r="100" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B100" s="232" t="s">
+      <c r="B100" s="231" t="s">
         <v>86</v>
       </c>
-      <c r="C100" s="233"/>
-      <c r="D100" s="233"/>
-      <c r="E100" s="233"/>
-      <c r="F100" s="233"/>
-      <c r="G100" s="233"/>
-      <c r="H100" s="233"/>
-      <c r="I100" s="233"/>
-      <c r="J100" s="233"/>
-      <c r="K100" s="233"/>
-      <c r="L100" s="233"/>
-      <c r="M100" s="233"/>
-      <c r="N100" s="233"/>
-      <c r="O100" s="233"/>
-      <c r="P100" s="233"/>
-      <c r="Q100" s="233"/>
-      <c r="R100" s="233"/>
-      <c r="S100" s="251"/>
+      <c r="C100" s="261"/>
+      <c r="D100" s="261"/>
+      <c r="E100" s="261"/>
+      <c r="F100" s="261"/>
+      <c r="G100" s="261"/>
+      <c r="H100" s="261"/>
+      <c r="I100" s="261"/>
+      <c r="J100" s="261"/>
+      <c r="K100" s="261"/>
+      <c r="L100" s="261"/>
+      <c r="M100" s="261"/>
+      <c r="N100" s="261"/>
+      <c r="O100" s="261"/>
+      <c r="P100" s="261"/>
+      <c r="Q100" s="261"/>
+      <c r="R100" s="261"/>
+      <c r="S100" s="289"/>
     </row>
     <row r="101" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B101" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C101" s="271" t="s">
+      <c r="C101" s="276" t="s">
         <v>2</v>
       </c>
-      <c r="D101" s="272"/>
+      <c r="D101" s="277"/>
       <c r="E101" s="120" t="s">
         <v>3</v>
       </c>
@@ -7747,16 +7756,16 @@
       <c r="Q101" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R101" s="271" t="s">
+      <c r="R101" s="276" t="s">
         <v>36</v>
       </c>
-      <c r="S101" s="273"/>
+      <c r="S101" s="278"/>
     </row>
     <row r="102" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B102" s="248" t="s">
+      <c r="B102" s="279" t="s">
         <v>87</v>
       </c>
-      <c r="C102" s="249" t="s">
+      <c r="C102" s="280" t="s">
         <v>29</v>
       </c>
       <c r="D102" s="137" t="s">
@@ -7804,15 +7813,15 @@
       <c r="Q102" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R102" s="254" t="s">
-        <v>85</v>
-      </c>
-      <c r="S102" s="255"/>
+      <c r="R102" s="281" t="s">
+        <v>85</v>
+      </c>
+      <c r="S102" s="282"/>
       <c r="T102"/>
     </row>
     <row r="103" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B103" s="248"/>
-      <c r="C103" s="249"/>
+      <c r="B103" s="279"/>
+      <c r="C103" s="280"/>
       <c r="D103" s="137" t="s">
         <v>22</v>
       </c>
@@ -7858,8 +7867,8 @@
       <c r="Q103" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R103" s="256"/>
-      <c r="S103" s="257"/>
+      <c r="R103" s="283"/>
+      <c r="S103" s="284"/>
       <c r="T103"/>
     </row>
     <row r="104" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7883,137 +7892,137 @@
       <c r="S104" s="134"/>
     </row>
     <row r="105" spans="2:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B105" s="278" t="s">
+      <c r="B105" s="267" t="s">
         <v>32</v>
       </c>
-      <c r="C105" s="279"/>
-      <c r="D105" s="279"/>
-      <c r="E105" s="279"/>
-      <c r="F105" s="279"/>
-      <c r="G105" s="279"/>
-      <c r="H105" s="279"/>
-      <c r="I105" s="279"/>
-      <c r="J105" s="279"/>
-      <c r="K105" s="279"/>
-      <c r="L105" s="279"/>
-      <c r="M105" s="279"/>
-      <c r="N105" s="279"/>
-      <c r="O105" s="279"/>
-      <c r="P105" s="279"/>
-      <c r="Q105" s="279"/>
-      <c r="R105" s="279"/>
-      <c r="S105" s="280"/>
+      <c r="C105" s="268"/>
+      <c r="D105" s="268"/>
+      <c r="E105" s="268"/>
+      <c r="F105" s="268"/>
+      <c r="G105" s="268"/>
+      <c r="H105" s="268"/>
+      <c r="I105" s="268"/>
+      <c r="J105" s="268"/>
+      <c r="K105" s="268"/>
+      <c r="L105" s="268"/>
+      <c r="M105" s="268"/>
+      <c r="N105" s="268"/>
+      <c r="O105" s="268"/>
+      <c r="P105" s="268"/>
+      <c r="Q105" s="268"/>
+      <c r="R105" s="268"/>
+      <c r="S105" s="269"/>
     </row>
     <row r="106" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B106" s="281" t="s">
+      <c r="B106" s="270" t="s">
         <v>33</v>
       </c>
-      <c r="C106" s="282"/>
-      <c r="D106" s="282"/>
-      <c r="E106" s="282"/>
-      <c r="F106" s="282"/>
-      <c r="G106" s="282"/>
-      <c r="H106" s="282"/>
-      <c r="I106" s="282"/>
-      <c r="J106" s="282"/>
-      <c r="K106" s="282"/>
-      <c r="L106" s="282"/>
-      <c r="M106" s="282"/>
-      <c r="N106" s="282"/>
-      <c r="O106" s="282"/>
-      <c r="P106" s="282"/>
-      <c r="Q106" s="282"/>
-      <c r="R106" s="282"/>
-      <c r="S106" s="283"/>
+      <c r="C106" s="222"/>
+      <c r="D106" s="222"/>
+      <c r="E106" s="222"/>
+      <c r="F106" s="222"/>
+      <c r="G106" s="222"/>
+      <c r="H106" s="222"/>
+      <c r="I106" s="222"/>
+      <c r="J106" s="222"/>
+      <c r="K106" s="222"/>
+      <c r="L106" s="222"/>
+      <c r="M106" s="222"/>
+      <c r="N106" s="222"/>
+      <c r="O106" s="222"/>
+      <c r="P106" s="222"/>
+      <c r="Q106" s="222"/>
+      <c r="R106" s="222"/>
+      <c r="S106" s="271"/>
     </row>
     <row r="107" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B107" s="281"/>
-      <c r="C107" s="282"/>
-      <c r="D107" s="282"/>
-      <c r="E107" s="282"/>
-      <c r="F107" s="282"/>
-      <c r="G107" s="282"/>
-      <c r="H107" s="282"/>
-      <c r="I107" s="282"/>
-      <c r="J107" s="282"/>
-      <c r="K107" s="282"/>
-      <c r="L107" s="282"/>
-      <c r="M107" s="282"/>
-      <c r="N107" s="282"/>
-      <c r="O107" s="282"/>
-      <c r="P107" s="282"/>
-      <c r="Q107" s="282"/>
-      <c r="R107" s="282"/>
-      <c r="S107" s="283"/>
+      <c r="B107" s="270"/>
+      <c r="C107" s="222"/>
+      <c r="D107" s="222"/>
+      <c r="E107" s="222"/>
+      <c r="F107" s="222"/>
+      <c r="G107" s="222"/>
+      <c r="H107" s="222"/>
+      <c r="I107" s="222"/>
+      <c r="J107" s="222"/>
+      <c r="K107" s="222"/>
+      <c r="L107" s="222"/>
+      <c r="M107" s="222"/>
+      <c r="N107" s="222"/>
+      <c r="O107" s="222"/>
+      <c r="P107" s="222"/>
+      <c r="Q107" s="222"/>
+      <c r="R107" s="222"/>
+      <c r="S107" s="271"/>
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B108" s="281"/>
-      <c r="C108" s="282"/>
-      <c r="D108" s="282"/>
-      <c r="E108" s="282"/>
-      <c r="F108" s="282"/>
-      <c r="G108" s="282"/>
-      <c r="H108" s="282"/>
-      <c r="I108" s="282"/>
-      <c r="J108" s="282"/>
-      <c r="K108" s="282"/>
-      <c r="L108" s="282"/>
-      <c r="M108" s="282"/>
-      <c r="N108" s="282"/>
-      <c r="O108" s="282"/>
-      <c r="P108" s="282"/>
-      <c r="Q108" s="282"/>
-      <c r="R108" s="282"/>
-      <c r="S108" s="283"/>
+      <c r="B108" s="270"/>
+      <c r="C108" s="222"/>
+      <c r="D108" s="222"/>
+      <c r="E108" s="222"/>
+      <c r="F108" s="222"/>
+      <c r="G108" s="222"/>
+      <c r="H108" s="222"/>
+      <c r="I108" s="222"/>
+      <c r="J108" s="222"/>
+      <c r="K108" s="222"/>
+      <c r="L108" s="222"/>
+      <c r="M108" s="222"/>
+      <c r="N108" s="222"/>
+      <c r="O108" s="222"/>
+      <c r="P108" s="222"/>
+      <c r="Q108" s="222"/>
+      <c r="R108" s="222"/>
+      <c r="S108" s="271"/>
     </row>
     <row r="109" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="284"/>
-      <c r="C109" s="285"/>
-      <c r="D109" s="285"/>
-      <c r="E109" s="285"/>
-      <c r="F109" s="285"/>
-      <c r="G109" s="285"/>
-      <c r="H109" s="285"/>
-      <c r="I109" s="285"/>
-      <c r="J109" s="285"/>
-      <c r="K109" s="285"/>
-      <c r="L109" s="285"/>
-      <c r="M109" s="285"/>
-      <c r="N109" s="285"/>
-      <c r="O109" s="285"/>
-      <c r="P109" s="285"/>
-      <c r="Q109" s="285"/>
-      <c r="R109" s="285"/>
-      <c r="S109" s="286"/>
+      <c r="B109" s="272"/>
+      <c r="C109" s="273"/>
+      <c r="D109" s="273"/>
+      <c r="E109" s="273"/>
+      <c r="F109" s="273"/>
+      <c r="G109" s="273"/>
+      <c r="H109" s="273"/>
+      <c r="I109" s="273"/>
+      <c r="J109" s="273"/>
+      <c r="K109" s="273"/>
+      <c r="L109" s="273"/>
+      <c r="M109" s="273"/>
+      <c r="N109" s="273"/>
+      <c r="O109" s="273"/>
+      <c r="P109" s="273"/>
+      <c r="Q109" s="273"/>
+      <c r="R109" s="273"/>
+      <c r="S109" s="274"/>
     </row>
     <row r="118" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B118" s="287" t="s">
+      <c r="B118" s="275" t="s">
         <v>88</v>
       </c>
-      <c r="C118" s="287"/>
-      <c r="D118" s="287"/>
-      <c r="E118" s="287"/>
-      <c r="F118" s="287"/>
-      <c r="G118" s="287"/>
-      <c r="H118" s="287"/>
-      <c r="I118" s="287"/>
-      <c r="J118" s="287"/>
-      <c r="K118" s="287"/>
-      <c r="L118" s="287"/>
-      <c r="M118" s="287"/>
-      <c r="N118" s="287"/>
-      <c r="O118" s="287"/>
-      <c r="P118" s="287"/>
+      <c r="C118" s="275"/>
+      <c r="D118" s="275"/>
+      <c r="E118" s="275"/>
+      <c r="F118" s="275"/>
+      <c r="G118" s="275"/>
+      <c r="H118" s="275"/>
+      <c r="I118" s="275"/>
+      <c r="J118" s="275"/>
+      <c r="K118" s="275"/>
+      <c r="L118" s="275"/>
+      <c r="M118" s="275"/>
+      <c r="N118" s="275"/>
+      <c r="O118" s="275"/>
+      <c r="P118" s="275"/>
       <c r="Q118" s="129"/>
     </row>
     <row r="119" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B119" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="C119" s="217" t="s">
+      <c r="C119" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D119" s="217"/>
+      <c r="D119" s="232"/>
       <c r="E119" s="120" t="s">
         <v>3</v>
       </c>
@@ -8044,17 +8053,17 @@
       <c r="N119" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="O119" s="217" t="s">
+      <c r="O119" s="232" t="s">
         <v>36</v>
       </c>
-      <c r="P119" s="217"/>
-      <c r="Q119" s="217"/>
+      <c r="P119" s="232"/>
+      <c r="Q119" s="232"/>
     </row>
     <row r="120" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="214" t="s">
+      <c r="B120" s="228" t="s">
         <v>90</v>
       </c>
-      <c r="C120" s="239" t="s">
+      <c r="C120" s="214" t="s">
         <v>16</v>
       </c>
       <c r="D120" s="20" t="s">
@@ -8092,15 +8101,15 @@
       <c r="N120" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="O120" s="246" t="s">
+      <c r="O120" s="229" t="s">
         <v>44</v>
       </c>
-      <c r="P120" s="246"/>
-      <c r="Q120" s="246"/>
+      <c r="P120" s="229"/>
+      <c r="Q120" s="229"/>
     </row>
     <row r="121" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B121" s="214"/>
-      <c r="C121" s="239"/>
+      <c r="B121" s="228"/>
+      <c r="C121" s="214"/>
       <c r="D121" s="20" t="s">
         <v>22</v>
       </c>
@@ -8136,9 +8145,9 @@
       <c r="N121" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="O121" s="246"/>
-      <c r="P121" s="246"/>
-      <c r="Q121" s="246"/>
+      <c r="O121" s="229"/>
+      <c r="P121" s="229"/>
+      <c r="Q121" s="229"/>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B122" s="42"/>
@@ -8179,78 +8188,78 @@
       <c r="Q123" s="7"/>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B124" s="224" t="s">
+      <c r="B124" s="243" t="s">
         <v>33</v>
       </c>
-      <c r="C124" s="225"/>
-      <c r="D124" s="225"/>
-      <c r="E124" s="225"/>
-      <c r="F124" s="225"/>
-      <c r="G124" s="225"/>
-      <c r="H124" s="225"/>
-      <c r="I124" s="225"/>
-      <c r="J124" s="225"/>
-      <c r="K124" s="225"/>
-      <c r="L124" s="225"/>
-      <c r="M124" s="225"/>
-      <c r="N124" s="225"/>
-      <c r="O124" s="225"/>
-      <c r="P124" s="225"/>
-      <c r="Q124" s="226"/>
+      <c r="C124" s="263"/>
+      <c r="D124" s="263"/>
+      <c r="E124" s="263"/>
+      <c r="F124" s="263"/>
+      <c r="G124" s="263"/>
+      <c r="H124" s="263"/>
+      <c r="I124" s="263"/>
+      <c r="J124" s="263"/>
+      <c r="K124" s="263"/>
+      <c r="L124" s="263"/>
+      <c r="M124" s="263"/>
+      <c r="N124" s="263"/>
+      <c r="O124" s="263"/>
+      <c r="P124" s="263"/>
+      <c r="Q124" s="264"/>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B125" s="224"/>
-      <c r="C125" s="225"/>
-      <c r="D125" s="225"/>
-      <c r="E125" s="225"/>
-      <c r="F125" s="225"/>
-      <c r="G125" s="225"/>
-      <c r="H125" s="225"/>
-      <c r="I125" s="225"/>
-      <c r="J125" s="225"/>
-      <c r="K125" s="225"/>
-      <c r="L125" s="225"/>
-      <c r="M125" s="225"/>
-      <c r="N125" s="225"/>
-      <c r="O125" s="225"/>
-      <c r="P125" s="225"/>
-      <c r="Q125" s="226"/>
+      <c r="B125" s="243"/>
+      <c r="C125" s="263"/>
+      <c r="D125" s="263"/>
+      <c r="E125" s="263"/>
+      <c r="F125" s="263"/>
+      <c r="G125" s="263"/>
+      <c r="H125" s="263"/>
+      <c r="I125" s="263"/>
+      <c r="J125" s="263"/>
+      <c r="K125" s="263"/>
+      <c r="L125" s="263"/>
+      <c r="M125" s="263"/>
+      <c r="N125" s="263"/>
+      <c r="O125" s="263"/>
+      <c r="P125" s="263"/>
+      <c r="Q125" s="264"/>
     </row>
     <row r="126" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B126" s="224"/>
-      <c r="C126" s="225"/>
-      <c r="D126" s="225"/>
-      <c r="E126" s="225"/>
-      <c r="F126" s="225"/>
-      <c r="G126" s="225"/>
-      <c r="H126" s="225"/>
-      <c r="I126" s="225"/>
-      <c r="J126" s="225"/>
-      <c r="K126" s="225"/>
-      <c r="L126" s="225"/>
-      <c r="M126" s="225"/>
-      <c r="N126" s="225"/>
-      <c r="O126" s="225"/>
-      <c r="P126" s="225"/>
-      <c r="Q126" s="226"/>
+      <c r="B126" s="243"/>
+      <c r="C126" s="263"/>
+      <c r="D126" s="263"/>
+      <c r="E126" s="263"/>
+      <c r="F126" s="263"/>
+      <c r="G126" s="263"/>
+      <c r="H126" s="263"/>
+      <c r="I126" s="263"/>
+      <c r="J126" s="263"/>
+      <c r="K126" s="263"/>
+      <c r="L126" s="263"/>
+      <c r="M126" s="263"/>
+      <c r="N126" s="263"/>
+      <c r="O126" s="263"/>
+      <c r="P126" s="263"/>
+      <c r="Q126" s="264"/>
     </row>
     <row r="127" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B127" s="227"/>
-      <c r="C127" s="228"/>
-      <c r="D127" s="228"/>
-      <c r="E127" s="228"/>
-      <c r="F127" s="228"/>
-      <c r="G127" s="228"/>
-      <c r="H127" s="228"/>
-      <c r="I127" s="228"/>
-      <c r="J127" s="228"/>
-      <c r="K127" s="228"/>
-      <c r="L127" s="228"/>
-      <c r="M127" s="228"/>
-      <c r="N127" s="228"/>
-      <c r="O127" s="228"/>
-      <c r="P127" s="228"/>
-      <c r="Q127" s="229"/>
+      <c r="B127" s="244"/>
+      <c r="C127" s="265"/>
+      <c r="D127" s="265"/>
+      <c r="E127" s="265"/>
+      <c r="F127" s="265"/>
+      <c r="G127" s="265"/>
+      <c r="H127" s="265"/>
+      <c r="I127" s="265"/>
+      <c r="J127" s="265"/>
+      <c r="K127" s="265"/>
+      <c r="L127" s="265"/>
+      <c r="M127" s="265"/>
+      <c r="N127" s="265"/>
+      <c r="O127" s="265"/>
+      <c r="P127" s="265"/>
+      <c r="Q127" s="266"/>
     </row>
     <row r="128" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B128" s="35"/>
@@ -8272,32 +8281,32 @@
     </row>
     <row r="133" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="134" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B134" s="232" t="s">
+      <c r="B134" s="231" t="s">
         <v>92</v>
       </c>
-      <c r="C134" s="233"/>
-      <c r="D134" s="233"/>
-      <c r="E134" s="233"/>
-      <c r="F134" s="233"/>
-      <c r="G134" s="233"/>
-      <c r="H134" s="233"/>
-      <c r="I134" s="233"/>
-      <c r="J134" s="233"/>
-      <c r="K134" s="233"/>
-      <c r="L134" s="233"/>
-      <c r="M134" s="233"/>
-      <c r="N134" s="233"/>
-      <c r="O134" s="233"/>
-      <c r="P134" s="233"/>
+      <c r="C134" s="261"/>
+      <c r="D134" s="261"/>
+      <c r="E134" s="261"/>
+      <c r="F134" s="261"/>
+      <c r="G134" s="261"/>
+      <c r="H134" s="261"/>
+      <c r="I134" s="261"/>
+      <c r="J134" s="261"/>
+      <c r="K134" s="261"/>
+      <c r="L134" s="261"/>
+      <c r="M134" s="261"/>
+      <c r="N134" s="261"/>
+      <c r="O134" s="261"/>
+      <c r="P134" s="261"/>
     </row>
     <row r="135" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B135" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C135" s="217" t="s">
+      <c r="C135" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D135" s="217"/>
+      <c r="D135" s="232"/>
       <c r="E135" s="120" t="s">
         <v>3</v>
       </c>
@@ -8385,10 +8394,10 @@
       </c>
     </row>
     <row r="137" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B137" s="234" t="s">
+      <c r="B137" s="262" t="s">
         <v>96</v>
       </c>
-      <c r="C137" s="214" t="s">
+      <c r="C137" s="228" t="s">
         <v>29</v>
       </c>
       <c r="D137" s="117" t="s">
@@ -8435,8 +8444,8 @@
       </c>
     </row>
     <row r="138" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B138" s="234"/>
-      <c r="C138" s="214"/>
+      <c r="B138" s="262"/>
+      <c r="C138" s="228"/>
       <c r="D138" s="117" t="s">
         <v>22</v>
       </c>
@@ -8482,32 +8491,32 @@
     </row>
     <row r="140" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="141" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B141" s="232" t="s">
+      <c r="B141" s="231" t="s">
         <v>97</v>
       </c>
-      <c r="C141" s="233"/>
-      <c r="D141" s="233"/>
-      <c r="E141" s="233"/>
-      <c r="F141" s="233"/>
-      <c r="G141" s="233"/>
-      <c r="H141" s="233"/>
-      <c r="I141" s="233"/>
-      <c r="J141" s="233"/>
-      <c r="K141" s="233"/>
-      <c r="L141" s="233"/>
-      <c r="M141" s="233"/>
-      <c r="N141" s="233"/>
-      <c r="O141" s="233"/>
-      <c r="P141" s="233"/>
+      <c r="C141" s="261"/>
+      <c r="D141" s="261"/>
+      <c r="E141" s="261"/>
+      <c r="F141" s="261"/>
+      <c r="G141" s="261"/>
+      <c r="H141" s="261"/>
+      <c r="I141" s="261"/>
+      <c r="J141" s="261"/>
+      <c r="K141" s="261"/>
+      <c r="L141" s="261"/>
+      <c r="M141" s="261"/>
+      <c r="N141" s="261"/>
+      <c r="O141" s="261"/>
+      <c r="P141" s="261"/>
     </row>
     <row r="142" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B142" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C142" s="217" t="s">
+      <c r="C142" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D142" s="217"/>
+      <c r="D142" s="232"/>
       <c r="E142" s="120" t="s">
         <v>3</v>
       </c>
@@ -8546,10 +8555,10 @@
       </c>
     </row>
     <row r="143" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B143" s="214" t="s">
+      <c r="B143" s="228" t="s">
         <v>98</v>
       </c>
-      <c r="C143" s="214" t="s">
+      <c r="C143" s="228" t="s">
         <v>16</v>
       </c>
       <c r="D143" s="117" t="s">
@@ -8595,8 +8604,8 @@
       </c>
     </row>
     <row r="144" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B144" s="214"/>
-      <c r="C144" s="214"/>
+      <c r="B144" s="228"/>
+      <c r="C144" s="228"/>
       <c r="D144" s="117" t="s">
         <v>22</v>
       </c>
@@ -8640,10 +8649,10 @@
       </c>
     </row>
     <row r="145" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B145" s="214" t="s">
+      <c r="B145" s="228" t="s">
         <v>100</v>
       </c>
-      <c r="C145" s="214" t="s">
+      <c r="C145" s="228" t="s">
         <v>29</v>
       </c>
       <c r="D145" s="117" t="s">
@@ -8689,8 +8698,8 @@
       </c>
     </row>
     <row r="146" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B146" s="214"/>
-      <c r="C146" s="214"/>
+      <c r="B146" s="228"/>
+      <c r="C146" s="228"/>
       <c r="D146" s="117" t="s">
         <v>22</v>
       </c>
@@ -8760,78 +8769,78 @@
       <c r="Q148" s="7"/>
     </row>
     <row r="149" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B149" s="224" t="s">
+      <c r="B149" s="243" t="s">
         <v>33</v>
       </c>
-      <c r="C149" s="225"/>
-      <c r="D149" s="225"/>
-      <c r="E149" s="225"/>
-      <c r="F149" s="225"/>
-      <c r="G149" s="225"/>
-      <c r="H149" s="225"/>
-      <c r="I149" s="225"/>
-      <c r="J149" s="225"/>
-      <c r="K149" s="225"/>
-      <c r="L149" s="225"/>
-      <c r="M149" s="225"/>
-      <c r="N149" s="225"/>
-      <c r="O149" s="225"/>
-      <c r="P149" s="225"/>
-      <c r="Q149" s="226"/>
+      <c r="C149" s="263"/>
+      <c r="D149" s="263"/>
+      <c r="E149" s="263"/>
+      <c r="F149" s="263"/>
+      <c r="G149" s="263"/>
+      <c r="H149" s="263"/>
+      <c r="I149" s="263"/>
+      <c r="J149" s="263"/>
+      <c r="K149" s="263"/>
+      <c r="L149" s="263"/>
+      <c r="M149" s="263"/>
+      <c r="N149" s="263"/>
+      <c r="O149" s="263"/>
+      <c r="P149" s="263"/>
+      <c r="Q149" s="264"/>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B150" s="224"/>
-      <c r="C150" s="225"/>
-      <c r="D150" s="225"/>
-      <c r="E150" s="225"/>
-      <c r="F150" s="225"/>
-      <c r="G150" s="225"/>
-      <c r="H150" s="225"/>
-      <c r="I150" s="225"/>
-      <c r="J150" s="225"/>
-      <c r="K150" s="225"/>
-      <c r="L150" s="225"/>
-      <c r="M150" s="225"/>
-      <c r="N150" s="225"/>
-      <c r="O150" s="225"/>
-      <c r="P150" s="225"/>
-      <c r="Q150" s="226"/>
+      <c r="B150" s="243"/>
+      <c r="C150" s="263"/>
+      <c r="D150" s="263"/>
+      <c r="E150" s="263"/>
+      <c r="F150" s="263"/>
+      <c r="G150" s="263"/>
+      <c r="H150" s="263"/>
+      <c r="I150" s="263"/>
+      <c r="J150" s="263"/>
+      <c r="K150" s="263"/>
+      <c r="L150" s="263"/>
+      <c r="M150" s="263"/>
+      <c r="N150" s="263"/>
+      <c r="O150" s="263"/>
+      <c r="P150" s="263"/>
+      <c r="Q150" s="264"/>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B151" s="224"/>
-      <c r="C151" s="225"/>
-      <c r="D151" s="225"/>
-      <c r="E151" s="225"/>
-      <c r="F151" s="225"/>
-      <c r="G151" s="225"/>
-      <c r="H151" s="225"/>
-      <c r="I151" s="225"/>
-      <c r="J151" s="225"/>
-      <c r="K151" s="225"/>
-      <c r="L151" s="225"/>
-      <c r="M151" s="225"/>
-      <c r="N151" s="225"/>
-      <c r="O151" s="225"/>
-      <c r="P151" s="225"/>
-      <c r="Q151" s="226"/>
+      <c r="B151" s="243"/>
+      <c r="C151" s="263"/>
+      <c r="D151" s="263"/>
+      <c r="E151" s="263"/>
+      <c r="F151" s="263"/>
+      <c r="G151" s="263"/>
+      <c r="H151" s="263"/>
+      <c r="I151" s="263"/>
+      <c r="J151" s="263"/>
+      <c r="K151" s="263"/>
+      <c r="L151" s="263"/>
+      <c r="M151" s="263"/>
+      <c r="N151" s="263"/>
+      <c r="O151" s="263"/>
+      <c r="P151" s="263"/>
+      <c r="Q151" s="264"/>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B152" s="227"/>
-      <c r="C152" s="228"/>
-      <c r="D152" s="228"/>
-      <c r="E152" s="228"/>
-      <c r="F152" s="228"/>
-      <c r="G152" s="228"/>
-      <c r="H152" s="228"/>
-      <c r="I152" s="228"/>
-      <c r="J152" s="228"/>
-      <c r="K152" s="228"/>
-      <c r="L152" s="228"/>
-      <c r="M152" s="228"/>
-      <c r="N152" s="228"/>
-      <c r="O152" s="228"/>
-      <c r="P152" s="228"/>
-      <c r="Q152" s="229"/>
+      <c r="B152" s="244"/>
+      <c r="C152" s="265"/>
+      <c r="D152" s="265"/>
+      <c r="E152" s="265"/>
+      <c r="F152" s="265"/>
+      <c r="G152" s="265"/>
+      <c r="H152" s="265"/>
+      <c r="I152" s="265"/>
+      <c r="J152" s="265"/>
+      <c r="K152" s="265"/>
+      <c r="L152" s="265"/>
+      <c r="M152" s="265"/>
+      <c r="N152" s="265"/>
+      <c r="O152" s="265"/>
+      <c r="P152" s="265"/>
+      <c r="Q152" s="266"/>
     </row>
     <row r="154" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B154" s="35"/>
@@ -8852,32 +8861,32 @@
     </row>
     <row r="159" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="160" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B160" s="232" t="s">
+      <c r="B160" s="231" t="s">
         <v>101</v>
       </c>
-      <c r="C160" s="233"/>
-      <c r="D160" s="233"/>
-      <c r="E160" s="233"/>
-      <c r="F160" s="233"/>
-      <c r="G160" s="233"/>
-      <c r="H160" s="233"/>
-      <c r="I160" s="233"/>
-      <c r="J160" s="233"/>
-      <c r="K160" s="233"/>
-      <c r="L160" s="233"/>
-      <c r="M160" s="233"/>
-      <c r="N160" s="233"/>
-      <c r="O160" s="233"/>
-      <c r="P160" s="233"/>
+      <c r="C160" s="261"/>
+      <c r="D160" s="261"/>
+      <c r="E160" s="261"/>
+      <c r="F160" s="261"/>
+      <c r="G160" s="261"/>
+      <c r="H160" s="261"/>
+      <c r="I160" s="261"/>
+      <c r="J160" s="261"/>
+      <c r="K160" s="261"/>
+      <c r="L160" s="261"/>
+      <c r="M160" s="261"/>
+      <c r="N160" s="261"/>
+      <c r="O160" s="261"/>
+      <c r="P160" s="261"/>
     </row>
     <row r="161" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B161" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C161" s="217" t="s">
+      <c r="C161" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D161" s="217"/>
+      <c r="D161" s="232"/>
       <c r="E161" s="120" t="s">
         <v>3</v>
       </c>
@@ -8916,10 +8925,10 @@
       </c>
     </row>
     <row r="162" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B162" s="234" t="s">
+      <c r="B162" s="262" t="s">
         <v>102</v>
       </c>
-      <c r="C162" s="214" t="s">
+      <c r="C162" s="228" t="s">
         <v>103</v>
       </c>
       <c r="D162" s="117" t="s">
@@ -8965,8 +8974,8 @@
       </c>
     </row>
     <row r="163" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B163" s="234"/>
-      <c r="C163" s="214"/>
+      <c r="B163" s="262"/>
+      <c r="C163" s="228"/>
       <c r="D163" s="117" t="s">
         <v>22</v>
       </c>
@@ -9030,78 +9039,78 @@
       <c r="Q165" s="7"/>
     </row>
     <row r="166" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B166" s="224" t="s">
+      <c r="B166" s="243" t="s">
         <v>33</v>
       </c>
-      <c r="C166" s="225"/>
-      <c r="D166" s="225"/>
-      <c r="E166" s="225"/>
-      <c r="F166" s="225"/>
-      <c r="G166" s="225"/>
-      <c r="H166" s="225"/>
-      <c r="I166" s="225"/>
-      <c r="J166" s="225"/>
-      <c r="K166" s="225"/>
-      <c r="L166" s="225"/>
-      <c r="M166" s="225"/>
-      <c r="N166" s="225"/>
-      <c r="O166" s="225"/>
-      <c r="P166" s="225"/>
-      <c r="Q166" s="226"/>
+      <c r="C166" s="263"/>
+      <c r="D166" s="263"/>
+      <c r="E166" s="263"/>
+      <c r="F166" s="263"/>
+      <c r="G166" s="263"/>
+      <c r="H166" s="263"/>
+      <c r="I166" s="263"/>
+      <c r="J166" s="263"/>
+      <c r="K166" s="263"/>
+      <c r="L166" s="263"/>
+      <c r="M166" s="263"/>
+      <c r="N166" s="263"/>
+      <c r="O166" s="263"/>
+      <c r="P166" s="263"/>
+      <c r="Q166" s="264"/>
     </row>
     <row r="167" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B167" s="224"/>
-      <c r="C167" s="225"/>
-      <c r="D167" s="225"/>
-      <c r="E167" s="225"/>
-      <c r="F167" s="225"/>
-      <c r="G167" s="225"/>
-      <c r="H167" s="225"/>
-      <c r="I167" s="225"/>
-      <c r="J167" s="225"/>
-      <c r="K167" s="225"/>
-      <c r="L167" s="225"/>
-      <c r="M167" s="225"/>
-      <c r="N167" s="225"/>
-      <c r="O167" s="225"/>
-      <c r="P167" s="225"/>
-      <c r="Q167" s="226"/>
+      <c r="B167" s="243"/>
+      <c r="C167" s="263"/>
+      <c r="D167" s="263"/>
+      <c r="E167" s="263"/>
+      <c r="F167" s="263"/>
+      <c r="G167" s="263"/>
+      <c r="H167" s="263"/>
+      <c r="I167" s="263"/>
+      <c r="J167" s="263"/>
+      <c r="K167" s="263"/>
+      <c r="L167" s="263"/>
+      <c r="M167" s="263"/>
+      <c r="N167" s="263"/>
+      <c r="O167" s="263"/>
+      <c r="P167" s="263"/>
+      <c r="Q167" s="264"/>
     </row>
     <row r="168" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B168" s="224"/>
-      <c r="C168" s="225"/>
-      <c r="D168" s="225"/>
-      <c r="E168" s="225"/>
-      <c r="F168" s="225"/>
-      <c r="G168" s="225"/>
-      <c r="H168" s="225"/>
-      <c r="I168" s="225"/>
-      <c r="J168" s="225"/>
-      <c r="K168" s="225"/>
-      <c r="L168" s="225"/>
-      <c r="M168" s="225"/>
-      <c r="N168" s="225"/>
-      <c r="O168" s="225"/>
-      <c r="P168" s="225"/>
-      <c r="Q168" s="226"/>
+      <c r="B168" s="243"/>
+      <c r="C168" s="263"/>
+      <c r="D168" s="263"/>
+      <c r="E168" s="263"/>
+      <c r="F168" s="263"/>
+      <c r="G168" s="263"/>
+      <c r="H168" s="263"/>
+      <c r="I168" s="263"/>
+      <c r="J168" s="263"/>
+      <c r="K168" s="263"/>
+      <c r="L168" s="263"/>
+      <c r="M168" s="263"/>
+      <c r="N168" s="263"/>
+      <c r="O168" s="263"/>
+      <c r="P168" s="263"/>
+      <c r="Q168" s="264"/>
     </row>
     <row r="169" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B169" s="227"/>
-      <c r="C169" s="228"/>
-      <c r="D169" s="228"/>
-      <c r="E169" s="228"/>
-      <c r="F169" s="228"/>
-      <c r="G169" s="228"/>
-      <c r="H169" s="228"/>
-      <c r="I169" s="228"/>
-      <c r="J169" s="228"/>
-      <c r="K169" s="228"/>
-      <c r="L169" s="228"/>
-      <c r="M169" s="228"/>
-      <c r="N169" s="228"/>
-      <c r="O169" s="228"/>
-      <c r="P169" s="228"/>
-      <c r="Q169" s="229"/>
+      <c r="B169" s="244"/>
+      <c r="C169" s="265"/>
+      <c r="D169" s="265"/>
+      <c r="E169" s="265"/>
+      <c r="F169" s="265"/>
+      <c r="G169" s="265"/>
+      <c r="H169" s="265"/>
+      <c r="I169" s="265"/>
+      <c r="J169" s="265"/>
+      <c r="K169" s="265"/>
+      <c r="L169" s="265"/>
+      <c r="M169" s="265"/>
+      <c r="N169" s="265"/>
+      <c r="O169" s="265"/>
+      <c r="P169" s="265"/>
+      <c r="Q169" s="266"/>
     </row>
     <row r="170" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B170" s="35"/>
@@ -9140,33 +9149,33 @@
       <c r="Q171" s="35"/>
     </row>
     <row r="173" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B173" s="215" t="s">
+      <c r="B173" s="238" t="s">
         <v>104</v>
       </c>
-      <c r="C173" s="216"/>
-      <c r="D173" s="216"/>
-      <c r="E173" s="216"/>
-      <c r="F173" s="216"/>
-      <c r="G173" s="216"/>
-      <c r="H173" s="216"/>
-      <c r="I173" s="216"/>
-      <c r="J173" s="216"/>
-      <c r="K173" s="216"/>
-      <c r="L173" s="216"/>
-      <c r="M173" s="216"/>
-      <c r="N173" s="216"/>
-      <c r="O173" s="216"/>
-      <c r="P173" s="216"/>
-      <c r="Q173" s="216"/>
+      <c r="C173" s="233"/>
+      <c r="D173" s="233"/>
+      <c r="E173" s="233"/>
+      <c r="F173" s="233"/>
+      <c r="G173" s="233"/>
+      <c r="H173" s="233"/>
+      <c r="I173" s="233"/>
+      <c r="J173" s="233"/>
+      <c r="K173" s="233"/>
+      <c r="L173" s="233"/>
+      <c r="M173" s="233"/>
+      <c r="N173" s="233"/>
+      <c r="O173" s="233"/>
+      <c r="P173" s="233"/>
+      <c r="Q173" s="233"/>
     </row>
     <row r="174" spans="2:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B174" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C174" s="217" t="s">
+      <c r="C174" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D174" s="217"/>
+      <c r="D174" s="232"/>
       <c r="E174" s="120" t="s">
         <v>3</v>
       </c>
@@ -9208,10 +9217,10 @@
       </c>
     </row>
     <row r="175" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B175" s="218" t="s">
+      <c r="B175" s="227" t="s">
         <v>110</v>
       </c>
-      <c r="C175" s="214" t="s">
+      <c r="C175" s="228" t="s">
         <v>29</v>
       </c>
       <c r="D175" s="117" t="s">
@@ -9260,8 +9269,8 @@
       </c>
     </row>
     <row r="176" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B176" s="219"/>
-      <c r="C176" s="214"/>
+      <c r="B176" s="298"/>
+      <c r="C176" s="228"/>
       <c r="D176" s="117" t="s">
         <v>22</v>
       </c>
@@ -9326,32 +9335,32 @@
     </row>
     <row r="185" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="186" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B186" s="232" t="s">
+      <c r="B186" s="231" t="s">
         <v>112</v>
       </c>
-      <c r="C186" s="233"/>
-      <c r="D186" s="233"/>
-      <c r="E186" s="233"/>
-      <c r="F186" s="233"/>
-      <c r="G186" s="233"/>
-      <c r="H186" s="233"/>
-      <c r="I186" s="233"/>
-      <c r="J186" s="233"/>
-      <c r="K186" s="233"/>
-      <c r="L186" s="233"/>
-      <c r="M186" s="233"/>
-      <c r="N186" s="233"/>
-      <c r="O186" s="233"/>
-      <c r="P186" s="233"/>
+      <c r="C186" s="261"/>
+      <c r="D186" s="261"/>
+      <c r="E186" s="261"/>
+      <c r="F186" s="261"/>
+      <c r="G186" s="261"/>
+      <c r="H186" s="261"/>
+      <c r="I186" s="261"/>
+      <c r="J186" s="261"/>
+      <c r="K186" s="261"/>
+      <c r="L186" s="261"/>
+      <c r="M186" s="261"/>
+      <c r="N186" s="261"/>
+      <c r="O186" s="261"/>
+      <c r="P186" s="261"/>
     </row>
     <row r="187" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B187" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C187" s="217" t="s">
+      <c r="C187" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D187" s="217"/>
+      <c r="D187" s="232"/>
       <c r="E187" s="120" t="s">
         <v>3</v>
       </c>
@@ -9390,10 +9399,10 @@
       </c>
     </row>
     <row r="188" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B188" s="234" t="s">
+      <c r="B188" s="262" t="s">
         <v>114</v>
       </c>
-      <c r="C188" s="214" t="s">
+      <c r="C188" s="228" t="s">
         <v>81</v>
       </c>
       <c r="D188" s="117" t="s">
@@ -9439,8 +9448,8 @@
       </c>
     </row>
     <row r="189" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B189" s="234"/>
-      <c r="C189" s="214"/>
+      <c r="B189" s="262"/>
+      <c r="C189" s="228"/>
       <c r="D189" s="117" t="s">
         <v>22</v>
       </c>
@@ -9488,62 +9497,48 @@
     </row>
   </sheetData>
   <mergeCells count="122">
-    <mergeCell ref="B160:P160"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="B166:Q169"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="C145:C146"/>
-    <mergeCell ref="B149:Q152"/>
-    <mergeCell ref="B124:Q127"/>
-    <mergeCell ref="B134:P134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="B141:P141"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="B105:S105"/>
-    <mergeCell ref="B106:S109"/>
-    <mergeCell ref="B118:P118"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="O119:Q119"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="O120:Q121"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="R101:S101"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="R102:S103"/>
-    <mergeCell ref="B96:S96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="R97:S97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="R98:S99"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="R94:S95"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="R89:S89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="R90:S91"/>
-    <mergeCell ref="B100:S100"/>
-    <mergeCell ref="R86:S87"/>
-    <mergeCell ref="B80:S80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="R82:S83"/>
-    <mergeCell ref="B92:S92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="B88:S88"/>
+    <mergeCell ref="B186:P186"/>
+    <mergeCell ref="C187:D187"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="C188:C189"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="B175:B176"/>
+    <mergeCell ref="C175:C176"/>
+    <mergeCell ref="B8:P8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B35:P35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="O37:P38"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B24:P27"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="B43:Q46"/>
+    <mergeCell ref="B56:S56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="R58:S61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="R74:S79"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
     <mergeCell ref="B173:Q173"/>
     <mergeCell ref="R72:S73"/>
     <mergeCell ref="B62:B63"/>
@@ -9568,48 +9563,62 @@
     <mergeCell ref="B86:B87"/>
     <mergeCell ref="C86:C87"/>
     <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B24:P27"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="B43:Q46"/>
-    <mergeCell ref="B56:S56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="R58:S61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="R74:S79"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="B186:P186"/>
-    <mergeCell ref="C187:D187"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="C188:C189"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="B175:B176"/>
-    <mergeCell ref="C175:C176"/>
-    <mergeCell ref="B8:P8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B35:P35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="O37:P38"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="R86:S87"/>
+    <mergeCell ref="B80:S80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="R82:S83"/>
+    <mergeCell ref="B92:S92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="B88:S88"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="R94:S95"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="R89:S89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="R90:S91"/>
+    <mergeCell ref="B100:S100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="R101:S101"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="R102:S103"/>
+    <mergeCell ref="B96:S96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="R97:S97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="R98:S99"/>
+    <mergeCell ref="B124:Q127"/>
+    <mergeCell ref="B134:P134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="B141:P141"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="B105:S105"/>
+    <mergeCell ref="B106:S109"/>
+    <mergeCell ref="B118:P118"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="O119:Q119"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="O120:Q121"/>
+    <mergeCell ref="B160:P160"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="B166:Q169"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="C145:C146"/>
+    <mergeCell ref="B149:Q152"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9646,33 +9655,33 @@
   </cols>
   <sheetData>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="216" t="s">
+      <c r="B9" s="233" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="216"/>
-      <c r="D9" s="216"/>
-      <c r="E9" s="216"/>
-      <c r="F9" s="216"/>
-      <c r="G9" s="216"/>
-      <c r="H9" s="216"/>
-      <c r="I9" s="216"/>
-      <c r="J9" s="216"/>
-      <c r="K9" s="216"/>
-      <c r="L9" s="216"/>
-      <c r="M9" s="216"/>
-      <c r="N9" s="216"/>
-      <c r="O9" s="216"/>
-      <c r="P9" s="216"/>
-      <c r="Q9" s="216"/>
+      <c r="C9" s="233"/>
+      <c r="D9" s="233"/>
+      <c r="E9" s="233"/>
+      <c r="F9" s="233"/>
+      <c r="G9" s="233"/>
+      <c r="H9" s="233"/>
+      <c r="I9" s="233"/>
+      <c r="J9" s="233"/>
+      <c r="K9" s="233"/>
+      <c r="L9" s="233"/>
+      <c r="M9" s="233"/>
+      <c r="N9" s="233"/>
+      <c r="O9" s="233"/>
+      <c r="P9" s="233"/>
+      <c r="Q9" s="233"/>
     </row>
     <row r="10" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="303" t="s">
+      <c r="C10" s="234" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="303"/>
+      <c r="D10" s="234"/>
       <c r="E10" s="8" t="s">
         <v>3</v>
       </c>
@@ -9712,10 +9721,10 @@
       <c r="Q10" s="17"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="239" t="s">
+      <c r="B11" s="214" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="239" t="s">
+      <c r="C11" s="214" t="s">
         <v>110</v>
       </c>
       <c r="D11" s="53" t="s">
@@ -9763,8 +9772,8 @@
       <c r="Q11" s="49"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="239"/>
-      <c r="C12" s="239"/>
+      <c r="B12" s="214"/>
+      <c r="C12" s="214"/>
       <c r="D12" s="53" t="s">
         <v>22</v>
       </c>
@@ -9810,10 +9819,10 @@
       <c r="Q12" s="49"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="239" t="s">
+      <c r="B13" s="214" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="239" t="s">
+      <c r="C13" s="214" t="s">
         <v>110</v>
       </c>
       <c r="D13" s="53" t="s">
@@ -9861,8 +9870,8 @@
       <c r="Q13" s="49"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="239"/>
-      <c r="C14" s="239"/>
+      <c r="B14" s="214"/>
+      <c r="C14" s="214"/>
       <c r="D14" s="53" t="s">
         <v>22</v>
       </c>
@@ -9908,10 +9917,10 @@
       <c r="Q14" s="49"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="253" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="239" t="s">
+      <c r="C15" s="214" t="s">
         <v>110</v>
       </c>
       <c r="D15" s="53" t="s">
@@ -9959,8 +9968,8 @@
       <c r="Q15" s="49"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="237"/>
-      <c r="C16" s="239"/>
+      <c r="B16" s="253"/>
+      <c r="C16" s="214"/>
       <c r="D16" s="53" t="s">
         <v>22</v>
       </c>
@@ -10006,10 +10015,10 @@
       <c r="Q16" s="49"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="239" t="s">
+      <c r="B17" s="214" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="239" t="s">
+      <c r="C17" s="214" t="s">
         <v>110</v>
       </c>
       <c r="D17" s="53" t="s">
@@ -10057,8 +10066,8 @@
       <c r="Q17" s="49"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="239"/>
-      <c r="C18" s="239"/>
+      <c r="B18" s="214"/>
+      <c r="C18" s="214"/>
       <c r="D18" s="53" t="s">
         <v>22</v>
       </c>
@@ -10121,103 +10130,103 @@
       <c r="Q19" s="34"/>
     </row>
     <row r="20" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="306" t="s">
+      <c r="B20" s="215" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="307"/>
-      <c r="D20" s="307"/>
-      <c r="E20" s="307"/>
-      <c r="F20" s="307"/>
-      <c r="G20" s="307"/>
-      <c r="H20" s="307"/>
-      <c r="I20" s="307"/>
-      <c r="J20" s="307"/>
-      <c r="K20" s="307"/>
-      <c r="L20" s="307"/>
-      <c r="M20" s="307"/>
-      <c r="N20" s="307"/>
-      <c r="O20" s="307"/>
-      <c r="P20" s="307"/>
-      <c r="Q20" s="307"/>
-      <c r="R20" s="308"/>
+      <c r="C20" s="216"/>
+      <c r="D20" s="216"/>
+      <c r="E20" s="216"/>
+      <c r="F20" s="216"/>
+      <c r="G20" s="216"/>
+      <c r="H20" s="216"/>
+      <c r="I20" s="216"/>
+      <c r="J20" s="216"/>
+      <c r="K20" s="216"/>
+      <c r="L20" s="216"/>
+      <c r="M20" s="216"/>
+      <c r="N20" s="216"/>
+      <c r="O20" s="216"/>
+      <c r="P20" s="216"/>
+      <c r="Q20" s="216"/>
+      <c r="R20" s="217"/>
     </row>
     <row r="21" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="309" t="s">
+      <c r="B21" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="310"/>
-      <c r="D21" s="310"/>
-      <c r="E21" s="310"/>
-      <c r="F21" s="310"/>
-      <c r="G21" s="310"/>
-      <c r="H21" s="310"/>
-      <c r="I21" s="310"/>
-      <c r="J21" s="310"/>
-      <c r="K21" s="310"/>
-      <c r="L21" s="310"/>
-      <c r="M21" s="310"/>
-      <c r="N21" s="310"/>
-      <c r="O21" s="310"/>
-      <c r="P21" s="310"/>
-      <c r="Q21" s="310"/>
-      <c r="R21" s="311"/>
+      <c r="C21" s="219"/>
+      <c r="D21" s="219"/>
+      <c r="E21" s="219"/>
+      <c r="F21" s="219"/>
+      <c r="G21" s="219"/>
+      <c r="H21" s="219"/>
+      <c r="I21" s="219"/>
+      <c r="J21" s="219"/>
+      <c r="K21" s="219"/>
+      <c r="L21" s="219"/>
+      <c r="M21" s="219"/>
+      <c r="N21" s="219"/>
+      <c r="O21" s="219"/>
+      <c r="P21" s="219"/>
+      <c r="Q21" s="219"/>
+      <c r="R21" s="220"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B22" s="312"/>
-      <c r="C22" s="282"/>
-      <c r="D22" s="282"/>
-      <c r="E22" s="282"/>
-      <c r="F22" s="282"/>
-      <c r="G22" s="282"/>
-      <c r="H22" s="282"/>
-      <c r="I22" s="282"/>
-      <c r="J22" s="282"/>
-      <c r="K22" s="282"/>
-      <c r="L22" s="282"/>
-      <c r="M22" s="282"/>
-      <c r="N22" s="282"/>
-      <c r="O22" s="282"/>
-      <c r="P22" s="282"/>
-      <c r="Q22" s="282"/>
-      <c r="R22" s="313"/>
+      <c r="B22" s="221"/>
+      <c r="C22" s="222"/>
+      <c r="D22" s="222"/>
+      <c r="E22" s="222"/>
+      <c r="F22" s="222"/>
+      <c r="G22" s="222"/>
+      <c r="H22" s="222"/>
+      <c r="I22" s="222"/>
+      <c r="J22" s="222"/>
+      <c r="K22" s="222"/>
+      <c r="L22" s="222"/>
+      <c r="M22" s="222"/>
+      <c r="N22" s="222"/>
+      <c r="O22" s="222"/>
+      <c r="P22" s="222"/>
+      <c r="Q22" s="222"/>
+      <c r="R22" s="223"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B23" s="312"/>
-      <c r="C23" s="282"/>
-      <c r="D23" s="282"/>
-      <c r="E23" s="282"/>
-      <c r="F23" s="282"/>
-      <c r="G23" s="282"/>
-      <c r="H23" s="282"/>
-      <c r="I23" s="282"/>
-      <c r="J23" s="282"/>
-      <c r="K23" s="282"/>
-      <c r="L23" s="282"/>
-      <c r="M23" s="282"/>
-      <c r="N23" s="282"/>
-      <c r="O23" s="282"/>
-      <c r="P23" s="282"/>
-      <c r="Q23" s="282"/>
-      <c r="R23" s="313"/>
+      <c r="B23" s="221"/>
+      <c r="C23" s="222"/>
+      <c r="D23" s="222"/>
+      <c r="E23" s="222"/>
+      <c r="F23" s="222"/>
+      <c r="G23" s="222"/>
+      <c r="H23" s="222"/>
+      <c r="I23" s="222"/>
+      <c r="J23" s="222"/>
+      <c r="K23" s="222"/>
+      <c r="L23" s="222"/>
+      <c r="M23" s="222"/>
+      <c r="N23" s="222"/>
+      <c r="O23" s="222"/>
+      <c r="P23" s="222"/>
+      <c r="Q23" s="222"/>
+      <c r="R23" s="223"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B24" s="314"/>
-      <c r="C24" s="315"/>
-      <c r="D24" s="315"/>
-      <c r="E24" s="315"/>
-      <c r="F24" s="315"/>
-      <c r="G24" s="315"/>
-      <c r="H24" s="315"/>
-      <c r="I24" s="315"/>
-      <c r="J24" s="315"/>
-      <c r="K24" s="315"/>
-      <c r="L24" s="315"/>
-      <c r="M24" s="315"/>
-      <c r="N24" s="315"/>
-      <c r="O24" s="315"/>
-      <c r="P24" s="315"/>
-      <c r="Q24" s="315"/>
-      <c r="R24" s="316"/>
+      <c r="B24" s="224"/>
+      <c r="C24" s="225"/>
+      <c r="D24" s="225"/>
+      <c r="E24" s="225"/>
+      <c r="F24" s="225"/>
+      <c r="G24" s="225"/>
+      <c r="H24" s="225"/>
+      <c r="I24" s="225"/>
+      <c r="J24" s="225"/>
+      <c r="K24" s="225"/>
+      <c r="L24" s="225"/>
+      <c r="M24" s="225"/>
+      <c r="N24" s="225"/>
+      <c r="O24" s="225"/>
+      <c r="P24" s="225"/>
+      <c r="Q24" s="225"/>
+      <c r="R24" s="226"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B25" s="27"/>
@@ -10373,34 +10382,34 @@
       <c r="Q33" s="34"/>
     </row>
     <row r="34" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B34" s="240" t="s">
+      <c r="B34" s="245" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="240"/>
-      <c r="D34" s="240"/>
-      <c r="E34" s="240"/>
-      <c r="F34" s="240"/>
-      <c r="G34" s="240"/>
-      <c r="H34" s="240"/>
-      <c r="I34" s="240"/>
-      <c r="J34" s="240"/>
-      <c r="K34" s="240"/>
-      <c r="L34" s="240"/>
-      <c r="M34" s="240"/>
-      <c r="N34" s="240"/>
-      <c r="O34" s="240"/>
-      <c r="P34" s="240"/>
-      <c r="Q34" s="240"/>
-      <c r="R34" s="240"/>
+      <c r="C34" s="245"/>
+      <c r="D34" s="245"/>
+      <c r="E34" s="245"/>
+      <c r="F34" s="245"/>
+      <c r="G34" s="245"/>
+      <c r="H34" s="245"/>
+      <c r="I34" s="245"/>
+      <c r="J34" s="245"/>
+      <c r="K34" s="245"/>
+      <c r="L34" s="245"/>
+      <c r="M34" s="245"/>
+      <c r="N34" s="245"/>
+      <c r="O34" s="245"/>
+      <c r="P34" s="245"/>
+      <c r="Q34" s="245"/>
+      <c r="R34" s="245"/>
     </row>
     <row r="35" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="303" t="s">
+      <c r="C35" s="234" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="303"/>
+      <c r="D35" s="234"/>
       <c r="E35" s="127" t="s">
         <v>125</v>
       </c>
@@ -10432,17 +10441,17 @@
         <v>14</v>
       </c>
       <c r="O35" s="124"/>
-      <c r="P35" s="217" t="s">
+      <c r="P35" s="232" t="s">
         <v>36</v>
       </c>
-      <c r="Q35" s="217"/>
-      <c r="R35" s="217"/>
+      <c r="Q35" s="232"/>
+      <c r="R35" s="232"/>
     </row>
     <row r="36" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="241" t="s">
+      <c r="B36" s="254" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="239" t="s">
+      <c r="C36" s="214" t="s">
         <v>110</v>
       </c>
       <c r="D36" s="53" t="s">
@@ -10482,15 +10491,15 @@
         <v>91</v>
       </c>
       <c r="O36" s="53"/>
-      <c r="P36" s="242" t="s">
+      <c r="P36" s="255" t="s">
         <v>129</v>
       </c>
-      <c r="Q36" s="298"/>
-      <c r="R36" s="243"/>
+      <c r="Q36" s="256"/>
+      <c r="R36" s="257"/>
     </row>
     <row r="37" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B37" s="241"/>
-      <c r="C37" s="239"/>
+      <c r="B37" s="254"/>
+      <c r="C37" s="214"/>
       <c r="D37" s="53" t="s">
         <v>22</v>
       </c>
@@ -10528,9 +10537,9 @@
         <v>91</v>
       </c>
       <c r="O37" s="53"/>
-      <c r="P37" s="299"/>
-      <c r="Q37" s="300"/>
-      <c r="R37" s="301"/>
+      <c r="P37" s="258"/>
+      <c r="Q37" s="259"/>
+      <c r="R37" s="260"/>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B38" s="123" t="s">
@@ -10575,11 +10584,11 @@
         <v>43</v>
       </c>
       <c r="O38" s="53"/>
-      <c r="P38" s="295" t="s">
+      <c r="P38" s="246" t="s">
         <v>132</v>
       </c>
-      <c r="Q38" s="296"/>
-      <c r="R38" s="297"/>
+      <c r="Q38" s="247"/>
+      <c r="R38" s="248"/>
     </row>
     <row r="39" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="125" t="s">
@@ -10625,11 +10634,11 @@
         <v>91</v>
       </c>
       <c r="O39" s="53"/>
-      <c r="P39" s="295" t="s">
+      <c r="P39" s="246" t="s">
         <v>132</v>
       </c>
-      <c r="Q39" s="296"/>
-      <c r="R39" s="297"/>
+      <c r="Q39" s="247"/>
+      <c r="R39" s="248"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="42"/>
@@ -10672,86 +10681,86 @@
       <c r="S41" s="7"/>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B42" s="224" t="s">
+      <c r="B42" s="243" t="s">
         <v>33</v>
       </c>
-      <c r="C42" s="224"/>
-      <c r="D42" s="224"/>
-      <c r="E42" s="224"/>
-      <c r="F42" s="224"/>
-      <c r="G42" s="224"/>
-      <c r="H42" s="224"/>
-      <c r="I42" s="224"/>
-      <c r="J42" s="224"/>
-      <c r="K42" s="224"/>
-      <c r="L42" s="224"/>
-      <c r="M42" s="224"/>
-      <c r="N42" s="224"/>
-      <c r="O42" s="224"/>
-      <c r="P42" s="224"/>
-      <c r="Q42" s="224"/>
-      <c r="R42" s="224"/>
-      <c r="S42" s="224"/>
+      <c r="C42" s="243"/>
+      <c r="D42" s="243"/>
+      <c r="E42" s="243"/>
+      <c r="F42" s="243"/>
+      <c r="G42" s="243"/>
+      <c r="H42" s="243"/>
+      <c r="I42" s="243"/>
+      <c r="J42" s="243"/>
+      <c r="K42" s="243"/>
+      <c r="L42" s="243"/>
+      <c r="M42" s="243"/>
+      <c r="N42" s="243"/>
+      <c r="O42" s="243"/>
+      <c r="P42" s="243"/>
+      <c r="Q42" s="243"/>
+      <c r="R42" s="243"/>
+      <c r="S42" s="243"/>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B43" s="224"/>
-      <c r="C43" s="224"/>
-      <c r="D43" s="224"/>
-      <c r="E43" s="224"/>
-      <c r="F43" s="224"/>
-      <c r="G43" s="224"/>
-      <c r="H43" s="224"/>
-      <c r="I43" s="224"/>
-      <c r="J43" s="224"/>
-      <c r="K43" s="224"/>
-      <c r="L43" s="224"/>
-      <c r="M43" s="224"/>
-      <c r="N43" s="224"/>
-      <c r="O43" s="224"/>
-      <c r="P43" s="224"/>
-      <c r="Q43" s="224"/>
-      <c r="R43" s="224"/>
-      <c r="S43" s="224"/>
+      <c r="B43" s="243"/>
+      <c r="C43" s="243"/>
+      <c r="D43" s="243"/>
+      <c r="E43" s="243"/>
+      <c r="F43" s="243"/>
+      <c r="G43" s="243"/>
+      <c r="H43" s="243"/>
+      <c r="I43" s="243"/>
+      <c r="J43" s="243"/>
+      <c r="K43" s="243"/>
+      <c r="L43" s="243"/>
+      <c r="M43" s="243"/>
+      <c r="N43" s="243"/>
+      <c r="O43" s="243"/>
+      <c r="P43" s="243"/>
+      <c r="Q43" s="243"/>
+      <c r="R43" s="243"/>
+      <c r="S43" s="243"/>
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B44" s="224"/>
-      <c r="C44" s="224"/>
-      <c r="D44" s="224"/>
-      <c r="E44" s="224"/>
-      <c r="F44" s="224"/>
-      <c r="G44" s="224"/>
-      <c r="H44" s="224"/>
-      <c r="I44" s="224"/>
-      <c r="J44" s="224"/>
-      <c r="K44" s="224"/>
-      <c r="L44" s="224"/>
-      <c r="M44" s="224"/>
-      <c r="N44" s="224"/>
-      <c r="O44" s="224"/>
-      <c r="P44" s="224"/>
-      <c r="Q44" s="224"/>
-      <c r="R44" s="224"/>
-      <c r="S44" s="224"/>
+      <c r="B44" s="243"/>
+      <c r="C44" s="243"/>
+      <c r="D44" s="243"/>
+      <c r="E44" s="243"/>
+      <c r="F44" s="243"/>
+      <c r="G44" s="243"/>
+      <c r="H44" s="243"/>
+      <c r="I44" s="243"/>
+      <c r="J44" s="243"/>
+      <c r="K44" s="243"/>
+      <c r="L44" s="243"/>
+      <c r="M44" s="243"/>
+      <c r="N44" s="243"/>
+      <c r="O44" s="243"/>
+      <c r="P44" s="243"/>
+      <c r="Q44" s="243"/>
+      <c r="R44" s="243"/>
+      <c r="S44" s="243"/>
     </row>
     <row r="45" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B45" s="227"/>
-      <c r="C45" s="227"/>
-      <c r="D45" s="227"/>
-      <c r="E45" s="227"/>
-      <c r="F45" s="227"/>
-      <c r="G45" s="227"/>
-      <c r="H45" s="227"/>
-      <c r="I45" s="227"/>
-      <c r="J45" s="227"/>
-      <c r="K45" s="227"/>
-      <c r="L45" s="227"/>
-      <c r="M45" s="227"/>
-      <c r="N45" s="227"/>
-      <c r="O45" s="227"/>
-      <c r="P45" s="227"/>
-      <c r="Q45" s="227"/>
-      <c r="R45" s="227"/>
-      <c r="S45" s="227"/>
+      <c r="B45" s="244"/>
+      <c r="C45" s="244"/>
+      <c r="D45" s="244"/>
+      <c r="E45" s="244"/>
+      <c r="F45" s="244"/>
+      <c r="G45" s="244"/>
+      <c r="H45" s="244"/>
+      <c r="I45" s="244"/>
+      <c r="J45" s="244"/>
+      <c r="K45" s="244"/>
+      <c r="L45" s="244"/>
+      <c r="M45" s="244"/>
+      <c r="N45" s="244"/>
+      <c r="O45" s="244"/>
+      <c r="P45" s="244"/>
+      <c r="Q45" s="244"/>
+      <c r="R45" s="244"/>
+      <c r="S45" s="244"/>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B46" s="42"/>
@@ -10909,33 +10918,33 @@
       <c r="R54" s="126"/>
     </row>
     <row r="55" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B55" s="232" t="s">
+      <c r="B55" s="231" t="s">
         <v>135</v>
       </c>
-      <c r="C55" s="232"/>
-      <c r="D55" s="232"/>
-      <c r="E55" s="232"/>
-      <c r="F55" s="232"/>
-      <c r="G55" s="232"/>
-      <c r="H55" s="232"/>
-      <c r="I55" s="232"/>
-      <c r="J55" s="232"/>
-      <c r="K55" s="232"/>
-      <c r="L55" s="232"/>
-      <c r="M55" s="232"/>
-      <c r="N55" s="232"/>
-      <c r="O55" s="232"/>
-      <c r="P55" s="232"/>
-      <c r="Q55" s="232"/>
+      <c r="C55" s="231"/>
+      <c r="D55" s="231"/>
+      <c r="E55" s="231"/>
+      <c r="F55" s="231"/>
+      <c r="G55" s="231"/>
+      <c r="H55" s="231"/>
+      <c r="I55" s="231"/>
+      <c r="J55" s="231"/>
+      <c r="K55" s="231"/>
+      <c r="L55" s="231"/>
+      <c r="M55" s="231"/>
+      <c r="N55" s="231"/>
+      <c r="O55" s="231"/>
+      <c r="P55" s="231"/>
+      <c r="Q55" s="231"/>
     </row>
     <row r="56" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B56" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C56" s="217" t="s">
+      <c r="C56" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D56" s="217"/>
+      <c r="D56" s="232"/>
       <c r="E56" s="120" t="s">
         <v>3</v>
       </c>
@@ -10975,10 +10984,10 @@
       <c r="Q56" s="121"/>
     </row>
     <row r="57" spans="2:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="294" t="s">
+      <c r="B57" s="235" t="s">
         <v>139</v>
       </c>
-      <c r="C57" s="302" t="s">
+      <c r="C57" s="236" t="s">
         <v>110</v>
       </c>
       <c r="D57" s="141" t="s">
@@ -11020,14 +11029,14 @@
       <c r="O57" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P57" s="288" t="s">
+      <c r="P57" s="241" t="s">
         <v>73</v>
       </c>
       <c r="Q57" s="141"/>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B58" s="294"/>
-      <c r="C58" s="302"/>
+      <c r="B58" s="235"/>
+      <c r="C58" s="236"/>
       <c r="D58" s="141" t="s">
         <v>22</v>
       </c>
@@ -11067,14 +11076,14 @@
       <c r="O58" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P58" s="289"/>
+      <c r="P58" s="242"/>
       <c r="Q58" s="141"/>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B59" s="294" t="s">
+      <c r="B59" s="235" t="s">
         <v>140</v>
       </c>
-      <c r="C59" s="302" t="s">
+      <c r="C59" s="236" t="s">
         <v>110</v>
       </c>
       <c r="D59" s="141" t="s">
@@ -11116,12 +11125,12 @@
       <c r="O59" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P59" s="289"/>
+      <c r="P59" s="242"/>
       <c r="Q59" s="141"/>
     </row>
     <row r="60" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="294"/>
-      <c r="C60" s="302"/>
+      <c r="B60" s="235"/>
+      <c r="C60" s="236"/>
       <c r="D60" s="141" t="s">
         <v>22</v>
       </c>
@@ -11161,14 +11170,14 @@
       <c r="O60" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P60" s="290"/>
+      <c r="P60" s="249"/>
       <c r="Q60" s="141"/>
     </row>
     <row r="61" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="294" t="s">
+      <c r="B61" s="235" t="s">
         <v>141</v>
       </c>
-      <c r="C61" s="302" t="s">
+      <c r="C61" s="236" t="s">
         <v>110</v>
       </c>
       <c r="D61" s="141" t="s">
@@ -11210,14 +11219,14 @@
       <c r="O61" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P61" s="291" t="s">
+      <c r="P61" s="250" t="s">
         <v>59</v>
       </c>
       <c r="Q61" s="141"/>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B62" s="294"/>
-      <c r="C62" s="302"/>
+      <c r="B62" s="235"/>
+      <c r="C62" s="236"/>
       <c r="D62" s="141" t="s">
         <v>22</v>
       </c>
@@ -11257,14 +11266,14 @@
       <c r="O62" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P62" s="292"/>
+      <c r="P62" s="251"/>
       <c r="Q62" s="141"/>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B63" s="294" t="s">
+      <c r="B63" s="235" t="s">
         <v>143</v>
       </c>
-      <c r="C63" s="302" t="s">
+      <c r="C63" s="236" t="s">
         <v>110</v>
       </c>
       <c r="D63" s="141" t="s">
@@ -11306,12 +11315,12 @@
       <c r="O63" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P63" s="292"/>
+      <c r="P63" s="251"/>
       <c r="Q63" s="141"/>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B64" s="294"/>
-      <c r="C64" s="302"/>
+      <c r="B64" s="235"/>
+      <c r="C64" s="236"/>
       <c r="D64" s="141" t="s">
         <v>22</v>
       </c>
@@ -11351,37 +11360,37 @@
       <c r="O64" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P64" s="293"/>
+      <c r="P64" s="252"/>
       <c r="Q64" s="141"/>
     </row>
     <row r="65" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="212" t="s">
+      <c r="B65" s="237" t="s">
         <v>144</v>
       </c>
-      <c r="C65" s="212"/>
-      <c r="D65" s="215"/>
-      <c r="E65" s="215"/>
-      <c r="F65" s="212"/>
-      <c r="G65" s="215"/>
-      <c r="H65" s="215"/>
-      <c r="I65" s="212"/>
-      <c r="J65" s="215"/>
-      <c r="K65" s="215"/>
-      <c r="L65" s="215"/>
-      <c r="M65" s="212"/>
-      <c r="N65" s="215"/>
-      <c r="O65" s="215"/>
-      <c r="P65" s="215"/>
-      <c r="Q65" s="215"/>
+      <c r="C65" s="237"/>
+      <c r="D65" s="238"/>
+      <c r="E65" s="238"/>
+      <c r="F65" s="237"/>
+      <c r="G65" s="238"/>
+      <c r="H65" s="238"/>
+      <c r="I65" s="237"/>
+      <c r="J65" s="238"/>
+      <c r="K65" s="238"/>
+      <c r="L65" s="238"/>
+      <c r="M65" s="237"/>
+      <c r="N65" s="238"/>
+      <c r="O65" s="238"/>
+      <c r="P65" s="238"/>
+      <c r="Q65" s="238"/>
     </row>
     <row r="66" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B66" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C66" s="217" t="s">
+      <c r="C66" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D66" s="217"/>
+      <c r="D66" s="232"/>
       <c r="E66" s="8" t="s">
         <v>3</v>
       </c>
@@ -11421,7 +11430,7 @@
       <c r="Q66" s="103"/>
     </row>
     <row r="67" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B67" s="275" t="s">
+      <c r="B67" s="239" t="s">
         <v>145</v>
       </c>
       <c r="C67" s="202" t="s">
@@ -11466,7 +11475,7 @@
       <c r="O67" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P67" s="288" t="s">
+      <c r="P67" s="241" t="s">
         <v>73</v>
       </c>
       <c r="Q67" s="147"/>
@@ -42920,7 +42929,7 @@
       </c>
     </row>
     <row r="68" spans="2:62 3072:12198 12789:15082" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="304"/>
+      <c r="B68" s="240"/>
       <c r="C68" s="202" t="s">
         <v>110</v>
       </c>
@@ -42963,7 +42972,7 @@
       <c r="O68" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P68" s="289"/>
+      <c r="P68" s="242"/>
       <c r="Q68" s="147"/>
       <c r="R68" s="170"/>
       <c r="S68" s="163"/>
@@ -54433,33 +54442,33 @@
       <c r="VHB68" s="156"/>
     </row>
     <row r="69" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B69" s="232" t="s">
+      <c r="B69" s="231" t="s">
         <v>146</v>
       </c>
-      <c r="C69" s="232"/>
-      <c r="D69" s="232"/>
-      <c r="E69" s="232"/>
-      <c r="F69" s="232"/>
-      <c r="G69" s="232"/>
-      <c r="H69" s="232"/>
-      <c r="I69" s="232"/>
-      <c r="J69" s="232"/>
-      <c r="K69" s="232"/>
-      <c r="L69" s="232"/>
-      <c r="M69" s="232"/>
-      <c r="N69" s="232"/>
-      <c r="O69" s="232"/>
-      <c r="P69" s="232"/>
-      <c r="Q69" s="232"/>
+      <c r="C69" s="231"/>
+      <c r="D69" s="231"/>
+      <c r="E69" s="231"/>
+      <c r="F69" s="231"/>
+      <c r="G69" s="231"/>
+      <c r="H69" s="231"/>
+      <c r="I69" s="231"/>
+      <c r="J69" s="231"/>
+      <c r="K69" s="231"/>
+      <c r="L69" s="231"/>
+      <c r="M69" s="231"/>
+      <c r="N69" s="231"/>
+      <c r="O69" s="231"/>
+      <c r="P69" s="231"/>
+      <c r="Q69" s="231"/>
     </row>
     <row r="70" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B70" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C70" s="217" t="s">
+      <c r="C70" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D70" s="217"/>
+      <c r="D70" s="232"/>
       <c r="E70" s="8" t="s">
         <v>3</v>
       </c>
@@ -54499,7 +54508,7 @@
       <c r="Q70" s="103"/>
     </row>
     <row r="71" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B71" s="275" t="s">
+      <c r="B71" s="239" t="s">
         <v>147</v>
       </c>
       <c r="C71" s="202" t="s">
@@ -54544,13 +54553,13 @@
       <c r="O71" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P71" s="288" t="s">
+      <c r="P71" s="241" t="s">
         <v>73</v>
       </c>
       <c r="Q71" s="147"/>
     </row>
     <row r="72" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B72" s="304"/>
+      <c r="B72" s="240"/>
       <c r="C72" s="202" t="s">
         <v>110</v>
       </c>
@@ -54593,7 +54602,7 @@
       <c r="O72" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P72" s="289"/>
+      <c r="P72" s="242"/>
       <c r="Q72" s="147"/>
     </row>
     <row r="74" spans="2:62 3072:12198 12789:15082" ht="15.6" x14ac:dyDescent="0.3">
@@ -54620,121 +54629,121 @@
       <c r="T74" s="6"/>
     </row>
     <row r="75" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B75" s="250" t="s">
+      <c r="B75" s="230" t="s">
         <v>33</v>
       </c>
-      <c r="C75" s="250"/>
-      <c r="D75" s="250"/>
-      <c r="E75" s="250"/>
-      <c r="F75" s="250"/>
-      <c r="G75" s="250"/>
-      <c r="H75" s="250"/>
-      <c r="I75" s="250"/>
-      <c r="J75" s="250"/>
-      <c r="K75" s="250"/>
-      <c r="L75" s="250"/>
-      <c r="M75" s="250"/>
-      <c r="N75" s="250"/>
-      <c r="O75" s="250"/>
-      <c r="P75" s="250"/>
-      <c r="Q75" s="250"/>
-      <c r="R75" s="250"/>
-      <c r="S75" s="250"/>
-      <c r="T75" s="250"/>
+      <c r="C75" s="230"/>
+      <c r="D75" s="230"/>
+      <c r="E75" s="230"/>
+      <c r="F75" s="230"/>
+      <c r="G75" s="230"/>
+      <c r="H75" s="230"/>
+      <c r="I75" s="230"/>
+      <c r="J75" s="230"/>
+      <c r="K75" s="230"/>
+      <c r="L75" s="230"/>
+      <c r="M75" s="230"/>
+      <c r="N75" s="230"/>
+      <c r="O75" s="230"/>
+      <c r="P75" s="230"/>
+      <c r="Q75" s="230"/>
+      <c r="R75" s="230"/>
+      <c r="S75" s="230"/>
+      <c r="T75" s="230"/>
     </row>
     <row r="76" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B76" s="250"/>
-      <c r="C76" s="250"/>
-      <c r="D76" s="250"/>
-      <c r="E76" s="250"/>
-      <c r="F76" s="250"/>
-      <c r="G76" s="250"/>
-      <c r="H76" s="250"/>
-      <c r="I76" s="250"/>
-      <c r="J76" s="250"/>
-      <c r="K76" s="250"/>
-      <c r="L76" s="250"/>
-      <c r="M76" s="250"/>
-      <c r="N76" s="250"/>
-      <c r="O76" s="250"/>
-      <c r="P76" s="250"/>
-      <c r="Q76" s="250"/>
-      <c r="R76" s="250"/>
-      <c r="S76" s="250"/>
-      <c r="T76" s="250"/>
+      <c r="B76" s="230"/>
+      <c r="C76" s="230"/>
+      <c r="D76" s="230"/>
+      <c r="E76" s="230"/>
+      <c r="F76" s="230"/>
+      <c r="G76" s="230"/>
+      <c r="H76" s="230"/>
+      <c r="I76" s="230"/>
+      <c r="J76" s="230"/>
+      <c r="K76" s="230"/>
+      <c r="L76" s="230"/>
+      <c r="M76" s="230"/>
+      <c r="N76" s="230"/>
+      <c r="O76" s="230"/>
+      <c r="P76" s="230"/>
+      <c r="Q76" s="230"/>
+      <c r="R76" s="230"/>
+      <c r="S76" s="230"/>
+      <c r="T76" s="230"/>
     </row>
     <row r="77" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B77" s="250"/>
-      <c r="C77" s="250"/>
-      <c r="D77" s="250"/>
-      <c r="E77" s="250"/>
-      <c r="F77" s="250"/>
-      <c r="G77" s="250"/>
-      <c r="H77" s="250"/>
-      <c r="I77" s="250"/>
-      <c r="J77" s="250"/>
-      <c r="K77" s="250"/>
-      <c r="L77" s="250"/>
-      <c r="M77" s="250"/>
-      <c r="N77" s="250"/>
-      <c r="O77" s="250"/>
-      <c r="P77" s="250"/>
-      <c r="Q77" s="250"/>
-      <c r="R77" s="250"/>
-      <c r="S77" s="250"/>
-      <c r="T77" s="250"/>
+      <c r="B77" s="230"/>
+      <c r="C77" s="230"/>
+      <c r="D77" s="230"/>
+      <c r="E77" s="230"/>
+      <c r="F77" s="230"/>
+      <c r="G77" s="230"/>
+      <c r="H77" s="230"/>
+      <c r="I77" s="230"/>
+      <c r="J77" s="230"/>
+      <c r="K77" s="230"/>
+      <c r="L77" s="230"/>
+      <c r="M77" s="230"/>
+      <c r="N77" s="230"/>
+      <c r="O77" s="230"/>
+      <c r="P77" s="230"/>
+      <c r="Q77" s="230"/>
+      <c r="R77" s="230"/>
+      <c r="S77" s="230"/>
+      <c r="T77" s="230"/>
     </row>
     <row r="78" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B78" s="250"/>
-      <c r="C78" s="250"/>
-      <c r="D78" s="250"/>
-      <c r="E78" s="250"/>
-      <c r="F78" s="250"/>
-      <c r="G78" s="250"/>
-      <c r="H78" s="250"/>
-      <c r="I78" s="250"/>
-      <c r="J78" s="250"/>
-      <c r="K78" s="250"/>
-      <c r="L78" s="250"/>
-      <c r="M78" s="250"/>
-      <c r="N78" s="250"/>
-      <c r="O78" s="250"/>
-      <c r="P78" s="250"/>
-      <c r="Q78" s="250"/>
-      <c r="R78" s="250"/>
-      <c r="S78" s="250"/>
-      <c r="T78" s="250"/>
+      <c r="B78" s="230"/>
+      <c r="C78" s="230"/>
+      <c r="D78" s="230"/>
+      <c r="E78" s="230"/>
+      <c r="F78" s="230"/>
+      <c r="G78" s="230"/>
+      <c r="H78" s="230"/>
+      <c r="I78" s="230"/>
+      <c r="J78" s="230"/>
+      <c r="K78" s="230"/>
+      <c r="L78" s="230"/>
+      <c r="M78" s="230"/>
+      <c r="N78" s="230"/>
+      <c r="O78" s="230"/>
+      <c r="P78" s="230"/>
+      <c r="Q78" s="230"/>
+      <c r="R78" s="230"/>
+      <c r="S78" s="230"/>
+      <c r="T78" s="230"/>
     </row>
     <row r="87" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B87" s="216" t="s">
+      <c r="B87" s="233" t="s">
         <v>149</v>
       </c>
-      <c r="C87" s="216"/>
-      <c r="D87" s="216"/>
-      <c r="E87" s="216"/>
-      <c r="F87" s="216"/>
-      <c r="G87" s="216"/>
-      <c r="H87" s="216"/>
-      <c r="I87" s="216"/>
-      <c r="J87" s="216"/>
-      <c r="K87" s="216"/>
-      <c r="L87" s="216"/>
-      <c r="M87" s="216"/>
-      <c r="N87" s="216"/>
-      <c r="O87" s="216"/>
-      <c r="P87" s="216"/>
-      <c r="Q87" s="216"/>
-      <c r="R87" s="216"/>
-      <c r="S87" s="216"/>
+      <c r="C87" s="233"/>
+      <c r="D87" s="233"/>
+      <c r="E87" s="233"/>
+      <c r="F87" s="233"/>
+      <c r="G87" s="233"/>
+      <c r="H87" s="233"/>
+      <c r="I87" s="233"/>
+      <c r="J87" s="233"/>
+      <c r="K87" s="233"/>
+      <c r="L87" s="233"/>
+      <c r="M87" s="233"/>
+      <c r="N87" s="233"/>
+      <c r="O87" s="233"/>
+      <c r="P87" s="233"/>
+      <c r="Q87" s="233"/>
+      <c r="R87" s="233"/>
+      <c r="S87" s="233"/>
     </row>
     <row r="88" spans="2:20" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C88" s="303" t="s">
+      <c r="C88" s="234" t="s">
         <v>2</v>
       </c>
-      <c r="D88" s="303"/>
+      <c r="D88" s="234"/>
       <c r="E88" s="127" t="s">
         <v>125</v>
       </c>
@@ -54769,17 +54778,17 @@
         <v>14</v>
       </c>
       <c r="P88" s="17"/>
-      <c r="Q88" s="217" t="s">
+      <c r="Q88" s="232" t="s">
         <v>36</v>
       </c>
-      <c r="R88" s="217"/>
-      <c r="S88" s="217"/>
+      <c r="R88" s="232"/>
+      <c r="S88" s="232"/>
     </row>
     <row r="89" spans="2:20" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="218" t="s">
+      <c r="B89" s="227" t="s">
         <v>90</v>
       </c>
-      <c r="C89" s="239" t="s">
+      <c r="C89" s="214" t="s">
         <v>110</v>
       </c>
       <c r="D89" s="53" t="s">
@@ -54821,15 +54830,15 @@
         <v>43</v>
       </c>
       <c r="P89" s="53"/>
-      <c r="Q89" s="246" t="s">
+      <c r="Q89" s="229" t="s">
         <v>44</v>
       </c>
-      <c r="R89" s="246"/>
-      <c r="S89" s="246"/>
+      <c r="R89" s="229"/>
+      <c r="S89" s="229"/>
     </row>
     <row r="90" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B90" s="214"/>
-      <c r="C90" s="239"/>
+      <c r="B90" s="228"/>
+      <c r="C90" s="214"/>
       <c r="D90" s="53" t="s">
         <v>22</v>
       </c>
@@ -54869,9 +54878,9 @@
         <v>43</v>
       </c>
       <c r="P90" s="53"/>
-      <c r="Q90" s="246"/>
-      <c r="R90" s="246"/>
-      <c r="S90" s="246"/>
+      <c r="Q90" s="229"/>
+      <c r="R90" s="229"/>
+      <c r="S90" s="229"/>
     </row>
     <row r="92" spans="2:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B92" s="5" t="s">
@@ -54897,120 +54906,120 @@
       <c r="T92" s="6"/>
     </row>
     <row r="93" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B93" s="250" t="s">
+      <c r="B93" s="230" t="s">
         <v>33</v>
       </c>
-      <c r="C93" s="250"/>
-      <c r="D93" s="250"/>
-      <c r="E93" s="250"/>
-      <c r="F93" s="250"/>
-      <c r="G93" s="250"/>
-      <c r="H93" s="250"/>
-      <c r="I93" s="250"/>
-      <c r="J93" s="250"/>
-      <c r="K93" s="250"/>
-      <c r="L93" s="250"/>
-      <c r="M93" s="250"/>
-      <c r="N93" s="250"/>
-      <c r="O93" s="250"/>
-      <c r="P93" s="250"/>
-      <c r="Q93" s="250"/>
-      <c r="R93" s="250"/>
-      <c r="S93" s="250"/>
-      <c r="T93" s="250"/>
+      <c r="C93" s="230"/>
+      <c r="D93" s="230"/>
+      <c r="E93" s="230"/>
+      <c r="F93" s="230"/>
+      <c r="G93" s="230"/>
+      <c r="H93" s="230"/>
+      <c r="I93" s="230"/>
+      <c r="J93" s="230"/>
+      <c r="K93" s="230"/>
+      <c r="L93" s="230"/>
+      <c r="M93" s="230"/>
+      <c r="N93" s="230"/>
+      <c r="O93" s="230"/>
+      <c r="P93" s="230"/>
+      <c r="Q93" s="230"/>
+      <c r="R93" s="230"/>
+      <c r="S93" s="230"/>
+      <c r="T93" s="230"/>
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B94" s="250"/>
-      <c r="C94" s="250"/>
-      <c r="D94" s="250"/>
-      <c r="E94" s="250"/>
-      <c r="F94" s="250"/>
-      <c r="G94" s="250"/>
-      <c r="H94" s="250"/>
-      <c r="I94" s="250"/>
-      <c r="J94" s="250"/>
-      <c r="K94" s="250"/>
-      <c r="L94" s="250"/>
-      <c r="M94" s="250"/>
-      <c r="N94" s="250"/>
-      <c r="O94" s="250"/>
-      <c r="P94" s="250"/>
-      <c r="Q94" s="250"/>
-      <c r="R94" s="250"/>
-      <c r="S94" s="250"/>
-      <c r="T94" s="250"/>
+      <c r="B94" s="230"/>
+      <c r="C94" s="230"/>
+      <c r="D94" s="230"/>
+      <c r="E94" s="230"/>
+      <c r="F94" s="230"/>
+      <c r="G94" s="230"/>
+      <c r="H94" s="230"/>
+      <c r="I94" s="230"/>
+      <c r="J94" s="230"/>
+      <c r="K94" s="230"/>
+      <c r="L94" s="230"/>
+      <c r="M94" s="230"/>
+      <c r="N94" s="230"/>
+      <c r="O94" s="230"/>
+      <c r="P94" s="230"/>
+      <c r="Q94" s="230"/>
+      <c r="R94" s="230"/>
+      <c r="S94" s="230"/>
+      <c r="T94" s="230"/>
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B95" s="250"/>
-      <c r="C95" s="250"/>
-      <c r="D95" s="250"/>
-      <c r="E95" s="250"/>
-      <c r="F95" s="250"/>
-      <c r="G95" s="250"/>
-      <c r="H95" s="250"/>
-      <c r="I95" s="250"/>
-      <c r="J95" s="250"/>
-      <c r="K95" s="250"/>
-      <c r="L95" s="250"/>
-      <c r="M95" s="250"/>
-      <c r="N95" s="250"/>
-      <c r="O95" s="250"/>
-      <c r="P95" s="250"/>
-      <c r="Q95" s="250"/>
-      <c r="R95" s="250"/>
-      <c r="S95" s="250"/>
-      <c r="T95" s="250"/>
+      <c r="B95" s="230"/>
+      <c r="C95" s="230"/>
+      <c r="D95" s="230"/>
+      <c r="E95" s="230"/>
+      <c r="F95" s="230"/>
+      <c r="G95" s="230"/>
+      <c r="H95" s="230"/>
+      <c r="I95" s="230"/>
+      <c r="J95" s="230"/>
+      <c r="K95" s="230"/>
+      <c r="L95" s="230"/>
+      <c r="M95" s="230"/>
+      <c r="N95" s="230"/>
+      <c r="O95" s="230"/>
+      <c r="P95" s="230"/>
+      <c r="Q95" s="230"/>
+      <c r="R95" s="230"/>
+      <c r="S95" s="230"/>
+      <c r="T95" s="230"/>
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B96" s="250"/>
-      <c r="C96" s="250"/>
-      <c r="D96" s="250"/>
-      <c r="E96" s="250"/>
-      <c r="F96" s="250"/>
-      <c r="G96" s="250"/>
-      <c r="H96" s="250"/>
-      <c r="I96" s="250"/>
-      <c r="J96" s="250"/>
-      <c r="K96" s="250"/>
-      <c r="L96" s="250"/>
-      <c r="M96" s="250"/>
-      <c r="N96" s="250"/>
-      <c r="O96" s="250"/>
-      <c r="P96" s="250"/>
-      <c r="Q96" s="250"/>
-      <c r="R96" s="250"/>
-      <c r="S96" s="250"/>
-      <c r="T96" s="250"/>
+      <c r="B96" s="230"/>
+      <c r="C96" s="230"/>
+      <c r="D96" s="230"/>
+      <c r="E96" s="230"/>
+      <c r="F96" s="230"/>
+      <c r="G96" s="230"/>
+      <c r="H96" s="230"/>
+      <c r="I96" s="230"/>
+      <c r="J96" s="230"/>
+      <c r="K96" s="230"/>
+      <c r="L96" s="230"/>
+      <c r="M96" s="230"/>
+      <c r="N96" s="230"/>
+      <c r="O96" s="230"/>
+      <c r="P96" s="230"/>
+      <c r="Q96" s="230"/>
+      <c r="R96" s="230"/>
+      <c r="S96" s="230"/>
+      <c r="T96" s="230"/>
     </row>
     <row r="106" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="107" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B107" s="232" t="s">
+      <c r="B107" s="231" t="s">
         <v>153</v>
       </c>
-      <c r="C107" s="232"/>
-      <c r="D107" s="232"/>
-      <c r="E107" s="232"/>
-      <c r="F107" s="232"/>
-      <c r="G107" s="232"/>
-      <c r="H107" s="232"/>
-      <c r="I107" s="232"/>
-      <c r="J107" s="232"/>
-      <c r="K107" s="232"/>
-      <c r="L107" s="232"/>
-      <c r="M107" s="232"/>
-      <c r="N107" s="232"/>
-      <c r="O107" s="232"/>
-      <c r="P107" s="232"/>
-      <c r="Q107" s="232"/>
+      <c r="C107" s="231"/>
+      <c r="D107" s="231"/>
+      <c r="E107" s="231"/>
+      <c r="F107" s="231"/>
+      <c r="G107" s="231"/>
+      <c r="H107" s="231"/>
+      <c r="I107" s="231"/>
+      <c r="J107" s="231"/>
+      <c r="K107" s="231"/>
+      <c r="L107" s="231"/>
+      <c r="M107" s="231"/>
+      <c r="N107" s="231"/>
+      <c r="O107" s="231"/>
+      <c r="P107" s="231"/>
+      <c r="Q107" s="231"/>
     </row>
     <row r="108" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B108" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C108" s="217" t="s">
+      <c r="C108" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D108" s="217"/>
+      <c r="D108" s="232"/>
       <c r="E108" s="8" t="s">
         <v>3</v>
       </c>
@@ -55050,10 +55059,10 @@
       <c r="Q108" s="103"/>
     </row>
     <row r="109" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B109" s="305" t="s">
+      <c r="B109" s="213" t="s">
         <v>154</v>
       </c>
-      <c r="C109" s="239" t="s">
+      <c r="C109" s="214" t="s">
         <v>110</v>
       </c>
       <c r="D109" s="53" t="s">
@@ -55100,8 +55109,8 @@
       <c r="Q109" s="104"/>
     </row>
     <row r="110" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B110" s="305"/>
-      <c r="C110" s="239"/>
+      <c r="B110" s="213"/>
+      <c r="C110" s="214"/>
       <c r="D110" s="53" t="s">
         <v>22</v>
       </c>
@@ -55147,33 +55156,33 @@
     </row>
     <row r="119" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="120" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B120" s="232" t="s">
+      <c r="B120" s="231" t="s">
         <v>158</v>
       </c>
-      <c r="C120" s="232"/>
-      <c r="D120" s="232"/>
-      <c r="E120" s="232"/>
-      <c r="F120" s="232"/>
-      <c r="G120" s="232"/>
-      <c r="H120" s="232"/>
-      <c r="I120" s="232"/>
-      <c r="J120" s="232"/>
-      <c r="K120" s="232"/>
-      <c r="L120" s="232"/>
-      <c r="M120" s="232"/>
-      <c r="N120" s="232"/>
-      <c r="O120" s="232"/>
-      <c r="P120" s="232"/>
-      <c r="Q120" s="232"/>
+      <c r="C120" s="231"/>
+      <c r="D120" s="231"/>
+      <c r="E120" s="231"/>
+      <c r="F120" s="231"/>
+      <c r="G120" s="231"/>
+      <c r="H120" s="231"/>
+      <c r="I120" s="231"/>
+      <c r="J120" s="231"/>
+      <c r="K120" s="231"/>
+      <c r="L120" s="231"/>
+      <c r="M120" s="231"/>
+      <c r="N120" s="231"/>
+      <c r="O120" s="231"/>
+      <c r="P120" s="231"/>
+      <c r="Q120" s="231"/>
     </row>
     <row r="121" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B121" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C121" s="217" t="s">
+      <c r="C121" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D121" s="217"/>
+      <c r="D121" s="232"/>
       <c r="E121" s="8" t="s">
         <v>3</v>
       </c>
@@ -55213,10 +55222,10 @@
       <c r="Q121" s="103"/>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B122" s="305" t="s">
+      <c r="B122" s="213" t="s">
         <v>159</v>
       </c>
-      <c r="C122" s="239" t="s">
+      <c r="C122" s="214" t="s">
         <v>110</v>
       </c>
       <c r="D122" s="53" t="s">
@@ -55263,10 +55272,10 @@
       <c r="Q122" s="196"/>
     </row>
     <row r="123" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B123" s="305" t="s">
+      <c r="B123" s="213" t="s">
         <v>159</v>
       </c>
-      <c r="C123" s="239" t="s">
+      <c r="C123" s="214" t="s">
         <v>110</v>
       </c>
       <c r="D123" s="53" t="s">
@@ -55313,10 +55322,10 @@
       <c r="Q123" s="196"/>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B124" s="305" t="s">
+      <c r="B124" s="213" t="s">
         <v>160</v>
       </c>
-      <c r="C124" s="239" t="s">
+      <c r="C124" s="214" t="s">
         <v>110</v>
       </c>
       <c r="D124" s="53" t="s">
@@ -55364,8 +55373,8 @@
       <c r="Q124" s="196"/>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B125" s="305"/>
-      <c r="C125" s="239"/>
+      <c r="B125" s="213"/>
+      <c r="C125" s="214"/>
       <c r="D125" s="53" t="s">
         <v>22</v>
       </c>
@@ -55412,6 +55421,49 @@
     </row>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="P57:P60"/>
+    <mergeCell ref="P61:P64"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="P36:R37"/>
+    <mergeCell ref="B9:Q9"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="B42:S45"/>
+    <mergeCell ref="B55:Q55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="B34:R34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="P35:R35"/>
+    <mergeCell ref="P38:R38"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="Q88:S88"/>
+    <mergeCell ref="B87:S87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="B65:Q65"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="B75:T78"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B69:Q69"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="P67:P68"/>
+    <mergeCell ref="P71:P72"/>
     <mergeCell ref="B124:B125"/>
     <mergeCell ref="C124:C125"/>
     <mergeCell ref="B122:B123"/>
@@ -55428,49 +55480,6 @@
     <mergeCell ref="C108:D108"/>
     <mergeCell ref="B120:Q120"/>
     <mergeCell ref="C121:D121"/>
-    <mergeCell ref="Q88:S88"/>
-    <mergeCell ref="B87:S87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="B65:Q65"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="B75:T78"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="B69:Q69"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="P67:P68"/>
-    <mergeCell ref="P71:P72"/>
-    <mergeCell ref="B9:Q9"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="B42:S45"/>
-    <mergeCell ref="B55:Q55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="B34:R34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="P35:R35"/>
-    <mergeCell ref="P38:R38"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="P57:P60"/>
-    <mergeCell ref="P61:P64"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="P39:R39"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="P36:R37"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55507,8 +55516,8 @@
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B8" s="126"/>
       <c r="C8" s="126"/>
-      <c r="D8" s="319"/>
-      <c r="E8" s="319"/>
+      <c r="D8" s="320"/>
+      <c r="E8" s="320"/>
       <c r="F8" s="126"/>
       <c r="G8" s="126"/>
       <c r="H8" s="126"/>
@@ -55524,32 +55533,32 @@
       <c r="R8" s="126"/>
     </row>
     <row r="9" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="328" t="s">
+      <c r="B9" s="323" t="s">
         <v>161</v>
       </c>
-      <c r="C9" s="328"/>
-      <c r="D9" s="328"/>
-      <c r="E9" s="328"/>
-      <c r="F9" s="328"/>
-      <c r="G9" s="328"/>
-      <c r="H9" s="328"/>
-      <c r="I9" s="328"/>
-      <c r="J9" s="328"/>
-      <c r="K9" s="328"/>
-      <c r="L9" s="328"/>
-      <c r="M9" s="328"/>
-      <c r="N9" s="328"/>
-      <c r="O9" s="328"/>
-      <c r="P9" s="328"/>
+      <c r="C9" s="323"/>
+      <c r="D9" s="323"/>
+      <c r="E9" s="323"/>
+      <c r="F9" s="323"/>
+      <c r="G9" s="323"/>
+      <c r="H9" s="323"/>
+      <c r="I9" s="323"/>
+      <c r="J9" s="323"/>
+      <c r="K9" s="323"/>
+      <c r="L9" s="323"/>
+      <c r="M9" s="323"/>
+      <c r="N9" s="323"/>
+      <c r="O9" s="323"/>
+      <c r="P9" s="323"/>
     </row>
     <row r="10" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="338" t="s">
+      <c r="C10" s="321" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="339"/>
+      <c r="D10" s="322"/>
       <c r="E10" s="12" t="s">
         <v>3</v>
       </c>
@@ -55589,10 +55598,10 @@
       <c r="Q10" s="126"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B11" s="340" t="s">
+      <c r="B11" s="312" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="340" t="s">
+      <c r="C11" s="312" t="s">
         <v>165</v>
       </c>
       <c r="D11" s="41" t="s">
@@ -55640,8 +55649,8 @@
       <c r="Q11" s="126"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="341"/>
-      <c r="C12" s="341"/>
+      <c r="B12" s="313"/>
+      <c r="C12" s="313"/>
       <c r="D12" s="41" t="s">
         <v>22</v>
       </c>
@@ -55687,10 +55696,10 @@
       <c r="Q12" s="126"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="340" t="s">
+      <c r="B13" s="312" t="s">
         <v>167</v>
       </c>
-      <c r="C13" s="340" t="s">
+      <c r="C13" s="312" t="s">
         <v>165</v>
       </c>
       <c r="D13" s="41" t="s">
@@ -55738,8 +55747,8 @@
       <c r="Q13" s="126"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B14" s="341"/>
-      <c r="C14" s="341"/>
+      <c r="B14" s="313"/>
+      <c r="C14" s="313"/>
       <c r="D14" s="41" t="s">
         <v>22</v>
       </c>
@@ -55785,10 +55794,10 @@
       <c r="Q14" s="126"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="340" t="s">
+      <c r="B15" s="312" t="s">
         <v>122</v>
       </c>
-      <c r="C15" s="340" t="s">
+      <c r="C15" s="312" t="s">
         <v>165</v>
       </c>
       <c r="D15" s="41" t="s">
@@ -55836,8 +55845,8 @@
       <c r="Q15" s="126"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B16" s="341"/>
-      <c r="C16" s="341"/>
+      <c r="B16" s="313"/>
+      <c r="C16" s="313"/>
       <c r="D16" s="41" t="s">
         <v>22</v>
       </c>
@@ -55897,93 +55906,93 @@
       <c r="N17" s="34"/>
     </row>
     <row r="18" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="344" t="s">
+      <c r="B18" s="317" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
-      <c r="G18" s="345"/>
-      <c r="H18" s="345"/>
-      <c r="I18" s="345"/>
-      <c r="J18" s="345"/>
-      <c r="K18" s="345"/>
-      <c r="L18" s="345"/>
-      <c r="M18" s="345"/>
-      <c r="N18" s="345"/>
-      <c r="O18" s="345"/>
-      <c r="P18" s="346"/>
+      <c r="C18" s="318"/>
+      <c r="D18" s="318"/>
+      <c r="E18" s="318"/>
+      <c r="F18" s="318"/>
+      <c r="G18" s="318"/>
+      <c r="H18" s="318"/>
+      <c r="I18" s="318"/>
+      <c r="J18" s="318"/>
+      <c r="K18" s="318"/>
+      <c r="L18" s="318"/>
+      <c r="M18" s="318"/>
+      <c r="N18" s="318"/>
+      <c r="O18" s="318"/>
+      <c r="P18" s="319"/>
     </row>
     <row r="19" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="309" t="s">
+      <c r="B19" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="310"/>
-      <c r="D19" s="310"/>
-      <c r="E19" s="310"/>
-      <c r="F19" s="310"/>
-      <c r="G19" s="310"/>
-      <c r="H19" s="310"/>
-      <c r="I19" s="310"/>
-      <c r="J19" s="310"/>
-      <c r="K19" s="310"/>
-      <c r="L19" s="310"/>
-      <c r="M19" s="310"/>
-      <c r="N19" s="310"/>
-      <c r="O19" s="310"/>
-      <c r="P19" s="311"/>
+      <c r="C19" s="219"/>
+      <c r="D19" s="219"/>
+      <c r="E19" s="219"/>
+      <c r="F19" s="219"/>
+      <c r="G19" s="219"/>
+      <c r="H19" s="219"/>
+      <c r="I19" s="219"/>
+      <c r="J19" s="219"/>
+      <c r="K19" s="219"/>
+      <c r="L19" s="219"/>
+      <c r="M19" s="219"/>
+      <c r="N19" s="219"/>
+      <c r="O19" s="219"/>
+      <c r="P19" s="220"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="312"/>
-      <c r="C20" s="282"/>
-      <c r="D20" s="282"/>
-      <c r="E20" s="282"/>
-      <c r="F20" s="282"/>
-      <c r="G20" s="282"/>
-      <c r="H20" s="282"/>
-      <c r="I20" s="282"/>
-      <c r="J20" s="282"/>
-      <c r="K20" s="282"/>
-      <c r="L20" s="282"/>
-      <c r="M20" s="282"/>
-      <c r="N20" s="282"/>
-      <c r="O20" s="282"/>
-      <c r="P20" s="313"/>
+      <c r="B20" s="221"/>
+      <c r="C20" s="222"/>
+      <c r="D20" s="222"/>
+      <c r="E20" s="222"/>
+      <c r="F20" s="222"/>
+      <c r="G20" s="222"/>
+      <c r="H20" s="222"/>
+      <c r="I20" s="222"/>
+      <c r="J20" s="222"/>
+      <c r="K20" s="222"/>
+      <c r="L20" s="222"/>
+      <c r="M20" s="222"/>
+      <c r="N20" s="222"/>
+      <c r="O20" s="222"/>
+      <c r="P20" s="223"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="312"/>
-      <c r="C21" s="282"/>
-      <c r="D21" s="282"/>
-      <c r="E21" s="282"/>
-      <c r="F21" s="282"/>
-      <c r="G21" s="282"/>
-      <c r="H21" s="282"/>
-      <c r="I21" s="282"/>
-      <c r="J21" s="282"/>
-      <c r="K21" s="282"/>
-      <c r="L21" s="282"/>
-      <c r="M21" s="282"/>
-      <c r="N21" s="282"/>
-      <c r="O21" s="282"/>
-      <c r="P21" s="313"/>
+      <c r="B21" s="221"/>
+      <c r="C21" s="222"/>
+      <c r="D21" s="222"/>
+      <c r="E21" s="222"/>
+      <c r="F21" s="222"/>
+      <c r="G21" s="222"/>
+      <c r="H21" s="222"/>
+      <c r="I21" s="222"/>
+      <c r="J21" s="222"/>
+      <c r="K21" s="222"/>
+      <c r="L21" s="222"/>
+      <c r="M21" s="222"/>
+      <c r="N21" s="222"/>
+      <c r="O21" s="222"/>
+      <c r="P21" s="223"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="314"/>
-      <c r="C22" s="315"/>
-      <c r="D22" s="315"/>
-      <c r="E22" s="315"/>
-      <c r="F22" s="315"/>
-      <c r="G22" s="315"/>
-      <c r="H22" s="315"/>
-      <c r="I22" s="315"/>
-      <c r="J22" s="315"/>
-      <c r="K22" s="315"/>
-      <c r="L22" s="315"/>
-      <c r="M22" s="315"/>
-      <c r="N22" s="315"/>
-      <c r="O22" s="315"/>
-      <c r="P22" s="316"/>
+      <c r="B22" s="224"/>
+      <c r="C22" s="225"/>
+      <c r="D22" s="225"/>
+      <c r="E22" s="225"/>
+      <c r="F22" s="225"/>
+      <c r="G22" s="225"/>
+      <c r="H22" s="225"/>
+      <c r="I22" s="225"/>
+      <c r="J22" s="225"/>
+      <c r="K22" s="225"/>
+      <c r="L22" s="225"/>
+      <c r="M22" s="225"/>
+      <c r="N22" s="225"/>
+      <c r="O22" s="225"/>
+      <c r="P22" s="226"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="27"/>
@@ -56113,33 +56122,33 @@
       <c r="N31" s="34"/>
     </row>
     <row r="32" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="342" t="s">
+      <c r="B32" s="314" t="s">
         <v>169</v>
       </c>
-      <c r="C32" s="322"/>
-      <c r="D32" s="322"/>
-      <c r="E32" s="322"/>
-      <c r="F32" s="322"/>
-      <c r="G32" s="322"/>
-      <c r="H32" s="322"/>
-      <c r="I32" s="322"/>
-      <c r="J32" s="322"/>
-      <c r="K32" s="322"/>
-      <c r="L32" s="322"/>
-      <c r="M32" s="322"/>
-      <c r="N32" s="322"/>
-      <c r="O32" s="322"/>
-      <c r="P32" s="322"/>
-      <c r="Q32" s="343"/>
+      <c r="C32" s="315"/>
+      <c r="D32" s="315"/>
+      <c r="E32" s="315"/>
+      <c r="F32" s="315"/>
+      <c r="G32" s="315"/>
+      <c r="H32" s="315"/>
+      <c r="I32" s="315"/>
+      <c r="J32" s="315"/>
+      <c r="K32" s="315"/>
+      <c r="L32" s="315"/>
+      <c r="M32" s="315"/>
+      <c r="N32" s="315"/>
+      <c r="O32" s="315"/>
+      <c r="P32" s="315"/>
+      <c r="Q32" s="316"/>
     </row>
     <row r="33" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B33" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="332" t="s">
+      <c r="C33" s="324" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="332"/>
+      <c r="D33" s="324"/>
       <c r="E33" s="127" t="s">
         <v>125</v>
       </c>
@@ -56173,16 +56182,16 @@
       <c r="O33" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="P33" s="271" t="s">
+      <c r="P33" s="276" t="s">
         <v>36</v>
       </c>
-      <c r="Q33" s="272"/>
+      <c r="Q33" s="277"/>
     </row>
     <row r="34" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="336" t="s">
+      <c r="B34" s="329" t="s">
         <v>173</v>
       </c>
-      <c r="C34" s="337" t="s">
+      <c r="C34" s="330" t="s">
         <v>165</v>
       </c>
       <c r="D34" s="40" t="s">
@@ -56223,14 +56232,14 @@
       <c r="O34" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P34" s="242" t="s">
+      <c r="P34" s="255" t="s">
         <v>174</v>
       </c>
-      <c r="Q34" s="243"/>
+      <c r="Q34" s="257"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B35" s="336"/>
-      <c r="C35" s="337"/>
+      <c r="B35" s="329"/>
+      <c r="C35" s="330"/>
       <c r="D35" s="40" t="s">
         <v>22</v>
       </c>
@@ -56269,8 +56278,8 @@
       <c r="O35" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P35" s="299"/>
-      <c r="Q35" s="301"/>
+      <c r="P35" s="258"/>
+      <c r="Q35" s="260"/>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B36" s="119" t="s">
@@ -56317,8 +56326,8 @@
       <c r="O36" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P36" s="244"/>
-      <c r="Q36" s="245"/>
+      <c r="P36" s="299"/>
+      <c r="Q36" s="300"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B37" s="72"/>
@@ -56371,74 +56380,74 @@
       <c r="P39" s="7"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B40" s="224" t="s">
+      <c r="B40" s="243" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="225"/>
-      <c r="D40" s="225"/>
-      <c r="E40" s="225"/>
-      <c r="F40" s="225"/>
-      <c r="G40" s="225"/>
-      <c r="H40" s="225"/>
-      <c r="I40" s="225"/>
-      <c r="J40" s="225"/>
-      <c r="K40" s="225"/>
-      <c r="L40" s="225"/>
-      <c r="M40" s="225"/>
-      <c r="N40" s="225"/>
-      <c r="O40" s="225"/>
-      <c r="P40" s="226"/>
+      <c r="C40" s="263"/>
+      <c r="D40" s="263"/>
+      <c r="E40" s="263"/>
+      <c r="F40" s="263"/>
+      <c r="G40" s="263"/>
+      <c r="H40" s="263"/>
+      <c r="I40" s="263"/>
+      <c r="J40" s="263"/>
+      <c r="K40" s="263"/>
+      <c r="L40" s="263"/>
+      <c r="M40" s="263"/>
+      <c r="N40" s="263"/>
+      <c r="O40" s="263"/>
+      <c r="P40" s="264"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B41" s="224"/>
-      <c r="C41" s="225"/>
-      <c r="D41" s="225"/>
-      <c r="E41" s="225"/>
-      <c r="F41" s="225"/>
-      <c r="G41" s="225"/>
-      <c r="H41" s="225"/>
-      <c r="I41" s="225"/>
-      <c r="J41" s="225"/>
-      <c r="K41" s="225"/>
-      <c r="L41" s="225"/>
-      <c r="M41" s="225"/>
-      <c r="N41" s="225"/>
-      <c r="O41" s="225"/>
-      <c r="P41" s="226"/>
+      <c r="B41" s="243"/>
+      <c r="C41" s="263"/>
+      <c r="D41" s="263"/>
+      <c r="E41" s="263"/>
+      <c r="F41" s="263"/>
+      <c r="G41" s="263"/>
+      <c r="H41" s="263"/>
+      <c r="I41" s="263"/>
+      <c r="J41" s="263"/>
+      <c r="K41" s="263"/>
+      <c r="L41" s="263"/>
+      <c r="M41" s="263"/>
+      <c r="N41" s="263"/>
+      <c r="O41" s="263"/>
+      <c r="P41" s="264"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B42" s="224"/>
-      <c r="C42" s="225"/>
-      <c r="D42" s="225"/>
-      <c r="E42" s="225"/>
-      <c r="F42" s="225"/>
-      <c r="G42" s="225"/>
-      <c r="H42" s="225"/>
-      <c r="I42" s="225"/>
-      <c r="J42" s="225"/>
-      <c r="K42" s="225"/>
-      <c r="L42" s="225"/>
-      <c r="M42" s="225"/>
-      <c r="N42" s="225"/>
-      <c r="O42" s="225"/>
-      <c r="P42" s="226"/>
+      <c r="B42" s="243"/>
+      <c r="C42" s="263"/>
+      <c r="D42" s="263"/>
+      <c r="E42" s="263"/>
+      <c r="F42" s="263"/>
+      <c r="G42" s="263"/>
+      <c r="H42" s="263"/>
+      <c r="I42" s="263"/>
+      <c r="J42" s="263"/>
+      <c r="K42" s="263"/>
+      <c r="L42" s="263"/>
+      <c r="M42" s="263"/>
+      <c r="N42" s="263"/>
+      <c r="O42" s="263"/>
+      <c r="P42" s="264"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B43" s="227"/>
-      <c r="C43" s="228"/>
-      <c r="D43" s="228"/>
-      <c r="E43" s="228"/>
-      <c r="F43" s="228"/>
-      <c r="G43" s="228"/>
-      <c r="H43" s="228"/>
-      <c r="I43" s="228"/>
-      <c r="J43" s="228"/>
-      <c r="K43" s="228"/>
-      <c r="L43" s="228"/>
-      <c r="M43" s="228"/>
-      <c r="N43" s="228"/>
-      <c r="O43" s="228"/>
-      <c r="P43" s="229"/>
+      <c r="B43" s="244"/>
+      <c r="C43" s="265"/>
+      <c r="D43" s="265"/>
+      <c r="E43" s="265"/>
+      <c r="F43" s="265"/>
+      <c r="G43" s="265"/>
+      <c r="H43" s="265"/>
+      <c r="I43" s="265"/>
+      <c r="J43" s="265"/>
+      <c r="K43" s="265"/>
+      <c r="L43" s="265"/>
+      <c r="M43" s="265"/>
+      <c r="N43" s="265"/>
+      <c r="O43" s="265"/>
+      <c r="P43" s="266"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B44" s="42"/>
@@ -56553,33 +56562,33 @@
       <c r="O51" s="126"/>
     </row>
     <row r="52" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="333" t="s">
+      <c r="B52" s="326" t="s">
         <v>178</v>
       </c>
-      <c r="C52" s="334"/>
-      <c r="D52" s="334"/>
-      <c r="E52" s="334"/>
-      <c r="F52" s="334"/>
-      <c r="G52" s="334"/>
-      <c r="H52" s="334"/>
-      <c r="I52" s="334"/>
-      <c r="J52" s="334"/>
-      <c r="K52" s="334"/>
-      <c r="L52" s="334"/>
-      <c r="M52" s="334"/>
-      <c r="N52" s="334"/>
-      <c r="O52" s="334"/>
-      <c r="P52" s="334"/>
-      <c r="Q52" s="335"/>
+      <c r="C52" s="327"/>
+      <c r="D52" s="327"/>
+      <c r="E52" s="327"/>
+      <c r="F52" s="327"/>
+      <c r="G52" s="327"/>
+      <c r="H52" s="327"/>
+      <c r="I52" s="327"/>
+      <c r="J52" s="327"/>
+      <c r="K52" s="327"/>
+      <c r="L52" s="327"/>
+      <c r="M52" s="327"/>
+      <c r="N52" s="327"/>
+      <c r="O52" s="327"/>
+      <c r="P52" s="327"/>
+      <c r="Q52" s="328"/>
     </row>
     <row r="53" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B53" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C53" s="217" t="s">
+      <c r="C53" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D53" s="217"/>
+      <c r="D53" s="232"/>
       <c r="E53" s="120" t="s">
         <v>3</v>
       </c>
@@ -56621,10 +56630,10 @@
       </c>
     </row>
     <row r="54" spans="2:17" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="234" t="s">
+      <c r="B54" s="262" t="s">
         <v>179</v>
       </c>
-      <c r="C54" s="317" t="s">
+      <c r="C54" s="325" t="s">
         <v>165</v>
       </c>
       <c r="D54" s="53" t="s">
@@ -56674,8 +56683,8 @@
       </c>
     </row>
     <row r="55" spans="2:17" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="234"/>
-      <c r="C55" s="317"/>
+      <c r="B55" s="262"/>
+      <c r="C55" s="325"/>
       <c r="D55" s="53" t="s">
         <v>22</v>
       </c>
@@ -56723,33 +56732,33 @@
       </c>
     </row>
     <row r="56" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="333" t="s">
+      <c r="B56" s="326" t="s">
         <v>181</v>
       </c>
-      <c r="C56" s="334"/>
-      <c r="D56" s="334"/>
-      <c r="E56" s="334"/>
-      <c r="F56" s="334"/>
-      <c r="G56" s="334"/>
-      <c r="H56" s="334"/>
-      <c r="I56" s="334"/>
-      <c r="J56" s="334"/>
-      <c r="K56" s="334"/>
-      <c r="L56" s="334"/>
-      <c r="M56" s="334"/>
-      <c r="N56" s="334"/>
-      <c r="O56" s="334"/>
-      <c r="P56" s="334"/>
-      <c r="Q56" s="335"/>
+      <c r="C56" s="327"/>
+      <c r="D56" s="327"/>
+      <c r="E56" s="327"/>
+      <c r="F56" s="327"/>
+      <c r="G56" s="327"/>
+      <c r="H56" s="327"/>
+      <c r="I56" s="327"/>
+      <c r="J56" s="327"/>
+      <c r="K56" s="327"/>
+      <c r="L56" s="327"/>
+      <c r="M56" s="327"/>
+      <c r="N56" s="327"/>
+      <c r="O56" s="327"/>
+      <c r="P56" s="327"/>
+      <c r="Q56" s="328"/>
     </row>
     <row r="57" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="217" t="s">
+      <c r="C57" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="217"/>
+      <c r="D57" s="232"/>
       <c r="E57" s="120" t="s">
         <v>3</v>
       </c>
@@ -56791,10 +56800,10 @@
       </c>
     </row>
     <row r="58" spans="2:17" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="234" t="s">
+      <c r="B58" s="262" t="s">
         <v>71</v>
       </c>
-      <c r="C58" s="317" t="s">
+      <c r="C58" s="325" t="s">
         <v>165</v>
       </c>
       <c r="D58" s="53" t="s">
@@ -56839,13 +56848,13 @@
       <c r="P58" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q58" s="324" t="s">
+      <c r="Q58" s="334" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="59" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B59" s="234"/>
-      <c r="C59" s="317"/>
+      <c r="B59" s="262"/>
+      <c r="C59" s="325"/>
       <c r="D59" s="53" t="s">
         <v>22</v>
       </c>
@@ -56888,36 +56897,36 @@
       <c r="P59" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q59" s="325"/>
+      <c r="Q59" s="335"/>
     </row>
     <row r="60" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="321" t="s">
+      <c r="B60" s="331" t="s">
         <v>183</v>
       </c>
-      <c r="C60" s="322"/>
-      <c r="D60" s="322"/>
-      <c r="E60" s="322"/>
-      <c r="F60" s="322"/>
-      <c r="G60" s="322"/>
-      <c r="H60" s="322"/>
-      <c r="I60" s="322"/>
-      <c r="J60" s="322"/>
-      <c r="K60" s="322"/>
-      <c r="L60" s="322"/>
-      <c r="M60" s="322"/>
-      <c r="N60" s="322"/>
-      <c r="O60" s="322"/>
-      <c r="P60" s="322"/>
-      <c r="Q60" s="323"/>
+      <c r="C60" s="315"/>
+      <c r="D60" s="315"/>
+      <c r="E60" s="315"/>
+      <c r="F60" s="315"/>
+      <c r="G60" s="315"/>
+      <c r="H60" s="315"/>
+      <c r="I60" s="315"/>
+      <c r="J60" s="315"/>
+      <c r="K60" s="315"/>
+      <c r="L60" s="315"/>
+      <c r="M60" s="315"/>
+      <c r="N60" s="315"/>
+      <c r="O60" s="315"/>
+      <c r="P60" s="315"/>
+      <c r="Q60" s="332"/>
     </row>
     <row r="61" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B61" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C61" s="303" t="s">
+      <c r="C61" s="234" t="s">
         <v>2</v>
       </c>
-      <c r="D61" s="303"/>
+      <c r="D61" s="234"/>
       <c r="E61" s="8" t="s">
         <v>3</v>
       </c>
@@ -56959,10 +56968,10 @@
       </c>
     </row>
     <row r="62" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="329" t="s">
+      <c r="B62" s="333" t="s">
         <v>184</v>
       </c>
-      <c r="C62" s="317" t="s">
+      <c r="C62" s="325" t="s">
         <v>165</v>
       </c>
       <c r="D62" s="53" t="s">
@@ -57007,13 +57016,13 @@
       <c r="P62" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q62" s="324" t="s">
+      <c r="Q62" s="334" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="63" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B63" s="329"/>
-      <c r="C63" s="317"/>
+      <c r="B63" s="333"/>
+      <c r="C63" s="325"/>
       <c r="D63" s="53" t="s">
         <v>22</v>
       </c>
@@ -57056,36 +57065,36 @@
       <c r="P63" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q63" s="325"/>
+      <c r="Q63" s="335"/>
     </row>
     <row r="64" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="321" t="s">
+      <c r="B64" s="331" t="s">
         <v>185</v>
       </c>
-      <c r="C64" s="322"/>
-      <c r="D64" s="322"/>
-      <c r="E64" s="322"/>
-      <c r="F64" s="322"/>
-      <c r="G64" s="322"/>
-      <c r="H64" s="322"/>
-      <c r="I64" s="322"/>
-      <c r="J64" s="322"/>
-      <c r="K64" s="322"/>
-      <c r="L64" s="322"/>
-      <c r="M64" s="322"/>
-      <c r="N64" s="322"/>
-      <c r="O64" s="322"/>
-      <c r="P64" s="322"/>
-      <c r="Q64" s="323"/>
+      <c r="C64" s="315"/>
+      <c r="D64" s="315"/>
+      <c r="E64" s="315"/>
+      <c r="F64" s="315"/>
+      <c r="G64" s="315"/>
+      <c r="H64" s="315"/>
+      <c r="I64" s="315"/>
+      <c r="J64" s="315"/>
+      <c r="K64" s="315"/>
+      <c r="L64" s="315"/>
+      <c r="M64" s="315"/>
+      <c r="N64" s="315"/>
+      <c r="O64" s="315"/>
+      <c r="P64" s="315"/>
+      <c r="Q64" s="332"/>
     </row>
     <row r="65" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B65" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="303" t="s">
+      <c r="C65" s="234" t="s">
         <v>2</v>
       </c>
-      <c r="D65" s="303"/>
+      <c r="D65" s="234"/>
       <c r="E65" s="8" t="s">
         <v>3</v>
       </c>
@@ -57127,10 +57136,10 @@
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B66" s="329" t="s">
+      <c r="B66" s="333" t="s">
         <v>186</v>
       </c>
-      <c r="C66" s="317" t="s">
+      <c r="C66" s="325" t="s">
         <v>165</v>
       </c>
       <c r="D66" s="53" t="s">
@@ -57175,13 +57184,13 @@
       <c r="P66" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q66" s="326" t="s">
+      <c r="Q66" s="336" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B67" s="329"/>
-      <c r="C67" s="317"/>
+      <c r="B67" s="333"/>
+      <c r="C67" s="325"/>
       <c r="D67" s="53" t="s">
         <v>22</v>
       </c>
@@ -57224,36 +57233,36 @@
       <c r="P67" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q67" s="330"/>
+      <c r="Q67" s="337"/>
     </row>
     <row r="68" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="321" t="s">
+      <c r="B68" s="331" t="s">
         <v>188</v>
       </c>
-      <c r="C68" s="322"/>
-      <c r="D68" s="322"/>
-      <c r="E68" s="322"/>
-      <c r="F68" s="322"/>
-      <c r="G68" s="322"/>
-      <c r="H68" s="322"/>
-      <c r="I68" s="322"/>
-      <c r="J68" s="322"/>
-      <c r="K68" s="322"/>
-      <c r="L68" s="322"/>
-      <c r="M68" s="322"/>
-      <c r="N68" s="322"/>
-      <c r="O68" s="322"/>
-      <c r="P68" s="322"/>
-      <c r="Q68" s="323"/>
+      <c r="C68" s="315"/>
+      <c r="D68" s="315"/>
+      <c r="E68" s="315"/>
+      <c r="F68" s="315"/>
+      <c r="G68" s="315"/>
+      <c r="H68" s="315"/>
+      <c r="I68" s="315"/>
+      <c r="J68" s="315"/>
+      <c r="K68" s="315"/>
+      <c r="L68" s="315"/>
+      <c r="M68" s="315"/>
+      <c r="N68" s="315"/>
+      <c r="O68" s="315"/>
+      <c r="P68" s="315"/>
+      <c r="Q68" s="332"/>
     </row>
     <row r="69" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B69" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C69" s="303" t="s">
+      <c r="C69" s="234" t="s">
         <v>2</v>
       </c>
-      <c r="D69" s="303"/>
+      <c r="D69" s="234"/>
       <c r="E69" s="8" t="s">
         <v>3</v>
       </c>
@@ -57295,10 +57304,10 @@
       </c>
     </row>
     <row r="70" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="234" t="s">
+      <c r="B70" s="262" t="s">
         <v>189</v>
       </c>
-      <c r="C70" s="317" t="s">
+      <c r="C70" s="325" t="s">
         <v>165</v>
       </c>
       <c r="D70" s="53" t="s">
@@ -57343,13 +57352,13 @@
       <c r="P70" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="Q70" s="326" t="s">
+      <c r="Q70" s="336" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B71" s="234"/>
-      <c r="C71" s="317"/>
+      <c r="B71" s="262"/>
+      <c r="C71" s="325"/>
       <c r="D71" s="53" t="s">
         <v>22</v>
       </c>
@@ -57392,36 +57401,36 @@
       <c r="P71" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="Q71" s="331"/>
+      <c r="Q71" s="338"/>
     </row>
     <row r="72" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="321" t="s">
+      <c r="B72" s="331" t="s">
         <v>190</v>
       </c>
-      <c r="C72" s="322"/>
-      <c r="D72" s="322"/>
-      <c r="E72" s="322"/>
-      <c r="F72" s="322"/>
-      <c r="G72" s="322"/>
-      <c r="H72" s="322"/>
-      <c r="I72" s="322"/>
-      <c r="J72" s="322"/>
-      <c r="K72" s="322"/>
-      <c r="L72" s="322"/>
-      <c r="M72" s="322"/>
-      <c r="N72" s="328"/>
-      <c r="O72" s="322"/>
-      <c r="P72" s="322"/>
-      <c r="Q72" s="323"/>
+      <c r="C72" s="315"/>
+      <c r="D72" s="315"/>
+      <c r="E72" s="315"/>
+      <c r="F72" s="315"/>
+      <c r="G72" s="315"/>
+      <c r="H72" s="315"/>
+      <c r="I72" s="315"/>
+      <c r="J72" s="315"/>
+      <c r="K72" s="315"/>
+      <c r="L72" s="315"/>
+      <c r="M72" s="315"/>
+      <c r="N72" s="323"/>
+      <c r="O72" s="315"/>
+      <c r="P72" s="315"/>
+      <c r="Q72" s="332"/>
     </row>
     <row r="73" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B73" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C73" s="303" t="s">
+      <c r="C73" s="234" t="s">
         <v>2</v>
       </c>
-      <c r="D73" s="303"/>
+      <c r="D73" s="234"/>
       <c r="E73" s="8" t="s">
         <v>3</v>
       </c>
@@ -57463,10 +57472,10 @@
       </c>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B74" s="234" t="s">
+      <c r="B74" s="262" t="s">
         <v>191</v>
       </c>
-      <c r="C74" s="317" t="s">
+      <c r="C74" s="325" t="s">
         <v>165</v>
       </c>
       <c r="D74" s="53" t="s">
@@ -57511,13 +57520,13 @@
       <c r="P74" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q74" s="326" t="s">
+      <c r="Q74" s="336" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="75" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="320"/>
-      <c r="C75" s="318"/>
+      <c r="B75" s="341"/>
+      <c r="C75" s="340"/>
       <c r="D75" s="90" t="s">
         <v>22</v>
       </c>
@@ -57560,15 +57569,15 @@
       <c r="P75" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="Q75" s="327"/>
+      <c r="Q75" s="339"/>
     </row>
     <row r="76" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="126"/>
       <c r="C76" s="126"/>
-      <c r="D76" s="319" t="s">
+      <c r="D76" s="320" t="s">
         <v>192</v>
       </c>
-      <c r="E76" s="319"/>
+      <c r="E76" s="320"/>
       <c r="F76" s="126"/>
       <c r="G76" s="126"/>
       <c r="H76" s="126"/>
@@ -57584,133 +57593,133 @@
       <c r="R76" s="126"/>
     </row>
     <row r="77" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B77" s="278" t="s">
+      <c r="B77" s="267" t="s">
         <v>32</v>
       </c>
-      <c r="C77" s="279"/>
-      <c r="D77" s="279"/>
-      <c r="E77" s="279"/>
-      <c r="F77" s="279"/>
-      <c r="G77" s="279"/>
-      <c r="H77" s="279"/>
-      <c r="I77" s="279"/>
-      <c r="J77" s="279"/>
-      <c r="K77" s="279"/>
-      <c r="L77" s="279"/>
-      <c r="M77" s="279"/>
-      <c r="N77" s="279"/>
-      <c r="O77" s="279"/>
-      <c r="P77" s="279"/>
-      <c r="Q77" s="279"/>
-      <c r="R77" s="280"/>
+      <c r="C77" s="268"/>
+      <c r="D77" s="268"/>
+      <c r="E77" s="268"/>
+      <c r="F77" s="268"/>
+      <c r="G77" s="268"/>
+      <c r="H77" s="268"/>
+      <c r="I77" s="268"/>
+      <c r="J77" s="268"/>
+      <c r="K77" s="268"/>
+      <c r="L77" s="268"/>
+      <c r="M77" s="268"/>
+      <c r="N77" s="268"/>
+      <c r="O77" s="268"/>
+      <c r="P77" s="268"/>
+      <c r="Q77" s="268"/>
+      <c r="R77" s="269"/>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B78" s="281" t="s">
+      <c r="B78" s="270" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="282"/>
-      <c r="D78" s="282"/>
-      <c r="E78" s="282"/>
-      <c r="F78" s="282"/>
-      <c r="G78" s="282"/>
-      <c r="H78" s="282"/>
-      <c r="I78" s="282"/>
-      <c r="J78" s="282"/>
-      <c r="K78" s="282"/>
-      <c r="L78" s="282"/>
-      <c r="M78" s="282"/>
-      <c r="N78" s="282"/>
-      <c r="O78" s="282"/>
-      <c r="P78" s="282"/>
-      <c r="Q78" s="282"/>
-      <c r="R78" s="283"/>
+      <c r="C78" s="222"/>
+      <c r="D78" s="222"/>
+      <c r="E78" s="222"/>
+      <c r="F78" s="222"/>
+      <c r="G78" s="222"/>
+      <c r="H78" s="222"/>
+      <c r="I78" s="222"/>
+      <c r="J78" s="222"/>
+      <c r="K78" s="222"/>
+      <c r="L78" s="222"/>
+      <c r="M78" s="222"/>
+      <c r="N78" s="222"/>
+      <c r="O78" s="222"/>
+      <c r="P78" s="222"/>
+      <c r="Q78" s="222"/>
+      <c r="R78" s="271"/>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B79" s="281"/>
-      <c r="C79" s="282"/>
-      <c r="D79" s="282"/>
-      <c r="E79" s="282"/>
-      <c r="F79" s="282"/>
-      <c r="G79" s="282"/>
-      <c r="H79" s="282"/>
-      <c r="I79" s="282"/>
-      <c r="J79" s="282"/>
-      <c r="K79" s="282"/>
-      <c r="L79" s="282"/>
-      <c r="M79" s="282"/>
-      <c r="N79" s="282"/>
-      <c r="O79" s="282"/>
-      <c r="P79" s="282"/>
-      <c r="Q79" s="282"/>
-      <c r="R79" s="283"/>
+      <c r="B79" s="270"/>
+      <c r="C79" s="222"/>
+      <c r="D79" s="222"/>
+      <c r="E79" s="222"/>
+      <c r="F79" s="222"/>
+      <c r="G79" s="222"/>
+      <c r="H79" s="222"/>
+      <c r="I79" s="222"/>
+      <c r="J79" s="222"/>
+      <c r="K79" s="222"/>
+      <c r="L79" s="222"/>
+      <c r="M79" s="222"/>
+      <c r="N79" s="222"/>
+      <c r="O79" s="222"/>
+      <c r="P79" s="222"/>
+      <c r="Q79" s="222"/>
+      <c r="R79" s="271"/>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B80" s="281"/>
-      <c r="C80" s="282"/>
-      <c r="D80" s="282"/>
-      <c r="E80" s="282"/>
-      <c r="F80" s="282"/>
-      <c r="G80" s="282"/>
-      <c r="H80" s="282"/>
-      <c r="I80" s="282"/>
-      <c r="J80" s="282"/>
-      <c r="K80" s="282"/>
-      <c r="L80" s="282"/>
-      <c r="M80" s="282"/>
-      <c r="N80" s="282"/>
-      <c r="O80" s="282"/>
-      <c r="P80" s="282"/>
-      <c r="Q80" s="282"/>
-      <c r="R80" s="283"/>
+      <c r="B80" s="270"/>
+      <c r="C80" s="222"/>
+      <c r="D80" s="222"/>
+      <c r="E80" s="222"/>
+      <c r="F80" s="222"/>
+      <c r="G80" s="222"/>
+      <c r="H80" s="222"/>
+      <c r="I80" s="222"/>
+      <c r="J80" s="222"/>
+      <c r="K80" s="222"/>
+      <c r="L80" s="222"/>
+      <c r="M80" s="222"/>
+      <c r="N80" s="222"/>
+      <c r="O80" s="222"/>
+      <c r="P80" s="222"/>
+      <c r="Q80" s="222"/>
+      <c r="R80" s="271"/>
     </row>
     <row r="81" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="284"/>
-      <c r="C81" s="285"/>
-      <c r="D81" s="285"/>
-      <c r="E81" s="285"/>
-      <c r="F81" s="285"/>
-      <c r="G81" s="285"/>
-      <c r="H81" s="285"/>
-      <c r="I81" s="285"/>
-      <c r="J81" s="285"/>
-      <c r="K81" s="285"/>
-      <c r="L81" s="285"/>
-      <c r="M81" s="285"/>
-      <c r="N81" s="285"/>
-      <c r="O81" s="285"/>
-      <c r="P81" s="285"/>
-      <c r="Q81" s="285"/>
-      <c r="R81" s="286"/>
+      <c r="B81" s="272"/>
+      <c r="C81" s="273"/>
+      <c r="D81" s="273"/>
+      <c r="E81" s="273"/>
+      <c r="F81" s="273"/>
+      <c r="G81" s="273"/>
+      <c r="H81" s="273"/>
+      <c r="I81" s="273"/>
+      <c r="J81" s="273"/>
+      <c r="K81" s="273"/>
+      <c r="L81" s="273"/>
+      <c r="M81" s="273"/>
+      <c r="N81" s="273"/>
+      <c r="O81" s="273"/>
+      <c r="P81" s="273"/>
+      <c r="Q81" s="273"/>
+      <c r="R81" s="274"/>
     </row>
     <row r="89" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B89" s="287" t="s">
+      <c r="B89" s="275" t="s">
         <v>193</v>
       </c>
-      <c r="C89" s="287"/>
-      <c r="D89" s="287"/>
-      <c r="E89" s="287"/>
-      <c r="F89" s="287"/>
-      <c r="G89" s="287"/>
-      <c r="H89" s="287"/>
-      <c r="I89" s="287"/>
-      <c r="J89" s="287"/>
-      <c r="K89" s="287"/>
-      <c r="L89" s="287"/>
-      <c r="M89" s="287"/>
-      <c r="N89" s="287"/>
-      <c r="O89" s="287"/>
-      <c r="P89" s="287"/>
-      <c r="Q89" s="287"/>
-      <c r="R89" s="287"/>
+      <c r="C89" s="275"/>
+      <c r="D89" s="275"/>
+      <c r="E89" s="275"/>
+      <c r="F89" s="275"/>
+      <c r="G89" s="275"/>
+      <c r="H89" s="275"/>
+      <c r="I89" s="275"/>
+      <c r="J89" s="275"/>
+      <c r="K89" s="275"/>
+      <c r="L89" s="275"/>
+      <c r="M89" s="275"/>
+      <c r="N89" s="275"/>
+      <c r="O89" s="275"/>
+      <c r="P89" s="275"/>
+      <c r="Q89" s="275"/>
+      <c r="R89" s="275"/>
     </row>
     <row r="90" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C90" s="303" t="s">
+      <c r="C90" s="234" t="s">
         <v>2</v>
       </c>
-      <c r="D90" s="303"/>
+      <c r="D90" s="234"/>
       <c r="E90" s="127" t="s">
         <v>125</v>
       </c>
@@ -57747,16 +57756,16 @@
       <c r="P90" s="124" t="s">
         <v>118</v>
       </c>
-      <c r="Q90" s="217" t="s">
+      <c r="Q90" s="232" t="s">
         <v>36</v>
       </c>
-      <c r="R90" s="217"/>
+      <c r="R90" s="232"/>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B91" s="214" t="s">
+      <c r="B91" s="228" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="239" t="s">
+      <c r="C91" s="214" t="s">
         <v>165</v>
       </c>
       <c r="D91" s="53" t="s">
@@ -57800,14 +57809,14 @@
       <c r="P91" s="53" t="s">
         <v>152</v>
       </c>
-      <c r="Q91" s="246" t="s">
+      <c r="Q91" s="229" t="s">
         <v>44</v>
       </c>
-      <c r="R91" s="246"/>
+      <c r="R91" s="229"/>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B92" s="214"/>
-      <c r="C92" s="239"/>
+      <c r="B92" s="228"/>
+      <c r="C92" s="214"/>
       <c r="D92" s="53" t="s">
         <v>22</v>
       </c>
@@ -57849,8 +57858,8 @@
       <c r="P92" s="53" t="s">
         <v>152</v>
       </c>
-      <c r="Q92" s="246"/>
-      <c r="R92" s="246"/>
+      <c r="Q92" s="229"/>
+      <c r="R92" s="229"/>
     </row>
     <row r="94" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B94" s="5" t="s">
@@ -57874,82 +57883,82 @@
       <c r="R94" s="6"/>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B95" s="250" t="s">
+      <c r="B95" s="230" t="s">
         <v>33</v>
       </c>
-      <c r="C95" s="250"/>
-      <c r="D95" s="250"/>
-      <c r="E95" s="250"/>
-      <c r="F95" s="250"/>
-      <c r="G95" s="250"/>
-      <c r="H95" s="250"/>
-      <c r="I95" s="250"/>
-      <c r="J95" s="250"/>
-      <c r="K95" s="250"/>
-      <c r="L95" s="250"/>
-      <c r="M95" s="250"/>
-      <c r="N95" s="250"/>
-      <c r="O95" s="250"/>
-      <c r="P95" s="250"/>
-      <c r="Q95" s="250"/>
-      <c r="R95" s="250"/>
+      <c r="C95" s="230"/>
+      <c r="D95" s="230"/>
+      <c r="E95" s="230"/>
+      <c r="F95" s="230"/>
+      <c r="G95" s="230"/>
+      <c r="H95" s="230"/>
+      <c r="I95" s="230"/>
+      <c r="J95" s="230"/>
+      <c r="K95" s="230"/>
+      <c r="L95" s="230"/>
+      <c r="M95" s="230"/>
+      <c r="N95" s="230"/>
+      <c r="O95" s="230"/>
+      <c r="P95" s="230"/>
+      <c r="Q95" s="230"/>
+      <c r="R95" s="230"/>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B96" s="250"/>
-      <c r="C96" s="250"/>
-      <c r="D96" s="250"/>
-      <c r="E96" s="250"/>
-      <c r="F96" s="250"/>
-      <c r="G96" s="250"/>
-      <c r="H96" s="250"/>
-      <c r="I96" s="250"/>
-      <c r="J96" s="250"/>
-      <c r="K96" s="250"/>
-      <c r="L96" s="250"/>
-      <c r="M96" s="250"/>
-      <c r="N96" s="250"/>
-      <c r="O96" s="250"/>
-      <c r="P96" s="250"/>
-      <c r="Q96" s="250"/>
-      <c r="R96" s="250"/>
+      <c r="B96" s="230"/>
+      <c r="C96" s="230"/>
+      <c r="D96" s="230"/>
+      <c r="E96" s="230"/>
+      <c r="F96" s="230"/>
+      <c r="G96" s="230"/>
+      <c r="H96" s="230"/>
+      <c r="I96" s="230"/>
+      <c r="J96" s="230"/>
+      <c r="K96" s="230"/>
+      <c r="L96" s="230"/>
+      <c r="M96" s="230"/>
+      <c r="N96" s="230"/>
+      <c r="O96" s="230"/>
+      <c r="P96" s="230"/>
+      <c r="Q96" s="230"/>
+      <c r="R96" s="230"/>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B97" s="250"/>
-      <c r="C97" s="250"/>
-      <c r="D97" s="250"/>
-      <c r="E97" s="250"/>
-      <c r="F97" s="250"/>
-      <c r="G97" s="250"/>
-      <c r="H97" s="250"/>
-      <c r="I97" s="250"/>
-      <c r="J97" s="250"/>
-      <c r="K97" s="250"/>
-      <c r="L97" s="250"/>
-      <c r="M97" s="250"/>
-      <c r="N97" s="250"/>
-      <c r="O97" s="250"/>
-      <c r="P97" s="250"/>
-      <c r="Q97" s="250"/>
-      <c r="R97" s="250"/>
+      <c r="B97" s="230"/>
+      <c r="C97" s="230"/>
+      <c r="D97" s="230"/>
+      <c r="E97" s="230"/>
+      <c r="F97" s="230"/>
+      <c r="G97" s="230"/>
+      <c r="H97" s="230"/>
+      <c r="I97" s="230"/>
+      <c r="J97" s="230"/>
+      <c r="K97" s="230"/>
+      <c r="L97" s="230"/>
+      <c r="M97" s="230"/>
+      <c r="N97" s="230"/>
+      <c r="O97" s="230"/>
+      <c r="P97" s="230"/>
+      <c r="Q97" s="230"/>
+      <c r="R97" s="230"/>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B98" s="250"/>
-      <c r="C98" s="250"/>
-      <c r="D98" s="250"/>
-      <c r="E98" s="250"/>
-      <c r="F98" s="250"/>
-      <c r="G98" s="250"/>
-      <c r="H98" s="250"/>
-      <c r="I98" s="250"/>
-      <c r="J98" s="250"/>
-      <c r="K98" s="250"/>
-      <c r="L98" s="250"/>
-      <c r="M98" s="250"/>
-      <c r="N98" s="250"/>
-      <c r="O98" s="250"/>
-      <c r="P98" s="250"/>
-      <c r="Q98" s="250"/>
-      <c r="R98" s="250"/>
+      <c r="B98" s="230"/>
+      <c r="C98" s="230"/>
+      <c r="D98" s="230"/>
+      <c r="E98" s="230"/>
+      <c r="F98" s="230"/>
+      <c r="G98" s="230"/>
+      <c r="H98" s="230"/>
+      <c r="I98" s="230"/>
+      <c r="J98" s="230"/>
+      <c r="K98" s="230"/>
+      <c r="L98" s="230"/>
+      <c r="M98" s="230"/>
+      <c r="N98" s="230"/>
+      <c r="O98" s="230"/>
+      <c r="P98" s="230"/>
+      <c r="Q98" s="230"/>
+      <c r="R98" s="230"/>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B99" s="122"/>
@@ -57989,34 +57998,34 @@
       <c r="C106" s="28"/>
     </row>
     <row r="107" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B107" s="215" t="s">
+      <c r="B107" s="238" t="s">
         <v>196</v>
       </c>
-      <c r="C107" s="216"/>
-      <c r="D107" s="216"/>
-      <c r="E107" s="216"/>
-      <c r="F107" s="216"/>
-      <c r="G107" s="216"/>
-      <c r="H107" s="216"/>
-      <c r="I107" s="216"/>
-      <c r="J107" s="216"/>
-      <c r="K107" s="216"/>
-      <c r="L107" s="216"/>
-      <c r="M107" s="216"/>
-      <c r="N107" s="216"/>
-      <c r="O107" s="216"/>
-      <c r="P107" s="216"/>
-      <c r="Q107" s="216"/>
-      <c r="R107" s="216"/>
+      <c r="C107" s="233"/>
+      <c r="D107" s="233"/>
+      <c r="E107" s="233"/>
+      <c r="F107" s="233"/>
+      <c r="G107" s="233"/>
+      <c r="H107" s="233"/>
+      <c r="I107" s="233"/>
+      <c r="J107" s="233"/>
+      <c r="K107" s="233"/>
+      <c r="L107" s="233"/>
+      <c r="M107" s="233"/>
+      <c r="N107" s="233"/>
+      <c r="O107" s="233"/>
+      <c r="P107" s="233"/>
+      <c r="Q107" s="233"/>
+      <c r="R107" s="233"/>
     </row>
     <row r="108" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B108" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C108" s="217" t="s">
+      <c r="C108" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D108" s="217"/>
+      <c r="D108" s="232"/>
       <c r="E108" s="8" t="s">
         <v>3</v>
       </c>
@@ -58061,10 +58070,10 @@
       </c>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B109" s="305" t="s">
+      <c r="B109" s="213" t="s">
         <v>98</v>
       </c>
-      <c r="C109" s="239" t="s">
+      <c r="C109" s="214" t="s">
         <v>165</v>
       </c>
       <c r="D109" s="53" t="s">
@@ -58116,8 +58125,8 @@
       </c>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B110" s="305"/>
-      <c r="C110" s="239"/>
+      <c r="B110" s="213"/>
+      <c r="C110" s="214"/>
       <c r="D110" s="53" t="s">
         <v>22</v>
       </c>
@@ -58167,10 +58176,10 @@
       </c>
     </row>
     <row r="111" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B111" s="305" t="s">
+      <c r="B111" s="213" t="s">
         <v>160</v>
       </c>
-      <c r="C111" s="239" t="s">
+      <c r="C111" s="214" t="s">
         <v>165</v>
       </c>
       <c r="D111" s="53" t="s">
@@ -58223,8 +58232,8 @@
       </c>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B112" s="305"/>
-      <c r="C112" s="239"/>
+      <c r="B112" s="213"/>
+      <c r="C112" s="214"/>
       <c r="D112" s="53" t="s">
         <v>22</v>
       </c>
@@ -58276,29 +58285,30 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="B32:Q32"/>
-    <mergeCell ref="B18:P18"/>
-    <mergeCell ref="B19:P22"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B9:P9"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B56:Q56"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B40:P43"/>
-    <mergeCell ref="B52:Q52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="P34:Q36"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B89:R89"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="B77:R77"/>
+    <mergeCell ref="B78:R81"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="B107:R107"/>
+    <mergeCell ref="B64:Q64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="Q58:Q59"/>
+    <mergeCell ref="B95:R98"/>
+    <mergeCell ref="Q90:R90"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="Q91:R92"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="C73:D73"/>
     <mergeCell ref="C57:D57"/>
     <mergeCell ref="B68:Q68"/>
     <mergeCell ref="C69:D69"/>
@@ -58315,30 +58325,29 @@
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="Q66:Q67"/>
     <mergeCell ref="Q70:Q71"/>
-    <mergeCell ref="B64:Q64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="Q58:Q59"/>
-    <mergeCell ref="B95:R98"/>
-    <mergeCell ref="Q90:R90"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="Q91:R92"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B89:R89"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="B77:R77"/>
-    <mergeCell ref="B78:R81"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="B107:R107"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B56:Q56"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B40:P43"/>
+    <mergeCell ref="B52:Q52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="P34:Q36"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B9:P9"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="B32:Q32"/>
+    <mergeCell ref="B18:P18"/>
+    <mergeCell ref="B19:P22"/>
+    <mergeCell ref="C33:D33"/>
   </mergeCells>
   <phoneticPr fontId="12" alignment="center"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -58352,7 +58361,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B8:S40"/>
+  <dimension ref="B8:S41"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="19"/>
@@ -58381,33 +58390,33 @@
   </cols>
   <sheetData>
     <row r="8" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="215" t="s">
+      <c r="B8" s="238" t="s">
         <v>197</v>
       </c>
-      <c r="C8" s="216"/>
-      <c r="D8" s="216"/>
-      <c r="E8" s="216"/>
-      <c r="F8" s="216"/>
-      <c r="G8" s="216"/>
-      <c r="H8" s="216"/>
-      <c r="I8" s="216"/>
-      <c r="J8" s="216"/>
-      <c r="K8" s="216"/>
-      <c r="L8" s="216"/>
-      <c r="M8" s="216"/>
-      <c r="N8" s="216"/>
-      <c r="O8" s="216"/>
-      <c r="P8" s="216"/>
-      <c r="Q8" s="216"/>
+      <c r="C8" s="233"/>
+      <c r="D8" s="233"/>
+      <c r="E8" s="233"/>
+      <c r="F8" s="233"/>
+      <c r="G8" s="233"/>
+      <c r="H8" s="233"/>
+      <c r="I8" s="233"/>
+      <c r="J8" s="233"/>
+      <c r="K8" s="233"/>
+      <c r="L8" s="233"/>
+      <c r="M8" s="233"/>
+      <c r="N8" s="233"/>
+      <c r="O8" s="233"/>
+      <c r="P8" s="233"/>
+      <c r="Q8" s="233"/>
     </row>
     <row r="9" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B9" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="217" t="s">
+      <c r="C9" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="217"/>
+      <c r="D9" s="232"/>
       <c r="E9" s="120" t="s">
         <v>3</v>
       </c>
@@ -58449,10 +58458,10 @@
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="218" t="s">
+      <c r="B10" s="227" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="214" t="s">
+      <c r="C10" s="228" t="s">
         <v>110</v>
       </c>
       <c r="D10" s="117" t="s">
@@ -58501,8 +58510,8 @@
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="219"/>
-      <c r="C11" s="214"/>
+      <c r="B11" s="298"/>
+      <c r="C11" s="228"/>
       <c r="D11" s="117" t="s">
         <v>22</v>
       </c>
@@ -58548,150 +58557,148 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="215" t="s">
+    <row r="12" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B12" s="362" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="212" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="117" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="142">
+        <v>1300</v>
+      </c>
+      <c r="F12" s="142" t="s">
+        <v>177</v>
+      </c>
+      <c r="G12" s="95">
+        <v>410</v>
+      </c>
+      <c r="H12" s="95">
+        <v>54.2</v>
+      </c>
+      <c r="I12" s="363" t="s">
+        <v>177</v>
+      </c>
+      <c r="J12" s="95">
+        <v>40</v>
+      </c>
+      <c r="K12" s="184">
+        <v>65</v>
+      </c>
+      <c r="L12" s="96">
+        <f>SUM(E12:K12)</f>
+        <v>1869.2</v>
+      </c>
+      <c r="M12" s="95">
+        <v>200</v>
+      </c>
+      <c r="N12" s="96">
+        <f>L12+M12</f>
+        <v>2069.1999999999998</v>
+      </c>
+      <c r="O12" s="181" t="s">
+        <v>111</v>
+      </c>
+      <c r="P12" s="204" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q12" s="94" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="238" t="s">
         <v>199</v>
       </c>
-      <c r="C12" s="216"/>
-      <c r="D12" s="216"/>
-      <c r="E12" s="216"/>
-      <c r="F12" s="216"/>
-      <c r="G12" s="216"/>
-      <c r="H12" s="216"/>
-      <c r="I12" s="216"/>
-      <c r="J12" s="216"/>
-      <c r="K12" s="216"/>
-      <c r="L12" s="216"/>
-      <c r="M12" s="216"/>
-      <c r="N12" s="216"/>
-      <c r="O12" s="216"/>
-      <c r="P12" s="216"/>
-      <c r="Q12" s="216"/>
-      <c r="R12" s="216"/>
+      <c r="C13" s="233"/>
+      <c r="D13" s="233"/>
+      <c r="E13" s="233"/>
+      <c r="F13" s="233"/>
+      <c r="G13" s="233"/>
+      <c r="H13" s="233"/>
+      <c r="I13" s="233"/>
+      <c r="J13" s="233"/>
+      <c r="K13" s="233"/>
+      <c r="L13" s="233"/>
+      <c r="M13" s="233"/>
+      <c r="N13" s="233"/>
+      <c r="O13" s="233"/>
+      <c r="P13" s="233"/>
+      <c r="Q13" s="233"/>
+      <c r="R13" s="233"/>
     </row>
-    <row r="13" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="97" t="s">
+    <row r="14" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="217" t="s">
+      <c r="C14" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="217"/>
-      <c r="E13" s="120" t="s">
+      <c r="D14" s="232"/>
+      <c r="E14" s="120" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="120" t="s">
+      <c r="G14" s="120" t="s">
         <v>106</v>
       </c>
-      <c r="H13" s="120" t="s">
+      <c r="H14" s="120" t="s">
         <v>198</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="L13" s="3" t="s">
+      <c r="K14" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="N13" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O13" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P13" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q13" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="R13" s="120" t="s">
+      <c r="R14" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="S13" s="120" t="s">
+      <c r="S14" s="120" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="214" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="214" t="s">
-        <v>165</v>
-      </c>
-      <c r="D14" s="117" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="118">
-        <v>400</v>
-      </c>
-      <c r="F14" s="142">
-        <v>120</v>
-      </c>
-      <c r="G14" s="95">
-        <v>340</v>
-      </c>
-      <c r="H14" s="95">
-        <v>97.87</v>
-      </c>
-      <c r="I14" s="95">
-        <v>150</v>
-      </c>
-      <c r="J14" s="95">
-        <v>50</v>
-      </c>
-      <c r="K14" s="95">
-        <v>165</v>
-      </c>
-      <c r="L14" s="95">
-        <v>175</v>
-      </c>
-      <c r="M14" s="184">
-        <v>66</v>
-      </c>
-      <c r="N14" s="96">
-        <f>SUM(E14:M14)</f>
-        <v>1563.87</v>
-      </c>
-      <c r="O14" s="95">
-        <v>200</v>
-      </c>
-      <c r="P14" s="96">
-        <f>N14+O14</f>
-        <v>1763.87</v>
-      </c>
-      <c r="Q14" s="181" t="s">
-        <v>111</v>
-      </c>
-      <c r="R14" s="204" t="s">
-        <v>20</v>
-      </c>
-      <c r="S14" s="94" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="214"/>
-      <c r="C15" s="214"/>
+      <c r="B15" s="228" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="228" t="s">
+        <v>165</v>
+      </c>
       <c r="D15" s="117" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E15" s="118">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="F15" s="142">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="G15" s="95">
         <v>340</v>
@@ -58700,7 +58707,7 @@
         <v>97.87</v>
       </c>
       <c r="I15" s="95">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="J15" s="95">
         <v>50</v>
@@ -58716,14 +58723,14 @@
       </c>
       <c r="N15" s="96">
         <f>SUM(E15:M15)</f>
-        <v>1883.87</v>
+        <v>1563.87</v>
       </c>
       <c r="O15" s="95">
         <v>200</v>
       </c>
       <c r="P15" s="96">
         <f>N15+O15</f>
-        <v>2083.87</v>
+        <v>1763.87</v>
       </c>
       <c r="Q15" s="181" t="s">
         <v>111</v>
@@ -58735,133 +58742,141 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="222" t="s">
-        <v>203</v>
-      </c>
-      <c r="C16" s="223"/>
-      <c r="D16" s="223"/>
-      <c r="E16" s="223"/>
-      <c r="F16" s="223"/>
-      <c r="G16" s="223"/>
-      <c r="H16" s="223"/>
-      <c r="I16" s="223"/>
-      <c r="J16" s="223"/>
-      <c r="K16" s="223"/>
-      <c r="L16" s="223"/>
-      <c r="M16" s="223"/>
-      <c r="N16" s="223"/>
-      <c r="O16" s="223"/>
-      <c r="P16" s="223"/>
-      <c r="Q16" s="223"/>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B16" s="228"/>
+      <c r="C16" s="228"/>
+      <c r="D16" s="117" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="118">
+        <v>550</v>
+      </c>
+      <c r="F16" s="142">
+        <v>240</v>
+      </c>
+      <c r="G16" s="95">
+        <v>340</v>
+      </c>
+      <c r="H16" s="95">
+        <v>97.87</v>
+      </c>
+      <c r="I16" s="95">
+        <v>200</v>
+      </c>
+      <c r="J16" s="95">
+        <v>50</v>
+      </c>
+      <c r="K16" s="95">
+        <v>165</v>
+      </c>
+      <c r="L16" s="95">
+        <v>175</v>
+      </c>
+      <c r="M16" s="184">
+        <v>66</v>
+      </c>
+      <c r="N16" s="96">
+        <f>SUM(E16:M16)</f>
+        <v>1883.87</v>
+      </c>
+      <c r="O16" s="95">
+        <v>200</v>
+      </c>
+      <c r="P16" s="96">
+        <f>N16+O16</f>
+        <v>2083.87</v>
+      </c>
+      <c r="Q16" s="181" t="s">
+        <v>111</v>
+      </c>
+      <c r="R16" s="204" t="s">
+        <v>20</v>
+      </c>
+      <c r="S16" s="94" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="17" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="97" t="s">
+      <c r="B17" s="346" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" s="347"/>
+      <c r="D17" s="347"/>
+      <c r="E17" s="347"/>
+      <c r="F17" s="347"/>
+      <c r="G17" s="347"/>
+      <c r="H17" s="347"/>
+      <c r="I17" s="347"/>
+      <c r="J17" s="347"/>
+      <c r="K17" s="347"/>
+      <c r="L17" s="347"/>
+      <c r="M17" s="347"/>
+      <c r="N17" s="347"/>
+      <c r="O17" s="347"/>
+      <c r="P17" s="347"/>
+      <c r="Q17" s="347"/>
+    </row>
+    <row r="18" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B18" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="217" t="s">
+      <c r="C18" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="217"/>
-      <c r="E17" s="120" t="s">
+      <c r="D18" s="232"/>
+      <c r="E18" s="120" t="s">
         <v>3</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G17" s="120" t="s">
+      <c r="G18" s="120" t="s">
         <v>106</v>
       </c>
-      <c r="H17" s="120" t="s">
+      <c r="H18" s="120" t="s">
         <v>198</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L17" s="3" t="s">
+      <c r="L18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="3" t="s">
+      <c r="M18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N17" s="120" t="s">
+      <c r="N18" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="O17" s="120" t="s">
+      <c r="O18" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="P17" s="220" t="s">
+      <c r="P18" s="344" t="s">
         <v>137</v>
       </c>
-      <c r="Q17" s="221"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="214" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="214" t="s">
-        <v>204</v>
-      </c>
-      <c r="D18" s="117" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="118">
-        <v>1000</v>
-      </c>
-      <c r="F18" s="95">
-        <v>130</v>
-      </c>
-      <c r="G18" s="95">
-        <v>355</v>
-      </c>
-      <c r="H18" s="95">
-        <v>76.5</v>
-      </c>
-      <c r="I18" s="95">
-        <v>50</v>
-      </c>
-      <c r="J18" s="96">
-        <f>SUM(E18:I18)</f>
-        <v>1611.5</v>
-      </c>
-      <c r="K18" s="95">
-        <v>200</v>
-      </c>
-      <c r="L18" s="96">
-        <f>J18+K18</f>
-        <v>1811.5</v>
-      </c>
-      <c r="M18" s="181" t="s">
-        <v>111</v>
-      </c>
-      <c r="N18" s="204" t="s">
-        <v>20</v>
-      </c>
-      <c r="O18" s="94" t="s">
-        <v>43</v>
-      </c>
-      <c r="P18" s="182" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q18" s="53"/>
+      <c r="Q18" s="345"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="214"/>
-      <c r="C19" s="214"/>
+      <c r="B19" s="228" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="228" t="s">
+        <v>204</v>
+      </c>
       <c r="D19" s="117" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E19" s="118">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F19" s="95">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="G19" s="95">
         <v>355</v>
@@ -58874,14 +58889,14 @@
       </c>
       <c r="J19" s="96">
         <f>SUM(E19:I19)</f>
-        <v>2741.5</v>
+        <v>1611.5</v>
       </c>
       <c r="K19" s="95">
         <v>200</v>
       </c>
       <c r="L19" s="96">
         <f>J19+K19</f>
-        <v>2941.5</v>
+        <v>1811.5</v>
       </c>
       <c r="M19" s="181" t="s">
         <v>111</v>
@@ -58897,281 +58912,282 @@
       </c>
       <c r="Q19" s="53"/>
     </row>
-    <row r="20" spans="2:17" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="212" t="s">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B20" s="228"/>
+      <c r="C20" s="228"/>
+      <c r="D20" s="117" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="118">
+        <v>2000</v>
+      </c>
+      <c r="F20" s="95">
+        <v>260</v>
+      </c>
+      <c r="G20" s="95">
+        <v>355</v>
+      </c>
+      <c r="H20" s="95">
+        <v>76.5</v>
+      </c>
+      <c r="I20" s="95">
+        <v>50</v>
+      </c>
+      <c r="J20" s="96">
+        <f>SUM(E20:I20)</f>
+        <v>2741.5</v>
+      </c>
+      <c r="K20" s="95">
+        <v>200</v>
+      </c>
+      <c r="L20" s="96">
+        <f>J20+K20</f>
+        <v>2941.5</v>
+      </c>
+      <c r="M20" s="181" t="s">
+        <v>111</v>
+      </c>
+      <c r="N20" s="204" t="s">
+        <v>20</v>
+      </c>
+      <c r="O20" s="94" t="s">
+        <v>43</v>
+      </c>
+      <c r="P20" s="182" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q20" s="53"/>
+    </row>
+    <row r="21" spans="2:17" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="237" t="s">
         <v>206</v>
       </c>
-      <c r="C20" s="213"/>
-      <c r="D20" s="213"/>
-      <c r="E20" s="213"/>
-      <c r="F20" s="213"/>
-      <c r="G20" s="213"/>
-      <c r="H20" s="213"/>
-      <c r="I20" s="213"/>
-      <c r="J20" s="213"/>
-      <c r="K20" s="213"/>
-      <c r="L20" s="213"/>
-      <c r="M20" s="213"/>
-      <c r="N20" s="213"/>
-      <c r="O20" s="213"/>
-      <c r="P20" s="207"/>
+      <c r="C21" s="294"/>
+      <c r="D21" s="294"/>
+      <c r="E21" s="294"/>
+      <c r="F21" s="294"/>
+      <c r="G21" s="294"/>
+      <c r="H21" s="294"/>
+      <c r="I21" s="294"/>
+      <c r="J21" s="294"/>
+      <c r="K21" s="294"/>
+      <c r="L21" s="294"/>
+      <c r="M21" s="294"/>
+      <c r="N21" s="294"/>
+      <c r="O21" s="294"/>
+      <c r="P21" s="207"/>
     </row>
-    <row r="21" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="97" t="s">
+    <row r="22" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B22" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="217" t="s">
+      <c r="C22" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="217"/>
-      <c r="E21" s="120" t="s">
+      <c r="D22" s="232"/>
+      <c r="E22" s="120" t="s">
         <v>3</v>
       </c>
-      <c r="F21" s="120" t="s">
+      <c r="F22" s="120" t="s">
         <v>106</v>
       </c>
-      <c r="G21" s="120" t="s">
+      <c r="G22" s="120" t="s">
         <v>198</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M21" s="120" t="s">
+      <c r="M22" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="N21" s="120" t="s">
+      <c r="N22" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="O21" s="120" t="s">
+      <c r="O22" s="120" t="s">
         <v>137</v>
       </c>
-      <c r="P21" s="230"/>
-      <c r="Q21" s="231"/>
+      <c r="P22" s="342"/>
+      <c r="Q22" s="343"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="214" t="s">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B23" s="228" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="214" t="s">
+      <c r="C23" s="228" t="s">
         <v>207</v>
       </c>
-      <c r="D22" s="117" t="s">
+      <c r="D23" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="138">
+      <c r="E23" s="138">
         <f>CEILING((((725)*1.5)-355),100)</f>
         <v>800</v>
       </c>
-      <c r="F22" s="95">
+      <c r="F23" s="95">
         <v>355</v>
       </c>
-      <c r="G22" s="95">
+      <c r="G23" s="95">
         <v>76.5</v>
       </c>
-      <c r="H22" s="95">
+      <c r="H23" s="95">
         <v>50</v>
       </c>
-      <c r="I22" s="96">
-        <f>SUM(E22:H22)</f>
+      <c r="I23" s="96">
+        <f>SUM(E23:H23)</f>
         <v>1281.5</v>
       </c>
-      <c r="J22" s="95">
-        <v>200</v>
-      </c>
-      <c r="K22" s="96">
-        <f>I22+J22</f>
+      <c r="J23" s="95">
+        <v>200</v>
+      </c>
+      <c r="K23" s="96">
+        <f>I23+J23</f>
         <v>1481.5</v>
       </c>
-      <c r="L22" s="181" t="s">
+      <c r="L23" s="181" t="s">
         <v>208</v>
       </c>
-      <c r="M22" s="204" t="s">
+      <c r="M23" s="204" t="s">
         <v>20</v>
       </c>
-      <c r="N22" s="94" t="s">
+      <c r="N23" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="O22" s="206" t="s">
+      <c r="O23" s="206" t="s">
         <v>205</v>
       </c>
-      <c r="P22" s="205"/>
+      <c r="P23" s="205"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B23" s="214"/>
-      <c r="C23" s="214"/>
-      <c r="D23" s="117" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="138">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B24" s="228"/>
+      <c r="C24" s="228"/>
+      <c r="D24" s="117" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="138">
         <f>CEILING((((1200)*1.4)-289),50)</f>
         <v>1400</v>
       </c>
-      <c r="F23" s="95">
+      <c r="F24" s="95">
         <v>355</v>
       </c>
-      <c r="G23" s="95">
+      <c r="G24" s="95">
         <v>76.5</v>
       </c>
-      <c r="H23" s="95">
+      <c r="H24" s="95">
         <v>50</v>
       </c>
-      <c r="I23" s="96">
-        <f>SUM(E23:H23)</f>
+      <c r="I24" s="96">
+        <f>SUM(E24:H24)</f>
         <v>1881.5</v>
       </c>
-      <c r="J23" s="95">
-        <v>200</v>
-      </c>
-      <c r="K23" s="96">
-        <f>I23+J23</f>
+      <c r="J24" s="95">
+        <v>200</v>
+      </c>
+      <c r="K24" s="96">
+        <f>I24+J24</f>
         <v>2081.5</v>
       </c>
-      <c r="L23" s="181" t="s">
+      <c r="L24" s="181" t="s">
         <v>208</v>
       </c>
-      <c r="M23" s="204" t="s">
+      <c r="M24" s="204" t="s">
         <v>20</v>
       </c>
-      <c r="N23" s="94" t="s">
+      <c r="N24" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="O23" s="206" t="s">
+      <c r="O24" s="206" t="s">
         <v>205</v>
       </c>
-      <c r="P23" s="205"/>
-    </row>
-    <row r="24" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="215" t="s">
-        <v>209</v>
-      </c>
-      <c r="C24" s="216"/>
-      <c r="D24" s="216"/>
-      <c r="E24" s="216"/>
-      <c r="F24" s="216"/>
-      <c r="G24" s="216"/>
-      <c r="H24" s="216"/>
-      <c r="I24" s="216"/>
-      <c r="J24" s="216"/>
-      <c r="K24" s="216"/>
-      <c r="L24" s="216"/>
-      <c r="M24" s="216"/>
-      <c r="N24" s="216"/>
-      <c r="O24" s="216"/>
-      <c r="P24" s="61"/>
+      <c r="P24" s="205"/>
     </row>
     <row r="25" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B25" s="97" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="217" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="217"/>
-      <c r="E25" s="120" t="s">
-        <v>3</v>
-      </c>
-      <c r="F25" s="120" t="s">
-        <v>106</v>
-      </c>
-      <c r="G25" s="120" t="s">
-        <v>198</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M25" s="120" t="s">
-        <v>13</v>
-      </c>
-      <c r="N25" s="120" t="s">
-        <v>14</v>
-      </c>
-      <c r="O25" s="120" t="s">
-        <v>137</v>
-      </c>
+      <c r="B25" s="238" t="s">
+        <v>209</v>
+      </c>
+      <c r="C25" s="233"/>
+      <c r="D25" s="233"/>
+      <c r="E25" s="233"/>
+      <c r="F25" s="233"/>
+      <c r="G25" s="233"/>
+      <c r="H25" s="233"/>
+      <c r="I25" s="233"/>
+      <c r="J25" s="233"/>
+      <c r="K25" s="233"/>
+      <c r="L25" s="233"/>
+      <c r="M25" s="233"/>
+      <c r="N25" s="233"/>
+      <c r="O25" s="233"/>
       <c r="P25" s="61"/>
     </row>
-    <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="214" t="s">
+    <row r="26" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B26" s="97" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="232" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="232"/>
+      <c r="E26" s="120" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="120" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" s="120" t="s">
+        <v>198</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M26" s="120" t="s">
+        <v>13</v>
+      </c>
+      <c r="N26" s="120" t="s">
+        <v>14</v>
+      </c>
+      <c r="O26" s="120" t="s">
+        <v>137</v>
+      </c>
+      <c r="P26" s="61"/>
+    </row>
+    <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="228" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="214" t="s">
+      <c r="C27" s="228" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="117" t="s">
+      <c r="D27" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="138">
+      <c r="E27" s="138">
         <f>CEILING((((490+5+85+15)*1.15)),75)</f>
         <v>750</v>
-      </c>
-      <c r="F26" s="95">
-        <v>259</v>
-      </c>
-      <c r="G26" s="95">
-        <f>60*1.125</f>
-        <v>67.5</v>
-      </c>
-      <c r="H26" s="95">
-        <v>60</v>
-      </c>
-      <c r="I26" s="96">
-        <f>SUM(E26:H26)</f>
-        <v>1136.5</v>
-      </c>
-      <c r="J26" s="95">
-        <v>200</v>
-      </c>
-      <c r="K26" s="96">
-        <f>I26+J26</f>
-        <v>1336.5</v>
-      </c>
-      <c r="L26" s="181" t="s">
-        <v>25</v>
-      </c>
-      <c r="M26" s="204" t="s">
-        <v>20</v>
-      </c>
-      <c r="N26" s="94" t="s">
-        <v>175</v>
-      </c>
-      <c r="O26" s="182" t="s">
-        <v>205</v>
-      </c>
-      <c r="P26" s="61"/>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B27" s="214"/>
-      <c r="C27" s="214"/>
-      <c r="D27" s="117" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="138">
-        <f>CEILING((((500+5+175+15)*1.15)),75)</f>
-        <v>825</v>
       </c>
       <c r="F27" s="95">
         <v>259</v>
@@ -59185,14 +59201,14 @@
       </c>
       <c r="I27" s="96">
         <f>SUM(E27:H27)</f>
-        <v>1211.5</v>
+        <v>1136.5</v>
       </c>
       <c r="J27" s="95">
         <v>200</v>
       </c>
       <c r="K27" s="96">
         <f>I27+J27</f>
-        <v>1411.5</v>
+        <v>1336.5</v>
       </c>
       <c r="L27" s="181" t="s">
         <v>25</v>
@@ -59208,117 +59224,144 @@
       </c>
       <c r="P27" s="61"/>
     </row>
-    <row r="29" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="5" t="s">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B28" s="228"/>
+      <c r="C28" s="228"/>
+      <c r="D28" s="117" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="138">
+        <f>CEILING((((500+5+175+15)*1.15)),75)</f>
+        <v>825</v>
+      </c>
+      <c r="F28" s="95">
+        <v>259</v>
+      </c>
+      <c r="G28" s="95">
+        <f>60*1.125</f>
+        <v>67.5</v>
+      </c>
+      <c r="H28" s="95">
+        <v>60</v>
+      </c>
+      <c r="I28" s="96">
+        <f>SUM(E28:H28)</f>
+        <v>1211.5</v>
+      </c>
+      <c r="J28" s="95">
+        <v>200</v>
+      </c>
+      <c r="K28" s="96">
+        <f>I28+J28</f>
+        <v>1411.5</v>
+      </c>
+      <c r="L28" s="181" t="s">
+        <v>25</v>
+      </c>
+      <c r="M28" s="204" t="s">
+        <v>20</v>
+      </c>
+      <c r="N28" s="94" t="s">
+        <v>175</v>
+      </c>
+      <c r="O28" s="182" t="s">
+        <v>205</v>
+      </c>
+      <c r="P28" s="61"/>
+    </row>
+    <row r="30" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B30" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="7"/>
-    </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B30" s="224" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="225"/>
-      <c r="D30" s="225"/>
-      <c r="E30" s="225"/>
-      <c r="F30" s="225"/>
-      <c r="G30" s="225"/>
-      <c r="H30" s="225"/>
-      <c r="I30" s="225"/>
-      <c r="J30" s="225"/>
-      <c r="K30" s="225"/>
-      <c r="L30" s="225"/>
-      <c r="M30" s="225"/>
-      <c r="N30" s="225"/>
-      <c r="O30" s="225"/>
-      <c r="P30" s="225"/>
-      <c r="Q30" s="226"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="7"/>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B31" s="224"/>
-      <c r="C31" s="225"/>
-      <c r="D31" s="225"/>
-      <c r="E31" s="225"/>
-      <c r="F31" s="225"/>
-      <c r="G31" s="225"/>
-      <c r="H31" s="225"/>
-      <c r="I31" s="225"/>
-      <c r="J31" s="225"/>
-      <c r="K31" s="225"/>
-      <c r="L31" s="225"/>
-      <c r="M31" s="225"/>
-      <c r="N31" s="225"/>
-      <c r="O31" s="225"/>
-      <c r="P31" s="225"/>
-      <c r="Q31" s="226"/>
+      <c r="B31" s="243" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="263"/>
+      <c r="D31" s="263"/>
+      <c r="E31" s="263"/>
+      <c r="F31" s="263"/>
+      <c r="G31" s="263"/>
+      <c r="H31" s="263"/>
+      <c r="I31" s="263"/>
+      <c r="J31" s="263"/>
+      <c r="K31" s="263"/>
+      <c r="L31" s="263"/>
+      <c r="M31" s="263"/>
+      <c r="N31" s="263"/>
+      <c r="O31" s="263"/>
+      <c r="P31" s="263"/>
+      <c r="Q31" s="264"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B32" s="224"/>
-      <c r="C32" s="225"/>
-      <c r="D32" s="225"/>
-      <c r="E32" s="225"/>
-      <c r="F32" s="225"/>
-      <c r="G32" s="225"/>
-      <c r="H32" s="225"/>
-      <c r="I32" s="225"/>
-      <c r="J32" s="225"/>
-      <c r="K32" s="225"/>
-      <c r="L32" s="225"/>
-      <c r="M32" s="225"/>
-      <c r="N32" s="225"/>
-      <c r="O32" s="225"/>
-      <c r="P32" s="225"/>
-      <c r="Q32" s="226"/>
+      <c r="B32" s="243"/>
+      <c r="C32" s="263"/>
+      <c r="D32" s="263"/>
+      <c r="E32" s="263"/>
+      <c r="F32" s="263"/>
+      <c r="G32" s="263"/>
+      <c r="H32" s="263"/>
+      <c r="I32" s="263"/>
+      <c r="J32" s="263"/>
+      <c r="K32" s="263"/>
+      <c r="L32" s="263"/>
+      <c r="M32" s="263"/>
+      <c r="N32" s="263"/>
+      <c r="O32" s="263"/>
+      <c r="P32" s="263"/>
+      <c r="Q32" s="264"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B33" s="227"/>
-      <c r="C33" s="228"/>
-      <c r="D33" s="228"/>
-      <c r="E33" s="228"/>
-      <c r="F33" s="228"/>
-      <c r="G33" s="228"/>
-      <c r="H33" s="228"/>
-      <c r="I33" s="228"/>
-      <c r="J33" s="228"/>
-      <c r="K33" s="228"/>
-      <c r="L33" s="228"/>
-      <c r="M33" s="228"/>
-      <c r="N33" s="228"/>
-      <c r="O33" s="228"/>
-      <c r="P33" s="228"/>
-      <c r="Q33" s="229"/>
+      <c r="B33" s="243"/>
+      <c r="C33" s="263"/>
+      <c r="D33" s="263"/>
+      <c r="E33" s="263"/>
+      <c r="F33" s="263"/>
+      <c r="G33" s="263"/>
+      <c r="H33" s="263"/>
+      <c r="I33" s="263"/>
+      <c r="J33" s="263"/>
+      <c r="K33" s="263"/>
+      <c r="L33" s="263"/>
+      <c r="M33" s="263"/>
+      <c r="N33" s="263"/>
+      <c r="O33" s="263"/>
+      <c r="P33" s="263"/>
+      <c r="Q33" s="264"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="35"/>
-      <c r="N34" s="35"/>
-      <c r="O34" s="35"/>
-      <c r="P34" s="35"/>
-      <c r="Q34" s="35"/>
+      <c r="B34" s="244"/>
+      <c r="C34" s="265"/>
+      <c r="D34" s="265"/>
+      <c r="E34" s="265"/>
+      <c r="F34" s="265"/>
+      <c r="G34" s="265"/>
+      <c r="H34" s="265"/>
+      <c r="I34" s="265"/>
+      <c r="J34" s="265"/>
+      <c r="K34" s="265"/>
+      <c r="L34" s="265"/>
+      <c r="M34" s="265"/>
+      <c r="N34" s="265"/>
+      <c r="O34" s="265"/>
+      <c r="P34" s="265"/>
+      <c r="Q34" s="266"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B35" s="35"/>
@@ -59428,31 +59471,49 @@
       <c r="P40" s="35"/>
       <c r="Q40" s="35"/>
     </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B41" s="35"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="35"/>
+      <c r="M41" s="35"/>
+      <c r="N41" s="35"/>
+      <c r="O41" s="35"/>
+      <c r="P41" s="35"/>
+      <c r="Q41" s="35"/>
+    </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B30:Q33"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B24:O24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="B21:O21"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B19:B20"/>
     <mergeCell ref="B8:Q8"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B12:R12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B13:R13"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="B16:Q16"/>
-    <mergeCell ref="B20:O20"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="B17:Q17"/>
+    <mergeCell ref="B31:Q34"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B25:O25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="P22:Q22"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -59639,10 +59700,10 @@
       <c r="B10" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="359" t="s">
+      <c r="C10" s="348" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="359"/>
+      <c r="D10" s="348"/>
       <c r="E10" s="15" t="s">
         <v>3</v>
       </c>
@@ -59681,10 +59742,10 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="355" t="s">
+      <c r="B11" s="349" t="s">
         <v>211</v>
       </c>
-      <c r="C11" s="357" t="s">
+      <c r="C11" s="352" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="45" t="s">
@@ -59730,8 +59791,8 @@
       </c>
     </row>
     <row r="12" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="360"/>
-      <c r="C12" s="357"/>
+      <c r="B12" s="350"/>
+      <c r="C12" s="352"/>
       <c r="D12" s="45" t="s">
         <v>22</v>
       </c>
@@ -59775,8 +59836,8 @@
       </c>
     </row>
     <row r="13" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="360"/>
-      <c r="C13" s="357" t="s">
+      <c r="B13" s="350"/>
+      <c r="C13" s="352" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="45" t="s">
@@ -59822,8 +59883,8 @@
       </c>
     </row>
     <row r="14" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="360"/>
-      <c r="C14" s="357"/>
+      <c r="B14" s="350"/>
+      <c r="C14" s="352"/>
       <c r="D14" s="45" t="s">
         <v>22</v>
       </c>
@@ -59867,8 +59928,8 @@
       </c>
     </row>
     <row r="15" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="360"/>
-      <c r="C15" s="357" t="s">
+      <c r="B15" s="350"/>
+      <c r="C15" s="352" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="45" t="s">
@@ -59914,8 +59975,8 @@
       </c>
     </row>
     <row r="16" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="360"/>
-      <c r="C16" s="357"/>
+      <c r="B16" s="350"/>
+      <c r="C16" s="352"/>
       <c r="D16" s="45" t="s">
         <v>22</v>
       </c>
@@ -59959,8 +60020,8 @@
       </c>
     </row>
     <row r="17" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="360"/>
-      <c r="C17" s="357" t="s">
+      <c r="B17" s="350"/>
+      <c r="C17" s="352" t="s">
         <v>29</v>
       </c>
       <c r="D17" s="45" t="s">
@@ -60006,8 +60067,8 @@
       </c>
     </row>
     <row r="18" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="360"/>
-      <c r="C18" s="357"/>
+      <c r="B18" s="350"/>
+      <c r="C18" s="352"/>
       <c r="D18" s="45" t="s">
         <v>22</v>
       </c>
@@ -60051,8 +60112,8 @@
       </c>
     </row>
     <row r="19" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="360"/>
-      <c r="C19" s="357" t="s">
+      <c r="B19" s="350"/>
+      <c r="C19" s="352" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="45" t="s">
@@ -60098,8 +60159,8 @@
       </c>
     </row>
     <row r="20" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="356"/>
-      <c r="C20" s="357"/>
+      <c r="B20" s="351"/>
+      <c r="C20" s="352"/>
       <c r="D20" s="45" t="s">
         <v>22</v>
       </c>
@@ -60143,10 +60204,10 @@
       </c>
     </row>
     <row r="21" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="355" t="s">
+      <c r="B21" s="349" t="s">
         <v>216</v>
       </c>
-      <c r="C21" s="357" t="s">
+      <c r="C21" s="352" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="45" t="s">
@@ -60192,8 +60253,8 @@
       </c>
     </row>
     <row r="22" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="356"/>
-      <c r="C22" s="357"/>
+      <c r="B22" s="351"/>
+      <c r="C22" s="352"/>
       <c r="D22" s="45" t="s">
         <v>22</v>
       </c>
@@ -60237,10 +60298,10 @@
       </c>
     </row>
     <row r="23" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B23" s="355" t="s">
+      <c r="B23" s="349" t="s">
         <v>217</v>
       </c>
-      <c r="C23" s="357" t="s">
+      <c r="C23" s="352" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="45" t="s">
@@ -60286,8 +60347,8 @@
       </c>
     </row>
     <row r="24" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="356"/>
-      <c r="C24" s="357"/>
+      <c r="B24" s="351"/>
+      <c r="C24" s="352"/>
       <c r="D24" s="45" t="s">
         <v>22</v>
       </c>
@@ -60331,10 +60392,10 @@
       </c>
     </row>
     <row r="25" spans="2:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="234" t="s">
+      <c r="B25" s="262" t="s">
         <v>219</v>
       </c>
-      <c r="C25" s="214" t="s">
+      <c r="C25" s="228" t="s">
         <v>29</v>
       </c>
       <c r="D25" s="40" t="s">
@@ -60380,8 +60441,8 @@
       </c>
     </row>
     <row r="26" spans="2:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="234"/>
-      <c r="C26" s="214"/>
+      <c r="B26" s="262"/>
+      <c r="C26" s="228"/>
       <c r="D26" s="40" t="s">
         <v>22</v>
       </c>
@@ -60425,8 +60486,8 @@
       </c>
     </row>
     <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="320"/>
-      <c r="C27" s="358"/>
+      <c r="B27" s="341"/>
+      <c r="C27" s="361"/>
       <c r="D27" s="84" t="s">
         <v>17</v>
       </c>
@@ -60486,103 +60547,96 @@
       <c r="O28" s="28"/>
     </row>
     <row r="29" spans="2:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="347" t="s">
+      <c r="B29" s="353" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="348"/>
-      <c r="D29" s="348"/>
-      <c r="E29" s="348"/>
-      <c r="F29" s="348"/>
-      <c r="G29" s="348"/>
-      <c r="H29" s="348"/>
-      <c r="I29" s="348"/>
-      <c r="J29" s="348"/>
-      <c r="K29" s="348"/>
-      <c r="L29" s="348"/>
-      <c r="M29" s="348"/>
-      <c r="N29" s="348"/>
-      <c r="O29" s="348"/>
-      <c r="P29" s="349"/>
+      <c r="C29" s="354"/>
+      <c r="D29" s="354"/>
+      <c r="E29" s="354"/>
+      <c r="F29" s="354"/>
+      <c r="G29" s="354"/>
+      <c r="H29" s="354"/>
+      <c r="I29" s="354"/>
+      <c r="J29" s="354"/>
+      <c r="K29" s="354"/>
+      <c r="L29" s="354"/>
+      <c r="M29" s="354"/>
+      <c r="N29" s="354"/>
+      <c r="O29" s="354"/>
+      <c r="P29" s="355"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B30" s="350" t="s">
+      <c r="B30" s="356" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="225"/>
-      <c r="D30" s="225"/>
-      <c r="E30" s="225"/>
-      <c r="F30" s="225"/>
-      <c r="G30" s="225"/>
-      <c r="H30" s="225"/>
-      <c r="I30" s="225"/>
-      <c r="J30" s="225"/>
-      <c r="K30" s="225"/>
-      <c r="L30" s="225"/>
-      <c r="M30" s="225"/>
-      <c r="N30" s="225"/>
-      <c r="O30" s="225"/>
-      <c r="P30" s="351"/>
+      <c r="C30" s="263"/>
+      <c r="D30" s="263"/>
+      <c r="E30" s="263"/>
+      <c r="F30" s="263"/>
+      <c r="G30" s="263"/>
+      <c r="H30" s="263"/>
+      <c r="I30" s="263"/>
+      <c r="J30" s="263"/>
+      <c r="K30" s="263"/>
+      <c r="L30" s="263"/>
+      <c r="M30" s="263"/>
+      <c r="N30" s="263"/>
+      <c r="O30" s="263"/>
+      <c r="P30" s="357"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="350"/>
-      <c r="C31" s="225"/>
-      <c r="D31" s="225"/>
-      <c r="E31" s="225"/>
-      <c r="F31" s="225"/>
-      <c r="G31" s="225"/>
-      <c r="H31" s="225"/>
-      <c r="I31" s="225"/>
-      <c r="J31" s="225"/>
-      <c r="K31" s="225"/>
-      <c r="L31" s="225"/>
-      <c r="M31" s="225"/>
-      <c r="N31" s="225"/>
-      <c r="O31" s="225"/>
-      <c r="P31" s="351"/>
+      <c r="B31" s="356"/>
+      <c r="C31" s="263"/>
+      <c r="D31" s="263"/>
+      <c r="E31" s="263"/>
+      <c r="F31" s="263"/>
+      <c r="G31" s="263"/>
+      <c r="H31" s="263"/>
+      <c r="I31" s="263"/>
+      <c r="J31" s="263"/>
+      <c r="K31" s="263"/>
+      <c r="L31" s="263"/>
+      <c r="M31" s="263"/>
+      <c r="N31" s="263"/>
+      <c r="O31" s="263"/>
+      <c r="P31" s="357"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B32" s="350"/>
-      <c r="C32" s="225"/>
-      <c r="D32" s="225"/>
-      <c r="E32" s="225"/>
-      <c r="F32" s="225"/>
-      <c r="G32" s="225"/>
-      <c r="H32" s="225"/>
-      <c r="I32" s="225"/>
-      <c r="J32" s="225"/>
-      <c r="K32" s="225"/>
-      <c r="L32" s="225"/>
-      <c r="M32" s="225"/>
-      <c r="N32" s="225"/>
-      <c r="O32" s="225"/>
-      <c r="P32" s="351"/>
+      <c r="B32" s="356"/>
+      <c r="C32" s="263"/>
+      <c r="D32" s="263"/>
+      <c r="E32" s="263"/>
+      <c r="F32" s="263"/>
+      <c r="G32" s="263"/>
+      <c r="H32" s="263"/>
+      <c r="I32" s="263"/>
+      <c r="J32" s="263"/>
+      <c r="K32" s="263"/>
+      <c r="L32" s="263"/>
+      <c r="M32" s="263"/>
+      <c r="N32" s="263"/>
+      <c r="O32" s="263"/>
+      <c r="P32" s="357"/>
     </row>
     <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="352"/>
-      <c r="C33" s="353"/>
-      <c r="D33" s="353"/>
-      <c r="E33" s="353"/>
-      <c r="F33" s="353"/>
-      <c r="G33" s="353"/>
-      <c r="H33" s="353"/>
-      <c r="I33" s="353"/>
-      <c r="J33" s="353"/>
-      <c r="K33" s="353"/>
-      <c r="L33" s="353"/>
-      <c r="M33" s="353"/>
-      <c r="N33" s="353"/>
-      <c r="O33" s="353"/>
-      <c r="P33" s="354"/>
+      <c r="B33" s="358"/>
+      <c r="C33" s="359"/>
+      <c r="D33" s="359"/>
+      <c r="E33" s="359"/>
+      <c r="F33" s="359"/>
+      <c r="G33" s="359"/>
+      <c r="H33" s="359"/>
+      <c r="I33" s="359"/>
+      <c r="J33" s="359"/>
+      <c r="K33" s="359"/>
+      <c r="L33" s="359"/>
+      <c r="M33" s="359"/>
+      <c r="N33" s="359"/>
+      <c r="O33" s="359"/>
+      <c r="P33" s="360"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B20"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
     <mergeCell ref="B29:P29"/>
     <mergeCell ref="B30:P33"/>
     <mergeCell ref="B21:B22"/>
@@ -60591,6 +60645,13 @@
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="B25:B27"/>
     <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B20"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="67" orientation="landscape" r:id="rId1"/>
@@ -60599,12 +60660,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bf418b7-79e0-4993-aa07-d31c53a64380">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="268ad1c4-fabf-4dd0-b894-8fd5403102c0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -60831,20 +60894,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bf418b7-79e0-4993-aa07-d31c53a64380">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="268ad1c4-fabf-4dd0-b894-8fd5403102c0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
+    <ds:schemaRef ds:uri="268ad1c4-fabf-4dd0-b894-8fd5403102c0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -60869,12 +60933,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
-    <ds:schemaRef ds:uri="268ad1c4-fabf-4dd0-b894-8fd5403102c0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Customer Rate Tariff Template_Week 33_2026.xlsx
+++ b/Customer Rate Tariff Template_Week 33_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stephanie.galera.RAMPSLOGISTICS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40202C9-680B-46E2-8F05-6892BF060277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500FBC82-7468-4898-B2EF-D9D1B161F089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
   </bookViews>
@@ -2230,10 +2230,292 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2257,9 +2539,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2272,267 +2551,67 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2547,95 +2626,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2660,14 +2651,23 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4128,32 +4128,32 @@
       <c r="P7" s="18"/>
     </row>
     <row r="8" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="233" t="s">
+      <c r="B8" s="219" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="233"/>
-      <c r="D8" s="233"/>
-      <c r="E8" s="233"/>
-      <c r="F8" s="233"/>
-      <c r="G8" s="233"/>
-      <c r="H8" s="233"/>
-      <c r="I8" s="233"/>
-      <c r="J8" s="233"/>
-      <c r="K8" s="233"/>
-      <c r="L8" s="233"/>
-      <c r="M8" s="233"/>
-      <c r="N8" s="233"/>
-      <c r="O8" s="233"/>
-      <c r="P8" s="233"/>
+      <c r="C8" s="219"/>
+      <c r="D8" s="219"/>
+      <c r="E8" s="219"/>
+      <c r="F8" s="219"/>
+      <c r="G8" s="219"/>
+      <c r="H8" s="219"/>
+      <c r="I8" s="219"/>
+      <c r="J8" s="219"/>
+      <c r="K8" s="219"/>
+      <c r="L8" s="219"/>
+      <c r="M8" s="219"/>
+      <c r="N8" s="219"/>
+      <c r="O8" s="219"/>
+      <c r="P8" s="219"/>
     </row>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="232" t="s">
+      <c r="C9" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="232"/>
+      <c r="D9" s="220"/>
       <c r="E9" s="120" t="s">
         <v>3</v>
       </c>
@@ -4192,10 +4192,10 @@
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="308" t="s">
+      <c r="B10" s="238" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="308" t="s">
+      <c r="C10" s="238" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="20" t="s">
@@ -4241,8 +4241,8 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="309"/>
-      <c r="C11" s="309"/>
+      <c r="B11" s="239"/>
+      <c r="C11" s="239"/>
       <c r="D11" s="20" t="s">
         <v>22</v>
       </c>
@@ -4286,8 +4286,8 @@
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="309"/>
-      <c r="C12" s="308" t="s">
+      <c r="B12" s="239"/>
+      <c r="C12" s="238" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="111" t="s">
@@ -4334,8 +4334,8 @@
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="309"/>
-      <c r="C13" s="309"/>
+      <c r="B13" s="239"/>
+      <c r="C13" s="239"/>
       <c r="D13" s="111" t="s">
         <v>22</v>
       </c>
@@ -4381,10 +4381,10 @@
       <c r="Q13" s="26"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="253" t="s">
+      <c r="B14" s="240" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="214" t="s">
+      <c r="C14" s="242" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="20" t="s">
@@ -4431,8 +4431,8 @@
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="310"/>
-      <c r="C15" s="214"/>
+      <c r="B15" s="241"/>
+      <c r="C15" s="242"/>
       <c r="D15" s="20" t="s">
         <v>22</v>
       </c>
@@ -4477,10 +4477,10 @@
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="253" t="s">
+      <c r="B16" s="240" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="253" t="s">
+      <c r="C16" s="240" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="20" t="s">
@@ -4527,8 +4527,8 @@
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B17" s="310"/>
-      <c r="C17" s="310"/>
+      <c r="B17" s="241"/>
+      <c r="C17" s="241"/>
       <c r="D17" s="20" t="s">
         <v>22</v>
       </c>
@@ -4573,10 +4573,10 @@
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="253" t="s">
+      <c r="B18" s="240" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="214" t="s">
+      <c r="C18" s="242" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -4624,8 +4624,8 @@
       <c r="Q18" s="26"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="311"/>
-      <c r="C19" s="214"/>
+      <c r="B19" s="250"/>
+      <c r="C19" s="242"/>
       <c r="D19" s="20" t="s">
         <v>22</v>
       </c>
@@ -4671,8 +4671,8 @@
       <c r="Q19" s="26"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="311"/>
-      <c r="C20" s="214" t="s">
+      <c r="B20" s="250"/>
+      <c r="C20" s="242" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="20" t="s">
@@ -4719,8 +4719,8 @@
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="310"/>
-      <c r="C21" s="214"/>
+      <c r="B21" s="241"/>
+      <c r="C21" s="242"/>
       <c r="D21" s="20" t="s">
         <v>22</v>
       </c>
@@ -4802,74 +4802,74 @@
       <c r="P23" s="186"/>
     </row>
     <row r="24" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="230" t="s">
+      <c r="B24" s="252" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="230"/>
-      <c r="D24" s="230"/>
-      <c r="E24" s="230"/>
-      <c r="F24" s="230"/>
-      <c r="G24" s="230"/>
-      <c r="H24" s="230"/>
-      <c r="I24" s="230"/>
-      <c r="J24" s="230"/>
-      <c r="K24" s="230"/>
-      <c r="L24" s="230"/>
-      <c r="M24" s="230"/>
-      <c r="N24" s="230"/>
-      <c r="O24" s="230"/>
-      <c r="P24" s="230"/>
+      <c r="C24" s="252"/>
+      <c r="D24" s="252"/>
+      <c r="E24" s="252"/>
+      <c r="F24" s="252"/>
+      <c r="G24" s="252"/>
+      <c r="H24" s="252"/>
+      <c r="I24" s="252"/>
+      <c r="J24" s="252"/>
+      <c r="K24" s="252"/>
+      <c r="L24" s="252"/>
+      <c r="M24" s="252"/>
+      <c r="N24" s="252"/>
+      <c r="O24" s="252"/>
+      <c r="P24" s="252"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B25" s="230"/>
-      <c r="C25" s="230"/>
-      <c r="D25" s="230"/>
-      <c r="E25" s="230"/>
-      <c r="F25" s="230"/>
-      <c r="G25" s="230"/>
-      <c r="H25" s="230"/>
-      <c r="I25" s="230"/>
-      <c r="J25" s="230"/>
-      <c r="K25" s="230"/>
-      <c r="L25" s="230"/>
-      <c r="M25" s="230"/>
-      <c r="N25" s="230"/>
-      <c r="O25" s="230"/>
-      <c r="P25" s="230"/>
+      <c r="B25" s="252"/>
+      <c r="C25" s="252"/>
+      <c r="D25" s="252"/>
+      <c r="E25" s="252"/>
+      <c r="F25" s="252"/>
+      <c r="G25" s="252"/>
+      <c r="H25" s="252"/>
+      <c r="I25" s="252"/>
+      <c r="J25" s="252"/>
+      <c r="K25" s="252"/>
+      <c r="L25" s="252"/>
+      <c r="M25" s="252"/>
+      <c r="N25" s="252"/>
+      <c r="O25" s="252"/>
+      <c r="P25" s="252"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B26" s="230"/>
-      <c r="C26" s="230"/>
-      <c r="D26" s="230"/>
-      <c r="E26" s="230"/>
-      <c r="F26" s="230"/>
-      <c r="G26" s="230"/>
-      <c r="H26" s="230"/>
-      <c r="I26" s="230"/>
-      <c r="J26" s="230"/>
-      <c r="K26" s="230"/>
-      <c r="L26" s="230"/>
-      <c r="M26" s="230"/>
-      <c r="N26" s="230"/>
-      <c r="O26" s="230"/>
-      <c r="P26" s="230"/>
+      <c r="B26" s="252"/>
+      <c r="C26" s="252"/>
+      <c r="D26" s="252"/>
+      <c r="E26" s="252"/>
+      <c r="F26" s="252"/>
+      <c r="G26" s="252"/>
+      <c r="H26" s="252"/>
+      <c r="I26" s="252"/>
+      <c r="J26" s="252"/>
+      <c r="K26" s="252"/>
+      <c r="L26" s="252"/>
+      <c r="M26" s="252"/>
+      <c r="N26" s="252"/>
+      <c r="O26" s="252"/>
+      <c r="P26" s="252"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B27" s="230"/>
-      <c r="C27" s="230"/>
-      <c r="D27" s="230"/>
-      <c r="E27" s="230"/>
-      <c r="F27" s="230"/>
-      <c r="G27" s="230"/>
-      <c r="H27" s="230"/>
-      <c r="I27" s="230"/>
-      <c r="J27" s="230"/>
-      <c r="K27" s="230"/>
-      <c r="L27" s="230"/>
-      <c r="M27" s="230"/>
-      <c r="N27" s="230"/>
-      <c r="O27" s="230"/>
-      <c r="P27" s="230"/>
+      <c r="B27" s="252"/>
+      <c r="C27" s="252"/>
+      <c r="D27" s="252"/>
+      <c r="E27" s="252"/>
+      <c r="F27" s="252"/>
+      <c r="G27" s="252"/>
+      <c r="H27" s="252"/>
+      <c r="I27" s="252"/>
+      <c r="J27" s="252"/>
+      <c r="K27" s="252"/>
+      <c r="L27" s="252"/>
+      <c r="M27" s="252"/>
+      <c r="N27" s="252"/>
+      <c r="O27" s="252"/>
+      <c r="P27" s="252"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B28" s="35"/>
@@ -4998,32 +4998,32 @@
       <c r="Q34" s="28"/>
     </row>
     <row r="35" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="245" t="s">
+      <c r="B35" s="243" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="294"/>
-      <c r="D35" s="294"/>
-      <c r="E35" s="294"/>
-      <c r="F35" s="294"/>
-      <c r="G35" s="294"/>
-      <c r="H35" s="294"/>
-      <c r="I35" s="294"/>
-      <c r="J35" s="294"/>
-      <c r="K35" s="294"/>
-      <c r="L35" s="294"/>
-      <c r="M35" s="294"/>
-      <c r="N35" s="294"/>
-      <c r="O35" s="294"/>
-      <c r="P35" s="294"/>
+      <c r="C35" s="216"/>
+      <c r="D35" s="216"/>
+      <c r="E35" s="216"/>
+      <c r="F35" s="216"/>
+      <c r="G35" s="216"/>
+      <c r="H35" s="216"/>
+      <c r="I35" s="216"/>
+      <c r="J35" s="216"/>
+      <c r="K35" s="216"/>
+      <c r="L35" s="216"/>
+      <c r="M35" s="216"/>
+      <c r="N35" s="216"/>
+      <c r="O35" s="216"/>
+      <c r="P35" s="216"/>
     </row>
     <row r="36" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B36" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="232" t="s">
+      <c r="C36" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="232"/>
+      <c r="D36" s="220"/>
       <c r="E36" s="120" t="s">
         <v>3</v>
       </c>
@@ -5054,13 +5054,13 @@
       <c r="N36" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="O36" s="232" t="s">
+      <c r="O36" s="220" t="s">
         <v>36</v>
       </c>
-      <c r="P36" s="232"/>
+      <c r="P36" s="220"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B37" s="254" t="s">
+      <c r="B37" s="244" t="s">
         <v>37</v>
       </c>
       <c r="C37" s="136" t="s">
@@ -5102,13 +5102,13 @@
       <c r="N37" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O37" s="255" t="s">
+      <c r="O37" s="245" t="s">
         <v>40</v>
       </c>
-      <c r="P37" s="257"/>
+      <c r="P37" s="246"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B38" s="254"/>
+      <c r="B38" s="244"/>
       <c r="C38" s="136" t="s">
         <v>16</v>
       </c>
@@ -5148,8 +5148,8 @@
       <c r="N38" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O38" s="299"/>
-      <c r="P38" s="300"/>
+      <c r="O38" s="247"/>
+      <c r="P38" s="248"/>
     </row>
     <row r="39" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="187" t="s">
@@ -5193,10 +5193,10 @@
       <c r="N39" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="O39" s="229" t="s">
+      <c r="O39" s="249" t="s">
         <v>44</v>
       </c>
-      <c r="P39" s="229"/>
+      <c r="P39" s="249"/>
     </row>
     <row r="40" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="187" t="s">
@@ -5241,10 +5241,10 @@
       <c r="N40" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O40" s="229" t="s">
+      <c r="O40" s="249" t="s">
         <v>44</v>
       </c>
-      <c r="P40" s="229"/>
+      <c r="P40" s="249"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B41" s="42"/>
@@ -5285,78 +5285,78 @@
       <c r="Q42" s="7"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B43" s="243" t="s">
+      <c r="B43" s="227" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="263"/>
-      <c r="D43" s="263"/>
-      <c r="E43" s="263"/>
-      <c r="F43" s="263"/>
-      <c r="G43" s="263"/>
-      <c r="H43" s="263"/>
-      <c r="I43" s="263"/>
-      <c r="J43" s="263"/>
-      <c r="K43" s="263"/>
-      <c r="L43" s="263"/>
-      <c r="M43" s="263"/>
-      <c r="N43" s="263"/>
-      <c r="O43" s="263"/>
-      <c r="P43" s="263"/>
-      <c r="Q43" s="264"/>
+      <c r="C43" s="228"/>
+      <c r="D43" s="228"/>
+      <c r="E43" s="228"/>
+      <c r="F43" s="228"/>
+      <c r="G43" s="228"/>
+      <c r="H43" s="228"/>
+      <c r="I43" s="228"/>
+      <c r="J43" s="228"/>
+      <c r="K43" s="228"/>
+      <c r="L43" s="228"/>
+      <c r="M43" s="228"/>
+      <c r="N43" s="228"/>
+      <c r="O43" s="228"/>
+      <c r="P43" s="228"/>
+      <c r="Q43" s="229"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B44" s="243"/>
-      <c r="C44" s="263"/>
-      <c r="D44" s="263"/>
-      <c r="E44" s="263"/>
-      <c r="F44" s="263"/>
-      <c r="G44" s="263"/>
-      <c r="H44" s="263"/>
-      <c r="I44" s="263"/>
-      <c r="J44" s="263"/>
-      <c r="K44" s="263"/>
-      <c r="L44" s="263"/>
-      <c r="M44" s="263"/>
-      <c r="N44" s="263"/>
-      <c r="O44" s="263"/>
-      <c r="P44" s="263"/>
-      <c r="Q44" s="264"/>
+      <c r="B44" s="227"/>
+      <c r="C44" s="228"/>
+      <c r="D44" s="228"/>
+      <c r="E44" s="228"/>
+      <c r="F44" s="228"/>
+      <c r="G44" s="228"/>
+      <c r="H44" s="228"/>
+      <c r="I44" s="228"/>
+      <c r="J44" s="228"/>
+      <c r="K44" s="228"/>
+      <c r="L44" s="228"/>
+      <c r="M44" s="228"/>
+      <c r="N44" s="228"/>
+      <c r="O44" s="228"/>
+      <c r="P44" s="228"/>
+      <c r="Q44" s="229"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B45" s="243"/>
-      <c r="C45" s="263"/>
-      <c r="D45" s="263"/>
-      <c r="E45" s="263"/>
-      <c r="F45" s="263"/>
-      <c r="G45" s="263"/>
-      <c r="H45" s="263"/>
-      <c r="I45" s="263"/>
-      <c r="J45" s="263"/>
-      <c r="K45" s="263"/>
-      <c r="L45" s="263"/>
-      <c r="M45" s="263"/>
-      <c r="N45" s="263"/>
-      <c r="O45" s="263"/>
-      <c r="P45" s="263"/>
-      <c r="Q45" s="264"/>
+      <c r="B45" s="227"/>
+      <c r="C45" s="228"/>
+      <c r="D45" s="228"/>
+      <c r="E45" s="228"/>
+      <c r="F45" s="228"/>
+      <c r="G45" s="228"/>
+      <c r="H45" s="228"/>
+      <c r="I45" s="228"/>
+      <c r="J45" s="228"/>
+      <c r="K45" s="228"/>
+      <c r="L45" s="228"/>
+      <c r="M45" s="228"/>
+      <c r="N45" s="228"/>
+      <c r="O45" s="228"/>
+      <c r="P45" s="228"/>
+      <c r="Q45" s="229"/>
     </row>
     <row r="46" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B46" s="244"/>
-      <c r="C46" s="265"/>
-      <c r="D46" s="265"/>
-      <c r="E46" s="265"/>
-      <c r="F46" s="265"/>
-      <c r="G46" s="265"/>
-      <c r="H46" s="265"/>
-      <c r="I46" s="265"/>
-      <c r="J46" s="265"/>
-      <c r="K46" s="265"/>
-      <c r="L46" s="265"/>
-      <c r="M46" s="265"/>
-      <c r="N46" s="265"/>
-      <c r="O46" s="265"/>
-      <c r="P46" s="265"/>
-      <c r="Q46" s="266"/>
+      <c r="B46" s="230"/>
+      <c r="C46" s="231"/>
+      <c r="D46" s="231"/>
+      <c r="E46" s="231"/>
+      <c r="F46" s="231"/>
+      <c r="G46" s="231"/>
+      <c r="H46" s="231"/>
+      <c r="I46" s="231"/>
+      <c r="J46" s="231"/>
+      <c r="K46" s="231"/>
+      <c r="L46" s="231"/>
+      <c r="M46" s="231"/>
+      <c r="N46" s="231"/>
+      <c r="O46" s="231"/>
+      <c r="P46" s="231"/>
+      <c r="Q46" s="232"/>
     </row>
     <row r="47" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B47" s="35"/>
@@ -5522,35 +5522,35 @@
       <c r="R55" s="28"/>
     </row>
     <row r="56" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B56" s="231" t="s">
+      <c r="B56" s="235" t="s">
         <v>46</v>
       </c>
-      <c r="C56" s="261"/>
-      <c r="D56" s="261"/>
-      <c r="E56" s="261"/>
-      <c r="F56" s="261"/>
-      <c r="G56" s="261"/>
-      <c r="H56" s="261"/>
-      <c r="I56" s="261"/>
-      <c r="J56" s="261"/>
-      <c r="K56" s="261"/>
-      <c r="L56" s="261"/>
-      <c r="M56" s="261"/>
-      <c r="N56" s="261"/>
-      <c r="O56" s="261"/>
-      <c r="P56" s="261"/>
-      <c r="Q56" s="261"/>
-      <c r="R56" s="261"/>
-      <c r="S56" s="289"/>
+      <c r="C56" s="236"/>
+      <c r="D56" s="236"/>
+      <c r="E56" s="236"/>
+      <c r="F56" s="236"/>
+      <c r="G56" s="236"/>
+      <c r="H56" s="236"/>
+      <c r="I56" s="236"/>
+      <c r="J56" s="236"/>
+      <c r="K56" s="236"/>
+      <c r="L56" s="236"/>
+      <c r="M56" s="236"/>
+      <c r="N56" s="236"/>
+      <c r="O56" s="236"/>
+      <c r="P56" s="236"/>
+      <c r="Q56" s="236"/>
+      <c r="R56" s="236"/>
+      <c r="S56" s="253"/>
     </row>
     <row r="57" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="232" t="s">
+      <c r="C57" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="232"/>
+      <c r="D57" s="220"/>
       <c r="E57" s="120" t="s">
         <v>3</v>
       </c>
@@ -5590,16 +5590,16 @@
       <c r="Q57" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R57" s="306" t="s">
+      <c r="R57" s="254" t="s">
         <v>36</v>
       </c>
-      <c r="S57" s="307"/>
+      <c r="S57" s="255"/>
     </row>
     <row r="58" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="279" t="s">
+      <c r="B58" s="256" t="s">
         <v>51</v>
       </c>
-      <c r="C58" s="280" t="s">
+      <c r="C58" s="251" t="s">
         <v>52</v>
       </c>
       <c r="D58" s="137" t="s">
@@ -5647,14 +5647,14 @@
       <c r="Q58" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R58" s="281" t="s">
+      <c r="R58" s="257" t="s">
         <v>55</v>
       </c>
-      <c r="S58" s="282"/>
+      <c r="S58" s="258"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B59" s="279"/>
-      <c r="C59" s="280"/>
+      <c r="B59" s="256"/>
+      <c r="C59" s="251"/>
       <c r="D59" s="137" t="s">
         <v>22</v>
       </c>
@@ -5700,14 +5700,14 @@
       <c r="Q59" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R59" s="283"/>
-      <c r="S59" s="284"/>
+      <c r="R59" s="259"/>
+      <c r="S59" s="260"/>
     </row>
     <row r="60" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="279" t="s">
+      <c r="B60" s="256" t="s">
         <v>56</v>
       </c>
-      <c r="C60" s="280" t="s">
+      <c r="C60" s="251" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="137" t="s">
@@ -5755,12 +5755,12 @@
       <c r="Q60" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R60" s="283"/>
-      <c r="S60" s="284"/>
+      <c r="R60" s="259"/>
+      <c r="S60" s="260"/>
     </row>
     <row r="61" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B61" s="279"/>
-      <c r="C61" s="280"/>
+      <c r="B61" s="256"/>
+      <c r="C61" s="251"/>
       <c r="D61" s="137" t="s">
         <v>22</v>
       </c>
@@ -5806,14 +5806,14 @@
       <c r="Q61" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R61" s="302"/>
-      <c r="S61" s="303"/>
+      <c r="R61" s="261"/>
+      <c r="S61" s="262"/>
     </row>
     <row r="62" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="296" t="s">
+      <c r="B62" s="267" t="s">
         <v>57</v>
       </c>
-      <c r="C62" s="227" t="s">
+      <c r="C62" s="221" t="s">
         <v>29</v>
       </c>
       <c r="D62" s="117" t="s">
@@ -5861,14 +5861,14 @@
       <c r="Q62" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="R62" s="255" t="s">
+      <c r="R62" s="245" t="s">
         <v>59</v>
       </c>
-      <c r="S62" s="257"/>
+      <c r="S62" s="246"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B63" s="297"/>
-      <c r="C63" s="298"/>
+      <c r="B63" s="268"/>
+      <c r="C63" s="222"/>
       <c r="D63" s="117" t="s">
         <v>22</v>
       </c>
@@ -5914,14 +5914,14 @@
       <c r="Q63" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="R63" s="299"/>
-      <c r="S63" s="300"/>
+      <c r="R63" s="247"/>
+      <c r="S63" s="248"/>
     </row>
     <row r="64" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="279" t="s">
+      <c r="B64" s="256" t="s">
         <v>60</v>
       </c>
-      <c r="C64" s="280" t="s">
+      <c r="C64" s="251" t="s">
         <v>52</v>
       </c>
       <c r="D64" s="137" t="s">
@@ -5969,14 +5969,14 @@
       <c r="Q64" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R64" s="281" t="s">
+      <c r="R64" s="257" t="s">
         <v>55</v>
       </c>
-      <c r="S64" s="282"/>
+      <c r="S64" s="258"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B65" s="279"/>
-      <c r="C65" s="280"/>
+      <c r="B65" s="256"/>
+      <c r="C65" s="251"/>
       <c r="D65" s="137" t="s">
         <v>22</v>
       </c>
@@ -6022,14 +6022,14 @@
       <c r="Q65" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R65" s="283"/>
-      <c r="S65" s="284"/>
+      <c r="R65" s="259"/>
+      <c r="S65" s="260"/>
     </row>
     <row r="66" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="304" t="s">
+      <c r="B66" s="271" t="s">
         <v>61</v>
       </c>
-      <c r="C66" s="292" t="s">
+      <c r="C66" s="269" t="s">
         <v>29</v>
       </c>
       <c r="D66" s="137" t="s">
@@ -6077,14 +6077,14 @@
       <c r="Q66" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="R66" s="255" t="s">
+      <c r="R66" s="245" t="s">
         <v>59</v>
       </c>
-      <c r="S66" s="257"/>
+      <c r="S66" s="246"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B67" s="305"/>
-      <c r="C67" s="301"/>
+      <c r="B67" s="272"/>
+      <c r="C67" s="270"/>
       <c r="D67" s="137" t="s">
         <v>22</v>
       </c>
@@ -6130,14 +6130,14 @@
       <c r="Q67" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="R67" s="299"/>
-      <c r="S67" s="300"/>
+      <c r="R67" s="247"/>
+      <c r="S67" s="248"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B68" s="304" t="s">
+      <c r="B68" s="271" t="s">
         <v>62</v>
       </c>
-      <c r="C68" s="280" t="s">
+      <c r="C68" s="251" t="s">
         <v>52</v>
       </c>
       <c r="D68" s="137" t="s">
@@ -6185,14 +6185,14 @@
       <c r="Q68" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R68" s="281" t="s">
+      <c r="R68" s="257" t="s">
         <v>55</v>
       </c>
-      <c r="S68" s="282"/>
+      <c r="S68" s="258"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B69" s="305"/>
-      <c r="C69" s="280"/>
+      <c r="B69" s="272"/>
+      <c r="C69" s="251"/>
       <c r="D69" s="137" t="s">
         <v>22</v>
       </c>
@@ -6238,14 +6238,14 @@
       <c r="Q69" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R69" s="283"/>
-      <c r="S69" s="284"/>
+      <c r="R69" s="259"/>
+      <c r="S69" s="260"/>
     </row>
     <row r="70" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="279" t="s">
+      <c r="B70" s="256" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="280" t="s">
+      <c r="C70" s="251" t="s">
         <v>52</v>
       </c>
       <c r="D70" s="137" t="s">
@@ -6293,12 +6293,12 @@
       <c r="Q70" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R70" s="283"/>
-      <c r="S70" s="284"/>
+      <c r="R70" s="259"/>
+      <c r="S70" s="260"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B71" s="279"/>
-      <c r="C71" s="280"/>
+      <c r="B71" s="256"/>
+      <c r="C71" s="251"/>
       <c r="D71" s="137" t="s">
         <v>22</v>
       </c>
@@ -6344,14 +6344,14 @@
       <c r="Q71" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R71" s="302"/>
-      <c r="S71" s="303"/>
+      <c r="R71" s="261"/>
+      <c r="S71" s="262"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B72" s="279" t="s">
+      <c r="B72" s="256" t="s">
         <v>64</v>
       </c>
-      <c r="C72" s="292" t="s">
+      <c r="C72" s="269" t="s">
         <v>29</v>
       </c>
       <c r="D72" s="137" t="s">
@@ -6399,14 +6399,14 @@
       <c r="Q72" s="211" t="s">
         <v>65</v>
       </c>
-      <c r="R72" s="285" t="s">
+      <c r="R72" s="263" t="s">
         <v>66</v>
       </c>
-      <c r="S72" s="286"/>
+      <c r="S72" s="264"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B73" s="279"/>
-      <c r="C73" s="301"/>
+      <c r="B73" s="256"/>
+      <c r="C73" s="270"/>
       <c r="D73" s="137" t="s">
         <v>22</v>
       </c>
@@ -6452,14 +6452,14 @@
       <c r="Q73" s="211" t="s">
         <v>65</v>
       </c>
-      <c r="R73" s="287"/>
-      <c r="S73" s="288"/>
+      <c r="R73" s="265"/>
+      <c r="S73" s="266"/>
     </row>
     <row r="74" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="279" t="s">
+      <c r="B74" s="256" t="s">
         <v>67</v>
       </c>
-      <c r="C74" s="280" t="s">
+      <c r="C74" s="251" t="s">
         <v>52</v>
       </c>
       <c r="D74" s="137" t="s">
@@ -6507,14 +6507,14 @@
       <c r="Q74" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R74" s="281" t="s">
+      <c r="R74" s="257" t="s">
         <v>55</v>
       </c>
-      <c r="S74" s="282"/>
+      <c r="S74" s="258"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B75" s="279"/>
-      <c r="C75" s="280"/>
+      <c r="B75" s="256"/>
+      <c r="C75" s="251"/>
       <c r="D75" s="137" t="s">
         <v>22</v>
       </c>
@@ -6560,14 +6560,14 @@
       <c r="Q75" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R75" s="283"/>
-      <c r="S75" s="284"/>
+      <c r="R75" s="259"/>
+      <c r="S75" s="260"/>
     </row>
     <row r="76" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="279" t="s">
+      <c r="B76" s="256" t="s">
         <v>68</v>
       </c>
-      <c r="C76" s="280" t="s">
+      <c r="C76" s="251" t="s">
         <v>52</v>
       </c>
       <c r="D76" s="137" t="s">
@@ -6615,12 +6615,12 @@
       <c r="Q76" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R76" s="283"/>
-      <c r="S76" s="284"/>
+      <c r="R76" s="259"/>
+      <c r="S76" s="260"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B77" s="279"/>
-      <c r="C77" s="280"/>
+      <c r="B77" s="256"/>
+      <c r="C77" s="251"/>
       <c r="D77" s="137" t="s">
         <v>22</v>
       </c>
@@ -6666,14 +6666,14 @@
       <c r="Q77" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R77" s="283"/>
-      <c r="S77" s="284"/>
+      <c r="R77" s="259"/>
+      <c r="S77" s="260"/>
     </row>
     <row r="78" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="279" t="s">
+      <c r="B78" s="256" t="s">
         <v>69</v>
       </c>
-      <c r="C78" s="280" t="s">
+      <c r="C78" s="251" t="s">
         <v>52</v>
       </c>
       <c r="D78" s="137" t="s">
@@ -6721,12 +6721,12 @@
       <c r="Q78" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R78" s="283"/>
-      <c r="S78" s="284"/>
+      <c r="R78" s="259"/>
+      <c r="S78" s="260"/>
     </row>
     <row r="79" spans="2:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="279"/>
-      <c r="C79" s="280"/>
+      <c r="B79" s="256"/>
+      <c r="C79" s="251"/>
       <c r="D79" s="137" t="s">
         <v>22</v>
       </c>
@@ -6772,39 +6772,39 @@
       <c r="Q79" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R79" s="302"/>
-      <c r="S79" s="303"/>
+      <c r="R79" s="261"/>
+      <c r="S79" s="262"/>
     </row>
     <row r="80" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B80" s="231" t="s">
+      <c r="B80" s="235" t="s">
         <v>70</v>
       </c>
-      <c r="C80" s="261"/>
-      <c r="D80" s="261"/>
-      <c r="E80" s="261"/>
-      <c r="F80" s="261"/>
-      <c r="G80" s="261"/>
-      <c r="H80" s="261"/>
-      <c r="I80" s="261"/>
-      <c r="J80" s="261"/>
-      <c r="K80" s="261"/>
-      <c r="L80" s="261"/>
-      <c r="M80" s="261"/>
-      <c r="N80" s="261"/>
-      <c r="O80" s="261"/>
-      <c r="P80" s="261"/>
-      <c r="Q80" s="261"/>
-      <c r="R80" s="233"/>
-      <c r="S80" s="290"/>
+      <c r="C80" s="236"/>
+      <c r="D80" s="236"/>
+      <c r="E80" s="236"/>
+      <c r="F80" s="236"/>
+      <c r="G80" s="236"/>
+      <c r="H80" s="236"/>
+      <c r="I80" s="236"/>
+      <c r="J80" s="236"/>
+      <c r="K80" s="236"/>
+      <c r="L80" s="236"/>
+      <c r="M80" s="236"/>
+      <c r="N80" s="236"/>
+      <c r="O80" s="236"/>
+      <c r="P80" s="236"/>
+      <c r="Q80" s="236"/>
+      <c r="R80" s="219"/>
+      <c r="S80" s="276"/>
     </row>
     <row r="81" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B81" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C81" s="276" t="s">
+      <c r="C81" s="273" t="s">
         <v>2</v>
       </c>
-      <c r="D81" s="277"/>
+      <c r="D81" s="274"/>
       <c r="E81" s="120" t="s">
         <v>3</v>
       </c>
@@ -6844,16 +6844,16 @@
       <c r="Q81" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R81" s="276" t="s">
+      <c r="R81" s="273" t="s">
         <v>36</v>
       </c>
-      <c r="S81" s="278"/>
+      <c r="S81" s="275"/>
     </row>
     <row r="82" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="239" t="s">
+      <c r="B82" s="277" t="s">
         <v>71</v>
       </c>
-      <c r="C82" s="292" t="s">
+      <c r="C82" s="269" t="s">
         <v>72</v>
       </c>
       <c r="D82" s="137" t="s">
@@ -6901,14 +6901,14 @@
       <c r="Q82" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R82" s="285" t="s">
+      <c r="R82" s="263" t="s">
         <v>73</v>
       </c>
-      <c r="S82" s="286"/>
+      <c r="S82" s="264"/>
     </row>
     <row r="83" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="291"/>
-      <c r="C83" s="293"/>
+      <c r="B83" s="278"/>
+      <c r="C83" s="279"/>
       <c r="D83" s="137" t="s">
         <v>22</v>
       </c>
@@ -6954,39 +6954,39 @@
       <c r="Q83" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R83" s="287"/>
-      <c r="S83" s="288"/>
+      <c r="R83" s="265"/>
+      <c r="S83" s="266"/>
     </row>
     <row r="84" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B84" s="231" t="s">
+      <c r="B84" s="235" t="s">
         <v>74</v>
       </c>
-      <c r="C84" s="261"/>
-      <c r="D84" s="261"/>
-      <c r="E84" s="261"/>
-      <c r="F84" s="261"/>
-      <c r="G84" s="261"/>
-      <c r="H84" s="261"/>
-      <c r="I84" s="261"/>
-      <c r="J84" s="261"/>
-      <c r="K84" s="261"/>
-      <c r="L84" s="261"/>
-      <c r="M84" s="261"/>
-      <c r="N84" s="261"/>
-      <c r="O84" s="261"/>
-      <c r="P84" s="261"/>
-      <c r="Q84" s="261"/>
-      <c r="R84" s="261"/>
-      <c r="S84" s="289"/>
+      <c r="C84" s="236"/>
+      <c r="D84" s="236"/>
+      <c r="E84" s="236"/>
+      <c r="F84" s="236"/>
+      <c r="G84" s="236"/>
+      <c r="H84" s="236"/>
+      <c r="I84" s="236"/>
+      <c r="J84" s="236"/>
+      <c r="K84" s="236"/>
+      <c r="L84" s="236"/>
+      <c r="M84" s="236"/>
+      <c r="N84" s="236"/>
+      <c r="O84" s="236"/>
+      <c r="P84" s="236"/>
+      <c r="Q84" s="236"/>
+      <c r="R84" s="236"/>
+      <c r="S84" s="253"/>
     </row>
     <row r="85" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B85" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="276" t="s">
+      <c r="C85" s="273" t="s">
         <v>2</v>
       </c>
-      <c r="D85" s="277"/>
+      <c r="D85" s="274"/>
       <c r="E85" s="120" t="s">
         <v>3</v>
       </c>
@@ -7026,16 +7026,16 @@
       <c r="Q85" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R85" s="276" t="s">
+      <c r="R85" s="273" t="s">
         <v>36</v>
       </c>
-      <c r="S85" s="278"/>
+      <c r="S85" s="275"/>
     </row>
     <row r="86" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="279" t="s">
-        <v>75</v>
-      </c>
-      <c r="C86" s="280" t="s">
+      <c r="B86" s="256" t="s">
+        <v>75</v>
+      </c>
+      <c r="C86" s="251" t="s">
         <v>72</v>
       </c>
       <c r="D86" s="137" t="s">
@@ -7083,14 +7083,14 @@
       <c r="Q86" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R86" s="285" t="s">
+      <c r="R86" s="263" t="s">
         <v>73</v>
       </c>
-      <c r="S86" s="286"/>
+      <c r="S86" s="264"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B87" s="279"/>
-      <c r="C87" s="280"/>
+      <c r="B87" s="256"/>
+      <c r="C87" s="251"/>
       <c r="D87" s="137" t="s">
         <v>22</v>
       </c>
@@ -7136,39 +7136,39 @@
       <c r="Q87" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R87" s="287"/>
-      <c r="S87" s="288"/>
+      <c r="R87" s="265"/>
+      <c r="S87" s="266"/>
     </row>
     <row r="88" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B88" s="237" t="s">
+      <c r="B88" s="215" t="s">
         <v>77</v>
       </c>
-      <c r="C88" s="294"/>
-      <c r="D88" s="294"/>
-      <c r="E88" s="294"/>
-      <c r="F88" s="294"/>
-      <c r="G88" s="294"/>
-      <c r="H88" s="294"/>
-      <c r="I88" s="294"/>
-      <c r="J88" s="294"/>
-      <c r="K88" s="294"/>
-      <c r="L88" s="294"/>
-      <c r="M88" s="294"/>
-      <c r="N88" s="294"/>
-      <c r="O88" s="294"/>
-      <c r="P88" s="294"/>
-      <c r="Q88" s="294"/>
-      <c r="R88" s="294"/>
-      <c r="S88" s="295"/>
+      <c r="C88" s="216"/>
+      <c r="D88" s="216"/>
+      <c r="E88" s="216"/>
+      <c r="F88" s="216"/>
+      <c r="G88" s="216"/>
+      <c r="H88" s="216"/>
+      <c r="I88" s="216"/>
+      <c r="J88" s="216"/>
+      <c r="K88" s="216"/>
+      <c r="L88" s="216"/>
+      <c r="M88" s="216"/>
+      <c r="N88" s="216"/>
+      <c r="O88" s="216"/>
+      <c r="P88" s="216"/>
+      <c r="Q88" s="216"/>
+      <c r="R88" s="216"/>
+      <c r="S88" s="280"/>
     </row>
     <row r="89" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B89" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C89" s="276" t="s">
+      <c r="C89" s="273" t="s">
         <v>2</v>
       </c>
-      <c r="D89" s="277"/>
+      <c r="D89" s="274"/>
       <c r="E89" s="120" t="s">
         <v>3</v>
       </c>
@@ -7208,16 +7208,16 @@
       <c r="Q89" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R89" s="276" t="s">
+      <c r="R89" s="273" t="s">
         <v>36</v>
       </c>
-      <c r="S89" s="278"/>
+      <c r="S89" s="275"/>
     </row>
     <row r="90" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="279" t="s">
+      <c r="B90" s="256" t="s">
         <v>78</v>
       </c>
-      <c r="C90" s="280" t="s">
+      <c r="C90" s="251" t="s">
         <v>72</v>
       </c>
       <c r="D90" s="137" t="s">
@@ -7265,14 +7265,14 @@
       <c r="Q90" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R90" s="285" t="s">
+      <c r="R90" s="263" t="s">
         <v>73</v>
       </c>
-      <c r="S90" s="286"/>
+      <c r="S90" s="264"/>
     </row>
     <row r="91" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="279"/>
-      <c r="C91" s="280"/>
+      <c r="B91" s="256"/>
+      <c r="C91" s="251"/>
       <c r="D91" s="137" t="s">
         <v>22</v>
       </c>
@@ -7318,39 +7318,39 @@
       <c r="Q91" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R91" s="287"/>
-      <c r="S91" s="288"/>
+      <c r="R91" s="265"/>
+      <c r="S91" s="266"/>
     </row>
     <row r="92" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B92" s="237" t="s">
+      <c r="B92" s="215" t="s">
         <v>79</v>
       </c>
-      <c r="C92" s="294"/>
-      <c r="D92" s="294"/>
-      <c r="E92" s="294"/>
-      <c r="F92" s="294"/>
-      <c r="G92" s="294"/>
-      <c r="H92" s="294"/>
-      <c r="I92" s="294"/>
-      <c r="J92" s="294"/>
-      <c r="K92" s="294"/>
-      <c r="L92" s="294"/>
-      <c r="M92" s="294"/>
-      <c r="N92" s="294"/>
-      <c r="O92" s="294"/>
-      <c r="P92" s="294"/>
-      <c r="Q92" s="294"/>
-      <c r="R92" s="294"/>
-      <c r="S92" s="295"/>
+      <c r="C92" s="216"/>
+      <c r="D92" s="216"/>
+      <c r="E92" s="216"/>
+      <c r="F92" s="216"/>
+      <c r="G92" s="216"/>
+      <c r="H92" s="216"/>
+      <c r="I92" s="216"/>
+      <c r="J92" s="216"/>
+      <c r="K92" s="216"/>
+      <c r="L92" s="216"/>
+      <c r="M92" s="216"/>
+      <c r="N92" s="216"/>
+      <c r="O92" s="216"/>
+      <c r="P92" s="216"/>
+      <c r="Q92" s="216"/>
+      <c r="R92" s="216"/>
+      <c r="S92" s="280"/>
     </row>
     <row r="93" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B93" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C93" s="276" t="s">
+      <c r="C93" s="273" t="s">
         <v>2</v>
       </c>
-      <c r="D93" s="277"/>
+      <c r="D93" s="274"/>
       <c r="E93" s="120" t="s">
         <v>3</v>
       </c>
@@ -7390,16 +7390,16 @@
       <c r="Q93" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R93" s="276" t="s">
+      <c r="R93" s="273" t="s">
         <v>36</v>
       </c>
-      <c r="S93" s="278"/>
+      <c r="S93" s="275"/>
     </row>
     <row r="94" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="279" t="s">
+      <c r="B94" s="256" t="s">
         <v>80</v>
       </c>
-      <c r="C94" s="280" t="s">
+      <c r="C94" s="251" t="s">
         <v>72</v>
       </c>
       <c r="D94" s="137" t="s">
@@ -7447,14 +7447,14 @@
       <c r="Q94" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R94" s="285" t="s">
+      <c r="R94" s="263" t="s">
         <v>73</v>
       </c>
-      <c r="S94" s="286"/>
+      <c r="S94" s="264"/>
     </row>
     <row r="95" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="279"/>
-      <c r="C95" s="280"/>
+      <c r="B95" s="256"/>
+      <c r="C95" s="251"/>
       <c r="D95" s="137" t="s">
         <v>22</v>
       </c>
@@ -7500,39 +7500,39 @@
       <c r="Q95" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R95" s="287"/>
-      <c r="S95" s="288"/>
+      <c r="R95" s="265"/>
+      <c r="S95" s="266"/>
     </row>
     <row r="96" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B96" s="231" t="s">
+      <c r="B96" s="235" t="s">
         <v>83</v>
       </c>
-      <c r="C96" s="261"/>
-      <c r="D96" s="261"/>
-      <c r="E96" s="261"/>
-      <c r="F96" s="261"/>
-      <c r="G96" s="261"/>
-      <c r="H96" s="261"/>
-      <c r="I96" s="261"/>
-      <c r="J96" s="261"/>
-      <c r="K96" s="261"/>
-      <c r="L96" s="261"/>
-      <c r="M96" s="261"/>
-      <c r="N96" s="261"/>
-      <c r="O96" s="261"/>
-      <c r="P96" s="261"/>
-      <c r="Q96" s="261"/>
-      <c r="R96" s="233"/>
-      <c r="S96" s="233"/>
+      <c r="C96" s="236"/>
+      <c r="D96" s="236"/>
+      <c r="E96" s="236"/>
+      <c r="F96" s="236"/>
+      <c r="G96" s="236"/>
+      <c r="H96" s="236"/>
+      <c r="I96" s="236"/>
+      <c r="J96" s="236"/>
+      <c r="K96" s="236"/>
+      <c r="L96" s="236"/>
+      <c r="M96" s="236"/>
+      <c r="N96" s="236"/>
+      <c r="O96" s="236"/>
+      <c r="P96" s="236"/>
+      <c r="Q96" s="236"/>
+      <c r="R96" s="219"/>
+      <c r="S96" s="219"/>
     </row>
     <row r="97" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B97" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C97" s="276" t="s">
+      <c r="C97" s="273" t="s">
         <v>2</v>
       </c>
-      <c r="D97" s="277"/>
+      <c r="D97" s="274"/>
       <c r="E97" s="120" t="s">
         <v>3</v>
       </c>
@@ -7572,16 +7572,16 @@
       <c r="Q97" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R97" s="276" t="s">
+      <c r="R97" s="273" t="s">
         <v>36</v>
       </c>
-      <c r="S97" s="278"/>
+      <c r="S97" s="275"/>
     </row>
     <row r="98" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B98" s="279" t="s">
+      <c r="B98" s="256" t="s">
         <v>84</v>
       </c>
-      <c r="C98" s="280" t="s">
+      <c r="C98" s="251" t="s">
         <v>72</v>
       </c>
       <c r="D98" s="137" t="s">
@@ -7629,15 +7629,15 @@
       <c r="Q98" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R98" s="281" t="s">
-        <v>85</v>
-      </c>
-      <c r="S98" s="282"/>
+      <c r="R98" s="257" t="s">
+        <v>85</v>
+      </c>
+      <c r="S98" s="258"/>
       <c r="T98"/>
     </row>
     <row r="99" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="279"/>
-      <c r="C99" s="280"/>
+      <c r="B99" s="256"/>
+      <c r="C99" s="251"/>
       <c r="D99" s="137" t="s">
         <v>22</v>
       </c>
@@ -7683,40 +7683,40 @@
       <c r="Q99" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R99" s="283"/>
-      <c r="S99" s="284"/>
+      <c r="R99" s="259"/>
+      <c r="S99" s="260"/>
       <c r="T99"/>
     </row>
     <row r="100" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B100" s="231" t="s">
+      <c r="B100" s="235" t="s">
         <v>86</v>
       </c>
-      <c r="C100" s="261"/>
-      <c r="D100" s="261"/>
-      <c r="E100" s="261"/>
-      <c r="F100" s="261"/>
-      <c r="G100" s="261"/>
-      <c r="H100" s="261"/>
-      <c r="I100" s="261"/>
-      <c r="J100" s="261"/>
-      <c r="K100" s="261"/>
-      <c r="L100" s="261"/>
-      <c r="M100" s="261"/>
-      <c r="N100" s="261"/>
-      <c r="O100" s="261"/>
-      <c r="P100" s="261"/>
-      <c r="Q100" s="261"/>
-      <c r="R100" s="261"/>
-      <c r="S100" s="289"/>
+      <c r="C100" s="236"/>
+      <c r="D100" s="236"/>
+      <c r="E100" s="236"/>
+      <c r="F100" s="236"/>
+      <c r="G100" s="236"/>
+      <c r="H100" s="236"/>
+      <c r="I100" s="236"/>
+      <c r="J100" s="236"/>
+      <c r="K100" s="236"/>
+      <c r="L100" s="236"/>
+      <c r="M100" s="236"/>
+      <c r="N100" s="236"/>
+      <c r="O100" s="236"/>
+      <c r="P100" s="236"/>
+      <c r="Q100" s="236"/>
+      <c r="R100" s="236"/>
+      <c r="S100" s="253"/>
     </row>
     <row r="101" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B101" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C101" s="276" t="s">
+      <c r="C101" s="273" t="s">
         <v>2</v>
       </c>
-      <c r="D101" s="277"/>
+      <c r="D101" s="274"/>
       <c r="E101" s="120" t="s">
         <v>3</v>
       </c>
@@ -7756,16 +7756,16 @@
       <c r="Q101" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R101" s="276" t="s">
+      <c r="R101" s="273" t="s">
         <v>36</v>
       </c>
-      <c r="S101" s="278"/>
+      <c r="S101" s="275"/>
     </row>
     <row r="102" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B102" s="279" t="s">
+      <c r="B102" s="256" t="s">
         <v>87</v>
       </c>
-      <c r="C102" s="280" t="s">
+      <c r="C102" s="251" t="s">
         <v>29</v>
       </c>
       <c r="D102" s="137" t="s">
@@ -7813,15 +7813,15 @@
       <c r="Q102" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R102" s="281" t="s">
-        <v>85</v>
-      </c>
-      <c r="S102" s="282"/>
+      <c r="R102" s="257" t="s">
+        <v>85</v>
+      </c>
+      <c r="S102" s="258"/>
       <c r="T102"/>
     </row>
     <row r="103" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B103" s="279"/>
-      <c r="C103" s="280"/>
+      <c r="B103" s="256"/>
+      <c r="C103" s="251"/>
       <c r="D103" s="137" t="s">
         <v>22</v>
       </c>
@@ -7867,8 +7867,8 @@
       <c r="Q103" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R103" s="283"/>
-      <c r="S103" s="284"/>
+      <c r="R103" s="259"/>
+      <c r="S103" s="260"/>
       <c r="T103"/>
     </row>
     <row r="104" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7892,137 +7892,137 @@
       <c r="S104" s="134"/>
     </row>
     <row r="105" spans="2:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B105" s="267" t="s">
+      <c r="B105" s="281" t="s">
         <v>32</v>
       </c>
-      <c r="C105" s="268"/>
-      <c r="D105" s="268"/>
-      <c r="E105" s="268"/>
-      <c r="F105" s="268"/>
-      <c r="G105" s="268"/>
-      <c r="H105" s="268"/>
-      <c r="I105" s="268"/>
-      <c r="J105" s="268"/>
-      <c r="K105" s="268"/>
-      <c r="L105" s="268"/>
-      <c r="M105" s="268"/>
-      <c r="N105" s="268"/>
-      <c r="O105" s="268"/>
-      <c r="P105" s="268"/>
-      <c r="Q105" s="268"/>
-      <c r="R105" s="268"/>
-      <c r="S105" s="269"/>
+      <c r="C105" s="282"/>
+      <c r="D105" s="282"/>
+      <c r="E105" s="282"/>
+      <c r="F105" s="282"/>
+      <c r="G105" s="282"/>
+      <c r="H105" s="282"/>
+      <c r="I105" s="282"/>
+      <c r="J105" s="282"/>
+      <c r="K105" s="282"/>
+      <c r="L105" s="282"/>
+      <c r="M105" s="282"/>
+      <c r="N105" s="282"/>
+      <c r="O105" s="282"/>
+      <c r="P105" s="282"/>
+      <c r="Q105" s="282"/>
+      <c r="R105" s="282"/>
+      <c r="S105" s="283"/>
     </row>
     <row r="106" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B106" s="270" t="s">
+      <c r="B106" s="284" t="s">
         <v>33</v>
       </c>
-      <c r="C106" s="222"/>
-      <c r="D106" s="222"/>
-      <c r="E106" s="222"/>
-      <c r="F106" s="222"/>
-      <c r="G106" s="222"/>
-      <c r="H106" s="222"/>
-      <c r="I106" s="222"/>
-      <c r="J106" s="222"/>
-      <c r="K106" s="222"/>
-      <c r="L106" s="222"/>
-      <c r="M106" s="222"/>
-      <c r="N106" s="222"/>
-      <c r="O106" s="222"/>
-      <c r="P106" s="222"/>
-      <c r="Q106" s="222"/>
-      <c r="R106" s="222"/>
-      <c r="S106" s="271"/>
+      <c r="C106" s="285"/>
+      <c r="D106" s="285"/>
+      <c r="E106" s="285"/>
+      <c r="F106" s="285"/>
+      <c r="G106" s="285"/>
+      <c r="H106" s="285"/>
+      <c r="I106" s="285"/>
+      <c r="J106" s="285"/>
+      <c r="K106" s="285"/>
+      <c r="L106" s="285"/>
+      <c r="M106" s="285"/>
+      <c r="N106" s="285"/>
+      <c r="O106" s="285"/>
+      <c r="P106" s="285"/>
+      <c r="Q106" s="285"/>
+      <c r="R106" s="285"/>
+      <c r="S106" s="286"/>
     </row>
     <row r="107" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B107" s="270"/>
-      <c r="C107" s="222"/>
-      <c r="D107" s="222"/>
-      <c r="E107" s="222"/>
-      <c r="F107" s="222"/>
-      <c r="G107" s="222"/>
-      <c r="H107" s="222"/>
-      <c r="I107" s="222"/>
-      <c r="J107" s="222"/>
-      <c r="K107" s="222"/>
-      <c r="L107" s="222"/>
-      <c r="M107" s="222"/>
-      <c r="N107" s="222"/>
-      <c r="O107" s="222"/>
-      <c r="P107" s="222"/>
-      <c r="Q107" s="222"/>
-      <c r="R107" s="222"/>
-      <c r="S107" s="271"/>
+      <c r="B107" s="284"/>
+      <c r="C107" s="285"/>
+      <c r="D107" s="285"/>
+      <c r="E107" s="285"/>
+      <c r="F107" s="285"/>
+      <c r="G107" s="285"/>
+      <c r="H107" s="285"/>
+      <c r="I107" s="285"/>
+      <c r="J107" s="285"/>
+      <c r="K107" s="285"/>
+      <c r="L107" s="285"/>
+      <c r="M107" s="285"/>
+      <c r="N107" s="285"/>
+      <c r="O107" s="285"/>
+      <c r="P107" s="285"/>
+      <c r="Q107" s="285"/>
+      <c r="R107" s="285"/>
+      <c r="S107" s="286"/>
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B108" s="270"/>
-      <c r="C108" s="222"/>
-      <c r="D108" s="222"/>
-      <c r="E108" s="222"/>
-      <c r="F108" s="222"/>
-      <c r="G108" s="222"/>
-      <c r="H108" s="222"/>
-      <c r="I108" s="222"/>
-      <c r="J108" s="222"/>
-      <c r="K108" s="222"/>
-      <c r="L108" s="222"/>
-      <c r="M108" s="222"/>
-      <c r="N108" s="222"/>
-      <c r="O108" s="222"/>
-      <c r="P108" s="222"/>
-      <c r="Q108" s="222"/>
-      <c r="R108" s="222"/>
-      <c r="S108" s="271"/>
+      <c r="B108" s="284"/>
+      <c r="C108" s="285"/>
+      <c r="D108" s="285"/>
+      <c r="E108" s="285"/>
+      <c r="F108" s="285"/>
+      <c r="G108" s="285"/>
+      <c r="H108" s="285"/>
+      <c r="I108" s="285"/>
+      <c r="J108" s="285"/>
+      <c r="K108" s="285"/>
+      <c r="L108" s="285"/>
+      <c r="M108" s="285"/>
+      <c r="N108" s="285"/>
+      <c r="O108" s="285"/>
+      <c r="P108" s="285"/>
+      <c r="Q108" s="285"/>
+      <c r="R108" s="285"/>
+      <c r="S108" s="286"/>
     </row>
     <row r="109" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="272"/>
-      <c r="C109" s="273"/>
-      <c r="D109" s="273"/>
-      <c r="E109" s="273"/>
-      <c r="F109" s="273"/>
-      <c r="G109" s="273"/>
-      <c r="H109" s="273"/>
-      <c r="I109" s="273"/>
-      <c r="J109" s="273"/>
-      <c r="K109" s="273"/>
-      <c r="L109" s="273"/>
-      <c r="M109" s="273"/>
-      <c r="N109" s="273"/>
-      <c r="O109" s="273"/>
-      <c r="P109" s="273"/>
-      <c r="Q109" s="273"/>
-      <c r="R109" s="273"/>
-      <c r="S109" s="274"/>
+      <c r="B109" s="287"/>
+      <c r="C109" s="288"/>
+      <c r="D109" s="288"/>
+      <c r="E109" s="288"/>
+      <c r="F109" s="288"/>
+      <c r="G109" s="288"/>
+      <c r="H109" s="288"/>
+      <c r="I109" s="288"/>
+      <c r="J109" s="288"/>
+      <c r="K109" s="288"/>
+      <c r="L109" s="288"/>
+      <c r="M109" s="288"/>
+      <c r="N109" s="288"/>
+      <c r="O109" s="288"/>
+      <c r="P109" s="288"/>
+      <c r="Q109" s="288"/>
+      <c r="R109" s="288"/>
+      <c r="S109" s="289"/>
     </row>
     <row r="118" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B118" s="275" t="s">
+      <c r="B118" s="290" t="s">
         <v>88</v>
       </c>
-      <c r="C118" s="275"/>
-      <c r="D118" s="275"/>
-      <c r="E118" s="275"/>
-      <c r="F118" s="275"/>
-      <c r="G118" s="275"/>
-      <c r="H118" s="275"/>
-      <c r="I118" s="275"/>
-      <c r="J118" s="275"/>
-      <c r="K118" s="275"/>
-      <c r="L118" s="275"/>
-      <c r="M118" s="275"/>
-      <c r="N118" s="275"/>
-      <c r="O118" s="275"/>
-      <c r="P118" s="275"/>
+      <c r="C118" s="290"/>
+      <c r="D118" s="290"/>
+      <c r="E118" s="290"/>
+      <c r="F118" s="290"/>
+      <c r="G118" s="290"/>
+      <c r="H118" s="290"/>
+      <c r="I118" s="290"/>
+      <c r="J118" s="290"/>
+      <c r="K118" s="290"/>
+      <c r="L118" s="290"/>
+      <c r="M118" s="290"/>
+      <c r="N118" s="290"/>
+      <c r="O118" s="290"/>
+      <c r="P118" s="290"/>
       <c r="Q118" s="129"/>
     </row>
     <row r="119" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B119" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="C119" s="232" t="s">
+      <c r="C119" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D119" s="232"/>
+      <c r="D119" s="220"/>
       <c r="E119" s="120" t="s">
         <v>3</v>
       </c>
@@ -8053,17 +8053,17 @@
       <c r="N119" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="O119" s="232" t="s">
+      <c r="O119" s="220" t="s">
         <v>36</v>
       </c>
-      <c r="P119" s="232"/>
-      <c r="Q119" s="232"/>
+      <c r="P119" s="220"/>
+      <c r="Q119" s="220"/>
     </row>
     <row r="120" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="228" t="s">
+      <c r="B120" s="217" t="s">
         <v>90</v>
       </c>
-      <c r="C120" s="214" t="s">
+      <c r="C120" s="242" t="s">
         <v>16</v>
       </c>
       <c r="D120" s="20" t="s">
@@ -8101,15 +8101,15 @@
       <c r="N120" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="O120" s="229" t="s">
+      <c r="O120" s="249" t="s">
         <v>44</v>
       </c>
-      <c r="P120" s="229"/>
-      <c r="Q120" s="229"/>
+      <c r="P120" s="249"/>
+      <c r="Q120" s="249"/>
     </row>
     <row r="121" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B121" s="228"/>
-      <c r="C121" s="214"/>
+      <c r="B121" s="217"/>
+      <c r="C121" s="242"/>
       <c r="D121" s="20" t="s">
         <v>22</v>
       </c>
@@ -8145,9 +8145,9 @@
       <c r="N121" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="O121" s="229"/>
-      <c r="P121" s="229"/>
-      <c r="Q121" s="229"/>
+      <c r="O121" s="249"/>
+      <c r="P121" s="249"/>
+      <c r="Q121" s="249"/>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B122" s="42"/>
@@ -8188,78 +8188,78 @@
       <c r="Q123" s="7"/>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B124" s="243" t="s">
+      <c r="B124" s="227" t="s">
         <v>33</v>
       </c>
-      <c r="C124" s="263"/>
-      <c r="D124" s="263"/>
-      <c r="E124" s="263"/>
-      <c r="F124" s="263"/>
-      <c r="G124" s="263"/>
-      <c r="H124" s="263"/>
-      <c r="I124" s="263"/>
-      <c r="J124" s="263"/>
-      <c r="K124" s="263"/>
-      <c r="L124" s="263"/>
-      <c r="M124" s="263"/>
-      <c r="N124" s="263"/>
-      <c r="O124" s="263"/>
-      <c r="P124" s="263"/>
-      <c r="Q124" s="264"/>
+      <c r="C124" s="228"/>
+      <c r="D124" s="228"/>
+      <c r="E124" s="228"/>
+      <c r="F124" s="228"/>
+      <c r="G124" s="228"/>
+      <c r="H124" s="228"/>
+      <c r="I124" s="228"/>
+      <c r="J124" s="228"/>
+      <c r="K124" s="228"/>
+      <c r="L124" s="228"/>
+      <c r="M124" s="228"/>
+      <c r="N124" s="228"/>
+      <c r="O124" s="228"/>
+      <c r="P124" s="228"/>
+      <c r="Q124" s="229"/>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B125" s="243"/>
-      <c r="C125" s="263"/>
-      <c r="D125" s="263"/>
-      <c r="E125" s="263"/>
-      <c r="F125" s="263"/>
-      <c r="G125" s="263"/>
-      <c r="H125" s="263"/>
-      <c r="I125" s="263"/>
-      <c r="J125" s="263"/>
-      <c r="K125" s="263"/>
-      <c r="L125" s="263"/>
-      <c r="M125" s="263"/>
-      <c r="N125" s="263"/>
-      <c r="O125" s="263"/>
-      <c r="P125" s="263"/>
-      <c r="Q125" s="264"/>
+      <c r="B125" s="227"/>
+      <c r="C125" s="228"/>
+      <c r="D125" s="228"/>
+      <c r="E125" s="228"/>
+      <c r="F125" s="228"/>
+      <c r="G125" s="228"/>
+      <c r="H125" s="228"/>
+      <c r="I125" s="228"/>
+      <c r="J125" s="228"/>
+      <c r="K125" s="228"/>
+      <c r="L125" s="228"/>
+      <c r="M125" s="228"/>
+      <c r="N125" s="228"/>
+      <c r="O125" s="228"/>
+      <c r="P125" s="228"/>
+      <c r="Q125" s="229"/>
     </row>
     <row r="126" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B126" s="243"/>
-      <c r="C126" s="263"/>
-      <c r="D126" s="263"/>
-      <c r="E126" s="263"/>
-      <c r="F126" s="263"/>
-      <c r="G126" s="263"/>
-      <c r="H126" s="263"/>
-      <c r="I126" s="263"/>
-      <c r="J126" s="263"/>
-      <c r="K126" s="263"/>
-      <c r="L126" s="263"/>
-      <c r="M126" s="263"/>
-      <c r="N126" s="263"/>
-      <c r="O126" s="263"/>
-      <c r="P126" s="263"/>
-      <c r="Q126" s="264"/>
+      <c r="B126" s="227"/>
+      <c r="C126" s="228"/>
+      <c r="D126" s="228"/>
+      <c r="E126" s="228"/>
+      <c r="F126" s="228"/>
+      <c r="G126" s="228"/>
+      <c r="H126" s="228"/>
+      <c r="I126" s="228"/>
+      <c r="J126" s="228"/>
+      <c r="K126" s="228"/>
+      <c r="L126" s="228"/>
+      <c r="M126" s="228"/>
+      <c r="N126" s="228"/>
+      <c r="O126" s="228"/>
+      <c r="P126" s="228"/>
+      <c r="Q126" s="229"/>
     </row>
     <row r="127" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B127" s="244"/>
-      <c r="C127" s="265"/>
-      <c r="D127" s="265"/>
-      <c r="E127" s="265"/>
-      <c r="F127" s="265"/>
-      <c r="G127" s="265"/>
-      <c r="H127" s="265"/>
-      <c r="I127" s="265"/>
-      <c r="J127" s="265"/>
-      <c r="K127" s="265"/>
-      <c r="L127" s="265"/>
-      <c r="M127" s="265"/>
-      <c r="N127" s="265"/>
-      <c r="O127" s="265"/>
-      <c r="P127" s="265"/>
-      <c r="Q127" s="266"/>
+      <c r="B127" s="230"/>
+      <c r="C127" s="231"/>
+      <c r="D127" s="231"/>
+      <c r="E127" s="231"/>
+      <c r="F127" s="231"/>
+      <c r="G127" s="231"/>
+      <c r="H127" s="231"/>
+      <c r="I127" s="231"/>
+      <c r="J127" s="231"/>
+      <c r="K127" s="231"/>
+      <c r="L127" s="231"/>
+      <c r="M127" s="231"/>
+      <c r="N127" s="231"/>
+      <c r="O127" s="231"/>
+      <c r="P127" s="231"/>
+      <c r="Q127" s="232"/>
     </row>
     <row r="128" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B128" s="35"/>
@@ -8281,32 +8281,32 @@
     </row>
     <row r="133" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="134" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B134" s="231" t="s">
+      <c r="B134" s="235" t="s">
         <v>92</v>
       </c>
-      <c r="C134" s="261"/>
-      <c r="D134" s="261"/>
-      <c r="E134" s="261"/>
-      <c r="F134" s="261"/>
-      <c r="G134" s="261"/>
-      <c r="H134" s="261"/>
-      <c r="I134" s="261"/>
-      <c r="J134" s="261"/>
-      <c r="K134" s="261"/>
-      <c r="L134" s="261"/>
-      <c r="M134" s="261"/>
-      <c r="N134" s="261"/>
-      <c r="O134" s="261"/>
-      <c r="P134" s="261"/>
+      <c r="C134" s="236"/>
+      <c r="D134" s="236"/>
+      <c r="E134" s="236"/>
+      <c r="F134" s="236"/>
+      <c r="G134" s="236"/>
+      <c r="H134" s="236"/>
+      <c r="I134" s="236"/>
+      <c r="J134" s="236"/>
+      <c r="K134" s="236"/>
+      <c r="L134" s="236"/>
+      <c r="M134" s="236"/>
+      <c r="N134" s="236"/>
+      <c r="O134" s="236"/>
+      <c r="P134" s="236"/>
     </row>
     <row r="135" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B135" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C135" s="232" t="s">
+      <c r="C135" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D135" s="232"/>
+      <c r="D135" s="220"/>
       <c r="E135" s="120" t="s">
         <v>3</v>
       </c>
@@ -8394,10 +8394,10 @@
       </c>
     </row>
     <row r="137" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B137" s="262" t="s">
+      <c r="B137" s="237" t="s">
         <v>96</v>
       </c>
-      <c r="C137" s="228" t="s">
+      <c r="C137" s="217" t="s">
         <v>29</v>
       </c>
       <c r="D137" s="117" t="s">
@@ -8444,8 +8444,8 @@
       </c>
     </row>
     <row r="138" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B138" s="262"/>
-      <c r="C138" s="228"/>
+      <c r="B138" s="237"/>
+      <c r="C138" s="217"/>
       <c r="D138" s="117" t="s">
         <v>22</v>
       </c>
@@ -8491,32 +8491,32 @@
     </row>
     <row r="140" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="141" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B141" s="231" t="s">
+      <c r="B141" s="235" t="s">
         <v>97</v>
       </c>
-      <c r="C141" s="261"/>
-      <c r="D141" s="261"/>
-      <c r="E141" s="261"/>
-      <c r="F141" s="261"/>
-      <c r="G141" s="261"/>
-      <c r="H141" s="261"/>
-      <c r="I141" s="261"/>
-      <c r="J141" s="261"/>
-      <c r="K141" s="261"/>
-      <c r="L141" s="261"/>
-      <c r="M141" s="261"/>
-      <c r="N141" s="261"/>
-      <c r="O141" s="261"/>
-      <c r="P141" s="261"/>
+      <c r="C141" s="236"/>
+      <c r="D141" s="236"/>
+      <c r="E141" s="236"/>
+      <c r="F141" s="236"/>
+      <c r="G141" s="236"/>
+      <c r="H141" s="236"/>
+      <c r="I141" s="236"/>
+      <c r="J141" s="236"/>
+      <c r="K141" s="236"/>
+      <c r="L141" s="236"/>
+      <c r="M141" s="236"/>
+      <c r="N141" s="236"/>
+      <c r="O141" s="236"/>
+      <c r="P141" s="236"/>
     </row>
     <row r="142" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B142" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C142" s="232" t="s">
+      <c r="C142" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D142" s="232"/>
+      <c r="D142" s="220"/>
       <c r="E142" s="120" t="s">
         <v>3</v>
       </c>
@@ -8555,10 +8555,10 @@
       </c>
     </row>
     <row r="143" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B143" s="228" t="s">
+      <c r="B143" s="217" t="s">
         <v>98</v>
       </c>
-      <c r="C143" s="228" t="s">
+      <c r="C143" s="217" t="s">
         <v>16</v>
       </c>
       <c r="D143" s="117" t="s">
@@ -8604,8 +8604,8 @@
       </c>
     </row>
     <row r="144" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B144" s="228"/>
-      <c r="C144" s="228"/>
+      <c r="B144" s="217"/>
+      <c r="C144" s="217"/>
       <c r="D144" s="117" t="s">
         <v>22</v>
       </c>
@@ -8649,10 +8649,10 @@
       </c>
     </row>
     <row r="145" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B145" s="228" t="s">
+      <c r="B145" s="217" t="s">
         <v>100</v>
       </c>
-      <c r="C145" s="228" t="s">
+      <c r="C145" s="217" t="s">
         <v>29</v>
       </c>
       <c r="D145" s="117" t="s">
@@ -8698,8 +8698,8 @@
       </c>
     </row>
     <row r="146" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B146" s="228"/>
-      <c r="C146" s="228"/>
+      <c r="B146" s="217"/>
+      <c r="C146" s="217"/>
       <c r="D146" s="117" t="s">
         <v>22</v>
       </c>
@@ -8769,78 +8769,78 @@
       <c r="Q148" s="7"/>
     </row>
     <row r="149" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B149" s="243" t="s">
+      <c r="B149" s="227" t="s">
         <v>33</v>
       </c>
-      <c r="C149" s="263"/>
-      <c r="D149" s="263"/>
-      <c r="E149" s="263"/>
-      <c r="F149" s="263"/>
-      <c r="G149" s="263"/>
-      <c r="H149" s="263"/>
-      <c r="I149" s="263"/>
-      <c r="J149" s="263"/>
-      <c r="K149" s="263"/>
-      <c r="L149" s="263"/>
-      <c r="M149" s="263"/>
-      <c r="N149" s="263"/>
-      <c r="O149" s="263"/>
-      <c r="P149" s="263"/>
-      <c r="Q149" s="264"/>
+      <c r="C149" s="228"/>
+      <c r="D149" s="228"/>
+      <c r="E149" s="228"/>
+      <c r="F149" s="228"/>
+      <c r="G149" s="228"/>
+      <c r="H149" s="228"/>
+      <c r="I149" s="228"/>
+      <c r="J149" s="228"/>
+      <c r="K149" s="228"/>
+      <c r="L149" s="228"/>
+      <c r="M149" s="228"/>
+      <c r="N149" s="228"/>
+      <c r="O149" s="228"/>
+      <c r="P149" s="228"/>
+      <c r="Q149" s="229"/>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B150" s="243"/>
-      <c r="C150" s="263"/>
-      <c r="D150" s="263"/>
-      <c r="E150" s="263"/>
-      <c r="F150" s="263"/>
-      <c r="G150" s="263"/>
-      <c r="H150" s="263"/>
-      <c r="I150" s="263"/>
-      <c r="J150" s="263"/>
-      <c r="K150" s="263"/>
-      <c r="L150" s="263"/>
-      <c r="M150" s="263"/>
-      <c r="N150" s="263"/>
-      <c r="O150" s="263"/>
-      <c r="P150" s="263"/>
-      <c r="Q150" s="264"/>
+      <c r="B150" s="227"/>
+      <c r="C150" s="228"/>
+      <c r="D150" s="228"/>
+      <c r="E150" s="228"/>
+      <c r="F150" s="228"/>
+      <c r="G150" s="228"/>
+      <c r="H150" s="228"/>
+      <c r="I150" s="228"/>
+      <c r="J150" s="228"/>
+      <c r="K150" s="228"/>
+      <c r="L150" s="228"/>
+      <c r="M150" s="228"/>
+      <c r="N150" s="228"/>
+      <c r="O150" s="228"/>
+      <c r="P150" s="228"/>
+      <c r="Q150" s="229"/>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B151" s="243"/>
-      <c r="C151" s="263"/>
-      <c r="D151" s="263"/>
-      <c r="E151" s="263"/>
-      <c r="F151" s="263"/>
-      <c r="G151" s="263"/>
-      <c r="H151" s="263"/>
-      <c r="I151" s="263"/>
-      <c r="J151" s="263"/>
-      <c r="K151" s="263"/>
-      <c r="L151" s="263"/>
-      <c r="M151" s="263"/>
-      <c r="N151" s="263"/>
-      <c r="O151" s="263"/>
-      <c r="P151" s="263"/>
-      <c r="Q151" s="264"/>
+      <c r="B151" s="227"/>
+      <c r="C151" s="228"/>
+      <c r="D151" s="228"/>
+      <c r="E151" s="228"/>
+      <c r="F151" s="228"/>
+      <c r="G151" s="228"/>
+      <c r="H151" s="228"/>
+      <c r="I151" s="228"/>
+      <c r="J151" s="228"/>
+      <c r="K151" s="228"/>
+      <c r="L151" s="228"/>
+      <c r="M151" s="228"/>
+      <c r="N151" s="228"/>
+      <c r="O151" s="228"/>
+      <c r="P151" s="228"/>
+      <c r="Q151" s="229"/>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B152" s="244"/>
-      <c r="C152" s="265"/>
-      <c r="D152" s="265"/>
-      <c r="E152" s="265"/>
-      <c r="F152" s="265"/>
-      <c r="G152" s="265"/>
-      <c r="H152" s="265"/>
-      <c r="I152" s="265"/>
-      <c r="J152" s="265"/>
-      <c r="K152" s="265"/>
-      <c r="L152" s="265"/>
-      <c r="M152" s="265"/>
-      <c r="N152" s="265"/>
-      <c r="O152" s="265"/>
-      <c r="P152" s="265"/>
-      <c r="Q152" s="266"/>
+      <c r="B152" s="230"/>
+      <c r="C152" s="231"/>
+      <c r="D152" s="231"/>
+      <c r="E152" s="231"/>
+      <c r="F152" s="231"/>
+      <c r="G152" s="231"/>
+      <c r="H152" s="231"/>
+      <c r="I152" s="231"/>
+      <c r="J152" s="231"/>
+      <c r="K152" s="231"/>
+      <c r="L152" s="231"/>
+      <c r="M152" s="231"/>
+      <c r="N152" s="231"/>
+      <c r="O152" s="231"/>
+      <c r="P152" s="231"/>
+      <c r="Q152" s="232"/>
     </row>
     <row r="154" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B154" s="35"/>
@@ -8861,32 +8861,32 @@
     </row>
     <row r="159" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="160" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B160" s="231" t="s">
+      <c r="B160" s="235" t="s">
         <v>101</v>
       </c>
-      <c r="C160" s="261"/>
-      <c r="D160" s="261"/>
-      <c r="E160" s="261"/>
-      <c r="F160" s="261"/>
-      <c r="G160" s="261"/>
-      <c r="H160" s="261"/>
-      <c r="I160" s="261"/>
-      <c r="J160" s="261"/>
-      <c r="K160" s="261"/>
-      <c r="L160" s="261"/>
-      <c r="M160" s="261"/>
-      <c r="N160" s="261"/>
-      <c r="O160" s="261"/>
-      <c r="P160" s="261"/>
+      <c r="C160" s="236"/>
+      <c r="D160" s="236"/>
+      <c r="E160" s="236"/>
+      <c r="F160" s="236"/>
+      <c r="G160" s="236"/>
+      <c r="H160" s="236"/>
+      <c r="I160" s="236"/>
+      <c r="J160" s="236"/>
+      <c r="K160" s="236"/>
+      <c r="L160" s="236"/>
+      <c r="M160" s="236"/>
+      <c r="N160" s="236"/>
+      <c r="O160" s="236"/>
+      <c r="P160" s="236"/>
     </row>
     <row r="161" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B161" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C161" s="232" t="s">
+      <c r="C161" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D161" s="232"/>
+      <c r="D161" s="220"/>
       <c r="E161" s="120" t="s">
         <v>3</v>
       </c>
@@ -8925,10 +8925,10 @@
       </c>
     </row>
     <row r="162" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B162" s="262" t="s">
+      <c r="B162" s="237" t="s">
         <v>102</v>
       </c>
-      <c r="C162" s="228" t="s">
+      <c r="C162" s="217" t="s">
         <v>103</v>
       </c>
       <c r="D162" s="117" t="s">
@@ -8974,8 +8974,8 @@
       </c>
     </row>
     <row r="163" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B163" s="262"/>
-      <c r="C163" s="228"/>
+      <c r="B163" s="237"/>
+      <c r="C163" s="217"/>
       <c r="D163" s="117" t="s">
         <v>22</v>
       </c>
@@ -9039,78 +9039,78 @@
       <c r="Q165" s="7"/>
     </row>
     <row r="166" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B166" s="243" t="s">
+      <c r="B166" s="227" t="s">
         <v>33</v>
       </c>
-      <c r="C166" s="263"/>
-      <c r="D166" s="263"/>
-      <c r="E166" s="263"/>
-      <c r="F166" s="263"/>
-      <c r="G166" s="263"/>
-      <c r="H166" s="263"/>
-      <c r="I166" s="263"/>
-      <c r="J166" s="263"/>
-      <c r="K166" s="263"/>
-      <c r="L166" s="263"/>
-      <c r="M166" s="263"/>
-      <c r="N166" s="263"/>
-      <c r="O166" s="263"/>
-      <c r="P166" s="263"/>
-      <c r="Q166" s="264"/>
+      <c r="C166" s="228"/>
+      <c r="D166" s="228"/>
+      <c r="E166" s="228"/>
+      <c r="F166" s="228"/>
+      <c r="G166" s="228"/>
+      <c r="H166" s="228"/>
+      <c r="I166" s="228"/>
+      <c r="J166" s="228"/>
+      <c r="K166" s="228"/>
+      <c r="L166" s="228"/>
+      <c r="M166" s="228"/>
+      <c r="N166" s="228"/>
+      <c r="O166" s="228"/>
+      <c r="P166" s="228"/>
+      <c r="Q166" s="229"/>
     </row>
     <row r="167" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B167" s="243"/>
-      <c r="C167" s="263"/>
-      <c r="D167" s="263"/>
-      <c r="E167" s="263"/>
-      <c r="F167" s="263"/>
-      <c r="G167" s="263"/>
-      <c r="H167" s="263"/>
-      <c r="I167" s="263"/>
-      <c r="J167" s="263"/>
-      <c r="K167" s="263"/>
-      <c r="L167" s="263"/>
-      <c r="M167" s="263"/>
-      <c r="N167" s="263"/>
-      <c r="O167" s="263"/>
-      <c r="P167" s="263"/>
-      <c r="Q167" s="264"/>
+      <c r="B167" s="227"/>
+      <c r="C167" s="228"/>
+      <c r="D167" s="228"/>
+      <c r="E167" s="228"/>
+      <c r="F167" s="228"/>
+      <c r="G167" s="228"/>
+      <c r="H167" s="228"/>
+      <c r="I167" s="228"/>
+      <c r="J167" s="228"/>
+      <c r="K167" s="228"/>
+      <c r="L167" s="228"/>
+      <c r="M167" s="228"/>
+      <c r="N167" s="228"/>
+      <c r="O167" s="228"/>
+      <c r="P167" s="228"/>
+      <c r="Q167" s="229"/>
     </row>
     <row r="168" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B168" s="243"/>
-      <c r="C168" s="263"/>
-      <c r="D168" s="263"/>
-      <c r="E168" s="263"/>
-      <c r="F168" s="263"/>
-      <c r="G168" s="263"/>
-      <c r="H168" s="263"/>
-      <c r="I168" s="263"/>
-      <c r="J168" s="263"/>
-      <c r="K168" s="263"/>
-      <c r="L168" s="263"/>
-      <c r="M168" s="263"/>
-      <c r="N168" s="263"/>
-      <c r="O168" s="263"/>
-      <c r="P168" s="263"/>
-      <c r="Q168" s="264"/>
+      <c r="B168" s="227"/>
+      <c r="C168" s="228"/>
+      <c r="D168" s="228"/>
+      <c r="E168" s="228"/>
+      <c r="F168" s="228"/>
+      <c r="G168" s="228"/>
+      <c r="H168" s="228"/>
+      <c r="I168" s="228"/>
+      <c r="J168" s="228"/>
+      <c r="K168" s="228"/>
+      <c r="L168" s="228"/>
+      <c r="M168" s="228"/>
+      <c r="N168" s="228"/>
+      <c r="O168" s="228"/>
+      <c r="P168" s="228"/>
+      <c r="Q168" s="229"/>
     </row>
     <row r="169" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B169" s="244"/>
-      <c r="C169" s="265"/>
-      <c r="D169" s="265"/>
-      <c r="E169" s="265"/>
-      <c r="F169" s="265"/>
-      <c r="G169" s="265"/>
-      <c r="H169" s="265"/>
-      <c r="I169" s="265"/>
-      <c r="J169" s="265"/>
-      <c r="K169" s="265"/>
-      <c r="L169" s="265"/>
-      <c r="M169" s="265"/>
-      <c r="N169" s="265"/>
-      <c r="O169" s="265"/>
-      <c r="P169" s="265"/>
-      <c r="Q169" s="266"/>
+      <c r="B169" s="230"/>
+      <c r="C169" s="231"/>
+      <c r="D169" s="231"/>
+      <c r="E169" s="231"/>
+      <c r="F169" s="231"/>
+      <c r="G169" s="231"/>
+      <c r="H169" s="231"/>
+      <c r="I169" s="231"/>
+      <c r="J169" s="231"/>
+      <c r="K169" s="231"/>
+      <c r="L169" s="231"/>
+      <c r="M169" s="231"/>
+      <c r="N169" s="231"/>
+      <c r="O169" s="231"/>
+      <c r="P169" s="231"/>
+      <c r="Q169" s="232"/>
     </row>
     <row r="170" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B170" s="35"/>
@@ -9149,33 +9149,33 @@
       <c r="Q171" s="35"/>
     </row>
     <row r="173" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B173" s="238" t="s">
+      <c r="B173" s="218" t="s">
         <v>104</v>
       </c>
-      <c r="C173" s="233"/>
-      <c r="D173" s="233"/>
-      <c r="E173" s="233"/>
-      <c r="F173" s="233"/>
-      <c r="G173" s="233"/>
-      <c r="H173" s="233"/>
-      <c r="I173" s="233"/>
-      <c r="J173" s="233"/>
-      <c r="K173" s="233"/>
-      <c r="L173" s="233"/>
-      <c r="M173" s="233"/>
-      <c r="N173" s="233"/>
-      <c r="O173" s="233"/>
-      <c r="P173" s="233"/>
-      <c r="Q173" s="233"/>
+      <c r="C173" s="219"/>
+      <c r="D173" s="219"/>
+      <c r="E173" s="219"/>
+      <c r="F173" s="219"/>
+      <c r="G173" s="219"/>
+      <c r="H173" s="219"/>
+      <c r="I173" s="219"/>
+      <c r="J173" s="219"/>
+      <c r="K173" s="219"/>
+      <c r="L173" s="219"/>
+      <c r="M173" s="219"/>
+      <c r="N173" s="219"/>
+      <c r="O173" s="219"/>
+      <c r="P173" s="219"/>
+      <c r="Q173" s="219"/>
     </row>
     <row r="174" spans="2:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B174" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C174" s="232" t="s">
+      <c r="C174" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D174" s="232"/>
+      <c r="D174" s="220"/>
       <c r="E174" s="120" t="s">
         <v>3</v>
       </c>
@@ -9217,10 +9217,10 @@
       </c>
     </row>
     <row r="175" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B175" s="227" t="s">
+      <c r="B175" s="221" t="s">
         <v>110</v>
       </c>
-      <c r="C175" s="228" t="s">
+      <c r="C175" s="217" t="s">
         <v>29</v>
       </c>
       <c r="D175" s="117" t="s">
@@ -9269,8 +9269,8 @@
       </c>
     </row>
     <row r="176" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B176" s="298"/>
-      <c r="C176" s="228"/>
+      <c r="B176" s="222"/>
+      <c r="C176" s="217"/>
       <c r="D176" s="117" t="s">
         <v>22</v>
       </c>
@@ -9335,32 +9335,32 @@
     </row>
     <row r="185" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="186" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B186" s="231" t="s">
+      <c r="B186" s="235" t="s">
         <v>112</v>
       </c>
-      <c r="C186" s="261"/>
-      <c r="D186" s="261"/>
-      <c r="E186" s="261"/>
-      <c r="F186" s="261"/>
-      <c r="G186" s="261"/>
-      <c r="H186" s="261"/>
-      <c r="I186" s="261"/>
-      <c r="J186" s="261"/>
-      <c r="K186" s="261"/>
-      <c r="L186" s="261"/>
-      <c r="M186" s="261"/>
-      <c r="N186" s="261"/>
-      <c r="O186" s="261"/>
-      <c r="P186" s="261"/>
+      <c r="C186" s="236"/>
+      <c r="D186" s="236"/>
+      <c r="E186" s="236"/>
+      <c r="F186" s="236"/>
+      <c r="G186" s="236"/>
+      <c r="H186" s="236"/>
+      <c r="I186" s="236"/>
+      <c r="J186" s="236"/>
+      <c r="K186" s="236"/>
+      <c r="L186" s="236"/>
+      <c r="M186" s="236"/>
+      <c r="N186" s="236"/>
+      <c r="O186" s="236"/>
+      <c r="P186" s="236"/>
     </row>
     <row r="187" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B187" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C187" s="232" t="s">
+      <c r="C187" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D187" s="232"/>
+      <c r="D187" s="220"/>
       <c r="E187" s="120" t="s">
         <v>3</v>
       </c>
@@ -9399,10 +9399,10 @@
       </c>
     </row>
     <row r="188" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B188" s="262" t="s">
+      <c r="B188" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="C188" s="228" t="s">
+      <c r="C188" s="217" t="s">
         <v>81</v>
       </c>
       <c r="D188" s="117" t="s">
@@ -9448,8 +9448,8 @@
       </c>
     </row>
     <row r="189" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B189" s="262"/>
-      <c r="C189" s="228"/>
+      <c r="B189" s="237"/>
+      <c r="C189" s="217"/>
       <c r="D189" s="117" t="s">
         <v>22</v>
       </c>
@@ -9497,6 +9497,104 @@
     </row>
   </sheetData>
   <mergeCells count="122">
+    <mergeCell ref="B160:P160"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="B166:Q169"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="C145:C146"/>
+    <mergeCell ref="B149:Q152"/>
+    <mergeCell ref="B124:Q127"/>
+    <mergeCell ref="B134:P134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="B141:P141"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="B105:S105"/>
+    <mergeCell ref="B106:S109"/>
+    <mergeCell ref="B118:P118"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="O119:Q119"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="O120:Q121"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="R101:S101"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="R102:S103"/>
+    <mergeCell ref="B96:S96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="R97:S97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="R98:S99"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="R94:S95"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="R89:S89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="R90:S91"/>
+    <mergeCell ref="B100:S100"/>
+    <mergeCell ref="R86:S87"/>
+    <mergeCell ref="B80:S80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="R82:S83"/>
+    <mergeCell ref="B92:S92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="B88:S88"/>
+    <mergeCell ref="B173:Q173"/>
+    <mergeCell ref="R72:S73"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="R64:S65"/>
+    <mergeCell ref="R62:S63"/>
+    <mergeCell ref="R66:S67"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="R68:S71"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B84:S84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="R85:S85"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B24:P27"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="B43:Q46"/>
+    <mergeCell ref="B56:S56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="R58:S61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="R74:S79"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
     <mergeCell ref="B186:P186"/>
     <mergeCell ref="C187:D187"/>
     <mergeCell ref="B188:B189"/>
@@ -9521,104 +9619,6 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B24:P27"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="B43:Q46"/>
-    <mergeCell ref="B56:S56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="R58:S61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="R74:S79"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="B173:Q173"/>
-    <mergeCell ref="R72:S73"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="R64:S65"/>
-    <mergeCell ref="R62:S63"/>
-    <mergeCell ref="R66:S67"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="R68:S71"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="B84:S84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="R85:S85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="R86:S87"/>
-    <mergeCell ref="B80:S80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="R82:S83"/>
-    <mergeCell ref="B92:S92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="B88:S88"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="R94:S95"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="R89:S89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="R90:S91"/>
-    <mergeCell ref="B100:S100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="R101:S101"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="R102:S103"/>
-    <mergeCell ref="B96:S96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="R97:S97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="R98:S99"/>
-    <mergeCell ref="B124:Q127"/>
-    <mergeCell ref="B134:P134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="B141:P141"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="B105:S105"/>
-    <mergeCell ref="B106:S109"/>
-    <mergeCell ref="B118:P118"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="O119:Q119"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="O120:Q121"/>
-    <mergeCell ref="B160:P160"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="B166:Q169"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="C145:C146"/>
-    <mergeCell ref="B149:Q152"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9655,33 +9655,33 @@
   </cols>
   <sheetData>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="233" t="s">
+      <c r="B9" s="219" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="233"/>
-      <c r="D9" s="233"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="233"/>
-      <c r="G9" s="233"/>
-      <c r="H9" s="233"/>
-      <c r="I9" s="233"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="233"/>
-      <c r="L9" s="233"/>
-      <c r="M9" s="233"/>
-      <c r="N9" s="233"/>
-      <c r="O9" s="233"/>
-      <c r="P9" s="233"/>
-      <c r="Q9" s="233"/>
+      <c r="C9" s="219"/>
+      <c r="D9" s="219"/>
+      <c r="E9" s="219"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="219"/>
+      <c r="H9" s="219"/>
+      <c r="I9" s="219"/>
+      <c r="J9" s="219"/>
+      <c r="K9" s="219"/>
+      <c r="L9" s="219"/>
+      <c r="M9" s="219"/>
+      <c r="N9" s="219"/>
+      <c r="O9" s="219"/>
+      <c r="P9" s="219"/>
+      <c r="Q9" s="219"/>
     </row>
     <row r="10" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="234" t="s">
+      <c r="C10" s="306" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="234"/>
+      <c r="D10" s="306"/>
       <c r="E10" s="8" t="s">
         <v>3</v>
       </c>
@@ -9721,10 +9721,10 @@
       <c r="Q10" s="17"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="214" t="s">
+      <c r="B11" s="242" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="214" t="s">
+      <c r="C11" s="242" t="s">
         <v>110</v>
       </c>
       <c r="D11" s="53" t="s">
@@ -9772,8 +9772,8 @@
       <c r="Q11" s="49"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="214"/>
-      <c r="C12" s="214"/>
+      <c r="B12" s="242"/>
+      <c r="C12" s="242"/>
       <c r="D12" s="53" t="s">
         <v>22</v>
       </c>
@@ -9819,10 +9819,10 @@
       <c r="Q12" s="49"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="214" t="s">
+      <c r="B13" s="242" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="214" t="s">
+      <c r="C13" s="242" t="s">
         <v>110</v>
       </c>
       <c r="D13" s="53" t="s">
@@ -9870,8 +9870,8 @@
       <c r="Q13" s="49"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="214"/>
-      <c r="C14" s="214"/>
+      <c r="B14" s="242"/>
+      <c r="C14" s="242"/>
       <c r="D14" s="53" t="s">
         <v>22</v>
       </c>
@@ -9917,10 +9917,10 @@
       <c r="Q14" s="49"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="253" t="s">
+      <c r="B15" s="240" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="214" t="s">
+      <c r="C15" s="242" t="s">
         <v>110</v>
       </c>
       <c r="D15" s="53" t="s">
@@ -9968,8 +9968,8 @@
       <c r="Q15" s="49"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="253"/>
-      <c r="C16" s="214"/>
+      <c r="B16" s="240"/>
+      <c r="C16" s="242"/>
       <c r="D16" s="53" t="s">
         <v>22</v>
       </c>
@@ -10015,10 +10015,10 @@
       <c r="Q16" s="49"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="214" t="s">
+      <c r="B17" s="242" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="214" t="s">
+      <c r="C17" s="242" t="s">
         <v>110</v>
       </c>
       <c r="D17" s="53" t="s">
@@ -10066,8 +10066,8 @@
       <c r="Q17" s="49"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="214"/>
-      <c r="C18" s="214"/>
+      <c r="B18" s="242"/>
+      <c r="C18" s="242"/>
       <c r="D18" s="53" t="s">
         <v>22</v>
       </c>
@@ -10130,103 +10130,103 @@
       <c r="Q19" s="34"/>
     </row>
     <row r="20" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="215" t="s">
+      <c r="B20" s="309" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="216"/>
-      <c r="D20" s="216"/>
-      <c r="E20" s="216"/>
-      <c r="F20" s="216"/>
-      <c r="G20" s="216"/>
-      <c r="H20" s="216"/>
-      <c r="I20" s="216"/>
-      <c r="J20" s="216"/>
-      <c r="K20" s="216"/>
-      <c r="L20" s="216"/>
-      <c r="M20" s="216"/>
-      <c r="N20" s="216"/>
-      <c r="O20" s="216"/>
-      <c r="P20" s="216"/>
-      <c r="Q20" s="216"/>
-      <c r="R20" s="217"/>
+      <c r="C20" s="310"/>
+      <c r="D20" s="310"/>
+      <c r="E20" s="310"/>
+      <c r="F20" s="310"/>
+      <c r="G20" s="310"/>
+      <c r="H20" s="310"/>
+      <c r="I20" s="310"/>
+      <c r="J20" s="310"/>
+      <c r="K20" s="310"/>
+      <c r="L20" s="310"/>
+      <c r="M20" s="310"/>
+      <c r="N20" s="310"/>
+      <c r="O20" s="310"/>
+      <c r="P20" s="310"/>
+      <c r="Q20" s="310"/>
+      <c r="R20" s="311"/>
     </row>
     <row r="21" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="218" t="s">
+      <c r="B21" s="312" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="219"/>
-      <c r="D21" s="219"/>
-      <c r="E21" s="219"/>
-      <c r="F21" s="219"/>
-      <c r="G21" s="219"/>
-      <c r="H21" s="219"/>
-      <c r="I21" s="219"/>
-      <c r="J21" s="219"/>
-      <c r="K21" s="219"/>
-      <c r="L21" s="219"/>
-      <c r="M21" s="219"/>
-      <c r="N21" s="219"/>
-      <c r="O21" s="219"/>
-      <c r="P21" s="219"/>
-      <c r="Q21" s="219"/>
-      <c r="R21" s="220"/>
+      <c r="C21" s="313"/>
+      <c r="D21" s="313"/>
+      <c r="E21" s="313"/>
+      <c r="F21" s="313"/>
+      <c r="G21" s="313"/>
+      <c r="H21" s="313"/>
+      <c r="I21" s="313"/>
+      <c r="J21" s="313"/>
+      <c r="K21" s="313"/>
+      <c r="L21" s="313"/>
+      <c r="M21" s="313"/>
+      <c r="N21" s="313"/>
+      <c r="O21" s="313"/>
+      <c r="P21" s="313"/>
+      <c r="Q21" s="313"/>
+      <c r="R21" s="314"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B22" s="221"/>
-      <c r="C22" s="222"/>
-      <c r="D22" s="222"/>
-      <c r="E22" s="222"/>
-      <c r="F22" s="222"/>
-      <c r="G22" s="222"/>
-      <c r="H22" s="222"/>
-      <c r="I22" s="222"/>
-      <c r="J22" s="222"/>
-      <c r="K22" s="222"/>
-      <c r="L22" s="222"/>
-      <c r="M22" s="222"/>
-      <c r="N22" s="222"/>
-      <c r="O22" s="222"/>
-      <c r="P22" s="222"/>
-      <c r="Q22" s="222"/>
-      <c r="R22" s="223"/>
+      <c r="B22" s="315"/>
+      <c r="C22" s="285"/>
+      <c r="D22" s="285"/>
+      <c r="E22" s="285"/>
+      <c r="F22" s="285"/>
+      <c r="G22" s="285"/>
+      <c r="H22" s="285"/>
+      <c r="I22" s="285"/>
+      <c r="J22" s="285"/>
+      <c r="K22" s="285"/>
+      <c r="L22" s="285"/>
+      <c r="M22" s="285"/>
+      <c r="N22" s="285"/>
+      <c r="O22" s="285"/>
+      <c r="P22" s="285"/>
+      <c r="Q22" s="285"/>
+      <c r="R22" s="316"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B23" s="221"/>
-      <c r="C23" s="222"/>
-      <c r="D23" s="222"/>
-      <c r="E23" s="222"/>
-      <c r="F23" s="222"/>
-      <c r="G23" s="222"/>
-      <c r="H23" s="222"/>
-      <c r="I23" s="222"/>
-      <c r="J23" s="222"/>
-      <c r="K23" s="222"/>
-      <c r="L23" s="222"/>
-      <c r="M23" s="222"/>
-      <c r="N23" s="222"/>
-      <c r="O23" s="222"/>
-      <c r="P23" s="222"/>
-      <c r="Q23" s="222"/>
-      <c r="R23" s="223"/>
+      <c r="B23" s="315"/>
+      <c r="C23" s="285"/>
+      <c r="D23" s="285"/>
+      <c r="E23" s="285"/>
+      <c r="F23" s="285"/>
+      <c r="G23" s="285"/>
+      <c r="H23" s="285"/>
+      <c r="I23" s="285"/>
+      <c r="J23" s="285"/>
+      <c r="K23" s="285"/>
+      <c r="L23" s="285"/>
+      <c r="M23" s="285"/>
+      <c r="N23" s="285"/>
+      <c r="O23" s="285"/>
+      <c r="P23" s="285"/>
+      <c r="Q23" s="285"/>
+      <c r="R23" s="316"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B24" s="224"/>
-      <c r="C24" s="225"/>
-      <c r="D24" s="225"/>
-      <c r="E24" s="225"/>
-      <c r="F24" s="225"/>
-      <c r="G24" s="225"/>
-      <c r="H24" s="225"/>
-      <c r="I24" s="225"/>
-      <c r="J24" s="225"/>
-      <c r="K24" s="225"/>
-      <c r="L24" s="225"/>
-      <c r="M24" s="225"/>
-      <c r="N24" s="225"/>
-      <c r="O24" s="225"/>
-      <c r="P24" s="225"/>
-      <c r="Q24" s="225"/>
-      <c r="R24" s="226"/>
+      <c r="B24" s="317"/>
+      <c r="C24" s="318"/>
+      <c r="D24" s="318"/>
+      <c r="E24" s="318"/>
+      <c r="F24" s="318"/>
+      <c r="G24" s="318"/>
+      <c r="H24" s="318"/>
+      <c r="I24" s="318"/>
+      <c r="J24" s="318"/>
+      <c r="K24" s="318"/>
+      <c r="L24" s="318"/>
+      <c r="M24" s="318"/>
+      <c r="N24" s="318"/>
+      <c r="O24" s="318"/>
+      <c r="P24" s="318"/>
+      <c r="Q24" s="318"/>
+      <c r="R24" s="319"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B25" s="27"/>
@@ -10382,34 +10382,34 @@
       <c r="Q33" s="34"/>
     </row>
     <row r="34" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B34" s="245" t="s">
+      <c r="B34" s="243" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="245"/>
-      <c r="D34" s="245"/>
-      <c r="E34" s="245"/>
-      <c r="F34" s="245"/>
-      <c r="G34" s="245"/>
-      <c r="H34" s="245"/>
-      <c r="I34" s="245"/>
-      <c r="J34" s="245"/>
-      <c r="K34" s="245"/>
-      <c r="L34" s="245"/>
-      <c r="M34" s="245"/>
-      <c r="N34" s="245"/>
-      <c r="O34" s="245"/>
-      <c r="P34" s="245"/>
-      <c r="Q34" s="245"/>
-      <c r="R34" s="245"/>
+      <c r="C34" s="243"/>
+      <c r="D34" s="243"/>
+      <c r="E34" s="243"/>
+      <c r="F34" s="243"/>
+      <c r="G34" s="243"/>
+      <c r="H34" s="243"/>
+      <c r="I34" s="243"/>
+      <c r="J34" s="243"/>
+      <c r="K34" s="243"/>
+      <c r="L34" s="243"/>
+      <c r="M34" s="243"/>
+      <c r="N34" s="243"/>
+      <c r="O34" s="243"/>
+      <c r="P34" s="243"/>
+      <c r="Q34" s="243"/>
+      <c r="R34" s="243"/>
     </row>
     <row r="35" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="234" t="s">
+      <c r="C35" s="306" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="234"/>
+      <c r="D35" s="306"/>
       <c r="E35" s="127" t="s">
         <v>125</v>
       </c>
@@ -10441,17 +10441,17 @@
         <v>14</v>
       </c>
       <c r="O35" s="124"/>
-      <c r="P35" s="232" t="s">
+      <c r="P35" s="220" t="s">
         <v>36</v>
       </c>
-      <c r="Q35" s="232"/>
-      <c r="R35" s="232"/>
+      <c r="Q35" s="220"/>
+      <c r="R35" s="220"/>
     </row>
     <row r="36" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="254" t="s">
+      <c r="B36" s="244" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="214" t="s">
+      <c r="C36" s="242" t="s">
         <v>110</v>
       </c>
       <c r="D36" s="53" t="s">
@@ -10491,15 +10491,15 @@
         <v>91</v>
       </c>
       <c r="O36" s="53"/>
-      <c r="P36" s="255" t="s">
+      <c r="P36" s="245" t="s">
         <v>129</v>
       </c>
-      <c r="Q36" s="256"/>
-      <c r="R36" s="257"/>
+      <c r="Q36" s="301"/>
+      <c r="R36" s="246"/>
     </row>
     <row r="37" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B37" s="254"/>
-      <c r="C37" s="214"/>
+      <c r="B37" s="244"/>
+      <c r="C37" s="242"/>
       <c r="D37" s="53" t="s">
         <v>22</v>
       </c>
@@ -10537,9 +10537,9 @@
         <v>91</v>
       </c>
       <c r="O37" s="53"/>
-      <c r="P37" s="258"/>
-      <c r="Q37" s="259"/>
-      <c r="R37" s="260"/>
+      <c r="P37" s="302"/>
+      <c r="Q37" s="303"/>
+      <c r="R37" s="304"/>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B38" s="123" t="s">
@@ -10584,11 +10584,11 @@
         <v>43</v>
       </c>
       <c r="O38" s="53"/>
-      <c r="P38" s="246" t="s">
+      <c r="P38" s="298" t="s">
         <v>132</v>
       </c>
-      <c r="Q38" s="247"/>
-      <c r="R38" s="248"/>
+      <c r="Q38" s="299"/>
+      <c r="R38" s="300"/>
     </row>
     <row r="39" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="125" t="s">
@@ -10634,11 +10634,11 @@
         <v>91</v>
       </c>
       <c r="O39" s="53"/>
-      <c r="P39" s="246" t="s">
+      <c r="P39" s="298" t="s">
         <v>132</v>
       </c>
-      <c r="Q39" s="247"/>
-      <c r="R39" s="248"/>
+      <c r="Q39" s="299"/>
+      <c r="R39" s="300"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="42"/>
@@ -10681,86 +10681,86 @@
       <c r="S41" s="7"/>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B42" s="243" t="s">
+      <c r="B42" s="227" t="s">
         <v>33</v>
       </c>
-      <c r="C42" s="243"/>
-      <c r="D42" s="243"/>
-      <c r="E42" s="243"/>
-      <c r="F42" s="243"/>
-      <c r="G42" s="243"/>
-      <c r="H42" s="243"/>
-      <c r="I42" s="243"/>
-      <c r="J42" s="243"/>
-      <c r="K42" s="243"/>
-      <c r="L42" s="243"/>
-      <c r="M42" s="243"/>
-      <c r="N42" s="243"/>
-      <c r="O42" s="243"/>
-      <c r="P42" s="243"/>
-      <c r="Q42" s="243"/>
-      <c r="R42" s="243"/>
-      <c r="S42" s="243"/>
+      <c r="C42" s="227"/>
+      <c r="D42" s="227"/>
+      <c r="E42" s="227"/>
+      <c r="F42" s="227"/>
+      <c r="G42" s="227"/>
+      <c r="H42" s="227"/>
+      <c r="I42" s="227"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="227"/>
+      <c r="L42" s="227"/>
+      <c r="M42" s="227"/>
+      <c r="N42" s="227"/>
+      <c r="O42" s="227"/>
+      <c r="P42" s="227"/>
+      <c r="Q42" s="227"/>
+      <c r="R42" s="227"/>
+      <c r="S42" s="227"/>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B43" s="243"/>
-      <c r="C43" s="243"/>
-      <c r="D43" s="243"/>
-      <c r="E43" s="243"/>
-      <c r="F43" s="243"/>
-      <c r="G43" s="243"/>
-      <c r="H43" s="243"/>
-      <c r="I43" s="243"/>
-      <c r="J43" s="243"/>
-      <c r="K43" s="243"/>
-      <c r="L43" s="243"/>
-      <c r="M43" s="243"/>
-      <c r="N43" s="243"/>
-      <c r="O43" s="243"/>
-      <c r="P43" s="243"/>
-      <c r="Q43" s="243"/>
-      <c r="R43" s="243"/>
-      <c r="S43" s="243"/>
+      <c r="B43" s="227"/>
+      <c r="C43" s="227"/>
+      <c r="D43" s="227"/>
+      <c r="E43" s="227"/>
+      <c r="F43" s="227"/>
+      <c r="G43" s="227"/>
+      <c r="H43" s="227"/>
+      <c r="I43" s="227"/>
+      <c r="J43" s="227"/>
+      <c r="K43" s="227"/>
+      <c r="L43" s="227"/>
+      <c r="M43" s="227"/>
+      <c r="N43" s="227"/>
+      <c r="O43" s="227"/>
+      <c r="P43" s="227"/>
+      <c r="Q43" s="227"/>
+      <c r="R43" s="227"/>
+      <c r="S43" s="227"/>
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B44" s="243"/>
-      <c r="C44" s="243"/>
-      <c r="D44" s="243"/>
-      <c r="E44" s="243"/>
-      <c r="F44" s="243"/>
-      <c r="G44" s="243"/>
-      <c r="H44" s="243"/>
-      <c r="I44" s="243"/>
-      <c r="J44" s="243"/>
-      <c r="K44" s="243"/>
-      <c r="L44" s="243"/>
-      <c r="M44" s="243"/>
-      <c r="N44" s="243"/>
-      <c r="O44" s="243"/>
-      <c r="P44" s="243"/>
-      <c r="Q44" s="243"/>
-      <c r="R44" s="243"/>
-      <c r="S44" s="243"/>
+      <c r="B44" s="227"/>
+      <c r="C44" s="227"/>
+      <c r="D44" s="227"/>
+      <c r="E44" s="227"/>
+      <c r="F44" s="227"/>
+      <c r="G44" s="227"/>
+      <c r="H44" s="227"/>
+      <c r="I44" s="227"/>
+      <c r="J44" s="227"/>
+      <c r="K44" s="227"/>
+      <c r="L44" s="227"/>
+      <c r="M44" s="227"/>
+      <c r="N44" s="227"/>
+      <c r="O44" s="227"/>
+      <c r="P44" s="227"/>
+      <c r="Q44" s="227"/>
+      <c r="R44" s="227"/>
+      <c r="S44" s="227"/>
     </row>
     <row r="45" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B45" s="244"/>
-      <c r="C45" s="244"/>
-      <c r="D45" s="244"/>
-      <c r="E45" s="244"/>
-      <c r="F45" s="244"/>
-      <c r="G45" s="244"/>
-      <c r="H45" s="244"/>
-      <c r="I45" s="244"/>
-      <c r="J45" s="244"/>
-      <c r="K45" s="244"/>
-      <c r="L45" s="244"/>
-      <c r="M45" s="244"/>
-      <c r="N45" s="244"/>
-      <c r="O45" s="244"/>
-      <c r="P45" s="244"/>
-      <c r="Q45" s="244"/>
-      <c r="R45" s="244"/>
-      <c r="S45" s="244"/>
+      <c r="B45" s="230"/>
+      <c r="C45" s="230"/>
+      <c r="D45" s="230"/>
+      <c r="E45" s="230"/>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="230"/>
+      <c r="K45" s="230"/>
+      <c r="L45" s="230"/>
+      <c r="M45" s="230"/>
+      <c r="N45" s="230"/>
+      <c r="O45" s="230"/>
+      <c r="P45" s="230"/>
+      <c r="Q45" s="230"/>
+      <c r="R45" s="230"/>
+      <c r="S45" s="230"/>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B46" s="42"/>
@@ -10918,33 +10918,33 @@
       <c r="R54" s="126"/>
     </row>
     <row r="55" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B55" s="231" t="s">
+      <c r="B55" s="235" t="s">
         <v>135</v>
       </c>
-      <c r="C55" s="231"/>
-      <c r="D55" s="231"/>
-      <c r="E55" s="231"/>
-      <c r="F55" s="231"/>
-      <c r="G55" s="231"/>
-      <c r="H55" s="231"/>
-      <c r="I55" s="231"/>
-      <c r="J55" s="231"/>
-      <c r="K55" s="231"/>
-      <c r="L55" s="231"/>
-      <c r="M55" s="231"/>
-      <c r="N55" s="231"/>
-      <c r="O55" s="231"/>
-      <c r="P55" s="231"/>
-      <c r="Q55" s="231"/>
+      <c r="C55" s="235"/>
+      <c r="D55" s="235"/>
+      <c r="E55" s="235"/>
+      <c r="F55" s="235"/>
+      <c r="G55" s="235"/>
+      <c r="H55" s="235"/>
+      <c r="I55" s="235"/>
+      <c r="J55" s="235"/>
+      <c r="K55" s="235"/>
+      <c r="L55" s="235"/>
+      <c r="M55" s="235"/>
+      <c r="N55" s="235"/>
+      <c r="O55" s="235"/>
+      <c r="P55" s="235"/>
+      <c r="Q55" s="235"/>
     </row>
     <row r="56" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B56" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C56" s="232" t="s">
+      <c r="C56" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D56" s="232"/>
+      <c r="D56" s="220"/>
       <c r="E56" s="120" t="s">
         <v>3</v>
       </c>
@@ -10984,10 +10984,10 @@
       <c r="Q56" s="121"/>
     </row>
     <row r="57" spans="2:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="235" t="s">
+      <c r="B57" s="297" t="s">
         <v>139</v>
       </c>
-      <c r="C57" s="236" t="s">
+      <c r="C57" s="305" t="s">
         <v>110</v>
       </c>
       <c r="D57" s="141" t="s">
@@ -11029,14 +11029,14 @@
       <c r="O57" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P57" s="241" t="s">
+      <c r="P57" s="291" t="s">
         <v>73</v>
       </c>
       <c r="Q57" s="141"/>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B58" s="235"/>
-      <c r="C58" s="236"/>
+      <c r="B58" s="297"/>
+      <c r="C58" s="305"/>
       <c r="D58" s="141" t="s">
         <v>22</v>
       </c>
@@ -11076,14 +11076,14 @@
       <c r="O58" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P58" s="242"/>
+      <c r="P58" s="292"/>
       <c r="Q58" s="141"/>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B59" s="235" t="s">
+      <c r="B59" s="297" t="s">
         <v>140</v>
       </c>
-      <c r="C59" s="236" t="s">
+      <c r="C59" s="305" t="s">
         <v>110</v>
       </c>
       <c r="D59" s="141" t="s">
@@ -11125,12 +11125,12 @@
       <c r="O59" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P59" s="242"/>
+      <c r="P59" s="292"/>
       <c r="Q59" s="141"/>
     </row>
     <row r="60" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="235"/>
-      <c r="C60" s="236"/>
+      <c r="B60" s="297"/>
+      <c r="C60" s="305"/>
       <c r="D60" s="141" t="s">
         <v>22</v>
       </c>
@@ -11170,14 +11170,14 @@
       <c r="O60" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P60" s="249"/>
+      <c r="P60" s="293"/>
       <c r="Q60" s="141"/>
     </row>
     <row r="61" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="235" t="s">
+      <c r="B61" s="297" t="s">
         <v>141</v>
       </c>
-      <c r="C61" s="236" t="s">
+      <c r="C61" s="305" t="s">
         <v>110</v>
       </c>
       <c r="D61" s="141" t="s">
@@ -11219,14 +11219,14 @@
       <c r="O61" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P61" s="250" t="s">
+      <c r="P61" s="294" t="s">
         <v>59</v>
       </c>
       <c r="Q61" s="141"/>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B62" s="235"/>
-      <c r="C62" s="236"/>
+      <c r="B62" s="297"/>
+      <c r="C62" s="305"/>
       <c r="D62" s="141" t="s">
         <v>22</v>
       </c>
@@ -11266,14 +11266,14 @@
       <c r="O62" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P62" s="251"/>
+      <c r="P62" s="295"/>
       <c r="Q62" s="141"/>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B63" s="235" t="s">
+      <c r="B63" s="297" t="s">
         <v>143</v>
       </c>
-      <c r="C63" s="236" t="s">
+      <c r="C63" s="305" t="s">
         <v>110</v>
       </c>
       <c r="D63" s="141" t="s">
@@ -11315,12 +11315,12 @@
       <c r="O63" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P63" s="251"/>
+      <c r="P63" s="295"/>
       <c r="Q63" s="141"/>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B64" s="235"/>
-      <c r="C64" s="236"/>
+      <c r="B64" s="297"/>
+      <c r="C64" s="305"/>
       <c r="D64" s="141" t="s">
         <v>22</v>
       </c>
@@ -11360,37 +11360,37 @@
       <c r="O64" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P64" s="252"/>
+      <c r="P64" s="296"/>
       <c r="Q64" s="141"/>
     </row>
     <row r="65" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="237" t="s">
+      <c r="B65" s="215" t="s">
         <v>144</v>
       </c>
-      <c r="C65" s="237"/>
-      <c r="D65" s="238"/>
-      <c r="E65" s="238"/>
-      <c r="F65" s="237"/>
-      <c r="G65" s="238"/>
-      <c r="H65" s="238"/>
-      <c r="I65" s="237"/>
-      <c r="J65" s="238"/>
-      <c r="K65" s="238"/>
-      <c r="L65" s="238"/>
-      <c r="M65" s="237"/>
-      <c r="N65" s="238"/>
-      <c r="O65" s="238"/>
-      <c r="P65" s="238"/>
-      <c r="Q65" s="238"/>
+      <c r="C65" s="215"/>
+      <c r="D65" s="218"/>
+      <c r="E65" s="218"/>
+      <c r="F65" s="215"/>
+      <c r="G65" s="218"/>
+      <c r="H65" s="218"/>
+      <c r="I65" s="215"/>
+      <c r="J65" s="218"/>
+      <c r="K65" s="218"/>
+      <c r="L65" s="218"/>
+      <c r="M65" s="215"/>
+      <c r="N65" s="218"/>
+      <c r="O65" s="218"/>
+      <c r="P65" s="218"/>
+      <c r="Q65" s="218"/>
     </row>
     <row r="66" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B66" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C66" s="232" t="s">
+      <c r="C66" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D66" s="232"/>
+      <c r="D66" s="220"/>
       <c r="E66" s="8" t="s">
         <v>3</v>
       </c>
@@ -11430,7 +11430,7 @@
       <c r="Q66" s="103"/>
     </row>
     <row r="67" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B67" s="239" t="s">
+      <c r="B67" s="277" t="s">
         <v>145</v>
       </c>
       <c r="C67" s="202" t="s">
@@ -11475,7 +11475,7 @@
       <c r="O67" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P67" s="241" t="s">
+      <c r="P67" s="291" t="s">
         <v>73</v>
       </c>
       <c r="Q67" s="147"/>
@@ -42929,7 +42929,7 @@
       </c>
     </row>
     <row r="68" spans="2:62 3072:12198 12789:15082" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="240"/>
+      <c r="B68" s="307"/>
       <c r="C68" s="202" t="s">
         <v>110</v>
       </c>
@@ -42972,7 +42972,7 @@
       <c r="O68" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P68" s="242"/>
+      <c r="P68" s="292"/>
       <c r="Q68" s="147"/>
       <c r="R68" s="170"/>
       <c r="S68" s="163"/>
@@ -54442,33 +54442,33 @@
       <c r="VHB68" s="156"/>
     </row>
     <row r="69" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B69" s="231" t="s">
+      <c r="B69" s="235" t="s">
         <v>146</v>
       </c>
-      <c r="C69" s="231"/>
-      <c r="D69" s="231"/>
-      <c r="E69" s="231"/>
-      <c r="F69" s="231"/>
-      <c r="G69" s="231"/>
-      <c r="H69" s="231"/>
-      <c r="I69" s="231"/>
-      <c r="J69" s="231"/>
-      <c r="K69" s="231"/>
-      <c r="L69" s="231"/>
-      <c r="M69" s="231"/>
-      <c r="N69" s="231"/>
-      <c r="O69" s="231"/>
-      <c r="P69" s="231"/>
-      <c r="Q69" s="231"/>
+      <c r="C69" s="235"/>
+      <c r="D69" s="235"/>
+      <c r="E69" s="235"/>
+      <c r="F69" s="235"/>
+      <c r="G69" s="235"/>
+      <c r="H69" s="235"/>
+      <c r="I69" s="235"/>
+      <c r="J69" s="235"/>
+      <c r="K69" s="235"/>
+      <c r="L69" s="235"/>
+      <c r="M69" s="235"/>
+      <c r="N69" s="235"/>
+      <c r="O69" s="235"/>
+      <c r="P69" s="235"/>
+      <c r="Q69" s="235"/>
     </row>
     <row r="70" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B70" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C70" s="232" t="s">
+      <c r="C70" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D70" s="232"/>
+      <c r="D70" s="220"/>
       <c r="E70" s="8" t="s">
         <v>3</v>
       </c>
@@ -54508,7 +54508,7 @@
       <c r="Q70" s="103"/>
     </row>
     <row r="71" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B71" s="239" t="s">
+      <c r="B71" s="277" t="s">
         <v>147</v>
       </c>
       <c r="C71" s="202" t="s">
@@ -54553,13 +54553,13 @@
       <c r="O71" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P71" s="241" t="s">
+      <c r="P71" s="291" t="s">
         <v>73</v>
       </c>
       <c r="Q71" s="147"/>
     </row>
     <row r="72" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B72" s="240"/>
+      <c r="B72" s="307"/>
       <c r="C72" s="202" t="s">
         <v>110</v>
       </c>
@@ -54602,7 +54602,7 @@
       <c r="O72" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P72" s="242"/>
+      <c r="P72" s="292"/>
       <c r="Q72" s="147"/>
     </row>
     <row r="74" spans="2:62 3072:12198 12789:15082" ht="15.6" x14ac:dyDescent="0.3">
@@ -54629,121 +54629,121 @@
       <c r="T74" s="6"/>
     </row>
     <row r="75" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B75" s="230" t="s">
+      <c r="B75" s="252" t="s">
         <v>33</v>
       </c>
-      <c r="C75" s="230"/>
-      <c r="D75" s="230"/>
-      <c r="E75" s="230"/>
-      <c r="F75" s="230"/>
-      <c r="G75" s="230"/>
-      <c r="H75" s="230"/>
-      <c r="I75" s="230"/>
-      <c r="J75" s="230"/>
-      <c r="K75" s="230"/>
-      <c r="L75" s="230"/>
-      <c r="M75" s="230"/>
-      <c r="N75" s="230"/>
-      <c r="O75" s="230"/>
-      <c r="P75" s="230"/>
-      <c r="Q75" s="230"/>
-      <c r="R75" s="230"/>
-      <c r="S75" s="230"/>
-      <c r="T75" s="230"/>
+      <c r="C75" s="252"/>
+      <c r="D75" s="252"/>
+      <c r="E75" s="252"/>
+      <c r="F75" s="252"/>
+      <c r="G75" s="252"/>
+      <c r="H75" s="252"/>
+      <c r="I75" s="252"/>
+      <c r="J75" s="252"/>
+      <c r="K75" s="252"/>
+      <c r="L75" s="252"/>
+      <c r="M75" s="252"/>
+      <c r="N75" s="252"/>
+      <c r="O75" s="252"/>
+      <c r="P75" s="252"/>
+      <c r="Q75" s="252"/>
+      <c r="R75" s="252"/>
+      <c r="S75" s="252"/>
+      <c r="T75" s="252"/>
     </row>
     <row r="76" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B76" s="230"/>
-      <c r="C76" s="230"/>
-      <c r="D76" s="230"/>
-      <c r="E76" s="230"/>
-      <c r="F76" s="230"/>
-      <c r="G76" s="230"/>
-      <c r="H76" s="230"/>
-      <c r="I76" s="230"/>
-      <c r="J76" s="230"/>
-      <c r="K76" s="230"/>
-      <c r="L76" s="230"/>
-      <c r="M76" s="230"/>
-      <c r="N76" s="230"/>
-      <c r="O76" s="230"/>
-      <c r="P76" s="230"/>
-      <c r="Q76" s="230"/>
-      <c r="R76" s="230"/>
-      <c r="S76" s="230"/>
-      <c r="T76" s="230"/>
+      <c r="B76" s="252"/>
+      <c r="C76" s="252"/>
+      <c r="D76" s="252"/>
+      <c r="E76" s="252"/>
+      <c r="F76" s="252"/>
+      <c r="G76" s="252"/>
+      <c r="H76" s="252"/>
+      <c r="I76" s="252"/>
+      <c r="J76" s="252"/>
+      <c r="K76" s="252"/>
+      <c r="L76" s="252"/>
+      <c r="M76" s="252"/>
+      <c r="N76" s="252"/>
+      <c r="O76" s="252"/>
+      <c r="P76" s="252"/>
+      <c r="Q76" s="252"/>
+      <c r="R76" s="252"/>
+      <c r="S76" s="252"/>
+      <c r="T76" s="252"/>
     </row>
     <row r="77" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B77" s="230"/>
-      <c r="C77" s="230"/>
-      <c r="D77" s="230"/>
-      <c r="E77" s="230"/>
-      <c r="F77" s="230"/>
-      <c r="G77" s="230"/>
-      <c r="H77" s="230"/>
-      <c r="I77" s="230"/>
-      <c r="J77" s="230"/>
-      <c r="K77" s="230"/>
-      <c r="L77" s="230"/>
-      <c r="M77" s="230"/>
-      <c r="N77" s="230"/>
-      <c r="O77" s="230"/>
-      <c r="P77" s="230"/>
-      <c r="Q77" s="230"/>
-      <c r="R77" s="230"/>
-      <c r="S77" s="230"/>
-      <c r="T77" s="230"/>
+      <c r="B77" s="252"/>
+      <c r="C77" s="252"/>
+      <c r="D77" s="252"/>
+      <c r="E77" s="252"/>
+      <c r="F77" s="252"/>
+      <c r="G77" s="252"/>
+      <c r="H77" s="252"/>
+      <c r="I77" s="252"/>
+      <c r="J77" s="252"/>
+      <c r="K77" s="252"/>
+      <c r="L77" s="252"/>
+      <c r="M77" s="252"/>
+      <c r="N77" s="252"/>
+      <c r="O77" s="252"/>
+      <c r="P77" s="252"/>
+      <c r="Q77" s="252"/>
+      <c r="R77" s="252"/>
+      <c r="S77" s="252"/>
+      <c r="T77" s="252"/>
     </row>
     <row r="78" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B78" s="230"/>
-      <c r="C78" s="230"/>
-      <c r="D78" s="230"/>
-      <c r="E78" s="230"/>
-      <c r="F78" s="230"/>
-      <c r="G78" s="230"/>
-      <c r="H78" s="230"/>
-      <c r="I78" s="230"/>
-      <c r="J78" s="230"/>
-      <c r="K78" s="230"/>
-      <c r="L78" s="230"/>
-      <c r="M78" s="230"/>
-      <c r="N78" s="230"/>
-      <c r="O78" s="230"/>
-      <c r="P78" s="230"/>
-      <c r="Q78" s="230"/>
-      <c r="R78" s="230"/>
-      <c r="S78" s="230"/>
-      <c r="T78" s="230"/>
+      <c r="B78" s="252"/>
+      <c r="C78" s="252"/>
+      <c r="D78" s="252"/>
+      <c r="E78" s="252"/>
+      <c r="F78" s="252"/>
+      <c r="G78" s="252"/>
+      <c r="H78" s="252"/>
+      <c r="I78" s="252"/>
+      <c r="J78" s="252"/>
+      <c r="K78" s="252"/>
+      <c r="L78" s="252"/>
+      <c r="M78" s="252"/>
+      <c r="N78" s="252"/>
+      <c r="O78" s="252"/>
+      <c r="P78" s="252"/>
+      <c r="Q78" s="252"/>
+      <c r="R78" s="252"/>
+      <c r="S78" s="252"/>
+      <c r="T78" s="252"/>
     </row>
     <row r="87" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B87" s="233" t="s">
+      <c r="B87" s="219" t="s">
         <v>149</v>
       </c>
-      <c r="C87" s="233"/>
-      <c r="D87" s="233"/>
-      <c r="E87" s="233"/>
-      <c r="F87" s="233"/>
-      <c r="G87" s="233"/>
-      <c r="H87" s="233"/>
-      <c r="I87" s="233"/>
-      <c r="J87" s="233"/>
-      <c r="K87" s="233"/>
-      <c r="L87" s="233"/>
-      <c r="M87" s="233"/>
-      <c r="N87" s="233"/>
-      <c r="O87" s="233"/>
-      <c r="P87" s="233"/>
-      <c r="Q87" s="233"/>
-      <c r="R87" s="233"/>
-      <c r="S87" s="233"/>
+      <c r="C87" s="219"/>
+      <c r="D87" s="219"/>
+      <c r="E87" s="219"/>
+      <c r="F87" s="219"/>
+      <c r="G87" s="219"/>
+      <c r="H87" s="219"/>
+      <c r="I87" s="219"/>
+      <c r="J87" s="219"/>
+      <c r="K87" s="219"/>
+      <c r="L87" s="219"/>
+      <c r="M87" s="219"/>
+      <c r="N87" s="219"/>
+      <c r="O87" s="219"/>
+      <c r="P87" s="219"/>
+      <c r="Q87" s="219"/>
+      <c r="R87" s="219"/>
+      <c r="S87" s="219"/>
     </row>
     <row r="88" spans="2:20" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C88" s="234" t="s">
+      <c r="C88" s="306" t="s">
         <v>2</v>
       </c>
-      <c r="D88" s="234"/>
+      <c r="D88" s="306"/>
       <c r="E88" s="127" t="s">
         <v>125</v>
       </c>
@@ -54778,17 +54778,17 @@
         <v>14</v>
       </c>
       <c r="P88" s="17"/>
-      <c r="Q88" s="232" t="s">
+      <c r="Q88" s="220" t="s">
         <v>36</v>
       </c>
-      <c r="R88" s="232"/>
-      <c r="S88" s="232"/>
+      <c r="R88" s="220"/>
+      <c r="S88" s="220"/>
     </row>
     <row r="89" spans="2:20" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="227" t="s">
+      <c r="B89" s="221" t="s">
         <v>90</v>
       </c>
-      <c r="C89" s="214" t="s">
+      <c r="C89" s="242" t="s">
         <v>110</v>
       </c>
       <c r="D89" s="53" t="s">
@@ -54830,15 +54830,15 @@
         <v>43</v>
       </c>
       <c r="P89" s="53"/>
-      <c r="Q89" s="229" t="s">
+      <c r="Q89" s="249" t="s">
         <v>44</v>
       </c>
-      <c r="R89" s="229"/>
-      <c r="S89" s="229"/>
+      <c r="R89" s="249"/>
+      <c r="S89" s="249"/>
     </row>
     <row r="90" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B90" s="228"/>
-      <c r="C90" s="214"/>
+      <c r="B90" s="217"/>
+      <c r="C90" s="242"/>
       <c r="D90" s="53" t="s">
         <v>22</v>
       </c>
@@ -54878,9 +54878,9 @@
         <v>43</v>
       </c>
       <c r="P90" s="53"/>
-      <c r="Q90" s="229"/>
-      <c r="R90" s="229"/>
-      <c r="S90" s="229"/>
+      <c r="Q90" s="249"/>
+      <c r="R90" s="249"/>
+      <c r="S90" s="249"/>
     </row>
     <row r="92" spans="2:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B92" s="5" t="s">
@@ -54906,120 +54906,120 @@
       <c r="T92" s="6"/>
     </row>
     <row r="93" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B93" s="230" t="s">
+      <c r="B93" s="252" t="s">
         <v>33</v>
       </c>
-      <c r="C93" s="230"/>
-      <c r="D93" s="230"/>
-      <c r="E93" s="230"/>
-      <c r="F93" s="230"/>
-      <c r="G93" s="230"/>
-      <c r="H93" s="230"/>
-      <c r="I93" s="230"/>
-      <c r="J93" s="230"/>
-      <c r="K93" s="230"/>
-      <c r="L93" s="230"/>
-      <c r="M93" s="230"/>
-      <c r="N93" s="230"/>
-      <c r="O93" s="230"/>
-      <c r="P93" s="230"/>
-      <c r="Q93" s="230"/>
-      <c r="R93" s="230"/>
-      <c r="S93" s="230"/>
-      <c r="T93" s="230"/>
+      <c r="C93" s="252"/>
+      <c r="D93" s="252"/>
+      <c r="E93" s="252"/>
+      <c r="F93" s="252"/>
+      <c r="G93" s="252"/>
+      <c r="H93" s="252"/>
+      <c r="I93" s="252"/>
+      <c r="J93" s="252"/>
+      <c r="K93" s="252"/>
+      <c r="L93" s="252"/>
+      <c r="M93" s="252"/>
+      <c r="N93" s="252"/>
+      <c r="O93" s="252"/>
+      <c r="P93" s="252"/>
+      <c r="Q93" s="252"/>
+      <c r="R93" s="252"/>
+      <c r="S93" s="252"/>
+      <c r="T93" s="252"/>
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B94" s="230"/>
-      <c r="C94" s="230"/>
-      <c r="D94" s="230"/>
-      <c r="E94" s="230"/>
-      <c r="F94" s="230"/>
-      <c r="G94" s="230"/>
-      <c r="H94" s="230"/>
-      <c r="I94" s="230"/>
-      <c r="J94" s="230"/>
-      <c r="K94" s="230"/>
-      <c r="L94" s="230"/>
-      <c r="M94" s="230"/>
-      <c r="N94" s="230"/>
-      <c r="O94" s="230"/>
-      <c r="P94" s="230"/>
-      <c r="Q94" s="230"/>
-      <c r="R94" s="230"/>
-      <c r="S94" s="230"/>
-      <c r="T94" s="230"/>
+      <c r="B94" s="252"/>
+      <c r="C94" s="252"/>
+      <c r="D94" s="252"/>
+      <c r="E94" s="252"/>
+      <c r="F94" s="252"/>
+      <c r="G94" s="252"/>
+      <c r="H94" s="252"/>
+      <c r="I94" s="252"/>
+      <c r="J94" s="252"/>
+      <c r="K94" s="252"/>
+      <c r="L94" s="252"/>
+      <c r="M94" s="252"/>
+      <c r="N94" s="252"/>
+      <c r="O94" s="252"/>
+      <c r="P94" s="252"/>
+      <c r="Q94" s="252"/>
+      <c r="R94" s="252"/>
+      <c r="S94" s="252"/>
+      <c r="T94" s="252"/>
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B95" s="230"/>
-      <c r="C95" s="230"/>
-      <c r="D95" s="230"/>
-      <c r="E95" s="230"/>
-      <c r="F95" s="230"/>
-      <c r="G95" s="230"/>
-      <c r="H95" s="230"/>
-      <c r="I95" s="230"/>
-      <c r="J95" s="230"/>
-      <c r="K95" s="230"/>
-      <c r="L95" s="230"/>
-      <c r="M95" s="230"/>
-      <c r="N95" s="230"/>
-      <c r="O95" s="230"/>
-      <c r="P95" s="230"/>
-      <c r="Q95" s="230"/>
-      <c r="R95" s="230"/>
-      <c r="S95" s="230"/>
-      <c r="T95" s="230"/>
+      <c r="B95" s="252"/>
+      <c r="C95" s="252"/>
+      <c r="D95" s="252"/>
+      <c r="E95" s="252"/>
+      <c r="F95" s="252"/>
+      <c r="G95" s="252"/>
+      <c r="H95" s="252"/>
+      <c r="I95" s="252"/>
+      <c r="J95" s="252"/>
+      <c r="K95" s="252"/>
+      <c r="L95" s="252"/>
+      <c r="M95" s="252"/>
+      <c r="N95" s="252"/>
+      <c r="O95" s="252"/>
+      <c r="P95" s="252"/>
+      <c r="Q95" s="252"/>
+      <c r="R95" s="252"/>
+      <c r="S95" s="252"/>
+      <c r="T95" s="252"/>
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B96" s="230"/>
-      <c r="C96" s="230"/>
-      <c r="D96" s="230"/>
-      <c r="E96" s="230"/>
-      <c r="F96" s="230"/>
-      <c r="G96" s="230"/>
-      <c r="H96" s="230"/>
-      <c r="I96" s="230"/>
-      <c r="J96" s="230"/>
-      <c r="K96" s="230"/>
-      <c r="L96" s="230"/>
-      <c r="M96" s="230"/>
-      <c r="N96" s="230"/>
-      <c r="O96" s="230"/>
-      <c r="P96" s="230"/>
-      <c r="Q96" s="230"/>
-      <c r="R96" s="230"/>
-      <c r="S96" s="230"/>
-      <c r="T96" s="230"/>
+      <c r="B96" s="252"/>
+      <c r="C96" s="252"/>
+      <c r="D96" s="252"/>
+      <c r="E96" s="252"/>
+      <c r="F96" s="252"/>
+      <c r="G96" s="252"/>
+      <c r="H96" s="252"/>
+      <c r="I96" s="252"/>
+      <c r="J96" s="252"/>
+      <c r="K96" s="252"/>
+      <c r="L96" s="252"/>
+      <c r="M96" s="252"/>
+      <c r="N96" s="252"/>
+      <c r="O96" s="252"/>
+      <c r="P96" s="252"/>
+      <c r="Q96" s="252"/>
+      <c r="R96" s="252"/>
+      <c r="S96" s="252"/>
+      <c r="T96" s="252"/>
     </row>
     <row r="106" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="107" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B107" s="231" t="s">
+      <c r="B107" s="235" t="s">
         <v>153</v>
       </c>
-      <c r="C107" s="231"/>
-      <c r="D107" s="231"/>
-      <c r="E107" s="231"/>
-      <c r="F107" s="231"/>
-      <c r="G107" s="231"/>
-      <c r="H107" s="231"/>
-      <c r="I107" s="231"/>
-      <c r="J107" s="231"/>
-      <c r="K107" s="231"/>
-      <c r="L107" s="231"/>
-      <c r="M107" s="231"/>
-      <c r="N107" s="231"/>
-      <c r="O107" s="231"/>
-      <c r="P107" s="231"/>
-      <c r="Q107" s="231"/>
+      <c r="C107" s="235"/>
+      <c r="D107" s="235"/>
+      <c r="E107" s="235"/>
+      <c r="F107" s="235"/>
+      <c r="G107" s="235"/>
+      <c r="H107" s="235"/>
+      <c r="I107" s="235"/>
+      <c r="J107" s="235"/>
+      <c r="K107" s="235"/>
+      <c r="L107" s="235"/>
+      <c r="M107" s="235"/>
+      <c r="N107" s="235"/>
+      <c r="O107" s="235"/>
+      <c r="P107" s="235"/>
+      <c r="Q107" s="235"/>
     </row>
     <row r="108" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B108" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C108" s="232" t="s">
+      <c r="C108" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D108" s="232"/>
+      <c r="D108" s="220"/>
       <c r="E108" s="8" t="s">
         <v>3</v>
       </c>
@@ -55059,10 +55059,10 @@
       <c r="Q108" s="103"/>
     </row>
     <row r="109" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B109" s="213" t="s">
+      <c r="B109" s="308" t="s">
         <v>154</v>
       </c>
-      <c r="C109" s="214" t="s">
+      <c r="C109" s="242" t="s">
         <v>110</v>
       </c>
       <c r="D109" s="53" t="s">
@@ -55109,8 +55109,8 @@
       <c r="Q109" s="104"/>
     </row>
     <row r="110" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B110" s="213"/>
-      <c r="C110" s="214"/>
+      <c r="B110" s="308"/>
+      <c r="C110" s="242"/>
       <c r="D110" s="53" t="s">
         <v>22</v>
       </c>
@@ -55156,33 +55156,33 @@
     </row>
     <row r="119" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="120" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B120" s="231" t="s">
+      <c r="B120" s="235" t="s">
         <v>158</v>
       </c>
-      <c r="C120" s="231"/>
-      <c r="D120" s="231"/>
-      <c r="E120" s="231"/>
-      <c r="F120" s="231"/>
-      <c r="G120" s="231"/>
-      <c r="H120" s="231"/>
-      <c r="I120" s="231"/>
-      <c r="J120" s="231"/>
-      <c r="K120" s="231"/>
-      <c r="L120" s="231"/>
-      <c r="M120" s="231"/>
-      <c r="N120" s="231"/>
-      <c r="O120" s="231"/>
-      <c r="P120" s="231"/>
-      <c r="Q120" s="231"/>
+      <c r="C120" s="235"/>
+      <c r="D120" s="235"/>
+      <c r="E120" s="235"/>
+      <c r="F120" s="235"/>
+      <c r="G120" s="235"/>
+      <c r="H120" s="235"/>
+      <c r="I120" s="235"/>
+      <c r="J120" s="235"/>
+      <c r="K120" s="235"/>
+      <c r="L120" s="235"/>
+      <c r="M120" s="235"/>
+      <c r="N120" s="235"/>
+      <c r="O120" s="235"/>
+      <c r="P120" s="235"/>
+      <c r="Q120" s="235"/>
     </row>
     <row r="121" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B121" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C121" s="232" t="s">
+      <c r="C121" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D121" s="232"/>
+      <c r="D121" s="220"/>
       <c r="E121" s="8" t="s">
         <v>3</v>
       </c>
@@ -55222,10 +55222,10 @@
       <c r="Q121" s="103"/>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B122" s="213" t="s">
+      <c r="B122" s="308" t="s">
         <v>159</v>
       </c>
-      <c r="C122" s="214" t="s">
+      <c r="C122" s="242" t="s">
         <v>110</v>
       </c>
       <c r="D122" s="53" t="s">
@@ -55272,10 +55272,10 @@
       <c r="Q122" s="196"/>
     </row>
     <row r="123" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B123" s="213" t="s">
+      <c r="B123" s="308" t="s">
         <v>159</v>
       </c>
-      <c r="C123" s="214" t="s">
+      <c r="C123" s="242" t="s">
         <v>110</v>
       </c>
       <c r="D123" s="53" t="s">
@@ -55322,10 +55322,10 @@
       <c r="Q123" s="196"/>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B124" s="213" t="s">
+      <c r="B124" s="308" t="s">
         <v>160</v>
       </c>
-      <c r="C124" s="214" t="s">
+      <c r="C124" s="242" t="s">
         <v>110</v>
       </c>
       <c r="D124" s="53" t="s">
@@ -55373,8 +55373,8 @@
       <c r="Q124" s="196"/>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B125" s="213"/>
-      <c r="C125" s="214"/>
+      <c r="B125" s="308"/>
+      <c r="C125" s="242"/>
       <c r="D125" s="53" t="s">
         <v>22</v>
       </c>
@@ -55421,19 +55421,36 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="P57:P60"/>
-    <mergeCell ref="P61:P64"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="P39:R39"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="P36:R37"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="B20:R20"/>
+    <mergeCell ref="B21:R24"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="Q89:S90"/>
+    <mergeCell ref="B93:T96"/>
+    <mergeCell ref="B107:Q107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B120:Q120"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="Q88:S88"/>
+    <mergeCell ref="B87:S87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="B65:Q65"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="B75:T78"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B69:Q69"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="P67:P68"/>
+    <mergeCell ref="P71:P72"/>
     <mergeCell ref="B9:Q9"/>
     <mergeCell ref="C61:C62"/>
     <mergeCell ref="B13:B14"/>
@@ -55450,36 +55467,19 @@
     <mergeCell ref="B59:B60"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="Q88:S88"/>
-    <mergeCell ref="B87:S87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="B65:Q65"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="B75:T78"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="B69:Q69"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="P67:P68"/>
-    <mergeCell ref="P71:P72"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="B20:R20"/>
-    <mergeCell ref="B21:R24"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="Q89:S90"/>
-    <mergeCell ref="B93:T96"/>
-    <mergeCell ref="B107:Q107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B120:Q120"/>
-    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="P57:P60"/>
+    <mergeCell ref="P61:P64"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="P36:R37"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55516,8 +55516,8 @@
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B8" s="126"/>
       <c r="C8" s="126"/>
-      <c r="D8" s="320"/>
-      <c r="E8" s="320"/>
+      <c r="D8" s="322"/>
+      <c r="E8" s="322"/>
       <c r="F8" s="126"/>
       <c r="G8" s="126"/>
       <c r="H8" s="126"/>
@@ -55533,32 +55533,32 @@
       <c r="R8" s="126"/>
     </row>
     <row r="9" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="323" t="s">
+      <c r="B9" s="331" t="s">
         <v>161</v>
       </c>
-      <c r="C9" s="323"/>
-      <c r="D9" s="323"/>
-      <c r="E9" s="323"/>
-      <c r="F9" s="323"/>
-      <c r="G9" s="323"/>
-      <c r="H9" s="323"/>
-      <c r="I9" s="323"/>
-      <c r="J9" s="323"/>
-      <c r="K9" s="323"/>
-      <c r="L9" s="323"/>
-      <c r="M9" s="323"/>
-      <c r="N9" s="323"/>
-      <c r="O9" s="323"/>
-      <c r="P9" s="323"/>
+      <c r="C9" s="331"/>
+      <c r="D9" s="331"/>
+      <c r="E9" s="331"/>
+      <c r="F9" s="331"/>
+      <c r="G9" s="331"/>
+      <c r="H9" s="331"/>
+      <c r="I9" s="331"/>
+      <c r="J9" s="331"/>
+      <c r="K9" s="331"/>
+      <c r="L9" s="331"/>
+      <c r="M9" s="331"/>
+      <c r="N9" s="331"/>
+      <c r="O9" s="331"/>
+      <c r="P9" s="331"/>
     </row>
     <row r="10" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="321" t="s">
+      <c r="C10" s="340" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="322"/>
+      <c r="D10" s="341"/>
       <c r="E10" s="12" t="s">
         <v>3</v>
       </c>
@@ -55598,10 +55598,10 @@
       <c r="Q10" s="126"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B11" s="312" t="s">
+      <c r="B11" s="342" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="312" t="s">
+      <c r="C11" s="342" t="s">
         <v>165</v>
       </c>
       <c r="D11" s="41" t="s">
@@ -55649,8 +55649,8 @@
       <c r="Q11" s="126"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="313"/>
-      <c r="C12" s="313"/>
+      <c r="B12" s="343"/>
+      <c r="C12" s="343"/>
       <c r="D12" s="41" t="s">
         <v>22</v>
       </c>
@@ -55696,10 +55696,10 @@
       <c r="Q12" s="126"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="312" t="s">
+      <c r="B13" s="342" t="s">
         <v>167</v>
       </c>
-      <c r="C13" s="312" t="s">
+      <c r="C13" s="342" t="s">
         <v>165</v>
       </c>
       <c r="D13" s="41" t="s">
@@ -55747,8 +55747,8 @@
       <c r="Q13" s="126"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B14" s="313"/>
-      <c r="C14" s="313"/>
+      <c r="B14" s="343"/>
+      <c r="C14" s="343"/>
       <c r="D14" s="41" t="s">
         <v>22</v>
       </c>
@@ -55794,10 +55794,10 @@
       <c r="Q14" s="126"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="312" t="s">
+      <c r="B15" s="342" t="s">
         <v>122</v>
       </c>
-      <c r="C15" s="312" t="s">
+      <c r="C15" s="342" t="s">
         <v>165</v>
       </c>
       <c r="D15" s="41" t="s">
@@ -55845,8 +55845,8 @@
       <c r="Q15" s="126"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B16" s="313"/>
-      <c r="C16" s="313"/>
+      <c r="B16" s="343"/>
+      <c r="C16" s="343"/>
       <c r="D16" s="41" t="s">
         <v>22</v>
       </c>
@@ -55906,93 +55906,93 @@
       <c r="N17" s="34"/>
     </row>
     <row r="18" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="317" t="s">
+      <c r="B18" s="346" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="318"/>
-      <c r="D18" s="318"/>
-      <c r="E18" s="318"/>
-      <c r="F18" s="318"/>
-      <c r="G18" s="318"/>
-      <c r="H18" s="318"/>
-      <c r="I18" s="318"/>
-      <c r="J18" s="318"/>
-      <c r="K18" s="318"/>
-      <c r="L18" s="318"/>
-      <c r="M18" s="318"/>
-      <c r="N18" s="318"/>
-      <c r="O18" s="318"/>
-      <c r="P18" s="319"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
+      <c r="G18" s="347"/>
+      <c r="H18" s="347"/>
+      <c r="I18" s="347"/>
+      <c r="J18" s="347"/>
+      <c r="K18" s="347"/>
+      <c r="L18" s="347"/>
+      <c r="M18" s="347"/>
+      <c r="N18" s="347"/>
+      <c r="O18" s="347"/>
+      <c r="P18" s="348"/>
     </row>
     <row r="19" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="218" t="s">
+      <c r="B19" s="312" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="219"/>
-      <c r="D19" s="219"/>
-      <c r="E19" s="219"/>
-      <c r="F19" s="219"/>
-      <c r="G19" s="219"/>
-      <c r="H19" s="219"/>
-      <c r="I19" s="219"/>
-      <c r="J19" s="219"/>
-      <c r="K19" s="219"/>
-      <c r="L19" s="219"/>
-      <c r="M19" s="219"/>
-      <c r="N19" s="219"/>
-      <c r="O19" s="219"/>
-      <c r="P19" s="220"/>
+      <c r="C19" s="313"/>
+      <c r="D19" s="313"/>
+      <c r="E19" s="313"/>
+      <c r="F19" s="313"/>
+      <c r="G19" s="313"/>
+      <c r="H19" s="313"/>
+      <c r="I19" s="313"/>
+      <c r="J19" s="313"/>
+      <c r="K19" s="313"/>
+      <c r="L19" s="313"/>
+      <c r="M19" s="313"/>
+      <c r="N19" s="313"/>
+      <c r="O19" s="313"/>
+      <c r="P19" s="314"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="221"/>
-      <c r="C20" s="222"/>
-      <c r="D20" s="222"/>
-      <c r="E20" s="222"/>
-      <c r="F20" s="222"/>
-      <c r="G20" s="222"/>
-      <c r="H20" s="222"/>
-      <c r="I20" s="222"/>
-      <c r="J20" s="222"/>
-      <c r="K20" s="222"/>
-      <c r="L20" s="222"/>
-      <c r="M20" s="222"/>
-      <c r="N20" s="222"/>
-      <c r="O20" s="222"/>
-      <c r="P20" s="223"/>
+      <c r="B20" s="315"/>
+      <c r="C20" s="285"/>
+      <c r="D20" s="285"/>
+      <c r="E20" s="285"/>
+      <c r="F20" s="285"/>
+      <c r="G20" s="285"/>
+      <c r="H20" s="285"/>
+      <c r="I20" s="285"/>
+      <c r="J20" s="285"/>
+      <c r="K20" s="285"/>
+      <c r="L20" s="285"/>
+      <c r="M20" s="285"/>
+      <c r="N20" s="285"/>
+      <c r="O20" s="285"/>
+      <c r="P20" s="316"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="221"/>
-      <c r="C21" s="222"/>
-      <c r="D21" s="222"/>
-      <c r="E21" s="222"/>
-      <c r="F21" s="222"/>
-      <c r="G21" s="222"/>
-      <c r="H21" s="222"/>
-      <c r="I21" s="222"/>
-      <c r="J21" s="222"/>
-      <c r="K21" s="222"/>
-      <c r="L21" s="222"/>
-      <c r="M21" s="222"/>
-      <c r="N21" s="222"/>
-      <c r="O21" s="222"/>
-      <c r="P21" s="223"/>
+      <c r="B21" s="315"/>
+      <c r="C21" s="285"/>
+      <c r="D21" s="285"/>
+      <c r="E21" s="285"/>
+      <c r="F21" s="285"/>
+      <c r="G21" s="285"/>
+      <c r="H21" s="285"/>
+      <c r="I21" s="285"/>
+      <c r="J21" s="285"/>
+      <c r="K21" s="285"/>
+      <c r="L21" s="285"/>
+      <c r="M21" s="285"/>
+      <c r="N21" s="285"/>
+      <c r="O21" s="285"/>
+      <c r="P21" s="316"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="224"/>
-      <c r="C22" s="225"/>
-      <c r="D22" s="225"/>
-      <c r="E22" s="225"/>
-      <c r="F22" s="225"/>
-      <c r="G22" s="225"/>
-      <c r="H22" s="225"/>
-      <c r="I22" s="225"/>
-      <c r="J22" s="225"/>
-      <c r="K22" s="225"/>
-      <c r="L22" s="225"/>
-      <c r="M22" s="225"/>
-      <c r="N22" s="225"/>
-      <c r="O22" s="225"/>
-      <c r="P22" s="226"/>
+      <c r="B22" s="317"/>
+      <c r="C22" s="318"/>
+      <c r="D22" s="318"/>
+      <c r="E22" s="318"/>
+      <c r="F22" s="318"/>
+      <c r="G22" s="318"/>
+      <c r="H22" s="318"/>
+      <c r="I22" s="318"/>
+      <c r="J22" s="318"/>
+      <c r="K22" s="318"/>
+      <c r="L22" s="318"/>
+      <c r="M22" s="318"/>
+      <c r="N22" s="318"/>
+      <c r="O22" s="318"/>
+      <c r="P22" s="319"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="27"/>
@@ -56122,33 +56122,33 @@
       <c r="N31" s="34"/>
     </row>
     <row r="32" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="314" t="s">
+      <c r="B32" s="344" t="s">
         <v>169</v>
       </c>
-      <c r="C32" s="315"/>
-      <c r="D32" s="315"/>
-      <c r="E32" s="315"/>
-      <c r="F32" s="315"/>
-      <c r="G32" s="315"/>
-      <c r="H32" s="315"/>
-      <c r="I32" s="315"/>
-      <c r="J32" s="315"/>
-      <c r="K32" s="315"/>
-      <c r="L32" s="315"/>
-      <c r="M32" s="315"/>
-      <c r="N32" s="315"/>
-      <c r="O32" s="315"/>
-      <c r="P32" s="315"/>
-      <c r="Q32" s="316"/>
+      <c r="C32" s="325"/>
+      <c r="D32" s="325"/>
+      <c r="E32" s="325"/>
+      <c r="F32" s="325"/>
+      <c r="G32" s="325"/>
+      <c r="H32" s="325"/>
+      <c r="I32" s="325"/>
+      <c r="J32" s="325"/>
+      <c r="K32" s="325"/>
+      <c r="L32" s="325"/>
+      <c r="M32" s="325"/>
+      <c r="N32" s="325"/>
+      <c r="O32" s="325"/>
+      <c r="P32" s="325"/>
+      <c r="Q32" s="345"/>
     </row>
     <row r="33" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B33" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="324" t="s">
+      <c r="C33" s="349" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="324"/>
+      <c r="D33" s="349"/>
       <c r="E33" s="127" t="s">
         <v>125</v>
       </c>
@@ -56182,16 +56182,16 @@
       <c r="O33" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="P33" s="276" t="s">
+      <c r="P33" s="273" t="s">
         <v>36</v>
       </c>
-      <c r="Q33" s="277"/>
+      <c r="Q33" s="274"/>
     </row>
     <row r="34" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="329" t="s">
+      <c r="B34" s="338" t="s">
         <v>173</v>
       </c>
-      <c r="C34" s="330" t="s">
+      <c r="C34" s="339" t="s">
         <v>165</v>
       </c>
       <c r="D34" s="40" t="s">
@@ -56232,14 +56232,14 @@
       <c r="O34" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P34" s="255" t="s">
+      <c r="P34" s="245" t="s">
         <v>174</v>
       </c>
-      <c r="Q34" s="257"/>
+      <c r="Q34" s="246"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B35" s="329"/>
-      <c r="C35" s="330"/>
+      <c r="B35" s="338"/>
+      <c r="C35" s="339"/>
       <c r="D35" s="40" t="s">
         <v>22</v>
       </c>
@@ -56278,8 +56278,8 @@
       <c r="O35" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P35" s="258"/>
-      <c r="Q35" s="260"/>
+      <c r="P35" s="302"/>
+      <c r="Q35" s="304"/>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B36" s="119" t="s">
@@ -56326,8 +56326,8 @@
       <c r="O36" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P36" s="299"/>
-      <c r="Q36" s="300"/>
+      <c r="P36" s="247"/>
+      <c r="Q36" s="248"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B37" s="72"/>
@@ -56380,74 +56380,74 @@
       <c r="P39" s="7"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B40" s="243" t="s">
+      <c r="B40" s="227" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="263"/>
-      <c r="D40" s="263"/>
-      <c r="E40" s="263"/>
-      <c r="F40" s="263"/>
-      <c r="G40" s="263"/>
-      <c r="H40" s="263"/>
-      <c r="I40" s="263"/>
-      <c r="J40" s="263"/>
-      <c r="K40" s="263"/>
-      <c r="L40" s="263"/>
-      <c r="M40" s="263"/>
-      <c r="N40" s="263"/>
-      <c r="O40" s="263"/>
-      <c r="P40" s="264"/>
+      <c r="C40" s="228"/>
+      <c r="D40" s="228"/>
+      <c r="E40" s="228"/>
+      <c r="F40" s="228"/>
+      <c r="G40" s="228"/>
+      <c r="H40" s="228"/>
+      <c r="I40" s="228"/>
+      <c r="J40" s="228"/>
+      <c r="K40" s="228"/>
+      <c r="L40" s="228"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="228"/>
+      <c r="O40" s="228"/>
+      <c r="P40" s="229"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B41" s="243"/>
-      <c r="C41" s="263"/>
-      <c r="D41" s="263"/>
-      <c r="E41" s="263"/>
-      <c r="F41" s="263"/>
-      <c r="G41" s="263"/>
-      <c r="H41" s="263"/>
-      <c r="I41" s="263"/>
-      <c r="J41" s="263"/>
-      <c r="K41" s="263"/>
-      <c r="L41" s="263"/>
-      <c r="M41" s="263"/>
-      <c r="N41" s="263"/>
-      <c r="O41" s="263"/>
-      <c r="P41" s="264"/>
+      <c r="B41" s="227"/>
+      <c r="C41" s="228"/>
+      <c r="D41" s="228"/>
+      <c r="E41" s="228"/>
+      <c r="F41" s="228"/>
+      <c r="G41" s="228"/>
+      <c r="H41" s="228"/>
+      <c r="I41" s="228"/>
+      <c r="J41" s="228"/>
+      <c r="K41" s="228"/>
+      <c r="L41" s="228"/>
+      <c r="M41" s="228"/>
+      <c r="N41" s="228"/>
+      <c r="O41" s="228"/>
+      <c r="P41" s="229"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B42" s="243"/>
-      <c r="C42" s="263"/>
-      <c r="D42" s="263"/>
-      <c r="E42" s="263"/>
-      <c r="F42" s="263"/>
-      <c r="G42" s="263"/>
-      <c r="H42" s="263"/>
-      <c r="I42" s="263"/>
-      <c r="J42" s="263"/>
-      <c r="K42" s="263"/>
-      <c r="L42" s="263"/>
-      <c r="M42" s="263"/>
-      <c r="N42" s="263"/>
-      <c r="O42" s="263"/>
-      <c r="P42" s="264"/>
+      <c r="B42" s="227"/>
+      <c r="C42" s="228"/>
+      <c r="D42" s="228"/>
+      <c r="E42" s="228"/>
+      <c r="F42" s="228"/>
+      <c r="G42" s="228"/>
+      <c r="H42" s="228"/>
+      <c r="I42" s="228"/>
+      <c r="J42" s="228"/>
+      <c r="K42" s="228"/>
+      <c r="L42" s="228"/>
+      <c r="M42" s="228"/>
+      <c r="N42" s="228"/>
+      <c r="O42" s="228"/>
+      <c r="P42" s="229"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B43" s="244"/>
-      <c r="C43" s="265"/>
-      <c r="D43" s="265"/>
-      <c r="E43" s="265"/>
-      <c r="F43" s="265"/>
-      <c r="G43" s="265"/>
-      <c r="H43" s="265"/>
-      <c r="I43" s="265"/>
-      <c r="J43" s="265"/>
-      <c r="K43" s="265"/>
-      <c r="L43" s="265"/>
-      <c r="M43" s="265"/>
-      <c r="N43" s="265"/>
-      <c r="O43" s="265"/>
-      <c r="P43" s="266"/>
+      <c r="B43" s="230"/>
+      <c r="C43" s="231"/>
+      <c r="D43" s="231"/>
+      <c r="E43" s="231"/>
+      <c r="F43" s="231"/>
+      <c r="G43" s="231"/>
+      <c r="H43" s="231"/>
+      <c r="I43" s="231"/>
+      <c r="J43" s="231"/>
+      <c r="K43" s="231"/>
+      <c r="L43" s="231"/>
+      <c r="M43" s="231"/>
+      <c r="N43" s="231"/>
+      <c r="O43" s="231"/>
+      <c r="P43" s="232"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B44" s="42"/>
@@ -56562,33 +56562,33 @@
       <c r="O51" s="126"/>
     </row>
     <row r="52" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="326" t="s">
+      <c r="B52" s="335" t="s">
         <v>178</v>
       </c>
-      <c r="C52" s="327"/>
-      <c r="D52" s="327"/>
-      <c r="E52" s="327"/>
-      <c r="F52" s="327"/>
-      <c r="G52" s="327"/>
-      <c r="H52" s="327"/>
-      <c r="I52" s="327"/>
-      <c r="J52" s="327"/>
-      <c r="K52" s="327"/>
-      <c r="L52" s="327"/>
-      <c r="M52" s="327"/>
-      <c r="N52" s="327"/>
-      <c r="O52" s="327"/>
-      <c r="P52" s="327"/>
-      <c r="Q52" s="328"/>
+      <c r="C52" s="336"/>
+      <c r="D52" s="336"/>
+      <c r="E52" s="336"/>
+      <c r="F52" s="336"/>
+      <c r="G52" s="336"/>
+      <c r="H52" s="336"/>
+      <c r="I52" s="336"/>
+      <c r="J52" s="336"/>
+      <c r="K52" s="336"/>
+      <c r="L52" s="336"/>
+      <c r="M52" s="336"/>
+      <c r="N52" s="336"/>
+      <c r="O52" s="336"/>
+      <c r="P52" s="336"/>
+      <c r="Q52" s="337"/>
     </row>
     <row r="53" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B53" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C53" s="232" t="s">
+      <c r="C53" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D53" s="232"/>
+      <c r="D53" s="220"/>
       <c r="E53" s="120" t="s">
         <v>3</v>
       </c>
@@ -56630,10 +56630,10 @@
       </c>
     </row>
     <row r="54" spans="2:17" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="262" t="s">
+      <c r="B54" s="237" t="s">
         <v>179</v>
       </c>
-      <c r="C54" s="325" t="s">
+      <c r="C54" s="320" t="s">
         <v>165</v>
       </c>
       <c r="D54" s="53" t="s">
@@ -56683,8 +56683,8 @@
       </c>
     </row>
     <row r="55" spans="2:17" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="262"/>
-      <c r="C55" s="325"/>
+      <c r="B55" s="237"/>
+      <c r="C55" s="320"/>
       <c r="D55" s="53" t="s">
         <v>22</v>
       </c>
@@ -56732,33 +56732,33 @@
       </c>
     </row>
     <row r="56" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="326" t="s">
+      <c r="B56" s="335" t="s">
         <v>181</v>
       </c>
-      <c r="C56" s="327"/>
-      <c r="D56" s="327"/>
-      <c r="E56" s="327"/>
-      <c r="F56" s="327"/>
-      <c r="G56" s="327"/>
-      <c r="H56" s="327"/>
-      <c r="I56" s="327"/>
-      <c r="J56" s="327"/>
-      <c r="K56" s="327"/>
-      <c r="L56" s="327"/>
-      <c r="M56" s="327"/>
-      <c r="N56" s="327"/>
-      <c r="O56" s="327"/>
-      <c r="P56" s="327"/>
-      <c r="Q56" s="328"/>
+      <c r="C56" s="336"/>
+      <c r="D56" s="336"/>
+      <c r="E56" s="336"/>
+      <c r="F56" s="336"/>
+      <c r="G56" s="336"/>
+      <c r="H56" s="336"/>
+      <c r="I56" s="336"/>
+      <c r="J56" s="336"/>
+      <c r="K56" s="336"/>
+      <c r="L56" s="336"/>
+      <c r="M56" s="336"/>
+      <c r="N56" s="336"/>
+      <c r="O56" s="336"/>
+      <c r="P56" s="336"/>
+      <c r="Q56" s="337"/>
     </row>
     <row r="57" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="232" t="s">
+      <c r="C57" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="232"/>
+      <c r="D57" s="220"/>
       <c r="E57" s="120" t="s">
         <v>3</v>
       </c>
@@ -56800,10 +56800,10 @@
       </c>
     </row>
     <row r="58" spans="2:17" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="262" t="s">
+      <c r="B58" s="237" t="s">
         <v>71</v>
       </c>
-      <c r="C58" s="325" t="s">
+      <c r="C58" s="320" t="s">
         <v>165</v>
       </c>
       <c r="D58" s="53" t="s">
@@ -56848,13 +56848,13 @@
       <c r="P58" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q58" s="334" t="s">
+      <c r="Q58" s="327" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="59" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B59" s="262"/>
-      <c r="C59" s="325"/>
+      <c r="B59" s="237"/>
+      <c r="C59" s="320"/>
       <c r="D59" s="53" t="s">
         <v>22</v>
       </c>
@@ -56897,36 +56897,36 @@
       <c r="P59" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q59" s="335"/>
+      <c r="Q59" s="328"/>
     </row>
     <row r="60" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="331" t="s">
+      <c r="B60" s="324" t="s">
         <v>183</v>
       </c>
-      <c r="C60" s="315"/>
-      <c r="D60" s="315"/>
-      <c r="E60" s="315"/>
-      <c r="F60" s="315"/>
-      <c r="G60" s="315"/>
-      <c r="H60" s="315"/>
-      <c r="I60" s="315"/>
-      <c r="J60" s="315"/>
-      <c r="K60" s="315"/>
-      <c r="L60" s="315"/>
-      <c r="M60" s="315"/>
-      <c r="N60" s="315"/>
-      <c r="O60" s="315"/>
-      <c r="P60" s="315"/>
-      <c r="Q60" s="332"/>
+      <c r="C60" s="325"/>
+      <c r="D60" s="325"/>
+      <c r="E60" s="325"/>
+      <c r="F60" s="325"/>
+      <c r="G60" s="325"/>
+      <c r="H60" s="325"/>
+      <c r="I60" s="325"/>
+      <c r="J60" s="325"/>
+      <c r="K60" s="325"/>
+      <c r="L60" s="325"/>
+      <c r="M60" s="325"/>
+      <c r="N60" s="325"/>
+      <c r="O60" s="325"/>
+      <c r="P60" s="325"/>
+      <c r="Q60" s="326"/>
     </row>
     <row r="61" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B61" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C61" s="234" t="s">
+      <c r="C61" s="306" t="s">
         <v>2</v>
       </c>
-      <c r="D61" s="234"/>
+      <c r="D61" s="306"/>
       <c r="E61" s="8" t="s">
         <v>3</v>
       </c>
@@ -56968,10 +56968,10 @@
       </c>
     </row>
     <row r="62" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="333" t="s">
+      <c r="B62" s="332" t="s">
         <v>184</v>
       </c>
-      <c r="C62" s="325" t="s">
+      <c r="C62" s="320" t="s">
         <v>165</v>
       </c>
       <c r="D62" s="53" t="s">
@@ -57016,13 +57016,13 @@
       <c r="P62" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q62" s="334" t="s">
+      <c r="Q62" s="327" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="63" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B63" s="333"/>
-      <c r="C63" s="325"/>
+      <c r="B63" s="332"/>
+      <c r="C63" s="320"/>
       <c r="D63" s="53" t="s">
         <v>22</v>
       </c>
@@ -57065,36 +57065,36 @@
       <c r="P63" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q63" s="335"/>
+      <c r="Q63" s="328"/>
     </row>
     <row r="64" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="331" t="s">
+      <c r="B64" s="324" t="s">
         <v>185</v>
       </c>
-      <c r="C64" s="315"/>
-      <c r="D64" s="315"/>
-      <c r="E64" s="315"/>
-      <c r="F64" s="315"/>
-      <c r="G64" s="315"/>
-      <c r="H64" s="315"/>
-      <c r="I64" s="315"/>
-      <c r="J64" s="315"/>
-      <c r="K64" s="315"/>
-      <c r="L64" s="315"/>
-      <c r="M64" s="315"/>
-      <c r="N64" s="315"/>
-      <c r="O64" s="315"/>
-      <c r="P64" s="315"/>
-      <c r="Q64" s="332"/>
+      <c r="C64" s="325"/>
+      <c r="D64" s="325"/>
+      <c r="E64" s="325"/>
+      <c r="F64" s="325"/>
+      <c r="G64" s="325"/>
+      <c r="H64" s="325"/>
+      <c r="I64" s="325"/>
+      <c r="J64" s="325"/>
+      <c r="K64" s="325"/>
+      <c r="L64" s="325"/>
+      <c r="M64" s="325"/>
+      <c r="N64" s="325"/>
+      <c r="O64" s="325"/>
+      <c r="P64" s="325"/>
+      <c r="Q64" s="326"/>
     </row>
     <row r="65" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B65" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="234" t="s">
+      <c r="C65" s="306" t="s">
         <v>2</v>
       </c>
-      <c r="D65" s="234"/>
+      <c r="D65" s="306"/>
       <c r="E65" s="8" t="s">
         <v>3</v>
       </c>
@@ -57136,10 +57136,10 @@
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B66" s="333" t="s">
+      <c r="B66" s="332" t="s">
         <v>186</v>
       </c>
-      <c r="C66" s="325" t="s">
+      <c r="C66" s="320" t="s">
         <v>165</v>
       </c>
       <c r="D66" s="53" t="s">
@@ -57184,13 +57184,13 @@
       <c r="P66" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q66" s="336" t="s">
+      <c r="Q66" s="329" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B67" s="333"/>
-      <c r="C67" s="325"/>
+      <c r="B67" s="332"/>
+      <c r="C67" s="320"/>
       <c r="D67" s="53" t="s">
         <v>22</v>
       </c>
@@ -57233,36 +57233,36 @@
       <c r="P67" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q67" s="337"/>
+      <c r="Q67" s="333"/>
     </row>
     <row r="68" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="331" t="s">
+      <c r="B68" s="324" t="s">
         <v>188</v>
       </c>
-      <c r="C68" s="315"/>
-      <c r="D68" s="315"/>
-      <c r="E68" s="315"/>
-      <c r="F68" s="315"/>
-      <c r="G68" s="315"/>
-      <c r="H68" s="315"/>
-      <c r="I68" s="315"/>
-      <c r="J68" s="315"/>
-      <c r="K68" s="315"/>
-      <c r="L68" s="315"/>
-      <c r="M68" s="315"/>
-      <c r="N68" s="315"/>
-      <c r="O68" s="315"/>
-      <c r="P68" s="315"/>
-      <c r="Q68" s="332"/>
+      <c r="C68" s="325"/>
+      <c r="D68" s="325"/>
+      <c r="E68" s="325"/>
+      <c r="F68" s="325"/>
+      <c r="G68" s="325"/>
+      <c r="H68" s="325"/>
+      <c r="I68" s="325"/>
+      <c r="J68" s="325"/>
+      <c r="K68" s="325"/>
+      <c r="L68" s="325"/>
+      <c r="M68" s="325"/>
+      <c r="N68" s="325"/>
+      <c r="O68" s="325"/>
+      <c r="P68" s="325"/>
+      <c r="Q68" s="326"/>
     </row>
     <row r="69" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B69" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C69" s="234" t="s">
+      <c r="C69" s="306" t="s">
         <v>2</v>
       </c>
-      <c r="D69" s="234"/>
+      <c r="D69" s="306"/>
       <c r="E69" s="8" t="s">
         <v>3</v>
       </c>
@@ -57304,10 +57304,10 @@
       </c>
     </row>
     <row r="70" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="262" t="s">
+      <c r="B70" s="237" t="s">
         <v>189</v>
       </c>
-      <c r="C70" s="325" t="s">
+      <c r="C70" s="320" t="s">
         <v>165</v>
       </c>
       <c r="D70" s="53" t="s">
@@ -57352,13 +57352,13 @@
       <c r="P70" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="Q70" s="336" t="s">
+      <c r="Q70" s="329" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B71" s="262"/>
-      <c r="C71" s="325"/>
+      <c r="B71" s="237"/>
+      <c r="C71" s="320"/>
       <c r="D71" s="53" t="s">
         <v>22</v>
       </c>
@@ -57401,36 +57401,36 @@
       <c r="P71" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="Q71" s="338"/>
+      <c r="Q71" s="334"/>
     </row>
     <row r="72" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="331" t="s">
+      <c r="B72" s="324" t="s">
         <v>190</v>
       </c>
-      <c r="C72" s="315"/>
-      <c r="D72" s="315"/>
-      <c r="E72" s="315"/>
-      <c r="F72" s="315"/>
-      <c r="G72" s="315"/>
-      <c r="H72" s="315"/>
-      <c r="I72" s="315"/>
-      <c r="J72" s="315"/>
-      <c r="K72" s="315"/>
-      <c r="L72" s="315"/>
-      <c r="M72" s="315"/>
-      <c r="N72" s="323"/>
-      <c r="O72" s="315"/>
-      <c r="P72" s="315"/>
-      <c r="Q72" s="332"/>
+      <c r="C72" s="325"/>
+      <c r="D72" s="325"/>
+      <c r="E72" s="325"/>
+      <c r="F72" s="325"/>
+      <c r="G72" s="325"/>
+      <c r="H72" s="325"/>
+      <c r="I72" s="325"/>
+      <c r="J72" s="325"/>
+      <c r="K72" s="325"/>
+      <c r="L72" s="325"/>
+      <c r="M72" s="325"/>
+      <c r="N72" s="331"/>
+      <c r="O72" s="325"/>
+      <c r="P72" s="325"/>
+      <c r="Q72" s="326"/>
     </row>
     <row r="73" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B73" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C73" s="234" t="s">
+      <c r="C73" s="306" t="s">
         <v>2</v>
       </c>
-      <c r="D73" s="234"/>
+      <c r="D73" s="306"/>
       <c r="E73" s="8" t="s">
         <v>3</v>
       </c>
@@ -57472,10 +57472,10 @@
       </c>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B74" s="262" t="s">
+      <c r="B74" s="237" t="s">
         <v>191</v>
       </c>
-      <c r="C74" s="325" t="s">
+      <c r="C74" s="320" t="s">
         <v>165</v>
       </c>
       <c r="D74" s="53" t="s">
@@ -57520,13 +57520,13 @@
       <c r="P74" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q74" s="336" t="s">
+      <c r="Q74" s="329" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="75" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="341"/>
-      <c r="C75" s="340"/>
+      <c r="B75" s="323"/>
+      <c r="C75" s="321"/>
       <c r="D75" s="90" t="s">
         <v>22</v>
       </c>
@@ -57569,15 +57569,15 @@
       <c r="P75" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="Q75" s="339"/>
+      <c r="Q75" s="330"/>
     </row>
     <row r="76" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="126"/>
       <c r="C76" s="126"/>
-      <c r="D76" s="320" t="s">
+      <c r="D76" s="322" t="s">
         <v>192</v>
       </c>
-      <c r="E76" s="320"/>
+      <c r="E76" s="322"/>
       <c r="F76" s="126"/>
       <c r="G76" s="126"/>
       <c r="H76" s="126"/>
@@ -57593,133 +57593,133 @@
       <c r="R76" s="126"/>
     </row>
     <row r="77" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B77" s="267" t="s">
+      <c r="B77" s="281" t="s">
         <v>32</v>
       </c>
-      <c r="C77" s="268"/>
-      <c r="D77" s="268"/>
-      <c r="E77" s="268"/>
-      <c r="F77" s="268"/>
-      <c r="G77" s="268"/>
-      <c r="H77" s="268"/>
-      <c r="I77" s="268"/>
-      <c r="J77" s="268"/>
-      <c r="K77" s="268"/>
-      <c r="L77" s="268"/>
-      <c r="M77" s="268"/>
-      <c r="N77" s="268"/>
-      <c r="O77" s="268"/>
-      <c r="P77" s="268"/>
-      <c r="Q77" s="268"/>
-      <c r="R77" s="269"/>
+      <c r="C77" s="282"/>
+      <c r="D77" s="282"/>
+      <c r="E77" s="282"/>
+      <c r="F77" s="282"/>
+      <c r="G77" s="282"/>
+      <c r="H77" s="282"/>
+      <c r="I77" s="282"/>
+      <c r="J77" s="282"/>
+      <c r="K77" s="282"/>
+      <c r="L77" s="282"/>
+      <c r="M77" s="282"/>
+      <c r="N77" s="282"/>
+      <c r="O77" s="282"/>
+      <c r="P77" s="282"/>
+      <c r="Q77" s="282"/>
+      <c r="R77" s="283"/>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B78" s="270" t="s">
+      <c r="B78" s="284" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="222"/>
-      <c r="D78" s="222"/>
-      <c r="E78" s="222"/>
-      <c r="F78" s="222"/>
-      <c r="G78" s="222"/>
-      <c r="H78" s="222"/>
-      <c r="I78" s="222"/>
-      <c r="J78" s="222"/>
-      <c r="K78" s="222"/>
-      <c r="L78" s="222"/>
-      <c r="M78" s="222"/>
-      <c r="N78" s="222"/>
-      <c r="O78" s="222"/>
-      <c r="P78" s="222"/>
-      <c r="Q78" s="222"/>
-      <c r="R78" s="271"/>
+      <c r="C78" s="285"/>
+      <c r="D78" s="285"/>
+      <c r="E78" s="285"/>
+      <c r="F78" s="285"/>
+      <c r="G78" s="285"/>
+      <c r="H78" s="285"/>
+      <c r="I78" s="285"/>
+      <c r="J78" s="285"/>
+      <c r="K78" s="285"/>
+      <c r="L78" s="285"/>
+      <c r="M78" s="285"/>
+      <c r="N78" s="285"/>
+      <c r="O78" s="285"/>
+      <c r="P78" s="285"/>
+      <c r="Q78" s="285"/>
+      <c r="R78" s="286"/>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B79" s="270"/>
-      <c r="C79" s="222"/>
-      <c r="D79" s="222"/>
-      <c r="E79" s="222"/>
-      <c r="F79" s="222"/>
-      <c r="G79" s="222"/>
-      <c r="H79" s="222"/>
-      <c r="I79" s="222"/>
-      <c r="J79" s="222"/>
-      <c r="K79" s="222"/>
-      <c r="L79" s="222"/>
-      <c r="M79" s="222"/>
-      <c r="N79" s="222"/>
-      <c r="O79" s="222"/>
-      <c r="P79" s="222"/>
-      <c r="Q79" s="222"/>
-      <c r="R79" s="271"/>
+      <c r="B79" s="284"/>
+      <c r="C79" s="285"/>
+      <c r="D79" s="285"/>
+      <c r="E79" s="285"/>
+      <c r="F79" s="285"/>
+      <c r="G79" s="285"/>
+      <c r="H79" s="285"/>
+      <c r="I79" s="285"/>
+      <c r="J79" s="285"/>
+      <c r="K79" s="285"/>
+      <c r="L79" s="285"/>
+      <c r="M79" s="285"/>
+      <c r="N79" s="285"/>
+      <c r="O79" s="285"/>
+      <c r="P79" s="285"/>
+      <c r="Q79" s="285"/>
+      <c r="R79" s="286"/>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B80" s="270"/>
-      <c r="C80" s="222"/>
-      <c r="D80" s="222"/>
-      <c r="E80" s="222"/>
-      <c r="F80" s="222"/>
-      <c r="G80" s="222"/>
-      <c r="H80" s="222"/>
-      <c r="I80" s="222"/>
-      <c r="J80" s="222"/>
-      <c r="K80" s="222"/>
-      <c r="L80" s="222"/>
-      <c r="M80" s="222"/>
-      <c r="N80" s="222"/>
-      <c r="O80" s="222"/>
-      <c r="P80" s="222"/>
-      <c r="Q80" s="222"/>
-      <c r="R80" s="271"/>
+      <c r="B80" s="284"/>
+      <c r="C80" s="285"/>
+      <c r="D80" s="285"/>
+      <c r="E80" s="285"/>
+      <c r="F80" s="285"/>
+      <c r="G80" s="285"/>
+      <c r="H80" s="285"/>
+      <c r="I80" s="285"/>
+      <c r="J80" s="285"/>
+      <c r="K80" s="285"/>
+      <c r="L80" s="285"/>
+      <c r="M80" s="285"/>
+      <c r="N80" s="285"/>
+      <c r="O80" s="285"/>
+      <c r="P80" s="285"/>
+      <c r="Q80" s="285"/>
+      <c r="R80" s="286"/>
     </row>
     <row r="81" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="272"/>
-      <c r="C81" s="273"/>
-      <c r="D81" s="273"/>
-      <c r="E81" s="273"/>
-      <c r="F81" s="273"/>
-      <c r="G81" s="273"/>
-      <c r="H81" s="273"/>
-      <c r="I81" s="273"/>
-      <c r="J81" s="273"/>
-      <c r="K81" s="273"/>
-      <c r="L81" s="273"/>
-      <c r="M81" s="273"/>
-      <c r="N81" s="273"/>
-      <c r="O81" s="273"/>
-      <c r="P81" s="273"/>
-      <c r="Q81" s="273"/>
-      <c r="R81" s="274"/>
+      <c r="B81" s="287"/>
+      <c r="C81" s="288"/>
+      <c r="D81" s="288"/>
+      <c r="E81" s="288"/>
+      <c r="F81" s="288"/>
+      <c r="G81" s="288"/>
+      <c r="H81" s="288"/>
+      <c r="I81" s="288"/>
+      <c r="J81" s="288"/>
+      <c r="K81" s="288"/>
+      <c r="L81" s="288"/>
+      <c r="M81" s="288"/>
+      <c r="N81" s="288"/>
+      <c r="O81" s="288"/>
+      <c r="P81" s="288"/>
+      <c r="Q81" s="288"/>
+      <c r="R81" s="289"/>
     </row>
     <row r="89" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B89" s="275" t="s">
+      <c r="B89" s="290" t="s">
         <v>193</v>
       </c>
-      <c r="C89" s="275"/>
-      <c r="D89" s="275"/>
-      <c r="E89" s="275"/>
-      <c r="F89" s="275"/>
-      <c r="G89" s="275"/>
-      <c r="H89" s="275"/>
-      <c r="I89" s="275"/>
-      <c r="J89" s="275"/>
-      <c r="K89" s="275"/>
-      <c r="L89" s="275"/>
-      <c r="M89" s="275"/>
-      <c r="N89" s="275"/>
-      <c r="O89" s="275"/>
-      <c r="P89" s="275"/>
-      <c r="Q89" s="275"/>
-      <c r="R89" s="275"/>
+      <c r="C89" s="290"/>
+      <c r="D89" s="290"/>
+      <c r="E89" s="290"/>
+      <c r="F89" s="290"/>
+      <c r="G89" s="290"/>
+      <c r="H89" s="290"/>
+      <c r="I89" s="290"/>
+      <c r="J89" s="290"/>
+      <c r="K89" s="290"/>
+      <c r="L89" s="290"/>
+      <c r="M89" s="290"/>
+      <c r="N89" s="290"/>
+      <c r="O89" s="290"/>
+      <c r="P89" s="290"/>
+      <c r="Q89" s="290"/>
+      <c r="R89" s="290"/>
     </row>
     <row r="90" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C90" s="234" t="s">
+      <c r="C90" s="306" t="s">
         <v>2</v>
       </c>
-      <c r="D90" s="234"/>
+      <c r="D90" s="306"/>
       <c r="E90" s="127" t="s">
         <v>125</v>
       </c>
@@ -57756,16 +57756,16 @@
       <c r="P90" s="124" t="s">
         <v>118</v>
       </c>
-      <c r="Q90" s="232" t="s">
+      <c r="Q90" s="220" t="s">
         <v>36</v>
       </c>
-      <c r="R90" s="232"/>
+      <c r="R90" s="220"/>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B91" s="228" t="s">
+      <c r="B91" s="217" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="214" t="s">
+      <c r="C91" s="242" t="s">
         <v>165</v>
       </c>
       <c r="D91" s="53" t="s">
@@ -57809,14 +57809,14 @@
       <c r="P91" s="53" t="s">
         <v>152</v>
       </c>
-      <c r="Q91" s="229" t="s">
+      <c r="Q91" s="249" t="s">
         <v>44</v>
       </c>
-      <c r="R91" s="229"/>
+      <c r="R91" s="249"/>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B92" s="228"/>
-      <c r="C92" s="214"/>
+      <c r="B92" s="217"/>
+      <c r="C92" s="242"/>
       <c r="D92" s="53" t="s">
         <v>22</v>
       </c>
@@ -57858,8 +57858,8 @@
       <c r="P92" s="53" t="s">
         <v>152</v>
       </c>
-      <c r="Q92" s="229"/>
-      <c r="R92" s="229"/>
+      <c r="Q92" s="249"/>
+      <c r="R92" s="249"/>
     </row>
     <row r="94" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B94" s="5" t="s">
@@ -57883,82 +57883,82 @@
       <c r="R94" s="6"/>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B95" s="230" t="s">
+      <c r="B95" s="252" t="s">
         <v>33</v>
       </c>
-      <c r="C95" s="230"/>
-      <c r="D95" s="230"/>
-      <c r="E95" s="230"/>
-      <c r="F95" s="230"/>
-      <c r="G95" s="230"/>
-      <c r="H95" s="230"/>
-      <c r="I95" s="230"/>
-      <c r="J95" s="230"/>
-      <c r="K95" s="230"/>
-      <c r="L95" s="230"/>
-      <c r="M95" s="230"/>
-      <c r="N95" s="230"/>
-      <c r="O95" s="230"/>
-      <c r="P95" s="230"/>
-      <c r="Q95" s="230"/>
-      <c r="R95" s="230"/>
+      <c r="C95" s="252"/>
+      <c r="D95" s="252"/>
+      <c r="E95" s="252"/>
+      <c r="F95" s="252"/>
+      <c r="G95" s="252"/>
+      <c r="H95" s="252"/>
+      <c r="I95" s="252"/>
+      <c r="J95" s="252"/>
+      <c r="K95" s="252"/>
+      <c r="L95" s="252"/>
+      <c r="M95" s="252"/>
+      <c r="N95" s="252"/>
+      <c r="O95" s="252"/>
+      <c r="P95" s="252"/>
+      <c r="Q95" s="252"/>
+      <c r="R95" s="252"/>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B96" s="230"/>
-      <c r="C96" s="230"/>
-      <c r="D96" s="230"/>
-      <c r="E96" s="230"/>
-      <c r="F96" s="230"/>
-      <c r="G96" s="230"/>
-      <c r="H96" s="230"/>
-      <c r="I96" s="230"/>
-      <c r="J96" s="230"/>
-      <c r="K96" s="230"/>
-      <c r="L96" s="230"/>
-      <c r="M96" s="230"/>
-      <c r="N96" s="230"/>
-      <c r="O96" s="230"/>
-      <c r="P96" s="230"/>
-      <c r="Q96" s="230"/>
-      <c r="R96" s="230"/>
+      <c r="B96" s="252"/>
+      <c r="C96" s="252"/>
+      <c r="D96" s="252"/>
+      <c r="E96" s="252"/>
+      <c r="F96" s="252"/>
+      <c r="G96" s="252"/>
+      <c r="H96" s="252"/>
+      <c r="I96" s="252"/>
+      <c r="J96" s="252"/>
+      <c r="K96" s="252"/>
+      <c r="L96" s="252"/>
+      <c r="M96" s="252"/>
+      <c r="N96" s="252"/>
+      <c r="O96" s="252"/>
+      <c r="P96" s="252"/>
+      <c r="Q96" s="252"/>
+      <c r="R96" s="252"/>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B97" s="230"/>
-      <c r="C97" s="230"/>
-      <c r="D97" s="230"/>
-      <c r="E97" s="230"/>
-      <c r="F97" s="230"/>
-      <c r="G97" s="230"/>
-      <c r="H97" s="230"/>
-      <c r="I97" s="230"/>
-      <c r="J97" s="230"/>
-      <c r="K97" s="230"/>
-      <c r="L97" s="230"/>
-      <c r="M97" s="230"/>
-      <c r="N97" s="230"/>
-      <c r="O97" s="230"/>
-      <c r="P97" s="230"/>
-      <c r="Q97" s="230"/>
-      <c r="R97" s="230"/>
+      <c r="B97" s="252"/>
+      <c r="C97" s="252"/>
+      <c r="D97" s="252"/>
+      <c r="E97" s="252"/>
+      <c r="F97" s="252"/>
+      <c r="G97" s="252"/>
+      <c r="H97" s="252"/>
+      <c r="I97" s="252"/>
+      <c r="J97" s="252"/>
+      <c r="K97" s="252"/>
+      <c r="L97" s="252"/>
+      <c r="M97" s="252"/>
+      <c r="N97" s="252"/>
+      <c r="O97" s="252"/>
+      <c r="P97" s="252"/>
+      <c r="Q97" s="252"/>
+      <c r="R97" s="252"/>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B98" s="230"/>
-      <c r="C98" s="230"/>
-      <c r="D98" s="230"/>
-      <c r="E98" s="230"/>
-      <c r="F98" s="230"/>
-      <c r="G98" s="230"/>
-      <c r="H98" s="230"/>
-      <c r="I98" s="230"/>
-      <c r="J98" s="230"/>
-      <c r="K98" s="230"/>
-      <c r="L98" s="230"/>
-      <c r="M98" s="230"/>
-      <c r="N98" s="230"/>
-      <c r="O98" s="230"/>
-      <c r="P98" s="230"/>
-      <c r="Q98" s="230"/>
-      <c r="R98" s="230"/>
+      <c r="B98" s="252"/>
+      <c r="C98" s="252"/>
+      <c r="D98" s="252"/>
+      <c r="E98" s="252"/>
+      <c r="F98" s="252"/>
+      <c r="G98" s="252"/>
+      <c r="H98" s="252"/>
+      <c r="I98" s="252"/>
+      <c r="J98" s="252"/>
+      <c r="K98" s="252"/>
+      <c r="L98" s="252"/>
+      <c r="M98" s="252"/>
+      <c r="N98" s="252"/>
+      <c r="O98" s="252"/>
+      <c r="P98" s="252"/>
+      <c r="Q98" s="252"/>
+      <c r="R98" s="252"/>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B99" s="122"/>
@@ -57998,34 +57998,34 @@
       <c r="C106" s="28"/>
     </row>
     <row r="107" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B107" s="238" t="s">
+      <c r="B107" s="218" t="s">
         <v>196</v>
       </c>
-      <c r="C107" s="233"/>
-      <c r="D107" s="233"/>
-      <c r="E107" s="233"/>
-      <c r="F107" s="233"/>
-      <c r="G107" s="233"/>
-      <c r="H107" s="233"/>
-      <c r="I107" s="233"/>
-      <c r="J107" s="233"/>
-      <c r="K107" s="233"/>
-      <c r="L107" s="233"/>
-      <c r="M107" s="233"/>
-      <c r="N107" s="233"/>
-      <c r="O107" s="233"/>
-      <c r="P107" s="233"/>
-      <c r="Q107" s="233"/>
-      <c r="R107" s="233"/>
+      <c r="C107" s="219"/>
+      <c r="D107" s="219"/>
+      <c r="E107" s="219"/>
+      <c r="F107" s="219"/>
+      <c r="G107" s="219"/>
+      <c r="H107" s="219"/>
+      <c r="I107" s="219"/>
+      <c r="J107" s="219"/>
+      <c r="K107" s="219"/>
+      <c r="L107" s="219"/>
+      <c r="M107" s="219"/>
+      <c r="N107" s="219"/>
+      <c r="O107" s="219"/>
+      <c r="P107" s="219"/>
+      <c r="Q107" s="219"/>
+      <c r="R107" s="219"/>
     </row>
     <row r="108" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B108" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C108" s="232" t="s">
+      <c r="C108" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D108" s="232"/>
+      <c r="D108" s="220"/>
       <c r="E108" s="8" t="s">
         <v>3</v>
       </c>
@@ -58070,10 +58070,10 @@
       </c>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B109" s="213" t="s">
+      <c r="B109" s="308" t="s">
         <v>98</v>
       </c>
-      <c r="C109" s="214" t="s">
+      <c r="C109" s="242" t="s">
         <v>165</v>
       </c>
       <c r="D109" s="53" t="s">
@@ -58125,8 +58125,8 @@
       </c>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B110" s="213"/>
-      <c r="C110" s="214"/>
+      <c r="B110" s="308"/>
+      <c r="C110" s="242"/>
       <c r="D110" s="53" t="s">
         <v>22</v>
       </c>
@@ -58176,10 +58176,10 @@
       </c>
     </row>
     <row r="111" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B111" s="213" t="s">
+      <c r="B111" s="308" t="s">
         <v>160</v>
       </c>
-      <c r="C111" s="214" t="s">
+      <c r="C111" s="242" t="s">
         <v>165</v>
       </c>
       <c r="D111" s="53" t="s">
@@ -58232,8 +58232,8 @@
       </c>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B112" s="213"/>
-      <c r="C112" s="214"/>
+      <c r="B112" s="308"/>
+      <c r="C112" s="242"/>
       <c r="D112" s="53" t="s">
         <v>22</v>
       </c>
@@ -58285,30 +58285,29 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B89:R89"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="B77:R77"/>
-    <mergeCell ref="B78:R81"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="B107:R107"/>
-    <mergeCell ref="B64:Q64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="Q58:Q59"/>
-    <mergeCell ref="B95:R98"/>
-    <mergeCell ref="Q90:R90"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="Q91:R92"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="B32:Q32"/>
+    <mergeCell ref="B18:P18"/>
+    <mergeCell ref="B19:P22"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B9:P9"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B56:Q56"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B40:P43"/>
+    <mergeCell ref="B52:Q52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="P34:Q36"/>
     <mergeCell ref="C57:D57"/>
     <mergeCell ref="B68:Q68"/>
     <mergeCell ref="C69:D69"/>
@@ -58325,29 +58324,30 @@
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="Q66:Q67"/>
     <mergeCell ref="Q70:Q71"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B56:Q56"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B40:P43"/>
-    <mergeCell ref="B52:Q52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="P34:Q36"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B9:P9"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="B32:Q32"/>
-    <mergeCell ref="B18:P18"/>
-    <mergeCell ref="B19:P22"/>
-    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B64:Q64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="Q58:Q59"/>
+    <mergeCell ref="B95:R98"/>
+    <mergeCell ref="Q90:R90"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="Q91:R92"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B89:R89"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="B77:R77"/>
+    <mergeCell ref="B78:R81"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="B107:R107"/>
   </mergeCells>
   <phoneticPr fontId="12" alignment="center"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -58390,33 +58390,33 @@
   </cols>
   <sheetData>
     <row r="8" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="238" t="s">
+      <c r="B8" s="218" t="s">
         <v>197</v>
       </c>
-      <c r="C8" s="233"/>
-      <c r="D8" s="233"/>
-      <c r="E8" s="233"/>
-      <c r="F8" s="233"/>
-      <c r="G8" s="233"/>
-      <c r="H8" s="233"/>
-      <c r="I8" s="233"/>
-      <c r="J8" s="233"/>
-      <c r="K8" s="233"/>
-      <c r="L8" s="233"/>
-      <c r="M8" s="233"/>
-      <c r="N8" s="233"/>
-      <c r="O8" s="233"/>
-      <c r="P8" s="233"/>
-      <c r="Q8" s="233"/>
+      <c r="C8" s="219"/>
+      <c r="D8" s="219"/>
+      <c r="E8" s="219"/>
+      <c r="F8" s="219"/>
+      <c r="G8" s="219"/>
+      <c r="H8" s="219"/>
+      <c r="I8" s="219"/>
+      <c r="J8" s="219"/>
+      <c r="K8" s="219"/>
+      <c r="L8" s="219"/>
+      <c r="M8" s="219"/>
+      <c r="N8" s="219"/>
+      <c r="O8" s="219"/>
+      <c r="P8" s="219"/>
+      <c r="Q8" s="219"/>
     </row>
     <row r="9" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B9" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="232" t="s">
+      <c r="C9" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="232"/>
+      <c r="D9" s="220"/>
       <c r="E9" s="120" t="s">
         <v>3</v>
       </c>
@@ -58458,10 +58458,10 @@
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="227" t="s">
+      <c r="B10" s="221" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="228" t="s">
+      <c r="C10" s="217" t="s">
         <v>110</v>
       </c>
       <c r="D10" s="117" t="s">
@@ -58510,8 +58510,8 @@
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="298"/>
-      <c r="C11" s="228"/>
+      <c r="B11" s="222"/>
+      <c r="C11" s="217"/>
       <c r="D11" s="117" t="s">
         <v>22</v>
       </c>
@@ -58558,8 +58558,8 @@
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B12" s="362" t="s">
-        <v>29</v>
+      <c r="B12" s="213" t="s">
+        <v>16</v>
       </c>
       <c r="C12" s="212" t="s">
         <v>110</v>
@@ -58579,7 +58579,7 @@
       <c r="H12" s="95">
         <v>54.2</v>
       </c>
-      <c r="I12" s="363" t="s">
+      <c r="I12" s="214" t="s">
         <v>177</v>
       </c>
       <c r="J12" s="95">
@@ -58610,34 +58610,34 @@
       </c>
     </row>
     <row r="13" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="238" t="s">
+      <c r="B13" s="218" t="s">
         <v>199</v>
       </c>
-      <c r="C13" s="233"/>
-      <c r="D13" s="233"/>
-      <c r="E13" s="233"/>
-      <c r="F13" s="233"/>
-      <c r="G13" s="233"/>
-      <c r="H13" s="233"/>
-      <c r="I13" s="233"/>
-      <c r="J13" s="233"/>
-      <c r="K13" s="233"/>
-      <c r="L13" s="233"/>
-      <c r="M13" s="233"/>
-      <c r="N13" s="233"/>
-      <c r="O13" s="233"/>
-      <c r="P13" s="233"/>
-      <c r="Q13" s="233"/>
-      <c r="R13" s="233"/>
+      <c r="C13" s="219"/>
+      <c r="D13" s="219"/>
+      <c r="E13" s="219"/>
+      <c r="F13" s="219"/>
+      <c r="G13" s="219"/>
+      <c r="H13" s="219"/>
+      <c r="I13" s="219"/>
+      <c r="J13" s="219"/>
+      <c r="K13" s="219"/>
+      <c r="L13" s="219"/>
+      <c r="M13" s="219"/>
+      <c r="N13" s="219"/>
+      <c r="O13" s="219"/>
+      <c r="P13" s="219"/>
+      <c r="Q13" s="219"/>
+      <c r="R13" s="219"/>
     </row>
     <row r="14" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B14" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="232" t="s">
+      <c r="C14" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="232"/>
+      <c r="D14" s="220"/>
       <c r="E14" s="120" t="s">
         <v>3</v>
       </c>
@@ -58685,10 +58685,10 @@
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="228" t="s">
+      <c r="B15" s="217" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="228" t="s">
+      <c r="C15" s="217" t="s">
         <v>165</v>
       </c>
       <c r="D15" s="117" t="s">
@@ -58743,8 +58743,8 @@
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B16" s="228"/>
-      <c r="C16" s="228"/>
+      <c r="B16" s="217"/>
+      <c r="C16" s="217"/>
       <c r="D16" s="117" t="s">
         <v>22</v>
       </c>
@@ -58797,33 +58797,33 @@
       </c>
     </row>
     <row r="17" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="346" t="s">
+      <c r="B17" s="225" t="s">
         <v>203</v>
       </c>
-      <c r="C17" s="347"/>
-      <c r="D17" s="347"/>
-      <c r="E17" s="347"/>
-      <c r="F17" s="347"/>
-      <c r="G17" s="347"/>
-      <c r="H17" s="347"/>
-      <c r="I17" s="347"/>
-      <c r="J17" s="347"/>
-      <c r="K17" s="347"/>
-      <c r="L17" s="347"/>
-      <c r="M17" s="347"/>
-      <c r="N17" s="347"/>
-      <c r="O17" s="347"/>
-      <c r="P17" s="347"/>
-      <c r="Q17" s="347"/>
+      <c r="C17" s="226"/>
+      <c r="D17" s="226"/>
+      <c r="E17" s="226"/>
+      <c r="F17" s="226"/>
+      <c r="G17" s="226"/>
+      <c r="H17" s="226"/>
+      <c r="I17" s="226"/>
+      <c r="J17" s="226"/>
+      <c r="K17" s="226"/>
+      <c r="L17" s="226"/>
+      <c r="M17" s="226"/>
+      <c r="N17" s="226"/>
+      <c r="O17" s="226"/>
+      <c r="P17" s="226"/>
+      <c r="Q17" s="226"/>
     </row>
     <row r="18" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B18" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="232" t="s">
+      <c r="C18" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="232"/>
+      <c r="D18" s="220"/>
       <c r="E18" s="120" t="s">
         <v>3</v>
       </c>
@@ -58857,16 +58857,16 @@
       <c r="O18" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="P18" s="344" t="s">
+      <c r="P18" s="223" t="s">
         <v>137</v>
       </c>
-      <c r="Q18" s="345"/>
+      <c r="Q18" s="224"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="228" t="s">
+      <c r="B19" s="217" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="228" t="s">
+      <c r="C19" s="217" t="s">
         <v>204</v>
       </c>
       <c r="D19" s="117" t="s">
@@ -58913,8 +58913,8 @@
       <c r="Q19" s="53"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="228"/>
-      <c r="C20" s="228"/>
+      <c r="B20" s="217"/>
+      <c r="C20" s="217"/>
       <c r="D20" s="117" t="s">
         <v>22</v>
       </c>
@@ -58959,32 +58959,32 @@
       <c r="Q20" s="53"/>
     </row>
     <row r="21" spans="2:17" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="237" t="s">
+      <c r="B21" s="215" t="s">
         <v>206</v>
       </c>
-      <c r="C21" s="294"/>
-      <c r="D21" s="294"/>
-      <c r="E21" s="294"/>
-      <c r="F21" s="294"/>
-      <c r="G21" s="294"/>
-      <c r="H21" s="294"/>
-      <c r="I21" s="294"/>
-      <c r="J21" s="294"/>
-      <c r="K21" s="294"/>
-      <c r="L21" s="294"/>
-      <c r="M21" s="294"/>
-      <c r="N21" s="294"/>
-      <c r="O21" s="294"/>
+      <c r="C21" s="216"/>
+      <c r="D21" s="216"/>
+      <c r="E21" s="216"/>
+      <c r="F21" s="216"/>
+      <c r="G21" s="216"/>
+      <c r="H21" s="216"/>
+      <c r="I21" s="216"/>
+      <c r="J21" s="216"/>
+      <c r="K21" s="216"/>
+      <c r="L21" s="216"/>
+      <c r="M21" s="216"/>
+      <c r="N21" s="216"/>
+      <c r="O21" s="216"/>
       <c r="P21" s="207"/>
     </row>
     <row r="22" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B22" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="232" t="s">
+      <c r="C22" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="232"/>
+      <c r="D22" s="220"/>
       <c r="E22" s="120" t="s">
         <v>3</v>
       </c>
@@ -59018,14 +59018,14 @@
       <c r="O22" s="120" t="s">
         <v>137</v>
       </c>
-      <c r="P22" s="342"/>
-      <c r="Q22" s="343"/>
+      <c r="P22" s="233"/>
+      <c r="Q22" s="234"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B23" s="228" t="s">
+      <c r="B23" s="217" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="228" t="s">
+      <c r="C23" s="217" t="s">
         <v>207</v>
       </c>
       <c r="D23" s="117" t="s">
@@ -59070,8 +59070,8 @@
       <c r="P23" s="205"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B24" s="228"/>
-      <c r="C24" s="228"/>
+      <c r="B24" s="217"/>
+      <c r="C24" s="217"/>
       <c r="D24" s="117" t="s">
         <v>22</v>
       </c>
@@ -59114,32 +59114,32 @@
       <c r="P24" s="205"/>
     </row>
     <row r="25" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B25" s="238" t="s">
+      <c r="B25" s="218" t="s">
         <v>209</v>
       </c>
-      <c r="C25" s="233"/>
-      <c r="D25" s="233"/>
-      <c r="E25" s="233"/>
-      <c r="F25" s="233"/>
-      <c r="G25" s="233"/>
-      <c r="H25" s="233"/>
-      <c r="I25" s="233"/>
-      <c r="J25" s="233"/>
-      <c r="K25" s="233"/>
-      <c r="L25" s="233"/>
-      <c r="M25" s="233"/>
-      <c r="N25" s="233"/>
-      <c r="O25" s="233"/>
+      <c r="C25" s="219"/>
+      <c r="D25" s="219"/>
+      <c r="E25" s="219"/>
+      <c r="F25" s="219"/>
+      <c r="G25" s="219"/>
+      <c r="H25" s="219"/>
+      <c r="I25" s="219"/>
+      <c r="J25" s="219"/>
+      <c r="K25" s="219"/>
+      <c r="L25" s="219"/>
+      <c r="M25" s="219"/>
+      <c r="N25" s="219"/>
+      <c r="O25" s="219"/>
       <c r="P25" s="61"/>
     </row>
     <row r="26" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B26" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C26" s="232" t="s">
+      <c r="C26" s="220" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="232"/>
+      <c r="D26" s="220"/>
       <c r="E26" s="120" t="s">
         <v>3</v>
       </c>
@@ -59176,10 +59176,10 @@
       <c r="P26" s="61"/>
     </row>
     <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="228" t="s">
+      <c r="B27" s="217" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="228" t="s">
+      <c r="C27" s="217" t="s">
         <v>114</v>
       </c>
       <c r="D27" s="117" t="s">
@@ -59225,8 +59225,8 @@
       <c r="P27" s="61"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B28" s="228"/>
-      <c r="C28" s="228"/>
+      <c r="B28" s="217"/>
+      <c r="C28" s="217"/>
       <c r="D28" s="117" t="s">
         <v>22</v>
       </c>
@@ -59290,78 +59290,78 @@
       <c r="Q30" s="7"/>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B31" s="243" t="s">
+      <c r="B31" s="227" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="263"/>
-      <c r="D31" s="263"/>
-      <c r="E31" s="263"/>
-      <c r="F31" s="263"/>
-      <c r="G31" s="263"/>
-      <c r="H31" s="263"/>
-      <c r="I31" s="263"/>
-      <c r="J31" s="263"/>
-      <c r="K31" s="263"/>
-      <c r="L31" s="263"/>
-      <c r="M31" s="263"/>
-      <c r="N31" s="263"/>
-      <c r="O31" s="263"/>
-      <c r="P31" s="263"/>
-      <c r="Q31" s="264"/>
+      <c r="C31" s="228"/>
+      <c r="D31" s="228"/>
+      <c r="E31" s="228"/>
+      <c r="F31" s="228"/>
+      <c r="G31" s="228"/>
+      <c r="H31" s="228"/>
+      <c r="I31" s="228"/>
+      <c r="J31" s="228"/>
+      <c r="K31" s="228"/>
+      <c r="L31" s="228"/>
+      <c r="M31" s="228"/>
+      <c r="N31" s="228"/>
+      <c r="O31" s="228"/>
+      <c r="P31" s="228"/>
+      <c r="Q31" s="229"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B32" s="243"/>
-      <c r="C32" s="263"/>
-      <c r="D32" s="263"/>
-      <c r="E32" s="263"/>
-      <c r="F32" s="263"/>
-      <c r="G32" s="263"/>
-      <c r="H32" s="263"/>
-      <c r="I32" s="263"/>
-      <c r="J32" s="263"/>
-      <c r="K32" s="263"/>
-      <c r="L32" s="263"/>
-      <c r="M32" s="263"/>
-      <c r="N32" s="263"/>
-      <c r="O32" s="263"/>
-      <c r="P32" s="263"/>
-      <c r="Q32" s="264"/>
+      <c r="B32" s="227"/>
+      <c r="C32" s="228"/>
+      <c r="D32" s="228"/>
+      <c r="E32" s="228"/>
+      <c r="F32" s="228"/>
+      <c r="G32" s="228"/>
+      <c r="H32" s="228"/>
+      <c r="I32" s="228"/>
+      <c r="J32" s="228"/>
+      <c r="K32" s="228"/>
+      <c r="L32" s="228"/>
+      <c r="M32" s="228"/>
+      <c r="N32" s="228"/>
+      <c r="O32" s="228"/>
+      <c r="P32" s="228"/>
+      <c r="Q32" s="229"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B33" s="243"/>
-      <c r="C33" s="263"/>
-      <c r="D33" s="263"/>
-      <c r="E33" s="263"/>
-      <c r="F33" s="263"/>
-      <c r="G33" s="263"/>
-      <c r="H33" s="263"/>
-      <c r="I33" s="263"/>
-      <c r="J33" s="263"/>
-      <c r="K33" s="263"/>
-      <c r="L33" s="263"/>
-      <c r="M33" s="263"/>
-      <c r="N33" s="263"/>
-      <c r="O33" s="263"/>
-      <c r="P33" s="263"/>
-      <c r="Q33" s="264"/>
+      <c r="B33" s="227"/>
+      <c r="C33" s="228"/>
+      <c r="D33" s="228"/>
+      <c r="E33" s="228"/>
+      <c r="F33" s="228"/>
+      <c r="G33" s="228"/>
+      <c r="H33" s="228"/>
+      <c r="I33" s="228"/>
+      <c r="J33" s="228"/>
+      <c r="K33" s="228"/>
+      <c r="L33" s="228"/>
+      <c r="M33" s="228"/>
+      <c r="N33" s="228"/>
+      <c r="O33" s="228"/>
+      <c r="P33" s="228"/>
+      <c r="Q33" s="229"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B34" s="244"/>
-      <c r="C34" s="265"/>
-      <c r="D34" s="265"/>
-      <c r="E34" s="265"/>
-      <c r="F34" s="265"/>
-      <c r="G34" s="265"/>
-      <c r="H34" s="265"/>
-      <c r="I34" s="265"/>
-      <c r="J34" s="265"/>
-      <c r="K34" s="265"/>
-      <c r="L34" s="265"/>
-      <c r="M34" s="265"/>
-      <c r="N34" s="265"/>
-      <c r="O34" s="265"/>
-      <c r="P34" s="265"/>
-      <c r="Q34" s="266"/>
+      <c r="B34" s="230"/>
+      <c r="C34" s="231"/>
+      <c r="D34" s="231"/>
+      <c r="E34" s="231"/>
+      <c r="F34" s="231"/>
+      <c r="G34" s="231"/>
+      <c r="H34" s="231"/>
+      <c r="I34" s="231"/>
+      <c r="J34" s="231"/>
+      <c r="K34" s="231"/>
+      <c r="L34" s="231"/>
+      <c r="M34" s="231"/>
+      <c r="N34" s="231"/>
+      <c r="O34" s="231"/>
+      <c r="P34" s="231"/>
+      <c r="Q34" s="232"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B35" s="35"/>
@@ -59491,11 +59491,15 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B21:O21"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B31:Q34"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B25:O25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="P22:Q22"/>
     <mergeCell ref="B8:Q8"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C18:D18"/>
@@ -59505,15 +59509,11 @@
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="P18:Q18"/>
     <mergeCell ref="B17:Q17"/>
-    <mergeCell ref="B31:Q34"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B25:O25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="B21:O21"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B19:B20"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -59700,10 +59700,10 @@
       <c r="B10" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="348" t="s">
+      <c r="C10" s="362" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="348"/>
+      <c r="D10" s="362"/>
       <c r="E10" s="15" t="s">
         <v>3</v>
       </c>
@@ -59742,10 +59742,10 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="349" t="s">
+      <c r="B11" s="358" t="s">
         <v>211</v>
       </c>
-      <c r="C11" s="352" t="s">
+      <c r="C11" s="360" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="45" t="s">
@@ -59791,8 +59791,8 @@
       </c>
     </row>
     <row r="12" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="350"/>
-      <c r="C12" s="352"/>
+      <c r="B12" s="363"/>
+      <c r="C12" s="360"/>
       <c r="D12" s="45" t="s">
         <v>22</v>
       </c>
@@ -59836,8 +59836,8 @@
       </c>
     </row>
     <row r="13" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="350"/>
-      <c r="C13" s="352" t="s">
+      <c r="B13" s="363"/>
+      <c r="C13" s="360" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="45" t="s">
@@ -59883,8 +59883,8 @@
       </c>
     </row>
     <row r="14" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="350"/>
-      <c r="C14" s="352"/>
+      <c r="B14" s="363"/>
+      <c r="C14" s="360"/>
       <c r="D14" s="45" t="s">
         <v>22</v>
       </c>
@@ -59928,8 +59928,8 @@
       </c>
     </row>
     <row r="15" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="350"/>
-      <c r="C15" s="352" t="s">
+      <c r="B15" s="363"/>
+      <c r="C15" s="360" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="45" t="s">
@@ -59975,8 +59975,8 @@
       </c>
     </row>
     <row r="16" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="350"/>
-      <c r="C16" s="352"/>
+      <c r="B16" s="363"/>
+      <c r="C16" s="360"/>
       <c r="D16" s="45" t="s">
         <v>22</v>
       </c>
@@ -60020,8 +60020,8 @@
       </c>
     </row>
     <row r="17" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="350"/>
-      <c r="C17" s="352" t="s">
+      <c r="B17" s="363"/>
+      <c r="C17" s="360" t="s">
         <v>29</v>
       </c>
       <c r="D17" s="45" t="s">
@@ -60067,8 +60067,8 @@
       </c>
     </row>
     <row r="18" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="350"/>
-      <c r="C18" s="352"/>
+      <c r="B18" s="363"/>
+      <c r="C18" s="360"/>
       <c r="D18" s="45" t="s">
         <v>22</v>
       </c>
@@ -60112,8 +60112,8 @@
       </c>
     </row>
     <row r="19" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="350"/>
-      <c r="C19" s="352" t="s">
+      <c r="B19" s="363"/>
+      <c r="C19" s="360" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="45" t="s">
@@ -60159,8 +60159,8 @@
       </c>
     </row>
     <row r="20" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="351"/>
-      <c r="C20" s="352"/>
+      <c r="B20" s="359"/>
+      <c r="C20" s="360"/>
       <c r="D20" s="45" t="s">
         <v>22</v>
       </c>
@@ -60204,10 +60204,10 @@
       </c>
     </row>
     <row r="21" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="349" t="s">
+      <c r="B21" s="358" t="s">
         <v>216</v>
       </c>
-      <c r="C21" s="352" t="s">
+      <c r="C21" s="360" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="45" t="s">
@@ -60253,8 +60253,8 @@
       </c>
     </row>
     <row r="22" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="351"/>
-      <c r="C22" s="352"/>
+      <c r="B22" s="359"/>
+      <c r="C22" s="360"/>
       <c r="D22" s="45" t="s">
         <v>22</v>
       </c>
@@ -60298,10 +60298,10 @@
       </c>
     </row>
     <row r="23" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B23" s="349" t="s">
+      <c r="B23" s="358" t="s">
         <v>217</v>
       </c>
-      <c r="C23" s="352" t="s">
+      <c r="C23" s="360" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="45" t="s">
@@ -60347,8 +60347,8 @@
       </c>
     </row>
     <row r="24" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="351"/>
-      <c r="C24" s="352"/>
+      <c r="B24" s="359"/>
+      <c r="C24" s="360"/>
       <c r="D24" s="45" t="s">
         <v>22</v>
       </c>
@@ -60392,10 +60392,10 @@
       </c>
     </row>
     <row r="25" spans="2:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="262" t="s">
+      <c r="B25" s="237" t="s">
         <v>219</v>
       </c>
-      <c r="C25" s="228" t="s">
+      <c r="C25" s="217" t="s">
         <v>29</v>
       </c>
       <c r="D25" s="40" t="s">
@@ -60441,8 +60441,8 @@
       </c>
     </row>
     <row r="26" spans="2:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="262"/>
-      <c r="C26" s="228"/>
+      <c r="B26" s="237"/>
+      <c r="C26" s="217"/>
       <c r="D26" s="40" t="s">
         <v>22</v>
       </c>
@@ -60486,7 +60486,7 @@
       </c>
     </row>
     <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="341"/>
+      <c r="B27" s="323"/>
       <c r="C27" s="361"/>
       <c r="D27" s="84" t="s">
         <v>17</v>
@@ -60547,96 +60547,103 @@
       <c r="O28" s="28"/>
     </row>
     <row r="29" spans="2:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="353" t="s">
+      <c r="B29" s="350" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="354"/>
-      <c r="D29" s="354"/>
-      <c r="E29" s="354"/>
-      <c r="F29" s="354"/>
-      <c r="G29" s="354"/>
-      <c r="H29" s="354"/>
-      <c r="I29" s="354"/>
-      <c r="J29" s="354"/>
-      <c r="K29" s="354"/>
-      <c r="L29" s="354"/>
-      <c r="M29" s="354"/>
-      <c r="N29" s="354"/>
-      <c r="O29" s="354"/>
-      <c r="P29" s="355"/>
+      <c r="C29" s="351"/>
+      <c r="D29" s="351"/>
+      <c r="E29" s="351"/>
+      <c r="F29" s="351"/>
+      <c r="G29" s="351"/>
+      <c r="H29" s="351"/>
+      <c r="I29" s="351"/>
+      <c r="J29" s="351"/>
+      <c r="K29" s="351"/>
+      <c r="L29" s="351"/>
+      <c r="M29" s="351"/>
+      <c r="N29" s="351"/>
+      <c r="O29" s="351"/>
+      <c r="P29" s="352"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B30" s="356" t="s">
+      <c r="B30" s="353" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="263"/>
-      <c r="D30" s="263"/>
-      <c r="E30" s="263"/>
-      <c r="F30" s="263"/>
-      <c r="G30" s="263"/>
-      <c r="H30" s="263"/>
-      <c r="I30" s="263"/>
-      <c r="J30" s="263"/>
-      <c r="K30" s="263"/>
-      <c r="L30" s="263"/>
-      <c r="M30" s="263"/>
-      <c r="N30" s="263"/>
-      <c r="O30" s="263"/>
-      <c r="P30" s="357"/>
+      <c r="C30" s="228"/>
+      <c r="D30" s="228"/>
+      <c r="E30" s="228"/>
+      <c r="F30" s="228"/>
+      <c r="G30" s="228"/>
+      <c r="H30" s="228"/>
+      <c r="I30" s="228"/>
+      <c r="J30" s="228"/>
+      <c r="K30" s="228"/>
+      <c r="L30" s="228"/>
+      <c r="M30" s="228"/>
+      <c r="N30" s="228"/>
+      <c r="O30" s="228"/>
+      <c r="P30" s="354"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="356"/>
-      <c r="C31" s="263"/>
-      <c r="D31" s="263"/>
-      <c r="E31" s="263"/>
-      <c r="F31" s="263"/>
-      <c r="G31" s="263"/>
-      <c r="H31" s="263"/>
-      <c r="I31" s="263"/>
-      <c r="J31" s="263"/>
-      <c r="K31" s="263"/>
-      <c r="L31" s="263"/>
-      <c r="M31" s="263"/>
-      <c r="N31" s="263"/>
-      <c r="O31" s="263"/>
-      <c r="P31" s="357"/>
+      <c r="B31" s="353"/>
+      <c r="C31" s="228"/>
+      <c r="D31" s="228"/>
+      <c r="E31" s="228"/>
+      <c r="F31" s="228"/>
+      <c r="G31" s="228"/>
+      <c r="H31" s="228"/>
+      <c r="I31" s="228"/>
+      <c r="J31" s="228"/>
+      <c r="K31" s="228"/>
+      <c r="L31" s="228"/>
+      <c r="M31" s="228"/>
+      <c r="N31" s="228"/>
+      <c r="O31" s="228"/>
+      <c r="P31" s="354"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B32" s="356"/>
-      <c r="C32" s="263"/>
-      <c r="D32" s="263"/>
-      <c r="E32" s="263"/>
-      <c r="F32" s="263"/>
-      <c r="G32" s="263"/>
-      <c r="H32" s="263"/>
-      <c r="I32" s="263"/>
-      <c r="J32" s="263"/>
-      <c r="K32" s="263"/>
-      <c r="L32" s="263"/>
-      <c r="M32" s="263"/>
-      <c r="N32" s="263"/>
-      <c r="O32" s="263"/>
-      <c r="P32" s="357"/>
+      <c r="B32" s="353"/>
+      <c r="C32" s="228"/>
+      <c r="D32" s="228"/>
+      <c r="E32" s="228"/>
+      <c r="F32" s="228"/>
+      <c r="G32" s="228"/>
+      <c r="H32" s="228"/>
+      <c r="I32" s="228"/>
+      <c r="J32" s="228"/>
+      <c r="K32" s="228"/>
+      <c r="L32" s="228"/>
+      <c r="M32" s="228"/>
+      <c r="N32" s="228"/>
+      <c r="O32" s="228"/>
+      <c r="P32" s="354"/>
     </row>
     <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="358"/>
-      <c r="C33" s="359"/>
-      <c r="D33" s="359"/>
-      <c r="E33" s="359"/>
-      <c r="F33" s="359"/>
-      <c r="G33" s="359"/>
-      <c r="H33" s="359"/>
-      <c r="I33" s="359"/>
-      <c r="J33" s="359"/>
-      <c r="K33" s="359"/>
-      <c r="L33" s="359"/>
-      <c r="M33" s="359"/>
-      <c r="N33" s="359"/>
-      <c r="O33" s="359"/>
-      <c r="P33" s="360"/>
+      <c r="B33" s="355"/>
+      <c r="C33" s="356"/>
+      <c r="D33" s="356"/>
+      <c r="E33" s="356"/>
+      <c r="F33" s="356"/>
+      <c r="G33" s="356"/>
+      <c r="H33" s="356"/>
+      <c r="I33" s="356"/>
+      <c r="J33" s="356"/>
+      <c r="K33" s="356"/>
+      <c r="L33" s="356"/>
+      <c r="M33" s="356"/>
+      <c r="N33" s="356"/>
+      <c r="O33" s="356"/>
+      <c r="P33" s="357"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B20"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
     <mergeCell ref="B29:P29"/>
     <mergeCell ref="B30:P33"/>
     <mergeCell ref="B21:B22"/>
@@ -60645,13 +60652,6 @@
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="B25:B27"/>
     <mergeCell ref="C25:C27"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B20"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="67" orientation="landscape" r:id="rId1"/>
@@ -60660,14 +60660,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bf418b7-79e0-4993-aa07-d31c53a64380">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="268ad1c4-fabf-4dd0-b894-8fd5403102c0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -60894,21 +60892,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bf418b7-79e0-4993-aa07-d31c53a64380">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="268ad1c4-fabf-4dd0-b894-8fd5403102c0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
-    <ds:schemaRef ds:uri="268ad1c4-fabf-4dd0-b894-8fd5403102c0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -60933,9 +60930,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
+    <ds:schemaRef ds:uri="268ad1c4-fabf-4dd0-b894-8fd5403102c0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Customer Rate Tariff Template_Week 33_2026.xlsx
+++ b/Customer Rate Tariff Template_Week 33_2026.xlsx
@@ -2236,13 +2236,25 @@
     <xf numFmtId="44" fontId="1" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2251,7 +2263,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2272,28 +2290,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2304,135 +2304,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2464,56 +2335,134 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2551,67 +2500,63 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2627,6 +2572,76 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2651,23 +2666,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4128,32 +4128,32 @@
       <c r="P7" s="18"/>
     </row>
     <row r="8" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="219" t="s">
+      <c r="B8" s="223" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="219"/>
-      <c r="D8" s="219"/>
-      <c r="E8" s="219"/>
-      <c r="F8" s="219"/>
-      <c r="G8" s="219"/>
-      <c r="H8" s="219"/>
-      <c r="I8" s="219"/>
-      <c r="J8" s="219"/>
-      <c r="K8" s="219"/>
-      <c r="L8" s="219"/>
-      <c r="M8" s="219"/>
-      <c r="N8" s="219"/>
-      <c r="O8" s="219"/>
-      <c r="P8" s="219"/>
+      <c r="C8" s="223"/>
+      <c r="D8" s="223"/>
+      <c r="E8" s="223"/>
+      <c r="F8" s="223"/>
+      <c r="G8" s="223"/>
+      <c r="H8" s="223"/>
+      <c r="I8" s="223"/>
+      <c r="J8" s="223"/>
+      <c r="K8" s="223"/>
+      <c r="L8" s="223"/>
+      <c r="M8" s="223"/>
+      <c r="N8" s="223"/>
+      <c r="O8" s="223"/>
+      <c r="P8" s="223"/>
     </row>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="220" t="s">
+      <c r="C9" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="220"/>
+      <c r="D9" s="221"/>
       <c r="E9" s="120" t="s">
         <v>3</v>
       </c>
@@ -4192,10 +4192,10 @@
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="238" t="s">
+      <c r="B10" s="284" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="238" t="s">
+      <c r="C10" s="284" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="20" t="s">
@@ -4241,8 +4241,8 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="239"/>
-      <c r="C11" s="239"/>
+      <c r="B11" s="285"/>
+      <c r="C11" s="285"/>
       <c r="D11" s="20" t="s">
         <v>22</v>
       </c>
@@ -4286,8 +4286,8 @@
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="239"/>
-      <c r="C12" s="238" t="s">
+      <c r="B12" s="285"/>
+      <c r="C12" s="284" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="111" t="s">
@@ -4334,8 +4334,8 @@
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="239"/>
-      <c r="C13" s="239"/>
+      <c r="B13" s="285"/>
+      <c r="C13" s="285"/>
       <c r="D13" s="111" t="s">
         <v>22</v>
       </c>
@@ -4381,10 +4381,10 @@
       <c r="Q13" s="26"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="240" t="s">
+      <c r="B14" s="286" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="242" t="s">
+      <c r="C14" s="248" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="20" t="s">
@@ -4431,8 +4431,8 @@
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="241"/>
-      <c r="C15" s="242"/>
+      <c r="B15" s="287"/>
+      <c r="C15" s="248"/>
       <c r="D15" s="20" t="s">
         <v>22</v>
       </c>
@@ -4477,10 +4477,10 @@
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="240" t="s">
+      <c r="B16" s="286" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="240" t="s">
+      <c r="C16" s="286" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="20" t="s">
@@ -4527,8 +4527,8 @@
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B17" s="241"/>
-      <c r="C17" s="241"/>
+      <c r="B17" s="287"/>
+      <c r="C17" s="287"/>
       <c r="D17" s="20" t="s">
         <v>22</v>
       </c>
@@ -4573,10 +4573,10 @@
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="240" t="s">
+      <c r="B18" s="286" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="242" t="s">
+      <c r="C18" s="248" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -4624,8 +4624,8 @@
       <c r="Q18" s="26"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="250"/>
-      <c r="C19" s="242"/>
+      <c r="B19" s="290"/>
+      <c r="C19" s="248"/>
       <c r="D19" s="20" t="s">
         <v>22</v>
       </c>
@@ -4671,8 +4671,8 @@
       <c r="Q19" s="26"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="250"/>
-      <c r="C20" s="242" t="s">
+      <c r="B20" s="290"/>
+      <c r="C20" s="248" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="20" t="s">
@@ -4719,8 +4719,8 @@
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="241"/>
-      <c r="C21" s="242"/>
+      <c r="B21" s="287"/>
+      <c r="C21" s="248"/>
       <c r="D21" s="20" t="s">
         <v>22</v>
       </c>
@@ -4802,74 +4802,74 @@
       <c r="P23" s="186"/>
     </row>
     <row r="24" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="252" t="s">
+      <c r="B24" s="281" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="252"/>
-      <c r="D24" s="252"/>
-      <c r="E24" s="252"/>
-      <c r="F24" s="252"/>
-      <c r="G24" s="252"/>
-      <c r="H24" s="252"/>
-      <c r="I24" s="252"/>
-      <c r="J24" s="252"/>
-      <c r="K24" s="252"/>
-      <c r="L24" s="252"/>
-      <c r="M24" s="252"/>
-      <c r="N24" s="252"/>
-      <c r="O24" s="252"/>
-      <c r="P24" s="252"/>
+      <c r="C24" s="281"/>
+      <c r="D24" s="281"/>
+      <c r="E24" s="281"/>
+      <c r="F24" s="281"/>
+      <c r="G24" s="281"/>
+      <c r="H24" s="281"/>
+      <c r="I24" s="281"/>
+      <c r="J24" s="281"/>
+      <c r="K24" s="281"/>
+      <c r="L24" s="281"/>
+      <c r="M24" s="281"/>
+      <c r="N24" s="281"/>
+      <c r="O24" s="281"/>
+      <c r="P24" s="281"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B25" s="252"/>
-      <c r="C25" s="252"/>
-      <c r="D25" s="252"/>
-      <c r="E25" s="252"/>
-      <c r="F25" s="252"/>
-      <c r="G25" s="252"/>
-      <c r="H25" s="252"/>
-      <c r="I25" s="252"/>
-      <c r="J25" s="252"/>
-      <c r="K25" s="252"/>
-      <c r="L25" s="252"/>
-      <c r="M25" s="252"/>
-      <c r="N25" s="252"/>
-      <c r="O25" s="252"/>
-      <c r="P25" s="252"/>
+      <c r="B25" s="281"/>
+      <c r="C25" s="281"/>
+      <c r="D25" s="281"/>
+      <c r="E25" s="281"/>
+      <c r="F25" s="281"/>
+      <c r="G25" s="281"/>
+      <c r="H25" s="281"/>
+      <c r="I25" s="281"/>
+      <c r="J25" s="281"/>
+      <c r="K25" s="281"/>
+      <c r="L25" s="281"/>
+      <c r="M25" s="281"/>
+      <c r="N25" s="281"/>
+      <c r="O25" s="281"/>
+      <c r="P25" s="281"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B26" s="252"/>
-      <c r="C26" s="252"/>
-      <c r="D26" s="252"/>
-      <c r="E26" s="252"/>
-      <c r="F26" s="252"/>
-      <c r="G26" s="252"/>
-      <c r="H26" s="252"/>
-      <c r="I26" s="252"/>
-      <c r="J26" s="252"/>
-      <c r="K26" s="252"/>
-      <c r="L26" s="252"/>
-      <c r="M26" s="252"/>
-      <c r="N26" s="252"/>
-      <c r="O26" s="252"/>
-      <c r="P26" s="252"/>
+      <c r="B26" s="281"/>
+      <c r="C26" s="281"/>
+      <c r="D26" s="281"/>
+      <c r="E26" s="281"/>
+      <c r="F26" s="281"/>
+      <c r="G26" s="281"/>
+      <c r="H26" s="281"/>
+      <c r="I26" s="281"/>
+      <c r="J26" s="281"/>
+      <c r="K26" s="281"/>
+      <c r="L26" s="281"/>
+      <c r="M26" s="281"/>
+      <c r="N26" s="281"/>
+      <c r="O26" s="281"/>
+      <c r="P26" s="281"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B27" s="252"/>
-      <c r="C27" s="252"/>
-      <c r="D27" s="252"/>
-      <c r="E27" s="252"/>
-      <c r="F27" s="252"/>
-      <c r="G27" s="252"/>
-      <c r="H27" s="252"/>
-      <c r="I27" s="252"/>
-      <c r="J27" s="252"/>
-      <c r="K27" s="252"/>
-      <c r="L27" s="252"/>
-      <c r="M27" s="252"/>
-      <c r="N27" s="252"/>
-      <c r="O27" s="252"/>
-      <c r="P27" s="252"/>
+      <c r="B27" s="281"/>
+      <c r="C27" s="281"/>
+      <c r="D27" s="281"/>
+      <c r="E27" s="281"/>
+      <c r="F27" s="281"/>
+      <c r="G27" s="281"/>
+      <c r="H27" s="281"/>
+      <c r="I27" s="281"/>
+      <c r="J27" s="281"/>
+      <c r="K27" s="281"/>
+      <c r="L27" s="281"/>
+      <c r="M27" s="281"/>
+      <c r="N27" s="281"/>
+      <c r="O27" s="281"/>
+      <c r="P27" s="281"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B28" s="35"/>
@@ -4998,32 +4998,32 @@
       <c r="Q34" s="28"/>
     </row>
     <row r="35" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="243" t="s">
+      <c r="B35" s="288" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="216"/>
-      <c r="D35" s="216"/>
-      <c r="E35" s="216"/>
-      <c r="F35" s="216"/>
-      <c r="G35" s="216"/>
-      <c r="H35" s="216"/>
-      <c r="I35" s="216"/>
-      <c r="J35" s="216"/>
-      <c r="K35" s="216"/>
-      <c r="L35" s="216"/>
-      <c r="M35" s="216"/>
-      <c r="N35" s="216"/>
-      <c r="O35" s="216"/>
-      <c r="P35" s="216"/>
+      <c r="C35" s="234"/>
+      <c r="D35" s="234"/>
+      <c r="E35" s="234"/>
+      <c r="F35" s="234"/>
+      <c r="G35" s="234"/>
+      <c r="H35" s="234"/>
+      <c r="I35" s="234"/>
+      <c r="J35" s="234"/>
+      <c r="K35" s="234"/>
+      <c r="L35" s="234"/>
+      <c r="M35" s="234"/>
+      <c r="N35" s="234"/>
+      <c r="O35" s="234"/>
+      <c r="P35" s="234"/>
     </row>
     <row r="36" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B36" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="220" t="s">
+      <c r="C36" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="220"/>
+      <c r="D36" s="221"/>
       <c r="E36" s="120" t="s">
         <v>3</v>
       </c>
@@ -5054,13 +5054,13 @@
       <c r="N36" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="O36" s="220" t="s">
+      <c r="O36" s="221" t="s">
         <v>36</v>
       </c>
-      <c r="P36" s="220"/>
+      <c r="P36" s="221"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B37" s="244" t="s">
+      <c r="B37" s="289" t="s">
         <v>37</v>
       </c>
       <c r="C37" s="136" t="s">
@@ -5102,13 +5102,13 @@
       <c r="N37" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O37" s="245" t="s">
+      <c r="O37" s="272" t="s">
         <v>40</v>
       </c>
-      <c r="P37" s="246"/>
+      <c r="P37" s="273"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B38" s="244"/>
+      <c r="B38" s="289"/>
       <c r="C38" s="136" t="s">
         <v>16</v>
       </c>
@@ -5148,8 +5148,8 @@
       <c r="N38" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O38" s="247"/>
-      <c r="P38" s="248"/>
+      <c r="O38" s="274"/>
+      <c r="P38" s="275"/>
     </row>
     <row r="39" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="187" t="s">
@@ -5285,78 +5285,78 @@
       <c r="Q42" s="7"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B43" s="227" t="s">
+      <c r="B43" s="215" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="228"/>
-      <c r="D43" s="228"/>
-      <c r="E43" s="228"/>
-      <c r="F43" s="228"/>
-      <c r="G43" s="228"/>
-      <c r="H43" s="228"/>
-      <c r="I43" s="228"/>
-      <c r="J43" s="228"/>
-      <c r="K43" s="228"/>
-      <c r="L43" s="228"/>
-      <c r="M43" s="228"/>
-      <c r="N43" s="228"/>
-      <c r="O43" s="228"/>
-      <c r="P43" s="228"/>
-      <c r="Q43" s="229"/>
+      <c r="C43" s="216"/>
+      <c r="D43" s="216"/>
+      <c r="E43" s="216"/>
+      <c r="F43" s="216"/>
+      <c r="G43" s="216"/>
+      <c r="H43" s="216"/>
+      <c r="I43" s="216"/>
+      <c r="J43" s="216"/>
+      <c r="K43" s="216"/>
+      <c r="L43" s="216"/>
+      <c r="M43" s="216"/>
+      <c r="N43" s="216"/>
+      <c r="O43" s="216"/>
+      <c r="P43" s="216"/>
+      <c r="Q43" s="217"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B44" s="227"/>
-      <c r="C44" s="228"/>
-      <c r="D44" s="228"/>
-      <c r="E44" s="228"/>
-      <c r="F44" s="228"/>
-      <c r="G44" s="228"/>
-      <c r="H44" s="228"/>
-      <c r="I44" s="228"/>
-      <c r="J44" s="228"/>
-      <c r="K44" s="228"/>
-      <c r="L44" s="228"/>
-      <c r="M44" s="228"/>
-      <c r="N44" s="228"/>
-      <c r="O44" s="228"/>
-      <c r="P44" s="228"/>
-      <c r="Q44" s="229"/>
+      <c r="B44" s="215"/>
+      <c r="C44" s="216"/>
+      <c r="D44" s="216"/>
+      <c r="E44" s="216"/>
+      <c r="F44" s="216"/>
+      <c r="G44" s="216"/>
+      <c r="H44" s="216"/>
+      <c r="I44" s="216"/>
+      <c r="J44" s="216"/>
+      <c r="K44" s="216"/>
+      <c r="L44" s="216"/>
+      <c r="M44" s="216"/>
+      <c r="N44" s="216"/>
+      <c r="O44" s="216"/>
+      <c r="P44" s="216"/>
+      <c r="Q44" s="217"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B45" s="227"/>
-      <c r="C45" s="228"/>
-      <c r="D45" s="228"/>
-      <c r="E45" s="228"/>
-      <c r="F45" s="228"/>
-      <c r="G45" s="228"/>
-      <c r="H45" s="228"/>
-      <c r="I45" s="228"/>
-      <c r="J45" s="228"/>
-      <c r="K45" s="228"/>
-      <c r="L45" s="228"/>
-      <c r="M45" s="228"/>
-      <c r="N45" s="228"/>
-      <c r="O45" s="228"/>
-      <c r="P45" s="228"/>
-      <c r="Q45" s="229"/>
+      <c r="B45" s="215"/>
+      <c r="C45" s="216"/>
+      <c r="D45" s="216"/>
+      <c r="E45" s="216"/>
+      <c r="F45" s="216"/>
+      <c r="G45" s="216"/>
+      <c r="H45" s="216"/>
+      <c r="I45" s="216"/>
+      <c r="J45" s="216"/>
+      <c r="K45" s="216"/>
+      <c r="L45" s="216"/>
+      <c r="M45" s="216"/>
+      <c r="N45" s="216"/>
+      <c r="O45" s="216"/>
+      <c r="P45" s="216"/>
+      <c r="Q45" s="217"/>
     </row>
     <row r="46" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B46" s="230"/>
-      <c r="C46" s="231"/>
-      <c r="D46" s="231"/>
-      <c r="E46" s="231"/>
-      <c r="F46" s="231"/>
-      <c r="G46" s="231"/>
-      <c r="H46" s="231"/>
-      <c r="I46" s="231"/>
-      <c r="J46" s="231"/>
-      <c r="K46" s="231"/>
-      <c r="L46" s="231"/>
-      <c r="M46" s="231"/>
-      <c r="N46" s="231"/>
-      <c r="O46" s="231"/>
-      <c r="P46" s="231"/>
-      <c r="Q46" s="232"/>
+      <c r="B46" s="218"/>
+      <c r="C46" s="219"/>
+      <c r="D46" s="219"/>
+      <c r="E46" s="219"/>
+      <c r="F46" s="219"/>
+      <c r="G46" s="219"/>
+      <c r="H46" s="219"/>
+      <c r="I46" s="219"/>
+      <c r="J46" s="219"/>
+      <c r="K46" s="219"/>
+      <c r="L46" s="219"/>
+      <c r="M46" s="219"/>
+      <c r="N46" s="219"/>
+      <c r="O46" s="219"/>
+      <c r="P46" s="219"/>
+      <c r="Q46" s="220"/>
     </row>
     <row r="47" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B47" s="35"/>
@@ -5541,16 +5541,16 @@
       <c r="P56" s="236"/>
       <c r="Q56" s="236"/>
       <c r="R56" s="236"/>
-      <c r="S56" s="253"/>
+      <c r="S56" s="263"/>
     </row>
     <row r="57" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="220" t="s">
+      <c r="C57" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="220"/>
+      <c r="D57" s="221"/>
       <c r="E57" s="120" t="s">
         <v>3</v>
       </c>
@@ -5590,16 +5590,16 @@
       <c r="Q57" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R57" s="254" t="s">
+      <c r="R57" s="282" t="s">
         <v>36</v>
       </c>
-      <c r="S57" s="255"/>
+      <c r="S57" s="283"/>
     </row>
     <row r="58" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="256" t="s">
+      <c r="B58" s="253" t="s">
         <v>51</v>
       </c>
-      <c r="C58" s="251" t="s">
+      <c r="C58" s="254" t="s">
         <v>52</v>
       </c>
       <c r="D58" s="137" t="s">
@@ -5647,14 +5647,14 @@
       <c r="Q58" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R58" s="257" t="s">
+      <c r="R58" s="255" t="s">
         <v>55</v>
       </c>
-      <c r="S58" s="258"/>
+      <c r="S58" s="256"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B59" s="256"/>
-      <c r="C59" s="251"/>
+      <c r="B59" s="253"/>
+      <c r="C59" s="254"/>
       <c r="D59" s="137" t="s">
         <v>22</v>
       </c>
@@ -5700,14 +5700,14 @@
       <c r="Q59" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R59" s="259"/>
-      <c r="S59" s="260"/>
+      <c r="R59" s="257"/>
+      <c r="S59" s="258"/>
     </row>
     <row r="60" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="256" t="s">
+      <c r="B60" s="253" t="s">
         <v>56</v>
       </c>
-      <c r="C60" s="251" t="s">
+      <c r="C60" s="254" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="137" t="s">
@@ -5755,12 +5755,12 @@
       <c r="Q60" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R60" s="259"/>
-      <c r="S60" s="260"/>
+      <c r="R60" s="257"/>
+      <c r="S60" s="258"/>
     </row>
     <row r="61" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B61" s="256"/>
-      <c r="C61" s="251"/>
+      <c r="B61" s="253"/>
+      <c r="C61" s="254"/>
       <c r="D61" s="137" t="s">
         <v>22</v>
       </c>
@@ -5806,14 +5806,14 @@
       <c r="Q61" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R61" s="261"/>
-      <c r="S61" s="262"/>
+      <c r="R61" s="277"/>
+      <c r="S61" s="278"/>
     </row>
     <row r="62" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="267" t="s">
+      <c r="B62" s="270" t="s">
         <v>57</v>
       </c>
-      <c r="C62" s="221" t="s">
+      <c r="C62" s="227" t="s">
         <v>29</v>
       </c>
       <c r="D62" s="117" t="s">
@@ -5861,14 +5861,14 @@
       <c r="Q62" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="R62" s="245" t="s">
+      <c r="R62" s="272" t="s">
         <v>59</v>
       </c>
-      <c r="S62" s="246"/>
+      <c r="S62" s="273"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B63" s="268"/>
-      <c r="C63" s="222"/>
+      <c r="B63" s="271"/>
+      <c r="C63" s="228"/>
       <c r="D63" s="117" t="s">
         <v>22</v>
       </c>
@@ -5914,14 +5914,14 @@
       <c r="Q63" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="R63" s="247"/>
-      <c r="S63" s="248"/>
+      <c r="R63" s="274"/>
+      <c r="S63" s="275"/>
     </row>
     <row r="64" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="256" t="s">
+      <c r="B64" s="253" t="s">
         <v>60</v>
       </c>
-      <c r="C64" s="251" t="s">
+      <c r="C64" s="254" t="s">
         <v>52</v>
       </c>
       <c r="D64" s="137" t="s">
@@ -5969,14 +5969,14 @@
       <c r="Q64" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R64" s="257" t="s">
+      <c r="R64" s="255" t="s">
         <v>55</v>
       </c>
-      <c r="S64" s="258"/>
+      <c r="S64" s="256"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B65" s="256"/>
-      <c r="C65" s="251"/>
+      <c r="B65" s="253"/>
+      <c r="C65" s="254"/>
       <c r="D65" s="137" t="s">
         <v>22</v>
       </c>
@@ -6022,14 +6022,14 @@
       <c r="Q65" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R65" s="259"/>
-      <c r="S65" s="260"/>
+      <c r="R65" s="257"/>
+      <c r="S65" s="258"/>
     </row>
     <row r="66" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="271" t="s">
+      <c r="B66" s="279" t="s">
         <v>61</v>
       </c>
-      <c r="C66" s="269" t="s">
+      <c r="C66" s="267" t="s">
         <v>29</v>
       </c>
       <c r="D66" s="137" t="s">
@@ -6077,14 +6077,14 @@
       <c r="Q66" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="R66" s="245" t="s">
+      <c r="R66" s="272" t="s">
         <v>59</v>
       </c>
-      <c r="S66" s="246"/>
+      <c r="S66" s="273"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B67" s="272"/>
-      <c r="C67" s="270"/>
+      <c r="B67" s="280"/>
+      <c r="C67" s="276"/>
       <c r="D67" s="137" t="s">
         <v>22</v>
       </c>
@@ -6130,14 +6130,14 @@
       <c r="Q67" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="R67" s="247"/>
-      <c r="S67" s="248"/>
+      <c r="R67" s="274"/>
+      <c r="S67" s="275"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B68" s="271" t="s">
+      <c r="B68" s="279" t="s">
         <v>62</v>
       </c>
-      <c r="C68" s="251" t="s">
+      <c r="C68" s="254" t="s">
         <v>52</v>
       </c>
       <c r="D68" s="137" t="s">
@@ -6185,14 +6185,14 @@
       <c r="Q68" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R68" s="257" t="s">
+      <c r="R68" s="255" t="s">
         <v>55</v>
       </c>
-      <c r="S68" s="258"/>
+      <c r="S68" s="256"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B69" s="272"/>
-      <c r="C69" s="251"/>
+      <c r="B69" s="280"/>
+      <c r="C69" s="254"/>
       <c r="D69" s="137" t="s">
         <v>22</v>
       </c>
@@ -6238,14 +6238,14 @@
       <c r="Q69" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R69" s="259"/>
-      <c r="S69" s="260"/>
+      <c r="R69" s="257"/>
+      <c r="S69" s="258"/>
     </row>
     <row r="70" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="256" t="s">
+      <c r="B70" s="253" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="251" t="s">
+      <c r="C70" s="254" t="s">
         <v>52</v>
       </c>
       <c r="D70" s="137" t="s">
@@ -6293,12 +6293,12 @@
       <c r="Q70" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R70" s="259"/>
-      <c r="S70" s="260"/>
+      <c r="R70" s="257"/>
+      <c r="S70" s="258"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B71" s="256"/>
-      <c r="C71" s="251"/>
+      <c r="B71" s="253"/>
+      <c r="C71" s="254"/>
       <c r="D71" s="137" t="s">
         <v>22</v>
       </c>
@@ -6344,14 +6344,14 @@
       <c r="Q71" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R71" s="261"/>
-      <c r="S71" s="262"/>
+      <c r="R71" s="277"/>
+      <c r="S71" s="278"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B72" s="256" t="s">
+      <c r="B72" s="253" t="s">
         <v>64</v>
       </c>
-      <c r="C72" s="269" t="s">
+      <c r="C72" s="267" t="s">
         <v>29</v>
       </c>
       <c r="D72" s="137" t="s">
@@ -6399,14 +6399,14 @@
       <c r="Q72" s="211" t="s">
         <v>65</v>
       </c>
-      <c r="R72" s="263" t="s">
+      <c r="R72" s="259" t="s">
         <v>66</v>
       </c>
-      <c r="S72" s="264"/>
+      <c r="S72" s="260"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B73" s="256"/>
-      <c r="C73" s="270"/>
+      <c r="B73" s="253"/>
+      <c r="C73" s="276"/>
       <c r="D73" s="137" t="s">
         <v>22</v>
       </c>
@@ -6452,14 +6452,14 @@
       <c r="Q73" s="211" t="s">
         <v>65</v>
       </c>
-      <c r="R73" s="265"/>
-      <c r="S73" s="266"/>
+      <c r="R73" s="261"/>
+      <c r="S73" s="262"/>
     </row>
     <row r="74" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="256" t="s">
+      <c r="B74" s="253" t="s">
         <v>67</v>
       </c>
-      <c r="C74" s="251" t="s">
+      <c r="C74" s="254" t="s">
         <v>52</v>
       </c>
       <c r="D74" s="137" t="s">
@@ -6507,14 +6507,14 @@
       <c r="Q74" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R74" s="257" t="s">
+      <c r="R74" s="255" t="s">
         <v>55</v>
       </c>
-      <c r="S74" s="258"/>
+      <c r="S74" s="256"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B75" s="256"/>
-      <c r="C75" s="251"/>
+      <c r="B75" s="253"/>
+      <c r="C75" s="254"/>
       <c r="D75" s="137" t="s">
         <v>22</v>
       </c>
@@ -6560,14 +6560,14 @@
       <c r="Q75" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R75" s="259"/>
-      <c r="S75" s="260"/>
+      <c r="R75" s="257"/>
+      <c r="S75" s="258"/>
     </row>
     <row r="76" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="256" t="s">
+      <c r="B76" s="253" t="s">
         <v>68</v>
       </c>
-      <c r="C76" s="251" t="s">
+      <c r="C76" s="254" t="s">
         <v>52</v>
       </c>
       <c r="D76" s="137" t="s">
@@ -6615,12 +6615,12 @@
       <c r="Q76" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R76" s="259"/>
-      <c r="S76" s="260"/>
+      <c r="R76" s="257"/>
+      <c r="S76" s="258"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B77" s="256"/>
-      <c r="C77" s="251"/>
+      <c r="B77" s="253"/>
+      <c r="C77" s="254"/>
       <c r="D77" s="137" t="s">
         <v>22</v>
       </c>
@@ -6666,14 +6666,14 @@
       <c r="Q77" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R77" s="259"/>
-      <c r="S77" s="260"/>
+      <c r="R77" s="257"/>
+      <c r="S77" s="258"/>
     </row>
     <row r="78" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="256" t="s">
+      <c r="B78" s="253" t="s">
         <v>69</v>
       </c>
-      <c r="C78" s="251" t="s">
+      <c r="C78" s="254" t="s">
         <v>52</v>
       </c>
       <c r="D78" s="137" t="s">
@@ -6721,12 +6721,12 @@
       <c r="Q78" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R78" s="259"/>
-      <c r="S78" s="260"/>
+      <c r="R78" s="257"/>
+      <c r="S78" s="258"/>
     </row>
     <row r="79" spans="2:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="256"/>
-      <c r="C79" s="251"/>
+      <c r="B79" s="253"/>
+      <c r="C79" s="254"/>
       <c r="D79" s="137" t="s">
         <v>22</v>
       </c>
@@ -6772,8 +6772,8 @@
       <c r="Q79" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R79" s="261"/>
-      <c r="S79" s="262"/>
+      <c r="R79" s="277"/>
+      <c r="S79" s="278"/>
     </row>
     <row r="80" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B80" s="235" t="s">
@@ -6794,17 +6794,17 @@
       <c r="O80" s="236"/>
       <c r="P80" s="236"/>
       <c r="Q80" s="236"/>
-      <c r="R80" s="219"/>
-      <c r="S80" s="276"/>
+      <c r="R80" s="223"/>
+      <c r="S80" s="264"/>
     </row>
     <row r="81" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B81" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C81" s="273" t="s">
+      <c r="C81" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D81" s="274"/>
+      <c r="D81" s="251"/>
       <c r="E81" s="120" t="s">
         <v>3</v>
       </c>
@@ -6844,16 +6844,16 @@
       <c r="Q81" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R81" s="273" t="s">
+      <c r="R81" s="250" t="s">
         <v>36</v>
       </c>
-      <c r="S81" s="275"/>
+      <c r="S81" s="252"/>
     </row>
     <row r="82" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="277" t="s">
+      <c r="B82" s="265" t="s">
         <v>71</v>
       </c>
-      <c r="C82" s="269" t="s">
+      <c r="C82" s="267" t="s">
         <v>72</v>
       </c>
       <c r="D82" s="137" t="s">
@@ -6901,14 +6901,14 @@
       <c r="Q82" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R82" s="263" t="s">
+      <c r="R82" s="259" t="s">
         <v>73</v>
       </c>
-      <c r="S82" s="264"/>
+      <c r="S82" s="260"/>
     </row>
     <row r="83" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="278"/>
-      <c r="C83" s="279"/>
+      <c r="B83" s="266"/>
+      <c r="C83" s="268"/>
       <c r="D83" s="137" t="s">
         <v>22</v>
       </c>
@@ -6954,8 +6954,8 @@
       <c r="Q83" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R83" s="265"/>
-      <c r="S83" s="266"/>
+      <c r="R83" s="261"/>
+      <c r="S83" s="262"/>
     </row>
     <row r="84" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B84" s="235" t="s">
@@ -6977,16 +6977,16 @@
       <c r="P84" s="236"/>
       <c r="Q84" s="236"/>
       <c r="R84" s="236"/>
-      <c r="S84" s="253"/>
+      <c r="S84" s="263"/>
     </row>
     <row r="85" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B85" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="273" t="s">
+      <c r="C85" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D85" s="274"/>
+      <c r="D85" s="251"/>
       <c r="E85" s="120" t="s">
         <v>3</v>
       </c>
@@ -7026,16 +7026,16 @@
       <c r="Q85" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R85" s="273" t="s">
+      <c r="R85" s="250" t="s">
         <v>36</v>
       </c>
-      <c r="S85" s="275"/>
+      <c r="S85" s="252"/>
     </row>
     <row r="86" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="256" t="s">
-        <v>75</v>
-      </c>
-      <c r="C86" s="251" t="s">
+      <c r="B86" s="253" t="s">
+        <v>75</v>
+      </c>
+      <c r="C86" s="254" t="s">
         <v>72</v>
       </c>
       <c r="D86" s="137" t="s">
@@ -7083,14 +7083,14 @@
       <c r="Q86" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R86" s="263" t="s">
+      <c r="R86" s="259" t="s">
         <v>73</v>
       </c>
-      <c r="S86" s="264"/>
+      <c r="S86" s="260"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B87" s="256"/>
-      <c r="C87" s="251"/>
+      <c r="B87" s="253"/>
+      <c r="C87" s="254"/>
       <c r="D87" s="137" t="s">
         <v>22</v>
       </c>
@@ -7136,39 +7136,39 @@
       <c r="Q87" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R87" s="265"/>
-      <c r="S87" s="266"/>
+      <c r="R87" s="261"/>
+      <c r="S87" s="262"/>
     </row>
     <row r="88" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B88" s="215" t="s">
+      <c r="B88" s="233" t="s">
         <v>77</v>
       </c>
-      <c r="C88" s="216"/>
-      <c r="D88" s="216"/>
-      <c r="E88" s="216"/>
-      <c r="F88" s="216"/>
-      <c r="G88" s="216"/>
-      <c r="H88" s="216"/>
-      <c r="I88" s="216"/>
-      <c r="J88" s="216"/>
-      <c r="K88" s="216"/>
-      <c r="L88" s="216"/>
-      <c r="M88" s="216"/>
-      <c r="N88" s="216"/>
-      <c r="O88" s="216"/>
-      <c r="P88" s="216"/>
-      <c r="Q88" s="216"/>
-      <c r="R88" s="216"/>
-      <c r="S88" s="280"/>
+      <c r="C88" s="234"/>
+      <c r="D88" s="234"/>
+      <c r="E88" s="234"/>
+      <c r="F88" s="234"/>
+      <c r="G88" s="234"/>
+      <c r="H88" s="234"/>
+      <c r="I88" s="234"/>
+      <c r="J88" s="234"/>
+      <c r="K88" s="234"/>
+      <c r="L88" s="234"/>
+      <c r="M88" s="234"/>
+      <c r="N88" s="234"/>
+      <c r="O88" s="234"/>
+      <c r="P88" s="234"/>
+      <c r="Q88" s="234"/>
+      <c r="R88" s="234"/>
+      <c r="S88" s="269"/>
     </row>
     <row r="89" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B89" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C89" s="273" t="s">
+      <c r="C89" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D89" s="274"/>
+      <c r="D89" s="251"/>
       <c r="E89" s="120" t="s">
         <v>3</v>
       </c>
@@ -7208,16 +7208,16 @@
       <c r="Q89" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R89" s="273" t="s">
+      <c r="R89" s="250" t="s">
         <v>36</v>
       </c>
-      <c r="S89" s="275"/>
+      <c r="S89" s="252"/>
     </row>
     <row r="90" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="256" t="s">
+      <c r="B90" s="253" t="s">
         <v>78</v>
       </c>
-      <c r="C90" s="251" t="s">
+      <c r="C90" s="254" t="s">
         <v>72</v>
       </c>
       <c r="D90" s="137" t="s">
@@ -7265,14 +7265,14 @@
       <c r="Q90" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R90" s="263" t="s">
+      <c r="R90" s="259" t="s">
         <v>73</v>
       </c>
-      <c r="S90" s="264"/>
+      <c r="S90" s="260"/>
     </row>
     <row r="91" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="256"/>
-      <c r="C91" s="251"/>
+      <c r="B91" s="253"/>
+      <c r="C91" s="254"/>
       <c r="D91" s="137" t="s">
         <v>22</v>
       </c>
@@ -7318,39 +7318,39 @@
       <c r="Q91" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R91" s="265"/>
-      <c r="S91" s="266"/>
+      <c r="R91" s="261"/>
+      <c r="S91" s="262"/>
     </row>
     <row r="92" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B92" s="215" t="s">
+      <c r="B92" s="233" t="s">
         <v>79</v>
       </c>
-      <c r="C92" s="216"/>
-      <c r="D92" s="216"/>
-      <c r="E92" s="216"/>
-      <c r="F92" s="216"/>
-      <c r="G92" s="216"/>
-      <c r="H92" s="216"/>
-      <c r="I92" s="216"/>
-      <c r="J92" s="216"/>
-      <c r="K92" s="216"/>
-      <c r="L92" s="216"/>
-      <c r="M92" s="216"/>
-      <c r="N92" s="216"/>
-      <c r="O92" s="216"/>
-      <c r="P92" s="216"/>
-      <c r="Q92" s="216"/>
-      <c r="R92" s="216"/>
-      <c r="S92" s="280"/>
+      <c r="C92" s="234"/>
+      <c r="D92" s="234"/>
+      <c r="E92" s="234"/>
+      <c r="F92" s="234"/>
+      <c r="G92" s="234"/>
+      <c r="H92" s="234"/>
+      <c r="I92" s="234"/>
+      <c r="J92" s="234"/>
+      <c r="K92" s="234"/>
+      <c r="L92" s="234"/>
+      <c r="M92" s="234"/>
+      <c r="N92" s="234"/>
+      <c r="O92" s="234"/>
+      <c r="P92" s="234"/>
+      <c r="Q92" s="234"/>
+      <c r="R92" s="234"/>
+      <c r="S92" s="269"/>
     </row>
     <row r="93" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B93" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C93" s="273" t="s">
+      <c r="C93" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D93" s="274"/>
+      <c r="D93" s="251"/>
       <c r="E93" s="120" t="s">
         <v>3</v>
       </c>
@@ -7390,16 +7390,16 @@
       <c r="Q93" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R93" s="273" t="s">
+      <c r="R93" s="250" t="s">
         <v>36</v>
       </c>
-      <c r="S93" s="275"/>
+      <c r="S93" s="252"/>
     </row>
     <row r="94" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="256" t="s">
+      <c r="B94" s="253" t="s">
         <v>80</v>
       </c>
-      <c r="C94" s="251" t="s">
+      <c r="C94" s="254" t="s">
         <v>72</v>
       </c>
       <c r="D94" s="137" t="s">
@@ -7447,14 +7447,14 @@
       <c r="Q94" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R94" s="263" t="s">
+      <c r="R94" s="259" t="s">
         <v>73</v>
       </c>
-      <c r="S94" s="264"/>
+      <c r="S94" s="260"/>
     </row>
     <row r="95" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="256"/>
-      <c r="C95" s="251"/>
+      <c r="B95" s="253"/>
+      <c r="C95" s="254"/>
       <c r="D95" s="137" t="s">
         <v>22</v>
       </c>
@@ -7500,8 +7500,8 @@
       <c r="Q95" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R95" s="265"/>
-      <c r="S95" s="266"/>
+      <c r="R95" s="261"/>
+      <c r="S95" s="262"/>
     </row>
     <row r="96" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B96" s="235" t="s">
@@ -7522,17 +7522,17 @@
       <c r="O96" s="236"/>
       <c r="P96" s="236"/>
       <c r="Q96" s="236"/>
-      <c r="R96" s="219"/>
-      <c r="S96" s="219"/>
+      <c r="R96" s="223"/>
+      <c r="S96" s="223"/>
     </row>
     <row r="97" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B97" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C97" s="273" t="s">
+      <c r="C97" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D97" s="274"/>
+      <c r="D97" s="251"/>
       <c r="E97" s="120" t="s">
         <v>3</v>
       </c>
@@ -7572,16 +7572,16 @@
       <c r="Q97" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R97" s="273" t="s">
+      <c r="R97" s="250" t="s">
         <v>36</v>
       </c>
-      <c r="S97" s="275"/>
+      <c r="S97" s="252"/>
     </row>
     <row r="98" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B98" s="256" t="s">
+      <c r="B98" s="253" t="s">
         <v>84</v>
       </c>
-      <c r="C98" s="251" t="s">
+      <c r="C98" s="254" t="s">
         <v>72</v>
       </c>
       <c r="D98" s="137" t="s">
@@ -7629,15 +7629,15 @@
       <c r="Q98" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R98" s="257" t="s">
-        <v>85</v>
-      </c>
-      <c r="S98" s="258"/>
+      <c r="R98" s="255" t="s">
+        <v>85</v>
+      </c>
+      <c r="S98" s="256"/>
       <c r="T98"/>
     </row>
     <row r="99" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="256"/>
-      <c r="C99" s="251"/>
+      <c r="B99" s="253"/>
+      <c r="C99" s="254"/>
       <c r="D99" s="137" t="s">
         <v>22</v>
       </c>
@@ -7683,8 +7683,8 @@
       <c r="Q99" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R99" s="259"/>
-      <c r="S99" s="260"/>
+      <c r="R99" s="257"/>
+      <c r="S99" s="258"/>
       <c r="T99"/>
     </row>
     <row r="100" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
@@ -7707,16 +7707,16 @@
       <c r="P100" s="236"/>
       <c r="Q100" s="236"/>
       <c r="R100" s="236"/>
-      <c r="S100" s="253"/>
+      <c r="S100" s="263"/>
     </row>
     <row r="101" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B101" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C101" s="273" t="s">
+      <c r="C101" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D101" s="274"/>
+      <c r="D101" s="251"/>
       <c r="E101" s="120" t="s">
         <v>3</v>
       </c>
@@ -7756,16 +7756,16 @@
       <c r="Q101" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R101" s="273" t="s">
+      <c r="R101" s="250" t="s">
         <v>36</v>
       </c>
-      <c r="S101" s="275"/>
+      <c r="S101" s="252"/>
     </row>
     <row r="102" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B102" s="256" t="s">
+      <c r="B102" s="253" t="s">
         <v>87</v>
       </c>
-      <c r="C102" s="251" t="s">
+      <c r="C102" s="254" t="s">
         <v>29</v>
       </c>
       <c r="D102" s="137" t="s">
@@ -7813,15 +7813,15 @@
       <c r="Q102" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R102" s="257" t="s">
-        <v>85</v>
-      </c>
-      <c r="S102" s="258"/>
+      <c r="R102" s="255" t="s">
+        <v>85</v>
+      </c>
+      <c r="S102" s="256"/>
       <c r="T102"/>
     </row>
     <row r="103" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B103" s="256"/>
-      <c r="C103" s="251"/>
+      <c r="B103" s="253"/>
+      <c r="C103" s="254"/>
       <c r="D103" s="137" t="s">
         <v>22</v>
       </c>
@@ -7867,8 +7867,8 @@
       <c r="Q103" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R103" s="259"/>
-      <c r="S103" s="260"/>
+      <c r="R103" s="257"/>
+      <c r="S103" s="258"/>
       <c r="T103"/>
     </row>
     <row r="104" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7892,137 +7892,137 @@
       <c r="S104" s="134"/>
     </row>
     <row r="105" spans="2:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B105" s="281" t="s">
+      <c r="B105" s="238" t="s">
         <v>32</v>
       </c>
-      <c r="C105" s="282"/>
-      <c r="D105" s="282"/>
-      <c r="E105" s="282"/>
-      <c r="F105" s="282"/>
-      <c r="G105" s="282"/>
-      <c r="H105" s="282"/>
-      <c r="I105" s="282"/>
-      <c r="J105" s="282"/>
-      <c r="K105" s="282"/>
-      <c r="L105" s="282"/>
-      <c r="M105" s="282"/>
-      <c r="N105" s="282"/>
-      <c r="O105" s="282"/>
-      <c r="P105" s="282"/>
-      <c r="Q105" s="282"/>
-      <c r="R105" s="282"/>
-      <c r="S105" s="283"/>
+      <c r="C105" s="239"/>
+      <c r="D105" s="239"/>
+      <c r="E105" s="239"/>
+      <c r="F105" s="239"/>
+      <c r="G105" s="239"/>
+      <c r="H105" s="239"/>
+      <c r="I105" s="239"/>
+      <c r="J105" s="239"/>
+      <c r="K105" s="239"/>
+      <c r="L105" s="239"/>
+      <c r="M105" s="239"/>
+      <c r="N105" s="239"/>
+      <c r="O105" s="239"/>
+      <c r="P105" s="239"/>
+      <c r="Q105" s="239"/>
+      <c r="R105" s="239"/>
+      <c r="S105" s="240"/>
     </row>
     <row r="106" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B106" s="284" t="s">
+      <c r="B106" s="241" t="s">
         <v>33</v>
       </c>
-      <c r="C106" s="285"/>
-      <c r="D106" s="285"/>
-      <c r="E106" s="285"/>
-      <c r="F106" s="285"/>
-      <c r="G106" s="285"/>
-      <c r="H106" s="285"/>
-      <c r="I106" s="285"/>
-      <c r="J106" s="285"/>
-      <c r="K106" s="285"/>
-      <c r="L106" s="285"/>
-      <c r="M106" s="285"/>
-      <c r="N106" s="285"/>
-      <c r="O106" s="285"/>
-      <c r="P106" s="285"/>
-      <c r="Q106" s="285"/>
-      <c r="R106" s="285"/>
-      <c r="S106" s="286"/>
+      <c r="C106" s="242"/>
+      <c r="D106" s="242"/>
+      <c r="E106" s="242"/>
+      <c r="F106" s="242"/>
+      <c r="G106" s="242"/>
+      <c r="H106" s="242"/>
+      <c r="I106" s="242"/>
+      <c r="J106" s="242"/>
+      <c r="K106" s="242"/>
+      <c r="L106" s="242"/>
+      <c r="M106" s="242"/>
+      <c r="N106" s="242"/>
+      <c r="O106" s="242"/>
+      <c r="P106" s="242"/>
+      <c r="Q106" s="242"/>
+      <c r="R106" s="242"/>
+      <c r="S106" s="243"/>
     </row>
     <row r="107" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B107" s="284"/>
-      <c r="C107" s="285"/>
-      <c r="D107" s="285"/>
-      <c r="E107" s="285"/>
-      <c r="F107" s="285"/>
-      <c r="G107" s="285"/>
-      <c r="H107" s="285"/>
-      <c r="I107" s="285"/>
-      <c r="J107" s="285"/>
-      <c r="K107" s="285"/>
-      <c r="L107" s="285"/>
-      <c r="M107" s="285"/>
-      <c r="N107" s="285"/>
-      <c r="O107" s="285"/>
-      <c r="P107" s="285"/>
-      <c r="Q107" s="285"/>
-      <c r="R107" s="285"/>
-      <c r="S107" s="286"/>
+      <c r="B107" s="241"/>
+      <c r="C107" s="242"/>
+      <c r="D107" s="242"/>
+      <c r="E107" s="242"/>
+      <c r="F107" s="242"/>
+      <c r="G107" s="242"/>
+      <c r="H107" s="242"/>
+      <c r="I107" s="242"/>
+      <c r="J107" s="242"/>
+      <c r="K107" s="242"/>
+      <c r="L107" s="242"/>
+      <c r="M107" s="242"/>
+      <c r="N107" s="242"/>
+      <c r="O107" s="242"/>
+      <c r="P107" s="242"/>
+      <c r="Q107" s="242"/>
+      <c r="R107" s="242"/>
+      <c r="S107" s="243"/>
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B108" s="284"/>
-      <c r="C108" s="285"/>
-      <c r="D108" s="285"/>
-      <c r="E108" s="285"/>
-      <c r="F108" s="285"/>
-      <c r="G108" s="285"/>
-      <c r="H108" s="285"/>
-      <c r="I108" s="285"/>
-      <c r="J108" s="285"/>
-      <c r="K108" s="285"/>
-      <c r="L108" s="285"/>
-      <c r="M108" s="285"/>
-      <c r="N108" s="285"/>
-      <c r="O108" s="285"/>
-      <c r="P108" s="285"/>
-      <c r="Q108" s="285"/>
-      <c r="R108" s="285"/>
-      <c r="S108" s="286"/>
+      <c r="B108" s="241"/>
+      <c r="C108" s="242"/>
+      <c r="D108" s="242"/>
+      <c r="E108" s="242"/>
+      <c r="F108" s="242"/>
+      <c r="G108" s="242"/>
+      <c r="H108" s="242"/>
+      <c r="I108" s="242"/>
+      <c r="J108" s="242"/>
+      <c r="K108" s="242"/>
+      <c r="L108" s="242"/>
+      <c r="M108" s="242"/>
+      <c r="N108" s="242"/>
+      <c r="O108" s="242"/>
+      <c r="P108" s="242"/>
+      <c r="Q108" s="242"/>
+      <c r="R108" s="242"/>
+      <c r="S108" s="243"/>
     </row>
     <row r="109" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="287"/>
-      <c r="C109" s="288"/>
-      <c r="D109" s="288"/>
-      <c r="E109" s="288"/>
-      <c r="F109" s="288"/>
-      <c r="G109" s="288"/>
-      <c r="H109" s="288"/>
-      <c r="I109" s="288"/>
-      <c r="J109" s="288"/>
-      <c r="K109" s="288"/>
-      <c r="L109" s="288"/>
-      <c r="M109" s="288"/>
-      <c r="N109" s="288"/>
-      <c r="O109" s="288"/>
-      <c r="P109" s="288"/>
-      <c r="Q109" s="288"/>
-      <c r="R109" s="288"/>
-      <c r="S109" s="289"/>
+      <c r="B109" s="244"/>
+      <c r="C109" s="245"/>
+      <c r="D109" s="245"/>
+      <c r="E109" s="245"/>
+      <c r="F109" s="245"/>
+      <c r="G109" s="245"/>
+      <c r="H109" s="245"/>
+      <c r="I109" s="245"/>
+      <c r="J109" s="245"/>
+      <c r="K109" s="245"/>
+      <c r="L109" s="245"/>
+      <c r="M109" s="245"/>
+      <c r="N109" s="245"/>
+      <c r="O109" s="245"/>
+      <c r="P109" s="245"/>
+      <c r="Q109" s="245"/>
+      <c r="R109" s="245"/>
+      <c r="S109" s="246"/>
     </row>
     <row r="118" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B118" s="290" t="s">
+      <c r="B118" s="247" t="s">
         <v>88</v>
       </c>
-      <c r="C118" s="290"/>
-      <c r="D118" s="290"/>
-      <c r="E118" s="290"/>
-      <c r="F118" s="290"/>
-      <c r="G118" s="290"/>
-      <c r="H118" s="290"/>
-      <c r="I118" s="290"/>
-      <c r="J118" s="290"/>
-      <c r="K118" s="290"/>
-      <c r="L118" s="290"/>
-      <c r="M118" s="290"/>
-      <c r="N118" s="290"/>
-      <c r="O118" s="290"/>
-      <c r="P118" s="290"/>
+      <c r="C118" s="247"/>
+      <c r="D118" s="247"/>
+      <c r="E118" s="247"/>
+      <c r="F118" s="247"/>
+      <c r="G118" s="247"/>
+      <c r="H118" s="247"/>
+      <c r="I118" s="247"/>
+      <c r="J118" s="247"/>
+      <c r="K118" s="247"/>
+      <c r="L118" s="247"/>
+      <c r="M118" s="247"/>
+      <c r="N118" s="247"/>
+      <c r="O118" s="247"/>
+      <c r="P118" s="247"/>
       <c r="Q118" s="129"/>
     </row>
     <row r="119" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B119" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="C119" s="220" t="s">
+      <c r="C119" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D119" s="220"/>
+      <c r="D119" s="221"/>
       <c r="E119" s="120" t="s">
         <v>3</v>
       </c>
@@ -8053,17 +8053,17 @@
       <c r="N119" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="O119" s="220" t="s">
+      <c r="O119" s="221" t="s">
         <v>36</v>
       </c>
-      <c r="P119" s="220"/>
-      <c r="Q119" s="220"/>
+      <c r="P119" s="221"/>
+      <c r="Q119" s="221"/>
     </row>
     <row r="120" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="217" t="s">
+      <c r="B120" s="224" t="s">
         <v>90</v>
       </c>
-      <c r="C120" s="242" t="s">
+      <c r="C120" s="248" t="s">
         <v>16</v>
       </c>
       <c r="D120" s="20" t="s">
@@ -8108,8 +8108,8 @@
       <c r="Q120" s="249"/>
     </row>
     <row r="121" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B121" s="217"/>
-      <c r="C121" s="242"/>
+      <c r="B121" s="224"/>
+      <c r="C121" s="248"/>
       <c r="D121" s="20" t="s">
         <v>22</v>
       </c>
@@ -8188,78 +8188,78 @@
       <c r="Q123" s="7"/>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B124" s="227" t="s">
+      <c r="B124" s="215" t="s">
         <v>33</v>
       </c>
-      <c r="C124" s="228"/>
-      <c r="D124" s="228"/>
-      <c r="E124" s="228"/>
-      <c r="F124" s="228"/>
-      <c r="G124" s="228"/>
-      <c r="H124" s="228"/>
-      <c r="I124" s="228"/>
-      <c r="J124" s="228"/>
-      <c r="K124" s="228"/>
-      <c r="L124" s="228"/>
-      <c r="M124" s="228"/>
-      <c r="N124" s="228"/>
-      <c r="O124" s="228"/>
-      <c r="P124" s="228"/>
-      <c r="Q124" s="229"/>
+      <c r="C124" s="216"/>
+      <c r="D124" s="216"/>
+      <c r="E124" s="216"/>
+      <c r="F124" s="216"/>
+      <c r="G124" s="216"/>
+      <c r="H124" s="216"/>
+      <c r="I124" s="216"/>
+      <c r="J124" s="216"/>
+      <c r="K124" s="216"/>
+      <c r="L124" s="216"/>
+      <c r="M124" s="216"/>
+      <c r="N124" s="216"/>
+      <c r="O124" s="216"/>
+      <c r="P124" s="216"/>
+      <c r="Q124" s="217"/>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B125" s="227"/>
-      <c r="C125" s="228"/>
-      <c r="D125" s="228"/>
-      <c r="E125" s="228"/>
-      <c r="F125" s="228"/>
-      <c r="G125" s="228"/>
-      <c r="H125" s="228"/>
-      <c r="I125" s="228"/>
-      <c r="J125" s="228"/>
-      <c r="K125" s="228"/>
-      <c r="L125" s="228"/>
-      <c r="M125" s="228"/>
-      <c r="N125" s="228"/>
-      <c r="O125" s="228"/>
-      <c r="P125" s="228"/>
-      <c r="Q125" s="229"/>
+      <c r="B125" s="215"/>
+      <c r="C125" s="216"/>
+      <c r="D125" s="216"/>
+      <c r="E125" s="216"/>
+      <c r="F125" s="216"/>
+      <c r="G125" s="216"/>
+      <c r="H125" s="216"/>
+      <c r="I125" s="216"/>
+      <c r="J125" s="216"/>
+      <c r="K125" s="216"/>
+      <c r="L125" s="216"/>
+      <c r="M125" s="216"/>
+      <c r="N125" s="216"/>
+      <c r="O125" s="216"/>
+      <c r="P125" s="216"/>
+      <c r="Q125" s="217"/>
     </row>
     <row r="126" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B126" s="227"/>
-      <c r="C126" s="228"/>
-      <c r="D126" s="228"/>
-      <c r="E126" s="228"/>
-      <c r="F126" s="228"/>
-      <c r="G126" s="228"/>
-      <c r="H126" s="228"/>
-      <c r="I126" s="228"/>
-      <c r="J126" s="228"/>
-      <c r="K126" s="228"/>
-      <c r="L126" s="228"/>
-      <c r="M126" s="228"/>
-      <c r="N126" s="228"/>
-      <c r="O126" s="228"/>
-      <c r="P126" s="228"/>
-      <c r="Q126" s="229"/>
+      <c r="B126" s="215"/>
+      <c r="C126" s="216"/>
+      <c r="D126" s="216"/>
+      <c r="E126" s="216"/>
+      <c r="F126" s="216"/>
+      <c r="G126" s="216"/>
+      <c r="H126" s="216"/>
+      <c r="I126" s="216"/>
+      <c r="J126" s="216"/>
+      <c r="K126" s="216"/>
+      <c r="L126" s="216"/>
+      <c r="M126" s="216"/>
+      <c r="N126" s="216"/>
+      <c r="O126" s="216"/>
+      <c r="P126" s="216"/>
+      <c r="Q126" s="217"/>
     </row>
     <row r="127" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B127" s="230"/>
-      <c r="C127" s="231"/>
-      <c r="D127" s="231"/>
-      <c r="E127" s="231"/>
-      <c r="F127" s="231"/>
-      <c r="G127" s="231"/>
-      <c r="H127" s="231"/>
-      <c r="I127" s="231"/>
-      <c r="J127" s="231"/>
-      <c r="K127" s="231"/>
-      <c r="L127" s="231"/>
-      <c r="M127" s="231"/>
-      <c r="N127" s="231"/>
-      <c r="O127" s="231"/>
-      <c r="P127" s="231"/>
-      <c r="Q127" s="232"/>
+      <c r="B127" s="218"/>
+      <c r="C127" s="219"/>
+      <c r="D127" s="219"/>
+      <c r="E127" s="219"/>
+      <c r="F127" s="219"/>
+      <c r="G127" s="219"/>
+      <c r="H127" s="219"/>
+      <c r="I127" s="219"/>
+      <c r="J127" s="219"/>
+      <c r="K127" s="219"/>
+      <c r="L127" s="219"/>
+      <c r="M127" s="219"/>
+      <c r="N127" s="219"/>
+      <c r="O127" s="219"/>
+      <c r="P127" s="219"/>
+      <c r="Q127" s="220"/>
     </row>
     <row r="128" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B128" s="35"/>
@@ -8303,10 +8303,10 @@
       <c r="B135" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C135" s="220" t="s">
+      <c r="C135" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D135" s="220"/>
+      <c r="D135" s="221"/>
       <c r="E135" s="120" t="s">
         <v>3</v>
       </c>
@@ -8397,7 +8397,7 @@
       <c r="B137" s="237" t="s">
         <v>96</v>
       </c>
-      <c r="C137" s="217" t="s">
+      <c r="C137" s="224" t="s">
         <v>29</v>
       </c>
       <c r="D137" s="117" t="s">
@@ -8445,7 +8445,7 @@
     </row>
     <row r="138" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B138" s="237"/>
-      <c r="C138" s="217"/>
+      <c r="C138" s="224"/>
       <c r="D138" s="117" t="s">
         <v>22</v>
       </c>
@@ -8513,10 +8513,10 @@
       <c r="B142" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C142" s="220" t="s">
+      <c r="C142" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D142" s="220"/>
+      <c r="D142" s="221"/>
       <c r="E142" s="120" t="s">
         <v>3</v>
       </c>
@@ -8555,10 +8555,10 @@
       </c>
     </row>
     <row r="143" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B143" s="217" t="s">
+      <c r="B143" s="224" t="s">
         <v>98</v>
       </c>
-      <c r="C143" s="217" t="s">
+      <c r="C143" s="224" t="s">
         <v>16</v>
       </c>
       <c r="D143" s="117" t="s">
@@ -8604,8 +8604,8 @@
       </c>
     </row>
     <row r="144" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B144" s="217"/>
-      <c r="C144" s="217"/>
+      <c r="B144" s="224"/>
+      <c r="C144" s="224"/>
       <c r="D144" s="117" t="s">
         <v>22</v>
       </c>
@@ -8649,10 +8649,10 @@
       </c>
     </row>
     <row r="145" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B145" s="217" t="s">
+      <c r="B145" s="224" t="s">
         <v>100</v>
       </c>
-      <c r="C145" s="217" t="s">
+      <c r="C145" s="224" t="s">
         <v>29</v>
       </c>
       <c r="D145" s="117" t="s">
@@ -8698,8 +8698,8 @@
       </c>
     </row>
     <row r="146" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B146" s="217"/>
-      <c r="C146" s="217"/>
+      <c r="B146" s="224"/>
+      <c r="C146" s="224"/>
       <c r="D146" s="117" t="s">
         <v>22</v>
       </c>
@@ -8769,78 +8769,78 @@
       <c r="Q148" s="7"/>
     </row>
     <row r="149" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B149" s="227" t="s">
+      <c r="B149" s="215" t="s">
         <v>33</v>
       </c>
-      <c r="C149" s="228"/>
-      <c r="D149" s="228"/>
-      <c r="E149" s="228"/>
-      <c r="F149" s="228"/>
-      <c r="G149" s="228"/>
-      <c r="H149" s="228"/>
-      <c r="I149" s="228"/>
-      <c r="J149" s="228"/>
-      <c r="K149" s="228"/>
-      <c r="L149" s="228"/>
-      <c r="M149" s="228"/>
-      <c r="N149" s="228"/>
-      <c r="O149" s="228"/>
-      <c r="P149" s="228"/>
-      <c r="Q149" s="229"/>
+      <c r="C149" s="216"/>
+      <c r="D149" s="216"/>
+      <c r="E149" s="216"/>
+      <c r="F149" s="216"/>
+      <c r="G149" s="216"/>
+      <c r="H149" s="216"/>
+      <c r="I149" s="216"/>
+      <c r="J149" s="216"/>
+      <c r="K149" s="216"/>
+      <c r="L149" s="216"/>
+      <c r="M149" s="216"/>
+      <c r="N149" s="216"/>
+      <c r="O149" s="216"/>
+      <c r="P149" s="216"/>
+      <c r="Q149" s="217"/>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B150" s="227"/>
-      <c r="C150" s="228"/>
-      <c r="D150" s="228"/>
-      <c r="E150" s="228"/>
-      <c r="F150" s="228"/>
-      <c r="G150" s="228"/>
-      <c r="H150" s="228"/>
-      <c r="I150" s="228"/>
-      <c r="J150" s="228"/>
-      <c r="K150" s="228"/>
-      <c r="L150" s="228"/>
-      <c r="M150" s="228"/>
-      <c r="N150" s="228"/>
-      <c r="O150" s="228"/>
-      <c r="P150" s="228"/>
-      <c r="Q150" s="229"/>
+      <c r="B150" s="215"/>
+      <c r="C150" s="216"/>
+      <c r="D150" s="216"/>
+      <c r="E150" s="216"/>
+      <c r="F150" s="216"/>
+      <c r="G150" s="216"/>
+      <c r="H150" s="216"/>
+      <c r="I150" s="216"/>
+      <c r="J150" s="216"/>
+      <c r="K150" s="216"/>
+      <c r="L150" s="216"/>
+      <c r="M150" s="216"/>
+      <c r="N150" s="216"/>
+      <c r="O150" s="216"/>
+      <c r="P150" s="216"/>
+      <c r="Q150" s="217"/>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B151" s="227"/>
-      <c r="C151" s="228"/>
-      <c r="D151" s="228"/>
-      <c r="E151" s="228"/>
-      <c r="F151" s="228"/>
-      <c r="G151" s="228"/>
-      <c r="H151" s="228"/>
-      <c r="I151" s="228"/>
-      <c r="J151" s="228"/>
-      <c r="K151" s="228"/>
-      <c r="L151" s="228"/>
-      <c r="M151" s="228"/>
-      <c r="N151" s="228"/>
-      <c r="O151" s="228"/>
-      <c r="P151" s="228"/>
-      <c r="Q151" s="229"/>
+      <c r="B151" s="215"/>
+      <c r="C151" s="216"/>
+      <c r="D151" s="216"/>
+      <c r="E151" s="216"/>
+      <c r="F151" s="216"/>
+      <c r="G151" s="216"/>
+      <c r="H151" s="216"/>
+      <c r="I151" s="216"/>
+      <c r="J151" s="216"/>
+      <c r="K151" s="216"/>
+      <c r="L151" s="216"/>
+      <c r="M151" s="216"/>
+      <c r="N151" s="216"/>
+      <c r="O151" s="216"/>
+      <c r="P151" s="216"/>
+      <c r="Q151" s="217"/>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B152" s="230"/>
-      <c r="C152" s="231"/>
-      <c r="D152" s="231"/>
-      <c r="E152" s="231"/>
-      <c r="F152" s="231"/>
-      <c r="G152" s="231"/>
-      <c r="H152" s="231"/>
-      <c r="I152" s="231"/>
-      <c r="J152" s="231"/>
-      <c r="K152" s="231"/>
-      <c r="L152" s="231"/>
-      <c r="M152" s="231"/>
-      <c r="N152" s="231"/>
-      <c r="O152" s="231"/>
-      <c r="P152" s="231"/>
-      <c r="Q152" s="232"/>
+      <c r="B152" s="218"/>
+      <c r="C152" s="219"/>
+      <c r="D152" s="219"/>
+      <c r="E152" s="219"/>
+      <c r="F152" s="219"/>
+      <c r="G152" s="219"/>
+      <c r="H152" s="219"/>
+      <c r="I152" s="219"/>
+      <c r="J152" s="219"/>
+      <c r="K152" s="219"/>
+      <c r="L152" s="219"/>
+      <c r="M152" s="219"/>
+      <c r="N152" s="219"/>
+      <c r="O152" s="219"/>
+      <c r="P152" s="219"/>
+      <c r="Q152" s="220"/>
     </row>
     <row r="154" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B154" s="35"/>
@@ -8883,10 +8883,10 @@
       <c r="B161" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C161" s="220" t="s">
+      <c r="C161" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D161" s="220"/>
+      <c r="D161" s="221"/>
       <c r="E161" s="120" t="s">
         <v>3</v>
       </c>
@@ -8928,7 +8928,7 @@
       <c r="B162" s="237" t="s">
         <v>102</v>
       </c>
-      <c r="C162" s="217" t="s">
+      <c r="C162" s="224" t="s">
         <v>103</v>
       </c>
       <c r="D162" s="117" t="s">
@@ -8975,7 +8975,7 @@
     </row>
     <row r="163" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B163" s="237"/>
-      <c r="C163" s="217"/>
+      <c r="C163" s="224"/>
       <c r="D163" s="117" t="s">
         <v>22</v>
       </c>
@@ -9039,78 +9039,78 @@
       <c r="Q165" s="7"/>
     </row>
     <row r="166" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B166" s="227" t="s">
+      <c r="B166" s="215" t="s">
         <v>33</v>
       </c>
-      <c r="C166" s="228"/>
-      <c r="D166" s="228"/>
-      <c r="E166" s="228"/>
-      <c r="F166" s="228"/>
-      <c r="G166" s="228"/>
-      <c r="H166" s="228"/>
-      <c r="I166" s="228"/>
-      <c r="J166" s="228"/>
-      <c r="K166" s="228"/>
-      <c r="L166" s="228"/>
-      <c r="M166" s="228"/>
-      <c r="N166" s="228"/>
-      <c r="O166" s="228"/>
-      <c r="P166" s="228"/>
-      <c r="Q166" s="229"/>
+      <c r="C166" s="216"/>
+      <c r="D166" s="216"/>
+      <c r="E166" s="216"/>
+      <c r="F166" s="216"/>
+      <c r="G166" s="216"/>
+      <c r="H166" s="216"/>
+      <c r="I166" s="216"/>
+      <c r="J166" s="216"/>
+      <c r="K166" s="216"/>
+      <c r="L166" s="216"/>
+      <c r="M166" s="216"/>
+      <c r="N166" s="216"/>
+      <c r="O166" s="216"/>
+      <c r="P166" s="216"/>
+      <c r="Q166" s="217"/>
     </row>
     <row r="167" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B167" s="227"/>
-      <c r="C167" s="228"/>
-      <c r="D167" s="228"/>
-      <c r="E167" s="228"/>
-      <c r="F167" s="228"/>
-      <c r="G167" s="228"/>
-      <c r="H167" s="228"/>
-      <c r="I167" s="228"/>
-      <c r="J167" s="228"/>
-      <c r="K167" s="228"/>
-      <c r="L167" s="228"/>
-      <c r="M167" s="228"/>
-      <c r="N167" s="228"/>
-      <c r="O167" s="228"/>
-      <c r="P167" s="228"/>
-      <c r="Q167" s="229"/>
+      <c r="B167" s="215"/>
+      <c r="C167" s="216"/>
+      <c r="D167" s="216"/>
+      <c r="E167" s="216"/>
+      <c r="F167" s="216"/>
+      <c r="G167" s="216"/>
+      <c r="H167" s="216"/>
+      <c r="I167" s="216"/>
+      <c r="J167" s="216"/>
+      <c r="K167" s="216"/>
+      <c r="L167" s="216"/>
+      <c r="M167" s="216"/>
+      <c r="N167" s="216"/>
+      <c r="O167" s="216"/>
+      <c r="P167" s="216"/>
+      <c r="Q167" s="217"/>
     </row>
     <row r="168" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B168" s="227"/>
-      <c r="C168" s="228"/>
-      <c r="D168" s="228"/>
-      <c r="E168" s="228"/>
-      <c r="F168" s="228"/>
-      <c r="G168" s="228"/>
-      <c r="H168" s="228"/>
-      <c r="I168" s="228"/>
-      <c r="J168" s="228"/>
-      <c r="K168" s="228"/>
-      <c r="L168" s="228"/>
-      <c r="M168" s="228"/>
-      <c r="N168" s="228"/>
-      <c r="O168" s="228"/>
-      <c r="P168" s="228"/>
-      <c r="Q168" s="229"/>
+      <c r="B168" s="215"/>
+      <c r="C168" s="216"/>
+      <c r="D168" s="216"/>
+      <c r="E168" s="216"/>
+      <c r="F168" s="216"/>
+      <c r="G168" s="216"/>
+      <c r="H168" s="216"/>
+      <c r="I168" s="216"/>
+      <c r="J168" s="216"/>
+      <c r="K168" s="216"/>
+      <c r="L168" s="216"/>
+      <c r="M168" s="216"/>
+      <c r="N168" s="216"/>
+      <c r="O168" s="216"/>
+      <c r="P168" s="216"/>
+      <c r="Q168" s="217"/>
     </row>
     <row r="169" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B169" s="230"/>
-      <c r="C169" s="231"/>
-      <c r="D169" s="231"/>
-      <c r="E169" s="231"/>
-      <c r="F169" s="231"/>
-      <c r="G169" s="231"/>
-      <c r="H169" s="231"/>
-      <c r="I169" s="231"/>
-      <c r="J169" s="231"/>
-      <c r="K169" s="231"/>
-      <c r="L169" s="231"/>
-      <c r="M169" s="231"/>
-      <c r="N169" s="231"/>
-      <c r="O169" s="231"/>
-      <c r="P169" s="231"/>
-      <c r="Q169" s="232"/>
+      <c r="B169" s="218"/>
+      <c r="C169" s="219"/>
+      <c r="D169" s="219"/>
+      <c r="E169" s="219"/>
+      <c r="F169" s="219"/>
+      <c r="G169" s="219"/>
+      <c r="H169" s="219"/>
+      <c r="I169" s="219"/>
+      <c r="J169" s="219"/>
+      <c r="K169" s="219"/>
+      <c r="L169" s="219"/>
+      <c r="M169" s="219"/>
+      <c r="N169" s="219"/>
+      <c r="O169" s="219"/>
+      <c r="P169" s="219"/>
+      <c r="Q169" s="220"/>
     </row>
     <row r="170" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B170" s="35"/>
@@ -9149,33 +9149,33 @@
       <c r="Q171" s="35"/>
     </row>
     <row r="173" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B173" s="218" t="s">
+      <c r="B173" s="222" t="s">
         <v>104</v>
       </c>
-      <c r="C173" s="219"/>
-      <c r="D173" s="219"/>
-      <c r="E173" s="219"/>
-      <c r="F173" s="219"/>
-      <c r="G173" s="219"/>
-      <c r="H173" s="219"/>
-      <c r="I173" s="219"/>
-      <c r="J173" s="219"/>
-      <c r="K173" s="219"/>
-      <c r="L173" s="219"/>
-      <c r="M173" s="219"/>
-      <c r="N173" s="219"/>
-      <c r="O173" s="219"/>
-      <c r="P173" s="219"/>
-      <c r="Q173" s="219"/>
+      <c r="C173" s="223"/>
+      <c r="D173" s="223"/>
+      <c r="E173" s="223"/>
+      <c r="F173" s="223"/>
+      <c r="G173" s="223"/>
+      <c r="H173" s="223"/>
+      <c r="I173" s="223"/>
+      <c r="J173" s="223"/>
+      <c r="K173" s="223"/>
+      <c r="L173" s="223"/>
+      <c r="M173" s="223"/>
+      <c r="N173" s="223"/>
+      <c r="O173" s="223"/>
+      <c r="P173" s="223"/>
+      <c r="Q173" s="223"/>
     </row>
     <row r="174" spans="2:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B174" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C174" s="220" t="s">
+      <c r="C174" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D174" s="220"/>
+      <c r="D174" s="221"/>
       <c r="E174" s="120" t="s">
         <v>3</v>
       </c>
@@ -9217,10 +9217,10 @@
       </c>
     </row>
     <row r="175" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B175" s="221" t="s">
+      <c r="B175" s="227" t="s">
         <v>110</v>
       </c>
-      <c r="C175" s="217" t="s">
+      <c r="C175" s="224" t="s">
         <v>29</v>
       </c>
       <c r="D175" s="117" t="s">
@@ -9269,8 +9269,8 @@
       </c>
     </row>
     <row r="176" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B176" s="222"/>
-      <c r="C176" s="217"/>
+      <c r="B176" s="228"/>
+      <c r="C176" s="224"/>
       <c r="D176" s="117" t="s">
         <v>22</v>
       </c>
@@ -9357,10 +9357,10 @@
       <c r="B187" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C187" s="220" t="s">
+      <c r="C187" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D187" s="220"/>
+      <c r="D187" s="221"/>
       <c r="E187" s="120" t="s">
         <v>3</v>
       </c>
@@ -9402,7 +9402,7 @@
       <c r="B188" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="C188" s="217" t="s">
+      <c r="C188" s="224" t="s">
         <v>81</v>
       </c>
       <c r="D188" s="117" t="s">
@@ -9449,7 +9449,7 @@
     </row>
     <row r="189" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B189" s="237"/>
-      <c r="C189" s="217"/>
+      <c r="C189" s="224"/>
       <c r="D189" s="117" t="s">
         <v>22</v>
       </c>
@@ -9497,62 +9497,48 @@
     </row>
   </sheetData>
   <mergeCells count="122">
-    <mergeCell ref="B160:P160"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="B166:Q169"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="C145:C146"/>
-    <mergeCell ref="B149:Q152"/>
-    <mergeCell ref="B124:Q127"/>
-    <mergeCell ref="B134:P134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="B141:P141"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="B105:S105"/>
-    <mergeCell ref="B106:S109"/>
-    <mergeCell ref="B118:P118"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="O119:Q119"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="O120:Q121"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="R101:S101"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="R102:S103"/>
-    <mergeCell ref="B96:S96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="R97:S97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="R98:S99"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="R94:S95"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="R89:S89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="R90:S91"/>
-    <mergeCell ref="B100:S100"/>
-    <mergeCell ref="R86:S87"/>
-    <mergeCell ref="B80:S80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="R82:S83"/>
-    <mergeCell ref="B92:S92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="B88:S88"/>
+    <mergeCell ref="B186:P186"/>
+    <mergeCell ref="C187:D187"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="C188:C189"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="B175:B176"/>
+    <mergeCell ref="C175:C176"/>
+    <mergeCell ref="B8:P8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B35:P35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="O37:P38"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B24:P27"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="B43:Q46"/>
+    <mergeCell ref="B56:S56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="R58:S61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="R74:S79"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
     <mergeCell ref="B173:Q173"/>
     <mergeCell ref="R72:S73"/>
     <mergeCell ref="B62:B63"/>
@@ -9577,48 +9563,62 @@
     <mergeCell ref="B86:B87"/>
     <mergeCell ref="C86:C87"/>
     <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B24:P27"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="B43:Q46"/>
-    <mergeCell ref="B56:S56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="R58:S61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="R74:S79"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="B186:P186"/>
-    <mergeCell ref="C187:D187"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="C188:C189"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="B175:B176"/>
-    <mergeCell ref="C175:C176"/>
-    <mergeCell ref="B8:P8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B35:P35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="O37:P38"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="R86:S87"/>
+    <mergeCell ref="B80:S80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="R82:S83"/>
+    <mergeCell ref="B92:S92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="B88:S88"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="R94:S95"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="R89:S89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="R90:S91"/>
+    <mergeCell ref="B100:S100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="R101:S101"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="R102:S103"/>
+    <mergeCell ref="B96:S96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="R97:S97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="R98:S99"/>
+    <mergeCell ref="B124:Q127"/>
+    <mergeCell ref="B134:P134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="B141:P141"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="B105:S105"/>
+    <mergeCell ref="B106:S109"/>
+    <mergeCell ref="B118:P118"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="O119:Q119"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="O120:Q121"/>
+    <mergeCell ref="B160:P160"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="B166:Q169"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="C145:C146"/>
+    <mergeCell ref="B149:Q152"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9655,33 +9655,33 @@
   </cols>
   <sheetData>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="219" t="s">
+      <c r="B9" s="223" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="219"/>
-      <c r="D9" s="219"/>
-      <c r="E9" s="219"/>
-      <c r="F9" s="219"/>
-      <c r="G9" s="219"/>
-      <c r="H9" s="219"/>
-      <c r="I9" s="219"/>
-      <c r="J9" s="219"/>
-      <c r="K9" s="219"/>
-      <c r="L9" s="219"/>
-      <c r="M9" s="219"/>
-      <c r="N9" s="219"/>
-      <c r="O9" s="219"/>
-      <c r="P9" s="219"/>
-      <c r="Q9" s="219"/>
+      <c r="C9" s="223"/>
+      <c r="D9" s="223"/>
+      <c r="E9" s="223"/>
+      <c r="F9" s="223"/>
+      <c r="G9" s="223"/>
+      <c r="H9" s="223"/>
+      <c r="I9" s="223"/>
+      <c r="J9" s="223"/>
+      <c r="K9" s="223"/>
+      <c r="L9" s="223"/>
+      <c r="M9" s="223"/>
+      <c r="N9" s="223"/>
+      <c r="O9" s="223"/>
+      <c r="P9" s="223"/>
+      <c r="Q9" s="223"/>
     </row>
     <row r="10" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="306" t="s">
+      <c r="C10" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="306"/>
+      <c r="D10" s="303"/>
       <c r="E10" s="8" t="s">
         <v>3</v>
       </c>
@@ -9721,10 +9721,10 @@
       <c r="Q10" s="17"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="242" t="s">
+      <c r="B11" s="248" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="242" t="s">
+      <c r="C11" s="248" t="s">
         <v>110</v>
       </c>
       <c r="D11" s="53" t="s">
@@ -9772,8 +9772,8 @@
       <c r="Q11" s="49"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="242"/>
-      <c r="C12" s="242"/>
+      <c r="B12" s="248"/>
+      <c r="C12" s="248"/>
       <c r="D12" s="53" t="s">
         <v>22</v>
       </c>
@@ -9819,10 +9819,10 @@
       <c r="Q12" s="49"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="242" t="s">
+      <c r="B13" s="248" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="242" t="s">
+      <c r="C13" s="248" t="s">
         <v>110</v>
       </c>
       <c r="D13" s="53" t="s">
@@ -9870,8 +9870,8 @@
       <c r="Q13" s="49"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="242"/>
-      <c r="C14" s="242"/>
+      <c r="B14" s="248"/>
+      <c r="C14" s="248"/>
       <c r="D14" s="53" t="s">
         <v>22</v>
       </c>
@@ -9917,10 +9917,10 @@
       <c r="Q14" s="49"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="286" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="242" t="s">
+      <c r="C15" s="248" t="s">
         <v>110</v>
       </c>
       <c r="D15" s="53" t="s">
@@ -9968,8 +9968,8 @@
       <c r="Q15" s="49"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="240"/>
-      <c r="C16" s="242"/>
+      <c r="B16" s="286"/>
+      <c r="C16" s="248"/>
       <c r="D16" s="53" t="s">
         <v>22</v>
       </c>
@@ -10015,10 +10015,10 @@
       <c r="Q16" s="49"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="242" t="s">
+      <c r="B17" s="248" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="242" t="s">
+      <c r="C17" s="248" t="s">
         <v>110</v>
       </c>
       <c r="D17" s="53" t="s">
@@ -10066,8 +10066,8 @@
       <c r="Q17" s="49"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="242"/>
-      <c r="C18" s="242"/>
+      <c r="B18" s="248"/>
+      <c r="C18" s="248"/>
       <c r="D18" s="53" t="s">
         <v>22</v>
       </c>
@@ -10130,103 +10130,103 @@
       <c r="Q19" s="34"/>
     </row>
     <row r="20" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="309" t="s">
+      <c r="B20" s="292" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="310"/>
-      <c r="D20" s="310"/>
-      <c r="E20" s="310"/>
-      <c r="F20" s="310"/>
-      <c r="G20" s="310"/>
-      <c r="H20" s="310"/>
-      <c r="I20" s="310"/>
-      <c r="J20" s="310"/>
-      <c r="K20" s="310"/>
-      <c r="L20" s="310"/>
-      <c r="M20" s="310"/>
-      <c r="N20" s="310"/>
-      <c r="O20" s="310"/>
-      <c r="P20" s="310"/>
-      <c r="Q20" s="310"/>
-      <c r="R20" s="311"/>
+      <c r="C20" s="293"/>
+      <c r="D20" s="293"/>
+      <c r="E20" s="293"/>
+      <c r="F20" s="293"/>
+      <c r="G20" s="293"/>
+      <c r="H20" s="293"/>
+      <c r="I20" s="293"/>
+      <c r="J20" s="293"/>
+      <c r="K20" s="293"/>
+      <c r="L20" s="293"/>
+      <c r="M20" s="293"/>
+      <c r="N20" s="293"/>
+      <c r="O20" s="293"/>
+      <c r="P20" s="293"/>
+      <c r="Q20" s="293"/>
+      <c r="R20" s="294"/>
     </row>
     <row r="21" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="312" t="s">
+      <c r="B21" s="295" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="313"/>
-      <c r="D21" s="313"/>
-      <c r="E21" s="313"/>
-      <c r="F21" s="313"/>
-      <c r="G21" s="313"/>
-      <c r="H21" s="313"/>
-      <c r="I21" s="313"/>
-      <c r="J21" s="313"/>
-      <c r="K21" s="313"/>
-      <c r="L21" s="313"/>
-      <c r="M21" s="313"/>
-      <c r="N21" s="313"/>
-      <c r="O21" s="313"/>
-      <c r="P21" s="313"/>
-      <c r="Q21" s="313"/>
-      <c r="R21" s="314"/>
+      <c r="C21" s="296"/>
+      <c r="D21" s="296"/>
+      <c r="E21" s="296"/>
+      <c r="F21" s="296"/>
+      <c r="G21" s="296"/>
+      <c r="H21" s="296"/>
+      <c r="I21" s="296"/>
+      <c r="J21" s="296"/>
+      <c r="K21" s="296"/>
+      <c r="L21" s="296"/>
+      <c r="M21" s="296"/>
+      <c r="N21" s="296"/>
+      <c r="O21" s="296"/>
+      <c r="P21" s="296"/>
+      <c r="Q21" s="296"/>
+      <c r="R21" s="297"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B22" s="315"/>
-      <c r="C22" s="285"/>
-      <c r="D22" s="285"/>
-      <c r="E22" s="285"/>
-      <c r="F22" s="285"/>
-      <c r="G22" s="285"/>
-      <c r="H22" s="285"/>
-      <c r="I22" s="285"/>
-      <c r="J22" s="285"/>
-      <c r="K22" s="285"/>
-      <c r="L22" s="285"/>
-      <c r="M22" s="285"/>
-      <c r="N22" s="285"/>
-      <c r="O22" s="285"/>
-      <c r="P22" s="285"/>
-      <c r="Q22" s="285"/>
-      <c r="R22" s="316"/>
+      <c r="B22" s="298"/>
+      <c r="C22" s="242"/>
+      <c r="D22" s="242"/>
+      <c r="E22" s="242"/>
+      <c r="F22" s="242"/>
+      <c r="G22" s="242"/>
+      <c r="H22" s="242"/>
+      <c r="I22" s="242"/>
+      <c r="J22" s="242"/>
+      <c r="K22" s="242"/>
+      <c r="L22" s="242"/>
+      <c r="M22" s="242"/>
+      <c r="N22" s="242"/>
+      <c r="O22" s="242"/>
+      <c r="P22" s="242"/>
+      <c r="Q22" s="242"/>
+      <c r="R22" s="299"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B23" s="315"/>
-      <c r="C23" s="285"/>
-      <c r="D23" s="285"/>
-      <c r="E23" s="285"/>
-      <c r="F23" s="285"/>
-      <c r="G23" s="285"/>
-      <c r="H23" s="285"/>
-      <c r="I23" s="285"/>
-      <c r="J23" s="285"/>
-      <c r="K23" s="285"/>
-      <c r="L23" s="285"/>
-      <c r="M23" s="285"/>
-      <c r="N23" s="285"/>
-      <c r="O23" s="285"/>
-      <c r="P23" s="285"/>
-      <c r="Q23" s="285"/>
-      <c r="R23" s="316"/>
+      <c r="B23" s="298"/>
+      <c r="C23" s="242"/>
+      <c r="D23" s="242"/>
+      <c r="E23" s="242"/>
+      <c r="F23" s="242"/>
+      <c r="G23" s="242"/>
+      <c r="H23" s="242"/>
+      <c r="I23" s="242"/>
+      <c r="J23" s="242"/>
+      <c r="K23" s="242"/>
+      <c r="L23" s="242"/>
+      <c r="M23" s="242"/>
+      <c r="N23" s="242"/>
+      <c r="O23" s="242"/>
+      <c r="P23" s="242"/>
+      <c r="Q23" s="242"/>
+      <c r="R23" s="299"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B24" s="317"/>
-      <c r="C24" s="318"/>
-      <c r="D24" s="318"/>
-      <c r="E24" s="318"/>
-      <c r="F24" s="318"/>
-      <c r="G24" s="318"/>
-      <c r="H24" s="318"/>
-      <c r="I24" s="318"/>
-      <c r="J24" s="318"/>
-      <c r="K24" s="318"/>
-      <c r="L24" s="318"/>
-      <c r="M24" s="318"/>
-      <c r="N24" s="318"/>
-      <c r="O24" s="318"/>
-      <c r="P24" s="318"/>
-      <c r="Q24" s="318"/>
-      <c r="R24" s="319"/>
+      <c r="B24" s="300"/>
+      <c r="C24" s="301"/>
+      <c r="D24" s="301"/>
+      <c r="E24" s="301"/>
+      <c r="F24" s="301"/>
+      <c r="G24" s="301"/>
+      <c r="H24" s="301"/>
+      <c r="I24" s="301"/>
+      <c r="J24" s="301"/>
+      <c r="K24" s="301"/>
+      <c r="L24" s="301"/>
+      <c r="M24" s="301"/>
+      <c r="N24" s="301"/>
+      <c r="O24" s="301"/>
+      <c r="P24" s="301"/>
+      <c r="Q24" s="301"/>
+      <c r="R24" s="302"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B25" s="27"/>
@@ -10382,34 +10382,34 @@
       <c r="Q33" s="34"/>
     </row>
     <row r="34" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B34" s="243" t="s">
+      <c r="B34" s="288" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="243"/>
-      <c r="D34" s="243"/>
-      <c r="E34" s="243"/>
-      <c r="F34" s="243"/>
-      <c r="G34" s="243"/>
-      <c r="H34" s="243"/>
-      <c r="I34" s="243"/>
-      <c r="J34" s="243"/>
-      <c r="K34" s="243"/>
-      <c r="L34" s="243"/>
-      <c r="M34" s="243"/>
-      <c r="N34" s="243"/>
-      <c r="O34" s="243"/>
-      <c r="P34" s="243"/>
-      <c r="Q34" s="243"/>
-      <c r="R34" s="243"/>
+      <c r="C34" s="288"/>
+      <c r="D34" s="288"/>
+      <c r="E34" s="288"/>
+      <c r="F34" s="288"/>
+      <c r="G34" s="288"/>
+      <c r="H34" s="288"/>
+      <c r="I34" s="288"/>
+      <c r="J34" s="288"/>
+      <c r="K34" s="288"/>
+      <c r="L34" s="288"/>
+      <c r="M34" s="288"/>
+      <c r="N34" s="288"/>
+      <c r="O34" s="288"/>
+      <c r="P34" s="288"/>
+      <c r="Q34" s="288"/>
+      <c r="R34" s="288"/>
     </row>
     <row r="35" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="306" t="s">
+      <c r="C35" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="306"/>
+      <c r="D35" s="303"/>
       <c r="E35" s="127" t="s">
         <v>125</v>
       </c>
@@ -10441,17 +10441,17 @@
         <v>14</v>
       </c>
       <c r="O35" s="124"/>
-      <c r="P35" s="220" t="s">
+      <c r="P35" s="221" t="s">
         <v>36</v>
       </c>
-      <c r="Q35" s="220"/>
-      <c r="R35" s="220"/>
+      <c r="Q35" s="221"/>
+      <c r="R35" s="221"/>
     </row>
     <row r="36" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="244" t="s">
+      <c r="B36" s="289" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="242" t="s">
+      <c r="C36" s="248" t="s">
         <v>110</v>
       </c>
       <c r="D36" s="53" t="s">
@@ -10491,15 +10491,15 @@
         <v>91</v>
       </c>
       <c r="O36" s="53"/>
-      <c r="P36" s="245" t="s">
+      <c r="P36" s="272" t="s">
         <v>129</v>
       </c>
-      <c r="Q36" s="301"/>
-      <c r="R36" s="246"/>
+      <c r="Q36" s="316"/>
+      <c r="R36" s="273"/>
     </row>
     <row r="37" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B37" s="244"/>
-      <c r="C37" s="242"/>
+      <c r="B37" s="289"/>
+      <c r="C37" s="248"/>
       <c r="D37" s="53" t="s">
         <v>22</v>
       </c>
@@ -10537,9 +10537,9 @@
         <v>91</v>
       </c>
       <c r="O37" s="53"/>
-      <c r="P37" s="302"/>
-      <c r="Q37" s="303"/>
-      <c r="R37" s="304"/>
+      <c r="P37" s="317"/>
+      <c r="Q37" s="318"/>
+      <c r="R37" s="319"/>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B38" s="123" t="s">
@@ -10584,11 +10584,11 @@
         <v>43</v>
       </c>
       <c r="O38" s="53"/>
-      <c r="P38" s="298" t="s">
+      <c r="P38" s="309" t="s">
         <v>132</v>
       </c>
-      <c r="Q38" s="299"/>
-      <c r="R38" s="300"/>
+      <c r="Q38" s="310"/>
+      <c r="R38" s="311"/>
     </row>
     <row r="39" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="125" t="s">
@@ -10634,11 +10634,11 @@
         <v>91</v>
       </c>
       <c r="O39" s="53"/>
-      <c r="P39" s="298" t="s">
+      <c r="P39" s="309" t="s">
         <v>132</v>
       </c>
-      <c r="Q39" s="299"/>
-      <c r="R39" s="300"/>
+      <c r="Q39" s="310"/>
+      <c r="R39" s="311"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="42"/>
@@ -10681,86 +10681,86 @@
       <c r="S41" s="7"/>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B42" s="227" t="s">
+      <c r="B42" s="215" t="s">
         <v>33</v>
       </c>
-      <c r="C42" s="227"/>
-      <c r="D42" s="227"/>
-      <c r="E42" s="227"/>
-      <c r="F42" s="227"/>
-      <c r="G42" s="227"/>
-      <c r="H42" s="227"/>
-      <c r="I42" s="227"/>
-      <c r="J42" s="227"/>
-      <c r="K42" s="227"/>
-      <c r="L42" s="227"/>
-      <c r="M42" s="227"/>
-      <c r="N42" s="227"/>
-      <c r="O42" s="227"/>
-      <c r="P42" s="227"/>
-      <c r="Q42" s="227"/>
-      <c r="R42" s="227"/>
-      <c r="S42" s="227"/>
+      <c r="C42" s="215"/>
+      <c r="D42" s="215"/>
+      <c r="E42" s="215"/>
+      <c r="F42" s="215"/>
+      <c r="G42" s="215"/>
+      <c r="H42" s="215"/>
+      <c r="I42" s="215"/>
+      <c r="J42" s="215"/>
+      <c r="K42" s="215"/>
+      <c r="L42" s="215"/>
+      <c r="M42" s="215"/>
+      <c r="N42" s="215"/>
+      <c r="O42" s="215"/>
+      <c r="P42" s="215"/>
+      <c r="Q42" s="215"/>
+      <c r="R42" s="215"/>
+      <c r="S42" s="215"/>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B43" s="227"/>
-      <c r="C43" s="227"/>
-      <c r="D43" s="227"/>
-      <c r="E43" s="227"/>
-      <c r="F43" s="227"/>
-      <c r="G43" s="227"/>
-      <c r="H43" s="227"/>
-      <c r="I43" s="227"/>
-      <c r="J43" s="227"/>
-      <c r="K43" s="227"/>
-      <c r="L43" s="227"/>
-      <c r="M43" s="227"/>
-      <c r="N43" s="227"/>
-      <c r="O43" s="227"/>
-      <c r="P43" s="227"/>
-      <c r="Q43" s="227"/>
-      <c r="R43" s="227"/>
-      <c r="S43" s="227"/>
+      <c r="B43" s="215"/>
+      <c r="C43" s="215"/>
+      <c r="D43" s="215"/>
+      <c r="E43" s="215"/>
+      <c r="F43" s="215"/>
+      <c r="G43" s="215"/>
+      <c r="H43" s="215"/>
+      <c r="I43" s="215"/>
+      <c r="J43" s="215"/>
+      <c r="K43" s="215"/>
+      <c r="L43" s="215"/>
+      <c r="M43" s="215"/>
+      <c r="N43" s="215"/>
+      <c r="O43" s="215"/>
+      <c r="P43" s="215"/>
+      <c r="Q43" s="215"/>
+      <c r="R43" s="215"/>
+      <c r="S43" s="215"/>
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B44" s="227"/>
-      <c r="C44" s="227"/>
-      <c r="D44" s="227"/>
-      <c r="E44" s="227"/>
-      <c r="F44" s="227"/>
-      <c r="G44" s="227"/>
-      <c r="H44" s="227"/>
-      <c r="I44" s="227"/>
-      <c r="J44" s="227"/>
-      <c r="K44" s="227"/>
-      <c r="L44" s="227"/>
-      <c r="M44" s="227"/>
-      <c r="N44" s="227"/>
-      <c r="O44" s="227"/>
-      <c r="P44" s="227"/>
-      <c r="Q44" s="227"/>
-      <c r="R44" s="227"/>
-      <c r="S44" s="227"/>
+      <c r="B44" s="215"/>
+      <c r="C44" s="215"/>
+      <c r="D44" s="215"/>
+      <c r="E44" s="215"/>
+      <c r="F44" s="215"/>
+      <c r="G44" s="215"/>
+      <c r="H44" s="215"/>
+      <c r="I44" s="215"/>
+      <c r="J44" s="215"/>
+      <c r="K44" s="215"/>
+      <c r="L44" s="215"/>
+      <c r="M44" s="215"/>
+      <c r="N44" s="215"/>
+      <c r="O44" s="215"/>
+      <c r="P44" s="215"/>
+      <c r="Q44" s="215"/>
+      <c r="R44" s="215"/>
+      <c r="S44" s="215"/>
     </row>
     <row r="45" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B45" s="230"/>
-      <c r="C45" s="230"/>
-      <c r="D45" s="230"/>
-      <c r="E45" s="230"/>
-      <c r="F45" s="230"/>
-      <c r="G45" s="230"/>
-      <c r="H45" s="230"/>
-      <c r="I45" s="230"/>
-      <c r="J45" s="230"/>
-      <c r="K45" s="230"/>
-      <c r="L45" s="230"/>
-      <c r="M45" s="230"/>
-      <c r="N45" s="230"/>
-      <c r="O45" s="230"/>
-      <c r="P45" s="230"/>
-      <c r="Q45" s="230"/>
-      <c r="R45" s="230"/>
-      <c r="S45" s="230"/>
+      <c r="B45" s="218"/>
+      <c r="C45" s="218"/>
+      <c r="D45" s="218"/>
+      <c r="E45" s="218"/>
+      <c r="F45" s="218"/>
+      <c r="G45" s="218"/>
+      <c r="H45" s="218"/>
+      <c r="I45" s="218"/>
+      <c r="J45" s="218"/>
+      <c r="K45" s="218"/>
+      <c r="L45" s="218"/>
+      <c r="M45" s="218"/>
+      <c r="N45" s="218"/>
+      <c r="O45" s="218"/>
+      <c r="P45" s="218"/>
+      <c r="Q45" s="218"/>
+      <c r="R45" s="218"/>
+      <c r="S45" s="218"/>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B46" s="42"/>
@@ -10941,10 +10941,10 @@
       <c r="B56" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C56" s="220" t="s">
+      <c r="C56" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D56" s="220"/>
+      <c r="D56" s="221"/>
       <c r="E56" s="120" t="s">
         <v>3</v>
       </c>
@@ -10984,7 +10984,7 @@
       <c r="Q56" s="121"/>
     </row>
     <row r="57" spans="2:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="297" t="s">
+      <c r="B57" s="304" t="s">
         <v>139</v>
       </c>
       <c r="C57" s="305" t="s">
@@ -11029,13 +11029,13 @@
       <c r="O57" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P57" s="291" t="s">
+      <c r="P57" s="307" t="s">
         <v>73</v>
       </c>
       <c r="Q57" s="141"/>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B58" s="297"/>
+      <c r="B58" s="304"/>
       <c r="C58" s="305"/>
       <c r="D58" s="141" t="s">
         <v>22</v>
@@ -11076,11 +11076,11 @@
       <c r="O58" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P58" s="292"/>
+      <c r="P58" s="308"/>
       <c r="Q58" s="141"/>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B59" s="297" t="s">
+      <c r="B59" s="304" t="s">
         <v>140</v>
       </c>
       <c r="C59" s="305" t="s">
@@ -11125,11 +11125,11 @@
       <c r="O59" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P59" s="292"/>
+      <c r="P59" s="308"/>
       <c r="Q59" s="141"/>
     </row>
     <row r="60" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="297"/>
+      <c r="B60" s="304"/>
       <c r="C60" s="305"/>
       <c r="D60" s="141" t="s">
         <v>22</v>
@@ -11170,11 +11170,11 @@
       <c r="O60" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P60" s="293"/>
+      <c r="P60" s="312"/>
       <c r="Q60" s="141"/>
     </row>
     <row r="61" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="297" t="s">
+      <c r="B61" s="304" t="s">
         <v>141</v>
       </c>
       <c r="C61" s="305" t="s">
@@ -11219,13 +11219,13 @@
       <c r="O61" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P61" s="294" t="s">
+      <c r="P61" s="313" t="s">
         <v>59</v>
       </c>
       <c r="Q61" s="141"/>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B62" s="297"/>
+      <c r="B62" s="304"/>
       <c r="C62" s="305"/>
       <c r="D62" s="141" t="s">
         <v>22</v>
@@ -11266,11 +11266,11 @@
       <c r="O62" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P62" s="295"/>
+      <c r="P62" s="314"/>
       <c r="Q62" s="141"/>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B63" s="297" t="s">
+      <c r="B63" s="304" t="s">
         <v>143</v>
       </c>
       <c r="C63" s="305" t="s">
@@ -11315,11 +11315,11 @@
       <c r="O63" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P63" s="295"/>
+      <c r="P63" s="314"/>
       <c r="Q63" s="141"/>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B64" s="297"/>
+      <c r="B64" s="304"/>
       <c r="C64" s="305"/>
       <c r="D64" s="141" t="s">
         <v>22</v>
@@ -11360,37 +11360,37 @@
       <c r="O64" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="P64" s="296"/>
+      <c r="P64" s="315"/>
       <c r="Q64" s="141"/>
     </row>
     <row r="65" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="215" t="s">
+      <c r="B65" s="233" t="s">
         <v>144</v>
       </c>
-      <c r="C65" s="215"/>
-      <c r="D65" s="218"/>
-      <c r="E65" s="218"/>
-      <c r="F65" s="215"/>
-      <c r="G65" s="218"/>
-      <c r="H65" s="218"/>
-      <c r="I65" s="215"/>
-      <c r="J65" s="218"/>
-      <c r="K65" s="218"/>
-      <c r="L65" s="218"/>
-      <c r="M65" s="215"/>
-      <c r="N65" s="218"/>
-      <c r="O65" s="218"/>
-      <c r="P65" s="218"/>
-      <c r="Q65" s="218"/>
+      <c r="C65" s="233"/>
+      <c r="D65" s="222"/>
+      <c r="E65" s="222"/>
+      <c r="F65" s="233"/>
+      <c r="G65" s="222"/>
+      <c r="H65" s="222"/>
+      <c r="I65" s="233"/>
+      <c r="J65" s="222"/>
+      <c r="K65" s="222"/>
+      <c r="L65" s="222"/>
+      <c r="M65" s="233"/>
+      <c r="N65" s="222"/>
+      <c r="O65" s="222"/>
+      <c r="P65" s="222"/>
+      <c r="Q65" s="222"/>
     </row>
     <row r="66" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B66" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C66" s="220" t="s">
+      <c r="C66" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D66" s="220"/>
+      <c r="D66" s="221"/>
       <c r="E66" s="8" t="s">
         <v>3</v>
       </c>
@@ -11430,7 +11430,7 @@
       <c r="Q66" s="103"/>
     </row>
     <row r="67" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B67" s="277" t="s">
+      <c r="B67" s="265" t="s">
         <v>145</v>
       </c>
       <c r="C67" s="202" t="s">
@@ -11475,7 +11475,7 @@
       <c r="O67" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P67" s="291" t="s">
+      <c r="P67" s="307" t="s">
         <v>73</v>
       </c>
       <c r="Q67" s="147"/>
@@ -42929,7 +42929,7 @@
       </c>
     </row>
     <row r="68" spans="2:62 3072:12198 12789:15082" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="307"/>
+      <c r="B68" s="306"/>
       <c r="C68" s="202" t="s">
         <v>110</v>
       </c>
@@ -42972,7 +42972,7 @@
       <c r="O68" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P68" s="292"/>
+      <c r="P68" s="308"/>
       <c r="Q68" s="147"/>
       <c r="R68" s="170"/>
       <c r="S68" s="163"/>
@@ -54465,10 +54465,10 @@
       <c r="B70" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C70" s="220" t="s">
+      <c r="C70" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D70" s="220"/>
+      <c r="D70" s="221"/>
       <c r="E70" s="8" t="s">
         <v>3</v>
       </c>
@@ -54508,7 +54508,7 @@
       <c r="Q70" s="103"/>
     </row>
     <row r="71" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B71" s="277" t="s">
+      <c r="B71" s="265" t="s">
         <v>147</v>
       </c>
       <c r="C71" s="202" t="s">
@@ -54553,13 +54553,13 @@
       <c r="O71" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P71" s="291" t="s">
+      <c r="P71" s="307" t="s">
         <v>73</v>
       </c>
       <c r="Q71" s="147"/>
     </row>
     <row r="72" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B72" s="307"/>
+      <c r="B72" s="306"/>
       <c r="C72" s="202" t="s">
         <v>110</v>
       </c>
@@ -54602,7 +54602,7 @@
       <c r="O72" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="P72" s="292"/>
+      <c r="P72" s="308"/>
       <c r="Q72" s="147"/>
     </row>
     <row r="74" spans="2:62 3072:12198 12789:15082" ht="15.6" x14ac:dyDescent="0.3">
@@ -54629,121 +54629,121 @@
       <c r="T74" s="6"/>
     </row>
     <row r="75" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B75" s="252" t="s">
+      <c r="B75" s="281" t="s">
         <v>33</v>
       </c>
-      <c r="C75" s="252"/>
-      <c r="D75" s="252"/>
-      <c r="E75" s="252"/>
-      <c r="F75" s="252"/>
-      <c r="G75" s="252"/>
-      <c r="H75" s="252"/>
-      <c r="I75" s="252"/>
-      <c r="J75" s="252"/>
-      <c r="K75" s="252"/>
-      <c r="L75" s="252"/>
-      <c r="M75" s="252"/>
-      <c r="N75" s="252"/>
-      <c r="O75" s="252"/>
-      <c r="P75" s="252"/>
-      <c r="Q75" s="252"/>
-      <c r="R75" s="252"/>
-      <c r="S75" s="252"/>
-      <c r="T75" s="252"/>
+      <c r="C75" s="281"/>
+      <c r="D75" s="281"/>
+      <c r="E75" s="281"/>
+      <c r="F75" s="281"/>
+      <c r="G75" s="281"/>
+      <c r="H75" s="281"/>
+      <c r="I75" s="281"/>
+      <c r="J75" s="281"/>
+      <c r="K75" s="281"/>
+      <c r="L75" s="281"/>
+      <c r="M75" s="281"/>
+      <c r="N75" s="281"/>
+      <c r="O75" s="281"/>
+      <c r="P75" s="281"/>
+      <c r="Q75" s="281"/>
+      <c r="R75" s="281"/>
+      <c r="S75" s="281"/>
+      <c r="T75" s="281"/>
     </row>
     <row r="76" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B76" s="252"/>
-      <c r="C76" s="252"/>
-      <c r="D76" s="252"/>
-      <c r="E76" s="252"/>
-      <c r="F76" s="252"/>
-      <c r="G76" s="252"/>
-      <c r="H76" s="252"/>
-      <c r="I76" s="252"/>
-      <c r="J76" s="252"/>
-      <c r="K76" s="252"/>
-      <c r="L76" s="252"/>
-      <c r="M76" s="252"/>
-      <c r="N76" s="252"/>
-      <c r="O76" s="252"/>
-      <c r="P76" s="252"/>
-      <c r="Q76" s="252"/>
-      <c r="R76" s="252"/>
-      <c r="S76" s="252"/>
-      <c r="T76" s="252"/>
+      <c r="B76" s="281"/>
+      <c r="C76" s="281"/>
+      <c r="D76" s="281"/>
+      <c r="E76" s="281"/>
+      <c r="F76" s="281"/>
+      <c r="G76" s="281"/>
+      <c r="H76" s="281"/>
+      <c r="I76" s="281"/>
+      <c r="J76" s="281"/>
+      <c r="K76" s="281"/>
+      <c r="L76" s="281"/>
+      <c r="M76" s="281"/>
+      <c r="N76" s="281"/>
+      <c r="O76" s="281"/>
+      <c r="P76" s="281"/>
+      <c r="Q76" s="281"/>
+      <c r="R76" s="281"/>
+      <c r="S76" s="281"/>
+      <c r="T76" s="281"/>
     </row>
     <row r="77" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B77" s="252"/>
-      <c r="C77" s="252"/>
-      <c r="D77" s="252"/>
-      <c r="E77" s="252"/>
-      <c r="F77" s="252"/>
-      <c r="G77" s="252"/>
-      <c r="H77" s="252"/>
-      <c r="I77" s="252"/>
-      <c r="J77" s="252"/>
-      <c r="K77" s="252"/>
-      <c r="L77" s="252"/>
-      <c r="M77" s="252"/>
-      <c r="N77" s="252"/>
-      <c r="O77" s="252"/>
-      <c r="P77" s="252"/>
-      <c r="Q77" s="252"/>
-      <c r="R77" s="252"/>
-      <c r="S77" s="252"/>
-      <c r="T77" s="252"/>
+      <c r="B77" s="281"/>
+      <c r="C77" s="281"/>
+      <c r="D77" s="281"/>
+      <c r="E77" s="281"/>
+      <c r="F77" s="281"/>
+      <c r="G77" s="281"/>
+      <c r="H77" s="281"/>
+      <c r="I77" s="281"/>
+      <c r="J77" s="281"/>
+      <c r="K77" s="281"/>
+      <c r="L77" s="281"/>
+      <c r="M77" s="281"/>
+      <c r="N77" s="281"/>
+      <c r="O77" s="281"/>
+      <c r="P77" s="281"/>
+      <c r="Q77" s="281"/>
+      <c r="R77" s="281"/>
+      <c r="S77" s="281"/>
+      <c r="T77" s="281"/>
     </row>
     <row r="78" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B78" s="252"/>
-      <c r="C78" s="252"/>
-      <c r="D78" s="252"/>
-      <c r="E78" s="252"/>
-      <c r="F78" s="252"/>
-      <c r="G78" s="252"/>
-      <c r="H78" s="252"/>
-      <c r="I78" s="252"/>
-      <c r="J78" s="252"/>
-      <c r="K78" s="252"/>
-      <c r="L78" s="252"/>
-      <c r="M78" s="252"/>
-      <c r="N78" s="252"/>
-      <c r="O78" s="252"/>
-      <c r="P78" s="252"/>
-      <c r="Q78" s="252"/>
-      <c r="R78" s="252"/>
-      <c r="S78" s="252"/>
-      <c r="T78" s="252"/>
+      <c r="B78" s="281"/>
+      <c r="C78" s="281"/>
+      <c r="D78" s="281"/>
+      <c r="E78" s="281"/>
+      <c r="F78" s="281"/>
+      <c r="G78" s="281"/>
+      <c r="H78" s="281"/>
+      <c r="I78" s="281"/>
+      <c r="J78" s="281"/>
+      <c r="K78" s="281"/>
+      <c r="L78" s="281"/>
+      <c r="M78" s="281"/>
+      <c r="N78" s="281"/>
+      <c r="O78" s="281"/>
+      <c r="P78" s="281"/>
+      <c r="Q78" s="281"/>
+      <c r="R78" s="281"/>
+      <c r="S78" s="281"/>
+      <c r="T78" s="281"/>
     </row>
     <row r="87" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B87" s="219" t="s">
+      <c r="B87" s="223" t="s">
         <v>149</v>
       </c>
-      <c r="C87" s="219"/>
-      <c r="D87" s="219"/>
-      <c r="E87" s="219"/>
-      <c r="F87" s="219"/>
-      <c r="G87" s="219"/>
-      <c r="H87" s="219"/>
-      <c r="I87" s="219"/>
-      <c r="J87" s="219"/>
-      <c r="K87" s="219"/>
-      <c r="L87" s="219"/>
-      <c r="M87" s="219"/>
-      <c r="N87" s="219"/>
-      <c r="O87" s="219"/>
-      <c r="P87" s="219"/>
-      <c r="Q87" s="219"/>
-      <c r="R87" s="219"/>
-      <c r="S87" s="219"/>
+      <c r="C87" s="223"/>
+      <c r="D87" s="223"/>
+      <c r="E87" s="223"/>
+      <c r="F87" s="223"/>
+      <c r="G87" s="223"/>
+      <c r="H87" s="223"/>
+      <c r="I87" s="223"/>
+      <c r="J87" s="223"/>
+      <c r="K87" s="223"/>
+      <c r="L87" s="223"/>
+      <c r="M87" s="223"/>
+      <c r="N87" s="223"/>
+      <c r="O87" s="223"/>
+      <c r="P87" s="223"/>
+      <c r="Q87" s="223"/>
+      <c r="R87" s="223"/>
+      <c r="S87" s="223"/>
     </row>
     <row r="88" spans="2:20" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C88" s="306" t="s">
+      <c r="C88" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D88" s="306"/>
+      <c r="D88" s="303"/>
       <c r="E88" s="127" t="s">
         <v>125</v>
       </c>
@@ -54778,17 +54778,17 @@
         <v>14</v>
       </c>
       <c r="P88" s="17"/>
-      <c r="Q88" s="220" t="s">
+      <c r="Q88" s="221" t="s">
         <v>36</v>
       </c>
-      <c r="R88" s="220"/>
-      <c r="S88" s="220"/>
+      <c r="R88" s="221"/>
+      <c r="S88" s="221"/>
     </row>
     <row r="89" spans="2:20" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="221" t="s">
+      <c r="B89" s="227" t="s">
         <v>90</v>
       </c>
-      <c r="C89" s="242" t="s">
+      <c r="C89" s="248" t="s">
         <v>110</v>
       </c>
       <c r="D89" s="53" t="s">
@@ -54837,8 +54837,8 @@
       <c r="S89" s="249"/>
     </row>
     <row r="90" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B90" s="217"/>
-      <c r="C90" s="242"/>
+      <c r="B90" s="224"/>
+      <c r="C90" s="248"/>
       <c r="D90" s="53" t="s">
         <v>22</v>
       </c>
@@ -54906,90 +54906,90 @@
       <c r="T92" s="6"/>
     </row>
     <row r="93" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B93" s="252" t="s">
+      <c r="B93" s="281" t="s">
         <v>33</v>
       </c>
-      <c r="C93" s="252"/>
-      <c r="D93" s="252"/>
-      <c r="E93" s="252"/>
-      <c r="F93" s="252"/>
-      <c r="G93" s="252"/>
-      <c r="H93" s="252"/>
-      <c r="I93" s="252"/>
-      <c r="J93" s="252"/>
-      <c r="K93" s="252"/>
-      <c r="L93" s="252"/>
-      <c r="M93" s="252"/>
-      <c r="N93" s="252"/>
-      <c r="O93" s="252"/>
-      <c r="P93" s="252"/>
-      <c r="Q93" s="252"/>
-      <c r="R93" s="252"/>
-      <c r="S93" s="252"/>
-      <c r="T93" s="252"/>
+      <c r="C93" s="281"/>
+      <c r="D93" s="281"/>
+      <c r="E93" s="281"/>
+      <c r="F93" s="281"/>
+      <c r="G93" s="281"/>
+      <c r="H93" s="281"/>
+      <c r="I93" s="281"/>
+      <c r="J93" s="281"/>
+      <c r="K93" s="281"/>
+      <c r="L93" s="281"/>
+      <c r="M93" s="281"/>
+      <c r="N93" s="281"/>
+      <c r="O93" s="281"/>
+      <c r="P93" s="281"/>
+      <c r="Q93" s="281"/>
+      <c r="R93" s="281"/>
+      <c r="S93" s="281"/>
+      <c r="T93" s="281"/>
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B94" s="252"/>
-      <c r="C94" s="252"/>
-      <c r="D94" s="252"/>
-      <c r="E94" s="252"/>
-      <c r="F94" s="252"/>
-      <c r="G94" s="252"/>
-      <c r="H94" s="252"/>
-      <c r="I94" s="252"/>
-      <c r="J94" s="252"/>
-      <c r="K94" s="252"/>
-      <c r="L94" s="252"/>
-      <c r="M94" s="252"/>
-      <c r="N94" s="252"/>
-      <c r="O94" s="252"/>
-      <c r="P94" s="252"/>
-      <c r="Q94" s="252"/>
-      <c r="R94" s="252"/>
-      <c r="S94" s="252"/>
-      <c r="T94" s="252"/>
+      <c r="B94" s="281"/>
+      <c r="C94" s="281"/>
+      <c r="D94" s="281"/>
+      <c r="E94" s="281"/>
+      <c r="F94" s="281"/>
+      <c r="G94" s="281"/>
+      <c r="H94" s="281"/>
+      <c r="I94" s="281"/>
+      <c r="J94" s="281"/>
+      <c r="K94" s="281"/>
+      <c r="L94" s="281"/>
+      <c r="M94" s="281"/>
+      <c r="N94" s="281"/>
+      <c r="O94" s="281"/>
+      <c r="P94" s="281"/>
+      <c r="Q94" s="281"/>
+      <c r="R94" s="281"/>
+      <c r="S94" s="281"/>
+      <c r="T94" s="281"/>
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B95" s="252"/>
-      <c r="C95" s="252"/>
-      <c r="D95" s="252"/>
-      <c r="E95" s="252"/>
-      <c r="F95" s="252"/>
-      <c r="G95" s="252"/>
-      <c r="H95" s="252"/>
-      <c r="I95" s="252"/>
-      <c r="J95" s="252"/>
-      <c r="K95" s="252"/>
-      <c r="L95" s="252"/>
-      <c r="M95" s="252"/>
-      <c r="N95" s="252"/>
-      <c r="O95" s="252"/>
-      <c r="P95" s="252"/>
-      <c r="Q95" s="252"/>
-      <c r="R95" s="252"/>
-      <c r="S95" s="252"/>
-      <c r="T95" s="252"/>
+      <c r="B95" s="281"/>
+      <c r="C95" s="281"/>
+      <c r="D95" s="281"/>
+      <c r="E95" s="281"/>
+      <c r="F95" s="281"/>
+      <c r="G95" s="281"/>
+      <c r="H95" s="281"/>
+      <c r="I95" s="281"/>
+      <c r="J95" s="281"/>
+      <c r="K95" s="281"/>
+      <c r="L95" s="281"/>
+      <c r="M95" s="281"/>
+      <c r="N95" s="281"/>
+      <c r="O95" s="281"/>
+      <c r="P95" s="281"/>
+      <c r="Q95" s="281"/>
+      <c r="R95" s="281"/>
+      <c r="S95" s="281"/>
+      <c r="T95" s="281"/>
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B96" s="252"/>
-      <c r="C96" s="252"/>
-      <c r="D96" s="252"/>
-      <c r="E96" s="252"/>
-      <c r="F96" s="252"/>
-      <c r="G96" s="252"/>
-      <c r="H96" s="252"/>
-      <c r="I96" s="252"/>
-      <c r="J96" s="252"/>
-      <c r="K96" s="252"/>
-      <c r="L96" s="252"/>
-      <c r="M96" s="252"/>
-      <c r="N96" s="252"/>
-      <c r="O96" s="252"/>
-      <c r="P96" s="252"/>
-      <c r="Q96" s="252"/>
-      <c r="R96" s="252"/>
-      <c r="S96" s="252"/>
-      <c r="T96" s="252"/>
+      <c r="B96" s="281"/>
+      <c r="C96" s="281"/>
+      <c r="D96" s="281"/>
+      <c r="E96" s="281"/>
+      <c r="F96" s="281"/>
+      <c r="G96" s="281"/>
+      <c r="H96" s="281"/>
+      <c r="I96" s="281"/>
+      <c r="J96" s="281"/>
+      <c r="K96" s="281"/>
+      <c r="L96" s="281"/>
+      <c r="M96" s="281"/>
+      <c r="N96" s="281"/>
+      <c r="O96" s="281"/>
+      <c r="P96" s="281"/>
+      <c r="Q96" s="281"/>
+      <c r="R96" s="281"/>
+      <c r="S96" s="281"/>
+      <c r="T96" s="281"/>
     </row>
     <row r="106" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="107" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -55016,10 +55016,10 @@
       <c r="B108" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C108" s="220" t="s">
+      <c r="C108" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D108" s="220"/>
+      <c r="D108" s="221"/>
       <c r="E108" s="8" t="s">
         <v>3</v>
       </c>
@@ -55059,10 +55059,10 @@
       <c r="Q108" s="103"/>
     </row>
     <row r="109" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B109" s="308" t="s">
+      <c r="B109" s="291" t="s">
         <v>154</v>
       </c>
-      <c r="C109" s="242" t="s">
+      <c r="C109" s="248" t="s">
         <v>110</v>
       </c>
       <c r="D109" s="53" t="s">
@@ -55109,8 +55109,8 @@
       <c r="Q109" s="104"/>
     </row>
     <row r="110" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B110" s="308"/>
-      <c r="C110" s="242"/>
+      <c r="B110" s="291"/>
+      <c r="C110" s="248"/>
       <c r="D110" s="53" t="s">
         <v>22</v>
       </c>
@@ -55179,10 +55179,10 @@
       <c r="B121" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C121" s="220" t="s">
+      <c r="C121" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D121" s="220"/>
+      <c r="D121" s="221"/>
       <c r="E121" s="8" t="s">
         <v>3</v>
       </c>
@@ -55222,10 +55222,10 @@
       <c r="Q121" s="103"/>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B122" s="308" t="s">
+      <c r="B122" s="291" t="s">
         <v>159</v>
       </c>
-      <c r="C122" s="242" t="s">
+      <c r="C122" s="248" t="s">
         <v>110</v>
       </c>
       <c r="D122" s="53" t="s">
@@ -55272,10 +55272,10 @@
       <c r="Q122" s="196"/>
     </row>
     <row r="123" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B123" s="308" t="s">
+      <c r="B123" s="291" t="s">
         <v>159</v>
       </c>
-      <c r="C123" s="242" t="s">
+      <c r="C123" s="248" t="s">
         <v>110</v>
       </c>
       <c r="D123" s="53" t="s">
@@ -55322,10 +55322,10 @@
       <c r="Q123" s="196"/>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B124" s="308" t="s">
+      <c r="B124" s="291" t="s">
         <v>160</v>
       </c>
-      <c r="C124" s="242" t="s">
+      <c r="C124" s="248" t="s">
         <v>110</v>
       </c>
       <c r="D124" s="53" t="s">
@@ -55373,8 +55373,8 @@
       <c r="Q124" s="196"/>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B125" s="308"/>
-      <c r="C125" s="242"/>
+      <c r="B125" s="291"/>
+      <c r="C125" s="248"/>
       <c r="D125" s="53" t="s">
         <v>22</v>
       </c>
@@ -55421,6 +55421,49 @@
     </row>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="P57:P60"/>
+    <mergeCell ref="P61:P64"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="P36:R37"/>
+    <mergeCell ref="B9:Q9"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="B42:S45"/>
+    <mergeCell ref="B55:Q55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="B34:R34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="P35:R35"/>
+    <mergeCell ref="P38:R38"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="Q88:S88"/>
+    <mergeCell ref="B87:S87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="B65:Q65"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="B75:T78"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B69:Q69"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="P67:P68"/>
+    <mergeCell ref="P71:P72"/>
     <mergeCell ref="B124:B125"/>
     <mergeCell ref="C124:C125"/>
     <mergeCell ref="B122:B123"/>
@@ -55437,49 +55480,6 @@
     <mergeCell ref="C108:D108"/>
     <mergeCell ref="B120:Q120"/>
     <mergeCell ref="C121:D121"/>
-    <mergeCell ref="Q88:S88"/>
-    <mergeCell ref="B87:S87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="B65:Q65"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="B75:T78"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="B69:Q69"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="P67:P68"/>
-    <mergeCell ref="P71:P72"/>
-    <mergeCell ref="B9:Q9"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="B42:S45"/>
-    <mergeCell ref="B55:Q55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="B34:R34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="P35:R35"/>
-    <mergeCell ref="P38:R38"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="P57:P60"/>
-    <mergeCell ref="P61:P64"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="P39:R39"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="P36:R37"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55516,8 +55516,8 @@
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B8" s="126"/>
       <c r="C8" s="126"/>
-      <c r="D8" s="322"/>
-      <c r="E8" s="322"/>
+      <c r="D8" s="329"/>
+      <c r="E8" s="329"/>
       <c r="F8" s="126"/>
       <c r="G8" s="126"/>
       <c r="H8" s="126"/>
@@ -55533,32 +55533,32 @@
       <c r="R8" s="126"/>
     </row>
     <row r="9" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="331" t="s">
+      <c r="B9" s="332" t="s">
         <v>161</v>
       </c>
-      <c r="C9" s="331"/>
-      <c r="D9" s="331"/>
-      <c r="E9" s="331"/>
-      <c r="F9" s="331"/>
-      <c r="G9" s="331"/>
-      <c r="H9" s="331"/>
-      <c r="I9" s="331"/>
-      <c r="J9" s="331"/>
-      <c r="K9" s="331"/>
-      <c r="L9" s="331"/>
-      <c r="M9" s="331"/>
-      <c r="N9" s="331"/>
-      <c r="O9" s="331"/>
-      <c r="P9" s="331"/>
+      <c r="C9" s="332"/>
+      <c r="D9" s="332"/>
+      <c r="E9" s="332"/>
+      <c r="F9" s="332"/>
+      <c r="G9" s="332"/>
+      <c r="H9" s="332"/>
+      <c r="I9" s="332"/>
+      <c r="J9" s="332"/>
+      <c r="K9" s="332"/>
+      <c r="L9" s="332"/>
+      <c r="M9" s="332"/>
+      <c r="N9" s="332"/>
+      <c r="O9" s="332"/>
+      <c r="P9" s="332"/>
     </row>
     <row r="10" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="340" t="s">
+      <c r="C10" s="330" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="341"/>
+      <c r="D10" s="331"/>
       <c r="E10" s="12" t="s">
         <v>3</v>
       </c>
@@ -55598,10 +55598,10 @@
       <c r="Q10" s="126"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B11" s="342" t="s">
+      <c r="B11" s="320" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="342" t="s">
+      <c r="C11" s="320" t="s">
         <v>165</v>
       </c>
       <c r="D11" s="41" t="s">
@@ -55649,8 +55649,8 @@
       <c r="Q11" s="126"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="343"/>
-      <c r="C12" s="343"/>
+      <c r="B12" s="321"/>
+      <c r="C12" s="321"/>
       <c r="D12" s="41" t="s">
         <v>22</v>
       </c>
@@ -55696,10 +55696,10 @@
       <c r="Q12" s="126"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="342" t="s">
+      <c r="B13" s="320" t="s">
         <v>167</v>
       </c>
-      <c r="C13" s="342" t="s">
+      <c r="C13" s="320" t="s">
         <v>165</v>
       </c>
       <c r="D13" s="41" t="s">
@@ -55747,8 +55747,8 @@
       <c r="Q13" s="126"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B14" s="343"/>
-      <c r="C14" s="343"/>
+      <c r="B14" s="321"/>
+      <c r="C14" s="321"/>
       <c r="D14" s="41" t="s">
         <v>22</v>
       </c>
@@ -55794,10 +55794,10 @@
       <c r="Q14" s="126"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="342" t="s">
+      <c r="B15" s="320" t="s">
         <v>122</v>
       </c>
-      <c r="C15" s="342" t="s">
+      <c r="C15" s="320" t="s">
         <v>165</v>
       </c>
       <c r="D15" s="41" t="s">
@@ -55845,8 +55845,8 @@
       <c r="Q15" s="126"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B16" s="343"/>
-      <c r="C16" s="343"/>
+      <c r="B16" s="321"/>
+      <c r="C16" s="321"/>
       <c r="D16" s="41" t="s">
         <v>22</v>
       </c>
@@ -55906,93 +55906,93 @@
       <c r="N17" s="34"/>
     </row>
     <row r="18" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="325" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="347"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
-      <c r="G18" s="347"/>
-      <c r="H18" s="347"/>
-      <c r="I18" s="347"/>
-      <c r="J18" s="347"/>
-      <c r="K18" s="347"/>
-      <c r="L18" s="347"/>
-      <c r="M18" s="347"/>
-      <c r="N18" s="347"/>
-      <c r="O18" s="347"/>
-      <c r="P18" s="348"/>
+      <c r="C18" s="326"/>
+      <c r="D18" s="326"/>
+      <c r="E18" s="326"/>
+      <c r="F18" s="326"/>
+      <c r="G18" s="326"/>
+      <c r="H18" s="326"/>
+      <c r="I18" s="326"/>
+      <c r="J18" s="326"/>
+      <c r="K18" s="326"/>
+      <c r="L18" s="326"/>
+      <c r="M18" s="326"/>
+      <c r="N18" s="326"/>
+      <c r="O18" s="326"/>
+      <c r="P18" s="327"/>
     </row>
     <row r="19" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="312" t="s">
+      <c r="B19" s="295" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="313"/>
-      <c r="D19" s="313"/>
-      <c r="E19" s="313"/>
-      <c r="F19" s="313"/>
-      <c r="G19" s="313"/>
-      <c r="H19" s="313"/>
-      <c r="I19" s="313"/>
-      <c r="J19" s="313"/>
-      <c r="K19" s="313"/>
-      <c r="L19" s="313"/>
-      <c r="M19" s="313"/>
-      <c r="N19" s="313"/>
-      <c r="O19" s="313"/>
-      <c r="P19" s="314"/>
+      <c r="C19" s="296"/>
+      <c r="D19" s="296"/>
+      <c r="E19" s="296"/>
+      <c r="F19" s="296"/>
+      <c r="G19" s="296"/>
+      <c r="H19" s="296"/>
+      <c r="I19" s="296"/>
+      <c r="J19" s="296"/>
+      <c r="K19" s="296"/>
+      <c r="L19" s="296"/>
+      <c r="M19" s="296"/>
+      <c r="N19" s="296"/>
+      <c r="O19" s="296"/>
+      <c r="P19" s="297"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="315"/>
-      <c r="C20" s="285"/>
-      <c r="D20" s="285"/>
-      <c r="E20" s="285"/>
-      <c r="F20" s="285"/>
-      <c r="G20" s="285"/>
-      <c r="H20" s="285"/>
-      <c r="I20" s="285"/>
-      <c r="J20" s="285"/>
-      <c r="K20" s="285"/>
-      <c r="L20" s="285"/>
-      <c r="M20" s="285"/>
-      <c r="N20" s="285"/>
-      <c r="O20" s="285"/>
-      <c r="P20" s="316"/>
+      <c r="B20" s="298"/>
+      <c r="C20" s="242"/>
+      <c r="D20" s="242"/>
+      <c r="E20" s="242"/>
+      <c r="F20" s="242"/>
+      <c r="G20" s="242"/>
+      <c r="H20" s="242"/>
+      <c r="I20" s="242"/>
+      <c r="J20" s="242"/>
+      <c r="K20" s="242"/>
+      <c r="L20" s="242"/>
+      <c r="M20" s="242"/>
+      <c r="N20" s="242"/>
+      <c r="O20" s="242"/>
+      <c r="P20" s="299"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="315"/>
-      <c r="C21" s="285"/>
-      <c r="D21" s="285"/>
-      <c r="E21" s="285"/>
-      <c r="F21" s="285"/>
-      <c r="G21" s="285"/>
-      <c r="H21" s="285"/>
-      <c r="I21" s="285"/>
-      <c r="J21" s="285"/>
-      <c r="K21" s="285"/>
-      <c r="L21" s="285"/>
-      <c r="M21" s="285"/>
-      <c r="N21" s="285"/>
-      <c r="O21" s="285"/>
-      <c r="P21" s="316"/>
+      <c r="B21" s="298"/>
+      <c r="C21" s="242"/>
+      <c r="D21" s="242"/>
+      <c r="E21" s="242"/>
+      <c r="F21" s="242"/>
+      <c r="G21" s="242"/>
+      <c r="H21" s="242"/>
+      <c r="I21" s="242"/>
+      <c r="J21" s="242"/>
+      <c r="K21" s="242"/>
+      <c r="L21" s="242"/>
+      <c r="M21" s="242"/>
+      <c r="N21" s="242"/>
+      <c r="O21" s="242"/>
+      <c r="P21" s="299"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="317"/>
-      <c r="C22" s="318"/>
-      <c r="D22" s="318"/>
-      <c r="E22" s="318"/>
-      <c r="F22" s="318"/>
-      <c r="G22" s="318"/>
-      <c r="H22" s="318"/>
-      <c r="I22" s="318"/>
-      <c r="J22" s="318"/>
-      <c r="K22" s="318"/>
-      <c r="L22" s="318"/>
-      <c r="M22" s="318"/>
-      <c r="N22" s="318"/>
-      <c r="O22" s="318"/>
-      <c r="P22" s="319"/>
+      <c r="B22" s="300"/>
+      <c r="C22" s="301"/>
+      <c r="D22" s="301"/>
+      <c r="E22" s="301"/>
+      <c r="F22" s="301"/>
+      <c r="G22" s="301"/>
+      <c r="H22" s="301"/>
+      <c r="I22" s="301"/>
+      <c r="J22" s="301"/>
+      <c r="K22" s="301"/>
+      <c r="L22" s="301"/>
+      <c r="M22" s="301"/>
+      <c r="N22" s="301"/>
+      <c r="O22" s="301"/>
+      <c r="P22" s="302"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="27"/>
@@ -56122,33 +56122,33 @@
       <c r="N31" s="34"/>
     </row>
     <row r="32" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="344" t="s">
+      <c r="B32" s="322" t="s">
         <v>169</v>
       </c>
-      <c r="C32" s="325"/>
-      <c r="D32" s="325"/>
-      <c r="E32" s="325"/>
-      <c r="F32" s="325"/>
-      <c r="G32" s="325"/>
-      <c r="H32" s="325"/>
-      <c r="I32" s="325"/>
-      <c r="J32" s="325"/>
-      <c r="K32" s="325"/>
-      <c r="L32" s="325"/>
-      <c r="M32" s="325"/>
-      <c r="N32" s="325"/>
-      <c r="O32" s="325"/>
-      <c r="P32" s="325"/>
-      <c r="Q32" s="345"/>
+      <c r="C32" s="323"/>
+      <c r="D32" s="323"/>
+      <c r="E32" s="323"/>
+      <c r="F32" s="323"/>
+      <c r="G32" s="323"/>
+      <c r="H32" s="323"/>
+      <c r="I32" s="323"/>
+      <c r="J32" s="323"/>
+      <c r="K32" s="323"/>
+      <c r="L32" s="323"/>
+      <c r="M32" s="323"/>
+      <c r="N32" s="323"/>
+      <c r="O32" s="323"/>
+      <c r="P32" s="323"/>
+      <c r="Q32" s="324"/>
     </row>
     <row r="33" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B33" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="349" t="s">
+      <c r="C33" s="328" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="349"/>
+      <c r="D33" s="328"/>
       <c r="E33" s="127" t="s">
         <v>125</v>
       </c>
@@ -56182,16 +56182,16 @@
       <c r="O33" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="P33" s="273" t="s">
+      <c r="P33" s="250" t="s">
         <v>36</v>
       </c>
-      <c r="Q33" s="274"/>
+      <c r="Q33" s="251"/>
     </row>
     <row r="34" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="338" t="s">
+      <c r="B34" s="337" t="s">
         <v>173</v>
       </c>
-      <c r="C34" s="339" t="s">
+      <c r="C34" s="338" t="s">
         <v>165</v>
       </c>
       <c r="D34" s="40" t="s">
@@ -56232,14 +56232,14 @@
       <c r="O34" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P34" s="245" t="s">
+      <c r="P34" s="272" t="s">
         <v>174</v>
       </c>
-      <c r="Q34" s="246"/>
+      <c r="Q34" s="273"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B35" s="338"/>
-      <c r="C35" s="339"/>
+      <c r="B35" s="337"/>
+      <c r="C35" s="338"/>
       <c r="D35" s="40" t="s">
         <v>22</v>
       </c>
@@ -56278,8 +56278,8 @@
       <c r="O35" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P35" s="302"/>
-      <c r="Q35" s="304"/>
+      <c r="P35" s="317"/>
+      <c r="Q35" s="319"/>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B36" s="119" t="s">
@@ -56326,8 +56326,8 @@
       <c r="O36" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P36" s="247"/>
-      <c r="Q36" s="248"/>
+      <c r="P36" s="274"/>
+      <c r="Q36" s="275"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B37" s="72"/>
@@ -56380,74 +56380,74 @@
       <c r="P39" s="7"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B40" s="227" t="s">
+      <c r="B40" s="215" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="228"/>
-      <c r="D40" s="228"/>
-      <c r="E40" s="228"/>
-      <c r="F40" s="228"/>
-      <c r="G40" s="228"/>
-      <c r="H40" s="228"/>
-      <c r="I40" s="228"/>
-      <c r="J40" s="228"/>
-      <c r="K40" s="228"/>
-      <c r="L40" s="228"/>
-      <c r="M40" s="228"/>
-      <c r="N40" s="228"/>
-      <c r="O40" s="228"/>
-      <c r="P40" s="229"/>
+      <c r="C40" s="216"/>
+      <c r="D40" s="216"/>
+      <c r="E40" s="216"/>
+      <c r="F40" s="216"/>
+      <c r="G40" s="216"/>
+      <c r="H40" s="216"/>
+      <c r="I40" s="216"/>
+      <c r="J40" s="216"/>
+      <c r="K40" s="216"/>
+      <c r="L40" s="216"/>
+      <c r="M40" s="216"/>
+      <c r="N40" s="216"/>
+      <c r="O40" s="216"/>
+      <c r="P40" s="217"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B41" s="227"/>
-      <c r="C41" s="228"/>
-      <c r="D41" s="228"/>
-      <c r="E41" s="228"/>
-      <c r="F41" s="228"/>
-      <c r="G41" s="228"/>
-      <c r="H41" s="228"/>
-      <c r="I41" s="228"/>
-      <c r="J41" s="228"/>
-      <c r="K41" s="228"/>
-      <c r="L41" s="228"/>
-      <c r="M41" s="228"/>
-      <c r="N41" s="228"/>
-      <c r="O41" s="228"/>
-      <c r="P41" s="229"/>
+      <c r="B41" s="215"/>
+      <c r="C41" s="216"/>
+      <c r="D41" s="216"/>
+      <c r="E41" s="216"/>
+      <c r="F41" s="216"/>
+      <c r="G41" s="216"/>
+      <c r="H41" s="216"/>
+      <c r="I41" s="216"/>
+      <c r="J41" s="216"/>
+      <c r="K41" s="216"/>
+      <c r="L41" s="216"/>
+      <c r="M41" s="216"/>
+      <c r="N41" s="216"/>
+      <c r="O41" s="216"/>
+      <c r="P41" s="217"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B42" s="227"/>
-      <c r="C42" s="228"/>
-      <c r="D42" s="228"/>
-      <c r="E42" s="228"/>
-      <c r="F42" s="228"/>
-      <c r="G42" s="228"/>
-      <c r="H42" s="228"/>
-      <c r="I42" s="228"/>
-      <c r="J42" s="228"/>
-      <c r="K42" s="228"/>
-      <c r="L42" s="228"/>
-      <c r="M42" s="228"/>
-      <c r="N42" s="228"/>
-      <c r="O42" s="228"/>
-      <c r="P42" s="229"/>
+      <c r="B42" s="215"/>
+      <c r="C42" s="216"/>
+      <c r="D42" s="216"/>
+      <c r="E42" s="216"/>
+      <c r="F42" s="216"/>
+      <c r="G42" s="216"/>
+      <c r="H42" s="216"/>
+      <c r="I42" s="216"/>
+      <c r="J42" s="216"/>
+      <c r="K42" s="216"/>
+      <c r="L42" s="216"/>
+      <c r="M42" s="216"/>
+      <c r="N42" s="216"/>
+      <c r="O42" s="216"/>
+      <c r="P42" s="217"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B43" s="230"/>
-      <c r="C43" s="231"/>
-      <c r="D43" s="231"/>
-      <c r="E43" s="231"/>
-      <c r="F43" s="231"/>
-      <c r="G43" s="231"/>
-      <c r="H43" s="231"/>
-      <c r="I43" s="231"/>
-      <c r="J43" s="231"/>
-      <c r="K43" s="231"/>
-      <c r="L43" s="231"/>
-      <c r="M43" s="231"/>
-      <c r="N43" s="231"/>
-      <c r="O43" s="231"/>
-      <c r="P43" s="232"/>
+      <c r="B43" s="218"/>
+      <c r="C43" s="219"/>
+      <c r="D43" s="219"/>
+      <c r="E43" s="219"/>
+      <c r="F43" s="219"/>
+      <c r="G43" s="219"/>
+      <c r="H43" s="219"/>
+      <c r="I43" s="219"/>
+      <c r="J43" s="219"/>
+      <c r="K43" s="219"/>
+      <c r="L43" s="219"/>
+      <c r="M43" s="219"/>
+      <c r="N43" s="219"/>
+      <c r="O43" s="219"/>
+      <c r="P43" s="220"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B44" s="42"/>
@@ -56562,33 +56562,33 @@
       <c r="O51" s="126"/>
     </row>
     <row r="52" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="335" t="s">
+      <c r="B52" s="334" t="s">
         <v>178</v>
       </c>
-      <c r="C52" s="336"/>
-      <c r="D52" s="336"/>
-      <c r="E52" s="336"/>
-      <c r="F52" s="336"/>
-      <c r="G52" s="336"/>
-      <c r="H52" s="336"/>
-      <c r="I52" s="336"/>
-      <c r="J52" s="336"/>
-      <c r="K52" s="336"/>
-      <c r="L52" s="336"/>
-      <c r="M52" s="336"/>
-      <c r="N52" s="336"/>
-      <c r="O52" s="336"/>
-      <c r="P52" s="336"/>
-      <c r="Q52" s="337"/>
+      <c r="C52" s="335"/>
+      <c r="D52" s="335"/>
+      <c r="E52" s="335"/>
+      <c r="F52" s="335"/>
+      <c r="G52" s="335"/>
+      <c r="H52" s="335"/>
+      <c r="I52" s="335"/>
+      <c r="J52" s="335"/>
+      <c r="K52" s="335"/>
+      <c r="L52" s="335"/>
+      <c r="M52" s="335"/>
+      <c r="N52" s="335"/>
+      <c r="O52" s="335"/>
+      <c r="P52" s="335"/>
+      <c r="Q52" s="336"/>
     </row>
     <row r="53" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B53" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C53" s="220" t="s">
+      <c r="C53" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D53" s="220"/>
+      <c r="D53" s="221"/>
       <c r="E53" s="120" t="s">
         <v>3</v>
       </c>
@@ -56633,7 +56633,7 @@
       <c r="B54" s="237" t="s">
         <v>179</v>
       </c>
-      <c r="C54" s="320" t="s">
+      <c r="C54" s="333" t="s">
         <v>165</v>
       </c>
       <c r="D54" s="53" t="s">
@@ -56684,7 +56684,7 @@
     </row>
     <row r="55" spans="2:17" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="237"/>
-      <c r="C55" s="320"/>
+      <c r="C55" s="333"/>
       <c r="D55" s="53" t="s">
         <v>22</v>
       </c>
@@ -56732,33 +56732,33 @@
       </c>
     </row>
     <row r="56" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="335" t="s">
+      <c r="B56" s="334" t="s">
         <v>181</v>
       </c>
-      <c r="C56" s="336"/>
-      <c r="D56" s="336"/>
-      <c r="E56" s="336"/>
-      <c r="F56" s="336"/>
-      <c r="G56" s="336"/>
-      <c r="H56" s="336"/>
-      <c r="I56" s="336"/>
-      <c r="J56" s="336"/>
-      <c r="K56" s="336"/>
-      <c r="L56" s="336"/>
-      <c r="M56" s="336"/>
-      <c r="N56" s="336"/>
-      <c r="O56" s="336"/>
-      <c r="P56" s="336"/>
-      <c r="Q56" s="337"/>
+      <c r="C56" s="335"/>
+      <c r="D56" s="335"/>
+      <c r="E56" s="335"/>
+      <c r="F56" s="335"/>
+      <c r="G56" s="335"/>
+      <c r="H56" s="335"/>
+      <c r="I56" s="335"/>
+      <c r="J56" s="335"/>
+      <c r="K56" s="335"/>
+      <c r="L56" s="335"/>
+      <c r="M56" s="335"/>
+      <c r="N56" s="335"/>
+      <c r="O56" s="335"/>
+      <c r="P56" s="335"/>
+      <c r="Q56" s="336"/>
     </row>
     <row r="57" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="220" t="s">
+      <c r="C57" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="220"/>
+      <c r="D57" s="221"/>
       <c r="E57" s="120" t="s">
         <v>3</v>
       </c>
@@ -56803,7 +56803,7 @@
       <c r="B58" s="237" t="s">
         <v>71</v>
       </c>
-      <c r="C58" s="320" t="s">
+      <c r="C58" s="333" t="s">
         <v>165</v>
       </c>
       <c r="D58" s="53" t="s">
@@ -56848,13 +56848,13 @@
       <c r="P58" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q58" s="327" t="s">
+      <c r="Q58" s="342" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="59" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B59" s="237"/>
-      <c r="C59" s="320"/>
+      <c r="C59" s="333"/>
       <c r="D59" s="53" t="s">
         <v>22</v>
       </c>
@@ -56897,36 +56897,36 @@
       <c r="P59" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q59" s="328"/>
+      <c r="Q59" s="343"/>
     </row>
     <row r="60" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="324" t="s">
+      <c r="B60" s="339" t="s">
         <v>183</v>
       </c>
-      <c r="C60" s="325"/>
-      <c r="D60" s="325"/>
-      <c r="E60" s="325"/>
-      <c r="F60" s="325"/>
-      <c r="G60" s="325"/>
-      <c r="H60" s="325"/>
-      <c r="I60" s="325"/>
-      <c r="J60" s="325"/>
-      <c r="K60" s="325"/>
-      <c r="L60" s="325"/>
-      <c r="M60" s="325"/>
-      <c r="N60" s="325"/>
-      <c r="O60" s="325"/>
-      <c r="P60" s="325"/>
-      <c r="Q60" s="326"/>
+      <c r="C60" s="323"/>
+      <c r="D60" s="323"/>
+      <c r="E60" s="323"/>
+      <c r="F60" s="323"/>
+      <c r="G60" s="323"/>
+      <c r="H60" s="323"/>
+      <c r="I60" s="323"/>
+      <c r="J60" s="323"/>
+      <c r="K60" s="323"/>
+      <c r="L60" s="323"/>
+      <c r="M60" s="323"/>
+      <c r="N60" s="323"/>
+      <c r="O60" s="323"/>
+      <c r="P60" s="323"/>
+      <c r="Q60" s="340"/>
     </row>
     <row r="61" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B61" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C61" s="306" t="s">
+      <c r="C61" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D61" s="306"/>
+      <c r="D61" s="303"/>
       <c r="E61" s="8" t="s">
         <v>3</v>
       </c>
@@ -56968,10 +56968,10 @@
       </c>
     </row>
     <row r="62" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="332" t="s">
+      <c r="B62" s="341" t="s">
         <v>184</v>
       </c>
-      <c r="C62" s="320" t="s">
+      <c r="C62" s="333" t="s">
         <v>165</v>
       </c>
       <c r="D62" s="53" t="s">
@@ -57016,13 +57016,13 @@
       <c r="P62" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q62" s="327" t="s">
+      <c r="Q62" s="342" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="63" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B63" s="332"/>
-      <c r="C63" s="320"/>
+      <c r="B63" s="341"/>
+      <c r="C63" s="333"/>
       <c r="D63" s="53" t="s">
         <v>22</v>
       </c>
@@ -57065,36 +57065,36 @@
       <c r="P63" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q63" s="328"/>
+      <c r="Q63" s="343"/>
     </row>
     <row r="64" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="324" t="s">
+      <c r="B64" s="339" t="s">
         <v>185</v>
       </c>
-      <c r="C64" s="325"/>
-      <c r="D64" s="325"/>
-      <c r="E64" s="325"/>
-      <c r="F64" s="325"/>
-      <c r="G64" s="325"/>
-      <c r="H64" s="325"/>
-      <c r="I64" s="325"/>
-      <c r="J64" s="325"/>
-      <c r="K64" s="325"/>
-      <c r="L64" s="325"/>
-      <c r="M64" s="325"/>
-      <c r="N64" s="325"/>
-      <c r="O64" s="325"/>
-      <c r="P64" s="325"/>
-      <c r="Q64" s="326"/>
+      <c r="C64" s="323"/>
+      <c r="D64" s="323"/>
+      <c r="E64" s="323"/>
+      <c r="F64" s="323"/>
+      <c r="G64" s="323"/>
+      <c r="H64" s="323"/>
+      <c r="I64" s="323"/>
+      <c r="J64" s="323"/>
+      <c r="K64" s="323"/>
+      <c r="L64" s="323"/>
+      <c r="M64" s="323"/>
+      <c r="N64" s="323"/>
+      <c r="O64" s="323"/>
+      <c r="P64" s="323"/>
+      <c r="Q64" s="340"/>
     </row>
     <row r="65" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B65" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="306" t="s">
+      <c r="C65" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D65" s="306"/>
+      <c r="D65" s="303"/>
       <c r="E65" s="8" t="s">
         <v>3</v>
       </c>
@@ -57136,10 +57136,10 @@
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B66" s="332" t="s">
+      <c r="B66" s="341" t="s">
         <v>186</v>
       </c>
-      <c r="C66" s="320" t="s">
+      <c r="C66" s="333" t="s">
         <v>165</v>
       </c>
       <c r="D66" s="53" t="s">
@@ -57184,13 +57184,13 @@
       <c r="P66" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q66" s="329" t="s">
+      <c r="Q66" s="344" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B67" s="332"/>
-      <c r="C67" s="320"/>
+      <c r="B67" s="341"/>
+      <c r="C67" s="333"/>
       <c r="D67" s="53" t="s">
         <v>22</v>
       </c>
@@ -57233,36 +57233,36 @@
       <c r="P67" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q67" s="333"/>
+      <c r="Q67" s="345"/>
     </row>
     <row r="68" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="324" t="s">
+      <c r="B68" s="339" t="s">
         <v>188</v>
       </c>
-      <c r="C68" s="325"/>
-      <c r="D68" s="325"/>
-      <c r="E68" s="325"/>
-      <c r="F68" s="325"/>
-      <c r="G68" s="325"/>
-      <c r="H68" s="325"/>
-      <c r="I68" s="325"/>
-      <c r="J68" s="325"/>
-      <c r="K68" s="325"/>
-      <c r="L68" s="325"/>
-      <c r="M68" s="325"/>
-      <c r="N68" s="325"/>
-      <c r="O68" s="325"/>
-      <c r="P68" s="325"/>
-      <c r="Q68" s="326"/>
+      <c r="C68" s="323"/>
+      <c r="D68" s="323"/>
+      <c r="E68" s="323"/>
+      <c r="F68" s="323"/>
+      <c r="G68" s="323"/>
+      <c r="H68" s="323"/>
+      <c r="I68" s="323"/>
+      <c r="J68" s="323"/>
+      <c r="K68" s="323"/>
+      <c r="L68" s="323"/>
+      <c r="M68" s="323"/>
+      <c r="N68" s="323"/>
+      <c r="O68" s="323"/>
+      <c r="P68" s="323"/>
+      <c r="Q68" s="340"/>
     </row>
     <row r="69" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B69" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C69" s="306" t="s">
+      <c r="C69" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D69" s="306"/>
+      <c r="D69" s="303"/>
       <c r="E69" s="8" t="s">
         <v>3</v>
       </c>
@@ -57307,7 +57307,7 @@
       <c r="B70" s="237" t="s">
         <v>189</v>
       </c>
-      <c r="C70" s="320" t="s">
+      <c r="C70" s="333" t="s">
         <v>165</v>
       </c>
       <c r="D70" s="53" t="s">
@@ -57352,13 +57352,13 @@
       <c r="P70" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="Q70" s="329" t="s">
+      <c r="Q70" s="344" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B71" s="237"/>
-      <c r="C71" s="320"/>
+      <c r="C71" s="333"/>
       <c r="D71" s="53" t="s">
         <v>22</v>
       </c>
@@ -57401,36 +57401,36 @@
       <c r="P71" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="Q71" s="334"/>
+      <c r="Q71" s="346"/>
     </row>
     <row r="72" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="324" t="s">
+      <c r="B72" s="339" t="s">
         <v>190</v>
       </c>
-      <c r="C72" s="325"/>
-      <c r="D72" s="325"/>
-      <c r="E72" s="325"/>
-      <c r="F72" s="325"/>
-      <c r="G72" s="325"/>
-      <c r="H72" s="325"/>
-      <c r="I72" s="325"/>
-      <c r="J72" s="325"/>
-      <c r="K72" s="325"/>
-      <c r="L72" s="325"/>
-      <c r="M72" s="325"/>
-      <c r="N72" s="331"/>
-      <c r="O72" s="325"/>
-      <c r="P72" s="325"/>
-      <c r="Q72" s="326"/>
+      <c r="C72" s="323"/>
+      <c r="D72" s="323"/>
+      <c r="E72" s="323"/>
+      <c r="F72" s="323"/>
+      <c r="G72" s="323"/>
+      <c r="H72" s="323"/>
+      <c r="I72" s="323"/>
+      <c r="J72" s="323"/>
+      <c r="K72" s="323"/>
+      <c r="L72" s="323"/>
+      <c r="M72" s="323"/>
+      <c r="N72" s="332"/>
+      <c r="O72" s="323"/>
+      <c r="P72" s="323"/>
+      <c r="Q72" s="340"/>
     </row>
     <row r="73" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B73" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C73" s="306" t="s">
+      <c r="C73" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D73" s="306"/>
+      <c r="D73" s="303"/>
       <c r="E73" s="8" t="s">
         <v>3</v>
       </c>
@@ -57475,7 +57475,7 @@
       <c r="B74" s="237" t="s">
         <v>191</v>
       </c>
-      <c r="C74" s="320" t="s">
+      <c r="C74" s="333" t="s">
         <v>165</v>
       </c>
       <c r="D74" s="53" t="s">
@@ -57520,13 +57520,13 @@
       <c r="P74" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q74" s="329" t="s">
+      <c r="Q74" s="344" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="75" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="323"/>
-      <c r="C75" s="321"/>
+      <c r="B75" s="349"/>
+      <c r="C75" s="348"/>
       <c r="D75" s="90" t="s">
         <v>22</v>
       </c>
@@ -57569,15 +57569,15 @@
       <c r="P75" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="Q75" s="330"/>
+      <c r="Q75" s="347"/>
     </row>
     <row r="76" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="126"/>
       <c r="C76" s="126"/>
-      <c r="D76" s="322" t="s">
+      <c r="D76" s="329" t="s">
         <v>192</v>
       </c>
-      <c r="E76" s="322"/>
+      <c r="E76" s="329"/>
       <c r="F76" s="126"/>
       <c r="G76" s="126"/>
       <c r="H76" s="126"/>
@@ -57593,133 +57593,133 @@
       <c r="R76" s="126"/>
     </row>
     <row r="77" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B77" s="281" t="s">
+      <c r="B77" s="238" t="s">
         <v>32</v>
       </c>
-      <c r="C77" s="282"/>
-      <c r="D77" s="282"/>
-      <c r="E77" s="282"/>
-      <c r="F77" s="282"/>
-      <c r="G77" s="282"/>
-      <c r="H77" s="282"/>
-      <c r="I77" s="282"/>
-      <c r="J77" s="282"/>
-      <c r="K77" s="282"/>
-      <c r="L77" s="282"/>
-      <c r="M77" s="282"/>
-      <c r="N77" s="282"/>
-      <c r="O77" s="282"/>
-      <c r="P77" s="282"/>
-      <c r="Q77" s="282"/>
-      <c r="R77" s="283"/>
+      <c r="C77" s="239"/>
+      <c r="D77" s="239"/>
+      <c r="E77" s="239"/>
+      <c r="F77" s="239"/>
+      <c r="G77" s="239"/>
+      <c r="H77" s="239"/>
+      <c r="I77" s="239"/>
+      <c r="J77" s="239"/>
+      <c r="K77" s="239"/>
+      <c r="L77" s="239"/>
+      <c r="M77" s="239"/>
+      <c r="N77" s="239"/>
+      <c r="O77" s="239"/>
+      <c r="P77" s="239"/>
+      <c r="Q77" s="239"/>
+      <c r="R77" s="240"/>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B78" s="284" t="s">
+      <c r="B78" s="241" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="285"/>
-      <c r="D78" s="285"/>
-      <c r="E78" s="285"/>
-      <c r="F78" s="285"/>
-      <c r="G78" s="285"/>
-      <c r="H78" s="285"/>
-      <c r="I78" s="285"/>
-      <c r="J78" s="285"/>
-      <c r="K78" s="285"/>
-      <c r="L78" s="285"/>
-      <c r="M78" s="285"/>
-      <c r="N78" s="285"/>
-      <c r="O78" s="285"/>
-      <c r="P78" s="285"/>
-      <c r="Q78" s="285"/>
-      <c r="R78" s="286"/>
+      <c r="C78" s="242"/>
+      <c r="D78" s="242"/>
+      <c r="E78" s="242"/>
+      <c r="F78" s="242"/>
+      <c r="G78" s="242"/>
+      <c r="H78" s="242"/>
+      <c r="I78" s="242"/>
+      <c r="J78" s="242"/>
+      <c r="K78" s="242"/>
+      <c r="L78" s="242"/>
+      <c r="M78" s="242"/>
+      <c r="N78" s="242"/>
+      <c r="O78" s="242"/>
+      <c r="P78" s="242"/>
+      <c r="Q78" s="242"/>
+      <c r="R78" s="243"/>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B79" s="284"/>
-      <c r="C79" s="285"/>
-      <c r="D79" s="285"/>
-      <c r="E79" s="285"/>
-      <c r="F79" s="285"/>
-      <c r="G79" s="285"/>
-      <c r="H79" s="285"/>
-      <c r="I79" s="285"/>
-      <c r="J79" s="285"/>
-      <c r="K79" s="285"/>
-      <c r="L79" s="285"/>
-      <c r="M79" s="285"/>
-      <c r="N79" s="285"/>
-      <c r="O79" s="285"/>
-      <c r="P79" s="285"/>
-      <c r="Q79" s="285"/>
-      <c r="R79" s="286"/>
+      <c r="B79" s="241"/>
+      <c r="C79" s="242"/>
+      <c r="D79" s="242"/>
+      <c r="E79" s="242"/>
+      <c r="F79" s="242"/>
+      <c r="G79" s="242"/>
+      <c r="H79" s="242"/>
+      <c r="I79" s="242"/>
+      <c r="J79" s="242"/>
+      <c r="K79" s="242"/>
+      <c r="L79" s="242"/>
+      <c r="M79" s="242"/>
+      <c r="N79" s="242"/>
+      <c r="O79" s="242"/>
+      <c r="P79" s="242"/>
+      <c r="Q79" s="242"/>
+      <c r="R79" s="243"/>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B80" s="284"/>
-      <c r="C80" s="285"/>
-      <c r="D80" s="285"/>
-      <c r="E80" s="285"/>
-      <c r="F80" s="285"/>
-      <c r="G80" s="285"/>
-      <c r="H80" s="285"/>
-      <c r="I80" s="285"/>
-      <c r="J80" s="285"/>
-      <c r="K80" s="285"/>
-      <c r="L80" s="285"/>
-      <c r="M80" s="285"/>
-      <c r="N80" s="285"/>
-      <c r="O80" s="285"/>
-      <c r="P80" s="285"/>
-      <c r="Q80" s="285"/>
-      <c r="R80" s="286"/>
+      <c r="B80" s="241"/>
+      <c r="C80" s="242"/>
+      <c r="D80" s="242"/>
+      <c r="E80" s="242"/>
+      <c r="F80" s="242"/>
+      <c r="G80" s="242"/>
+      <c r="H80" s="242"/>
+      <c r="I80" s="242"/>
+      <c r="J80" s="242"/>
+      <c r="K80" s="242"/>
+      <c r="L80" s="242"/>
+      <c r="M80" s="242"/>
+      <c r="N80" s="242"/>
+      <c r="O80" s="242"/>
+      <c r="P80" s="242"/>
+      <c r="Q80" s="242"/>
+      <c r="R80" s="243"/>
     </row>
     <row r="81" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="287"/>
-      <c r="C81" s="288"/>
-      <c r="D81" s="288"/>
-      <c r="E81" s="288"/>
-      <c r="F81" s="288"/>
-      <c r="G81" s="288"/>
-      <c r="H81" s="288"/>
-      <c r="I81" s="288"/>
-      <c r="J81" s="288"/>
-      <c r="K81" s="288"/>
-      <c r="L81" s="288"/>
-      <c r="M81" s="288"/>
-      <c r="N81" s="288"/>
-      <c r="O81" s="288"/>
-      <c r="P81" s="288"/>
-      <c r="Q81" s="288"/>
-      <c r="R81" s="289"/>
+      <c r="B81" s="244"/>
+      <c r="C81" s="245"/>
+      <c r="D81" s="245"/>
+      <c r="E81" s="245"/>
+      <c r="F81" s="245"/>
+      <c r="G81" s="245"/>
+      <c r="H81" s="245"/>
+      <c r="I81" s="245"/>
+      <c r="J81" s="245"/>
+      <c r="K81" s="245"/>
+      <c r="L81" s="245"/>
+      <c r="M81" s="245"/>
+      <c r="N81" s="245"/>
+      <c r="O81" s="245"/>
+      <c r="P81" s="245"/>
+      <c r="Q81" s="245"/>
+      <c r="R81" s="246"/>
     </row>
     <row r="89" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B89" s="290" t="s">
+      <c r="B89" s="247" t="s">
         <v>193</v>
       </c>
-      <c r="C89" s="290"/>
-      <c r="D89" s="290"/>
-      <c r="E89" s="290"/>
-      <c r="F89" s="290"/>
-      <c r="G89" s="290"/>
-      <c r="H89" s="290"/>
-      <c r="I89" s="290"/>
-      <c r="J89" s="290"/>
-      <c r="K89" s="290"/>
-      <c r="L89" s="290"/>
-      <c r="M89" s="290"/>
-      <c r="N89" s="290"/>
-      <c r="O89" s="290"/>
-      <c r="P89" s="290"/>
-      <c r="Q89" s="290"/>
-      <c r="R89" s="290"/>
+      <c r="C89" s="247"/>
+      <c r="D89" s="247"/>
+      <c r="E89" s="247"/>
+      <c r="F89" s="247"/>
+      <c r="G89" s="247"/>
+      <c r="H89" s="247"/>
+      <c r="I89" s="247"/>
+      <c r="J89" s="247"/>
+      <c r="K89" s="247"/>
+      <c r="L89" s="247"/>
+      <c r="M89" s="247"/>
+      <c r="N89" s="247"/>
+      <c r="O89" s="247"/>
+      <c r="P89" s="247"/>
+      <c r="Q89" s="247"/>
+      <c r="R89" s="247"/>
     </row>
     <row r="90" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C90" s="306" t="s">
+      <c r="C90" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D90" s="306"/>
+      <c r="D90" s="303"/>
       <c r="E90" s="127" t="s">
         <v>125</v>
       </c>
@@ -57756,16 +57756,16 @@
       <c r="P90" s="124" t="s">
         <v>118</v>
       </c>
-      <c r="Q90" s="220" t="s">
+      <c r="Q90" s="221" t="s">
         <v>36</v>
       </c>
-      <c r="R90" s="220"/>
+      <c r="R90" s="221"/>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B91" s="217" t="s">
+      <c r="B91" s="224" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="242" t="s">
+      <c r="C91" s="248" t="s">
         <v>165</v>
       </c>
       <c r="D91" s="53" t="s">
@@ -57815,8 +57815,8 @@
       <c r="R91" s="249"/>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B92" s="217"/>
-      <c r="C92" s="242"/>
+      <c r="B92" s="224"/>
+      <c r="C92" s="248"/>
       <c r="D92" s="53" t="s">
         <v>22</v>
       </c>
@@ -57883,82 +57883,82 @@
       <c r="R94" s="6"/>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B95" s="252" t="s">
+      <c r="B95" s="281" t="s">
         <v>33</v>
       </c>
-      <c r="C95" s="252"/>
-      <c r="D95" s="252"/>
-      <c r="E95" s="252"/>
-      <c r="F95" s="252"/>
-      <c r="G95" s="252"/>
-      <c r="H95" s="252"/>
-      <c r="I95" s="252"/>
-      <c r="J95" s="252"/>
-      <c r="K95" s="252"/>
-      <c r="L95" s="252"/>
-      <c r="M95" s="252"/>
-      <c r="N95" s="252"/>
-      <c r="O95" s="252"/>
-      <c r="P95" s="252"/>
-      <c r="Q95" s="252"/>
-      <c r="R95" s="252"/>
+      <c r="C95" s="281"/>
+      <c r="D95" s="281"/>
+      <c r="E95" s="281"/>
+      <c r="F95" s="281"/>
+      <c r="G95" s="281"/>
+      <c r="H95" s="281"/>
+      <c r="I95" s="281"/>
+      <c r="J95" s="281"/>
+      <c r="K95" s="281"/>
+      <c r="L95" s="281"/>
+      <c r="M95" s="281"/>
+      <c r="N95" s="281"/>
+      <c r="O95" s="281"/>
+      <c r="P95" s="281"/>
+      <c r="Q95" s="281"/>
+      <c r="R95" s="281"/>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B96" s="252"/>
-      <c r="C96" s="252"/>
-      <c r="D96" s="252"/>
-      <c r="E96" s="252"/>
-      <c r="F96" s="252"/>
-      <c r="G96" s="252"/>
-      <c r="H96" s="252"/>
-      <c r="I96" s="252"/>
-      <c r="J96" s="252"/>
-      <c r="K96" s="252"/>
-      <c r="L96" s="252"/>
-      <c r="M96" s="252"/>
-      <c r="N96" s="252"/>
-      <c r="O96" s="252"/>
-      <c r="P96" s="252"/>
-      <c r="Q96" s="252"/>
-      <c r="R96" s="252"/>
+      <c r="B96" s="281"/>
+      <c r="C96" s="281"/>
+      <c r="D96" s="281"/>
+      <c r="E96" s="281"/>
+      <c r="F96" s="281"/>
+      <c r="G96" s="281"/>
+      <c r="H96" s="281"/>
+      <c r="I96" s="281"/>
+      <c r="J96" s="281"/>
+      <c r="K96" s="281"/>
+      <c r="L96" s="281"/>
+      <c r="M96" s="281"/>
+      <c r="N96" s="281"/>
+      <c r="O96" s="281"/>
+      <c r="P96" s="281"/>
+      <c r="Q96" s="281"/>
+      <c r="R96" s="281"/>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B97" s="252"/>
-      <c r="C97" s="252"/>
-      <c r="D97" s="252"/>
-      <c r="E97" s="252"/>
-      <c r="F97" s="252"/>
-      <c r="G97" s="252"/>
-      <c r="H97" s="252"/>
-      <c r="I97" s="252"/>
-      <c r="J97" s="252"/>
-      <c r="K97" s="252"/>
-      <c r="L97" s="252"/>
-      <c r="M97" s="252"/>
-      <c r="N97" s="252"/>
-      <c r="O97" s="252"/>
-      <c r="P97" s="252"/>
-      <c r="Q97" s="252"/>
-      <c r="R97" s="252"/>
+      <c r="B97" s="281"/>
+      <c r="C97" s="281"/>
+      <c r="D97" s="281"/>
+      <c r="E97" s="281"/>
+      <c r="F97" s="281"/>
+      <c r="G97" s="281"/>
+      <c r="H97" s="281"/>
+      <c r="I97" s="281"/>
+      <c r="J97" s="281"/>
+      <c r="K97" s="281"/>
+      <c r="L97" s="281"/>
+      <c r="M97" s="281"/>
+      <c r="N97" s="281"/>
+      <c r="O97" s="281"/>
+      <c r="P97" s="281"/>
+      <c r="Q97" s="281"/>
+      <c r="R97" s="281"/>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B98" s="252"/>
-      <c r="C98" s="252"/>
-      <c r="D98" s="252"/>
-      <c r="E98" s="252"/>
-      <c r="F98" s="252"/>
-      <c r="G98" s="252"/>
-      <c r="H98" s="252"/>
-      <c r="I98" s="252"/>
-      <c r="J98" s="252"/>
-      <c r="K98" s="252"/>
-      <c r="L98" s="252"/>
-      <c r="M98" s="252"/>
-      <c r="N98" s="252"/>
-      <c r="O98" s="252"/>
-      <c r="P98" s="252"/>
-      <c r="Q98" s="252"/>
-      <c r="R98" s="252"/>
+      <c r="B98" s="281"/>
+      <c r="C98" s="281"/>
+      <c r="D98" s="281"/>
+      <c r="E98" s="281"/>
+      <c r="F98" s="281"/>
+      <c r="G98" s="281"/>
+      <c r="H98" s="281"/>
+      <c r="I98" s="281"/>
+      <c r="J98" s="281"/>
+      <c r="K98" s="281"/>
+      <c r="L98" s="281"/>
+      <c r="M98" s="281"/>
+      <c r="N98" s="281"/>
+      <c r="O98" s="281"/>
+      <c r="P98" s="281"/>
+      <c r="Q98" s="281"/>
+      <c r="R98" s="281"/>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B99" s="122"/>
@@ -57998,34 +57998,34 @@
       <c r="C106" s="28"/>
     </row>
     <row r="107" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B107" s="218" t="s">
+      <c r="B107" s="222" t="s">
         <v>196</v>
       </c>
-      <c r="C107" s="219"/>
-      <c r="D107" s="219"/>
-      <c r="E107" s="219"/>
-      <c r="F107" s="219"/>
-      <c r="G107" s="219"/>
-      <c r="H107" s="219"/>
-      <c r="I107" s="219"/>
-      <c r="J107" s="219"/>
-      <c r="K107" s="219"/>
-      <c r="L107" s="219"/>
-      <c r="M107" s="219"/>
-      <c r="N107" s="219"/>
-      <c r="O107" s="219"/>
-      <c r="P107" s="219"/>
-      <c r="Q107" s="219"/>
-      <c r="R107" s="219"/>
+      <c r="C107" s="223"/>
+      <c r="D107" s="223"/>
+      <c r="E107" s="223"/>
+      <c r="F107" s="223"/>
+      <c r="G107" s="223"/>
+      <c r="H107" s="223"/>
+      <c r="I107" s="223"/>
+      <c r="J107" s="223"/>
+      <c r="K107" s="223"/>
+      <c r="L107" s="223"/>
+      <c r="M107" s="223"/>
+      <c r="N107" s="223"/>
+      <c r="O107" s="223"/>
+      <c r="P107" s="223"/>
+      <c r="Q107" s="223"/>
+      <c r="R107" s="223"/>
     </row>
     <row r="108" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B108" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C108" s="220" t="s">
+      <c r="C108" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D108" s="220"/>
+      <c r="D108" s="221"/>
       <c r="E108" s="8" t="s">
         <v>3</v>
       </c>
@@ -58070,10 +58070,10 @@
       </c>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B109" s="308" t="s">
+      <c r="B109" s="291" t="s">
         <v>98</v>
       </c>
-      <c r="C109" s="242" t="s">
+      <c r="C109" s="248" t="s">
         <v>165</v>
       </c>
       <c r="D109" s="53" t="s">
@@ -58125,8 +58125,8 @@
       </c>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B110" s="308"/>
-      <c r="C110" s="242"/>
+      <c r="B110" s="291"/>
+      <c r="C110" s="248"/>
       <c r="D110" s="53" t="s">
         <v>22</v>
       </c>
@@ -58176,10 +58176,10 @@
       </c>
     </row>
     <row r="111" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B111" s="308" t="s">
+      <c r="B111" s="291" t="s">
         <v>160</v>
       </c>
-      <c r="C111" s="242" t="s">
+      <c r="C111" s="248" t="s">
         <v>165</v>
       </c>
       <c r="D111" s="53" t="s">
@@ -58232,8 +58232,8 @@
       </c>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B112" s="308"/>
-      <c r="C112" s="242"/>
+      <c r="B112" s="291"/>
+      <c r="C112" s="248"/>
       <c r="D112" s="53" t="s">
         <v>22</v>
       </c>
@@ -58285,29 +58285,30 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="B32:Q32"/>
-    <mergeCell ref="B18:P18"/>
-    <mergeCell ref="B19:P22"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B9:P9"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B56:Q56"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B40:P43"/>
-    <mergeCell ref="B52:Q52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="P34:Q36"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B89:R89"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="B77:R77"/>
+    <mergeCell ref="B78:R81"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="B107:R107"/>
+    <mergeCell ref="B64:Q64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="Q58:Q59"/>
+    <mergeCell ref="B95:R98"/>
+    <mergeCell ref="Q90:R90"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="Q91:R92"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="C73:D73"/>
     <mergeCell ref="C57:D57"/>
     <mergeCell ref="B68:Q68"/>
     <mergeCell ref="C69:D69"/>
@@ -58324,30 +58325,29 @@
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="Q66:Q67"/>
     <mergeCell ref="Q70:Q71"/>
-    <mergeCell ref="B64:Q64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="Q58:Q59"/>
-    <mergeCell ref="B95:R98"/>
-    <mergeCell ref="Q90:R90"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="Q91:R92"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B89:R89"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="B77:R77"/>
-    <mergeCell ref="B78:R81"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="B107:R107"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B56:Q56"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B40:P43"/>
+    <mergeCell ref="B52:Q52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="P34:Q36"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B9:P9"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="B32:Q32"/>
+    <mergeCell ref="B18:P18"/>
+    <mergeCell ref="B19:P22"/>
+    <mergeCell ref="C33:D33"/>
   </mergeCells>
   <phoneticPr fontId="12" alignment="center"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -58390,33 +58390,33 @@
   </cols>
   <sheetData>
     <row r="8" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="218" t="s">
+      <c r="B8" s="222" t="s">
         <v>197</v>
       </c>
-      <c r="C8" s="219"/>
-      <c r="D8" s="219"/>
-      <c r="E8" s="219"/>
-      <c r="F8" s="219"/>
-      <c r="G8" s="219"/>
-      <c r="H8" s="219"/>
-      <c r="I8" s="219"/>
-      <c r="J8" s="219"/>
-      <c r="K8" s="219"/>
-      <c r="L8" s="219"/>
-      <c r="M8" s="219"/>
-      <c r="N8" s="219"/>
-      <c r="O8" s="219"/>
-      <c r="P8" s="219"/>
-      <c r="Q8" s="219"/>
+      <c r="C8" s="223"/>
+      <c r="D8" s="223"/>
+      <c r="E8" s="223"/>
+      <c r="F8" s="223"/>
+      <c r="G8" s="223"/>
+      <c r="H8" s="223"/>
+      <c r="I8" s="223"/>
+      <c r="J8" s="223"/>
+      <c r="K8" s="223"/>
+      <c r="L8" s="223"/>
+      <c r="M8" s="223"/>
+      <c r="N8" s="223"/>
+      <c r="O8" s="223"/>
+      <c r="P8" s="223"/>
+      <c r="Q8" s="223"/>
     </row>
     <row r="9" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B9" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="220" t="s">
+      <c r="C9" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="220"/>
+      <c r="D9" s="221"/>
       <c r="E9" s="120" t="s">
         <v>3</v>
       </c>
@@ -58458,10 +58458,10 @@
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="221" t="s">
+      <c r="B10" s="227" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="217" t="s">
+      <c r="C10" s="224" t="s">
         <v>110</v>
       </c>
       <c r="D10" s="117" t="s">
@@ -58510,8 +58510,8 @@
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="222"/>
-      <c r="C11" s="217"/>
+      <c r="B11" s="228"/>
+      <c r="C11" s="224"/>
       <c r="D11" s="117" t="s">
         <v>22</v>
       </c>
@@ -58610,34 +58610,34 @@
       </c>
     </row>
     <row r="13" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="218" t="s">
+      <c r="B13" s="222" t="s">
         <v>199</v>
       </c>
-      <c r="C13" s="219"/>
-      <c r="D13" s="219"/>
-      <c r="E13" s="219"/>
-      <c r="F13" s="219"/>
-      <c r="G13" s="219"/>
-      <c r="H13" s="219"/>
-      <c r="I13" s="219"/>
-      <c r="J13" s="219"/>
-      <c r="K13" s="219"/>
-      <c r="L13" s="219"/>
-      <c r="M13" s="219"/>
-      <c r="N13" s="219"/>
-      <c r="O13" s="219"/>
-      <c r="P13" s="219"/>
-      <c r="Q13" s="219"/>
-      <c r="R13" s="219"/>
+      <c r="C13" s="223"/>
+      <c r="D13" s="223"/>
+      <c r="E13" s="223"/>
+      <c r="F13" s="223"/>
+      <c r="G13" s="223"/>
+      <c r="H13" s="223"/>
+      <c r="I13" s="223"/>
+      <c r="J13" s="223"/>
+      <c r="K13" s="223"/>
+      <c r="L13" s="223"/>
+      <c r="M13" s="223"/>
+      <c r="N13" s="223"/>
+      <c r="O13" s="223"/>
+      <c r="P13" s="223"/>
+      <c r="Q13" s="223"/>
+      <c r="R13" s="223"/>
     </row>
     <row r="14" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B14" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="220" t="s">
+      <c r="C14" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="220"/>
+      <c r="D14" s="221"/>
       <c r="E14" s="120" t="s">
         <v>3</v>
       </c>
@@ -58685,10 +58685,10 @@
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="217" t="s">
+      <c r="B15" s="224" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="217" t="s">
+      <c r="C15" s="224" t="s">
         <v>165</v>
       </c>
       <c r="D15" s="117" t="s">
@@ -58743,8 +58743,8 @@
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B16" s="217"/>
-      <c r="C16" s="217"/>
+      <c r="B16" s="224"/>
+      <c r="C16" s="224"/>
       <c r="D16" s="117" t="s">
         <v>22</v>
       </c>
@@ -58797,33 +58797,33 @@
       </c>
     </row>
     <row r="17" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="225" t="s">
+      <c r="B17" s="231" t="s">
         <v>203</v>
       </c>
-      <c r="C17" s="226"/>
-      <c r="D17" s="226"/>
-      <c r="E17" s="226"/>
-      <c r="F17" s="226"/>
-      <c r="G17" s="226"/>
-      <c r="H17" s="226"/>
-      <c r="I17" s="226"/>
-      <c r="J17" s="226"/>
-      <c r="K17" s="226"/>
-      <c r="L17" s="226"/>
-      <c r="M17" s="226"/>
-      <c r="N17" s="226"/>
-      <c r="O17" s="226"/>
-      <c r="P17" s="226"/>
-      <c r="Q17" s="226"/>
+      <c r="C17" s="232"/>
+      <c r="D17" s="232"/>
+      <c r="E17" s="232"/>
+      <c r="F17" s="232"/>
+      <c r="G17" s="232"/>
+      <c r="H17" s="232"/>
+      <c r="I17" s="232"/>
+      <c r="J17" s="232"/>
+      <c r="K17" s="232"/>
+      <c r="L17" s="232"/>
+      <c r="M17" s="232"/>
+      <c r="N17" s="232"/>
+      <c r="O17" s="232"/>
+      <c r="P17" s="232"/>
+      <c r="Q17" s="232"/>
     </row>
     <row r="18" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B18" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="220" t="s">
+      <c r="C18" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="220"/>
+      <c r="D18" s="221"/>
       <c r="E18" s="120" t="s">
         <v>3</v>
       </c>
@@ -58857,16 +58857,16 @@
       <c r="O18" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="P18" s="223" t="s">
+      <c r="P18" s="229" t="s">
         <v>137</v>
       </c>
-      <c r="Q18" s="224"/>
+      <c r="Q18" s="230"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="217" t="s">
+      <c r="B19" s="224" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="217" t="s">
+      <c r="C19" s="224" t="s">
         <v>204</v>
       </c>
       <c r="D19" s="117" t="s">
@@ -58913,8 +58913,8 @@
       <c r="Q19" s="53"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="217"/>
-      <c r="C20" s="217"/>
+      <c r="B20" s="224"/>
+      <c r="C20" s="224"/>
       <c r="D20" s="117" t="s">
         <v>22</v>
       </c>
@@ -58959,32 +58959,32 @@
       <c r="Q20" s="53"/>
     </row>
     <row r="21" spans="2:17" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="215" t="s">
+      <c r="B21" s="233" t="s">
         <v>206</v>
       </c>
-      <c r="C21" s="216"/>
-      <c r="D21" s="216"/>
-      <c r="E21" s="216"/>
-      <c r="F21" s="216"/>
-      <c r="G21" s="216"/>
-      <c r="H21" s="216"/>
-      <c r="I21" s="216"/>
-      <c r="J21" s="216"/>
-      <c r="K21" s="216"/>
-      <c r="L21" s="216"/>
-      <c r="M21" s="216"/>
-      <c r="N21" s="216"/>
-      <c r="O21" s="216"/>
+      <c r="C21" s="234"/>
+      <c r="D21" s="234"/>
+      <c r="E21" s="234"/>
+      <c r="F21" s="234"/>
+      <c r="G21" s="234"/>
+      <c r="H21" s="234"/>
+      <c r="I21" s="234"/>
+      <c r="J21" s="234"/>
+      <c r="K21" s="234"/>
+      <c r="L21" s="234"/>
+      <c r="M21" s="234"/>
+      <c r="N21" s="234"/>
+      <c r="O21" s="234"/>
       <c r="P21" s="207"/>
     </row>
     <row r="22" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B22" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="220" t="s">
+      <c r="C22" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="220"/>
+      <c r="D22" s="221"/>
       <c r="E22" s="120" t="s">
         <v>3</v>
       </c>
@@ -59018,14 +59018,14 @@
       <c r="O22" s="120" t="s">
         <v>137</v>
       </c>
-      <c r="P22" s="233"/>
-      <c r="Q22" s="234"/>
+      <c r="P22" s="225"/>
+      <c r="Q22" s="226"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B23" s="217" t="s">
+      <c r="B23" s="224" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="217" t="s">
+      <c r="C23" s="224" t="s">
         <v>207</v>
       </c>
       <c r="D23" s="117" t="s">
@@ -59070,8 +59070,8 @@
       <c r="P23" s="205"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B24" s="217"/>
-      <c r="C24" s="217"/>
+      <c r="B24" s="224"/>
+      <c r="C24" s="224"/>
       <c r="D24" s="117" t="s">
         <v>22</v>
       </c>
@@ -59114,32 +59114,32 @@
       <c r="P24" s="205"/>
     </row>
     <row r="25" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B25" s="218" t="s">
+      <c r="B25" s="222" t="s">
         <v>209</v>
       </c>
-      <c r="C25" s="219"/>
-      <c r="D25" s="219"/>
-      <c r="E25" s="219"/>
-      <c r="F25" s="219"/>
-      <c r="G25" s="219"/>
-      <c r="H25" s="219"/>
-      <c r="I25" s="219"/>
-      <c r="J25" s="219"/>
-      <c r="K25" s="219"/>
-      <c r="L25" s="219"/>
-      <c r="M25" s="219"/>
-      <c r="N25" s="219"/>
-      <c r="O25" s="219"/>
+      <c r="C25" s="223"/>
+      <c r="D25" s="223"/>
+      <c r="E25" s="223"/>
+      <c r="F25" s="223"/>
+      <c r="G25" s="223"/>
+      <c r="H25" s="223"/>
+      <c r="I25" s="223"/>
+      <c r="J25" s="223"/>
+      <c r="K25" s="223"/>
+      <c r="L25" s="223"/>
+      <c r="M25" s="223"/>
+      <c r="N25" s="223"/>
+      <c r="O25" s="223"/>
       <c r="P25" s="61"/>
     </row>
     <row r="26" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B26" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C26" s="220" t="s">
+      <c r="C26" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="220"/>
+      <c r="D26" s="221"/>
       <c r="E26" s="120" t="s">
         <v>3</v>
       </c>
@@ -59176,10 +59176,10 @@
       <c r="P26" s="61"/>
     </row>
     <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="217" t="s">
+      <c r="B27" s="224" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="217" t="s">
+      <c r="C27" s="224" t="s">
         <v>114</v>
       </c>
       <c r="D27" s="117" t="s">
@@ -59225,8 +59225,8 @@
       <c r="P27" s="61"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B28" s="217"/>
-      <c r="C28" s="217"/>
+      <c r="B28" s="224"/>
+      <c r="C28" s="224"/>
       <c r="D28" s="117" t="s">
         <v>22</v>
       </c>
@@ -59290,78 +59290,78 @@
       <c r="Q30" s="7"/>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B31" s="227" t="s">
+      <c r="B31" s="215" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="228"/>
-      <c r="D31" s="228"/>
-      <c r="E31" s="228"/>
-      <c r="F31" s="228"/>
-      <c r="G31" s="228"/>
-      <c r="H31" s="228"/>
-      <c r="I31" s="228"/>
-      <c r="J31" s="228"/>
-      <c r="K31" s="228"/>
-      <c r="L31" s="228"/>
-      <c r="M31" s="228"/>
-      <c r="N31" s="228"/>
-      <c r="O31" s="228"/>
-      <c r="P31" s="228"/>
-      <c r="Q31" s="229"/>
+      <c r="C31" s="216"/>
+      <c r="D31" s="216"/>
+      <c r="E31" s="216"/>
+      <c r="F31" s="216"/>
+      <c r="G31" s="216"/>
+      <c r="H31" s="216"/>
+      <c r="I31" s="216"/>
+      <c r="J31" s="216"/>
+      <c r="K31" s="216"/>
+      <c r="L31" s="216"/>
+      <c r="M31" s="216"/>
+      <c r="N31" s="216"/>
+      <c r="O31" s="216"/>
+      <c r="P31" s="216"/>
+      <c r="Q31" s="217"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B32" s="227"/>
-      <c r="C32" s="228"/>
-      <c r="D32" s="228"/>
-      <c r="E32" s="228"/>
-      <c r="F32" s="228"/>
-      <c r="G32" s="228"/>
-      <c r="H32" s="228"/>
-      <c r="I32" s="228"/>
-      <c r="J32" s="228"/>
-      <c r="K32" s="228"/>
-      <c r="L32" s="228"/>
-      <c r="M32" s="228"/>
-      <c r="N32" s="228"/>
-      <c r="O32" s="228"/>
-      <c r="P32" s="228"/>
-      <c r="Q32" s="229"/>
+      <c r="B32" s="215"/>
+      <c r="C32" s="216"/>
+      <c r="D32" s="216"/>
+      <c r="E32" s="216"/>
+      <c r="F32" s="216"/>
+      <c r="G32" s="216"/>
+      <c r="H32" s="216"/>
+      <c r="I32" s="216"/>
+      <c r="J32" s="216"/>
+      <c r="K32" s="216"/>
+      <c r="L32" s="216"/>
+      <c r="M32" s="216"/>
+      <c r="N32" s="216"/>
+      <c r="O32" s="216"/>
+      <c r="P32" s="216"/>
+      <c r="Q32" s="217"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B33" s="227"/>
-      <c r="C33" s="228"/>
-      <c r="D33" s="228"/>
-      <c r="E33" s="228"/>
-      <c r="F33" s="228"/>
-      <c r="G33" s="228"/>
-      <c r="H33" s="228"/>
-      <c r="I33" s="228"/>
-      <c r="J33" s="228"/>
-      <c r="K33" s="228"/>
-      <c r="L33" s="228"/>
-      <c r="M33" s="228"/>
-      <c r="N33" s="228"/>
-      <c r="O33" s="228"/>
-      <c r="P33" s="228"/>
-      <c r="Q33" s="229"/>
+      <c r="B33" s="215"/>
+      <c r="C33" s="216"/>
+      <c r="D33" s="216"/>
+      <c r="E33" s="216"/>
+      <c r="F33" s="216"/>
+      <c r="G33" s="216"/>
+      <c r="H33" s="216"/>
+      <c r="I33" s="216"/>
+      <c r="J33" s="216"/>
+      <c r="K33" s="216"/>
+      <c r="L33" s="216"/>
+      <c r="M33" s="216"/>
+      <c r="N33" s="216"/>
+      <c r="O33" s="216"/>
+      <c r="P33" s="216"/>
+      <c r="Q33" s="217"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B34" s="230"/>
-      <c r="C34" s="231"/>
-      <c r="D34" s="231"/>
-      <c r="E34" s="231"/>
-      <c r="F34" s="231"/>
-      <c r="G34" s="231"/>
-      <c r="H34" s="231"/>
-      <c r="I34" s="231"/>
-      <c r="J34" s="231"/>
-      <c r="K34" s="231"/>
-      <c r="L34" s="231"/>
-      <c r="M34" s="231"/>
-      <c r="N34" s="231"/>
-      <c r="O34" s="231"/>
-      <c r="P34" s="231"/>
-      <c r="Q34" s="232"/>
+      <c r="B34" s="218"/>
+      <c r="C34" s="219"/>
+      <c r="D34" s="219"/>
+      <c r="E34" s="219"/>
+      <c r="F34" s="219"/>
+      <c r="G34" s="219"/>
+      <c r="H34" s="219"/>
+      <c r="I34" s="219"/>
+      <c r="J34" s="219"/>
+      <c r="K34" s="219"/>
+      <c r="L34" s="219"/>
+      <c r="M34" s="219"/>
+      <c r="N34" s="219"/>
+      <c r="O34" s="219"/>
+      <c r="P34" s="219"/>
+      <c r="Q34" s="220"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B35" s="35"/>
@@ -59491,6 +59491,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B21:O21"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B8:Q8"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B13:R13"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="B17:Q17"/>
     <mergeCell ref="B31:Q34"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="B25:O25"/>
@@ -59500,20 +59514,6 @@
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="B8:Q8"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B13:R13"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="B17:Q17"/>
-    <mergeCell ref="B21:O21"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="B19:B20"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -59700,10 +59700,10 @@
       <c r="B10" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="362" t="s">
+      <c r="C10" s="350" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="362"/>
+      <c r="D10" s="350"/>
       <c r="E10" s="15" t="s">
         <v>3</v>
       </c>
@@ -59742,10 +59742,10 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="358" t="s">
+      <c r="B11" s="351" t="s">
         <v>211</v>
       </c>
-      <c r="C11" s="360" t="s">
+      <c r="C11" s="354" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="45" t="s">
@@ -59791,8 +59791,8 @@
       </c>
     </row>
     <row r="12" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="363"/>
-      <c r="C12" s="360"/>
+      <c r="B12" s="352"/>
+      <c r="C12" s="354"/>
       <c r="D12" s="45" t="s">
         <v>22</v>
       </c>
@@ -59836,8 +59836,8 @@
       </c>
     </row>
     <row r="13" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="363"/>
-      <c r="C13" s="360" t="s">
+      <c r="B13" s="352"/>
+      <c r="C13" s="354" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="45" t="s">
@@ -59883,8 +59883,8 @@
       </c>
     </row>
     <row r="14" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="363"/>
-      <c r="C14" s="360"/>
+      <c r="B14" s="352"/>
+      <c r="C14" s="354"/>
       <c r="D14" s="45" t="s">
         <v>22</v>
       </c>
@@ -59928,8 +59928,8 @@
       </c>
     </row>
     <row r="15" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="363"/>
-      <c r="C15" s="360" t="s">
+      <c r="B15" s="352"/>
+      <c r="C15" s="354" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="45" t="s">
@@ -59975,8 +59975,8 @@
       </c>
     </row>
     <row r="16" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="363"/>
-      <c r="C16" s="360"/>
+      <c r="B16" s="352"/>
+      <c r="C16" s="354"/>
       <c r="D16" s="45" t="s">
         <v>22</v>
       </c>
@@ -60020,8 +60020,8 @@
       </c>
     </row>
     <row r="17" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="363"/>
-      <c r="C17" s="360" t="s">
+      <c r="B17" s="352"/>
+      <c r="C17" s="354" t="s">
         <v>29</v>
       </c>
       <c r="D17" s="45" t="s">
@@ -60067,8 +60067,8 @@
       </c>
     </row>
     <row r="18" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="363"/>
-      <c r="C18" s="360"/>
+      <c r="B18" s="352"/>
+      <c r="C18" s="354"/>
       <c r="D18" s="45" t="s">
         <v>22</v>
       </c>
@@ -60112,8 +60112,8 @@
       </c>
     </row>
     <row r="19" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="363"/>
-      <c r="C19" s="360" t="s">
+      <c r="B19" s="352"/>
+      <c r="C19" s="354" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="45" t="s">
@@ -60159,8 +60159,8 @@
       </c>
     </row>
     <row r="20" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="359"/>
-      <c r="C20" s="360"/>
+      <c r="B20" s="353"/>
+      <c r="C20" s="354"/>
       <c r="D20" s="45" t="s">
         <v>22</v>
       </c>
@@ -60204,10 +60204,10 @@
       </c>
     </row>
     <row r="21" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="358" t="s">
+      <c r="B21" s="351" t="s">
         <v>216</v>
       </c>
-      <c r="C21" s="360" t="s">
+      <c r="C21" s="354" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="45" t="s">
@@ -60253,8 +60253,8 @@
       </c>
     </row>
     <row r="22" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="359"/>
-      <c r="C22" s="360"/>
+      <c r="B22" s="353"/>
+      <c r="C22" s="354"/>
       <c r="D22" s="45" t="s">
         <v>22</v>
       </c>
@@ -60298,10 +60298,10 @@
       </c>
     </row>
     <row r="23" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B23" s="358" t="s">
+      <c r="B23" s="351" t="s">
         <v>217</v>
       </c>
-      <c r="C23" s="360" t="s">
+      <c r="C23" s="354" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="45" t="s">
@@ -60347,8 +60347,8 @@
       </c>
     </row>
     <row r="24" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="359"/>
-      <c r="C24" s="360"/>
+      <c r="B24" s="353"/>
+      <c r="C24" s="354"/>
       <c r="D24" s="45" t="s">
         <v>22</v>
       </c>
@@ -60395,7 +60395,7 @@
       <c r="B25" s="237" t="s">
         <v>219</v>
       </c>
-      <c r="C25" s="217" t="s">
+      <c r="C25" s="224" t="s">
         <v>29</v>
       </c>
       <c r="D25" s="40" t="s">
@@ -60442,7 +60442,7 @@
     </row>
     <row r="26" spans="2:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="B26" s="237"/>
-      <c r="C26" s="217"/>
+      <c r="C26" s="224"/>
       <c r="D26" s="40" t="s">
         <v>22</v>
       </c>
@@ -60486,8 +60486,8 @@
       </c>
     </row>
     <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="323"/>
-      <c r="C27" s="361"/>
+      <c r="B27" s="349"/>
+      <c r="C27" s="363"/>
       <c r="D27" s="84" t="s">
         <v>17</v>
       </c>
@@ -60547,103 +60547,96 @@
       <c r="O28" s="28"/>
     </row>
     <row r="29" spans="2:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="350" t="s">
+      <c r="B29" s="355" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="351"/>
-      <c r="D29" s="351"/>
-      <c r="E29" s="351"/>
-      <c r="F29" s="351"/>
-      <c r="G29" s="351"/>
-      <c r="H29" s="351"/>
-      <c r="I29" s="351"/>
-      <c r="J29" s="351"/>
-      <c r="K29" s="351"/>
-      <c r="L29" s="351"/>
-      <c r="M29" s="351"/>
-      <c r="N29" s="351"/>
-      <c r="O29" s="351"/>
-      <c r="P29" s="352"/>
+      <c r="C29" s="356"/>
+      <c r="D29" s="356"/>
+      <c r="E29" s="356"/>
+      <c r="F29" s="356"/>
+      <c r="G29" s="356"/>
+      <c r="H29" s="356"/>
+      <c r="I29" s="356"/>
+      <c r="J29" s="356"/>
+      <c r="K29" s="356"/>
+      <c r="L29" s="356"/>
+      <c r="M29" s="356"/>
+      <c r="N29" s="356"/>
+      <c r="O29" s="356"/>
+      <c r="P29" s="357"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B30" s="353" t="s">
+      <c r="B30" s="358" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="228"/>
-      <c r="D30" s="228"/>
-      <c r="E30" s="228"/>
-      <c r="F30" s="228"/>
-      <c r="G30" s="228"/>
-      <c r="H30" s="228"/>
-      <c r="I30" s="228"/>
-      <c r="J30" s="228"/>
-      <c r="K30" s="228"/>
-      <c r="L30" s="228"/>
-      <c r="M30" s="228"/>
-      <c r="N30" s="228"/>
-      <c r="O30" s="228"/>
-      <c r="P30" s="354"/>
+      <c r="C30" s="216"/>
+      <c r="D30" s="216"/>
+      <c r="E30" s="216"/>
+      <c r="F30" s="216"/>
+      <c r="G30" s="216"/>
+      <c r="H30" s="216"/>
+      <c r="I30" s="216"/>
+      <c r="J30" s="216"/>
+      <c r="K30" s="216"/>
+      <c r="L30" s="216"/>
+      <c r="M30" s="216"/>
+      <c r="N30" s="216"/>
+      <c r="O30" s="216"/>
+      <c r="P30" s="359"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="353"/>
-      <c r="C31" s="228"/>
-      <c r="D31" s="228"/>
-      <c r="E31" s="228"/>
-      <c r="F31" s="228"/>
-      <c r="G31" s="228"/>
-      <c r="H31" s="228"/>
-      <c r="I31" s="228"/>
-      <c r="J31" s="228"/>
-      <c r="K31" s="228"/>
-      <c r="L31" s="228"/>
-      <c r="M31" s="228"/>
-      <c r="N31" s="228"/>
-      <c r="O31" s="228"/>
-      <c r="P31" s="354"/>
+      <c r="B31" s="358"/>
+      <c r="C31" s="216"/>
+      <c r="D31" s="216"/>
+      <c r="E31" s="216"/>
+      <c r="F31" s="216"/>
+      <c r="G31" s="216"/>
+      <c r="H31" s="216"/>
+      <c r="I31" s="216"/>
+      <c r="J31" s="216"/>
+      <c r="K31" s="216"/>
+      <c r="L31" s="216"/>
+      <c r="M31" s="216"/>
+      <c r="N31" s="216"/>
+      <c r="O31" s="216"/>
+      <c r="P31" s="359"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B32" s="353"/>
-      <c r="C32" s="228"/>
-      <c r="D32" s="228"/>
-      <c r="E32" s="228"/>
-      <c r="F32" s="228"/>
-      <c r="G32" s="228"/>
-      <c r="H32" s="228"/>
-      <c r="I32" s="228"/>
-      <c r="J32" s="228"/>
-      <c r="K32" s="228"/>
-      <c r="L32" s="228"/>
-      <c r="M32" s="228"/>
-      <c r="N32" s="228"/>
-      <c r="O32" s="228"/>
-      <c r="P32" s="354"/>
+      <c r="B32" s="358"/>
+      <c r="C32" s="216"/>
+      <c r="D32" s="216"/>
+      <c r="E32" s="216"/>
+      <c r="F32" s="216"/>
+      <c r="G32" s="216"/>
+      <c r="H32" s="216"/>
+      <c r="I32" s="216"/>
+      <c r="J32" s="216"/>
+      <c r="K32" s="216"/>
+      <c r="L32" s="216"/>
+      <c r="M32" s="216"/>
+      <c r="N32" s="216"/>
+      <c r="O32" s="216"/>
+      <c r="P32" s="359"/>
     </row>
     <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="355"/>
-      <c r="C33" s="356"/>
-      <c r="D33" s="356"/>
-      <c r="E33" s="356"/>
-      <c r="F33" s="356"/>
-      <c r="G33" s="356"/>
-      <c r="H33" s="356"/>
-      <c r="I33" s="356"/>
-      <c r="J33" s="356"/>
-      <c r="K33" s="356"/>
-      <c r="L33" s="356"/>
-      <c r="M33" s="356"/>
-      <c r="N33" s="356"/>
-      <c r="O33" s="356"/>
-      <c r="P33" s="357"/>
+      <c r="B33" s="360"/>
+      <c r="C33" s="361"/>
+      <c r="D33" s="361"/>
+      <c r="E33" s="361"/>
+      <c r="F33" s="361"/>
+      <c r="G33" s="361"/>
+      <c r="H33" s="361"/>
+      <c r="I33" s="361"/>
+      <c r="J33" s="361"/>
+      <c r="K33" s="361"/>
+      <c r="L33" s="361"/>
+      <c r="M33" s="361"/>
+      <c r="N33" s="361"/>
+      <c r="O33" s="361"/>
+      <c r="P33" s="362"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B20"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
     <mergeCell ref="B29:P29"/>
     <mergeCell ref="B30:P33"/>
     <mergeCell ref="B21:B22"/>
@@ -60652,6 +60645,13 @@
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="B25:B27"/>
     <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B20"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="67" orientation="landscape" r:id="rId1"/>
@@ -60660,15 +60660,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BF631F92D611394D900040A4BC36CE07" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="711a2ec75ffd0c152903cfa2dedf38be">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8bf418b7-79e0-4993-aa07-d31c53a64380" xmlns:ns3="268ad1c4-fabf-4dd0-b894-8fd5403102c0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0628c710989f2757c815e19c03677863" ns2:_="" ns3:_="">
     <xsd:import namespace="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
@@ -60891,6 +60882,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -60903,14 +60903,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A722593-7143-4ACD-9A00-2A0E70214590}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -60929,6 +60921,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
   <ds:schemaRefs>
